--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -707,12 +707,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4569,7 +4569,7 @@
         <v>34</v>
       </c>
       <c r="N62">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="O62" s="17">
         <v>1990000</v>
@@ -4601,7 +4601,7 @@
         <v>2</v>
       </c>
       <c r="I63" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="J63" s="19">
         <v>-1</v>
@@ -4616,7 +4616,7 @@
         <v>34</v>
       </c>
       <c r="N63">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="O63" s="17">
         <v>1990000</v>
@@ -4648,7 +4648,7 @@
         <v>3</v>
       </c>
       <c r="I64" s="2">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="J64" s="19">
         <v>-1</v>
@@ -4663,7 +4663,7 @@
         <v>34</v>
       </c>
       <c r="N64">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="O64" s="17">
         <v>1990000</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="114">
   <si>
     <t>sid</t>
   </si>
@@ -474,6 +474,9 @@
   </si>
   <si>
     <t>4:4</t>
+  </si>
+  <si>
+    <t>1:0</t>
   </si>
   <si>
     <t>俄罗斯轮盘</t>
@@ -707,12 +710,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4569,7 +4572,7 @@
         <v>34</v>
       </c>
       <c r="N62">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="O62" s="17">
         <v>1990000</v>
@@ -4601,7 +4604,7 @@
         <v>2</v>
       </c>
       <c r="I63" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="J63" s="19">
         <v>-1</v>
@@ -4616,7 +4619,7 @@
         <v>34</v>
       </c>
       <c r="N63">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="O63" s="17">
         <v>1990000</v>
@@ -4648,7 +4651,7 @@
         <v>3</v>
       </c>
       <c r="I64" s="2">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="J64" s="19">
         <v>-1</v>
@@ -4663,7 +4666,7 @@
         <v>34</v>
       </c>
       <c r="N64">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="O64" s="17">
         <v>1990000</v>
@@ -6450,7 +6453,7 @@
         <v>105</v>
       </c>
       <c r="M101" s="31" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="N101" s="26">
         <v>3000</v>
@@ -6498,7 +6501,7 @@
         <v>105</v>
       </c>
       <c r="M102" s="31" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="N102" s="26">
         <v>6000</v>
@@ -6546,7 +6549,7 @@
         <v>105</v>
       </c>
       <c r="M103" s="31" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="N103" s="26">
         <v>12000</v>
@@ -6567,13 +6570,13 @@
         <v>2</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E104" s="15">
         <v>201200001</v>
       </c>
       <c r="F104" s="25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>32</v>
@@ -6615,13 +6618,13 @@
         <v>2</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E105" s="15">
         <v>201200001</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>35</v>
@@ -6663,13 +6666,13 @@
         <v>2</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E106" s="15">
         <v>201200001</v>
       </c>
       <c r="F106" s="25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>36</v>
@@ -6720,7 +6723,7 @@
         <v>78</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H107" s="19">
         <v>10</v>
@@ -6735,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="L107" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M107" s="19">
         <v>0</v>
@@ -6768,7 +6771,7 @@
         <v>78</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H108" s="19">
         <v>11</v>
@@ -6783,7 +6786,7 @@
         <v>0</v>
       </c>
       <c r="L108" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M108" s="19">
         <v>0</v>
@@ -6816,7 +6819,7 @@
         <v>78</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H109" s="19">
         <v>12</v>
@@ -6831,7 +6834,7 @@
         <v>0</v>
       </c>
       <c r="L109" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M109" s="19">
         <v>0</v>
@@ -6864,7 +6867,7 @@
         <v>80</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H110" s="19">
         <v>10</v>
@@ -6879,7 +6882,7 @@
         <v>0</v>
       </c>
       <c r="L110" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M110" s="19">
         <v>0</v>
@@ -6912,7 +6915,7 @@
         <v>80</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H111" s="19">
         <v>11</v>
@@ -6927,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M111" s="19">
         <v>0</v>
@@ -6960,7 +6963,7 @@
         <v>80</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H112" s="19">
         <v>12</v>
@@ -6975,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M112" s="19">
         <v>0</v>
@@ -7008,7 +7011,7 @@
         <v>82</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H113" s="19">
         <v>10</v>
@@ -7023,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="L113" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M113" s="19">
         <v>0</v>
@@ -7056,7 +7059,7 @@
         <v>82</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H114" s="19">
         <v>11</v>
@@ -7071,7 +7074,7 @@
         <v>0</v>
       </c>
       <c r="L114" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M114" s="19">
         <v>0</v>
@@ -7104,7 +7107,7 @@
         <v>82</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H115" s="19">
         <v>12</v>
@@ -7119,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M115" s="19">
         <v>0</v>
@@ -7152,7 +7155,7 @@
         <v>84</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H116" s="19">
         <v>10</v>
@@ -7167,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M116" s="19">
         <v>0</v>
@@ -7200,7 +7203,7 @@
         <v>84</v>
       </c>
       <c r="G117" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H117" s="19">
         <v>11</v>
@@ -7215,7 +7218,7 @@
         <v>0</v>
       </c>
       <c r="L117" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M117" s="19">
         <v>0</v>
@@ -7248,7 +7251,7 @@
         <v>84</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H118" s="19">
         <v>12</v>
@@ -7263,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="L118" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M118" s="19">
         <v>0</v>
@@ -7296,7 +7299,7 @@
         <v>86</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H119" s="19">
         <v>10</v>
@@ -7311,7 +7314,7 @@
         <v>0</v>
       </c>
       <c r="L119" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M119" s="19">
         <v>0</v>
@@ -7344,7 +7347,7 @@
         <v>86</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H120" s="19">
         <v>11</v>
@@ -7359,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="L120" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M120" s="19">
         <v>0</v>
@@ -7392,7 +7395,7 @@
         <v>86</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H121" s="19">
         <v>12</v>
@@ -7407,7 +7410,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M121" s="19">
         <v>0</v>
@@ -7440,7 +7443,7 @@
         <v>89</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H122" s="19">
         <v>10</v>
@@ -7455,7 +7458,7 @@
         <v>0</v>
       </c>
       <c r="L122" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M122" s="19">
         <v>0</v>
@@ -7487,7 +7490,7 @@
         <v>89</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H123" s="19">
         <v>11</v>
@@ -7502,7 +7505,7 @@
         <v>0</v>
       </c>
       <c r="L123" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M123" s="19">
         <v>0</v>
@@ -7534,7 +7537,7 @@
         <v>89</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H124" s="19">
         <v>12</v>
@@ -7549,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M124" s="19">
         <v>0</v>
@@ -7581,7 +7584,7 @@
         <v>91</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H125" s="19">
         <v>10</v>
@@ -7596,7 +7599,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M125" s="19">
         <v>0</v>
@@ -7628,7 +7631,7 @@
         <v>91</v>
       </c>
       <c r="G126" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H126" s="19">
         <v>11</v>
@@ -7643,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M126" s="19">
         <v>0</v>
@@ -7675,7 +7678,7 @@
         <v>91</v>
       </c>
       <c r="G127" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H127" s="19">
         <v>12</v>
@@ -7690,7 +7693,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M127" s="19">
         <v>0</v>
@@ -7722,7 +7725,7 @@
         <v>93</v>
       </c>
       <c r="G128" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H128" s="19">
         <v>10</v>
@@ -7737,7 +7740,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M128" s="19">
         <v>0</v>
@@ -7769,7 +7772,7 @@
         <v>93</v>
       </c>
       <c r="G129" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H129" s="19">
         <v>11</v>
@@ -7784,7 +7787,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M129" s="19">
         <v>0</v>
@@ -7816,7 +7819,7 @@
         <v>93</v>
       </c>
       <c r="G130" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H130" s="19">
         <v>12</v>
@@ -7831,7 +7834,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M130" s="19">
         <v>0</v>
@@ -7863,7 +7866,7 @@
         <v>95</v>
       </c>
       <c r="G131" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H131" s="19">
         <v>10</v>
@@ -7878,7 +7881,7 @@
         <v>0</v>
       </c>
       <c r="L131" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M131" s="19">
         <v>0</v>
@@ -7910,7 +7913,7 @@
         <v>95</v>
       </c>
       <c r="G132" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H132" s="19">
         <v>11</v>
@@ -7925,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="L132" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M132" s="19">
         <v>0</v>
@@ -7957,7 +7960,7 @@
         <v>95</v>
       </c>
       <c r="G133" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H133" s="19">
         <v>12</v>
@@ -7972,7 +7975,7 @@
         <v>0</v>
       </c>
       <c r="L133" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M133" s="19">
         <v>0</v>
@@ -8004,7 +8007,7 @@
         <v>101</v>
       </c>
       <c r="G134" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H134" s="19">
         <v>10</v>
@@ -8019,7 +8022,7 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M134" s="19">
         <v>0</v>
@@ -8052,7 +8055,7 @@
         <v>101</v>
       </c>
       <c r="G135" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H135" s="19">
         <v>11</v>
@@ -8067,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M135" s="19">
         <v>0</v>
@@ -8100,7 +8103,7 @@
         <v>101</v>
       </c>
       <c r="G136" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H136" s="19">
         <v>12</v>
@@ -8115,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M136" s="19">
         <v>0</v>
@@ -8149,7 +8152,7 @@
         <v>31</v>
       </c>
       <c r="G137" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H137" s="19">
         <v>10</v>
@@ -8164,7 +8167,7 @@
         <v>0</v>
       </c>
       <c r="L137" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M137" s="19">
         <v>0</v>
@@ -8198,7 +8201,7 @@
         <v>31</v>
       </c>
       <c r="G138" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H138" s="19">
         <v>11</v>
@@ -8213,7 +8216,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M138" s="19">
         <v>0</v>
@@ -8247,7 +8250,7 @@
         <v>31</v>
       </c>
       <c r="G139" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H139" s="19">
         <v>12</v>
@@ -8262,7 +8265,7 @@
         <v>0</v>
       </c>
       <c r="L139" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M139" s="19">
         <v>0</v>
@@ -8295,7 +8298,7 @@
         <v>38</v>
       </c>
       <c r="G140" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H140" s="19">
         <v>10</v>
@@ -8310,7 +8313,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M140" s="19">
         <v>0</v>
@@ -8345,7 +8348,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G141" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H141" s="19">
         <v>11</v>
@@ -8360,7 +8363,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M141" s="19">
         <v>0</v>
@@ -8395,7 +8398,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G142" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H142" s="19">
         <v>12</v>
@@ -8410,7 +8413,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M142" s="19">
         <v>0</v>
@@ -8443,7 +8446,7 @@
         <v>40</v>
       </c>
       <c r="G143" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H143" s="19">
         <v>10</v>
@@ -8458,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M143" s="19">
         <v>0</v>
@@ -8493,7 +8496,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G144" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H144" s="19">
         <v>11</v>
@@ -8508,7 +8511,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M144" s="19">
         <v>0</v>
@@ -8543,7 +8546,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G145" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H145" s="19">
         <v>12</v>
@@ -8558,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M145" s="19">
         <v>0</v>
@@ -8591,7 +8594,7 @@
         <v>42</v>
       </c>
       <c r="G146" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H146" s="19">
         <v>10</v>
@@ -8606,7 +8609,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M146" s="19">
         <v>0</v>
@@ -8641,7 +8644,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G147" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H147" s="19">
         <v>11</v>
@@ -8656,7 +8659,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M147" s="19">
         <v>0</v>
@@ -8691,7 +8694,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G148" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H148" s="19">
         <v>12</v>
@@ -8706,7 +8709,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M148" s="19">
         <v>0</v>
@@ -8739,7 +8742,7 @@
         <v>44</v>
       </c>
       <c r="G149" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H149" s="19">
         <v>10</v>
@@ -8754,7 +8757,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M149" s="19">
         <v>0</v>
@@ -8789,7 +8792,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G150" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H150" s="19">
         <v>11</v>
@@ -8804,7 +8807,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M150" s="19">
         <v>0</v>
@@ -8839,7 +8842,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G151" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H151" s="19">
         <v>12</v>
@@ -8854,7 +8857,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M151" s="19">
         <v>0</v>
@@ -8887,7 +8890,7 @@
         <v>46</v>
       </c>
       <c r="G152" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H152" s="19">
         <v>10</v>
@@ -8902,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M152" s="19">
         <v>0</v>
@@ -8936,7 +8939,7 @@
         <v>46</v>
       </c>
       <c r="G153" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H153" s="19">
         <v>11</v>
@@ -8951,7 +8954,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M153" s="19">
         <v>0</v>
@@ -8985,7 +8988,7 @@
         <v>46</v>
       </c>
       <c r="G154" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H154" s="19">
         <v>12</v>
@@ -9000,7 +9003,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M154" s="19">
         <v>0</v>
@@ -9033,7 +9036,7 @@
         <v>48</v>
       </c>
       <c r="G155" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H155" s="19">
         <v>10</v>
@@ -9048,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M155" s="19">
         <v>0</v>
@@ -9081,7 +9084,7 @@
         <v>48</v>
       </c>
       <c r="G156" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H156" s="19">
         <v>11</v>
@@ -9096,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M156" s="19">
         <v>0</v>
@@ -9129,7 +9132,7 @@
         <v>48</v>
       </c>
       <c r="G157" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H157" s="19">
         <v>12</v>
@@ -9144,7 +9147,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M157" s="19">
         <v>0</v>
@@ -9177,7 +9180,7 @@
         <v>50</v>
       </c>
       <c r="G158" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H158" s="19">
         <v>10</v>
@@ -9192,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M158" s="19">
         <v>0</v>
@@ -9225,7 +9228,7 @@
         <v>50</v>
       </c>
       <c r="G159" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H159" s="19">
         <v>11</v>
@@ -9240,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M159" s="19">
         <v>0</v>
@@ -9273,7 +9276,7 @@
         <v>50</v>
       </c>
       <c r="G160" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H160" s="19">
         <v>12</v>
@@ -9288,7 +9291,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M160" s="19">
         <v>0</v>
@@ -9321,7 +9324,7 @@
         <v>52</v>
       </c>
       <c r="G161" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H161" s="19">
         <v>10</v>
@@ -9336,7 +9339,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M161" s="19">
         <v>0</v>
@@ -9369,7 +9372,7 @@
         <v>52</v>
       </c>
       <c r="G162" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H162" s="19">
         <v>11</v>
@@ -9384,7 +9387,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M162" s="19">
         <v>0</v>
@@ -9417,7 +9420,7 @@
         <v>52</v>
       </c>
       <c r="G163" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H163" s="19">
         <v>12</v>
@@ -9432,7 +9435,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M163" s="19">
         <v>0</v>
@@ -9465,7 +9468,7 @@
         <v>54</v>
       </c>
       <c r="G164" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H164" s="19">
         <v>10</v>
@@ -9480,7 +9483,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M164" s="19">
         <v>0</v>
@@ -9513,7 +9516,7 @@
         <v>54</v>
       </c>
       <c r="G165" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H165" s="19">
         <v>11</v>
@@ -9528,7 +9531,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M165" s="19">
         <v>0</v>
@@ -9561,7 +9564,7 @@
         <v>54</v>
       </c>
       <c r="G166" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H166" s="19">
         <v>12</v>
@@ -9576,7 +9579,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M166" s="19">
         <v>0</v>
@@ -9609,7 +9612,7 @@
         <v>56</v>
       </c>
       <c r="G167" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H167" s="19">
         <v>10</v>
@@ -9624,7 +9627,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M167" s="19">
         <v>0</v>
@@ -9657,7 +9660,7 @@
         <v>56</v>
       </c>
       <c r="G168" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H168" s="19">
         <v>11</v>
@@ -9672,7 +9675,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M168" s="19">
         <v>0</v>
@@ -9705,7 +9708,7 @@
         <v>56</v>
       </c>
       <c r="G169" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H169" s="19">
         <v>12</v>
@@ -9720,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M169" s="19">
         <v>0</v>
@@ -9753,7 +9756,7 @@
         <v>58</v>
       </c>
       <c r="G170" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H170" s="19">
         <v>10</v>
@@ -9768,7 +9771,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M170" s="19">
         <v>0</v>
@@ -9801,7 +9804,7 @@
         <v>58</v>
       </c>
       <c r="G171" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H171" s="19">
         <v>11</v>
@@ -9816,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M171" s="19">
         <v>0</v>
@@ -9849,7 +9852,7 @@
         <v>58</v>
       </c>
       <c r="G172" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H172" s="19">
         <v>12</v>
@@ -9864,7 +9867,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M172" s="19">
         <v>0</v>
@@ -9897,7 +9900,7 @@
         <v>60</v>
       </c>
       <c r="G173" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H173" s="1">
         <v>10</v>
@@ -9912,7 +9915,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M173" s="19">
         <v>0</v>
@@ -9945,7 +9948,7 @@
         <v>60</v>
       </c>
       <c r="G174" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H174" s="1">
         <v>11</v>
@@ -9960,7 +9963,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M174" s="19">
         <v>0</v>
@@ -9993,7 +9996,7 @@
         <v>60</v>
       </c>
       <c r="G175" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H175" s="1">
         <v>12</v>
@@ -10008,7 +10011,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M175" s="19">
         <v>0</v>
@@ -10041,7 +10044,7 @@
         <v>62</v>
       </c>
       <c r="G176" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H176" s="1">
         <v>10</v>
@@ -10056,7 +10059,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M176" s="19">
         <v>0</v>
@@ -10089,7 +10092,7 @@
         <v>62</v>
       </c>
       <c r="G177" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H177" s="1">
         <v>11</v>
@@ -10104,7 +10107,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M177" s="19">
         <v>0</v>
@@ -10137,7 +10140,7 @@
         <v>62</v>
       </c>
       <c r="G178" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H178" s="1">
         <v>12</v>
@@ -10152,7 +10155,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M178" s="19">
         <v>0</v>
@@ -10185,7 +10188,7 @@
         <v>64</v>
       </c>
       <c r="G179" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H179" s="1">
         <v>10</v>
@@ -10200,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M179" s="19">
         <v>0</v>
@@ -10233,7 +10236,7 @@
         <v>64</v>
       </c>
       <c r="G180" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H180" s="1">
         <v>11</v>
@@ -10248,7 +10251,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M180" s="19">
         <v>0</v>
@@ -10281,7 +10284,7 @@
         <v>64</v>
       </c>
       <c r="G181" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H181" s="1">
         <v>12</v>
@@ -10296,7 +10299,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M181" s="19">
         <v>0</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="128">
   <si>
     <t>sid</t>
   </si>
@@ -503,7 +503,13 @@
     <t>绿巨人</t>
   </si>
   <si>
+    <t>GreenGiant</t>
+  </si>
+  <si>
     <t>象财神</t>
+  </si>
+  <si>
+    <t>Ganesha</t>
   </si>
   <si>
     <t>愤怒的小鸟</t>
@@ -7037,7 +7043,9 @@
       <c r="E113" s="15">
         <v>103100001</v>
       </c>
-      <c r="F113" s="15"/>
+      <c r="F113" s="25" t="s">
+        <v>115</v>
+      </c>
       <c r="G113" s="1" t="s">
         <v>32</v>
       </c>
@@ -7083,7 +7091,9 @@
       <c r="E114" s="15">
         <v>103100001</v>
       </c>
-      <c r="F114" s="15"/>
+      <c r="F114" s="25" t="s">
+        <v>115</v>
+      </c>
       <c r="G114" s="1" t="s">
         <v>35</v>
       </c>
@@ -7129,7 +7139,9 @@
       <c r="E115" s="15">
         <v>103100001</v>
       </c>
-      <c r="F115" s="15"/>
+      <c r="F115" s="25" t="s">
+        <v>115</v>
+      </c>
       <c r="G115" s="1" t="s">
         <v>36</v>
       </c>
@@ -7170,12 +7182,14 @@
         <v>1</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E116" s="15">
         <v>102700001</v>
       </c>
-      <c r="F116" s="15"/>
+      <c r="F116" t="s">
+        <v>117</v>
+      </c>
       <c r="G116" s="1" t="s">
         <v>32</v>
       </c>
@@ -7216,12 +7230,14 @@
         <v>1</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E117" s="15">
         <v>102700001</v>
       </c>
-      <c r="F117" s="15"/>
+      <c r="F117" t="s">
+        <v>117</v>
+      </c>
       <c r="G117" s="1" t="s">
         <v>35</v>
       </c>
@@ -7262,12 +7278,14 @@
         <v>1</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E118" s="15">
         <v>102700001</v>
       </c>
-      <c r="F118" s="15"/>
+      <c r="F118" t="s">
+        <v>117</v>
+      </c>
       <c r="G118" s="1" t="s">
         <v>36</v>
       </c>
@@ -7308,7 +7326,7 @@
         <v>1</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E119" s="15">
         <v>103900001</v>
@@ -7354,7 +7372,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E120" s="15">
         <v>103900001</v>
@@ -7400,7 +7418,7 @@
         <v>1</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E121" s="15">
         <v>103900001</v>
@@ -7446,7 +7464,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E122" s="15">
         <v>101500001</v>
@@ -7492,7 +7510,7 @@
         <v>1</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E123" s="15">
         <v>101500001</v>
@@ -7538,7 +7556,7 @@
         <v>1</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E124" s="15">
         <v>101500001</v>
@@ -7584,7 +7602,7 @@
         <v>1</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E125" s="15">
         <v>105300001</v>
@@ -7630,7 +7648,7 @@
         <v>1</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E126" s="15">
         <v>105300001</v>
@@ -7676,7 +7694,7 @@
         <v>1</v>
       </c>
       <c r="D127" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E127" s="15">
         <v>105300001</v>
@@ -7722,7 +7740,7 @@
         <v>1</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E128" s="15">
         <v>105100001</v>
@@ -7768,7 +7786,7 @@
         <v>1</v>
       </c>
       <c r="D129" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E129" s="15">
         <v>105100001</v>
@@ -7814,7 +7832,7 @@
         <v>1</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E130" s="15">
         <v>105100001</v>
@@ -7869,7 +7887,7 @@
         <v>78</v>
       </c>
       <c r="G131" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H131" s="20">
         <v>10</v>
@@ -7884,7 +7902,7 @@
         <v>0</v>
       </c>
       <c r="L131" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M131" s="20">
         <v>0</v>
@@ -7917,7 +7935,7 @@
         <v>78</v>
       </c>
       <c r="G132" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H132" s="20">
         <v>11</v>
@@ -7932,7 +7950,7 @@
         <v>0</v>
       </c>
       <c r="L132" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M132" s="20">
         <v>0</v>
@@ -7965,7 +7983,7 @@
         <v>78</v>
       </c>
       <c r="G133" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H133" s="20">
         <v>12</v>
@@ -7980,7 +7998,7 @@
         <v>0</v>
       </c>
       <c r="L133" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M133" s="20">
         <v>0</v>
@@ -8013,7 +8031,7 @@
         <v>80</v>
       </c>
       <c r="G134" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H134" s="20">
         <v>10</v>
@@ -8028,7 +8046,7 @@
         <v>0</v>
       </c>
       <c r="L134" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M134" s="20">
         <v>0</v>
@@ -8061,7 +8079,7 @@
         <v>80</v>
       </c>
       <c r="G135" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H135" s="20">
         <v>11</v>
@@ -8076,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="L135" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M135" s="20">
         <v>0</v>
@@ -8109,7 +8127,7 @@
         <v>80</v>
       </c>
       <c r="G136" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H136" s="20">
         <v>12</v>
@@ -8124,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M136" s="20">
         <v>0</v>
@@ -8157,7 +8175,7 @@
         <v>82</v>
       </c>
       <c r="G137" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H137" s="20">
         <v>10</v>
@@ -8172,7 +8190,7 @@
         <v>0</v>
       </c>
       <c r="L137" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M137" s="20">
         <v>0</v>
@@ -8205,7 +8223,7 @@
         <v>82</v>
       </c>
       <c r="G138" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H138" s="20">
         <v>11</v>
@@ -8220,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M138" s="20">
         <v>0</v>
@@ -8253,7 +8271,7 @@
         <v>82</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H139" s="20">
         <v>12</v>
@@ -8268,7 +8286,7 @@
         <v>0</v>
       </c>
       <c r="L139" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M139" s="20">
         <v>0</v>
@@ -8301,7 +8319,7 @@
         <v>84</v>
       </c>
       <c r="G140" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H140" s="20">
         <v>10</v>
@@ -8316,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M140" s="20">
         <v>0</v>
@@ -8349,7 +8367,7 @@
         <v>84</v>
       </c>
       <c r="G141" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H141" s="20">
         <v>11</v>
@@ -8364,7 +8382,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M141" s="20">
         <v>0</v>
@@ -8397,7 +8415,7 @@
         <v>84</v>
       </c>
       <c r="G142" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H142" s="20">
         <v>12</v>
@@ -8412,7 +8430,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M142" s="20">
         <v>0</v>
@@ -8445,7 +8463,7 @@
         <v>86</v>
       </c>
       <c r="G143" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H143" s="20">
         <v>10</v>
@@ -8460,7 +8478,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M143" s="20">
         <v>0</v>
@@ -8493,7 +8511,7 @@
         <v>86</v>
       </c>
       <c r="G144" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H144" s="20">
         <v>11</v>
@@ -8508,7 +8526,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M144" s="20">
         <v>0</v>
@@ -8541,7 +8559,7 @@
         <v>86</v>
       </c>
       <c r="G145" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H145" s="20">
         <v>12</v>
@@ -8556,7 +8574,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M145" s="20">
         <v>0</v>
@@ -8589,7 +8607,7 @@
         <v>89</v>
       </c>
       <c r="G146" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H146" s="20">
         <v>10</v>
@@ -8604,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M146" s="20">
         <v>0</v>
@@ -8636,7 +8654,7 @@
         <v>89</v>
       </c>
       <c r="G147" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H147" s="20">
         <v>11</v>
@@ -8651,7 +8669,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M147" s="20">
         <v>0</v>
@@ -8683,7 +8701,7 @@
         <v>89</v>
       </c>
       <c r="G148" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H148" s="20">
         <v>12</v>
@@ -8698,7 +8716,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M148" s="20">
         <v>0</v>
@@ -8730,7 +8748,7 @@
         <v>91</v>
       </c>
       <c r="G149" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H149" s="20">
         <v>10</v>
@@ -8745,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M149" s="20">
         <v>0</v>
@@ -8777,7 +8795,7 @@
         <v>91</v>
       </c>
       <c r="G150" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H150" s="20">
         <v>11</v>
@@ -8792,7 +8810,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M150" s="20">
         <v>0</v>
@@ -8824,7 +8842,7 @@
         <v>91</v>
       </c>
       <c r="G151" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H151" s="20">
         <v>12</v>
@@ -8839,7 +8857,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M151" s="20">
         <v>0</v>
@@ -8871,7 +8889,7 @@
         <v>93</v>
       </c>
       <c r="G152" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H152" s="20">
         <v>10</v>
@@ -8886,7 +8904,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M152" s="20">
         <v>0</v>
@@ -8918,7 +8936,7 @@
         <v>93</v>
       </c>
       <c r="G153" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H153" s="20">
         <v>11</v>
@@ -8933,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M153" s="20">
         <v>0</v>
@@ -8965,7 +8983,7 @@
         <v>93</v>
       </c>
       <c r="G154" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H154" s="20">
         <v>12</v>
@@ -8980,7 +8998,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M154" s="20">
         <v>0</v>
@@ -9012,7 +9030,7 @@
         <v>95</v>
       </c>
       <c r="G155" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H155" s="20">
         <v>10</v>
@@ -9027,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M155" s="20">
         <v>0</v>
@@ -9059,7 +9077,7 @@
         <v>95</v>
       </c>
       <c r="G156" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H156" s="20">
         <v>11</v>
@@ -9074,7 +9092,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M156" s="20">
         <v>0</v>
@@ -9106,7 +9124,7 @@
         <v>95</v>
       </c>
       <c r="G157" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H157" s="20">
         <v>12</v>
@@ -9121,7 +9139,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M157" s="20">
         <v>0</v>
@@ -9153,7 +9171,7 @@
         <v>101</v>
       </c>
       <c r="G158" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H158" s="20">
         <v>10</v>
@@ -9168,7 +9186,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M158" s="20">
         <v>0</v>
@@ -9201,7 +9219,7 @@
         <v>101</v>
       </c>
       <c r="G159" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H159" s="20">
         <v>11</v>
@@ -9216,7 +9234,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M159" s="20">
         <v>0</v>
@@ -9249,7 +9267,7 @@
         <v>101</v>
       </c>
       <c r="G160" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H160" s="20">
         <v>12</v>
@@ -9264,7 +9282,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M160" s="20">
         <v>0</v>
@@ -9297,7 +9315,7 @@
         <v>104</v>
       </c>
       <c r="G161" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H161" s="20">
         <v>10</v>
@@ -9312,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M161" s="20">
         <v>0</v>
@@ -9345,7 +9363,7 @@
         <v>104</v>
       </c>
       <c r="G162" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H162" s="20">
         <v>11</v>
@@ -9360,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M162" s="20">
         <v>0</v>
@@ -9393,7 +9411,7 @@
         <v>104</v>
       </c>
       <c r="G163" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H163" s="20">
         <v>12</v>
@@ -9408,7 +9426,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M163" s="20">
         <v>0</v>
@@ -9441,7 +9459,7 @@
         <v>107</v>
       </c>
       <c r="G164" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H164" s="20">
         <v>10</v>
@@ -9456,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M164" s="20">
         <v>0</v>
@@ -9489,7 +9507,7 @@
         <v>107</v>
       </c>
       <c r="G165" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H165" s="20">
         <v>11</v>
@@ -9504,7 +9522,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M165" s="20">
         <v>0</v>
@@ -9537,7 +9555,7 @@
         <v>107</v>
       </c>
       <c r="G166" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H166" s="20">
         <v>12</v>
@@ -9552,7 +9570,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M166" s="20">
         <v>0</v>
@@ -9586,7 +9604,7 @@
         <v>31</v>
       </c>
       <c r="G167" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H167" s="20">
         <v>10</v>
@@ -9601,7 +9619,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M167" s="20">
         <v>0</v>
@@ -9635,7 +9653,7 @@
         <v>31</v>
       </c>
       <c r="G168" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H168" s="20">
         <v>11</v>
@@ -9650,7 +9668,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M168" s="20">
         <v>0</v>
@@ -9684,7 +9702,7 @@
         <v>31</v>
       </c>
       <c r="G169" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H169" s="20">
         <v>12</v>
@@ -9699,7 +9717,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M169" s="20">
         <v>0</v>
@@ -9732,7 +9750,7 @@
         <v>38</v>
       </c>
       <c r="G170" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H170" s="20">
         <v>10</v>
@@ -9747,7 +9765,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M170" s="20">
         <v>0</v>
@@ -9782,7 +9800,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G171" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H171" s="20">
         <v>11</v>
@@ -9797,7 +9815,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M171" s="20">
         <v>0</v>
@@ -9832,7 +9850,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G172" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H172" s="20">
         <v>12</v>
@@ -9847,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M172" s="20">
         <v>0</v>
@@ -9880,7 +9898,7 @@
         <v>40</v>
       </c>
       <c r="G173" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H173" s="20">
         <v>10</v>
@@ -9895,7 +9913,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M173" s="20">
         <v>0</v>
@@ -9930,7 +9948,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G174" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H174" s="20">
         <v>11</v>
@@ -9945,7 +9963,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M174" s="20">
         <v>0</v>
@@ -9980,7 +9998,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G175" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H175" s="20">
         <v>12</v>
@@ -9995,7 +10013,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M175" s="20">
         <v>0</v>
@@ -10028,7 +10046,7 @@
         <v>42</v>
       </c>
       <c r="G176" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H176" s="20">
         <v>10</v>
@@ -10043,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M176" s="20">
         <v>0</v>
@@ -10078,7 +10096,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G177" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H177" s="20">
         <v>11</v>
@@ -10093,7 +10111,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M177" s="20">
         <v>0</v>
@@ -10128,7 +10146,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G178" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H178" s="20">
         <v>12</v>
@@ -10143,7 +10161,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M178" s="20">
         <v>0</v>
@@ -10176,7 +10194,7 @@
         <v>44</v>
       </c>
       <c r="G179" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H179" s="20">
         <v>10</v>
@@ -10191,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M179" s="20">
         <v>0</v>
@@ -10226,7 +10244,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G180" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H180" s="20">
         <v>11</v>
@@ -10241,7 +10259,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M180" s="20">
         <v>0</v>
@@ -10276,7 +10294,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G181" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H181" s="20">
         <v>12</v>
@@ -10291,7 +10309,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M181" s="20">
         <v>0</v>
@@ -10324,7 +10342,7 @@
         <v>46</v>
       </c>
       <c r="G182" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H182" s="20">
         <v>10</v>
@@ -10339,7 +10357,7 @@
         <v>0</v>
       </c>
       <c r="L182" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M182" s="20">
         <v>0</v>
@@ -10373,7 +10391,7 @@
         <v>46</v>
       </c>
       <c r="G183" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H183" s="20">
         <v>11</v>
@@ -10388,7 +10406,7 @@
         <v>0</v>
       </c>
       <c r="L183" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M183" s="20">
         <v>0</v>
@@ -10422,7 +10440,7 @@
         <v>46</v>
       </c>
       <c r="G184" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H184" s="20">
         <v>12</v>
@@ -10437,7 +10455,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M184" s="20">
         <v>0</v>
@@ -10470,7 +10488,7 @@
         <v>48</v>
       </c>
       <c r="G185" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H185" s="20">
         <v>10</v>
@@ -10485,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="L185" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M185" s="20">
         <v>0</v>
@@ -10518,7 +10536,7 @@
         <v>48</v>
       </c>
       <c r="G186" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H186" s="20">
         <v>11</v>
@@ -10533,7 +10551,7 @@
         <v>0</v>
       </c>
       <c r="L186" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M186" s="20">
         <v>0</v>
@@ -10566,7 +10584,7 @@
         <v>48</v>
       </c>
       <c r="G187" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H187" s="20">
         <v>12</v>
@@ -10581,7 +10599,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M187" s="20">
         <v>0</v>
@@ -10614,7 +10632,7 @@
         <v>50</v>
       </c>
       <c r="G188" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H188" s="20">
         <v>10</v>
@@ -10629,7 +10647,7 @@
         <v>0</v>
       </c>
       <c r="L188" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M188" s="20">
         <v>0</v>
@@ -10662,7 +10680,7 @@
         <v>50</v>
       </c>
       <c r="G189" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H189" s="20">
         <v>11</v>
@@ -10677,7 +10695,7 @@
         <v>0</v>
       </c>
       <c r="L189" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M189" s="20">
         <v>0</v>
@@ -10710,7 +10728,7 @@
         <v>50</v>
       </c>
       <c r="G190" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H190" s="20">
         <v>12</v>
@@ -10725,7 +10743,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M190" s="20">
         <v>0</v>
@@ -10758,7 +10776,7 @@
         <v>52</v>
       </c>
       <c r="G191" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H191" s="20">
         <v>10</v>
@@ -10773,7 +10791,7 @@
         <v>0</v>
       </c>
       <c r="L191" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M191" s="20">
         <v>0</v>
@@ -10806,7 +10824,7 @@
         <v>52</v>
       </c>
       <c r="G192" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H192" s="20">
         <v>11</v>
@@ -10821,7 +10839,7 @@
         <v>0</v>
       </c>
       <c r="L192" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M192" s="20">
         <v>0</v>
@@ -10854,7 +10872,7 @@
         <v>52</v>
       </c>
       <c r="G193" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H193" s="20">
         <v>12</v>
@@ -10869,7 +10887,7 @@
         <v>0</v>
       </c>
       <c r="L193" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M193" s="20">
         <v>0</v>
@@ -10902,7 +10920,7 @@
         <v>54</v>
       </c>
       <c r="G194" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H194" s="20">
         <v>10</v>
@@ -10917,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="L194" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M194" s="20">
         <v>0</v>
@@ -10950,7 +10968,7 @@
         <v>54</v>
       </c>
       <c r="G195" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H195" s="20">
         <v>11</v>
@@ -10965,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="L195" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M195" s="20">
         <v>0</v>
@@ -10998,7 +11016,7 @@
         <v>54</v>
       </c>
       <c r="G196" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H196" s="20">
         <v>12</v>
@@ -11013,7 +11031,7 @@
         <v>0</v>
       </c>
       <c r="L196" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M196" s="20">
         <v>0</v>
@@ -11046,7 +11064,7 @@
         <v>56</v>
       </c>
       <c r="G197" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H197" s="20">
         <v>10</v>
@@ -11061,7 +11079,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M197" s="20">
         <v>0</v>
@@ -11094,7 +11112,7 @@
         <v>56</v>
       </c>
       <c r="G198" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H198" s="20">
         <v>11</v>
@@ -11109,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="L198" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M198" s="20">
         <v>0</v>
@@ -11142,7 +11160,7 @@
         <v>56</v>
       </c>
       <c r="G199" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H199" s="20">
         <v>12</v>
@@ -11157,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="L199" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M199" s="20">
         <v>0</v>
@@ -11190,7 +11208,7 @@
         <v>58</v>
       </c>
       <c r="G200" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H200" s="20">
         <v>10</v>
@@ -11205,7 +11223,7 @@
         <v>0</v>
       </c>
       <c r="L200" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M200" s="20">
         <v>0</v>
@@ -11238,7 +11256,7 @@
         <v>58</v>
       </c>
       <c r="G201" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H201" s="20">
         <v>11</v>
@@ -11253,7 +11271,7 @@
         <v>0</v>
       </c>
       <c r="L201" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M201" s="20">
         <v>0</v>
@@ -11286,7 +11304,7 @@
         <v>58</v>
       </c>
       <c r="G202" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H202" s="20">
         <v>12</v>
@@ -11301,7 +11319,7 @@
         <v>0</v>
       </c>
       <c r="L202" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M202" s="20">
         <v>0</v>
@@ -11334,7 +11352,7 @@
         <v>60</v>
       </c>
       <c r="G203" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H203" s="1">
         <v>10</v>
@@ -11349,7 +11367,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M203" s="20">
         <v>0</v>
@@ -11382,7 +11400,7 @@
         <v>60</v>
       </c>
       <c r="G204" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H204" s="1">
         <v>11</v>
@@ -11397,7 +11415,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M204" s="20">
         <v>0</v>
@@ -11430,7 +11448,7 @@
         <v>60</v>
       </c>
       <c r="G205" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H205" s="1">
         <v>12</v>
@@ -11445,7 +11463,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M205" s="20">
         <v>0</v>
@@ -11478,7 +11496,7 @@
         <v>62</v>
       </c>
       <c r="G206" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H206" s="1">
         <v>10</v>
@@ -11493,7 +11511,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M206" s="20">
         <v>0</v>
@@ -11526,7 +11544,7 @@
         <v>62</v>
       </c>
       <c r="G207" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H207" s="1">
         <v>11</v>
@@ -11541,7 +11559,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M207" s="20">
         <v>0</v>
@@ -11574,7 +11592,7 @@
         <v>62</v>
       </c>
       <c r="G208" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H208" s="1">
         <v>12</v>
@@ -11589,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="L208" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M208" s="20">
         <v>0</v>
@@ -11622,7 +11640,7 @@
         <v>64</v>
       </c>
       <c r="G209" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H209" s="1">
         <v>10</v>
@@ -11637,7 +11655,7 @@
         <v>0</v>
       </c>
       <c r="L209" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M209" s="20">
         <v>0</v>
@@ -11670,7 +11688,7 @@
         <v>64</v>
       </c>
       <c r="G210" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H210" s="1">
         <v>11</v>
@@ -11685,7 +11703,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M210" s="20">
         <v>0</v>
@@ -11718,7 +11736,7 @@
         <v>64</v>
       </c>
       <c r="G211" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H211" s="1">
         <v>12</v>
@@ -11733,7 +11751,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M211" s="20">
         <v>0</v>
@@ -11766,7 +11784,7 @@
         <v>66</v>
       </c>
       <c r="G212" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H212" s="1">
         <v>10</v>
@@ -11781,7 +11799,7 @@
         <v>0</v>
       </c>
       <c r="L212" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M212" s="20">
         <v>0</v>
@@ -11814,7 +11832,7 @@
         <v>66</v>
       </c>
       <c r="G213" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H213" s="1">
         <v>11</v>
@@ -11829,7 +11847,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M213" s="20">
         <v>0</v>
@@ -11862,7 +11880,7 @@
         <v>66</v>
       </c>
       <c r="G214" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H214" s="1">
         <v>12</v>
@@ -11877,7 +11895,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M214" s="20">
         <v>0</v>
@@ -11910,7 +11928,7 @@
         <v>68</v>
       </c>
       <c r="G215" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H215" s="1">
         <v>10</v>
@@ -11925,7 +11943,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M215" s="20">
         <v>0</v>
@@ -11958,7 +11976,7 @@
         <v>68</v>
       </c>
       <c r="G216" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H216" s="1">
         <v>11</v>
@@ -11973,7 +11991,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M216" s="20">
         <v>0</v>
@@ -12006,7 +12024,7 @@
         <v>68</v>
       </c>
       <c r="G217" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H217" s="1">
         <v>12</v>
@@ -12021,7 +12039,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M217" s="20">
         <v>0</v>
@@ -12054,7 +12072,7 @@
         <v>70</v>
       </c>
       <c r="G218" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H218" s="1">
         <v>10</v>
@@ -12069,7 +12087,7 @@
         <v>0</v>
       </c>
       <c r="L218" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M218" s="20">
         <v>0</v>
@@ -12102,7 +12120,7 @@
         <v>70</v>
       </c>
       <c r="G219" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H219" s="1">
         <v>11</v>
@@ -12117,7 +12135,7 @@
         <v>0</v>
       </c>
       <c r="L219" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M219" s="20">
         <v>0</v>
@@ -12150,7 +12168,7 @@
         <v>70</v>
       </c>
       <c r="G220" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H220" s="1">
         <v>12</v>
@@ -12165,7 +12183,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M220" s="20">
         <v>0</v>
@@ -12197,7 +12215,7 @@
         <v>72</v>
       </c>
       <c r="G221" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H221" s="1">
         <v>10</v>
@@ -12212,7 +12230,7 @@
         <v>0</v>
       </c>
       <c r="L221" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M221" s="20">
         <v>0</v>
@@ -12244,7 +12262,7 @@
         <v>72</v>
       </c>
       <c r="G222" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H222" s="1">
         <v>11</v>
@@ -12259,7 +12277,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M222" s="20">
         <v>0</v>
@@ -12291,7 +12309,7 @@
         <v>72</v>
       </c>
       <c r="G223" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H223" s="1">
         <v>12</v>
@@ -12306,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="L223" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M223" s="20">
         <v>0</v>
@@ -12338,7 +12356,7 @@
         <v>74</v>
       </c>
       <c r="G224" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H224" s="1">
         <v>10</v>
@@ -12353,7 +12371,7 @@
         <v>0</v>
       </c>
       <c r="L224" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M224" s="20">
         <v>0</v>
@@ -12385,7 +12403,7 @@
         <v>74</v>
       </c>
       <c r="G225" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H225" s="1">
         <v>11</v>
@@ -12400,7 +12418,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M225" s="20">
         <v>0</v>
@@ -12432,7 +12450,7 @@
         <v>74</v>
       </c>
       <c r="G226" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H226" s="1">
         <v>12</v>
@@ -12447,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="L226" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M226" s="20">
         <v>0</v>
@@ -12479,7 +12497,7 @@
         <v>76</v>
       </c>
       <c r="G227" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H227" s="1">
         <v>10</v>
@@ -12494,7 +12512,7 @@
         <v>0</v>
       </c>
       <c r="L227" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M227" s="20">
         <v>0</v>
@@ -12530,7 +12548,7 @@
         <v>76</v>
       </c>
       <c r="G228" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H228" s="1">
         <v>11</v>
@@ -12545,7 +12563,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M228" s="20">
         <v>0</v>
@@ -12581,7 +12599,7 @@
         <v>76</v>
       </c>
       <c r="G229" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H229" s="1">
         <v>12</v>
@@ -12596,7 +12614,7 @@
         <v>0</v>
       </c>
       <c r="L229" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M229" s="20">
         <v>0</v>
@@ -12630,7 +12648,7 @@
       </c>
       <c r="F230" s="15"/>
       <c r="G230" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H230" s="1">
         <v>10</v>
@@ -12645,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="L230" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M230" s="20">
         <v>0</v>
@@ -12676,7 +12694,7 @@
       </c>
       <c r="F231" s="15"/>
       <c r="G231" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H231" s="1">
         <v>11</v>
@@ -12691,7 +12709,7 @@
         <v>0</v>
       </c>
       <c r="L231" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M231" s="20">
         <v>0</v>
@@ -12722,7 +12740,7 @@
       </c>
       <c r="F232" s="15"/>
       <c r="G232" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H232" s="1">
         <v>12</v>
@@ -12737,7 +12755,7 @@
         <v>0</v>
       </c>
       <c r="L232" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M232" s="20">
         <v>0</v>
@@ -12766,9 +12784,11 @@
       <c r="E233" s="15">
         <v>103100001</v>
       </c>
-      <c r="F233" s="15"/>
+      <c r="F233" s="25" t="s">
+        <v>115</v>
+      </c>
       <c r="G233" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H233" s="1">
         <v>10</v>
@@ -12783,7 +12803,7 @@
         <v>0</v>
       </c>
       <c r="L233" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M233" s="20">
         <v>0</v>
@@ -12812,9 +12832,11 @@
       <c r="E234" s="15">
         <v>103100001</v>
       </c>
-      <c r="F234" s="15"/>
+      <c r="F234" s="25" t="s">
+        <v>115</v>
+      </c>
       <c r="G234" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H234" s="1">
         <v>11</v>
@@ -12829,7 +12851,7 @@
         <v>0</v>
       </c>
       <c r="L234" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M234" s="20">
         <v>0</v>
@@ -12858,9 +12880,11 @@
       <c r="E235" s="15">
         <v>103100001</v>
       </c>
-      <c r="F235" s="15"/>
+      <c r="F235" s="25" t="s">
+        <v>115</v>
+      </c>
       <c r="G235" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H235" s="1">
         <v>12</v>
@@ -12875,7 +12899,7 @@
         <v>0</v>
       </c>
       <c r="L235" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M235" s="20">
         <v>0</v>
@@ -12899,14 +12923,16 @@
         <v>1</v>
       </c>
       <c r="D236" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E236" s="15">
         <v>102700001</v>
       </c>
-      <c r="F236" s="15"/>
+      <c r="F236" t="s">
+        <v>117</v>
+      </c>
       <c r="G236" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H236" s="1">
         <v>10</v>
@@ -12921,7 +12947,7 @@
         <v>0</v>
       </c>
       <c r="L236" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M236" s="20">
         <v>0</v>
@@ -12945,14 +12971,16 @@
         <v>1</v>
       </c>
       <c r="D237" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E237" s="15">
         <v>102700001</v>
       </c>
-      <c r="F237" s="15"/>
+      <c r="F237" t="s">
+        <v>117</v>
+      </c>
       <c r="G237" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H237" s="1">
         <v>11</v>
@@ -12967,7 +12995,7 @@
         <v>0</v>
       </c>
       <c r="L237" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M237" s="20">
         <v>0</v>
@@ -12991,14 +13019,16 @@
         <v>1</v>
       </c>
       <c r="D238" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E238" s="15">
         <v>102700001</v>
       </c>
-      <c r="F238" s="15"/>
+      <c r="F238" t="s">
+        <v>117</v>
+      </c>
       <c r="G238" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H238" s="1">
         <v>12</v>
@@ -13013,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L238" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M238" s="20">
         <v>0</v>
@@ -13037,14 +13067,14 @@
         <v>1</v>
       </c>
       <c r="D239" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E239" s="15">
         <v>103900001</v>
       </c>
       <c r="F239" s="15"/>
       <c r="G239" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H239" s="1">
         <v>10</v>
@@ -13059,7 +13089,7 @@
         <v>0</v>
       </c>
       <c r="L239" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M239" s="20">
         <v>0</v>
@@ -13083,14 +13113,14 @@
         <v>1</v>
       </c>
       <c r="D240" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E240" s="15">
         <v>103900001</v>
       </c>
       <c r="F240" s="15"/>
       <c r="G240" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H240" s="1">
         <v>11</v>
@@ -13105,7 +13135,7 @@
         <v>0</v>
       </c>
       <c r="L240" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M240" s="20">
         <v>0</v>
@@ -13129,14 +13159,14 @@
         <v>1</v>
       </c>
       <c r="D241" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E241" s="15">
         <v>103900001</v>
       </c>
       <c r="F241" s="15"/>
       <c r="G241" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H241" s="1">
         <v>12</v>
@@ -13151,7 +13181,7 @@
         <v>0</v>
       </c>
       <c r="L241" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M241" s="20">
         <v>0</v>
@@ -13175,14 +13205,14 @@
         <v>1</v>
       </c>
       <c r="D242" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E242" s="15">
         <v>101500001</v>
       </c>
       <c r="F242" s="15"/>
       <c r="G242" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H242" s="1">
         <v>10</v>
@@ -13197,7 +13227,7 @@
         <v>0</v>
       </c>
       <c r="L242" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M242" s="20">
         <v>0</v>
@@ -13221,14 +13251,14 @@
         <v>1</v>
       </c>
       <c r="D243" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E243" s="15">
         <v>101500001</v>
       </c>
       <c r="F243" s="15"/>
       <c r="G243" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H243" s="1">
         <v>11</v>
@@ -13243,7 +13273,7 @@
         <v>0</v>
       </c>
       <c r="L243" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M243" s="20">
         <v>0</v>
@@ -13267,14 +13297,14 @@
         <v>1</v>
       </c>
       <c r="D244" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E244" s="15">
         <v>101500001</v>
       </c>
       <c r="F244" s="15"/>
       <c r="G244" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H244" s="1">
         <v>12</v>
@@ -13289,7 +13319,7 @@
         <v>0</v>
       </c>
       <c r="L244" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M244" s="20">
         <v>0</v>
@@ -13313,14 +13343,14 @@
         <v>1</v>
       </c>
       <c r="D245" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E245" s="15">
         <v>105300001</v>
       </c>
       <c r="F245" s="15"/>
       <c r="G245" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H245" s="1">
         <v>10</v>
@@ -13335,7 +13365,7 @@
         <v>0</v>
       </c>
       <c r="L245" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M245" s="20">
         <v>0</v>
@@ -13359,14 +13389,14 @@
         <v>1</v>
       </c>
       <c r="D246" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E246" s="15">
         <v>105300001</v>
       </c>
       <c r="F246" s="15"/>
       <c r="G246" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H246" s="1">
         <v>11</v>
@@ -13381,7 +13411,7 @@
         <v>0</v>
       </c>
       <c r="L246" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M246" s="20">
         <v>0</v>
@@ -13405,14 +13435,14 @@
         <v>1</v>
       </c>
       <c r="D247" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E247" s="15">
         <v>105300001</v>
       </c>
       <c r="F247" s="15"/>
       <c r="G247" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H247" s="1">
         <v>12</v>
@@ -13427,7 +13457,7 @@
         <v>0</v>
       </c>
       <c r="L247" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M247" s="20">
         <v>0</v>
@@ -13451,14 +13481,14 @@
         <v>1</v>
       </c>
       <c r="D248" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E248" s="15">
         <v>105100001</v>
       </c>
       <c r="F248" s="15"/>
       <c r="G248" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H248" s="1">
         <v>10</v>
@@ -13473,7 +13503,7 @@
         <v>0</v>
       </c>
       <c r="L248" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M248" s="20">
         <v>0</v>
@@ -13497,14 +13527,14 @@
         <v>1</v>
       </c>
       <c r="D249" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E249" s="15">
         <v>105100001</v>
       </c>
       <c r="F249" s="15"/>
       <c r="G249" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H249" s="1">
         <v>11</v>
@@ -13519,7 +13549,7 @@
         <v>0</v>
       </c>
       <c r="L249" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M249" s="20">
         <v>0</v>
@@ -13543,14 +13573,14 @@
         <v>1</v>
       </c>
       <c r="D250" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E250" s="15">
         <v>105100001</v>
       </c>
       <c r="F250" s="15"/>
       <c r="G250" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H250" s="1">
         <v>12</v>
@@ -13565,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="L250" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M250" s="20">
         <v>0</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\新建文件夹\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD1F749-0F5F-473E-BAFC-DFABEF91ADD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF667BFB-38F2-44A2-A58D-0A719F2CB8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="114">
   <si>
     <t>sid</t>
   </si>
@@ -511,13 +511,17 @@
   </si>
   <si>
     <t>9:999</t>
+  </si>
+  <si>
+    <t>1:0</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -594,6 +598,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -690,7 +702,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -769,6 +781,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5821,8 +5836,8 @@
       <c r="L101" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M101" s="26" t="s">
-        <v>99</v>
+      <c r="M101" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="N101" s="22">
         <v>100</v>
@@ -5869,8 +5884,8 @@
       <c r="L102" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M102" s="26" t="s">
-        <v>99</v>
+      <c r="M102" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="N102" s="22">
         <v>1000</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\新建文件夹\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF667BFB-38F2-44A2-A58D-0A719F2CB8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD1F749-0F5F-473E-BAFC-DFABEF91ADD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="113">
   <si>
     <t>sid</t>
   </si>
@@ -511,17 +511,13 @@
   </si>
   <si>
     <t>9:999</t>
-  </si>
-  <si>
-    <t>1:0</t>
-    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,14 +594,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -702,7 +690,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -781,9 +769,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5836,8 +5821,8 @@
       <c r="L101" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M101" s="27" t="s">
-        <v>113</v>
+      <c r="M101" s="26" t="s">
+        <v>99</v>
       </c>
       <c r="N101" s="22">
         <v>100</v>
@@ -5884,8 +5869,8 @@
       <c r="L102" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M102" s="27" t="s">
-        <v>113</v>
+      <c r="M102" s="26" t="s">
+        <v>99</v>
       </c>
       <c r="N102" s="22">
         <v>1000</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD1F749-0F5F-473E-BAFC-DFABEF91ADD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -33,19 +27,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -54,7 +47,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -65,14 +57,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -81,7 +72,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -89,14 +79,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -105,7 +94,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -114,40 +102,37 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最小准入金币</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>-1 表示无上限</t>
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -156,7 +141,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -172,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="114">
   <si>
     <t>sid</t>
   </si>
@@ -490,6 +474,9 @@
   </si>
   <si>
     <t>4:4</t>
+  </si>
+  <si>
+    <t>1:0</t>
   </si>
   <si>
     <t>俄罗斯轮盘</t>
@@ -516,8 +503,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -569,38 +562,173 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -609,42 +737,228 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7993408001953185"/>
+        <fgColor theme="5" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7993408001953185"/>
+        <fgColor theme="4" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -667,30 +981,272 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="12">
+  <cellStyleXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -707,13 +1263,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -731,6 +1287,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -758,6 +1317,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -768,32 +1330,79 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="60">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="常规 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="常规 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="常规 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="常规 6 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="常规 7" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2 2" xfId="50"/>
+    <cellStyle name="常规 2 2 2" xfId="51"/>
+    <cellStyle name="常规 3" xfId="52"/>
+    <cellStyle name="常规 3 2" xfId="53"/>
+    <cellStyle name="常规 4" xfId="54"/>
+    <cellStyle name="常规 5" xfId="55"/>
+    <cellStyle name="常规 6" xfId="56"/>
+    <cellStyle name="常规 6 2" xfId="57"/>
+    <cellStyle name="常规 6 2 2" xfId="58"/>
+    <cellStyle name="常规 7" xfId="59"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1051,13 +1660,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S182"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R182"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
@@ -1212,7 +1821,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25">
+    <row r="4" ht="14.25" spans="1:15">
       <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
@@ -1255,13 +1864,13 @@
       <c r="L5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="M5" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N5">
         <v>1000</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1302,13 +1911,13 @@
       <c r="L6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="26" t="s">
+      <c r="M6" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N6">
         <v>10000</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1349,13 +1958,13 @@
       <c r="L7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="M7" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N7">
         <v>100000</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1396,13 +2005,13 @@
       <c r="L8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="26" t="s">
+      <c r="M8" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N8">
         <v>1000</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1443,13 +2052,13 @@
       <c r="L9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M9" s="26" t="s">
+      <c r="M9" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N9">
         <v>10000</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1490,13 +2099,13 @@
       <c r="L10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N10">
         <v>100000</v>
       </c>
-      <c r="O10" s="14">
+      <c r="O10" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1537,13 +2146,13 @@
       <c r="L11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N11">
         <v>1000</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O11" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1584,13 +2193,13 @@
       <c r="L12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="26" t="s">
+      <c r="M12" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N12">
         <v>10000</v>
       </c>
-      <c r="O12" s="14">
+      <c r="O12" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1631,13 +2240,13 @@
       <c r="L13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="26" t="s">
+      <c r="M13" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N13">
         <v>100000</v>
       </c>
-      <c r="O13" s="14">
+      <c r="O13" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1678,13 +2287,13 @@
       <c r="L14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M14" s="26" t="s">
+      <c r="M14" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N14">
         <v>120</v>
       </c>
-      <c r="O14" s="14">
+      <c r="O14" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1725,13 +2334,13 @@
       <c r="L15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="26" t="s">
+      <c r="M15" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N15">
         <v>15000</v>
       </c>
-      <c r="O15" s="14">
+      <c r="O15" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1772,13 +2381,13 @@
       <c r="L16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M16" s="26" t="s">
+      <c r="M16" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N16">
         <v>150000</v>
       </c>
-      <c r="O16" s="14">
+      <c r="O16" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1819,13 +2428,13 @@
       <c r="L17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M17" s="26" t="s">
+      <c r="M17" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N17">
         <v>1000</v>
       </c>
-      <c r="O17" s="14">
+      <c r="O17" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1866,13 +2475,13 @@
       <c r="L18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M18" s="26" t="s">
+      <c r="M18" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N18">
         <v>10000</v>
       </c>
-      <c r="O18" s="14">
+      <c r="O18" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1913,13 +2522,13 @@
       <c r="L19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="26" t="s">
+      <c r="M19" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N19">
         <v>100000</v>
       </c>
-      <c r="O19" s="14">
+      <c r="O19" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1960,13 +2569,13 @@
       <c r="L20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M20" s="26" t="s">
+      <c r="M20" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N20">
         <v>100</v>
       </c>
-      <c r="O20" s="14">
+      <c r="O20" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2007,13 +2616,13 @@
       <c r="L21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M21" s="26" t="s">
+      <c r="M21" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N21">
         <v>10000</v>
       </c>
-      <c r="O21" s="14">
+      <c r="O21" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2054,13 +2663,13 @@
       <c r="L22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M22" s="26" t="s">
+      <c r="M22" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N22">
         <v>100000</v>
       </c>
-      <c r="O22" s="14">
+      <c r="O22" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2101,13 +2710,13 @@
       <c r="L23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M23" s="26" t="s">
+      <c r="M23" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N23">
         <v>1250</v>
       </c>
-      <c r="O23" s="14">
+      <c r="O23" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2148,13 +2757,13 @@
       <c r="L24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M24" s="26" t="s">
+      <c r="M24" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N24">
         <v>12500</v>
       </c>
-      <c r="O24" s="14">
+      <c r="O24" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2195,13 +2804,13 @@
       <c r="L25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M25" s="26" t="s">
+      <c r="M25" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N25">
         <v>125000</v>
       </c>
-      <c r="O25" s="14">
+      <c r="O25" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2242,13 +2851,13 @@
       <c r="L26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M26" s="26" t="s">
+      <c r="M26" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N26">
         <v>1000</v>
       </c>
-      <c r="O26" s="14">
+      <c r="O26" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2289,13 +2898,13 @@
       <c r="L27" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="26" t="s">
+      <c r="M27" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N27">
         <v>10000</v>
       </c>
-      <c r="O27" s="14">
+      <c r="O27" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2336,13 +2945,13 @@
       <c r="L28" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M28" s="26" t="s">
+      <c r="M28" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N28">
         <v>100000</v>
       </c>
-      <c r="O28" s="14">
+      <c r="O28" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2362,7 +2971,7 @@
       <c r="E29" s="13">
         <v>102100001</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="16" t="s">
         <v>52</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -2383,13 +2992,13 @@
       <c r="L29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M29" s="26" t="s">
+      <c r="M29" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N29">
         <v>1000</v>
       </c>
-      <c r="O29" s="14">
+      <c r="O29" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2409,7 +3018,7 @@
       <c r="E30" s="13">
         <v>102100001</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="16" t="s">
         <v>52</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -2430,13 +3039,13 @@
       <c r="L30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M30" s="26" t="s">
+      <c r="M30" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N30">
         <v>10000</v>
       </c>
-      <c r="O30" s="14">
+      <c r="O30" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2456,7 +3065,7 @@
       <c r="E31" s="13">
         <v>102100001</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="F31" s="16" t="s">
         <v>52</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -2477,13 +3086,13 @@
       <c r="L31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M31" s="26" t="s">
+      <c r="M31" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N31">
         <v>100000</v>
       </c>
-      <c r="O31" s="14">
+      <c r="O31" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2492,46 +3101,46 @@
         <f t="shared" ref="A32:A58" si="0">B32*10+H32</f>
         <v>1018001</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="16">
         <v>101800</v>
       </c>
-      <c r="C32" s="15">
-        <v>1</v>
-      </c>
-      <c r="D32" s="15" t="s">
+      <c r="C32" s="16">
+        <v>1</v>
+      </c>
+      <c r="D32" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="16">
         <v>101800001</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="17">
         <v>1</v>
       </c>
       <c r="I32" s="2">
         <v>0</v>
       </c>
-      <c r="J32" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K32" s="16">
+      <c r="J32" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K32" s="17">
         <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M32" s="26" t="s">
+      <c r="M32" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N32">
         <v>1000</v>
       </c>
-      <c r="O32" s="14">
+      <c r="O32" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2540,46 +3149,46 @@
         <f t="shared" si="0"/>
         <v>1018002</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="16">
         <v>101800</v>
       </c>
-      <c r="C33" s="15">
-        <v>1</v>
-      </c>
-      <c r="D33" s="15" t="s">
+      <c r="C33" s="16">
+        <v>1</v>
+      </c>
+      <c r="D33" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="16">
         <v>101800001</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="17">
         <v>2</v>
       </c>
       <c r="I33" s="2">
         <v>10000</v>
       </c>
-      <c r="J33" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K33" s="16">
+      <c r="J33" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K33" s="17">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M33" s="26" t="s">
+      <c r="M33" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N33">
         <v>10000</v>
       </c>
-      <c r="O33" s="14">
+      <c r="O33" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2588,46 +3197,46 @@
         <f t="shared" si="0"/>
         <v>1018003</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="16">
         <v>101800</v>
       </c>
-      <c r="C34" s="15">
-        <v>1</v>
-      </c>
-      <c r="D34" s="15" t="s">
+      <c r="C34" s="16">
+        <v>1</v>
+      </c>
+      <c r="D34" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="16">
         <v>101800001</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="17">
         <v>3</v>
       </c>
       <c r="I34" s="2">
         <v>100000</v>
       </c>
-      <c r="J34" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K34" s="16">
+      <c r="J34" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K34" s="17">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M34" s="26" t="s">
+      <c r="M34" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N34">
         <v>100000</v>
       </c>
-      <c r="O34" s="14">
+      <c r="O34" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2636,46 +3245,46 @@
         <f t="shared" si="0"/>
         <v>1025001</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="16">
         <v>102500</v>
       </c>
-      <c r="C35" s="15">
-        <v>1</v>
-      </c>
-      <c r="D35" s="15" t="s">
+      <c r="C35" s="16">
+        <v>1</v>
+      </c>
+      <c r="D35" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="16">
         <v>102500001</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="F35" s="16" t="s">
         <v>56</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="17">
         <v>1</v>
       </c>
       <c r="I35" s="2">
         <v>0</v>
       </c>
-      <c r="J35" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K35" s="16">
+      <c r="J35" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K35" s="17">
         <v>0</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M35" s="26" t="s">
+      <c r="M35" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N35">
         <v>1000</v>
       </c>
-      <c r="O35" s="14">
+      <c r="O35" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2684,46 +3293,46 @@
         <f t="shared" si="0"/>
         <v>1025002</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="16">
         <v>102500</v>
       </c>
-      <c r="C36" s="15">
-        <v>1</v>
-      </c>
-      <c r="D36" s="15" t="s">
+      <c r="C36" s="16">
+        <v>1</v>
+      </c>
+      <c r="D36" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="16">
         <v>102500001</v>
       </c>
-      <c r="F36" s="15" t="s">
+      <c r="F36" s="16" t="s">
         <v>56</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H36" s="17">
         <v>2</v>
       </c>
       <c r="I36" s="2">
         <v>10000</v>
       </c>
-      <c r="J36" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K36" s="16">
+      <c r="J36" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K36" s="17">
         <v>0</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M36" s="26" t="s">
+      <c r="M36" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N36">
         <v>10000</v>
       </c>
-      <c r="O36" s="14">
+      <c r="O36" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2732,46 +3341,46 @@
         <f t="shared" si="0"/>
         <v>1025003</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="16">
         <v>102500</v>
       </c>
-      <c r="C37" s="15">
-        <v>1</v>
-      </c>
-      <c r="D37" s="15" t="s">
+      <c r="C37" s="16">
+        <v>1</v>
+      </c>
+      <c r="D37" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="16">
         <v>102500001</v>
       </c>
-      <c r="F37" s="15" t="s">
+      <c r="F37" s="16" t="s">
         <v>56</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H37" s="16">
+      <c r="H37" s="17">
         <v>3</v>
       </c>
       <c r="I37" s="2">
         <v>100000</v>
       </c>
-      <c r="J37" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K37" s="16">
+      <c r="J37" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K37" s="17">
         <v>0</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M37" s="26" t="s">
+      <c r="M37" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N37">
         <v>100000</v>
       </c>
-      <c r="O37" s="14">
+      <c r="O37" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2804,22 +3413,22 @@
       <c r="I38" s="2">
         <v>0</v>
       </c>
-      <c r="J38" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K38" s="16">
+      <c r="J38" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K38" s="17">
         <v>0</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M38" s="26" t="s">
+      <c r="M38" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N38">
         <v>1000</v>
       </c>
-      <c r="O38" s="14">
+      <c r="O38" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2852,22 +3461,22 @@
       <c r="I39" s="2">
         <v>10000</v>
       </c>
-      <c r="J39" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K39" s="16">
+      <c r="J39" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K39" s="17">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M39" s="26" t="s">
+      <c r="M39" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N39">
         <v>10000</v>
       </c>
-      <c r="O39" s="14">
+      <c r="O39" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2900,22 +3509,22 @@
       <c r="I40" s="2">
         <v>100000</v>
       </c>
-      <c r="J40" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K40" s="16">
+      <c r="J40" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K40" s="17">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M40" s="26" t="s">
+      <c r="M40" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N40">
         <v>100000</v>
       </c>
-      <c r="O40" s="14">
+      <c r="O40" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2935,7 +3544,7 @@
       <c r="E41" s="13">
         <v>103000001</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="18" t="s">
         <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -2947,22 +3556,22 @@
       <c r="I41" s="2">
         <v>0</v>
       </c>
-      <c r="J41" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K41" s="16">
+      <c r="J41" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K41" s="17">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M41" s="26" t="s">
+      <c r="M41" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N41">
         <v>100</v>
       </c>
-      <c r="O41" s="14">
+      <c r="O41" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2983,7 +3592,7 @@
       <c r="E42" s="13">
         <v>103000001</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="18" t="s">
         <v>60</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -2995,22 +3604,22 @@
       <c r="I42" s="2">
         <v>10000</v>
       </c>
-      <c r="J42" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K42" s="16">
+      <c r="J42" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K42" s="17">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M42" s="26" t="s">
+      <c r="M42" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N42">
         <v>10000</v>
       </c>
-      <c r="O42" s="14">
+      <c r="O42" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3031,7 +3640,7 @@
       <c r="E43" s="13">
         <v>103000001</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="18" t="s">
         <v>60</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -3043,22 +3652,22 @@
       <c r="I43" s="2">
         <v>100000</v>
       </c>
-      <c r="J43" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K43" s="16">
+      <c r="J43" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K43" s="17">
         <v>0</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M43" s="26" t="s">
+      <c r="M43" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N43">
         <v>100000</v>
       </c>
-      <c r="O43" s="14">
+      <c r="O43" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3091,22 +3700,22 @@
       <c r="I44" s="2">
         <v>0</v>
       </c>
-      <c r="J44" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K44" s="16">
+      <c r="J44" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K44" s="17">
         <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M44" s="26" t="s">
+      <c r="M44" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N44">
         <v>1000</v>
       </c>
-      <c r="O44" s="14">
+      <c r="O44" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3139,22 +3748,22 @@
       <c r="I45" s="2">
         <v>10000</v>
       </c>
-      <c r="J45" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K45" s="16">
+      <c r="J45" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K45" s="17">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M45" s="26" t="s">
+      <c r="M45" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N45">
         <v>10000</v>
       </c>
-      <c r="O45" s="14">
+      <c r="O45" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3187,22 +3796,22 @@
       <c r="I46" s="2">
         <v>100000</v>
       </c>
-      <c r="J46" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K46" s="16">
+      <c r="J46" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K46" s="17">
         <v>0</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M46" s="26" t="s">
+      <c r="M46" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N46">
         <v>100000</v>
       </c>
-      <c r="O46" s="14">
+      <c r="O46" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3235,7 +3844,7 @@
       <c r="I47" s="2">
         <v>0</v>
       </c>
-      <c r="J47" s="16">
+      <c r="J47" s="17">
         <v>-1</v>
       </c>
       <c r="K47" s="1">
@@ -3244,13 +3853,13 @@
       <c r="L47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M47" s="26" t="s">
+      <c r="M47" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N47">
         <v>1000</v>
       </c>
-      <c r="O47" s="14">
+      <c r="O47" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3283,7 +3892,7 @@
       <c r="I48" s="2">
         <v>10000</v>
       </c>
-      <c r="J48" s="16">
+      <c r="J48" s="17">
         <v>-1</v>
       </c>
       <c r="K48" s="1">
@@ -3292,13 +3901,13 @@
       <c r="L48" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M48" s="26" t="s">
+      <c r="M48" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N48">
         <v>10000</v>
       </c>
-      <c r="O48" s="14">
+      <c r="O48" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3331,7 +3940,7 @@
       <c r="I49" s="2">
         <v>100000</v>
       </c>
-      <c r="J49" s="16">
+      <c r="J49" s="17">
         <v>-1</v>
       </c>
       <c r="K49" s="1">
@@ -3340,13 +3949,13 @@
       <c r="L49" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M49" s="26" t="s">
+      <c r="M49" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N49">
         <v>100000</v>
       </c>
-      <c r="O49" s="14">
+      <c r="O49" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3379,7 +3988,7 @@
       <c r="I50" s="2">
         <v>0</v>
       </c>
-      <c r="J50" s="16">
+      <c r="J50" s="17">
         <v>-1</v>
       </c>
       <c r="K50" s="1">
@@ -3388,13 +3997,13 @@
       <c r="L50" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M50" s="26" t="s">
+      <c r="M50" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N50">
         <v>1125</v>
       </c>
-      <c r="O50" s="14">
+      <c r="O50" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3427,7 +4036,7 @@
       <c r="I51" s="2">
         <v>10000</v>
       </c>
-      <c r="J51" s="16">
+      <c r="J51" s="17">
         <v>-1</v>
       </c>
       <c r="K51" s="1">
@@ -3436,13 +4045,13 @@
       <c r="L51" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M51" s="26" t="s">
+      <c r="M51" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N51">
         <v>11250</v>
       </c>
-      <c r="O51" s="14">
+      <c r="O51" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3475,7 +4084,7 @@
       <c r="I52" s="2">
         <v>100000</v>
       </c>
-      <c r="J52" s="16">
+      <c r="J52" s="17">
         <v>-1</v>
       </c>
       <c r="K52" s="1">
@@ -3484,13 +4093,13 @@
       <c r="L52" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M52" s="26" t="s">
+      <c r="M52" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N52">
         <v>112500</v>
       </c>
-      <c r="O52" s="14">
+      <c r="O52" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3523,7 +4132,7 @@
       <c r="I53" s="2">
         <v>0</v>
       </c>
-      <c r="J53" s="16">
+      <c r="J53" s="17">
         <v>-1</v>
       </c>
       <c r="K53" s="1">
@@ -3532,13 +4141,13 @@
       <c r="L53" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M53" s="26" t="s">
+      <c r="M53" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N53">
         <v>1000</v>
       </c>
-      <c r="O53" s="14">
+      <c r="O53" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3571,7 +4180,7 @@
       <c r="I54" s="2">
         <v>10000</v>
       </c>
-      <c r="J54" s="16">
+      <c r="J54" s="17">
         <v>-1</v>
       </c>
       <c r="K54" s="1">
@@ -3580,13 +4189,13 @@
       <c r="L54" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M54" s="26" t="s">
+      <c r="M54" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N54">
         <v>10000</v>
       </c>
-      <c r="O54" s="14">
+      <c r="O54" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3619,7 +4228,7 @@
       <c r="I55" s="2">
         <v>100000</v>
       </c>
-      <c r="J55" s="16">
+      <c r="J55" s="17">
         <v>-1</v>
       </c>
       <c r="K55" s="1">
@@ -3628,13 +4237,13 @@
       <c r="L55" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M55" s="26" t="s">
+      <c r="M55" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N55">
         <v>100000</v>
       </c>
-      <c r="O55" s="14">
+      <c r="O55" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3667,7 +4276,7 @@
       <c r="I56" s="2">
         <v>0</v>
       </c>
-      <c r="J56" s="16">
+      <c r="J56" s="17">
         <v>-1</v>
       </c>
       <c r="K56" s="1">
@@ -3676,13 +4285,13 @@
       <c r="L56" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M56" s="26" t="s">
+      <c r="M56" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N56">
         <v>1000</v>
       </c>
-      <c r="O56" s="14">
+      <c r="O56" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3715,7 +4324,7 @@
       <c r="I57" s="2">
         <v>10000</v>
       </c>
-      <c r="J57" s="16">
+      <c r="J57" s="17">
         <v>-1</v>
       </c>
       <c r="K57" s="1">
@@ -3724,13 +4333,13 @@
       <c r="L57" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M57" s="26" t="s">
+      <c r="M57" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N57">
         <v>10000</v>
       </c>
-      <c r="O57" s="14">
+      <c r="O57" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3763,7 +4372,7 @@
       <c r="I58" s="2">
         <v>100000</v>
       </c>
-      <c r="J58" s="16">
+      <c r="J58" s="17">
         <v>-1</v>
       </c>
       <c r="K58" s="1">
@@ -3772,13 +4381,13 @@
       <c r="L58" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M58" s="26" t="s">
+      <c r="M58" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N58">
         <v>100000</v>
       </c>
-      <c r="O58" s="14">
+      <c r="O58" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3810,7 +4419,7 @@
       <c r="I59" s="2">
         <v>0</v>
       </c>
-      <c r="J59" s="16">
+      <c r="J59" s="17">
         <v>-1</v>
       </c>
       <c r="K59" s="1">
@@ -3819,13 +4428,13 @@
       <c r="L59" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M59" s="26" t="s">
+      <c r="M59" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N59">
         <v>1000</v>
       </c>
-      <c r="O59" s="14">
+      <c r="O59" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3857,7 +4466,7 @@
       <c r="I60" s="2">
         <v>10000</v>
       </c>
-      <c r="J60" s="16">
+      <c r="J60" s="17">
         <v>-1</v>
       </c>
       <c r="K60" s="1">
@@ -3866,13 +4475,13 @@
       <c r="L60" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M60" s="26" t="s">
+      <c r="M60" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N60">
         <v>10000</v>
       </c>
-      <c r="O60" s="14">
+      <c r="O60" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3904,7 +4513,7 @@
       <c r="I61" s="2">
         <v>100000</v>
       </c>
-      <c r="J61" s="16">
+      <c r="J61" s="17">
         <v>-1</v>
       </c>
       <c r="K61" s="1">
@@ -3913,13 +4522,13 @@
       <c r="L61" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M61" s="26" t="s">
+      <c r="M61" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N61">
         <v>100000</v>
       </c>
-      <c r="O61" s="14">
+      <c r="O61" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3951,7 +4560,7 @@
       <c r="I62" s="2">
         <v>0</v>
       </c>
-      <c r="J62" s="16">
+      <c r="J62" s="17">
         <v>-1</v>
       </c>
       <c r="K62" s="1">
@@ -3960,13 +4569,13 @@
       <c r="L62" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M62" s="26" t="s">
+      <c r="M62" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N62">
         <v>1000</v>
       </c>
-      <c r="O62" s="14">
+      <c r="O62" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -3998,7 +4607,7 @@
       <c r="I63" s="2">
         <v>10000</v>
       </c>
-      <c r="J63" s="16">
+      <c r="J63" s="17">
         <v>-1</v>
       </c>
       <c r="K63" s="1">
@@ -4007,13 +4616,13 @@
       <c r="L63" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M63" s="26" t="s">
+      <c r="M63" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N63">
         <v>10000</v>
       </c>
-      <c r="O63" s="14">
+      <c r="O63" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4045,7 +4654,7 @@
       <c r="I64" s="2">
         <v>100000</v>
       </c>
-      <c r="J64" s="16">
+      <c r="J64" s="17">
         <v>-1</v>
       </c>
       <c r="K64" s="1">
@@ -4054,13 +4663,13 @@
       <c r="L64" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M64" s="26" t="s">
+      <c r="M64" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N64">
         <v>100000</v>
       </c>
-      <c r="O64" s="14">
+      <c r="O64" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4080,7 +4689,7 @@
       <c r="E65" s="13">
         <v>104000001</v>
       </c>
-      <c r="F65" s="18" t="s">
+      <c r="F65" s="19" t="s">
         <v>76</v>
       </c>
       <c r="G65" s="1" t="s">
@@ -4092,7 +4701,7 @@
       <c r="I65" s="2">
         <v>0</v>
       </c>
-      <c r="J65" s="16">
+      <c r="J65" s="17">
         <v>-1</v>
       </c>
       <c r="K65" s="1">
@@ -4101,13 +4710,13 @@
       <c r="L65" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M65" s="26" t="s">
+      <c r="M65" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N65">
         <v>1000</v>
       </c>
-      <c r="O65" s="14">
+      <c r="O65" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4127,7 +4736,7 @@
       <c r="E66" s="13">
         <v>104000001</v>
       </c>
-      <c r="F66" s="18" t="s">
+      <c r="F66" s="19" t="s">
         <v>76</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -4139,7 +4748,7 @@
       <c r="I66" s="2">
         <v>10000</v>
       </c>
-      <c r="J66" s="16">
+      <c r="J66" s="17">
         <v>-1</v>
       </c>
       <c r="K66" s="1">
@@ -4148,13 +4757,13 @@
       <c r="L66" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M66" s="26" t="s">
+      <c r="M66" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N66">
         <v>10000</v>
       </c>
-      <c r="O66" s="14">
+      <c r="O66" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4174,7 +4783,7 @@
       <c r="E67" s="13">
         <v>104000001</v>
       </c>
-      <c r="F67" s="18" t="s">
+      <c r="F67" s="19" t="s">
         <v>76</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -4186,7 +4795,7 @@
       <c r="I67" s="2">
         <v>100000</v>
       </c>
-      <c r="J67" s="16">
+      <c r="J67" s="17">
         <v>-1</v>
       </c>
       <c r="K67" s="1">
@@ -4195,13 +4804,13 @@
       <c r="L67" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M67" s="26" t="s">
+      <c r="M67" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N67">
         <v>100000</v>
       </c>
-      <c r="O67" s="14">
+      <c r="O67" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4242,13 +4851,13 @@
       <c r="L68" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M68" s="26" t="s">
+      <c r="M68" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N68">
         <v>1000</v>
       </c>
-      <c r="O68" s="14">
+      <c r="O68" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4289,13 +4898,13 @@
       <c r="L69" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M69" s="26" t="s">
+      <c r="M69" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N69">
         <v>10000</v>
       </c>
-      <c r="O69" s="14">
+      <c r="O69" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4336,13 +4945,13 @@
       <c r="L70" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M70" s="26" t="s">
+      <c r="M70" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N70">
         <v>100000</v>
       </c>
-      <c r="O70" s="14">
+      <c r="O70" s="15">
         <v>1990000</v>
       </c>
       <c r="Q70"/>
@@ -4384,13 +4993,13 @@
       <c r="L71" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M71" s="26" t="s">
+      <c r="M71" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N71">
         <v>1000</v>
       </c>
-      <c r="O71" s="14">
+      <c r="O71" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4431,13 +5040,13 @@
       <c r="L72" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M72" s="26" t="s">
+      <c r="M72" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N72">
         <v>10000</v>
       </c>
-      <c r="O72" s="14">
+      <c r="O72" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4478,13 +5087,13 @@
       <c r="L73" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M73" s="26" t="s">
+      <c r="M73" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N73">
         <v>100000</v>
       </c>
-      <c r="O73" s="14">
+      <c r="O73" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4525,13 +5134,13 @@
       <c r="L74" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M74" s="26" t="s">
+      <c r="M74" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N74">
         <v>1000</v>
       </c>
-      <c r="O74" s="14">
+      <c r="O74" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4572,13 +5181,13 @@
       <c r="L75" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M75" s="26" t="s">
+      <c r="M75" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N75">
         <v>10000</v>
       </c>
-      <c r="O75" s="14">
+      <c r="O75" s="15">
         <v>1990000</v>
       </c>
       <c r="Q75" s="2"/>
@@ -4621,13 +5230,13 @@
       <c r="L76" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M76" s="26" t="s">
+      <c r="M76" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N76">
         <v>100000</v>
       </c>
-      <c r="O76" s="14">
+      <c r="O76" s="15">
         <v>1990000</v>
       </c>
       <c r="Q76" s="2"/>
@@ -4670,13 +5279,13 @@
       <c r="L77" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M77" s="26" t="s">
+      <c r="M77" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N77">
         <v>1000</v>
       </c>
-      <c r="O77" s="14">
+      <c r="O77" s="15">
         <v>1990000</v>
       </c>
       <c r="Q77" s="2"/>
@@ -4719,13 +5328,13 @@
       <c r="L78" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M78" s="26" t="s">
+      <c r="M78" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N78">
         <v>10000</v>
       </c>
-      <c r="O78" s="14">
+      <c r="O78" s="15">
         <v>1990000</v>
       </c>
       <c r="Q78" s="2"/>
@@ -4768,13 +5377,13 @@
       <c r="L79" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M79" s="26" t="s">
+      <c r="M79" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N79">
         <v>100000</v>
       </c>
-      <c r="O79" s="14">
+      <c r="O79" s="15">
         <v>1990000</v>
       </c>
       <c r="Q79" s="2"/>
@@ -4817,13 +5426,13 @@
       <c r="L80" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M80" s="26" t="s">
+      <c r="M80" s="28" t="s">
         <v>87</v>
       </c>
       <c r="N80">
         <v>1000</v>
       </c>
-      <c r="O80" s="14">
+      <c r="O80" s="15">
         <v>1990000</v>
       </c>
       <c r="Q80" s="2"/>
@@ -4866,13 +5475,13 @@
       <c r="L81" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M81" s="26" t="s">
+      <c r="M81" s="28" t="s">
         <v>87</v>
       </c>
       <c r="N81">
         <v>10000</v>
       </c>
-      <c r="O81" s="14">
+      <c r="O81" s="15">
         <v>1990000</v>
       </c>
       <c r="Q81" s="2"/>
@@ -4915,13 +5524,13 @@
       <c r="L82" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M82" s="26" t="s">
+      <c r="M82" s="28" t="s">
         <v>87</v>
       </c>
       <c r="N82">
         <v>100000</v>
       </c>
-      <c r="O82" s="14">
+      <c r="O82" s="15">
         <v>1990000</v>
       </c>
       <c r="Q82" s="2"/>
@@ -4964,13 +5573,13 @@
       <c r="L83" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M83" s="26" t="s">
+      <c r="M83" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N83">
         <v>1000</v>
       </c>
-      <c r="O83" s="14">
+      <c r="O83" s="15">
         <v>1990000</v>
       </c>
       <c r="Q83" s="2"/>
@@ -5013,13 +5622,13 @@
       <c r="L84" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M84" s="26" t="s">
+      <c r="M84" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N84">
         <v>10000</v>
       </c>
-      <c r="O84" s="14">
+      <c r="O84" s="15">
         <v>1990000</v>
       </c>
       <c r="Q84" s="2"/>
@@ -5062,13 +5671,13 @@
       <c r="L85" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M85" s="26" t="s">
+      <c r="M85" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N85">
         <v>100000</v>
       </c>
-      <c r="O85" s="14">
+      <c r="O85" s="15">
         <v>1990000</v>
       </c>
       <c r="Q85" s="2"/>
@@ -5111,13 +5720,13 @@
       <c r="L86" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M86" s="26" t="s">
+      <c r="M86" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N86">
         <v>1000</v>
       </c>
-      <c r="O86" s="14">
+      <c r="O86" s="15">
         <v>1990000</v>
       </c>
       <c r="Q86" s="2"/>
@@ -5160,13 +5769,13 @@
       <c r="L87" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M87" s="26" t="s">
+      <c r="M87" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N87">
         <v>10000</v>
       </c>
-      <c r="O87" s="14">
+      <c r="O87" s="15">
         <v>1990000</v>
       </c>
       <c r="Q87" s="2"/>
@@ -5209,13 +5818,13 @@
       <c r="L88" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M88" s="26" t="s">
+      <c r="M88" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N88">
         <v>100000</v>
       </c>
-      <c r="O88" s="14">
+      <c r="O88" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5256,13 +5865,13 @@
       <c r="L89" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M89" s="26" t="s">
+      <c r="M89" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N89">
         <v>1000</v>
       </c>
-      <c r="O89" s="14">
+      <c r="O89" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5303,13 +5912,13 @@
       <c r="L90" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M90" s="26" t="s">
+      <c r="M90" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N90">
         <v>10000</v>
       </c>
-      <c r="O90" s="14">
+      <c r="O90" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5350,13 +5959,13 @@
       <c r="L91" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M91" s="26" t="s">
+      <c r="M91" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N91">
         <v>100000</v>
       </c>
-      <c r="O91" s="14">
+      <c r="O91" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5364,13 +5973,13 @@
       <c r="A92" s="1">
         <v>2009001</v>
       </c>
-      <c r="B92" s="19">
+      <c r="B92" s="20">
         <v>200900</v>
       </c>
       <c r="C92" s="4">
         <v>2</v>
       </c>
-      <c r="D92" s="19" t="s">
+      <c r="D92" s="20" t="s">
         <v>94</v>
       </c>
       <c r="E92" s="13">
@@ -5397,13 +6006,13 @@
       <c r="L92" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M92" s="26" t="s">
+      <c r="M92" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N92">
         <v>1000</v>
       </c>
-      <c r="O92" s="14">
+      <c r="O92" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5444,13 +6053,13 @@
       <c r="L93" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M93" s="26" t="s">
+      <c r="M93" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N93">
         <v>10000</v>
       </c>
-      <c r="O93" s="14">
+      <c r="O93" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5491,13 +6100,13 @@
       <c r="L94" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M94" s="26" t="s">
+      <c r="M94" s="28" t="s">
         <v>34</v>
       </c>
       <c r="N94">
         <v>100000</v>
       </c>
-      <c r="O94" s="14">
+      <c r="O94" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5538,13 +6147,13 @@
       <c r="L95" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="M95" s="26" t="s">
+      <c r="M95" s="28" t="s">
         <v>99</v>
       </c>
       <c r="N95">
         <v>1000</v>
       </c>
-      <c r="O95" s="14">
+      <c r="O95" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5585,13 +6194,13 @@
       <c r="L96" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="M96" s="26" t="s">
+      <c r="M96" s="28" t="s">
         <v>99</v>
       </c>
       <c r="N96">
         <v>10000</v>
       </c>
-      <c r="O96" s="14">
+      <c r="O96" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5632,13 +6241,13 @@
       <c r="L97" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="M97" s="26" t="s">
+      <c r="M97" s="28" t="s">
         <v>99</v>
       </c>
       <c r="N97">
         <v>100000</v>
       </c>
-      <c r="O97" s="14">
+      <c r="O97" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5679,13 +6288,13 @@
       <c r="L98" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="M98" s="26" t="s">
+      <c r="M98" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="N98" s="20">
+      <c r="N98" s="21">
         <v>1000</v>
       </c>
-      <c r="O98" s="14">
+      <c r="O98" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5726,13 +6335,13 @@
       <c r="L99" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="M99" s="26" t="s">
+      <c r="M99" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="N99" s="20">
+      <c r="N99" s="21">
         <v>10000</v>
       </c>
-      <c r="O99" s="14">
+      <c r="O99" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5773,13 +6382,13 @@
       <c r="L100" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="M100" s="26" t="s">
+      <c r="M100" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="N100" s="20">
+      <c r="N100" s="21">
         <v>100000</v>
       </c>
-      <c r="O100" s="14">
+      <c r="O100" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5799,7 +6408,7 @@
       <c r="E101" s="13">
         <v>300400001</v>
       </c>
-      <c r="F101" s="21" t="s">
+      <c r="F101" s="22" t="s">
         <v>104</v>
       </c>
       <c r="G101" s="1" t="s">
@@ -5808,7 +6417,7 @@
       <c r="H101" s="1">
         <v>1</v>
       </c>
-      <c r="I101" s="22">
+      <c r="I101" s="23">
         <f>N101*52</f>
         <v>5200</v>
       </c>
@@ -5821,13 +6430,13 @@
       <c r="L101" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M101" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="N101" s="22">
+      <c r="M101" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="N101" s="23">
         <v>100</v>
       </c>
-      <c r="O101" s="14">
+      <c r="O101" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5847,7 +6456,7 @@
       <c r="E102" s="13">
         <v>300400001</v>
       </c>
-      <c r="F102" s="21" t="s">
+      <c r="F102" s="22" t="s">
         <v>104</v>
       </c>
       <c r="G102" s="1" t="s">
@@ -5856,7 +6465,7 @@
       <c r="H102" s="1">
         <v>2</v>
       </c>
-      <c r="I102" s="22">
+      <c r="I102" s="23">
         <f>N102*52</f>
         <v>52000</v>
       </c>
@@ -5869,13 +6478,13 @@
       <c r="L102" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M102" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="N102" s="22">
+      <c r="M102" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="N102" s="23">
         <v>1000</v>
       </c>
-      <c r="O102" s="14">
+      <c r="O102" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5895,7 +6504,7 @@
       <c r="E103" s="13">
         <v>300400001</v>
       </c>
-      <c r="F103" s="21" t="s">
+      <c r="F103" s="22" t="s">
         <v>104</v>
       </c>
       <c r="G103" s="1" t="s">
@@ -5904,7 +6513,7 @@
       <c r="H103" s="1">
         <v>3</v>
       </c>
-      <c r="I103" s="22">
+      <c r="I103" s="23">
         <f>N103*52</f>
         <v>520000</v>
       </c>
@@ -5917,13 +6526,13 @@
       <c r="L103" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M103" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="N103" s="22">
+      <c r="M103" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="N103" s="23">
         <v>10000</v>
       </c>
-      <c r="O103" s="14">
+      <c r="O103" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5938,13 +6547,13 @@
         <v>2</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E104" s="13">
         <v>201200001</v>
       </c>
-      <c r="F104" s="21" t="s">
-        <v>107</v>
+      <c r="F104" s="22" t="s">
+        <v>108</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>32</v>
@@ -5964,13 +6573,13 @@
       <c r="L104" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M104" s="26" t="s">
+      <c r="M104" s="28" t="s">
         <v>87</v>
       </c>
       <c r="N104">
         <v>1000</v>
       </c>
-      <c r="O104" s="14">
+      <c r="O104" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -5985,13 +6594,13 @@
         <v>2</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E105" s="13">
         <v>201200001</v>
       </c>
-      <c r="F105" s="21" t="s">
-        <v>107</v>
+      <c r="F105" s="22" t="s">
+        <v>108</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>35</v>
@@ -6011,13 +6620,13 @@
       <c r="L105" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M105" s="26" t="s">
+      <c r="M105" s="28" t="s">
         <v>87</v>
       </c>
       <c r="N105">
         <v>10000</v>
       </c>
-      <c r="O105" s="14">
+      <c r="O105" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -6032,13 +6641,13 @@
         <v>2</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E106" s="13">
         <v>201200001</v>
       </c>
-      <c r="F106" s="21" t="s">
-        <v>107</v>
+      <c r="F106" s="22" t="s">
+        <v>108</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>36</v>
@@ -6058,13 +6667,13 @@
       <c r="L106" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M106" s="26" t="s">
+      <c r="M106" s="28" t="s">
         <v>87</v>
       </c>
       <c r="N106">
         <v>100000</v>
       </c>
-      <c r="O106" s="14">
+      <c r="O106" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -6072,46 +6681,46 @@
       <c r="A107" s="1">
         <v>20010010</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B107" s="16">
         <v>200100</v>
       </c>
-      <c r="C107" s="15">
+      <c r="C107" s="16">
         <v>2</v>
       </c>
-      <c r="D107" s="15" t="s">
+      <c r="D107" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E107" s="15">
+      <c r="E107" s="16">
         <v>200100038</v>
       </c>
-      <c r="F107" s="15" t="s">
+      <c r="F107" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="G107" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H107" s="16">
+      <c r="G107" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H107" s="17">
         <v>10</v>
       </c>
-      <c r="I107" s="23">
-        <v>0</v>
-      </c>
-      <c r="J107" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K107" s="16">
-        <v>0</v>
-      </c>
-      <c r="L107" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M107" s="16">
+      <c r="I107" s="25">
+        <v>0</v>
+      </c>
+      <c r="J107" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K107" s="17">
+        <v>0</v>
+      </c>
+      <c r="L107" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M107" s="17">
         <v>0</v>
       </c>
       <c r="N107">
         <v>1000</v>
       </c>
-      <c r="O107" s="25">
+      <c r="O107" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6119,46 +6728,46 @@
       <c r="A108" s="1">
         <v>20010011</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B108" s="16">
         <v>200100</v>
       </c>
-      <c r="C108" s="15">
+      <c r="C108" s="16">
         <v>2</v>
       </c>
-      <c r="D108" s="15" t="s">
+      <c r="D108" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E108" s="15">
+      <c r="E108" s="16">
         <v>200100038</v>
       </c>
-      <c r="F108" s="15" t="s">
+      <c r="F108" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="G108" s="16" t="s">
+      <c r="G108" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H108" s="17">
+        <v>11</v>
+      </c>
+      <c r="I108" s="25">
+        <v>0</v>
+      </c>
+      <c r="J108" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K108" s="17">
+        <v>0</v>
+      </c>
+      <c r="L108" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H108" s="16">
-        <v>11</v>
-      </c>
-      <c r="I108" s="23">
-        <v>0</v>
-      </c>
-      <c r="J108" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K108" s="16">
-        <v>0</v>
-      </c>
-      <c r="L108" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M108" s="16">
+      <c r="M108" s="17">
         <v>0</v>
       </c>
       <c r="N108">
         <v>10000</v>
       </c>
-      <c r="O108" s="25">
+      <c r="O108" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6166,46 +6775,46 @@
       <c r="A109" s="1">
         <v>20010012</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B109" s="16">
         <v>200100</v>
       </c>
-      <c r="C109" s="15">
+      <c r="C109" s="16">
         <v>2</v>
       </c>
-      <c r="D109" s="15" t="s">
+      <c r="D109" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E109" s="15">
+      <c r="E109" s="16">
         <v>200100038</v>
       </c>
-      <c r="F109" s="15" t="s">
+      <c r="F109" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="G109" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H109" s="16">
+      <c r="G109" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H109" s="17">
         <v>12</v>
       </c>
-      <c r="I109" s="23">
-        <v>0</v>
-      </c>
-      <c r="J109" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K109" s="16">
-        <v>0</v>
-      </c>
-      <c r="L109" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M109" s="16">
+      <c r="I109" s="25">
+        <v>0</v>
+      </c>
+      <c r="J109" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K109" s="17">
+        <v>0</v>
+      </c>
+      <c r="L109" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M109" s="17">
         <v>0</v>
       </c>
       <c r="N109">
         <v>100000</v>
       </c>
-      <c r="O109" s="25">
+      <c r="O109" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6213,46 +6822,46 @@
       <c r="A110" s="1">
         <v>20010110</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B110" s="16">
         <v>200101</v>
       </c>
-      <c r="C110" s="15">
+      <c r="C110" s="16">
         <v>2</v>
       </c>
-      <c r="D110" s="15" t="s">
+      <c r="D110" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E110" s="15">
+      <c r="E110" s="16">
         <v>200101001</v>
       </c>
-      <c r="F110" s="15" t="s">
+      <c r="F110" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G110" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H110" s="16">
+      <c r="G110" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H110" s="17">
         <v>10</v>
       </c>
-      <c r="I110" s="23">
-        <v>0</v>
-      </c>
-      <c r="J110" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K110" s="16">
-        <v>0</v>
-      </c>
-      <c r="L110" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M110" s="16">
+      <c r="I110" s="25">
+        <v>0</v>
+      </c>
+      <c r="J110" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K110" s="17">
+        <v>0</v>
+      </c>
+      <c r="L110" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M110" s="17">
         <v>0</v>
       </c>
       <c r="N110">
         <v>1000</v>
       </c>
-      <c r="O110" s="25">
+      <c r="O110" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6260,46 +6869,46 @@
       <c r="A111" s="1">
         <v>20010111</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B111" s="16">
         <v>200101</v>
       </c>
-      <c r="C111" s="15">
+      <c r="C111" s="16">
         <v>2</v>
       </c>
-      <c r="D111" s="15" t="s">
+      <c r="D111" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E111" s="15">
+      <c r="E111" s="16">
         <v>200101001</v>
       </c>
-      <c r="F111" s="15" t="s">
+      <c r="F111" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G111" s="16" t="s">
+      <c r="G111" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H111" s="17">
+        <v>11</v>
+      </c>
+      <c r="I111" s="25">
+        <v>0</v>
+      </c>
+      <c r="J111" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K111" s="17">
+        <v>0</v>
+      </c>
+      <c r="L111" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H111" s="16">
-        <v>11</v>
-      </c>
-      <c r="I111" s="23">
-        <v>0</v>
-      </c>
-      <c r="J111" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K111" s="16">
-        <v>0</v>
-      </c>
-      <c r="L111" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M111" s="16">
+      <c r="M111" s="17">
         <v>0</v>
       </c>
       <c r="N111">
         <v>10000</v>
       </c>
-      <c r="O111" s="25">
+      <c r="O111" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6307,46 +6916,46 @@
       <c r="A112" s="1">
         <v>20010112</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B112" s="16">
         <v>200101</v>
       </c>
-      <c r="C112" s="15">
+      <c r="C112" s="16">
         <v>2</v>
       </c>
-      <c r="D112" s="15" t="s">
+      <c r="D112" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E112" s="15">
+      <c r="E112" s="16">
         <v>200101001</v>
       </c>
-      <c r="F112" s="15" t="s">
+      <c r="F112" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G112" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H112" s="16">
+      <c r="G112" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H112" s="17">
         <v>12</v>
       </c>
-      <c r="I112" s="23">
-        <v>0</v>
-      </c>
-      <c r="J112" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K112" s="16">
-        <v>0</v>
-      </c>
-      <c r="L112" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M112" s="16">
+      <c r="I112" s="25">
+        <v>0</v>
+      </c>
+      <c r="J112" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K112" s="17">
+        <v>0</v>
+      </c>
+      <c r="L112" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M112" s="17">
         <v>0</v>
       </c>
       <c r="N112">
         <v>100000</v>
       </c>
-      <c r="O112" s="25">
+      <c r="O112" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6354,46 +6963,46 @@
       <c r="A113" s="1">
         <v>20030010</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B113" s="16">
         <v>200300</v>
       </c>
-      <c r="C113" s="15">
+      <c r="C113" s="16">
         <v>2</v>
       </c>
-      <c r="D113" s="15" t="s">
+      <c r="D113" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E113" s="15">
+      <c r="E113" s="16">
         <v>200300001</v>
       </c>
-      <c r="F113" s="15" t="s">
+      <c r="F113" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="G113" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H113" s="16">
+      <c r="G113" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H113" s="17">
         <v>10</v>
       </c>
-      <c r="I113" s="23">
-        <v>0</v>
-      </c>
-      <c r="J113" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K113" s="16">
-        <v>0</v>
-      </c>
-      <c r="L113" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M113" s="16">
+      <c r="I113" s="25">
+        <v>0</v>
+      </c>
+      <c r="J113" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K113" s="17">
+        <v>0</v>
+      </c>
+      <c r="L113" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M113" s="17">
         <v>0</v>
       </c>
       <c r="N113">
         <v>1000</v>
       </c>
-      <c r="O113" s="25">
+      <c r="O113" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6401,46 +7010,46 @@
       <c r="A114" s="1">
         <v>20030011</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B114" s="16">
         <v>200300</v>
       </c>
-      <c r="C114" s="15">
+      <c r="C114" s="16">
         <v>2</v>
       </c>
-      <c r="D114" s="15" t="s">
+      <c r="D114" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E114" s="15">
+      <c r="E114" s="16">
         <v>200300001</v>
       </c>
-      <c r="F114" s="15" t="s">
+      <c r="F114" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="G114" s="16" t="s">
+      <c r="G114" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H114" s="17">
+        <v>11</v>
+      </c>
+      <c r="I114" s="25">
+        <v>0</v>
+      </c>
+      <c r="J114" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K114" s="17">
+        <v>0</v>
+      </c>
+      <c r="L114" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H114" s="16">
-        <v>11</v>
-      </c>
-      <c r="I114" s="23">
-        <v>0</v>
-      </c>
-      <c r="J114" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K114" s="16">
-        <v>0</v>
-      </c>
-      <c r="L114" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M114" s="16">
+      <c r="M114" s="17">
         <v>0</v>
       </c>
       <c r="N114">
         <v>10000</v>
       </c>
-      <c r="O114" s="25">
+      <c r="O114" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6448,46 +7057,46 @@
       <c r="A115" s="1">
         <v>20030012</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B115" s="16">
         <v>200300</v>
       </c>
-      <c r="C115" s="15">
+      <c r="C115" s="16">
         <v>2</v>
       </c>
-      <c r="D115" s="15" t="s">
+      <c r="D115" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E115" s="15">
+      <c r="E115" s="16">
         <v>200300001</v>
       </c>
-      <c r="F115" s="15" t="s">
+      <c r="F115" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="G115" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H115" s="16">
+      <c r="G115" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H115" s="17">
         <v>12</v>
       </c>
-      <c r="I115" s="23">
-        <v>0</v>
-      </c>
-      <c r="J115" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K115" s="16">
-        <v>0</v>
-      </c>
-      <c r="L115" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M115" s="16">
+      <c r="I115" s="25">
+        <v>0</v>
+      </c>
+      <c r="J115" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K115" s="17">
+        <v>0</v>
+      </c>
+      <c r="L115" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M115" s="17">
         <v>0</v>
       </c>
       <c r="N115">
         <v>100000</v>
       </c>
-      <c r="O115" s="25">
+      <c r="O115" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6495,46 +7104,46 @@
       <c r="A116" s="1">
         <v>20040010</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B116" s="16">
         <v>200400</v>
       </c>
-      <c r="C116" s="15">
+      <c r="C116" s="16">
         <v>2</v>
       </c>
-      <c r="D116" s="23" t="s">
+      <c r="D116" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="E116" s="15">
+      <c r="E116" s="16">
         <v>200400009</v>
       </c>
-      <c r="F116" s="15" t="s">
+      <c r="F116" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="G116" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H116" s="16">
+      <c r="G116" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H116" s="17">
         <v>10</v>
       </c>
-      <c r="I116" s="23">
-        <v>0</v>
-      </c>
-      <c r="J116" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K116" s="16">
-        <v>0</v>
-      </c>
-      <c r="L116" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M116" s="16">
+      <c r="I116" s="25">
+        <v>0</v>
+      </c>
+      <c r="J116" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K116" s="17">
+        <v>0</v>
+      </c>
+      <c r="L116" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M116" s="17">
         <v>0</v>
       </c>
       <c r="N116">
         <v>1000</v>
       </c>
-      <c r="O116" s="25">
+      <c r="O116" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6542,46 +7151,46 @@
       <c r="A117" s="1">
         <v>20040011</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B117" s="16">
         <v>200400</v>
       </c>
-      <c r="C117" s="15">
+      <c r="C117" s="16">
         <v>2</v>
       </c>
-      <c r="D117" s="23" t="s">
+      <c r="D117" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="E117" s="15">
+      <c r="E117" s="16">
         <v>200400009</v>
       </c>
-      <c r="F117" s="15" t="s">
+      <c r="F117" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="G117" s="16" t="s">
+      <c r="G117" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H117" s="17">
+        <v>11</v>
+      </c>
+      <c r="I117" s="25">
+        <v>0</v>
+      </c>
+      <c r="J117" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K117" s="17">
+        <v>0</v>
+      </c>
+      <c r="L117" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H117" s="16">
-        <v>11</v>
-      </c>
-      <c r="I117" s="23">
-        <v>0</v>
-      </c>
-      <c r="J117" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K117" s="16">
-        <v>0</v>
-      </c>
-      <c r="L117" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M117" s="16">
+      <c r="M117" s="17">
         <v>0</v>
       </c>
       <c r="N117">
         <v>10000</v>
       </c>
-      <c r="O117" s="25">
+      <c r="O117" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6589,46 +7198,46 @@
       <c r="A118" s="1">
         <v>20040012</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B118" s="16">
         <v>200400</v>
       </c>
-      <c r="C118" s="15">
+      <c r="C118" s="16">
         <v>2</v>
       </c>
-      <c r="D118" s="23" t="s">
+      <c r="D118" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="E118" s="15">
+      <c r="E118" s="16">
         <v>200400009</v>
       </c>
-      <c r="F118" s="15" t="s">
+      <c r="F118" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="G118" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H118" s="16">
+      <c r="G118" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H118" s="17">
         <v>12</v>
       </c>
-      <c r="I118" s="23">
-        <v>0</v>
-      </c>
-      <c r="J118" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K118" s="16">
-        <v>0</v>
-      </c>
-      <c r="L118" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M118" s="16">
+      <c r="I118" s="25">
+        <v>0</v>
+      </c>
+      <c r="J118" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K118" s="17">
+        <v>0</v>
+      </c>
+      <c r="L118" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M118" s="17">
         <v>0</v>
       </c>
       <c r="N118">
         <v>100000</v>
       </c>
-      <c r="O118" s="25">
+      <c r="O118" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6636,46 +7245,46 @@
       <c r="A119" s="1">
         <v>20050010</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B119" s="16">
         <v>200500</v>
       </c>
-      <c r="C119" s="15">
+      <c r="C119" s="16">
         <v>2</v>
       </c>
-      <c r="D119" s="15" t="s">
+      <c r="D119" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E119" s="15">
+      <c r="E119" s="16">
         <v>200500025</v>
       </c>
-      <c r="F119" s="15" t="s">
+      <c r="F119" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="G119" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H119" s="16">
+      <c r="G119" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H119" s="17">
         <v>10</v>
       </c>
-      <c r="I119" s="23">
-        <v>0</v>
-      </c>
-      <c r="J119" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K119" s="16">
-        <v>0</v>
-      </c>
-      <c r="L119" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M119" s="16">
+      <c r="I119" s="25">
+        <v>0</v>
+      </c>
+      <c r="J119" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K119" s="17">
+        <v>0</v>
+      </c>
+      <c r="L119" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M119" s="17">
         <v>0</v>
       </c>
       <c r="N119">
         <v>1000</v>
       </c>
-      <c r="O119" s="25">
+      <c r="O119" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6683,46 +7292,46 @@
       <c r="A120" s="1">
         <v>20050011</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B120" s="16">
         <v>200500</v>
       </c>
-      <c r="C120" s="15">
+      <c r="C120" s="16">
         <v>2</v>
       </c>
-      <c r="D120" s="15" t="s">
+      <c r="D120" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E120" s="15">
+      <c r="E120" s="16">
         <v>200500025</v>
       </c>
-      <c r="F120" s="15" t="s">
+      <c r="F120" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="G120" s="16" t="s">
+      <c r="G120" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H120" s="17">
+        <v>11</v>
+      </c>
+      <c r="I120" s="25">
+        <v>0</v>
+      </c>
+      <c r="J120" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K120" s="17">
+        <v>0</v>
+      </c>
+      <c r="L120" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H120" s="16">
-        <v>11</v>
-      </c>
-      <c r="I120" s="23">
-        <v>0</v>
-      </c>
-      <c r="J120" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K120" s="16">
-        <v>0</v>
-      </c>
-      <c r="L120" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M120" s="16">
+      <c r="M120" s="17">
         <v>0</v>
       </c>
       <c r="N120">
         <v>10000</v>
       </c>
-      <c r="O120" s="25">
+      <c r="O120" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6730,46 +7339,46 @@
       <c r="A121" s="1">
         <v>20050012</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B121" s="16">
         <v>200500</v>
       </c>
-      <c r="C121" s="15">
+      <c r="C121" s="16">
         <v>2</v>
       </c>
-      <c r="D121" s="15" t="s">
+      <c r="D121" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E121" s="15">
+      <c r="E121" s="16">
         <v>200500025</v>
       </c>
-      <c r="F121" s="15" t="s">
+      <c r="F121" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="G121" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H121" s="16">
+      <c r="G121" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H121" s="17">
         <v>12</v>
       </c>
-      <c r="I121" s="23">
-        <v>0</v>
-      </c>
-      <c r="J121" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K121" s="16">
-        <v>0</v>
-      </c>
-      <c r="L121" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M121" s="16">
+      <c r="I121" s="25">
+        <v>0</v>
+      </c>
+      <c r="J121" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K121" s="17">
+        <v>0</v>
+      </c>
+      <c r="L121" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M121" s="17">
         <v>0</v>
       </c>
       <c r="N121">
         <v>100000</v>
       </c>
-      <c r="O121" s="25">
+      <c r="O121" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6777,46 +7386,46 @@
       <c r="A122" s="1">
         <v>20060010</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B122" s="16">
         <v>200600</v>
       </c>
-      <c r="C122" s="15">
+      <c r="C122" s="16">
         <v>2</v>
       </c>
-      <c r="D122" s="15" t="s">
+      <c r="D122" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E122" s="15">
+      <c r="E122" s="16">
         <v>200600001</v>
       </c>
-      <c r="F122" s="15" t="s">
+      <c r="F122" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="G122" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H122" s="16">
+      <c r="G122" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H122" s="17">
         <v>10</v>
       </c>
-      <c r="I122" s="23">
-        <v>0</v>
-      </c>
-      <c r="J122" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K122" s="16">
-        <v>0</v>
-      </c>
-      <c r="L122" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M122" s="16">
+      <c r="I122" s="25">
+        <v>0</v>
+      </c>
+      <c r="J122" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K122" s="17">
+        <v>0</v>
+      </c>
+      <c r="L122" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M122" s="17">
         <v>0</v>
       </c>
       <c r="N122">
         <v>1000</v>
       </c>
-      <c r="O122" s="25">
+      <c r="O122" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6824,46 +7433,46 @@
       <c r="A123" s="1">
         <v>20060011</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B123" s="16">
         <v>200600</v>
       </c>
-      <c r="C123" s="15">
+      <c r="C123" s="16">
         <v>2</v>
       </c>
-      <c r="D123" s="15" t="s">
+      <c r="D123" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E123" s="15">
+      <c r="E123" s="16">
         <v>200600001</v>
       </c>
-      <c r="F123" s="15" t="s">
+      <c r="F123" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="G123" s="16" t="s">
+      <c r="G123" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H123" s="17">
+        <v>11</v>
+      </c>
+      <c r="I123" s="25">
+        <v>0</v>
+      </c>
+      <c r="J123" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K123" s="17">
+        <v>0</v>
+      </c>
+      <c r="L123" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H123" s="16">
-        <v>11</v>
-      </c>
-      <c r="I123" s="23">
-        <v>0</v>
-      </c>
-      <c r="J123" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K123" s="16">
-        <v>0</v>
-      </c>
-      <c r="L123" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M123" s="16">
+      <c r="M123" s="17">
         <v>0</v>
       </c>
       <c r="N123">
         <v>10000</v>
       </c>
-      <c r="O123" s="25">
+      <c r="O123" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6871,46 +7480,46 @@
       <c r="A124" s="1">
         <v>20060012</v>
       </c>
-      <c r="B124" s="15">
+      <c r="B124" s="16">
         <v>200600</v>
       </c>
-      <c r="C124" s="15">
+      <c r="C124" s="16">
         <v>2</v>
       </c>
-      <c r="D124" s="15" t="s">
+      <c r="D124" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E124" s="15">
+      <c r="E124" s="16">
         <v>200600001</v>
       </c>
-      <c r="F124" s="15" t="s">
+      <c r="F124" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="G124" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H124" s="16">
+      <c r="G124" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H124" s="17">
         <v>12</v>
       </c>
-      <c r="I124" s="23">
-        <v>0</v>
-      </c>
-      <c r="J124" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K124" s="16">
-        <v>0</v>
-      </c>
-      <c r="L124" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M124" s="16">
+      <c r="I124" s="25">
+        <v>0</v>
+      </c>
+      <c r="J124" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K124" s="17">
+        <v>0</v>
+      </c>
+      <c r="L124" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M124" s="17">
         <v>0</v>
       </c>
       <c r="N124">
         <v>100000</v>
       </c>
-      <c r="O124" s="25">
+      <c r="O124" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6918,46 +7527,46 @@
       <c r="A125" s="1">
         <v>20070010</v>
       </c>
-      <c r="B125" s="15">
+      <c r="B125" s="16">
         <v>200700</v>
       </c>
-      <c r="C125" s="15">
+      <c r="C125" s="16">
         <v>2</v>
       </c>
-      <c r="D125" s="15" t="s">
+      <c r="D125" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="E125" s="15">
+      <c r="E125" s="16">
         <v>200700001</v>
       </c>
-      <c r="F125" s="15" t="s">
+      <c r="F125" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="G125" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H125" s="16">
+      <c r="G125" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H125" s="17">
         <v>10</v>
       </c>
-      <c r="I125" s="23">
-        <v>0</v>
-      </c>
-      <c r="J125" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K125" s="16">
-        <v>0</v>
-      </c>
-      <c r="L125" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M125" s="16">
+      <c r="I125" s="25">
+        <v>0</v>
+      </c>
+      <c r="J125" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K125" s="17">
+        <v>0</v>
+      </c>
+      <c r="L125" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M125" s="17">
         <v>0</v>
       </c>
       <c r="N125">
         <v>1000</v>
       </c>
-      <c r="O125" s="25">
+      <c r="O125" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -6965,46 +7574,46 @@
       <c r="A126" s="1">
         <v>20070011</v>
       </c>
-      <c r="B126" s="15">
+      <c r="B126" s="16">
         <v>200700</v>
       </c>
-      <c r="C126" s="15">
+      <c r="C126" s="16">
         <v>2</v>
       </c>
-      <c r="D126" s="15" t="s">
+      <c r="D126" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="E126" s="15">
+      <c r="E126" s="16">
         <v>200700001</v>
       </c>
-      <c r="F126" s="15" t="s">
+      <c r="F126" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="G126" s="16" t="s">
+      <c r="G126" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H126" s="17">
+        <v>11</v>
+      </c>
+      <c r="I126" s="25">
+        <v>0</v>
+      </c>
+      <c r="J126" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K126" s="17">
+        <v>0</v>
+      </c>
+      <c r="L126" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H126" s="16">
-        <v>11</v>
-      </c>
-      <c r="I126" s="23">
-        <v>0</v>
-      </c>
-      <c r="J126" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K126" s="16">
-        <v>0</v>
-      </c>
-      <c r="L126" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M126" s="16">
+      <c r="M126" s="17">
         <v>0</v>
       </c>
       <c r="N126">
         <v>10000</v>
       </c>
-      <c r="O126" s="25">
+      <c r="O126" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7012,46 +7621,46 @@
       <c r="A127" s="1">
         <v>20070012</v>
       </c>
-      <c r="B127" s="15">
+      <c r="B127" s="16">
         <v>200700</v>
       </c>
-      <c r="C127" s="15">
+      <c r="C127" s="16">
         <v>2</v>
       </c>
-      <c r="D127" s="15" t="s">
+      <c r="D127" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="E127" s="15">
+      <c r="E127" s="16">
         <v>200700001</v>
       </c>
-      <c r="F127" s="15" t="s">
+      <c r="F127" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="G127" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H127" s="16">
+      <c r="G127" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H127" s="17">
         <v>12</v>
       </c>
-      <c r="I127" s="23">
-        <v>0</v>
-      </c>
-      <c r="J127" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K127" s="16">
-        <v>0</v>
-      </c>
-      <c r="L127" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M127" s="16">
+      <c r="I127" s="25">
+        <v>0</v>
+      </c>
+      <c r="J127" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K127" s="17">
+        <v>0</v>
+      </c>
+      <c r="L127" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M127" s="17">
         <v>0</v>
       </c>
       <c r="N127">
         <v>100000</v>
       </c>
-      <c r="O127" s="25">
+      <c r="O127" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7059,46 +7668,46 @@
       <c r="A128" s="1">
         <v>20080010</v>
       </c>
-      <c r="B128" s="15">
+      <c r="B128" s="16">
         <v>200800</v>
       </c>
-      <c r="C128" s="15">
+      <c r="C128" s="16">
         <v>2</v>
       </c>
-      <c r="D128" s="15" t="s">
+      <c r="D128" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E128" s="15">
+      <c r="E128" s="16">
         <v>200800001</v>
       </c>
-      <c r="F128" s="15" t="s">
+      <c r="F128" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="G128" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H128" s="16">
+      <c r="G128" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H128" s="17">
         <v>10</v>
       </c>
-      <c r="I128" s="23">
-        <v>0</v>
-      </c>
-      <c r="J128" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K128" s="16">
-        <v>0</v>
-      </c>
-      <c r="L128" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M128" s="16">
+      <c r="I128" s="25">
+        <v>0</v>
+      </c>
+      <c r="J128" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K128" s="17">
+        <v>0</v>
+      </c>
+      <c r="L128" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M128" s="17">
         <v>0</v>
       </c>
       <c r="N128">
         <v>1000</v>
       </c>
-      <c r="O128" s="25">
+      <c r="O128" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7106,46 +7715,46 @@
       <c r="A129" s="1">
         <v>20080011</v>
       </c>
-      <c r="B129" s="15">
+      <c r="B129" s="16">
         <v>200800</v>
       </c>
-      <c r="C129" s="15">
+      <c r="C129" s="16">
         <v>2</v>
       </c>
-      <c r="D129" s="15" t="s">
+      <c r="D129" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E129" s="15">
+      <c r="E129" s="16">
         <v>200800001</v>
       </c>
-      <c r="F129" s="15" t="s">
+      <c r="F129" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="G129" s="16" t="s">
+      <c r="G129" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H129" s="17">
+        <v>11</v>
+      </c>
+      <c r="I129" s="25">
+        <v>0</v>
+      </c>
+      <c r="J129" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K129" s="17">
+        <v>0</v>
+      </c>
+      <c r="L129" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H129" s="16">
-        <v>11</v>
-      </c>
-      <c r="I129" s="23">
-        <v>0</v>
-      </c>
-      <c r="J129" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K129" s="16">
-        <v>0</v>
-      </c>
-      <c r="L129" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M129" s="16">
+      <c r="M129" s="17">
         <v>0</v>
       </c>
       <c r="N129">
         <v>10000</v>
       </c>
-      <c r="O129" s="25">
+      <c r="O129" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7153,46 +7762,46 @@
       <c r="A130" s="1">
         <v>20080012</v>
       </c>
-      <c r="B130" s="15">
+      <c r="B130" s="16">
         <v>200800</v>
       </c>
-      <c r="C130" s="15">
+      <c r="C130" s="16">
         <v>2</v>
       </c>
-      <c r="D130" s="15" t="s">
+      <c r="D130" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E130" s="15">
+      <c r="E130" s="16">
         <v>200800001</v>
       </c>
-      <c r="F130" s="15" t="s">
+      <c r="F130" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="G130" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H130" s="16">
+      <c r="G130" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H130" s="17">
         <v>12</v>
       </c>
-      <c r="I130" s="23">
-        <v>0</v>
-      </c>
-      <c r="J130" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K130" s="16">
-        <v>0</v>
-      </c>
-      <c r="L130" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M130" s="16">
+      <c r="I130" s="25">
+        <v>0</v>
+      </c>
+      <c r="J130" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K130" s="17">
+        <v>0</v>
+      </c>
+      <c r="L130" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M130" s="17">
         <v>0</v>
       </c>
       <c r="N130">
         <v>100000</v>
       </c>
-      <c r="O130" s="25">
+      <c r="O130" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7200,46 +7809,46 @@
       <c r="A131" s="1">
         <v>20090010</v>
       </c>
-      <c r="B131" s="15">
+      <c r="B131" s="16">
         <v>200900</v>
       </c>
-      <c r="C131" s="15">
+      <c r="C131" s="16">
         <v>2</v>
       </c>
-      <c r="D131" s="15" t="s">
+      <c r="D131" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E131" s="15">
+      <c r="E131" s="16">
         <v>200900001</v>
       </c>
-      <c r="F131" s="15" t="s">
+      <c r="F131" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="G131" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H131" s="16">
+      <c r="G131" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H131" s="17">
         <v>10</v>
       </c>
-      <c r="I131" s="23">
-        <v>0</v>
-      </c>
-      <c r="J131" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K131" s="16">
-        <v>0</v>
-      </c>
-      <c r="L131" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M131" s="16">
+      <c r="I131" s="25">
+        <v>0</v>
+      </c>
+      <c r="J131" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K131" s="17">
+        <v>0</v>
+      </c>
+      <c r="L131" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M131" s="17">
         <v>0</v>
       </c>
       <c r="N131">
         <v>1000</v>
       </c>
-      <c r="O131" s="25">
+      <c r="O131" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7247,46 +7856,46 @@
       <c r="A132" s="1">
         <v>20090011</v>
       </c>
-      <c r="B132" s="15">
+      <c r="B132" s="16">
         <v>200900</v>
       </c>
-      <c r="C132" s="15">
+      <c r="C132" s="16">
         <v>2</v>
       </c>
-      <c r="D132" s="15" t="s">
+      <c r="D132" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E132" s="15">
+      <c r="E132" s="16">
         <v>200900001</v>
       </c>
-      <c r="F132" s="15" t="s">
+      <c r="F132" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="G132" s="16" t="s">
+      <c r="G132" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H132" s="17">
+        <v>11</v>
+      </c>
+      <c r="I132" s="25">
+        <v>0</v>
+      </c>
+      <c r="J132" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K132" s="17">
+        <v>0</v>
+      </c>
+      <c r="L132" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H132" s="16">
-        <v>11</v>
-      </c>
-      <c r="I132" s="23">
-        <v>0</v>
-      </c>
-      <c r="J132" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K132" s="16">
-        <v>0</v>
-      </c>
-      <c r="L132" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M132" s="16">
+      <c r="M132" s="17">
         <v>0</v>
       </c>
       <c r="N132">
         <v>10000</v>
       </c>
-      <c r="O132" s="25">
+      <c r="O132" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7294,46 +7903,46 @@
       <c r="A133" s="1">
         <v>20090012</v>
       </c>
-      <c r="B133" s="15">
+      <c r="B133" s="16">
         <v>200900</v>
       </c>
-      <c r="C133" s="15">
+      <c r="C133" s="16">
         <v>2</v>
       </c>
-      <c r="D133" s="15" t="s">
+      <c r="D133" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E133" s="15">
+      <c r="E133" s="16">
         <v>200900001</v>
       </c>
-      <c r="F133" s="15" t="s">
+      <c r="F133" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="G133" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H133" s="16">
+      <c r="G133" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H133" s="17">
         <v>12</v>
       </c>
-      <c r="I133" s="23">
-        <v>0</v>
-      </c>
-      <c r="J133" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K133" s="16">
-        <v>0</v>
-      </c>
-      <c r="L133" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M133" s="16">
+      <c r="I133" s="25">
+        <v>0</v>
+      </c>
+      <c r="J133" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K133" s="17">
+        <v>0</v>
+      </c>
+      <c r="L133" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M133" s="17">
         <v>0</v>
       </c>
       <c r="N133">
         <v>100000</v>
       </c>
-      <c r="O133" s="25">
+      <c r="O133" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7341,46 +7950,46 @@
       <c r="A134" s="1">
         <v>30020010</v>
       </c>
-      <c r="B134" s="15">
+      <c r="B134" s="16">
         <v>300200</v>
       </c>
-      <c r="C134" s="15">
+      <c r="C134" s="16">
         <v>3</v>
       </c>
-      <c r="D134" s="15" t="s">
+      <c r="D134" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E134" s="15">
+      <c r="E134" s="16">
         <v>300200006</v>
       </c>
-      <c r="F134" s="15" t="s">
+      <c r="F134" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="G134" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H134" s="16">
+      <c r="G134" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H134" s="17">
         <v>10</v>
       </c>
-      <c r="I134" s="23">
-        <v>0</v>
-      </c>
-      <c r="J134" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K134" s="16">
+      <c r="I134" s="25">
+        <v>0</v>
+      </c>
+      <c r="J134" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K134" s="17">
         <v>0</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="M134" s="16">
-        <v>0</v>
-      </c>
-      <c r="N134" s="20">
+        <v>113</v>
+      </c>
+      <c r="M134" s="17">
+        <v>0</v>
+      </c>
+      <c r="N134" s="21">
         <v>1000</v>
       </c>
-      <c r="O134" s="25">
+      <c r="O134" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7388,46 +7997,46 @@
       <c r="A135" s="1">
         <v>30020011</v>
       </c>
-      <c r="B135" s="15">
+      <c r="B135" s="16">
         <v>300200</v>
       </c>
-      <c r="C135" s="15">
+      <c r="C135" s="16">
         <v>3</v>
       </c>
-      <c r="D135" s="15" t="s">
+      <c r="D135" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E135" s="15">
+      <c r="E135" s="16">
         <v>300200006</v>
       </c>
-      <c r="F135" s="15" t="s">
+      <c r="F135" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="G135" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H135" s="16">
+      <c r="G135" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H135" s="17">
         <v>11</v>
       </c>
-      <c r="I135" s="23">
-        <v>0</v>
-      </c>
-      <c r="J135" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K135" s="16">
+      <c r="I135" s="25">
+        <v>0</v>
+      </c>
+      <c r="J135" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K135" s="17">
         <v>0</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="M135" s="16">
-        <v>0</v>
-      </c>
-      <c r="N135" s="20">
+        <v>113</v>
+      </c>
+      <c r="M135" s="17">
+        <v>0</v>
+      </c>
+      <c r="N135" s="21">
         <v>10000</v>
       </c>
-      <c r="O135" s="25">
+      <c r="O135" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7435,46 +8044,46 @@
       <c r="A136" s="1">
         <v>30020012</v>
       </c>
-      <c r="B136" s="15">
+      <c r="B136" s="16">
         <v>300200</v>
       </c>
-      <c r="C136" s="15">
+      <c r="C136" s="16">
         <v>3</v>
       </c>
-      <c r="D136" s="15" t="s">
+      <c r="D136" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E136" s="15">
+      <c r="E136" s="16">
         <v>300200006</v>
       </c>
-      <c r="F136" s="15" t="s">
+      <c r="F136" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="G136" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H136" s="16">
+      <c r="G136" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H136" s="17">
         <v>12</v>
       </c>
-      <c r="I136" s="23">
-        <v>0</v>
-      </c>
-      <c r="J136" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K136" s="16">
+      <c r="I136" s="25">
+        <v>0</v>
+      </c>
+      <c r="J136" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K136" s="17">
         <v>0</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="M136" s="16">
-        <v>0</v>
-      </c>
-      <c r="N136" s="20">
+        <v>113</v>
+      </c>
+      <c r="M136" s="17">
+        <v>0</v>
+      </c>
+      <c r="N136" s="21">
         <v>100000</v>
       </c>
-      <c r="O136" s="25">
+      <c r="O136" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7483,46 +8092,46 @@
         <f>B137*100+H137</f>
         <v>10010010</v>
       </c>
-      <c r="B137" s="15">
+      <c r="B137" s="16">
         <v>100100</v>
       </c>
-      <c r="C137" s="15">
-        <v>1</v>
-      </c>
-      <c r="D137" s="15" t="s">
+      <c r="C137" s="16">
+        <v>1</v>
+      </c>
+      <c r="D137" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="E137" s="15">
+      <c r="E137" s="16">
         <v>100100026</v>
       </c>
-      <c r="F137" s="15" t="s">
+      <c r="F137" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G137" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H137" s="16">
+      <c r="G137" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H137" s="17">
         <v>10</v>
       </c>
-      <c r="I137" s="23">
-        <v>0</v>
-      </c>
-      <c r="J137" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K137" s="16">
-        <v>0</v>
-      </c>
-      <c r="L137" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M137" s="16">
+      <c r="I137" s="25">
+        <v>0</v>
+      </c>
+      <c r="J137" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K137" s="17">
+        <v>0</v>
+      </c>
+      <c r="L137" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M137" s="17">
         <v>0</v>
       </c>
       <c r="N137">
         <v>1000</v>
       </c>
-      <c r="O137" s="25">
+      <c r="O137" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7531,47 +8140,47 @@
         <f>B138*100+H138</f>
         <v>10010011</v>
       </c>
-      <c r="B138" s="15">
+      <c r="B138" s="16">
         <v>100100</v>
       </c>
-      <c r="C138" s="15">
-        <v>1</v>
-      </c>
-      <c r="D138" s="15" t="str">
+      <c r="C138" s="16">
+        <v>1</v>
+      </c>
+      <c r="D138" s="16" t="str">
         <f t="shared" ref="D138:D142" si="1">D137</f>
         <v>金礦大亨</v>
       </c>
-      <c r="E138" s="15">
+      <c r="E138" s="16">
         <v>100100026</v>
       </c>
-      <c r="F138" s="15" t="s">
+      <c r="F138" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G138" s="16" t="s">
+      <c r="G138" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H138" s="17">
+        <v>11</v>
+      </c>
+      <c r="I138" s="25">
+        <v>0</v>
+      </c>
+      <c r="J138" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K138" s="17">
+        <v>0</v>
+      </c>
+      <c r="L138" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H138" s="16">
-        <v>11</v>
-      </c>
-      <c r="I138" s="23">
-        <v>0</v>
-      </c>
-      <c r="J138" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K138" s="16">
-        <v>0</v>
-      </c>
-      <c r="L138" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M138" s="16">
+      <c r="M138" s="17">
         <v>0</v>
       </c>
       <c r="N138">
         <v>10000</v>
       </c>
-      <c r="O138" s="25">
+      <c r="O138" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7580,47 +8189,47 @@
         <f>B139*100+H139</f>
         <v>10010012</v>
       </c>
-      <c r="B139" s="15">
+      <c r="B139" s="16">
         <v>100100</v>
       </c>
-      <c r="C139" s="15">
-        <v>1</v>
-      </c>
-      <c r="D139" s="15" t="str">
+      <c r="C139" s="16">
+        <v>1</v>
+      </c>
+      <c r="D139" s="16" t="str">
         <f t="shared" si="1"/>
         <v>金礦大亨</v>
       </c>
-      <c r="E139" s="15">
+      <c r="E139" s="16">
         <v>100100026</v>
       </c>
-      <c r="F139" s="15" t="s">
+      <c r="F139" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G139" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H139" s="16">
+      <c r="G139" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H139" s="17">
         <v>12</v>
       </c>
-      <c r="I139" s="23">
-        <v>0</v>
-      </c>
-      <c r="J139" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K139" s="16">
-        <v>0</v>
-      </c>
-      <c r="L139" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M139" s="16">
+      <c r="I139" s="25">
+        <v>0</v>
+      </c>
+      <c r="J139" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K139" s="17">
+        <v>0</v>
+      </c>
+      <c r="L139" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M139" s="17">
         <v>0</v>
       </c>
       <c r="N139">
         <v>100000</v>
       </c>
-      <c r="O139" s="25">
+      <c r="O139" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7629,46 +8238,46 @@
         <f t="shared" ref="A140:A181" si="2">B140*100+H140</f>
         <v>10030010</v>
       </c>
-      <c r="B140" s="15">
+      <c r="B140" s="16">
         <v>100300</v>
       </c>
-      <c r="C140" s="15">
-        <v>1</v>
-      </c>
-      <c r="D140" s="15" t="s">
+      <c r="C140" s="16">
+        <v>1</v>
+      </c>
+      <c r="D140" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E140" s="15">
+      <c r="E140" s="16">
         <v>100300001</v>
       </c>
-      <c r="F140" s="15" t="s">
+      <c r="F140" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G140" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H140" s="16">
+      <c r="G140" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H140" s="17">
         <v>10</v>
       </c>
-      <c r="I140" s="23">
-        <v>0</v>
-      </c>
-      <c r="J140" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K140" s="16">
-        <v>0</v>
-      </c>
-      <c r="L140" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M140" s="16">
+      <c r="I140" s="25">
+        <v>0</v>
+      </c>
+      <c r="J140" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K140" s="17">
+        <v>0</v>
+      </c>
+      <c r="L140" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M140" s="17">
         <v>0</v>
       </c>
       <c r="N140">
         <v>1000</v>
       </c>
-      <c r="O140" s="25">
+      <c r="O140" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7677,48 +8286,48 @@
         <f t="shared" si="2"/>
         <v>10030011</v>
       </c>
-      <c r="B141" s="15">
+      <c r="B141" s="16">
         <v>100300</v>
       </c>
-      <c r="C141" s="15">
-        <v>1</v>
-      </c>
-      <c r="D141" s="15" t="str">
+      <c r="C141" s="16">
+        <v>1</v>
+      </c>
+      <c r="D141" s="16" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E141" s="15">
+      <c r="E141" s="16">
         <v>100300001</v>
       </c>
-      <c r="F141" s="15" t="str">
+      <c r="F141" s="16" t="str">
         <f t="shared" ref="F141:F145" si="3">F140</f>
         <v>SuperStar</v>
       </c>
-      <c r="G141" s="16" t="s">
+      <c r="G141" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H141" s="17">
+        <v>11</v>
+      </c>
+      <c r="I141" s="25">
+        <v>0</v>
+      </c>
+      <c r="J141" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K141" s="17">
+        <v>0</v>
+      </c>
+      <c r="L141" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H141" s="16">
-        <v>11</v>
-      </c>
-      <c r="I141" s="23">
-        <v>0</v>
-      </c>
-      <c r="J141" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K141" s="16">
-        <v>0</v>
-      </c>
-      <c r="L141" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M141" s="16">
+      <c r="M141" s="17">
         <v>0</v>
       </c>
       <c r="N141">
         <v>10000</v>
       </c>
-      <c r="O141" s="25">
+      <c r="O141" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7727,48 +8336,48 @@
         <f t="shared" si="2"/>
         <v>10030012</v>
       </c>
-      <c r="B142" s="15">
+      <c r="B142" s="16">
         <v>100300</v>
       </c>
-      <c r="C142" s="15">
-        <v>1</v>
-      </c>
-      <c r="D142" s="15" t="str">
+      <c r="C142" s="16">
+        <v>1</v>
+      </c>
+      <c r="D142" s="16" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E142" s="15">
+      <c r="E142" s="16">
         <v>100300001</v>
       </c>
-      <c r="F142" s="15" t="str">
+      <c r="F142" s="16" t="str">
         <f t="shared" si="3"/>
         <v>SuperStar</v>
       </c>
-      <c r="G142" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H142" s="16">
+      <c r="G142" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H142" s="17">
         <v>12</v>
       </c>
-      <c r="I142" s="23">
-        <v>0</v>
-      </c>
-      <c r="J142" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K142" s="16">
-        <v>0</v>
-      </c>
-      <c r="L142" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M142" s="16">
+      <c r="I142" s="25">
+        <v>0</v>
+      </c>
+      <c r="J142" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K142" s="17">
+        <v>0</v>
+      </c>
+      <c r="L142" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M142" s="17">
         <v>0</v>
       </c>
       <c r="N142">
         <v>100000</v>
       </c>
-      <c r="O142" s="25">
+      <c r="O142" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7777,46 +8386,46 @@
         <f t="shared" si="2"/>
         <v>10070010</v>
       </c>
-      <c r="B143" s="15">
+      <c r="B143" s="16">
         <v>100700</v>
       </c>
-      <c r="C143" s="15">
-        <v>1</v>
-      </c>
-      <c r="D143" s="15" t="s">
+      <c r="C143" s="16">
+        <v>1</v>
+      </c>
+      <c r="D143" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E143" s="15">
+      <c r="E143" s="16">
         <v>100700001</v>
       </c>
-      <c r="F143" s="15" t="s">
+      <c r="F143" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="G143" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H143" s="16">
+      <c r="G143" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H143" s="17">
         <v>10</v>
       </c>
-      <c r="I143" s="23">
-        <v>0</v>
-      </c>
-      <c r="J143" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K143" s="16">
-        <v>0</v>
-      </c>
-      <c r="L143" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M143" s="16">
+      <c r="I143" s="25">
+        <v>0</v>
+      </c>
+      <c r="J143" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K143" s="17">
+        <v>0</v>
+      </c>
+      <c r="L143" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M143" s="17">
         <v>0</v>
       </c>
       <c r="N143">
         <v>1000</v>
       </c>
-      <c r="O143" s="25">
+      <c r="O143" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7825,48 +8434,48 @@
         <f t="shared" si="2"/>
         <v>10070011</v>
       </c>
-      <c r="B144" s="15">
+      <c r="B144" s="16">
         <v>100700</v>
       </c>
-      <c r="C144" s="15">
-        <v>1</v>
-      </c>
-      <c r="D144" s="15" t="str">
+      <c r="C144" s="16">
+        <v>1</v>
+      </c>
+      <c r="D144" s="16" t="str">
         <f t="shared" ref="D144:D148" si="4">D143</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E144" s="15">
+      <c r="E144" s="16">
         <v>100700001</v>
       </c>
-      <c r="F144" s="15" t="str">
+      <c r="F144" s="16" t="str">
         <f t="shared" si="3"/>
         <v>MahjongWays</v>
       </c>
-      <c r="G144" s="16" t="s">
+      <c r="G144" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H144" s="17">
+        <v>11</v>
+      </c>
+      <c r="I144" s="25">
+        <v>0</v>
+      </c>
+      <c r="J144" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K144" s="17">
+        <v>0</v>
+      </c>
+      <c r="L144" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H144" s="16">
-        <v>11</v>
-      </c>
-      <c r="I144" s="23">
-        <v>0</v>
-      </c>
-      <c r="J144" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K144" s="16">
-        <v>0</v>
-      </c>
-      <c r="L144" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M144" s="16">
+      <c r="M144" s="17">
         <v>0</v>
       </c>
       <c r="N144">
         <v>10000</v>
       </c>
-      <c r="O144" s="25">
+      <c r="O144" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7875,48 +8484,48 @@
         <f t="shared" si="2"/>
         <v>10070012</v>
       </c>
-      <c r="B145" s="15">
+      <c r="B145" s="16">
         <v>100700</v>
       </c>
-      <c r="C145" s="15">
-        <v>1</v>
-      </c>
-      <c r="D145" s="15" t="str">
+      <c r="C145" s="16">
+        <v>1</v>
+      </c>
+      <c r="D145" s="16" t="str">
         <f t="shared" si="4"/>
         <v>麻将胡了</v>
       </c>
-      <c r="E145" s="15">
+      <c r="E145" s="16">
         <v>100700001</v>
       </c>
-      <c r="F145" s="15" t="str">
+      <c r="F145" s="16" t="str">
         <f t="shared" si="3"/>
         <v>MahjongWays</v>
       </c>
-      <c r="G145" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H145" s="16">
+      <c r="G145" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H145" s="17">
         <v>12</v>
       </c>
-      <c r="I145" s="23">
-        <v>0</v>
-      </c>
-      <c r="J145" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K145" s="16">
-        <v>0</v>
-      </c>
-      <c r="L145" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M145" s="16">
+      <c r="I145" s="25">
+        <v>0</v>
+      </c>
+      <c r="J145" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K145" s="17">
+        <v>0</v>
+      </c>
+      <c r="L145" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M145" s="17">
         <v>0</v>
       </c>
       <c r="N145">
         <v>100000</v>
       </c>
-      <c r="O145" s="25">
+      <c r="O145" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7925,46 +8534,46 @@
         <f t="shared" si="2"/>
         <v>10120010</v>
       </c>
-      <c r="B146" s="15">
+      <c r="B146" s="16">
         <v>101200</v>
       </c>
-      <c r="C146" s="15">
-        <v>1</v>
-      </c>
-      <c r="D146" s="15" t="s">
+      <c r="C146" s="16">
+        <v>1</v>
+      </c>
+      <c r="D146" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E146" s="15">
+      <c r="E146" s="16">
         <v>101200001</v>
       </c>
-      <c r="F146" s="15" t="s">
+      <c r="F146" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G146" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H146" s="16">
+      <c r="G146" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H146" s="17">
         <v>10</v>
       </c>
-      <c r="I146" s="23">
-        <v>0</v>
-      </c>
-      <c r="J146" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K146" s="16">
-        <v>0</v>
-      </c>
-      <c r="L146" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M146" s="16">
+      <c r="I146" s="25">
+        <v>0</v>
+      </c>
+      <c r="J146" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K146" s="17">
+        <v>0</v>
+      </c>
+      <c r="L146" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M146" s="17">
         <v>0</v>
       </c>
       <c r="N146">
         <v>1000</v>
       </c>
-      <c r="O146" s="25">
+      <c r="O146" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -7973,48 +8582,48 @@
         <f t="shared" si="2"/>
         <v>10120011</v>
       </c>
-      <c r="B147" s="15">
+      <c r="B147" s="16">
         <v>101200</v>
       </c>
-      <c r="C147" s="15">
-        <v>1</v>
-      </c>
-      <c r="D147" s="15" t="str">
+      <c r="C147" s="16">
+        <v>1</v>
+      </c>
+      <c r="D147" s="16" t="str">
         <f t="shared" si="4"/>
         <v>财神</v>
       </c>
-      <c r="E147" s="15">
+      <c r="E147" s="16">
         <v>101200001</v>
       </c>
-      <c r="F147" s="15" t="str">
+      <c r="F147" s="16" t="str">
         <f t="shared" ref="F147:F151" si="5">F146</f>
         <v>Godofwealth</v>
       </c>
-      <c r="G147" s="16" t="s">
+      <c r="G147" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H147" s="17">
+        <v>11</v>
+      </c>
+      <c r="I147" s="25">
+        <v>0</v>
+      </c>
+      <c r="J147" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K147" s="17">
+        <v>0</v>
+      </c>
+      <c r="L147" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H147" s="16">
-        <v>11</v>
-      </c>
-      <c r="I147" s="23">
-        <v>0</v>
-      </c>
-      <c r="J147" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K147" s="16">
-        <v>0</v>
-      </c>
-      <c r="L147" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M147" s="16">
+      <c r="M147" s="17">
         <v>0</v>
       </c>
       <c r="N147">
         <v>10000</v>
       </c>
-      <c r="O147" s="25">
+      <c r="O147" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8023,48 +8632,48 @@
         <f t="shared" si="2"/>
         <v>10120012</v>
       </c>
-      <c r="B148" s="15">
+      <c r="B148" s="16">
         <v>101200</v>
       </c>
-      <c r="C148" s="15">
-        <v>1</v>
-      </c>
-      <c r="D148" s="15" t="str">
+      <c r="C148" s="16">
+        <v>1</v>
+      </c>
+      <c r="D148" s="16" t="str">
         <f t="shared" si="4"/>
         <v>财神</v>
       </c>
-      <c r="E148" s="15">
+      <c r="E148" s="16">
         <v>101200001</v>
       </c>
-      <c r="F148" s="15" t="str">
+      <c r="F148" s="16" t="str">
         <f t="shared" si="5"/>
         <v>Godofwealth</v>
       </c>
-      <c r="G148" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H148" s="16">
+      <c r="G148" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H148" s="17">
         <v>12</v>
       </c>
-      <c r="I148" s="23">
-        <v>0</v>
-      </c>
-      <c r="J148" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K148" s="16">
-        <v>0</v>
-      </c>
-      <c r="L148" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M148" s="16">
+      <c r="I148" s="25">
+        <v>0</v>
+      </c>
+      <c r="J148" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K148" s="17">
+        <v>0</v>
+      </c>
+      <c r="L148" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M148" s="17">
         <v>0</v>
       </c>
       <c r="N148">
         <v>100000</v>
       </c>
-      <c r="O148" s="25">
+      <c r="O148" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8073,46 +8682,46 @@
         <f t="shared" si="2"/>
         <v>10140010</v>
       </c>
-      <c r="B149" s="15">
+      <c r="B149" s="16">
         <v>101400</v>
       </c>
-      <c r="C149" s="15">
-        <v>1</v>
-      </c>
-      <c r="D149" s="15" t="s">
+      <c r="C149" s="16">
+        <v>1</v>
+      </c>
+      <c r="D149" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E149" s="15">
+      <c r="E149" s="16">
         <v>101400001</v>
       </c>
-      <c r="F149" s="15" t="s">
+      <c r="F149" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G149" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H149" s="16">
+      <c r="G149" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H149" s="17">
         <v>10</v>
       </c>
-      <c r="I149" s="23">
-        <v>0</v>
-      </c>
-      <c r="J149" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K149" s="16">
-        <v>0</v>
-      </c>
-      <c r="L149" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M149" s="16">
+      <c r="I149" s="25">
+        <v>0</v>
+      </c>
+      <c r="J149" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K149" s="17">
+        <v>0</v>
+      </c>
+      <c r="L149" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M149" s="17">
         <v>0</v>
       </c>
       <c r="N149">
         <v>1000</v>
       </c>
-      <c r="O149" s="25">
+      <c r="O149" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8121,48 +8730,48 @@
         <f t="shared" si="2"/>
         <v>10140011</v>
       </c>
-      <c r="B150" s="15">
+      <c r="B150" s="16">
         <v>101400</v>
       </c>
-      <c r="C150" s="15">
-        <v>1</v>
-      </c>
-      <c r="D150" s="15" t="str">
+      <c r="C150" s="16">
+        <v>1</v>
+      </c>
+      <c r="D150" s="16" t="str">
         <f t="shared" ref="D150:D154" si="6">D149</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E150" s="15">
+      <c r="E150" s="16">
         <v>101400001</v>
       </c>
-      <c r="F150" s="15" t="str">
+      <c r="F150" s="16" t="str">
         <f t="shared" si="5"/>
         <v>Cleopatra</v>
       </c>
-      <c r="G150" s="16" t="s">
+      <c r="G150" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H150" s="17">
+        <v>11</v>
+      </c>
+      <c r="I150" s="25">
+        <v>0</v>
+      </c>
+      <c r="J150" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K150" s="17">
+        <v>0</v>
+      </c>
+      <c r="L150" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H150" s="16">
-        <v>11</v>
-      </c>
-      <c r="I150" s="23">
-        <v>0</v>
-      </c>
-      <c r="J150" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K150" s="16">
-        <v>0</v>
-      </c>
-      <c r="L150" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M150" s="16">
+      <c r="M150" s="17">
         <v>0</v>
       </c>
       <c r="N150">
         <v>10000</v>
       </c>
-      <c r="O150" s="25">
+      <c r="O150" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8171,48 +8780,48 @@
         <f t="shared" si="2"/>
         <v>10140012</v>
       </c>
-      <c r="B151" s="15">
+      <c r="B151" s="16">
         <v>101400</v>
       </c>
-      <c r="C151" s="15">
-        <v>1</v>
-      </c>
-      <c r="D151" s="15" t="str">
+      <c r="C151" s="16">
+        <v>1</v>
+      </c>
+      <c r="D151" s="16" t="str">
         <f t="shared" si="6"/>
         <v>埃及艳后</v>
       </c>
-      <c r="E151" s="15">
+      <c r="E151" s="16">
         <v>101400001</v>
       </c>
-      <c r="F151" s="15" t="str">
+      <c r="F151" s="16" t="str">
         <f t="shared" si="5"/>
         <v>Cleopatra</v>
       </c>
-      <c r="G151" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H151" s="16">
+      <c r="G151" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H151" s="17">
         <v>12</v>
       </c>
-      <c r="I151" s="23">
-        <v>0</v>
-      </c>
-      <c r="J151" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K151" s="16">
-        <v>0</v>
-      </c>
-      <c r="L151" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M151" s="16">
+      <c r="I151" s="25">
+        <v>0</v>
+      </c>
+      <c r="J151" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K151" s="17">
+        <v>0</v>
+      </c>
+      <c r="L151" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M151" s="17">
         <v>0</v>
       </c>
       <c r="N151">
         <v>100000</v>
       </c>
-      <c r="O151" s="25">
+      <c r="O151" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8221,46 +8830,46 @@
         <f t="shared" si="2"/>
         <v>10240010</v>
       </c>
-      <c r="B152" s="15">
+      <c r="B152" s="16">
         <v>102400</v>
       </c>
-      <c r="C152" s="15">
-        <v>1</v>
-      </c>
-      <c r="D152" s="15" t="s">
+      <c r="C152" s="16">
+        <v>1</v>
+      </c>
+      <c r="D152" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E152" s="15">
+      <c r="E152" s="16">
         <v>102400026</v>
       </c>
-      <c r="F152" s="15" t="s">
+      <c r="F152" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G152" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H152" s="16">
+      <c r="G152" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H152" s="17">
         <v>10</v>
       </c>
-      <c r="I152" s="23">
-        <v>0</v>
-      </c>
-      <c r="J152" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K152" s="16">
-        <v>0</v>
-      </c>
-      <c r="L152" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M152" s="16">
+      <c r="I152" s="25">
+        <v>0</v>
+      </c>
+      <c r="J152" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K152" s="17">
+        <v>0</v>
+      </c>
+      <c r="L152" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M152" s="17">
         <v>0</v>
       </c>
       <c r="N152">
         <v>1000</v>
       </c>
-      <c r="O152" s="25">
+      <c r="O152" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8269,47 +8878,47 @@
         <f t="shared" si="2"/>
         <v>10240011</v>
       </c>
-      <c r="B153" s="15">
+      <c r="B153" s="16">
         <v>102400</v>
       </c>
-      <c r="C153" s="15">
-        <v>1</v>
-      </c>
-      <c r="D153" s="15" t="str">
+      <c r="C153" s="16">
+        <v>1</v>
+      </c>
+      <c r="D153" s="16" t="str">
         <f t="shared" si="6"/>
         <v>财富银行</v>
       </c>
-      <c r="E153" s="15">
+      <c r="E153" s="16">
         <v>102400026</v>
       </c>
-      <c r="F153" s="15" t="s">
+      <c r="F153" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G153" s="16" t="s">
+      <c r="G153" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H153" s="17">
+        <v>11</v>
+      </c>
+      <c r="I153" s="25">
+        <v>0</v>
+      </c>
+      <c r="J153" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K153" s="17">
+        <v>0</v>
+      </c>
+      <c r="L153" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H153" s="16">
-        <v>11</v>
-      </c>
-      <c r="I153" s="23">
-        <v>0</v>
-      </c>
-      <c r="J153" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K153" s="16">
-        <v>0</v>
-      </c>
-      <c r="L153" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M153" s="16">
+      <c r="M153" s="17">
         <v>0</v>
       </c>
       <c r="N153">
         <v>10000</v>
       </c>
-      <c r="O153" s="25">
+      <c r="O153" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8318,47 +8927,47 @@
         <f t="shared" si="2"/>
         <v>10240012</v>
       </c>
-      <c r="B154" s="15">
+      <c r="B154" s="16">
         <v>102400</v>
       </c>
-      <c r="C154" s="15">
-        <v>1</v>
-      </c>
-      <c r="D154" s="15" t="str">
+      <c r="C154" s="16">
+        <v>1</v>
+      </c>
+      <c r="D154" s="16" t="str">
         <f t="shared" si="6"/>
         <v>财富银行</v>
       </c>
-      <c r="E154" s="15">
+      <c r="E154" s="16">
         <v>102400026</v>
       </c>
-      <c r="F154" s="15" t="s">
+      <c r="F154" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G154" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H154" s="16">
+      <c r="G154" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H154" s="17">
         <v>12</v>
       </c>
-      <c r="I154" s="23">
-        <v>0</v>
-      </c>
-      <c r="J154" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K154" s="16">
-        <v>0</v>
-      </c>
-      <c r="L154" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M154" s="16">
+      <c r="I154" s="25">
+        <v>0</v>
+      </c>
+      <c r="J154" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K154" s="17">
+        <v>0</v>
+      </c>
+      <c r="L154" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M154" s="17">
         <v>0</v>
       </c>
       <c r="N154">
         <v>100000</v>
       </c>
-      <c r="O154" s="25">
+      <c r="O154" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8367,46 +8976,46 @@
         <f t="shared" si="2"/>
         <v>10220010</v>
       </c>
-      <c r="B155" s="15">
+      <c r="B155" s="16">
         <v>102200</v>
       </c>
-      <c r="C155" s="15">
-        <v>1</v>
-      </c>
-      <c r="D155" s="15" t="s">
+      <c r="C155" s="16">
+        <v>1</v>
+      </c>
+      <c r="D155" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E155" s="15">
+      <c r="E155" s="16">
         <v>102200001</v>
       </c>
-      <c r="F155" s="15" t="s">
+      <c r="F155" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="G155" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H155" s="16">
+      <c r="G155" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H155" s="17">
         <v>10</v>
       </c>
-      <c r="I155" s="23">
-        <v>0</v>
-      </c>
-      <c r="J155" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K155" s="16">
-        <v>0</v>
-      </c>
-      <c r="L155" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M155" s="16">
+      <c r="I155" s="25">
+        <v>0</v>
+      </c>
+      <c r="J155" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K155" s="17">
+        <v>0</v>
+      </c>
+      <c r="L155" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M155" s="17">
         <v>0</v>
       </c>
       <c r="N155">
         <v>1000</v>
       </c>
-      <c r="O155" s="25">
+      <c r="O155" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8415,46 +9024,46 @@
         <f t="shared" si="2"/>
         <v>10220011</v>
       </c>
-      <c r="B156" s="15">
+      <c r="B156" s="16">
         <v>102200</v>
       </c>
-      <c r="C156" s="15">
-        <v>1</v>
-      </c>
-      <c r="D156" s="15" t="s">
+      <c r="C156" s="16">
+        <v>1</v>
+      </c>
+      <c r="D156" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E156" s="15">
+      <c r="E156" s="16">
         <v>102200001</v>
       </c>
-      <c r="F156" s="15" t="s">
+      <c r="F156" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="G156" s="16" t="s">
+      <c r="G156" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H156" s="17">
+        <v>11</v>
+      </c>
+      <c r="I156" s="25">
+        <v>0</v>
+      </c>
+      <c r="J156" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K156" s="17">
+        <v>0</v>
+      </c>
+      <c r="L156" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H156" s="16">
-        <v>11</v>
-      </c>
-      <c r="I156" s="23">
-        <v>0</v>
-      </c>
-      <c r="J156" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K156" s="16">
-        <v>0</v>
-      </c>
-      <c r="L156" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M156" s="16">
+      <c r="M156" s="17">
         <v>0</v>
       </c>
       <c r="N156">
         <v>10000</v>
       </c>
-      <c r="O156" s="25">
+      <c r="O156" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8463,46 +9072,46 @@
         <f t="shared" si="2"/>
         <v>10220012</v>
       </c>
-      <c r="B157" s="15">
+      <c r="B157" s="16">
         <v>102200</v>
       </c>
-      <c r="C157" s="15">
-        <v>1</v>
-      </c>
-      <c r="D157" s="15" t="s">
+      <c r="C157" s="16">
+        <v>1</v>
+      </c>
+      <c r="D157" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E157" s="15">
+      <c r="E157" s="16">
         <v>102200001</v>
       </c>
-      <c r="F157" s="15" t="s">
+      <c r="F157" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="G157" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H157" s="16">
+      <c r="G157" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H157" s="17">
         <v>12</v>
       </c>
-      <c r="I157" s="23">
-        <v>0</v>
-      </c>
-      <c r="J157" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K157" s="16">
-        <v>0</v>
-      </c>
-      <c r="L157" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M157" s="16">
+      <c r="I157" s="25">
+        <v>0</v>
+      </c>
+      <c r="J157" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K157" s="17">
+        <v>0</v>
+      </c>
+      <c r="L157" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M157" s="17">
         <v>0</v>
       </c>
       <c r="N157">
         <v>100000</v>
       </c>
-      <c r="O157" s="25">
+      <c r="O157" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8511,46 +9120,46 @@
         <f t="shared" si="2"/>
         <v>10170010</v>
       </c>
-      <c r="B158" s="15">
+      <c r="B158" s="16">
         <v>101700</v>
       </c>
-      <c r="C158" s="15">
-        <v>1</v>
-      </c>
-      <c r="D158" s="15" t="s">
+      <c r="C158" s="16">
+        <v>1</v>
+      </c>
+      <c r="D158" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E158" s="15">
+      <c r="E158" s="16">
         <v>101700001</v>
       </c>
-      <c r="F158" s="15" t="s">
+      <c r="F158" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="G158" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H158" s="16">
+      <c r="G158" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H158" s="17">
         <v>10</v>
       </c>
-      <c r="I158" s="23">
-        <v>0</v>
-      </c>
-      <c r="J158" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K158" s="16">
-        <v>0</v>
-      </c>
-      <c r="L158" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M158" s="16">
+      <c r="I158" s="25">
+        <v>0</v>
+      </c>
+      <c r="J158" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K158" s="17">
+        <v>0</v>
+      </c>
+      <c r="L158" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M158" s="17">
         <v>0</v>
       </c>
       <c r="N158">
         <v>1000</v>
       </c>
-      <c r="O158" s="25">
+      <c r="O158" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8559,46 +9168,46 @@
         <f t="shared" si="2"/>
         <v>10170011</v>
       </c>
-      <c r="B159" s="15">
+      <c r="B159" s="16">
         <v>101700</v>
       </c>
-      <c r="C159" s="15">
-        <v>1</v>
-      </c>
-      <c r="D159" s="15" t="s">
+      <c r="C159" s="16">
+        <v>1</v>
+      </c>
+      <c r="D159" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E159" s="15">
+      <c r="E159" s="16">
         <v>101700001</v>
       </c>
-      <c r="F159" s="15" t="s">
+      <c r="F159" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="G159" s="16" t="s">
+      <c r="G159" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H159" s="17">
+        <v>11</v>
+      </c>
+      <c r="I159" s="25">
+        <v>0</v>
+      </c>
+      <c r="J159" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K159" s="17">
+        <v>0</v>
+      </c>
+      <c r="L159" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H159" s="16">
-        <v>11</v>
-      </c>
-      <c r="I159" s="23">
-        <v>0</v>
-      </c>
-      <c r="J159" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K159" s="16">
-        <v>0</v>
-      </c>
-      <c r="L159" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M159" s="16">
+      <c r="M159" s="17">
         <v>0</v>
       </c>
       <c r="N159">
         <v>10000</v>
       </c>
-      <c r="O159" s="25">
+      <c r="O159" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8607,46 +9216,46 @@
         <f t="shared" si="2"/>
         <v>10170012</v>
       </c>
-      <c r="B160" s="15">
+      <c r="B160" s="16">
         <v>101700</v>
       </c>
-      <c r="C160" s="15">
-        <v>1</v>
-      </c>
-      <c r="D160" s="15" t="s">
+      <c r="C160" s="16">
+        <v>1</v>
+      </c>
+      <c r="D160" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E160" s="15">
+      <c r="E160" s="16">
         <v>101700001</v>
       </c>
-      <c r="F160" s="15" t="s">
+      <c r="F160" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="G160" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H160" s="16">
+      <c r="G160" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H160" s="17">
         <v>12</v>
       </c>
-      <c r="I160" s="23">
-        <v>0</v>
-      </c>
-      <c r="J160" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K160" s="16">
-        <v>0</v>
-      </c>
-      <c r="L160" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M160" s="16">
+      <c r="I160" s="25">
+        <v>0</v>
+      </c>
+      <c r="J160" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K160" s="17">
+        <v>0</v>
+      </c>
+      <c r="L160" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M160" s="17">
         <v>0</v>
       </c>
       <c r="N160">
         <v>100000</v>
       </c>
-      <c r="O160" s="25">
+      <c r="O160" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8655,46 +9264,46 @@
         <f t="shared" si="2"/>
         <v>10210010</v>
       </c>
-      <c r="B161" s="15">
+      <c r="B161" s="16">
         <v>102100</v>
       </c>
-      <c r="C161" s="15">
-        <v>1</v>
-      </c>
-      <c r="D161" s="15" t="s">
+      <c r="C161" s="16">
+        <v>1</v>
+      </c>
+      <c r="D161" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E161" s="15">
+      <c r="E161" s="16">
         <v>102100001</v>
       </c>
-      <c r="F161" s="15" t="s">
+      <c r="F161" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G161" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H161" s="16">
+      <c r="G161" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H161" s="17">
         <v>10</v>
       </c>
-      <c r="I161" s="23">
-        <v>0</v>
-      </c>
-      <c r="J161" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K161" s="16">
-        <v>0</v>
-      </c>
-      <c r="L161" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M161" s="16">
+      <c r="I161" s="25">
+        <v>0</v>
+      </c>
+      <c r="J161" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K161" s="17">
+        <v>0</v>
+      </c>
+      <c r="L161" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M161" s="17">
         <v>0</v>
       </c>
       <c r="N161">
         <v>1000</v>
       </c>
-      <c r="O161" s="25">
+      <c r="O161" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8703,46 +9312,46 @@
         <f t="shared" si="2"/>
         <v>10210011</v>
       </c>
-      <c r="B162" s="15">
+      <c r="B162" s="16">
         <v>102100</v>
       </c>
-      <c r="C162" s="15">
-        <v>1</v>
-      </c>
-      <c r="D162" s="15" t="s">
+      <c r="C162" s="16">
+        <v>1</v>
+      </c>
+      <c r="D162" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E162" s="15">
+      <c r="E162" s="16">
         <v>102100001</v>
       </c>
-      <c r="F162" s="15" t="s">
+      <c r="F162" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G162" s="16" t="s">
+      <c r="G162" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H162" s="17">
+        <v>11</v>
+      </c>
+      <c r="I162" s="25">
+        <v>0</v>
+      </c>
+      <c r="J162" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K162" s="17">
+        <v>0</v>
+      </c>
+      <c r="L162" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H162" s="16">
-        <v>11</v>
-      </c>
-      <c r="I162" s="23">
-        <v>0</v>
-      </c>
-      <c r="J162" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K162" s="16">
-        <v>0</v>
-      </c>
-      <c r="L162" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M162" s="16">
+      <c r="M162" s="17">
         <v>0</v>
       </c>
       <c r="N162">
         <v>10000</v>
       </c>
-      <c r="O162" s="25">
+      <c r="O162" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8751,46 +9360,46 @@
         <f t="shared" si="2"/>
         <v>10210012</v>
       </c>
-      <c r="B163" s="15">
+      <c r="B163" s="16">
         <v>102100</v>
       </c>
-      <c r="C163" s="15">
-        <v>1</v>
-      </c>
-      <c r="D163" s="15" t="s">
+      <c r="C163" s="16">
+        <v>1</v>
+      </c>
+      <c r="D163" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E163" s="15">
+      <c r="E163" s="16">
         <v>102100001</v>
       </c>
-      <c r="F163" s="15" t="s">
+      <c r="F163" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G163" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H163" s="16">
+      <c r="G163" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H163" s="17">
         <v>12</v>
       </c>
-      <c r="I163" s="23">
-        <v>0</v>
-      </c>
-      <c r="J163" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K163" s="16">
-        <v>0</v>
-      </c>
-      <c r="L163" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M163" s="16">
+      <c r="I163" s="25">
+        <v>0</v>
+      </c>
+      <c r="J163" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K163" s="17">
+        <v>0</v>
+      </c>
+      <c r="L163" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M163" s="17">
         <v>0</v>
       </c>
       <c r="N163">
         <v>100000</v>
       </c>
-      <c r="O163" s="25">
+      <c r="O163" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8799,46 +9408,46 @@
         <f t="shared" si="2"/>
         <v>10180010</v>
       </c>
-      <c r="B164" s="15">
+      <c r="B164" s="16">
         <v>101800</v>
       </c>
-      <c r="C164" s="15">
-        <v>1</v>
-      </c>
-      <c r="D164" s="15" t="s">
+      <c r="C164" s="16">
+        <v>1</v>
+      </c>
+      <c r="D164" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E164" s="15">
+      <c r="E164" s="16">
         <v>101800001</v>
       </c>
-      <c r="F164" s="15" t="s">
+      <c r="F164" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="G164" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H164" s="16">
+      <c r="G164" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H164" s="17">
         <v>10</v>
       </c>
-      <c r="I164" s="23">
-        <v>0</v>
-      </c>
-      <c r="J164" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K164" s="16">
-        <v>0</v>
-      </c>
-      <c r="L164" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M164" s="16">
+      <c r="I164" s="25">
+        <v>0</v>
+      </c>
+      <c r="J164" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K164" s="17">
+        <v>0</v>
+      </c>
+      <c r="L164" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M164" s="17">
         <v>0</v>
       </c>
       <c r="N164">
         <v>1000</v>
       </c>
-      <c r="O164" s="25">
+      <c r="O164" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8847,46 +9456,46 @@
         <f t="shared" si="2"/>
         <v>10180011</v>
       </c>
-      <c r="B165" s="15">
+      <c r="B165" s="16">
         <v>101800</v>
       </c>
-      <c r="C165" s="15">
-        <v>1</v>
-      </c>
-      <c r="D165" s="15" t="s">
+      <c r="C165" s="16">
+        <v>1</v>
+      </c>
+      <c r="D165" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E165" s="15">
+      <c r="E165" s="16">
         <v>101800001</v>
       </c>
-      <c r="F165" s="15" t="s">
+      <c r="F165" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="G165" s="16" t="s">
+      <c r="G165" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H165" s="17">
+        <v>11</v>
+      </c>
+      <c r="I165" s="25">
+        <v>0</v>
+      </c>
+      <c r="J165" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K165" s="17">
+        <v>0</v>
+      </c>
+      <c r="L165" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H165" s="16">
-        <v>11</v>
-      </c>
-      <c r="I165" s="23">
-        <v>0</v>
-      </c>
-      <c r="J165" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K165" s="16">
-        <v>0</v>
-      </c>
-      <c r="L165" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M165" s="16">
+      <c r="M165" s="17">
         <v>0</v>
       </c>
       <c r="N165">
         <v>10000</v>
       </c>
-      <c r="O165" s="25">
+      <c r="O165" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8895,46 +9504,46 @@
         <f t="shared" si="2"/>
         <v>10180012</v>
       </c>
-      <c r="B166" s="15">
+      <c r="B166" s="16">
         <v>101800</v>
       </c>
-      <c r="C166" s="15">
-        <v>1</v>
-      </c>
-      <c r="D166" s="15" t="s">
+      <c r="C166" s="16">
+        <v>1</v>
+      </c>
+      <c r="D166" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E166" s="15">
+      <c r="E166" s="16">
         <v>101800001</v>
       </c>
-      <c r="F166" s="15" t="s">
+      <c r="F166" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="G166" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H166" s="16">
+      <c r="G166" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H166" s="17">
         <v>12</v>
       </c>
-      <c r="I166" s="23">
-        <v>0</v>
-      </c>
-      <c r="J166" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K166" s="16">
-        <v>0</v>
-      </c>
-      <c r="L166" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M166" s="16">
+      <c r="I166" s="25">
+        <v>0</v>
+      </c>
+      <c r="J166" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K166" s="17">
+        <v>0</v>
+      </c>
+      <c r="L166" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M166" s="17">
         <v>0</v>
       </c>
       <c r="N166">
         <v>100000</v>
       </c>
-      <c r="O166" s="25">
+      <c r="O166" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8943,46 +9552,46 @@
         <f t="shared" si="2"/>
         <v>10250010</v>
       </c>
-      <c r="B167" s="15">
+      <c r="B167" s="16">
         <v>102500</v>
       </c>
-      <c r="C167" s="15">
-        <v>1</v>
-      </c>
-      <c r="D167" s="15" t="s">
+      <c r="C167" s="16">
+        <v>1</v>
+      </c>
+      <c r="D167" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E167" s="15">
+      <c r="E167" s="16">
         <v>102500001</v>
       </c>
-      <c r="F167" s="15" t="s">
+      <c r="F167" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="G167" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H167" s="16">
+      <c r="G167" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H167" s="17">
         <v>10</v>
       </c>
-      <c r="I167" s="23">
-        <v>0</v>
-      </c>
-      <c r="J167" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K167" s="16">
-        <v>0</v>
-      </c>
-      <c r="L167" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M167" s="16">
+      <c r="I167" s="25">
+        <v>0</v>
+      </c>
+      <c r="J167" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K167" s="17">
+        <v>0</v>
+      </c>
+      <c r="L167" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M167" s="17">
         <v>0</v>
       </c>
       <c r="N167">
         <v>1000</v>
       </c>
-      <c r="O167" s="25">
+      <c r="O167" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -8991,46 +9600,46 @@
         <f t="shared" si="2"/>
         <v>10250011</v>
       </c>
-      <c r="B168" s="15">
+      <c r="B168" s="16">
         <v>102500</v>
       </c>
-      <c r="C168" s="15">
-        <v>1</v>
-      </c>
-      <c r="D168" s="15" t="s">
+      <c r="C168" s="16">
+        <v>1</v>
+      </c>
+      <c r="D168" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E168" s="15">
+      <c r="E168" s="16">
         <v>102500001</v>
       </c>
-      <c r="F168" s="15" t="s">
+      <c r="F168" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="G168" s="16" t="s">
+      <c r="G168" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H168" s="17">
+        <v>11</v>
+      </c>
+      <c r="I168" s="25">
+        <v>0</v>
+      </c>
+      <c r="J168" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K168" s="17">
+        <v>0</v>
+      </c>
+      <c r="L168" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H168" s="16">
-        <v>11</v>
-      </c>
-      <c r="I168" s="23">
-        <v>0</v>
-      </c>
-      <c r="J168" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K168" s="16">
-        <v>0</v>
-      </c>
-      <c r="L168" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M168" s="16">
+      <c r="M168" s="17">
         <v>0</v>
       </c>
       <c r="N168">
         <v>10000</v>
       </c>
-      <c r="O168" s="25">
+      <c r="O168" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9039,46 +9648,46 @@
         <f t="shared" si="2"/>
         <v>10250012</v>
       </c>
-      <c r="B169" s="15">
+      <c r="B169" s="16">
         <v>102500</v>
       </c>
-      <c r="C169" s="15">
-        <v>1</v>
-      </c>
-      <c r="D169" s="15" t="s">
+      <c r="C169" s="16">
+        <v>1</v>
+      </c>
+      <c r="D169" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E169" s="15">
+      <c r="E169" s="16">
         <v>102500001</v>
       </c>
-      <c r="F169" s="15" t="s">
+      <c r="F169" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="G169" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H169" s="16">
+      <c r="G169" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H169" s="17">
         <v>12</v>
       </c>
-      <c r="I169" s="23">
-        <v>0</v>
-      </c>
-      <c r="J169" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K169" s="16">
-        <v>0</v>
-      </c>
-      <c r="L169" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M169" s="16">
+      <c r="I169" s="25">
+        <v>0</v>
+      </c>
+      <c r="J169" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K169" s="17">
+        <v>0</v>
+      </c>
+      <c r="L169" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M169" s="17">
         <v>0</v>
       </c>
       <c r="N169">
         <v>100000</v>
       </c>
-      <c r="O169" s="25">
+      <c r="O169" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9087,46 +9696,46 @@
         <f t="shared" si="2"/>
         <v>10230010</v>
       </c>
-      <c r="B170" s="15">
+      <c r="B170" s="16">
         <v>102300</v>
       </c>
-      <c r="C170" s="15">
-        <v>1</v>
-      </c>
-      <c r="D170" s="15" t="s">
+      <c r="C170" s="16">
+        <v>1</v>
+      </c>
+      <c r="D170" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E170" s="15">
+      <c r="E170" s="16">
         <v>102300001</v>
       </c>
-      <c r="F170" s="15" t="s">
+      <c r="F170" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G170" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H170" s="16">
+      <c r="G170" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H170" s="17">
         <v>10</v>
       </c>
-      <c r="I170" s="23">
-        <v>0</v>
-      </c>
-      <c r="J170" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K170" s="16">
-        <v>0</v>
-      </c>
-      <c r="L170" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M170" s="16">
+      <c r="I170" s="25">
+        <v>0</v>
+      </c>
+      <c r="J170" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K170" s="17">
+        <v>0</v>
+      </c>
+      <c r="L170" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M170" s="17">
         <v>0</v>
       </c>
       <c r="N170">
         <v>1000</v>
       </c>
-      <c r="O170" s="25">
+      <c r="O170" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9135,46 +9744,46 @@
         <f t="shared" si="2"/>
         <v>10230011</v>
       </c>
-      <c r="B171" s="15">
+      <c r="B171" s="16">
         <v>102300</v>
       </c>
-      <c r="C171" s="15">
-        <v>1</v>
-      </c>
-      <c r="D171" s="15" t="s">
+      <c r="C171" s="16">
+        <v>1</v>
+      </c>
+      <c r="D171" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E171" s="15">
+      <c r="E171" s="16">
         <v>102300001</v>
       </c>
-      <c r="F171" s="15" t="s">
+      <c r="F171" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G171" s="16" t="s">
+      <c r="G171" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H171" s="17">
+        <v>11</v>
+      </c>
+      <c r="I171" s="25">
+        <v>0</v>
+      </c>
+      <c r="J171" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K171" s="17">
+        <v>0</v>
+      </c>
+      <c r="L171" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H171" s="16">
-        <v>11</v>
-      </c>
-      <c r="I171" s="23">
-        <v>0</v>
-      </c>
-      <c r="J171" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K171" s="16">
-        <v>0</v>
-      </c>
-      <c r="L171" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M171" s="16">
+      <c r="M171" s="17">
         <v>0</v>
       </c>
       <c r="N171">
         <v>10000</v>
       </c>
-      <c r="O171" s="25">
+      <c r="O171" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9183,46 +9792,46 @@
         <f t="shared" si="2"/>
         <v>10230012</v>
       </c>
-      <c r="B172" s="15">
+      <c r="B172" s="16">
         <v>102300</v>
       </c>
-      <c r="C172" s="15">
-        <v>1</v>
-      </c>
-      <c r="D172" s="15" t="s">
+      <c r="C172" s="16">
+        <v>1</v>
+      </c>
+      <c r="D172" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E172" s="15">
+      <c r="E172" s="16">
         <v>102300001</v>
       </c>
-      <c r="F172" s="15" t="s">
+      <c r="F172" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G172" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H172" s="16">
+      <c r="G172" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="H172" s="17">
         <v>12</v>
       </c>
-      <c r="I172" s="23">
-        <v>0</v>
-      </c>
-      <c r="J172" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K172" s="16">
-        <v>0</v>
-      </c>
-      <c r="L172" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M172" s="16">
+      <c r="I172" s="25">
+        <v>0</v>
+      </c>
+      <c r="J172" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K172" s="17">
+        <v>0</v>
+      </c>
+      <c r="L172" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M172" s="17">
         <v>0</v>
       </c>
       <c r="N172">
         <v>100000</v>
       </c>
-      <c r="O172" s="25">
+      <c r="O172" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9246,8 +9855,8 @@
       <c r="F173" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G173" s="16" t="s">
-        <v>108</v>
+      <c r="G173" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="H173" s="1">
         <v>10</v>
@@ -9255,22 +9864,22 @@
       <c r="I173" s="2">
         <v>0</v>
       </c>
-      <c r="J173" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K173" s="16">
-        <v>0</v>
-      </c>
-      <c r="L173" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M173" s="16">
+      <c r="J173" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K173" s="17">
+        <v>0</v>
+      </c>
+      <c r="L173" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M173" s="17">
         <v>0</v>
       </c>
       <c r="N173">
         <v>1000</v>
       </c>
-      <c r="O173" s="25">
+      <c r="O173" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9294,8 +9903,8 @@
       <c r="F174" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G174" s="16" t="s">
-        <v>110</v>
+      <c r="G174" s="17" t="s">
+        <v>111</v>
       </c>
       <c r="H174" s="1">
         <v>11</v>
@@ -9303,22 +9912,22 @@
       <c r="I174" s="2">
         <v>0</v>
       </c>
-      <c r="J174" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K174" s="16">
-        <v>0</v>
-      </c>
-      <c r="L174" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M174" s="16">
+      <c r="J174" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K174" s="17">
+        <v>0</v>
+      </c>
+      <c r="L174" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M174" s="17">
         <v>0</v>
       </c>
       <c r="N174">
         <v>10000</v>
       </c>
-      <c r="O174" s="25">
+      <c r="O174" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9342,8 +9951,8 @@
       <c r="F175" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G175" s="16" t="s">
-        <v>111</v>
+      <c r="G175" s="17" t="s">
+        <v>112</v>
       </c>
       <c r="H175" s="1">
         <v>12</v>
@@ -9351,22 +9960,22 @@
       <c r="I175" s="2">
         <v>0</v>
       </c>
-      <c r="J175" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K175" s="16">
-        <v>0</v>
-      </c>
-      <c r="L175" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M175" s="16">
+      <c r="J175" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K175" s="17">
+        <v>0</v>
+      </c>
+      <c r="L175" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M175" s="17">
         <v>0</v>
       </c>
       <c r="N175">
         <v>100000</v>
       </c>
-      <c r="O175" s="25">
+      <c r="O175" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9390,8 +9999,8 @@
       <c r="F176" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G176" s="16" t="s">
-        <v>108</v>
+      <c r="G176" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="H176" s="1">
         <v>10</v>
@@ -9399,22 +10008,22 @@
       <c r="I176" s="2">
         <v>0</v>
       </c>
-      <c r="J176" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K176" s="16">
-        <v>0</v>
-      </c>
-      <c r="L176" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M176" s="16">
+      <c r="J176" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K176" s="17">
+        <v>0</v>
+      </c>
+      <c r="L176" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M176" s="17">
         <v>0</v>
       </c>
       <c r="N176">
         <v>1000</v>
       </c>
-      <c r="O176" s="25">
+      <c r="O176" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9438,8 +10047,8 @@
       <c r="F177" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G177" s="16" t="s">
-        <v>110</v>
+      <c r="G177" s="17" t="s">
+        <v>111</v>
       </c>
       <c r="H177" s="1">
         <v>11</v>
@@ -9447,22 +10056,22 @@
       <c r="I177" s="2">
         <v>0</v>
       </c>
-      <c r="J177" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K177" s="16">
-        <v>0</v>
-      </c>
-      <c r="L177" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M177" s="16">
+      <c r="J177" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K177" s="17">
+        <v>0</v>
+      </c>
+      <c r="L177" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M177" s="17">
         <v>0</v>
       </c>
       <c r="N177">
         <v>10000</v>
       </c>
-      <c r="O177" s="25">
+      <c r="O177" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9486,8 +10095,8 @@
       <c r="F178" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G178" s="16" t="s">
-        <v>111</v>
+      <c r="G178" s="17" t="s">
+        <v>112</v>
       </c>
       <c r="H178" s="1">
         <v>12</v>
@@ -9495,22 +10104,22 @@
       <c r="I178" s="2">
         <v>0</v>
       </c>
-      <c r="J178" s="16">
-        <v>-1</v>
-      </c>
-      <c r="K178" s="16">
-        <v>0</v>
-      </c>
-      <c r="L178" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M178" s="16">
+      <c r="J178" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K178" s="17">
+        <v>0</v>
+      </c>
+      <c r="L178" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M178" s="17">
         <v>0</v>
       </c>
       <c r="N178">
         <v>100000</v>
       </c>
-      <c r="O178" s="25">
+      <c r="O178" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9534,8 +10143,8 @@
       <c r="F179" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G179" s="16" t="s">
-        <v>108</v>
+      <c r="G179" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="H179" s="1">
         <v>10</v>
@@ -9543,22 +10152,22 @@
       <c r="I179" s="2">
         <v>0</v>
       </c>
-      <c r="J179" s="16">
+      <c r="J179" s="17">
         <v>-1</v>
       </c>
       <c r="K179" s="1">
         <v>0</v>
       </c>
-      <c r="L179" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M179" s="16">
+      <c r="L179" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M179" s="17">
         <v>0</v>
       </c>
       <c r="N179">
         <v>1000</v>
       </c>
-      <c r="O179" s="25">
+      <c r="O179" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9582,8 +10191,8 @@
       <c r="F180" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G180" s="16" t="s">
-        <v>110</v>
+      <c r="G180" s="17" t="s">
+        <v>111</v>
       </c>
       <c r="H180" s="1">
         <v>11</v>
@@ -9591,22 +10200,22 @@
       <c r="I180" s="2">
         <v>0</v>
       </c>
-      <c r="J180" s="16">
+      <c r="J180" s="17">
         <v>-1</v>
       </c>
       <c r="K180" s="1">
         <v>0</v>
       </c>
-      <c r="L180" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M180" s="16">
+      <c r="L180" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M180" s="17">
         <v>0</v>
       </c>
       <c r="N180">
         <v>10000</v>
       </c>
-      <c r="O180" s="25">
+      <c r="O180" s="27">
         <v>1980000</v>
       </c>
     </row>
@@ -9630,8 +10239,8 @@
       <c r="F181" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G181" s="16" t="s">
-        <v>111</v>
+      <c r="G181" s="17" t="s">
+        <v>112</v>
       </c>
       <c r="H181" s="1">
         <v>12</v>
@@ -9639,29 +10248,29 @@
       <c r="I181" s="2">
         <v>0</v>
       </c>
-      <c r="J181" s="16">
+      <c r="J181" s="17">
         <v>-1</v>
       </c>
       <c r="K181" s="1">
         <v>0</v>
       </c>
-      <c r="L181" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M181" s="16">
+      <c r="L181" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M181" s="17">
         <v>0</v>
       </c>
       <c r="N181">
         <v>100000</v>
       </c>
-      <c r="O181" s="25">
+      <c r="O181" s="27">
         <v>1980000</v>
       </c>
     </row>
-    <row r="182" spans="1:15" ht="12" customHeight="1"/>
+    <row r="182" ht="12" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD1F749-0F5F-473E-BAFC-DFABEF91ADD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -27,18 +33,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -47,6 +54,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -57,13 +65,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -72,6 +81,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -79,13 +89,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -94,6 +105,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -102,37 +114,40 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最小准入金币</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>-1 表示无上限</t>
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -141,6 +156,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -156,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="113">
   <si>
     <t>sid</t>
   </si>
@@ -474,9 +490,6 @@
   </si>
   <si>
     <t>4:4</t>
-  </si>
-  <si>
-    <t>1:0</t>
   </si>
   <si>
     <t>俄罗斯轮盘</t>
@@ -503,14 +516,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="31">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -562,173 +569,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -737,228 +609,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799340800195319"/>
+        <fgColor theme="5" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799340800195319"/>
+        <fgColor theme="4" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -981,272 +667,30 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="60">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1263,13 +707,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1287,9 +731,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1317,9 +758,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1330,79 +768,32 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="60">
+  <cellStyles count="12">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 2 2" xfId="50"/>
-    <cellStyle name="常规 2 2 2" xfId="51"/>
-    <cellStyle name="常规 3" xfId="52"/>
-    <cellStyle name="常规 3 2" xfId="53"/>
-    <cellStyle name="常规 4" xfId="54"/>
-    <cellStyle name="常规 5" xfId="55"/>
-    <cellStyle name="常规 6" xfId="56"/>
-    <cellStyle name="常规 6 2" xfId="57"/>
-    <cellStyle name="常规 6 2 2" xfId="58"/>
-    <cellStyle name="常规 7" xfId="59"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="常规 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="常规 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="常规 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="常规 6 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="常规 7" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1660,13 +1051,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:R182"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S182"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
@@ -1821,7 +1212,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:15">
+    <row r="4" spans="1:15" ht="14.25">
       <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
@@ -1864,13 +1255,13 @@
       <c r="L5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="28" t="s">
+      <c r="M5" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N5">
         <v>1000</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -1911,13 +1302,13 @@
       <c r="L6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="28" t="s">
+      <c r="M6" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N6">
         <v>10000</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -1958,13 +1349,13 @@
       <c r="L7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="28" t="s">
+      <c r="M7" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N7">
         <v>100000</v>
       </c>
-      <c r="O7" s="15">
+      <c r="O7" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2005,13 +1396,13 @@
       <c r="L8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="28" t="s">
+      <c r="M8" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N8">
         <v>1000</v>
       </c>
-      <c r="O8" s="15">
+      <c r="O8" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2052,13 +1443,13 @@
       <c r="L9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M9" s="28" t="s">
+      <c r="M9" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N9">
         <v>10000</v>
       </c>
-      <c r="O9" s="15">
+      <c r="O9" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2099,13 +1490,13 @@
       <c r="L10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M10" s="28" t="s">
+      <c r="M10" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N10">
         <v>100000</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2146,13 +1537,13 @@
       <c r="L11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="28" t="s">
+      <c r="M11" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N11">
         <v>1000</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2193,13 +1584,13 @@
       <c r="L12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="28" t="s">
+      <c r="M12" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N12">
         <v>10000</v>
       </c>
-      <c r="O12" s="15">
+      <c r="O12" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2240,13 +1631,13 @@
       <c r="L13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="28" t="s">
+      <c r="M13" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N13">
         <v>100000</v>
       </c>
-      <c r="O13" s="15">
+      <c r="O13" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2287,13 +1678,13 @@
       <c r="L14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M14" s="28" t="s">
+      <c r="M14" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N14">
         <v>120</v>
       </c>
-      <c r="O14" s="15">
+      <c r="O14" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2334,13 +1725,13 @@
       <c r="L15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="28" t="s">
+      <c r="M15" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N15">
         <v>15000</v>
       </c>
-      <c r="O15" s="15">
+      <c r="O15" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2381,13 +1772,13 @@
       <c r="L16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M16" s="28" t="s">
+      <c r="M16" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N16">
         <v>150000</v>
       </c>
-      <c r="O16" s="15">
+      <c r="O16" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2428,13 +1819,13 @@
       <c r="L17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M17" s="28" t="s">
+      <c r="M17" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N17">
         <v>1000</v>
       </c>
-      <c r="O17" s="15">
+      <c r="O17" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2475,13 +1866,13 @@
       <c r="L18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M18" s="28" t="s">
+      <c r="M18" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N18">
         <v>10000</v>
       </c>
-      <c r="O18" s="15">
+      <c r="O18" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2522,13 +1913,13 @@
       <c r="L19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="28" t="s">
+      <c r="M19" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N19">
         <v>100000</v>
       </c>
-      <c r="O19" s="15">
+      <c r="O19" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2569,13 +1960,13 @@
       <c r="L20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M20" s="28" t="s">
+      <c r="M20" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N20">
         <v>100</v>
       </c>
-      <c r="O20" s="15">
+      <c r="O20" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2616,13 +2007,13 @@
       <c r="L21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M21" s="28" t="s">
+      <c r="M21" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N21">
         <v>10000</v>
       </c>
-      <c r="O21" s="15">
+      <c r="O21" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2663,13 +2054,13 @@
       <c r="L22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M22" s="28" t="s">
+      <c r="M22" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N22">
         <v>100000</v>
       </c>
-      <c r="O22" s="15">
+      <c r="O22" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2710,13 +2101,13 @@
       <c r="L23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M23" s="28" t="s">
+      <c r="M23" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N23">
         <v>1250</v>
       </c>
-      <c r="O23" s="15">
+      <c r="O23" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2757,13 +2148,13 @@
       <c r="L24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M24" s="28" t="s">
+      <c r="M24" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N24">
         <v>12500</v>
       </c>
-      <c r="O24" s="15">
+      <c r="O24" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2804,13 +2195,13 @@
       <c r="L25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M25" s="28" t="s">
+      <c r="M25" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N25">
         <v>125000</v>
       </c>
-      <c r="O25" s="15">
+      <c r="O25" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2851,13 +2242,13 @@
       <c r="L26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M26" s="28" t="s">
+      <c r="M26" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N26">
         <v>1000</v>
       </c>
-      <c r="O26" s="15">
+      <c r="O26" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2898,13 +2289,13 @@
       <c r="L27" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="28" t="s">
+      <c r="M27" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N27">
         <v>10000</v>
       </c>
-      <c r="O27" s="15">
+      <c r="O27" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2945,13 +2336,13 @@
       <c r="L28" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N28">
         <v>100000</v>
       </c>
-      <c r="O28" s="15">
+      <c r="O28" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2971,7 +2362,7 @@
       <c r="E29" s="13">
         <v>102100001</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="15" t="s">
         <v>52</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -2992,13 +2383,13 @@
       <c r="L29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M29" s="28" t="s">
+      <c r="M29" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N29">
         <v>1000</v>
       </c>
-      <c r="O29" s="15">
+      <c r="O29" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3018,7 +2409,7 @@
       <c r="E30" s="13">
         <v>102100001</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="15" t="s">
         <v>52</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -3039,13 +2430,13 @@
       <c r="L30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M30" s="28" t="s">
+      <c r="M30" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N30">
         <v>10000</v>
       </c>
-      <c r="O30" s="15">
+      <c r="O30" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3065,7 +2456,7 @@
       <c r="E31" s="13">
         <v>102100001</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="15" t="s">
         <v>52</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -3086,13 +2477,13 @@
       <c r="L31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M31" s="28" t="s">
+      <c r="M31" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N31">
         <v>100000</v>
       </c>
-      <c r="O31" s="15">
+      <c r="O31" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3101,46 +2492,46 @@
         <f t="shared" ref="A32:A58" si="0">B32*10+H32</f>
         <v>1018001</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="15">
         <v>101800</v>
       </c>
-      <c r="C32" s="16">
-        <v>1</v>
-      </c>
-      <c r="D32" s="16" t="s">
+      <c r="C32" s="15">
+        <v>1</v>
+      </c>
+      <c r="D32" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="15">
         <v>101800001</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="15" t="s">
         <v>54</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="16">
         <v>1</v>
       </c>
       <c r="I32" s="2">
         <v>0</v>
       </c>
-      <c r="J32" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K32" s="17">
+      <c r="J32" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K32" s="16">
         <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M32" s="28" t="s">
+      <c r="M32" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N32">
         <v>1000</v>
       </c>
-      <c r="O32" s="15">
+      <c r="O32" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3149,46 +2540,46 @@
         <f t="shared" si="0"/>
         <v>1018002</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="15">
         <v>101800</v>
       </c>
-      <c r="C33" s="16">
-        <v>1</v>
-      </c>
-      <c r="D33" s="16" t="s">
+      <c r="C33" s="15">
+        <v>1</v>
+      </c>
+      <c r="D33" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="15">
         <v>101800001</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F33" s="15" t="s">
         <v>54</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="16">
         <v>2</v>
       </c>
       <c r="I33" s="2">
         <v>10000</v>
       </c>
-      <c r="J33" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K33" s="17">
+      <c r="J33" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K33" s="16">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M33" s="28" t="s">
+      <c r="M33" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N33">
         <v>10000</v>
       </c>
-      <c r="O33" s="15">
+      <c r="O33" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3197,46 +2588,46 @@
         <f t="shared" si="0"/>
         <v>1018003</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="15">
         <v>101800</v>
       </c>
-      <c r="C34" s="16">
-        <v>1</v>
-      </c>
-      <c r="D34" s="16" t="s">
+      <c r="C34" s="15">
+        <v>1</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="15">
         <v>101800001</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="15" t="s">
         <v>54</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="16">
         <v>3</v>
       </c>
       <c r="I34" s="2">
         <v>100000</v>
       </c>
-      <c r="J34" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K34" s="17">
+      <c r="J34" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K34" s="16">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M34" s="28" t="s">
+      <c r="M34" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N34">
         <v>100000</v>
       </c>
-      <c r="O34" s="15">
+      <c r="O34" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3245,46 +2636,46 @@
         <f t="shared" si="0"/>
         <v>1025001</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="15">
         <v>102500</v>
       </c>
-      <c r="C35" s="16">
-        <v>1</v>
-      </c>
-      <c r="D35" s="16" t="s">
+      <c r="C35" s="15">
+        <v>1</v>
+      </c>
+      <c r="D35" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="15">
         <v>102500001</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="15" t="s">
         <v>56</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="16">
         <v>1</v>
       </c>
       <c r="I35" s="2">
         <v>0</v>
       </c>
-      <c r="J35" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K35" s="17">
+      <c r="J35" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K35" s="16">
         <v>0</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M35" s="28" t="s">
+      <c r="M35" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N35">
         <v>1000</v>
       </c>
-      <c r="O35" s="15">
+      <c r="O35" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3293,46 +2684,46 @@
         <f t="shared" si="0"/>
         <v>1025002</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="15">
         <v>102500</v>
       </c>
-      <c r="C36" s="16">
-        <v>1</v>
-      </c>
-      <c r="D36" s="16" t="s">
+      <c r="C36" s="15">
+        <v>1</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="15">
         <v>102500001</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="15" t="s">
         <v>56</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H36" s="17">
+      <c r="H36" s="16">
         <v>2</v>
       </c>
       <c r="I36" s="2">
         <v>10000</v>
       </c>
-      <c r="J36" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K36" s="17">
+      <c r="J36" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K36" s="16">
         <v>0</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M36" s="28" t="s">
+      <c r="M36" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N36">
         <v>10000</v>
       </c>
-      <c r="O36" s="15">
+      <c r="O36" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3341,46 +2732,46 @@
         <f t="shared" si="0"/>
         <v>1025003</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="15">
         <v>102500</v>
       </c>
-      <c r="C37" s="16">
-        <v>1</v>
-      </c>
-      <c r="D37" s="16" t="s">
+      <c r="C37" s="15">
+        <v>1</v>
+      </c>
+      <c r="D37" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="15">
         <v>102500001</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="F37" s="15" t="s">
         <v>56</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="16">
         <v>3</v>
       </c>
       <c r="I37" s="2">
         <v>100000</v>
       </c>
-      <c r="J37" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K37" s="17">
+      <c r="J37" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K37" s="16">
         <v>0</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M37" s="28" t="s">
+      <c r="M37" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N37">
         <v>100000</v>
       </c>
-      <c r="O37" s="15">
+      <c r="O37" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3413,22 +2804,22 @@
       <c r="I38" s="2">
         <v>0</v>
       </c>
-      <c r="J38" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K38" s="17">
+      <c r="J38" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K38" s="16">
         <v>0</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M38" s="28" t="s">
+      <c r="M38" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N38">
         <v>1000</v>
       </c>
-      <c r="O38" s="15">
+      <c r="O38" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3461,22 +2852,22 @@
       <c r="I39" s="2">
         <v>10000</v>
       </c>
-      <c r="J39" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K39" s="17">
+      <c r="J39" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K39" s="16">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M39" s="28" t="s">
+      <c r="M39" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N39">
         <v>10000</v>
       </c>
-      <c r="O39" s="15">
+      <c r="O39" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3509,22 +2900,22 @@
       <c r="I40" s="2">
         <v>100000</v>
       </c>
-      <c r="J40" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K40" s="17">
+      <c r="J40" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K40" s="16">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M40" s="28" t="s">
+      <c r="M40" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N40">
         <v>100000</v>
       </c>
-      <c r="O40" s="15">
+      <c r="O40" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3544,7 +2935,7 @@
       <c r="E41" s="13">
         <v>103000001</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="17" t="s">
         <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -3556,22 +2947,22 @@
       <c r="I41" s="2">
         <v>0</v>
       </c>
-      <c r="J41" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K41" s="17">
+      <c r="J41" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K41" s="16">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M41" s="28" t="s">
+      <c r="M41" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N41">
         <v>100</v>
       </c>
-      <c r="O41" s="15">
+      <c r="O41" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3592,7 +2983,7 @@
       <c r="E42" s="13">
         <v>103000001</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="17" t="s">
         <v>60</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -3604,22 +2995,22 @@
       <c r="I42" s="2">
         <v>10000</v>
       </c>
-      <c r="J42" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K42" s="17">
+      <c r="J42" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K42" s="16">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M42" s="28" t="s">
+      <c r="M42" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N42">
         <v>10000</v>
       </c>
-      <c r="O42" s="15">
+      <c r="O42" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3640,7 +3031,7 @@
       <c r="E43" s="13">
         <v>103000001</v>
       </c>
-      <c r="F43" s="18" t="s">
+      <c r="F43" s="17" t="s">
         <v>60</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -3652,22 +3043,22 @@
       <c r="I43" s="2">
         <v>100000</v>
       </c>
-      <c r="J43" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K43" s="17">
+      <c r="J43" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K43" s="16">
         <v>0</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M43" s="28" t="s">
+      <c r="M43" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N43">
         <v>100000</v>
       </c>
-      <c r="O43" s="15">
+      <c r="O43" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3700,22 +3091,22 @@
       <c r="I44" s="2">
         <v>0</v>
       </c>
-      <c r="J44" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K44" s="17">
+      <c r="J44" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K44" s="16">
         <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M44" s="28" t="s">
+      <c r="M44" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N44">
         <v>1000</v>
       </c>
-      <c r="O44" s="15">
+      <c r="O44" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3748,22 +3139,22 @@
       <c r="I45" s="2">
         <v>10000</v>
       </c>
-      <c r="J45" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K45" s="17">
+      <c r="J45" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K45" s="16">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M45" s="28" t="s">
+      <c r="M45" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N45">
         <v>10000</v>
       </c>
-      <c r="O45" s="15">
+      <c r="O45" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3796,22 +3187,22 @@
       <c r="I46" s="2">
         <v>100000</v>
       </c>
-      <c r="J46" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K46" s="17">
+      <c r="J46" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K46" s="16">
         <v>0</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M46" s="28" t="s">
+      <c r="M46" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N46">
         <v>100000</v>
       </c>
-      <c r="O46" s="15">
+      <c r="O46" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3844,7 +3235,7 @@
       <c r="I47" s="2">
         <v>0</v>
       </c>
-      <c r="J47" s="17">
+      <c r="J47" s="16">
         <v>-1</v>
       </c>
       <c r="K47" s="1">
@@ -3853,13 +3244,13 @@
       <c r="L47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M47" s="28" t="s">
+      <c r="M47" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N47">
         <v>1000</v>
       </c>
-      <c r="O47" s="15">
+      <c r="O47" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3892,7 +3283,7 @@
       <c r="I48" s="2">
         <v>10000</v>
       </c>
-      <c r="J48" s="17">
+      <c r="J48" s="16">
         <v>-1</v>
       </c>
       <c r="K48" s="1">
@@ -3901,13 +3292,13 @@
       <c r="L48" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M48" s="28" t="s">
+      <c r="M48" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N48">
         <v>10000</v>
       </c>
-      <c r="O48" s="15">
+      <c r="O48" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3940,7 +3331,7 @@
       <c r="I49" s="2">
         <v>100000</v>
       </c>
-      <c r="J49" s="17">
+      <c r="J49" s="16">
         <v>-1</v>
       </c>
       <c r="K49" s="1">
@@ -3949,13 +3340,13 @@
       <c r="L49" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M49" s="28" t="s">
+      <c r="M49" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N49">
         <v>100000</v>
       </c>
-      <c r="O49" s="15">
+      <c r="O49" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3988,7 +3379,7 @@
       <c r="I50" s="2">
         <v>0</v>
       </c>
-      <c r="J50" s="17">
+      <c r="J50" s="16">
         <v>-1</v>
       </c>
       <c r="K50" s="1">
@@ -3997,13 +3388,13 @@
       <c r="L50" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M50" s="28" t="s">
+      <c r="M50" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N50">
         <v>1125</v>
       </c>
-      <c r="O50" s="15">
+      <c r="O50" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4036,7 +3427,7 @@
       <c r="I51" s="2">
         <v>10000</v>
       </c>
-      <c r="J51" s="17">
+      <c r="J51" s="16">
         <v>-1</v>
       </c>
       <c r="K51" s="1">
@@ -4045,13 +3436,13 @@
       <c r="L51" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M51" s="28" t="s">
+      <c r="M51" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N51">
         <v>11250</v>
       </c>
-      <c r="O51" s="15">
+      <c r="O51" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4084,7 +3475,7 @@
       <c r="I52" s="2">
         <v>100000</v>
       </c>
-      <c r="J52" s="17">
+      <c r="J52" s="16">
         <v>-1</v>
       </c>
       <c r="K52" s="1">
@@ -4093,13 +3484,13 @@
       <c r="L52" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M52" s="28" t="s">
+      <c r="M52" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N52">
         <v>112500</v>
       </c>
-      <c r="O52" s="15">
+      <c r="O52" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4132,7 +3523,7 @@
       <c r="I53" s="2">
         <v>0</v>
       </c>
-      <c r="J53" s="17">
+      <c r="J53" s="16">
         <v>-1</v>
       </c>
       <c r="K53" s="1">
@@ -4141,13 +3532,13 @@
       <c r="L53" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M53" s="28" t="s">
+      <c r="M53" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N53">
         <v>1000</v>
       </c>
-      <c r="O53" s="15">
+      <c r="O53" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4180,7 +3571,7 @@
       <c r="I54" s="2">
         <v>10000</v>
       </c>
-      <c r="J54" s="17">
+      <c r="J54" s="16">
         <v>-1</v>
       </c>
       <c r="K54" s="1">
@@ -4189,13 +3580,13 @@
       <c r="L54" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M54" s="28" t="s">
+      <c r="M54" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N54">
         <v>10000</v>
       </c>
-      <c r="O54" s="15">
+      <c r="O54" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4228,7 +3619,7 @@
       <c r="I55" s="2">
         <v>100000</v>
       </c>
-      <c r="J55" s="17">
+      <c r="J55" s="16">
         <v>-1</v>
       </c>
       <c r="K55" s="1">
@@ -4237,13 +3628,13 @@
       <c r="L55" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M55" s="28" t="s">
+      <c r="M55" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N55">
         <v>100000</v>
       </c>
-      <c r="O55" s="15">
+      <c r="O55" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4276,7 +3667,7 @@
       <c r="I56" s="2">
         <v>0</v>
       </c>
-      <c r="J56" s="17">
+      <c r="J56" s="16">
         <v>-1</v>
       </c>
       <c r="K56" s="1">
@@ -4285,13 +3676,13 @@
       <c r="L56" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M56" s="28" t="s">
+      <c r="M56" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N56">
         <v>1000</v>
       </c>
-      <c r="O56" s="15">
+      <c r="O56" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4324,7 +3715,7 @@
       <c r="I57" s="2">
         <v>10000</v>
       </c>
-      <c r="J57" s="17">
+      <c r="J57" s="16">
         <v>-1</v>
       </c>
       <c r="K57" s="1">
@@ -4333,13 +3724,13 @@
       <c r="L57" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M57" s="28" t="s">
+      <c r="M57" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N57">
         <v>10000</v>
       </c>
-      <c r="O57" s="15">
+      <c r="O57" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4372,7 +3763,7 @@
       <c r="I58" s="2">
         <v>100000</v>
       </c>
-      <c r="J58" s="17">
+      <c r="J58" s="16">
         <v>-1</v>
       </c>
       <c r="K58" s="1">
@@ -4381,13 +3772,13 @@
       <c r="L58" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M58" s="28" t="s">
+      <c r="M58" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N58">
         <v>100000</v>
       </c>
-      <c r="O58" s="15">
+      <c r="O58" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4419,7 +3810,7 @@
       <c r="I59" s="2">
         <v>0</v>
       </c>
-      <c r="J59" s="17">
+      <c r="J59" s="16">
         <v>-1</v>
       </c>
       <c r="K59" s="1">
@@ -4428,13 +3819,13 @@
       <c r="L59" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M59" s="28" t="s">
+      <c r="M59" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N59">
         <v>1000</v>
       </c>
-      <c r="O59" s="15">
+      <c r="O59" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4466,7 +3857,7 @@
       <c r="I60" s="2">
         <v>10000</v>
       </c>
-      <c r="J60" s="17">
+      <c r="J60" s="16">
         <v>-1</v>
       </c>
       <c r="K60" s="1">
@@ -4475,13 +3866,13 @@
       <c r="L60" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M60" s="28" t="s">
+      <c r="M60" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N60">
         <v>10000</v>
       </c>
-      <c r="O60" s="15">
+      <c r="O60" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4513,7 +3904,7 @@
       <c r="I61" s="2">
         <v>100000</v>
       </c>
-      <c r="J61" s="17">
+      <c r="J61" s="16">
         <v>-1</v>
       </c>
       <c r="K61" s="1">
@@ -4522,13 +3913,13 @@
       <c r="L61" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M61" s="28" t="s">
+      <c r="M61" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N61">
         <v>100000</v>
       </c>
-      <c r="O61" s="15">
+      <c r="O61" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4560,7 +3951,7 @@
       <c r="I62" s="2">
         <v>0</v>
       </c>
-      <c r="J62" s="17">
+      <c r="J62" s="16">
         <v>-1</v>
       </c>
       <c r="K62" s="1">
@@ -4569,13 +3960,13 @@
       <c r="L62" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M62" s="28" t="s">
+      <c r="M62" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N62">
         <v>1000</v>
       </c>
-      <c r="O62" s="15">
+      <c r="O62" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4607,7 +3998,7 @@
       <c r="I63" s="2">
         <v>10000</v>
       </c>
-      <c r="J63" s="17">
+      <c r="J63" s="16">
         <v>-1</v>
       </c>
       <c r="K63" s="1">
@@ -4616,13 +4007,13 @@
       <c r="L63" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M63" s="28" t="s">
+      <c r="M63" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N63">
         <v>10000</v>
       </c>
-      <c r="O63" s="15">
+      <c r="O63" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4654,7 +4045,7 @@
       <c r="I64" s="2">
         <v>100000</v>
       </c>
-      <c r="J64" s="17">
+      <c r="J64" s="16">
         <v>-1</v>
       </c>
       <c r="K64" s="1">
@@ -4663,13 +4054,13 @@
       <c r="L64" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M64" s="28" t="s">
+      <c r="M64" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N64">
         <v>100000</v>
       </c>
-      <c r="O64" s="15">
+      <c r="O64" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4689,7 +4080,7 @@
       <c r="E65" s="13">
         <v>104000001</v>
       </c>
-      <c r="F65" s="19" t="s">
+      <c r="F65" s="18" t="s">
         <v>76</v>
       </c>
       <c r="G65" s="1" t="s">
@@ -4701,7 +4092,7 @@
       <c r="I65" s="2">
         <v>0</v>
       </c>
-      <c r="J65" s="17">
+      <c r="J65" s="16">
         <v>-1</v>
       </c>
       <c r="K65" s="1">
@@ -4710,13 +4101,13 @@
       <c r="L65" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M65" s="28" t="s">
+      <c r="M65" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N65">
         <v>1000</v>
       </c>
-      <c r="O65" s="15">
+      <c r="O65" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4736,7 +4127,7 @@
       <c r="E66" s="13">
         <v>104000001</v>
       </c>
-      <c r="F66" s="19" t="s">
+      <c r="F66" s="18" t="s">
         <v>76</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -4748,7 +4139,7 @@
       <c r="I66" s="2">
         <v>10000</v>
       </c>
-      <c r="J66" s="17">
+      <c r="J66" s="16">
         <v>-1</v>
       </c>
       <c r="K66" s="1">
@@ -4757,13 +4148,13 @@
       <c r="L66" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M66" s="28" t="s">
+      <c r="M66" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N66">
         <v>10000</v>
       </c>
-      <c r="O66" s="15">
+      <c r="O66" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4783,7 +4174,7 @@
       <c r="E67" s="13">
         <v>104000001</v>
       </c>
-      <c r="F67" s="19" t="s">
+      <c r="F67" s="18" t="s">
         <v>76</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -4795,7 +4186,7 @@
       <c r="I67" s="2">
         <v>100000</v>
       </c>
-      <c r="J67" s="17">
+      <c r="J67" s="16">
         <v>-1</v>
       </c>
       <c r="K67" s="1">
@@ -4804,13 +4195,13 @@
       <c r="L67" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M67" s="28" t="s">
+      <c r="M67" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N67">
         <v>100000</v>
       </c>
-      <c r="O67" s="15">
+      <c r="O67" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4851,13 +4242,13 @@
       <c r="L68" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M68" s="28" t="s">
+      <c r="M68" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N68">
         <v>1000</v>
       </c>
-      <c r="O68" s="15">
+      <c r="O68" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4898,13 +4289,13 @@
       <c r="L69" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M69" s="28" t="s">
+      <c r="M69" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N69">
         <v>10000</v>
       </c>
-      <c r="O69" s="15">
+      <c r="O69" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -4945,13 +4336,13 @@
       <c r="L70" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M70" s="28" t="s">
+      <c r="M70" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N70">
         <v>100000</v>
       </c>
-      <c r="O70" s="15">
+      <c r="O70" s="14">
         <v>1990000</v>
       </c>
       <c r="Q70"/>
@@ -4993,13 +4384,13 @@
       <c r="L71" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M71" s="28" t="s">
+      <c r="M71" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N71">
         <v>1000</v>
       </c>
-      <c r="O71" s="15">
+      <c r="O71" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -5040,13 +4431,13 @@
       <c r="L72" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M72" s="28" t="s">
+      <c r="M72" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N72">
         <v>10000</v>
       </c>
-      <c r="O72" s="15">
+      <c r="O72" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -5087,13 +4478,13 @@
       <c r="L73" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M73" s="28" t="s">
+      <c r="M73" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N73">
         <v>100000</v>
       </c>
-      <c r="O73" s="15">
+      <c r="O73" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -5134,13 +4525,13 @@
       <c r="L74" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M74" s="28" t="s">
+      <c r="M74" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N74">
         <v>1000</v>
       </c>
-      <c r="O74" s="15">
+      <c r="O74" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -5181,13 +4572,13 @@
       <c r="L75" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M75" s="28" t="s">
+      <c r="M75" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N75">
         <v>10000</v>
       </c>
-      <c r="O75" s="15">
+      <c r="O75" s="14">
         <v>1990000</v>
       </c>
       <c r="Q75" s="2"/>
@@ -5230,13 +4621,13 @@
       <c r="L76" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M76" s="28" t="s">
+      <c r="M76" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N76">
         <v>100000</v>
       </c>
-      <c r="O76" s="15">
+      <c r="O76" s="14">
         <v>1990000</v>
       </c>
       <c r="Q76" s="2"/>
@@ -5279,13 +4670,13 @@
       <c r="L77" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M77" s="28" t="s">
+      <c r="M77" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N77">
         <v>1000</v>
       </c>
-      <c r="O77" s="15">
+      <c r="O77" s="14">
         <v>1990000</v>
       </c>
       <c r="Q77" s="2"/>
@@ -5328,13 +4719,13 @@
       <c r="L78" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M78" s="28" t="s">
+      <c r="M78" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N78">
         <v>10000</v>
       </c>
-      <c r="O78" s="15">
+      <c r="O78" s="14">
         <v>1990000</v>
       </c>
       <c r="Q78" s="2"/>
@@ -5377,13 +4768,13 @@
       <c r="L79" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M79" s="28" t="s">
+      <c r="M79" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N79">
         <v>100000</v>
       </c>
-      <c r="O79" s="15">
+      <c r="O79" s="14">
         <v>1990000</v>
       </c>
       <c r="Q79" s="2"/>
@@ -5426,13 +4817,13 @@
       <c r="L80" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M80" s="28" t="s">
+      <c r="M80" s="26" t="s">
         <v>87</v>
       </c>
       <c r="N80">
         <v>1000</v>
       </c>
-      <c r="O80" s="15">
+      <c r="O80" s="14">
         <v>1990000</v>
       </c>
       <c r="Q80" s="2"/>
@@ -5475,13 +4866,13 @@
       <c r="L81" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M81" s="28" t="s">
+      <c r="M81" s="26" t="s">
         <v>87</v>
       </c>
       <c r="N81">
         <v>10000</v>
       </c>
-      <c r="O81" s="15">
+      <c r="O81" s="14">
         <v>1990000</v>
       </c>
       <c r="Q81" s="2"/>
@@ -5524,13 +4915,13 @@
       <c r="L82" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M82" s="28" t="s">
+      <c r="M82" s="26" t="s">
         <v>87</v>
       </c>
       <c r="N82">
         <v>100000</v>
       </c>
-      <c r="O82" s="15">
+      <c r="O82" s="14">
         <v>1990000</v>
       </c>
       <c r="Q82" s="2"/>
@@ -5573,13 +4964,13 @@
       <c r="L83" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M83" s="28" t="s">
+      <c r="M83" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N83">
         <v>1000</v>
       </c>
-      <c r="O83" s="15">
+      <c r="O83" s="14">
         <v>1990000</v>
       </c>
       <c r="Q83" s="2"/>
@@ -5622,13 +5013,13 @@
       <c r="L84" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M84" s="28" t="s">
+      <c r="M84" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N84">
         <v>10000</v>
       </c>
-      <c r="O84" s="15">
+      <c r="O84" s="14">
         <v>1990000</v>
       </c>
       <c r="Q84" s="2"/>
@@ -5671,13 +5062,13 @@
       <c r="L85" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M85" s="28" t="s">
+      <c r="M85" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N85">
         <v>100000</v>
       </c>
-      <c r="O85" s="15">
+      <c r="O85" s="14">
         <v>1990000</v>
       </c>
       <c r="Q85" s="2"/>
@@ -5720,13 +5111,13 @@
       <c r="L86" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M86" s="28" t="s">
+      <c r="M86" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N86">
         <v>1000</v>
       </c>
-      <c r="O86" s="15">
+      <c r="O86" s="14">
         <v>1990000</v>
       </c>
       <c r="Q86" s="2"/>
@@ -5769,13 +5160,13 @@
       <c r="L87" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M87" s="28" t="s">
+      <c r="M87" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N87">
         <v>10000</v>
       </c>
-      <c r="O87" s="15">
+      <c r="O87" s="14">
         <v>1990000</v>
       </c>
       <c r="Q87" s="2"/>
@@ -5818,13 +5209,13 @@
       <c r="L88" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M88" s="28" t="s">
+      <c r="M88" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N88">
         <v>100000</v>
       </c>
-      <c r="O88" s="15">
+      <c r="O88" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -5865,13 +5256,13 @@
       <c r="L89" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M89" s="28" t="s">
+      <c r="M89" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N89">
         <v>1000</v>
       </c>
-      <c r="O89" s="15">
+      <c r="O89" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -5912,13 +5303,13 @@
       <c r="L90" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M90" s="28" t="s">
+      <c r="M90" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N90">
         <v>10000</v>
       </c>
-      <c r="O90" s="15">
+      <c r="O90" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -5959,13 +5350,13 @@
       <c r="L91" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M91" s="28" t="s">
+      <c r="M91" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N91">
         <v>100000</v>
       </c>
-      <c r="O91" s="15">
+      <c r="O91" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -5973,13 +5364,13 @@
       <c r="A92" s="1">
         <v>2009001</v>
       </c>
-      <c r="B92" s="20">
+      <c r="B92" s="19">
         <v>200900</v>
       </c>
       <c r="C92" s="4">
         <v>2</v>
       </c>
-      <c r="D92" s="20" t="s">
+      <c r="D92" s="19" t="s">
         <v>94</v>
       </c>
       <c r="E92" s="13">
@@ -6006,13 +5397,13 @@
       <c r="L92" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M92" s="28" t="s">
+      <c r="M92" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N92">
         <v>1000</v>
       </c>
-      <c r="O92" s="15">
+      <c r="O92" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6053,13 +5444,13 @@
       <c r="L93" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M93" s="28" t="s">
+      <c r="M93" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N93">
         <v>10000</v>
       </c>
-      <c r="O93" s="15">
+      <c r="O93" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6100,13 +5491,13 @@
       <c r="L94" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M94" s="28" t="s">
+      <c r="M94" s="26" t="s">
         <v>34</v>
       </c>
       <c r="N94">
         <v>100000</v>
       </c>
-      <c r="O94" s="15">
+      <c r="O94" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6147,13 +5538,13 @@
       <c r="L95" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="M95" s="28" t="s">
+      <c r="M95" s="26" t="s">
         <v>99</v>
       </c>
       <c r="N95">
         <v>1000</v>
       </c>
-      <c r="O95" s="15">
+      <c r="O95" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6194,13 +5585,13 @@
       <c r="L96" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="M96" s="28" t="s">
+      <c r="M96" s="26" t="s">
         <v>99</v>
       </c>
       <c r="N96">
         <v>10000</v>
       </c>
-      <c r="O96" s="15">
+      <c r="O96" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6241,13 +5632,13 @@
       <c r="L97" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="M97" s="28" t="s">
+      <c r="M97" s="26" t="s">
         <v>99</v>
       </c>
       <c r="N97">
         <v>100000</v>
       </c>
-      <c r="O97" s="15">
+      <c r="O97" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6288,13 +5679,13 @@
       <c r="L98" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="M98" s="28" t="s">
+      <c r="M98" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="N98" s="21">
+      <c r="N98" s="20">
         <v>1000</v>
       </c>
-      <c r="O98" s="15">
+      <c r="O98" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6335,13 +5726,13 @@
       <c r="L99" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="M99" s="28" t="s">
+      <c r="M99" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="N99" s="21">
+      <c r="N99" s="20">
         <v>10000</v>
       </c>
-      <c r="O99" s="15">
+      <c r="O99" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6382,13 +5773,13 @@
       <c r="L100" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="M100" s="28" t="s">
+      <c r="M100" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="N100" s="21">
+      <c r="N100" s="20">
         <v>100000</v>
       </c>
-      <c r="O100" s="15">
+      <c r="O100" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6408,7 +5799,7 @@
       <c r="E101" s="13">
         <v>300400001</v>
       </c>
-      <c r="F101" s="22" t="s">
+      <c r="F101" s="21" t="s">
         <v>104</v>
       </c>
       <c r="G101" s="1" t="s">
@@ -6417,7 +5808,7 @@
       <c r="H101" s="1">
         <v>1</v>
       </c>
-      <c r="I101" s="23">
+      <c r="I101" s="22">
         <f>N101*52</f>
         <v>5200</v>
       </c>
@@ -6430,13 +5821,13 @@
       <c r="L101" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M101" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="N101" s="23">
+      <c r="M101" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="N101" s="22">
         <v>100</v>
       </c>
-      <c r="O101" s="15">
+      <c r="O101" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6456,7 +5847,7 @@
       <c r="E102" s="13">
         <v>300400001</v>
       </c>
-      <c r="F102" s="22" t="s">
+      <c r="F102" s="21" t="s">
         <v>104</v>
       </c>
       <c r="G102" s="1" t="s">
@@ -6465,7 +5856,7 @@
       <c r="H102" s="1">
         <v>2</v>
       </c>
-      <c r="I102" s="23">
+      <c r="I102" s="22">
         <f>N102*52</f>
         <v>52000</v>
       </c>
@@ -6478,13 +5869,13 @@
       <c r="L102" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M102" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="N102" s="23">
+      <c r="M102" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="N102" s="22">
         <v>1000</v>
       </c>
-      <c r="O102" s="15">
+      <c r="O102" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6504,7 +5895,7 @@
       <c r="E103" s="13">
         <v>300400001</v>
       </c>
-      <c r="F103" s="22" t="s">
+      <c r="F103" s="21" t="s">
         <v>104</v>
       </c>
       <c r="G103" s="1" t="s">
@@ -6513,7 +5904,7 @@
       <c r="H103" s="1">
         <v>3</v>
       </c>
-      <c r="I103" s="23">
+      <c r="I103" s="22">
         <f>N103*52</f>
         <v>520000</v>
       </c>
@@ -6526,13 +5917,13 @@
       <c r="L103" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M103" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="N103" s="23">
+      <c r="M103" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="N103" s="22">
         <v>10000</v>
       </c>
-      <c r="O103" s="15">
+      <c r="O103" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6547,13 +5938,13 @@
         <v>2</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E104" s="13">
         <v>201200001</v>
       </c>
-      <c r="F104" s="22" t="s">
-        <v>108</v>
+      <c r="F104" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>32</v>
@@ -6573,13 +5964,13 @@
       <c r="L104" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M104" s="28" t="s">
+      <c r="M104" s="26" t="s">
         <v>87</v>
       </c>
       <c r="N104">
         <v>1000</v>
       </c>
-      <c r="O104" s="15">
+      <c r="O104" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6594,13 +5985,13 @@
         <v>2</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E105" s="13">
         <v>201200001</v>
       </c>
-      <c r="F105" s="22" t="s">
-        <v>108</v>
+      <c r="F105" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>35</v>
@@ -6620,13 +6011,13 @@
       <c r="L105" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M105" s="28" t="s">
+      <c r="M105" s="26" t="s">
         <v>87</v>
       </c>
       <c r="N105">
         <v>10000</v>
       </c>
-      <c r="O105" s="15">
+      <c r="O105" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6641,13 +6032,13 @@
         <v>2</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E106" s="13">
         <v>201200001</v>
       </c>
-      <c r="F106" s="22" t="s">
-        <v>108</v>
+      <c r="F106" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>36</v>
@@ -6667,13 +6058,13 @@
       <c r="L106" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M106" s="28" t="s">
+      <c r="M106" s="26" t="s">
         <v>87</v>
       </c>
       <c r="N106">
         <v>100000</v>
       </c>
-      <c r="O106" s="15">
+      <c r="O106" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -6681,46 +6072,46 @@
       <c r="A107" s="1">
         <v>20010010</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B107" s="15">
         <v>200100</v>
       </c>
-      <c r="C107" s="16">
+      <c r="C107" s="15">
         <v>2</v>
       </c>
-      <c r="D107" s="16" t="s">
+      <c r="D107" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E107" s="16">
+      <c r="E107" s="15">
         <v>200100038</v>
       </c>
-      <c r="F107" s="16" t="s">
+      <c r="F107" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="G107" s="17" t="s">
+      <c r="G107" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H107" s="16">
+        <v>10</v>
+      </c>
+      <c r="I107" s="23">
+        <v>0</v>
+      </c>
+      <c r="J107" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K107" s="16">
+        <v>0</v>
+      </c>
+      <c r="L107" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H107" s="17">
-        <v>10</v>
-      </c>
-      <c r="I107" s="25">
-        <v>0</v>
-      </c>
-      <c r="J107" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K107" s="17">
-        <v>0</v>
-      </c>
-      <c r="L107" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M107" s="17">
+      <c r="M107" s="16">
         <v>0</v>
       </c>
       <c r="N107">
         <v>1000</v>
       </c>
-      <c r="O107" s="27">
+      <c r="O107" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -6728,46 +6119,46 @@
       <c r="A108" s="1">
         <v>20010011</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B108" s="15">
         <v>200100</v>
       </c>
-      <c r="C108" s="16">
+      <c r="C108" s="15">
         <v>2</v>
       </c>
-      <c r="D108" s="16" t="s">
+      <c r="D108" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E108" s="16">
+      <c r="E108" s="15">
         <v>200100038</v>
       </c>
-      <c r="F108" s="16" t="s">
+      <c r="F108" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="G108" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H108" s="17">
+      <c r="G108" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H108" s="16">
         <v>11</v>
       </c>
-      <c r="I108" s="25">
-        <v>0</v>
-      </c>
-      <c r="J108" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K108" s="17">
-        <v>0</v>
-      </c>
-      <c r="L108" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M108" s="17">
+      <c r="I108" s="23">
+        <v>0</v>
+      </c>
+      <c r="J108" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K108" s="16">
+        <v>0</v>
+      </c>
+      <c r="L108" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M108" s="16">
         <v>0</v>
       </c>
       <c r="N108">
         <v>10000</v>
       </c>
-      <c r="O108" s="27">
+      <c r="O108" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -6775,46 +6166,46 @@
       <c r="A109" s="1">
         <v>20010012</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B109" s="15">
         <v>200100</v>
       </c>
-      <c r="C109" s="16">
+      <c r="C109" s="15">
         <v>2</v>
       </c>
-      <c r="D109" s="16" t="s">
+      <c r="D109" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E109" s="16">
+      <c r="E109" s="15">
         <v>200100038</v>
       </c>
-      <c r="F109" s="16" t="s">
+      <c r="F109" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="G109" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H109" s="17">
+      <c r="G109" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H109" s="16">
         <v>12</v>
       </c>
-      <c r="I109" s="25">
-        <v>0</v>
-      </c>
-      <c r="J109" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K109" s="17">
-        <v>0</v>
-      </c>
-      <c r="L109" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M109" s="17">
+      <c r="I109" s="23">
+        <v>0</v>
+      </c>
+      <c r="J109" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K109" s="16">
+        <v>0</v>
+      </c>
+      <c r="L109" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M109" s="16">
         <v>0</v>
       </c>
       <c r="N109">
         <v>100000</v>
       </c>
-      <c r="O109" s="27">
+      <c r="O109" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -6822,46 +6213,46 @@
       <c r="A110" s="1">
         <v>20010110</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B110" s="15">
         <v>200101</v>
       </c>
-      <c r="C110" s="16">
+      <c r="C110" s="15">
         <v>2</v>
       </c>
-      <c r="D110" s="16" t="s">
+      <c r="D110" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="E110" s="16">
+      <c r="E110" s="15">
         <v>200101001</v>
       </c>
-      <c r="F110" s="16" t="s">
+      <c r="F110" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="G110" s="17" t="s">
+      <c r="G110" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H110" s="16">
+        <v>10</v>
+      </c>
+      <c r="I110" s="23">
+        <v>0</v>
+      </c>
+      <c r="J110" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K110" s="16">
+        <v>0</v>
+      </c>
+      <c r="L110" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H110" s="17">
-        <v>10</v>
-      </c>
-      <c r="I110" s="25">
-        <v>0</v>
-      </c>
-      <c r="J110" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K110" s="17">
-        <v>0</v>
-      </c>
-      <c r="L110" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M110" s="17">
+      <c r="M110" s="16">
         <v>0</v>
       </c>
       <c r="N110">
         <v>1000</v>
       </c>
-      <c r="O110" s="27">
+      <c r="O110" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -6869,46 +6260,46 @@
       <c r="A111" s="1">
         <v>20010111</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B111" s="15">
         <v>200101</v>
       </c>
-      <c r="C111" s="16">
+      <c r="C111" s="15">
         <v>2</v>
       </c>
-      <c r="D111" s="16" t="s">
+      <c r="D111" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="E111" s="16">
+      <c r="E111" s="15">
         <v>200101001</v>
       </c>
-      <c r="F111" s="16" t="s">
+      <c r="F111" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="G111" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H111" s="17">
+      <c r="G111" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H111" s="16">
         <v>11</v>
       </c>
-      <c r="I111" s="25">
-        <v>0</v>
-      </c>
-      <c r="J111" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K111" s="17">
-        <v>0</v>
-      </c>
-      <c r="L111" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M111" s="17">
+      <c r="I111" s="23">
+        <v>0</v>
+      </c>
+      <c r="J111" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K111" s="16">
+        <v>0</v>
+      </c>
+      <c r="L111" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M111" s="16">
         <v>0</v>
       </c>
       <c r="N111">
         <v>10000</v>
       </c>
-      <c r="O111" s="27">
+      <c r="O111" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -6916,46 +6307,46 @@
       <c r="A112" s="1">
         <v>20010112</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B112" s="15">
         <v>200101</v>
       </c>
-      <c r="C112" s="16">
+      <c r="C112" s="15">
         <v>2</v>
       </c>
-      <c r="D112" s="16" t="s">
+      <c r="D112" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="E112" s="16">
+      <c r="E112" s="15">
         <v>200101001</v>
       </c>
-      <c r="F112" s="16" t="s">
+      <c r="F112" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="G112" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H112" s="17">
+      <c r="G112" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H112" s="16">
         <v>12</v>
       </c>
-      <c r="I112" s="25">
-        <v>0</v>
-      </c>
-      <c r="J112" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K112" s="17">
-        <v>0</v>
-      </c>
-      <c r="L112" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M112" s="17">
+      <c r="I112" s="23">
+        <v>0</v>
+      </c>
+      <c r="J112" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K112" s="16">
+        <v>0</v>
+      </c>
+      <c r="L112" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M112" s="16">
         <v>0</v>
       </c>
       <c r="N112">
         <v>100000</v>
       </c>
-      <c r="O112" s="27">
+      <c r="O112" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -6963,46 +6354,46 @@
       <c r="A113" s="1">
         <v>20030010</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B113" s="15">
         <v>200300</v>
       </c>
-      <c r="C113" s="16">
+      <c r="C113" s="15">
         <v>2</v>
       </c>
-      <c r="D113" s="16" t="s">
+      <c r="D113" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E113" s="16">
+      <c r="E113" s="15">
         <v>200300001</v>
       </c>
-      <c r="F113" s="16" t="s">
+      <c r="F113" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G113" s="17" t="s">
+      <c r="G113" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H113" s="16">
+        <v>10</v>
+      </c>
+      <c r="I113" s="23">
+        <v>0</v>
+      </c>
+      <c r="J113" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K113" s="16">
+        <v>0</v>
+      </c>
+      <c r="L113" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H113" s="17">
-        <v>10</v>
-      </c>
-      <c r="I113" s="25">
-        <v>0</v>
-      </c>
-      <c r="J113" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K113" s="17">
-        <v>0</v>
-      </c>
-      <c r="L113" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M113" s="17">
+      <c r="M113" s="16">
         <v>0</v>
       </c>
       <c r="N113">
         <v>1000</v>
       </c>
-      <c r="O113" s="27">
+      <c r="O113" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7010,46 +6401,46 @@
       <c r="A114" s="1">
         <v>20030011</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B114" s="15">
         <v>200300</v>
       </c>
-      <c r="C114" s="16">
+      <c r="C114" s="15">
         <v>2</v>
       </c>
-      <c r="D114" s="16" t="s">
+      <c r="D114" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E114" s="16">
+      <c r="E114" s="15">
         <v>200300001</v>
       </c>
-      <c r="F114" s="16" t="s">
+      <c r="F114" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G114" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H114" s="17">
+      <c r="G114" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H114" s="16">
         <v>11</v>
       </c>
-      <c r="I114" s="25">
-        <v>0</v>
-      </c>
-      <c r="J114" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K114" s="17">
-        <v>0</v>
-      </c>
-      <c r="L114" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M114" s="17">
+      <c r="I114" s="23">
+        <v>0</v>
+      </c>
+      <c r="J114" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K114" s="16">
+        <v>0</v>
+      </c>
+      <c r="L114" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M114" s="16">
         <v>0</v>
       </c>
       <c r="N114">
         <v>10000</v>
       </c>
-      <c r="O114" s="27">
+      <c r="O114" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7057,46 +6448,46 @@
       <c r="A115" s="1">
         <v>20030012</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="15">
         <v>200300</v>
       </c>
-      <c r="C115" s="16">
+      <c r="C115" s="15">
         <v>2</v>
       </c>
-      <c r="D115" s="16" t="s">
+      <c r="D115" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E115" s="16">
+      <c r="E115" s="15">
         <v>200300001</v>
       </c>
-      <c r="F115" s="16" t="s">
+      <c r="F115" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G115" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H115" s="17">
+      <c r="G115" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H115" s="16">
         <v>12</v>
       </c>
-      <c r="I115" s="25">
-        <v>0</v>
-      </c>
-      <c r="J115" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K115" s="17">
-        <v>0</v>
-      </c>
-      <c r="L115" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M115" s="17">
+      <c r="I115" s="23">
+        <v>0</v>
+      </c>
+      <c r="J115" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K115" s="16">
+        <v>0</v>
+      </c>
+      <c r="L115" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M115" s="16">
         <v>0</v>
       </c>
       <c r="N115">
         <v>100000</v>
       </c>
-      <c r="O115" s="27">
+      <c r="O115" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7104,46 +6495,46 @@
       <c r="A116" s="1">
         <v>20040010</v>
       </c>
-      <c r="B116" s="16">
+      <c r="B116" s="15">
         <v>200400</v>
       </c>
-      <c r="C116" s="16">
+      <c r="C116" s="15">
         <v>2</v>
       </c>
-      <c r="D116" s="25" t="s">
+      <c r="D116" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="E116" s="16">
+      <c r="E116" s="15">
         <v>200400009</v>
       </c>
-      <c r="F116" s="16" t="s">
+      <c r="F116" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="G116" s="17" t="s">
+      <c r="G116" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H116" s="16">
+        <v>10</v>
+      </c>
+      <c r="I116" s="23">
+        <v>0</v>
+      </c>
+      <c r="J116" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K116" s="16">
+        <v>0</v>
+      </c>
+      <c r="L116" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H116" s="17">
-        <v>10</v>
-      </c>
-      <c r="I116" s="25">
-        <v>0</v>
-      </c>
-      <c r="J116" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K116" s="17">
-        <v>0</v>
-      </c>
-      <c r="L116" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M116" s="17">
+      <c r="M116" s="16">
         <v>0</v>
       </c>
       <c r="N116">
         <v>1000</v>
       </c>
-      <c r="O116" s="27">
+      <c r="O116" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7151,46 +6542,46 @@
       <c r="A117" s="1">
         <v>20040011</v>
       </c>
-      <c r="B117" s="16">
+      <c r="B117" s="15">
         <v>200400</v>
       </c>
-      <c r="C117" s="16">
+      <c r="C117" s="15">
         <v>2</v>
       </c>
-      <c r="D117" s="25" t="s">
+      <c r="D117" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="E117" s="16">
+      <c r="E117" s="15">
         <v>200400009</v>
       </c>
-      <c r="F117" s="16" t="s">
+      <c r="F117" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="G117" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H117" s="17">
+      <c r="G117" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H117" s="16">
         <v>11</v>
       </c>
-      <c r="I117" s="25">
-        <v>0</v>
-      </c>
-      <c r="J117" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K117" s="17">
-        <v>0</v>
-      </c>
-      <c r="L117" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M117" s="17">
+      <c r="I117" s="23">
+        <v>0</v>
+      </c>
+      <c r="J117" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K117" s="16">
+        <v>0</v>
+      </c>
+      <c r="L117" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M117" s="16">
         <v>0</v>
       </c>
       <c r="N117">
         <v>10000</v>
       </c>
-      <c r="O117" s="27">
+      <c r="O117" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7198,46 +6589,46 @@
       <c r="A118" s="1">
         <v>20040012</v>
       </c>
-      <c r="B118" s="16">
+      <c r="B118" s="15">
         <v>200400</v>
       </c>
-      <c r="C118" s="16">
+      <c r="C118" s="15">
         <v>2</v>
       </c>
-      <c r="D118" s="25" t="s">
+      <c r="D118" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="E118" s="16">
+      <c r="E118" s="15">
         <v>200400009</v>
       </c>
-      <c r="F118" s="16" t="s">
+      <c r="F118" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="G118" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H118" s="17">
+      <c r="G118" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H118" s="16">
         <v>12</v>
       </c>
-      <c r="I118" s="25">
-        <v>0</v>
-      </c>
-      <c r="J118" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K118" s="17">
-        <v>0</v>
-      </c>
-      <c r="L118" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M118" s="17">
+      <c r="I118" s="23">
+        <v>0</v>
+      </c>
+      <c r="J118" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K118" s="16">
+        <v>0</v>
+      </c>
+      <c r="L118" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M118" s="16">
         <v>0</v>
       </c>
       <c r="N118">
         <v>100000</v>
       </c>
-      <c r="O118" s="27">
+      <c r="O118" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7245,46 +6636,46 @@
       <c r="A119" s="1">
         <v>20050010</v>
       </c>
-      <c r="B119" s="16">
+      <c r="B119" s="15">
         <v>200500</v>
       </c>
-      <c r="C119" s="16">
+      <c r="C119" s="15">
         <v>2</v>
       </c>
-      <c r="D119" s="16" t="s">
+      <c r="D119" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E119" s="16">
+      <c r="E119" s="15">
         <v>200500025</v>
       </c>
-      <c r="F119" s="16" t="s">
+      <c r="F119" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G119" s="17" t="s">
+      <c r="G119" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H119" s="16">
+        <v>10</v>
+      </c>
+      <c r="I119" s="23">
+        <v>0</v>
+      </c>
+      <c r="J119" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K119" s="16">
+        <v>0</v>
+      </c>
+      <c r="L119" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H119" s="17">
-        <v>10</v>
-      </c>
-      <c r="I119" s="25">
-        <v>0</v>
-      </c>
-      <c r="J119" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K119" s="17">
-        <v>0</v>
-      </c>
-      <c r="L119" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M119" s="17">
+      <c r="M119" s="16">
         <v>0</v>
       </c>
       <c r="N119">
         <v>1000</v>
       </c>
-      <c r="O119" s="27">
+      <c r="O119" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7292,46 +6683,46 @@
       <c r="A120" s="1">
         <v>20050011</v>
       </c>
-      <c r="B120" s="16">
+      <c r="B120" s="15">
         <v>200500</v>
       </c>
-      <c r="C120" s="16">
+      <c r="C120" s="15">
         <v>2</v>
       </c>
-      <c r="D120" s="16" t="s">
+      <c r="D120" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E120" s="16">
+      <c r="E120" s="15">
         <v>200500025</v>
       </c>
-      <c r="F120" s="16" t="s">
+      <c r="F120" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G120" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H120" s="17">
+      <c r="G120" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H120" s="16">
         <v>11</v>
       </c>
-      <c r="I120" s="25">
-        <v>0</v>
-      </c>
-      <c r="J120" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K120" s="17">
-        <v>0</v>
-      </c>
-      <c r="L120" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M120" s="17">
+      <c r="I120" s="23">
+        <v>0</v>
+      </c>
+      <c r="J120" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K120" s="16">
+        <v>0</v>
+      </c>
+      <c r="L120" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M120" s="16">
         <v>0</v>
       </c>
       <c r="N120">
         <v>10000</v>
       </c>
-      <c r="O120" s="27">
+      <c r="O120" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7339,46 +6730,46 @@
       <c r="A121" s="1">
         <v>20050012</v>
       </c>
-      <c r="B121" s="16">
+      <c r="B121" s="15">
         <v>200500</v>
       </c>
-      <c r="C121" s="16">
+      <c r="C121" s="15">
         <v>2</v>
       </c>
-      <c r="D121" s="16" t="s">
+      <c r="D121" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E121" s="16">
+      <c r="E121" s="15">
         <v>200500025</v>
       </c>
-      <c r="F121" s="16" t="s">
+      <c r="F121" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G121" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H121" s="17">
+      <c r="G121" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H121" s="16">
         <v>12</v>
       </c>
-      <c r="I121" s="25">
-        <v>0</v>
-      </c>
-      <c r="J121" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K121" s="17">
-        <v>0</v>
-      </c>
-      <c r="L121" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M121" s="17">
+      <c r="I121" s="23">
+        <v>0</v>
+      </c>
+      <c r="J121" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K121" s="16">
+        <v>0</v>
+      </c>
+      <c r="L121" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M121" s="16">
         <v>0</v>
       </c>
       <c r="N121">
         <v>100000</v>
       </c>
-      <c r="O121" s="27">
+      <c r="O121" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7386,46 +6777,46 @@
       <c r="A122" s="1">
         <v>20060010</v>
       </c>
-      <c r="B122" s="16">
+      <c r="B122" s="15">
         <v>200600</v>
       </c>
-      <c r="C122" s="16">
+      <c r="C122" s="15">
         <v>2</v>
       </c>
-      <c r="D122" s="16" t="s">
+      <c r="D122" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E122" s="16">
+      <c r="E122" s="15">
         <v>200600001</v>
       </c>
-      <c r="F122" s="16" t="s">
+      <c r="F122" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="G122" s="17" t="s">
+      <c r="G122" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H122" s="16">
+        <v>10</v>
+      </c>
+      <c r="I122" s="23">
+        <v>0</v>
+      </c>
+      <c r="J122" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K122" s="16">
+        <v>0</v>
+      </c>
+      <c r="L122" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H122" s="17">
-        <v>10</v>
-      </c>
-      <c r="I122" s="25">
-        <v>0</v>
-      </c>
-      <c r="J122" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K122" s="17">
-        <v>0</v>
-      </c>
-      <c r="L122" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M122" s="17">
+      <c r="M122" s="16">
         <v>0</v>
       </c>
       <c r="N122">
         <v>1000</v>
       </c>
-      <c r="O122" s="27">
+      <c r="O122" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7433,46 +6824,46 @@
       <c r="A123" s="1">
         <v>20060011</v>
       </c>
-      <c r="B123" s="16">
+      <c r="B123" s="15">
         <v>200600</v>
       </c>
-      <c r="C123" s="16">
+      <c r="C123" s="15">
         <v>2</v>
       </c>
-      <c r="D123" s="16" t="s">
+      <c r="D123" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E123" s="16">
+      <c r="E123" s="15">
         <v>200600001</v>
       </c>
-      <c r="F123" s="16" t="s">
+      <c r="F123" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="G123" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H123" s="17">
+      <c r="G123" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H123" s="16">
         <v>11</v>
       </c>
-      <c r="I123" s="25">
-        <v>0</v>
-      </c>
-      <c r="J123" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K123" s="17">
-        <v>0</v>
-      </c>
-      <c r="L123" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M123" s="17">
+      <c r="I123" s="23">
+        <v>0</v>
+      </c>
+      <c r="J123" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K123" s="16">
+        <v>0</v>
+      </c>
+      <c r="L123" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M123" s="16">
         <v>0</v>
       </c>
       <c r="N123">
         <v>10000</v>
       </c>
-      <c r="O123" s="27">
+      <c r="O123" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7480,46 +6871,46 @@
       <c r="A124" s="1">
         <v>20060012</v>
       </c>
-      <c r="B124" s="16">
+      <c r="B124" s="15">
         <v>200600</v>
       </c>
-      <c r="C124" s="16">
+      <c r="C124" s="15">
         <v>2</v>
       </c>
-      <c r="D124" s="16" t="s">
+      <c r="D124" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E124" s="16">
+      <c r="E124" s="15">
         <v>200600001</v>
       </c>
-      <c r="F124" s="16" t="s">
+      <c r="F124" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="G124" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H124" s="17">
+      <c r="G124" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H124" s="16">
         <v>12</v>
       </c>
-      <c r="I124" s="25">
-        <v>0</v>
-      </c>
-      <c r="J124" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K124" s="17">
-        <v>0</v>
-      </c>
-      <c r="L124" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M124" s="17">
+      <c r="I124" s="23">
+        <v>0</v>
+      </c>
+      <c r="J124" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K124" s="16">
+        <v>0</v>
+      </c>
+      <c r="L124" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M124" s="16">
         <v>0</v>
       </c>
       <c r="N124">
         <v>100000</v>
       </c>
-      <c r="O124" s="27">
+      <c r="O124" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7527,46 +6918,46 @@
       <c r="A125" s="1">
         <v>20070010</v>
       </c>
-      <c r="B125" s="16">
+      <c r="B125" s="15">
         <v>200700</v>
       </c>
-      <c r="C125" s="16">
+      <c r="C125" s="15">
         <v>2</v>
       </c>
-      <c r="D125" s="16" t="s">
+      <c r="D125" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E125" s="16">
+      <c r="E125" s="15">
         <v>200700001</v>
       </c>
-      <c r="F125" s="16" t="s">
+      <c r="F125" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="G125" s="17" t="s">
+      <c r="G125" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H125" s="16">
+        <v>10</v>
+      </c>
+      <c r="I125" s="23">
+        <v>0</v>
+      </c>
+      <c r="J125" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K125" s="16">
+        <v>0</v>
+      </c>
+      <c r="L125" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H125" s="17">
-        <v>10</v>
-      </c>
-      <c r="I125" s="25">
-        <v>0</v>
-      </c>
-      <c r="J125" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K125" s="17">
-        <v>0</v>
-      </c>
-      <c r="L125" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M125" s="17">
+      <c r="M125" s="16">
         <v>0</v>
       </c>
       <c r="N125">
         <v>1000</v>
       </c>
-      <c r="O125" s="27">
+      <c r="O125" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7574,46 +6965,46 @@
       <c r="A126" s="1">
         <v>20070011</v>
       </c>
-      <c r="B126" s="16">
+      <c r="B126" s="15">
         <v>200700</v>
       </c>
-      <c r="C126" s="16">
+      <c r="C126" s="15">
         <v>2</v>
       </c>
-      <c r="D126" s="16" t="s">
+      <c r="D126" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E126" s="16">
+      <c r="E126" s="15">
         <v>200700001</v>
       </c>
-      <c r="F126" s="16" t="s">
+      <c r="F126" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="G126" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H126" s="17">
+      <c r="G126" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H126" s="16">
         <v>11</v>
       </c>
-      <c r="I126" s="25">
-        <v>0</v>
-      </c>
-      <c r="J126" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K126" s="17">
-        <v>0</v>
-      </c>
-      <c r="L126" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M126" s="17">
+      <c r="I126" s="23">
+        <v>0</v>
+      </c>
+      <c r="J126" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K126" s="16">
+        <v>0</v>
+      </c>
+      <c r="L126" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M126" s="16">
         <v>0</v>
       </c>
       <c r="N126">
         <v>10000</v>
       </c>
-      <c r="O126" s="27">
+      <c r="O126" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7621,46 +7012,46 @@
       <c r="A127" s="1">
         <v>20070012</v>
       </c>
-      <c r="B127" s="16">
+      <c r="B127" s="15">
         <v>200700</v>
       </c>
-      <c r="C127" s="16">
+      <c r="C127" s="15">
         <v>2</v>
       </c>
-      <c r="D127" s="16" t="s">
+      <c r="D127" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E127" s="16">
+      <c r="E127" s="15">
         <v>200700001</v>
       </c>
-      <c r="F127" s="16" t="s">
+      <c r="F127" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="G127" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H127" s="17">
+      <c r="G127" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H127" s="16">
         <v>12</v>
       </c>
-      <c r="I127" s="25">
-        <v>0</v>
-      </c>
-      <c r="J127" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K127" s="17">
-        <v>0</v>
-      </c>
-      <c r="L127" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M127" s="17">
+      <c r="I127" s="23">
+        <v>0</v>
+      </c>
+      <c r="J127" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K127" s="16">
+        <v>0</v>
+      </c>
+      <c r="L127" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M127" s="16">
         <v>0</v>
       </c>
       <c r="N127">
         <v>100000</v>
       </c>
-      <c r="O127" s="27">
+      <c r="O127" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7668,46 +7059,46 @@
       <c r="A128" s="1">
         <v>20080010</v>
       </c>
-      <c r="B128" s="16">
+      <c r="B128" s="15">
         <v>200800</v>
       </c>
-      <c r="C128" s="16">
+      <c r="C128" s="15">
         <v>2</v>
       </c>
-      <c r="D128" s="16" t="s">
+      <c r="D128" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E128" s="16">
+      <c r="E128" s="15">
         <v>200800001</v>
       </c>
-      <c r="F128" s="16" t="s">
+      <c r="F128" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="G128" s="17" t="s">
+      <c r="G128" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H128" s="16">
+        <v>10</v>
+      </c>
+      <c r="I128" s="23">
+        <v>0</v>
+      </c>
+      <c r="J128" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K128" s="16">
+        <v>0</v>
+      </c>
+      <c r="L128" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H128" s="17">
-        <v>10</v>
-      </c>
-      <c r="I128" s="25">
-        <v>0</v>
-      </c>
-      <c r="J128" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K128" s="17">
-        <v>0</v>
-      </c>
-      <c r="L128" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M128" s="17">
+      <c r="M128" s="16">
         <v>0</v>
       </c>
       <c r="N128">
         <v>1000</v>
       </c>
-      <c r="O128" s="27">
+      <c r="O128" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7715,46 +7106,46 @@
       <c r="A129" s="1">
         <v>20080011</v>
       </c>
-      <c r="B129" s="16">
+      <c r="B129" s="15">
         <v>200800</v>
       </c>
-      <c r="C129" s="16">
+      <c r="C129" s="15">
         <v>2</v>
       </c>
-      <c r="D129" s="16" t="s">
+      <c r="D129" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E129" s="16">
+      <c r="E129" s="15">
         <v>200800001</v>
       </c>
-      <c r="F129" s="16" t="s">
+      <c r="F129" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="G129" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H129" s="17">
+      <c r="G129" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H129" s="16">
         <v>11</v>
       </c>
-      <c r="I129" s="25">
-        <v>0</v>
-      </c>
-      <c r="J129" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K129" s="17">
-        <v>0</v>
-      </c>
-      <c r="L129" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M129" s="17">
+      <c r="I129" s="23">
+        <v>0</v>
+      </c>
+      <c r="J129" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K129" s="16">
+        <v>0</v>
+      </c>
+      <c r="L129" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M129" s="16">
         <v>0</v>
       </c>
       <c r="N129">
         <v>10000</v>
       </c>
-      <c r="O129" s="27">
+      <c r="O129" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7762,46 +7153,46 @@
       <c r="A130" s="1">
         <v>20080012</v>
       </c>
-      <c r="B130" s="16">
+      <c r="B130" s="15">
         <v>200800</v>
       </c>
-      <c r="C130" s="16">
+      <c r="C130" s="15">
         <v>2</v>
       </c>
-      <c r="D130" s="16" t="s">
+      <c r="D130" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E130" s="16">
+      <c r="E130" s="15">
         <v>200800001</v>
       </c>
-      <c r="F130" s="16" t="s">
+      <c r="F130" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="G130" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H130" s="17">
+      <c r="G130" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H130" s="16">
         <v>12</v>
       </c>
-      <c r="I130" s="25">
-        <v>0</v>
-      </c>
-      <c r="J130" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K130" s="17">
-        <v>0</v>
-      </c>
-      <c r="L130" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M130" s="17">
+      <c r="I130" s="23">
+        <v>0</v>
+      </c>
+      <c r="J130" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K130" s="16">
+        <v>0</v>
+      </c>
+      <c r="L130" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M130" s="16">
         <v>0</v>
       </c>
       <c r="N130">
         <v>100000</v>
       </c>
-      <c r="O130" s="27">
+      <c r="O130" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7809,46 +7200,46 @@
       <c r="A131" s="1">
         <v>20090010</v>
       </c>
-      <c r="B131" s="16">
+      <c r="B131" s="15">
         <v>200900</v>
       </c>
-      <c r="C131" s="16">
+      <c r="C131" s="15">
         <v>2</v>
       </c>
-      <c r="D131" s="16" t="s">
+      <c r="D131" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="E131" s="16">
+      <c r="E131" s="15">
         <v>200900001</v>
       </c>
-      <c r="F131" s="16" t="s">
+      <c r="F131" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="G131" s="17" t="s">
+      <c r="G131" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H131" s="16">
+        <v>10</v>
+      </c>
+      <c r="I131" s="23">
+        <v>0</v>
+      </c>
+      <c r="J131" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K131" s="16">
+        <v>0</v>
+      </c>
+      <c r="L131" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H131" s="17">
-        <v>10</v>
-      </c>
-      <c r="I131" s="25">
-        <v>0</v>
-      </c>
-      <c r="J131" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K131" s="17">
-        <v>0</v>
-      </c>
-      <c r="L131" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M131" s="17">
+      <c r="M131" s="16">
         <v>0</v>
       </c>
       <c r="N131">
         <v>1000</v>
       </c>
-      <c r="O131" s="27">
+      <c r="O131" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7856,46 +7247,46 @@
       <c r="A132" s="1">
         <v>20090011</v>
       </c>
-      <c r="B132" s="16">
+      <c r="B132" s="15">
         <v>200900</v>
       </c>
-      <c r="C132" s="16">
+      <c r="C132" s="15">
         <v>2</v>
       </c>
-      <c r="D132" s="16" t="s">
+      <c r="D132" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="E132" s="16">
+      <c r="E132" s="15">
         <v>200900001</v>
       </c>
-      <c r="F132" s="16" t="s">
+      <c r="F132" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="G132" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H132" s="17">
+      <c r="G132" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H132" s="16">
         <v>11</v>
       </c>
-      <c r="I132" s="25">
-        <v>0</v>
-      </c>
-      <c r="J132" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K132" s="17">
-        <v>0</v>
-      </c>
-      <c r="L132" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M132" s="17">
+      <c r="I132" s="23">
+        <v>0</v>
+      </c>
+      <c r="J132" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K132" s="16">
+        <v>0</v>
+      </c>
+      <c r="L132" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M132" s="16">
         <v>0</v>
       </c>
       <c r="N132">
         <v>10000</v>
       </c>
-      <c r="O132" s="27">
+      <c r="O132" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7903,46 +7294,46 @@
       <c r="A133" s="1">
         <v>20090012</v>
       </c>
-      <c r="B133" s="16">
+      <c r="B133" s="15">
         <v>200900</v>
       </c>
-      <c r="C133" s="16">
+      <c r="C133" s="15">
         <v>2</v>
       </c>
-      <c r="D133" s="16" t="s">
+      <c r="D133" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="E133" s="16">
+      <c r="E133" s="15">
         <v>200900001</v>
       </c>
-      <c r="F133" s="16" t="s">
+      <c r="F133" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="G133" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H133" s="17">
+      <c r="G133" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H133" s="16">
         <v>12</v>
       </c>
-      <c r="I133" s="25">
-        <v>0</v>
-      </c>
-      <c r="J133" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K133" s="17">
-        <v>0</v>
-      </c>
-      <c r="L133" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M133" s="17">
+      <c r="I133" s="23">
+        <v>0</v>
+      </c>
+      <c r="J133" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K133" s="16">
+        <v>0</v>
+      </c>
+      <c r="L133" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M133" s="16">
         <v>0</v>
       </c>
       <c r="N133">
         <v>100000</v>
       </c>
-      <c r="O133" s="27">
+      <c r="O133" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7950,46 +7341,46 @@
       <c r="A134" s="1">
         <v>30020010</v>
       </c>
-      <c r="B134" s="16">
+      <c r="B134" s="15">
         <v>300200</v>
       </c>
-      <c r="C134" s="16">
+      <c r="C134" s="15">
         <v>3</v>
       </c>
-      <c r="D134" s="16" t="s">
+      <c r="D134" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E134" s="16">
+      <c r="E134" s="15">
         <v>300200006</v>
       </c>
-      <c r="F134" s="16" t="s">
+      <c r="F134" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="G134" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="H134" s="17">
+      <c r="G134" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H134" s="16">
         <v>10</v>
       </c>
-      <c r="I134" s="25">
-        <v>0</v>
-      </c>
-      <c r="J134" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K134" s="17">
+      <c r="I134" s="23">
+        <v>0</v>
+      </c>
+      <c r="J134" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K134" s="16">
         <v>0</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M134" s="17">
-        <v>0</v>
-      </c>
-      <c r="N134" s="21">
+        <v>112</v>
+      </c>
+      <c r="M134" s="16">
+        <v>0</v>
+      </c>
+      <c r="N134" s="20">
         <v>1000</v>
       </c>
-      <c r="O134" s="27">
+      <c r="O134" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -7997,46 +7388,46 @@
       <c r="A135" s="1">
         <v>30020011</v>
       </c>
-      <c r="B135" s="16">
+      <c r="B135" s="15">
         <v>300200</v>
       </c>
-      <c r="C135" s="16">
+      <c r="C135" s="15">
         <v>3</v>
       </c>
-      <c r="D135" s="16" t="s">
+      <c r="D135" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E135" s="16">
+      <c r="E135" s="15">
         <v>300200006</v>
       </c>
-      <c r="F135" s="16" t="s">
+      <c r="F135" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="G135" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H135" s="17">
+      <c r="G135" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H135" s="16">
         <v>11</v>
       </c>
-      <c r="I135" s="25">
-        <v>0</v>
-      </c>
-      <c r="J135" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K135" s="17">
+      <c r="I135" s="23">
+        <v>0</v>
+      </c>
+      <c r="J135" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K135" s="16">
         <v>0</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M135" s="17">
-        <v>0</v>
-      </c>
-      <c r="N135" s="21">
+        <v>112</v>
+      </c>
+      <c r="M135" s="16">
+        <v>0</v>
+      </c>
+      <c r="N135" s="20">
         <v>10000</v>
       </c>
-      <c r="O135" s="27">
+      <c r="O135" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8044,46 +7435,46 @@
       <c r="A136" s="1">
         <v>30020012</v>
       </c>
-      <c r="B136" s="16">
+      <c r="B136" s="15">
         <v>300200</v>
       </c>
-      <c r="C136" s="16">
+      <c r="C136" s="15">
         <v>3</v>
       </c>
-      <c r="D136" s="16" t="s">
+      <c r="D136" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E136" s="16">
+      <c r="E136" s="15">
         <v>300200006</v>
       </c>
-      <c r="F136" s="16" t="s">
+      <c r="F136" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="G136" s="17" t="s">
+      <c r="G136" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H136" s="16">
+        <v>12</v>
+      </c>
+      <c r="I136" s="23">
+        <v>0</v>
+      </c>
+      <c r="J136" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K136" s="16">
+        <v>0</v>
+      </c>
+      <c r="L136" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="H136" s="17">
-        <v>12</v>
-      </c>
-      <c r="I136" s="25">
-        <v>0</v>
-      </c>
-      <c r="J136" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K136" s="17">
-        <v>0</v>
-      </c>
-      <c r="L136" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M136" s="17">
-        <v>0</v>
-      </c>
-      <c r="N136" s="21">
+      <c r="M136" s="16">
+        <v>0</v>
+      </c>
+      <c r="N136" s="20">
         <v>100000</v>
       </c>
-      <c r="O136" s="27">
+      <c r="O136" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8092,46 +7483,46 @@
         <f>B137*100+H137</f>
         <v>10010010</v>
       </c>
-      <c r="B137" s="16">
+      <c r="B137" s="15">
         <v>100100</v>
       </c>
-      <c r="C137" s="16">
-        <v>1</v>
-      </c>
-      <c r="D137" s="16" t="s">
+      <c r="C137" s="15">
+        <v>1</v>
+      </c>
+      <c r="D137" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E137" s="16">
+      <c r="E137" s="15">
         <v>100100026</v>
       </c>
-      <c r="F137" s="16" t="s">
+      <c r="F137" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G137" s="17" t="s">
+      <c r="G137" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H137" s="16">
+        <v>10</v>
+      </c>
+      <c r="I137" s="23">
+        <v>0</v>
+      </c>
+      <c r="J137" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K137" s="16">
+        <v>0</v>
+      </c>
+      <c r="L137" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H137" s="17">
-        <v>10</v>
-      </c>
-      <c r="I137" s="25">
-        <v>0</v>
-      </c>
-      <c r="J137" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K137" s="17">
-        <v>0</v>
-      </c>
-      <c r="L137" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M137" s="17">
+      <c r="M137" s="16">
         <v>0</v>
       </c>
       <c r="N137">
         <v>1000</v>
       </c>
-      <c r="O137" s="27">
+      <c r="O137" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8140,47 +7531,47 @@
         <f>B138*100+H138</f>
         <v>10010011</v>
       </c>
-      <c r="B138" s="16">
+      <c r="B138" s="15">
         <v>100100</v>
       </c>
-      <c r="C138" s="16">
-        <v>1</v>
-      </c>
-      <c r="D138" s="16" t="str">
+      <c r="C138" s="15">
+        <v>1</v>
+      </c>
+      <c r="D138" s="15" t="str">
         <f t="shared" ref="D138:D142" si="1">D137</f>
         <v>金礦大亨</v>
       </c>
-      <c r="E138" s="16">
+      <c r="E138" s="15">
         <v>100100026</v>
       </c>
-      <c r="F138" s="16" t="s">
+      <c r="F138" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G138" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H138" s="17">
+      <c r="G138" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H138" s="16">
         <v>11</v>
       </c>
-      <c r="I138" s="25">
-        <v>0</v>
-      </c>
-      <c r="J138" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K138" s="17">
-        <v>0</v>
-      </c>
-      <c r="L138" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M138" s="17">
+      <c r="I138" s="23">
+        <v>0</v>
+      </c>
+      <c r="J138" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K138" s="16">
+        <v>0</v>
+      </c>
+      <c r="L138" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M138" s="16">
         <v>0</v>
       </c>
       <c r="N138">
         <v>10000</v>
       </c>
-      <c r="O138" s="27">
+      <c r="O138" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8189,47 +7580,47 @@
         <f>B139*100+H139</f>
         <v>10010012</v>
       </c>
-      <c r="B139" s="16">
+      <c r="B139" s="15">
         <v>100100</v>
       </c>
-      <c r="C139" s="16">
-        <v>1</v>
-      </c>
-      <c r="D139" s="16" t="str">
+      <c r="C139" s="15">
+        <v>1</v>
+      </c>
+      <c r="D139" s="15" t="str">
         <f t="shared" si="1"/>
         <v>金礦大亨</v>
       </c>
-      <c r="E139" s="16">
+      <c r="E139" s="15">
         <v>100100026</v>
       </c>
-      <c r="F139" s="16" t="s">
+      <c r="F139" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G139" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H139" s="17">
+      <c r="G139" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H139" s="16">
         <v>12</v>
       </c>
-      <c r="I139" s="25">
-        <v>0</v>
-      </c>
-      <c r="J139" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K139" s="17">
-        <v>0</v>
-      </c>
-      <c r="L139" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M139" s="17">
+      <c r="I139" s="23">
+        <v>0</v>
+      </c>
+      <c r="J139" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K139" s="16">
+        <v>0</v>
+      </c>
+      <c r="L139" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M139" s="16">
         <v>0</v>
       </c>
       <c r="N139">
         <v>100000</v>
       </c>
-      <c r="O139" s="27">
+      <c r="O139" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8238,46 +7629,46 @@
         <f t="shared" ref="A140:A181" si="2">B140*100+H140</f>
         <v>10030010</v>
       </c>
-      <c r="B140" s="16">
+      <c r="B140" s="15">
         <v>100300</v>
       </c>
-      <c r="C140" s="16">
-        <v>1</v>
-      </c>
-      <c r="D140" s="16" t="s">
+      <c r="C140" s="15">
+        <v>1</v>
+      </c>
+      <c r="D140" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E140" s="16">
+      <c r="E140" s="15">
         <v>100300001</v>
       </c>
-      <c r="F140" s="16" t="s">
+      <c r="F140" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="G140" s="17" t="s">
+      <c r="G140" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H140" s="16">
+        <v>10</v>
+      </c>
+      <c r="I140" s="23">
+        <v>0</v>
+      </c>
+      <c r="J140" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K140" s="16">
+        <v>0</v>
+      </c>
+      <c r="L140" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H140" s="17">
-        <v>10</v>
-      </c>
-      <c r="I140" s="25">
-        <v>0</v>
-      </c>
-      <c r="J140" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K140" s="17">
-        <v>0</v>
-      </c>
-      <c r="L140" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M140" s="17">
+      <c r="M140" s="16">
         <v>0</v>
       </c>
       <c r="N140">
         <v>1000</v>
       </c>
-      <c r="O140" s="27">
+      <c r="O140" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8286,48 +7677,48 @@
         <f t="shared" si="2"/>
         <v>10030011</v>
       </c>
-      <c r="B141" s="16">
+      <c r="B141" s="15">
         <v>100300</v>
       </c>
-      <c r="C141" s="16">
-        <v>1</v>
-      </c>
-      <c r="D141" s="16" t="str">
+      <c r="C141" s="15">
+        <v>1</v>
+      </c>
+      <c r="D141" s="15" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E141" s="16">
+      <c r="E141" s="15">
         <v>100300001</v>
       </c>
-      <c r="F141" s="16" t="str">
+      <c r="F141" s="15" t="str">
         <f t="shared" ref="F141:F145" si="3">F140</f>
         <v>SuperStar</v>
       </c>
-      <c r="G141" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H141" s="17">
+      <c r="G141" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H141" s="16">
         <v>11</v>
       </c>
-      <c r="I141" s="25">
-        <v>0</v>
-      </c>
-      <c r="J141" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K141" s="17">
-        <v>0</v>
-      </c>
-      <c r="L141" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M141" s="17">
+      <c r="I141" s="23">
+        <v>0</v>
+      </c>
+      <c r="J141" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K141" s="16">
+        <v>0</v>
+      </c>
+      <c r="L141" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M141" s="16">
         <v>0</v>
       </c>
       <c r="N141">
         <v>10000</v>
       </c>
-      <c r="O141" s="27">
+      <c r="O141" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8336,48 +7727,48 @@
         <f t="shared" si="2"/>
         <v>10030012</v>
       </c>
-      <c r="B142" s="16">
+      <c r="B142" s="15">
         <v>100300</v>
       </c>
-      <c r="C142" s="16">
-        <v>1</v>
-      </c>
-      <c r="D142" s="16" t="str">
+      <c r="C142" s="15">
+        <v>1</v>
+      </c>
+      <c r="D142" s="15" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E142" s="16">
+      <c r="E142" s="15">
         <v>100300001</v>
       </c>
-      <c r="F142" s="16" t="str">
+      <c r="F142" s="15" t="str">
         <f t="shared" si="3"/>
         <v>SuperStar</v>
       </c>
-      <c r="G142" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H142" s="17">
+      <c r="G142" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H142" s="16">
         <v>12</v>
       </c>
-      <c r="I142" s="25">
-        <v>0</v>
-      </c>
-      <c r="J142" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K142" s="17">
-        <v>0</v>
-      </c>
-      <c r="L142" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M142" s="17">
+      <c r="I142" s="23">
+        <v>0</v>
+      </c>
+      <c r="J142" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K142" s="16">
+        <v>0</v>
+      </c>
+      <c r="L142" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M142" s="16">
         <v>0</v>
       </c>
       <c r="N142">
         <v>100000</v>
       </c>
-      <c r="O142" s="27">
+      <c r="O142" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8386,46 +7777,46 @@
         <f t="shared" si="2"/>
         <v>10070010</v>
       </c>
-      <c r="B143" s="16">
+      <c r="B143" s="15">
         <v>100700</v>
       </c>
-      <c r="C143" s="16">
-        <v>1</v>
-      </c>
-      <c r="D143" s="16" t="s">
+      <c r="C143" s="15">
+        <v>1</v>
+      </c>
+      <c r="D143" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E143" s="16">
+      <c r="E143" s="15">
         <v>100700001</v>
       </c>
-      <c r="F143" s="16" t="s">
+      <c r="F143" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G143" s="17" t="s">
+      <c r="G143" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H143" s="16">
+        <v>10</v>
+      </c>
+      <c r="I143" s="23">
+        <v>0</v>
+      </c>
+      <c r="J143" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K143" s="16">
+        <v>0</v>
+      </c>
+      <c r="L143" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H143" s="17">
-        <v>10</v>
-      </c>
-      <c r="I143" s="25">
-        <v>0</v>
-      </c>
-      <c r="J143" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K143" s="17">
-        <v>0</v>
-      </c>
-      <c r="L143" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M143" s="17">
+      <c r="M143" s="16">
         <v>0</v>
       </c>
       <c r="N143">
         <v>1000</v>
       </c>
-      <c r="O143" s="27">
+      <c r="O143" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8434,48 +7825,48 @@
         <f t="shared" si="2"/>
         <v>10070011</v>
       </c>
-      <c r="B144" s="16">
+      <c r="B144" s="15">
         <v>100700</v>
       </c>
-      <c r="C144" s="16">
-        <v>1</v>
-      </c>
-      <c r="D144" s="16" t="str">
+      <c r="C144" s="15">
+        <v>1</v>
+      </c>
+      <c r="D144" s="15" t="str">
         <f t="shared" ref="D144:D148" si="4">D143</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E144" s="16">
+      <c r="E144" s="15">
         <v>100700001</v>
       </c>
-      <c r="F144" s="16" t="str">
+      <c r="F144" s="15" t="str">
         <f t="shared" si="3"/>
         <v>MahjongWays</v>
       </c>
-      <c r="G144" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H144" s="17">
+      <c r="G144" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H144" s="16">
         <v>11</v>
       </c>
-      <c r="I144" s="25">
-        <v>0</v>
-      </c>
-      <c r="J144" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K144" s="17">
-        <v>0</v>
-      </c>
-      <c r="L144" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M144" s="17">
+      <c r="I144" s="23">
+        <v>0</v>
+      </c>
+      <c r="J144" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K144" s="16">
+        <v>0</v>
+      </c>
+      <c r="L144" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M144" s="16">
         <v>0</v>
       </c>
       <c r="N144">
         <v>10000</v>
       </c>
-      <c r="O144" s="27">
+      <c r="O144" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8484,48 +7875,48 @@
         <f t="shared" si="2"/>
         <v>10070012</v>
       </c>
-      <c r="B145" s="16">
+      <c r="B145" s="15">
         <v>100700</v>
       </c>
-      <c r="C145" s="16">
-        <v>1</v>
-      </c>
-      <c r="D145" s="16" t="str">
+      <c r="C145" s="15">
+        <v>1</v>
+      </c>
+      <c r="D145" s="15" t="str">
         <f t="shared" si="4"/>
         <v>麻将胡了</v>
       </c>
-      <c r="E145" s="16">
+      <c r="E145" s="15">
         <v>100700001</v>
       </c>
-      <c r="F145" s="16" t="str">
+      <c r="F145" s="15" t="str">
         <f t="shared" si="3"/>
         <v>MahjongWays</v>
       </c>
-      <c r="G145" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H145" s="17">
+      <c r="G145" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H145" s="16">
         <v>12</v>
       </c>
-      <c r="I145" s="25">
-        <v>0</v>
-      </c>
-      <c r="J145" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K145" s="17">
-        <v>0</v>
-      </c>
-      <c r="L145" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M145" s="17">
+      <c r="I145" s="23">
+        <v>0</v>
+      </c>
+      <c r="J145" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K145" s="16">
+        <v>0</v>
+      </c>
+      <c r="L145" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M145" s="16">
         <v>0</v>
       </c>
       <c r="N145">
         <v>100000</v>
       </c>
-      <c r="O145" s="27">
+      <c r="O145" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8534,46 +7925,46 @@
         <f t="shared" si="2"/>
         <v>10120010</v>
       </c>
-      <c r="B146" s="16">
+      <c r="B146" s="15">
         <v>101200</v>
       </c>
-      <c r="C146" s="16">
-        <v>1</v>
-      </c>
-      <c r="D146" s="16" t="s">
+      <c r="C146" s="15">
+        <v>1</v>
+      </c>
+      <c r="D146" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E146" s="16">
+      <c r="E146" s="15">
         <v>101200001</v>
       </c>
-      <c r="F146" s="16" t="s">
+      <c r="F146" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="G146" s="17" t="s">
+      <c r="G146" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H146" s="16">
+        <v>10</v>
+      </c>
+      <c r="I146" s="23">
+        <v>0</v>
+      </c>
+      <c r="J146" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K146" s="16">
+        <v>0</v>
+      </c>
+      <c r="L146" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H146" s="17">
-        <v>10</v>
-      </c>
-      <c r="I146" s="25">
-        <v>0</v>
-      </c>
-      <c r="J146" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K146" s="17">
-        <v>0</v>
-      </c>
-      <c r="L146" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M146" s="17">
+      <c r="M146" s="16">
         <v>0</v>
       </c>
       <c r="N146">
         <v>1000</v>
       </c>
-      <c r="O146" s="27">
+      <c r="O146" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8582,48 +7973,48 @@
         <f t="shared" si="2"/>
         <v>10120011</v>
       </c>
-      <c r="B147" s="16">
+      <c r="B147" s="15">
         <v>101200</v>
       </c>
-      <c r="C147" s="16">
-        <v>1</v>
-      </c>
-      <c r="D147" s="16" t="str">
+      <c r="C147" s="15">
+        <v>1</v>
+      </c>
+      <c r="D147" s="15" t="str">
         <f t="shared" si="4"/>
         <v>财神</v>
       </c>
-      <c r="E147" s="16">
+      <c r="E147" s="15">
         <v>101200001</v>
       </c>
-      <c r="F147" s="16" t="str">
+      <c r="F147" s="15" t="str">
         <f t="shared" ref="F147:F151" si="5">F146</f>
         <v>Godofwealth</v>
       </c>
-      <c r="G147" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H147" s="17">
+      <c r="G147" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H147" s="16">
         <v>11</v>
       </c>
-      <c r="I147" s="25">
-        <v>0</v>
-      </c>
-      <c r="J147" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K147" s="17">
-        <v>0</v>
-      </c>
-      <c r="L147" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M147" s="17">
+      <c r="I147" s="23">
+        <v>0</v>
+      </c>
+      <c r="J147" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K147" s="16">
+        <v>0</v>
+      </c>
+      <c r="L147" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M147" s="16">
         <v>0</v>
       </c>
       <c r="N147">
         <v>10000</v>
       </c>
-      <c r="O147" s="27">
+      <c r="O147" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8632,48 +8023,48 @@
         <f t="shared" si="2"/>
         <v>10120012</v>
       </c>
-      <c r="B148" s="16">
+      <c r="B148" s="15">
         <v>101200</v>
       </c>
-      <c r="C148" s="16">
-        <v>1</v>
-      </c>
-      <c r="D148" s="16" t="str">
+      <c r="C148" s="15">
+        <v>1</v>
+      </c>
+      <c r="D148" s="15" t="str">
         <f t="shared" si="4"/>
         <v>财神</v>
       </c>
-      <c r="E148" s="16">
+      <c r="E148" s="15">
         <v>101200001</v>
       </c>
-      <c r="F148" s="16" t="str">
+      <c r="F148" s="15" t="str">
         <f t="shared" si="5"/>
         <v>Godofwealth</v>
       </c>
-      <c r="G148" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H148" s="17">
+      <c r="G148" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H148" s="16">
         <v>12</v>
       </c>
-      <c r="I148" s="25">
-        <v>0</v>
-      </c>
-      <c r="J148" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K148" s="17">
-        <v>0</v>
-      </c>
-      <c r="L148" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M148" s="17">
+      <c r="I148" s="23">
+        <v>0</v>
+      </c>
+      <c r="J148" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K148" s="16">
+        <v>0</v>
+      </c>
+      <c r="L148" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M148" s="16">
         <v>0</v>
       </c>
       <c r="N148">
         <v>100000</v>
       </c>
-      <c r="O148" s="27">
+      <c r="O148" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8682,46 +8073,46 @@
         <f t="shared" si="2"/>
         <v>10140010</v>
       </c>
-      <c r="B149" s="16">
+      <c r="B149" s="15">
         <v>101400</v>
       </c>
-      <c r="C149" s="16">
-        <v>1</v>
-      </c>
-      <c r="D149" s="16" t="s">
+      <c r="C149" s="15">
+        <v>1</v>
+      </c>
+      <c r="D149" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E149" s="16">
+      <c r="E149" s="15">
         <v>101400001</v>
       </c>
-      <c r="F149" s="16" t="s">
+      <c r="F149" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G149" s="17" t="s">
+      <c r="G149" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H149" s="16">
+        <v>10</v>
+      </c>
+      <c r="I149" s="23">
+        <v>0</v>
+      </c>
+      <c r="J149" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K149" s="16">
+        <v>0</v>
+      </c>
+      <c r="L149" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H149" s="17">
-        <v>10</v>
-      </c>
-      <c r="I149" s="25">
-        <v>0</v>
-      </c>
-      <c r="J149" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K149" s="17">
-        <v>0</v>
-      </c>
-      <c r="L149" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M149" s="17">
+      <c r="M149" s="16">
         <v>0</v>
       </c>
       <c r="N149">
         <v>1000</v>
       </c>
-      <c r="O149" s="27">
+      <c r="O149" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8730,48 +8121,48 @@
         <f t="shared" si="2"/>
         <v>10140011</v>
       </c>
-      <c r="B150" s="16">
+      <c r="B150" s="15">
         <v>101400</v>
       </c>
-      <c r="C150" s="16">
-        <v>1</v>
-      </c>
-      <c r="D150" s="16" t="str">
+      <c r="C150" s="15">
+        <v>1</v>
+      </c>
+      <c r="D150" s="15" t="str">
         <f t="shared" ref="D150:D154" si="6">D149</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E150" s="16">
+      <c r="E150" s="15">
         <v>101400001</v>
       </c>
-      <c r="F150" s="16" t="str">
+      <c r="F150" s="15" t="str">
         <f t="shared" si="5"/>
         <v>Cleopatra</v>
       </c>
-      <c r="G150" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H150" s="17">
+      <c r="G150" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H150" s="16">
         <v>11</v>
       </c>
-      <c r="I150" s="25">
-        <v>0</v>
-      </c>
-      <c r="J150" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K150" s="17">
-        <v>0</v>
-      </c>
-      <c r="L150" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M150" s="17">
+      <c r="I150" s="23">
+        <v>0</v>
+      </c>
+      <c r="J150" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K150" s="16">
+        <v>0</v>
+      </c>
+      <c r="L150" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M150" s="16">
         <v>0</v>
       </c>
       <c r="N150">
         <v>10000</v>
       </c>
-      <c r="O150" s="27">
+      <c r="O150" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8780,48 +8171,48 @@
         <f t="shared" si="2"/>
         <v>10140012</v>
       </c>
-      <c r="B151" s="16">
+      <c r="B151" s="15">
         <v>101400</v>
       </c>
-      <c r="C151" s="16">
-        <v>1</v>
-      </c>
-      <c r="D151" s="16" t="str">
+      <c r="C151" s="15">
+        <v>1</v>
+      </c>
+      <c r="D151" s="15" t="str">
         <f t="shared" si="6"/>
         <v>埃及艳后</v>
       </c>
-      <c r="E151" s="16">
+      <c r="E151" s="15">
         <v>101400001</v>
       </c>
-      <c r="F151" s="16" t="str">
+      <c r="F151" s="15" t="str">
         <f t="shared" si="5"/>
         <v>Cleopatra</v>
       </c>
-      <c r="G151" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H151" s="17">
+      <c r="G151" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H151" s="16">
         <v>12</v>
       </c>
-      <c r="I151" s="25">
-        <v>0</v>
-      </c>
-      <c r="J151" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K151" s="17">
-        <v>0</v>
-      </c>
-      <c r="L151" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M151" s="17">
+      <c r="I151" s="23">
+        <v>0</v>
+      </c>
+      <c r="J151" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K151" s="16">
+        <v>0</v>
+      </c>
+      <c r="L151" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M151" s="16">
         <v>0</v>
       </c>
       <c r="N151">
         <v>100000</v>
       </c>
-      <c r="O151" s="27">
+      <c r="O151" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8830,46 +8221,46 @@
         <f t="shared" si="2"/>
         <v>10240010</v>
       </c>
-      <c r="B152" s="16">
+      <c r="B152" s="15">
         <v>102400</v>
       </c>
-      <c r="C152" s="16">
-        <v>1</v>
-      </c>
-      <c r="D152" s="16" t="s">
+      <c r="C152" s="15">
+        <v>1</v>
+      </c>
+      <c r="D152" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E152" s="16">
+      <c r="E152" s="15">
         <v>102400026</v>
       </c>
-      <c r="F152" s="16" t="s">
+      <c r="F152" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G152" s="17" t="s">
+      <c r="G152" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H152" s="16">
+        <v>10</v>
+      </c>
+      <c r="I152" s="23">
+        <v>0</v>
+      </c>
+      <c r="J152" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K152" s="16">
+        <v>0</v>
+      </c>
+      <c r="L152" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H152" s="17">
-        <v>10</v>
-      </c>
-      <c r="I152" s="25">
-        <v>0</v>
-      </c>
-      <c r="J152" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K152" s="17">
-        <v>0</v>
-      </c>
-      <c r="L152" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M152" s="17">
+      <c r="M152" s="16">
         <v>0</v>
       </c>
       <c r="N152">
         <v>1000</v>
       </c>
-      <c r="O152" s="27">
+      <c r="O152" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8878,47 +8269,47 @@
         <f t="shared" si="2"/>
         <v>10240011</v>
       </c>
-      <c r="B153" s="16">
+      <c r="B153" s="15">
         <v>102400</v>
       </c>
-      <c r="C153" s="16">
-        <v>1</v>
-      </c>
-      <c r="D153" s="16" t="str">
+      <c r="C153" s="15">
+        <v>1</v>
+      </c>
+      <c r="D153" s="15" t="str">
         <f t="shared" si="6"/>
         <v>财富银行</v>
       </c>
-      <c r="E153" s="16">
+      <c r="E153" s="15">
         <v>102400026</v>
       </c>
-      <c r="F153" s="16" t="s">
+      <c r="F153" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G153" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H153" s="17">
+      <c r="G153" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H153" s="16">
         <v>11</v>
       </c>
-      <c r="I153" s="25">
-        <v>0</v>
-      </c>
-      <c r="J153" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K153" s="17">
-        <v>0</v>
-      </c>
-      <c r="L153" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M153" s="17">
+      <c r="I153" s="23">
+        <v>0</v>
+      </c>
+      <c r="J153" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K153" s="16">
+        <v>0</v>
+      </c>
+      <c r="L153" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M153" s="16">
         <v>0</v>
       </c>
       <c r="N153">
         <v>10000</v>
       </c>
-      <c r="O153" s="27">
+      <c r="O153" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8927,47 +8318,47 @@
         <f t="shared" si="2"/>
         <v>10240012</v>
       </c>
-      <c r="B154" s="16">
+      <c r="B154" s="15">
         <v>102400</v>
       </c>
-      <c r="C154" s="16">
-        <v>1</v>
-      </c>
-      <c r="D154" s="16" t="str">
+      <c r="C154" s="15">
+        <v>1</v>
+      </c>
+      <c r="D154" s="15" t="str">
         <f t="shared" si="6"/>
         <v>财富银行</v>
       </c>
-      <c r="E154" s="16">
+      <c r="E154" s="15">
         <v>102400026</v>
       </c>
-      <c r="F154" s="16" t="s">
+      <c r="F154" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G154" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H154" s="17">
+      <c r="G154" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H154" s="16">
         <v>12</v>
       </c>
-      <c r="I154" s="25">
-        <v>0</v>
-      </c>
-      <c r="J154" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K154" s="17">
-        <v>0</v>
-      </c>
-      <c r="L154" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M154" s="17">
+      <c r="I154" s="23">
+        <v>0</v>
+      </c>
+      <c r="J154" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K154" s="16">
+        <v>0</v>
+      </c>
+      <c r="L154" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M154" s="16">
         <v>0</v>
       </c>
       <c r="N154">
         <v>100000</v>
       </c>
-      <c r="O154" s="27">
+      <c r="O154" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -8976,46 +8367,46 @@
         <f t="shared" si="2"/>
         <v>10220010</v>
       </c>
-      <c r="B155" s="16">
+      <c r="B155" s="15">
         <v>102200</v>
       </c>
-      <c r="C155" s="16">
-        <v>1</v>
-      </c>
-      <c r="D155" s="16" t="s">
+      <c r="C155" s="15">
+        <v>1</v>
+      </c>
+      <c r="D155" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E155" s="16">
+      <c r="E155" s="15">
         <v>102200001</v>
       </c>
-      <c r="F155" s="16" t="s">
+      <c r="F155" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="G155" s="17" t="s">
+      <c r="G155" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H155" s="16">
+        <v>10</v>
+      </c>
+      <c r="I155" s="23">
+        <v>0</v>
+      </c>
+      <c r="J155" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K155" s="16">
+        <v>0</v>
+      </c>
+      <c r="L155" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H155" s="17">
-        <v>10</v>
-      </c>
-      <c r="I155" s="25">
-        <v>0</v>
-      </c>
-      <c r="J155" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K155" s="17">
-        <v>0</v>
-      </c>
-      <c r="L155" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M155" s="17">
+      <c r="M155" s="16">
         <v>0</v>
       </c>
       <c r="N155">
         <v>1000</v>
       </c>
-      <c r="O155" s="27">
+      <c r="O155" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9024,46 +8415,46 @@
         <f t="shared" si="2"/>
         <v>10220011</v>
       </c>
-      <c r="B156" s="16">
+      <c r="B156" s="15">
         <v>102200</v>
       </c>
-      <c r="C156" s="16">
-        <v>1</v>
-      </c>
-      <c r="D156" s="16" t="s">
+      <c r="C156" s="15">
+        <v>1</v>
+      </c>
+      <c r="D156" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E156" s="16">
+      <c r="E156" s="15">
         <v>102200001</v>
       </c>
-      <c r="F156" s="16" t="s">
+      <c r="F156" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="G156" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H156" s="17">
+      <c r="G156" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H156" s="16">
         <v>11</v>
       </c>
-      <c r="I156" s="25">
-        <v>0</v>
-      </c>
-      <c r="J156" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K156" s="17">
-        <v>0</v>
-      </c>
-      <c r="L156" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M156" s="17">
+      <c r="I156" s="23">
+        <v>0</v>
+      </c>
+      <c r="J156" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K156" s="16">
+        <v>0</v>
+      </c>
+      <c r="L156" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M156" s="16">
         <v>0</v>
       </c>
       <c r="N156">
         <v>10000</v>
       </c>
-      <c r="O156" s="27">
+      <c r="O156" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9072,46 +8463,46 @@
         <f t="shared" si="2"/>
         <v>10220012</v>
       </c>
-      <c r="B157" s="16">
+      <c r="B157" s="15">
         <v>102200</v>
       </c>
-      <c r="C157" s="16">
-        <v>1</v>
-      </c>
-      <c r="D157" s="16" t="s">
+      <c r="C157" s="15">
+        <v>1</v>
+      </c>
+      <c r="D157" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E157" s="16">
+      <c r="E157" s="15">
         <v>102200001</v>
       </c>
-      <c r="F157" s="16" t="s">
+      <c r="F157" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="G157" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H157" s="17">
+      <c r="G157" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H157" s="16">
         <v>12</v>
       </c>
-      <c r="I157" s="25">
-        <v>0</v>
-      </c>
-      <c r="J157" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K157" s="17">
-        <v>0</v>
-      </c>
-      <c r="L157" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M157" s="17">
+      <c r="I157" s="23">
+        <v>0</v>
+      </c>
+      <c r="J157" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K157" s="16">
+        <v>0</v>
+      </c>
+      <c r="L157" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M157" s="16">
         <v>0</v>
       </c>
       <c r="N157">
         <v>100000</v>
       </c>
-      <c r="O157" s="27">
+      <c r="O157" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9120,46 +8511,46 @@
         <f t="shared" si="2"/>
         <v>10170010</v>
       </c>
-      <c r="B158" s="16">
+      <c r="B158" s="15">
         <v>101700</v>
       </c>
-      <c r="C158" s="16">
-        <v>1</v>
-      </c>
-      <c r="D158" s="16" t="s">
+      <c r="C158" s="15">
+        <v>1</v>
+      </c>
+      <c r="D158" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E158" s="16">
+      <c r="E158" s="15">
         <v>101700001</v>
       </c>
-      <c r="F158" s="16" t="s">
+      <c r="F158" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="G158" s="17" t="s">
+      <c r="G158" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H158" s="16">
+        <v>10</v>
+      </c>
+      <c r="I158" s="23">
+        <v>0</v>
+      </c>
+      <c r="J158" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K158" s="16">
+        <v>0</v>
+      </c>
+      <c r="L158" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H158" s="17">
-        <v>10</v>
-      </c>
-      <c r="I158" s="25">
-        <v>0</v>
-      </c>
-      <c r="J158" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K158" s="17">
-        <v>0</v>
-      </c>
-      <c r="L158" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M158" s="17">
+      <c r="M158" s="16">
         <v>0</v>
       </c>
       <c r="N158">
         <v>1000</v>
       </c>
-      <c r="O158" s="27">
+      <c r="O158" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9168,46 +8559,46 @@
         <f t="shared" si="2"/>
         <v>10170011</v>
       </c>
-      <c r="B159" s="16">
+      <c r="B159" s="15">
         <v>101700</v>
       </c>
-      <c r="C159" s="16">
-        <v>1</v>
-      </c>
-      <c r="D159" s="16" t="s">
+      <c r="C159" s="15">
+        <v>1</v>
+      </c>
+      <c r="D159" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E159" s="16">
+      <c r="E159" s="15">
         <v>101700001</v>
       </c>
-      <c r="F159" s="16" t="s">
+      <c r="F159" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="G159" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H159" s="17">
+      <c r="G159" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H159" s="16">
         <v>11</v>
       </c>
-      <c r="I159" s="25">
-        <v>0</v>
-      </c>
-      <c r="J159" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K159" s="17">
-        <v>0</v>
-      </c>
-      <c r="L159" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M159" s="17">
+      <c r="I159" s="23">
+        <v>0</v>
+      </c>
+      <c r="J159" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K159" s="16">
+        <v>0</v>
+      </c>
+      <c r="L159" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M159" s="16">
         <v>0</v>
       </c>
       <c r="N159">
         <v>10000</v>
       </c>
-      <c r="O159" s="27">
+      <c r="O159" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9216,46 +8607,46 @@
         <f t="shared" si="2"/>
         <v>10170012</v>
       </c>
-      <c r="B160" s="16">
+      <c r="B160" s="15">
         <v>101700</v>
       </c>
-      <c r="C160" s="16">
-        <v>1</v>
-      </c>
-      <c r="D160" s="16" t="s">
+      <c r="C160" s="15">
+        <v>1</v>
+      </c>
+      <c r="D160" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E160" s="16">
+      <c r="E160" s="15">
         <v>101700001</v>
       </c>
-      <c r="F160" s="16" t="s">
+      <c r="F160" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="G160" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H160" s="17">
+      <c r="G160" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H160" s="16">
         <v>12</v>
       </c>
-      <c r="I160" s="25">
-        <v>0</v>
-      </c>
-      <c r="J160" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K160" s="17">
-        <v>0</v>
-      </c>
-      <c r="L160" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M160" s="17">
+      <c r="I160" s="23">
+        <v>0</v>
+      </c>
+      <c r="J160" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K160" s="16">
+        <v>0</v>
+      </c>
+      <c r="L160" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M160" s="16">
         <v>0</v>
       </c>
       <c r="N160">
         <v>100000</v>
       </c>
-      <c r="O160" s="27">
+      <c r="O160" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9264,46 +8655,46 @@
         <f t="shared" si="2"/>
         <v>10210010</v>
       </c>
-      <c r="B161" s="16">
+      <c r="B161" s="15">
         <v>102100</v>
       </c>
-      <c r="C161" s="16">
-        <v>1</v>
-      </c>
-      <c r="D161" s="16" t="s">
+      <c r="C161" s="15">
+        <v>1</v>
+      </c>
+      <c r="D161" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E161" s="16">
+      <c r="E161" s="15">
         <v>102100001</v>
       </c>
-      <c r="F161" s="16" t="s">
+      <c r="F161" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="G161" s="17" t="s">
+      <c r="G161" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H161" s="16">
+        <v>10</v>
+      </c>
+      <c r="I161" s="23">
+        <v>0</v>
+      </c>
+      <c r="J161" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K161" s="16">
+        <v>0</v>
+      </c>
+      <c r="L161" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H161" s="17">
-        <v>10</v>
-      </c>
-      <c r="I161" s="25">
-        <v>0</v>
-      </c>
-      <c r="J161" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K161" s="17">
-        <v>0</v>
-      </c>
-      <c r="L161" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M161" s="17">
+      <c r="M161" s="16">
         <v>0</v>
       </c>
       <c r="N161">
         <v>1000</v>
       </c>
-      <c r="O161" s="27">
+      <c r="O161" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9312,46 +8703,46 @@
         <f t="shared" si="2"/>
         <v>10210011</v>
       </c>
-      <c r="B162" s="16">
+      <c r="B162" s="15">
         <v>102100</v>
       </c>
-      <c r="C162" s="16">
-        <v>1</v>
-      </c>
-      <c r="D162" s="16" t="s">
+      <c r="C162" s="15">
+        <v>1</v>
+      </c>
+      <c r="D162" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E162" s="16">
+      <c r="E162" s="15">
         <v>102100001</v>
       </c>
-      <c r="F162" s="16" t="s">
+      <c r="F162" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="G162" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H162" s="17">
+      <c r="G162" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H162" s="16">
         <v>11</v>
       </c>
-      <c r="I162" s="25">
-        <v>0</v>
-      </c>
-      <c r="J162" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K162" s="17">
-        <v>0</v>
-      </c>
-      <c r="L162" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M162" s="17">
+      <c r="I162" s="23">
+        <v>0</v>
+      </c>
+      <c r="J162" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K162" s="16">
+        <v>0</v>
+      </c>
+      <c r="L162" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M162" s="16">
         <v>0</v>
       </c>
       <c r="N162">
         <v>10000</v>
       </c>
-      <c r="O162" s="27">
+      <c r="O162" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9360,46 +8751,46 @@
         <f t="shared" si="2"/>
         <v>10210012</v>
       </c>
-      <c r="B163" s="16">
+      <c r="B163" s="15">
         <v>102100</v>
       </c>
-      <c r="C163" s="16">
-        <v>1</v>
-      </c>
-      <c r="D163" s="16" t="s">
+      <c r="C163" s="15">
+        <v>1</v>
+      </c>
+      <c r="D163" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E163" s="16">
+      <c r="E163" s="15">
         <v>102100001</v>
       </c>
-      <c r="F163" s="16" t="s">
+      <c r="F163" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="G163" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H163" s="17">
+      <c r="G163" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H163" s="16">
         <v>12</v>
       </c>
-      <c r="I163" s="25">
-        <v>0</v>
-      </c>
-      <c r="J163" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K163" s="17">
-        <v>0</v>
-      </c>
-      <c r="L163" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M163" s="17">
+      <c r="I163" s="23">
+        <v>0</v>
+      </c>
+      <c r="J163" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K163" s="16">
+        <v>0</v>
+      </c>
+      <c r="L163" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M163" s="16">
         <v>0</v>
       </c>
       <c r="N163">
         <v>100000</v>
       </c>
-      <c r="O163" s="27">
+      <c r="O163" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9408,46 +8799,46 @@
         <f t="shared" si="2"/>
         <v>10180010</v>
       </c>
-      <c r="B164" s="16">
+      <c r="B164" s="15">
         <v>101800</v>
       </c>
-      <c r="C164" s="16">
-        <v>1</v>
-      </c>
-      <c r="D164" s="16" t="s">
+      <c r="C164" s="15">
+        <v>1</v>
+      </c>
+      <c r="D164" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E164" s="16">
+      <c r="E164" s="15">
         <v>101800001</v>
       </c>
-      <c r="F164" s="16" t="s">
+      <c r="F164" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="G164" s="17" t="s">
+      <c r="G164" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H164" s="16">
+        <v>10</v>
+      </c>
+      <c r="I164" s="23">
+        <v>0</v>
+      </c>
+      <c r="J164" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K164" s="16">
+        <v>0</v>
+      </c>
+      <c r="L164" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H164" s="17">
-        <v>10</v>
-      </c>
-      <c r="I164" s="25">
-        <v>0</v>
-      </c>
-      <c r="J164" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K164" s="17">
-        <v>0</v>
-      </c>
-      <c r="L164" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M164" s="17">
+      <c r="M164" s="16">
         <v>0</v>
       </c>
       <c r="N164">
         <v>1000</v>
       </c>
-      <c r="O164" s="27">
+      <c r="O164" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9456,46 +8847,46 @@
         <f t="shared" si="2"/>
         <v>10180011</v>
       </c>
-      <c r="B165" s="16">
+      <c r="B165" s="15">
         <v>101800</v>
       </c>
-      <c r="C165" s="16">
-        <v>1</v>
-      </c>
-      <c r="D165" s="16" t="s">
+      <c r="C165" s="15">
+        <v>1</v>
+      </c>
+      <c r="D165" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E165" s="16">
+      <c r="E165" s="15">
         <v>101800001</v>
       </c>
-      <c r="F165" s="16" t="s">
+      <c r="F165" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="G165" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H165" s="17">
+      <c r="G165" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H165" s="16">
         <v>11</v>
       </c>
-      <c r="I165" s="25">
-        <v>0</v>
-      </c>
-      <c r="J165" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K165" s="17">
-        <v>0</v>
-      </c>
-      <c r="L165" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M165" s="17">
+      <c r="I165" s="23">
+        <v>0</v>
+      </c>
+      <c r="J165" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K165" s="16">
+        <v>0</v>
+      </c>
+      <c r="L165" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M165" s="16">
         <v>0</v>
       </c>
       <c r="N165">
         <v>10000</v>
       </c>
-      <c r="O165" s="27">
+      <c r="O165" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9504,46 +8895,46 @@
         <f t="shared" si="2"/>
         <v>10180012</v>
       </c>
-      <c r="B166" s="16">
+      <c r="B166" s="15">
         <v>101800</v>
       </c>
-      <c r="C166" s="16">
-        <v>1</v>
-      </c>
-      <c r="D166" s="16" t="s">
+      <c r="C166" s="15">
+        <v>1</v>
+      </c>
+      <c r="D166" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E166" s="16">
+      <c r="E166" s="15">
         <v>101800001</v>
       </c>
-      <c r="F166" s="16" t="s">
+      <c r="F166" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="G166" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H166" s="17">
+      <c r="G166" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H166" s="16">
         <v>12</v>
       </c>
-      <c r="I166" s="25">
-        <v>0</v>
-      </c>
-      <c r="J166" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K166" s="17">
-        <v>0</v>
-      </c>
-      <c r="L166" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M166" s="17">
+      <c r="I166" s="23">
+        <v>0</v>
+      </c>
+      <c r="J166" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K166" s="16">
+        <v>0</v>
+      </c>
+      <c r="L166" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M166" s="16">
         <v>0</v>
       </c>
       <c r="N166">
         <v>100000</v>
       </c>
-      <c r="O166" s="27">
+      <c r="O166" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9552,46 +8943,46 @@
         <f t="shared" si="2"/>
         <v>10250010</v>
       </c>
-      <c r="B167" s="16">
+      <c r="B167" s="15">
         <v>102500</v>
       </c>
-      <c r="C167" s="16">
-        <v>1</v>
-      </c>
-      <c r="D167" s="16" t="s">
+      <c r="C167" s="15">
+        <v>1</v>
+      </c>
+      <c r="D167" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E167" s="16">
+      <c r="E167" s="15">
         <v>102500001</v>
       </c>
-      <c r="F167" s="16" t="s">
+      <c r="F167" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G167" s="17" t="s">
+      <c r="G167" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H167" s="16">
+        <v>10</v>
+      </c>
+      <c r="I167" s="23">
+        <v>0</v>
+      </c>
+      <c r="J167" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K167" s="16">
+        <v>0</v>
+      </c>
+      <c r="L167" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H167" s="17">
-        <v>10</v>
-      </c>
-      <c r="I167" s="25">
-        <v>0</v>
-      </c>
-      <c r="J167" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K167" s="17">
-        <v>0</v>
-      </c>
-      <c r="L167" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M167" s="17">
+      <c r="M167" s="16">
         <v>0</v>
       </c>
       <c r="N167">
         <v>1000</v>
       </c>
-      <c r="O167" s="27">
+      <c r="O167" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9600,46 +8991,46 @@
         <f t="shared" si="2"/>
         <v>10250011</v>
       </c>
-      <c r="B168" s="16">
+      <c r="B168" s="15">
         <v>102500</v>
       </c>
-      <c r="C168" s="16">
-        <v>1</v>
-      </c>
-      <c r="D168" s="16" t="s">
+      <c r="C168" s="15">
+        <v>1</v>
+      </c>
+      <c r="D168" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E168" s="16">
+      <c r="E168" s="15">
         <v>102500001</v>
       </c>
-      <c r="F168" s="16" t="s">
+      <c r="F168" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G168" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H168" s="17">
+      <c r="G168" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H168" s="16">
         <v>11</v>
       </c>
-      <c r="I168" s="25">
-        <v>0</v>
-      </c>
-      <c r="J168" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K168" s="17">
-        <v>0</v>
-      </c>
-      <c r="L168" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M168" s="17">
+      <c r="I168" s="23">
+        <v>0</v>
+      </c>
+      <c r="J168" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K168" s="16">
+        <v>0</v>
+      </c>
+      <c r="L168" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M168" s="16">
         <v>0</v>
       </c>
       <c r="N168">
         <v>10000</v>
       </c>
-      <c r="O168" s="27">
+      <c r="O168" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9648,46 +9039,46 @@
         <f t="shared" si="2"/>
         <v>10250012</v>
       </c>
-      <c r="B169" s="16">
+      <c r="B169" s="15">
         <v>102500</v>
       </c>
-      <c r="C169" s="16">
-        <v>1</v>
-      </c>
-      <c r="D169" s="16" t="s">
+      <c r="C169" s="15">
+        <v>1</v>
+      </c>
+      <c r="D169" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E169" s="16">
+      <c r="E169" s="15">
         <v>102500001</v>
       </c>
-      <c r="F169" s="16" t="s">
+      <c r="F169" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G169" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H169" s="17">
+      <c r="G169" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H169" s="16">
         <v>12</v>
       </c>
-      <c r="I169" s="25">
-        <v>0</v>
-      </c>
-      <c r="J169" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K169" s="17">
-        <v>0</v>
-      </c>
-      <c r="L169" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M169" s="17">
+      <c r="I169" s="23">
+        <v>0</v>
+      </c>
+      <c r="J169" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K169" s="16">
+        <v>0</v>
+      </c>
+      <c r="L169" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M169" s="16">
         <v>0</v>
       </c>
       <c r="N169">
         <v>100000</v>
       </c>
-      <c r="O169" s="27">
+      <c r="O169" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9696,46 +9087,46 @@
         <f t="shared" si="2"/>
         <v>10230010</v>
       </c>
-      <c r="B170" s="16">
+      <c r="B170" s="15">
         <v>102300</v>
       </c>
-      <c r="C170" s="16">
-        <v>1</v>
-      </c>
-      <c r="D170" s="16" t="s">
+      <c r="C170" s="15">
+        <v>1</v>
+      </c>
+      <c r="D170" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E170" s="16">
+      <c r="E170" s="15">
         <v>102300001</v>
       </c>
-      <c r="F170" s="16" t="s">
+      <c r="F170" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="G170" s="17" t="s">
+      <c r="G170" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H170" s="16">
+        <v>10</v>
+      </c>
+      <c r="I170" s="23">
+        <v>0</v>
+      </c>
+      <c r="J170" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K170" s="16">
+        <v>0</v>
+      </c>
+      <c r="L170" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="H170" s="17">
-        <v>10</v>
-      </c>
-      <c r="I170" s="25">
-        <v>0</v>
-      </c>
-      <c r="J170" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K170" s="17">
-        <v>0</v>
-      </c>
-      <c r="L170" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M170" s="17">
+      <c r="M170" s="16">
         <v>0</v>
       </c>
       <c r="N170">
         <v>1000</v>
       </c>
-      <c r="O170" s="27">
+      <c r="O170" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9744,46 +9135,46 @@
         <f t="shared" si="2"/>
         <v>10230011</v>
       </c>
-      <c r="B171" s="16">
+      <c r="B171" s="15">
         <v>102300</v>
       </c>
-      <c r="C171" s="16">
-        <v>1</v>
-      </c>
-      <c r="D171" s="16" t="s">
+      <c r="C171" s="15">
+        <v>1</v>
+      </c>
+      <c r="D171" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E171" s="16">
+      <c r="E171" s="15">
         <v>102300001</v>
       </c>
-      <c r="F171" s="16" t="s">
+      <c r="F171" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="G171" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H171" s="17">
+      <c r="G171" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H171" s="16">
         <v>11</v>
       </c>
-      <c r="I171" s="25">
-        <v>0</v>
-      </c>
-      <c r="J171" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K171" s="17">
-        <v>0</v>
-      </c>
-      <c r="L171" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M171" s="17">
+      <c r="I171" s="23">
+        <v>0</v>
+      </c>
+      <c r="J171" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K171" s="16">
+        <v>0</v>
+      </c>
+      <c r="L171" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M171" s="16">
         <v>0</v>
       </c>
       <c r="N171">
         <v>10000</v>
       </c>
-      <c r="O171" s="27">
+      <c r="O171" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9792,46 +9183,46 @@
         <f t="shared" si="2"/>
         <v>10230012</v>
       </c>
-      <c r="B172" s="16">
+      <c r="B172" s="15">
         <v>102300</v>
       </c>
-      <c r="C172" s="16">
-        <v>1</v>
-      </c>
-      <c r="D172" s="16" t="s">
+      <c r="C172" s="15">
+        <v>1</v>
+      </c>
+      <c r="D172" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E172" s="16">
+      <c r="E172" s="15">
         <v>102300001</v>
       </c>
-      <c r="F172" s="16" t="s">
+      <c r="F172" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="G172" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="H172" s="17">
+      <c r="G172" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H172" s="16">
         <v>12</v>
       </c>
-      <c r="I172" s="25">
-        <v>0</v>
-      </c>
-      <c r="J172" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K172" s="17">
-        <v>0</v>
-      </c>
-      <c r="L172" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M172" s="17">
+      <c r="I172" s="23">
+        <v>0</v>
+      </c>
+      <c r="J172" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K172" s="16">
+        <v>0</v>
+      </c>
+      <c r="L172" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M172" s="16">
         <v>0</v>
       </c>
       <c r="N172">
         <v>100000</v>
       </c>
-      <c r="O172" s="27">
+      <c r="O172" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9855,8 +9246,8 @@
       <c r="F173" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G173" s="17" t="s">
-        <v>109</v>
+      <c r="G173" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="H173" s="1">
         <v>10</v>
@@ -9864,22 +9255,22 @@
       <c r="I173" s="2">
         <v>0</v>
       </c>
-      <c r="J173" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K173" s="17">
-        <v>0</v>
-      </c>
-      <c r="L173" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M173" s="17">
+      <c r="J173" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K173" s="16">
+        <v>0</v>
+      </c>
+      <c r="L173" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M173" s="16">
         <v>0</v>
       </c>
       <c r="N173">
         <v>1000</v>
       </c>
-      <c r="O173" s="27">
+      <c r="O173" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9903,8 +9294,8 @@
       <c r="F174" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G174" s="17" t="s">
-        <v>111</v>
+      <c r="G174" s="16" t="s">
+        <v>110</v>
       </c>
       <c r="H174" s="1">
         <v>11</v>
@@ -9912,22 +9303,22 @@
       <c r="I174" s="2">
         <v>0</v>
       </c>
-      <c r="J174" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K174" s="17">
-        <v>0</v>
-      </c>
-      <c r="L174" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M174" s="17">
+      <c r="J174" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K174" s="16">
+        <v>0</v>
+      </c>
+      <c r="L174" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M174" s="16">
         <v>0</v>
       </c>
       <c r="N174">
         <v>10000</v>
       </c>
-      <c r="O174" s="27">
+      <c r="O174" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9951,8 +9342,8 @@
       <c r="F175" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G175" s="17" t="s">
-        <v>112</v>
+      <c r="G175" s="16" t="s">
+        <v>111</v>
       </c>
       <c r="H175" s="1">
         <v>12</v>
@@ -9960,22 +9351,22 @@
       <c r="I175" s="2">
         <v>0</v>
       </c>
-      <c r="J175" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K175" s="17">
-        <v>0</v>
-      </c>
-      <c r="L175" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M175" s="17">
+      <c r="J175" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K175" s="16">
+        <v>0</v>
+      </c>
+      <c r="L175" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M175" s="16">
         <v>0</v>
       </c>
       <c r="N175">
         <v>100000</v>
       </c>
-      <c r="O175" s="27">
+      <c r="O175" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -9999,8 +9390,8 @@
       <c r="F176" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G176" s="17" t="s">
-        <v>109</v>
+      <c r="G176" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="H176" s="1">
         <v>10</v>
@@ -10008,22 +9399,22 @@
       <c r="I176" s="2">
         <v>0</v>
       </c>
-      <c r="J176" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K176" s="17">
-        <v>0</v>
-      </c>
-      <c r="L176" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M176" s="17">
+      <c r="J176" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K176" s="16">
+        <v>0</v>
+      </c>
+      <c r="L176" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M176" s="16">
         <v>0</v>
       </c>
       <c r="N176">
         <v>1000</v>
       </c>
-      <c r="O176" s="27">
+      <c r="O176" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -10047,8 +9438,8 @@
       <c r="F177" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G177" s="17" t="s">
-        <v>111</v>
+      <c r="G177" s="16" t="s">
+        <v>110</v>
       </c>
       <c r="H177" s="1">
         <v>11</v>
@@ -10056,22 +9447,22 @@
       <c r="I177" s="2">
         <v>0</v>
       </c>
-      <c r="J177" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K177" s="17">
-        <v>0</v>
-      </c>
-      <c r="L177" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M177" s="17">
+      <c r="J177" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K177" s="16">
+        <v>0</v>
+      </c>
+      <c r="L177" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M177" s="16">
         <v>0</v>
       </c>
       <c r="N177">
         <v>10000</v>
       </c>
-      <c r="O177" s="27">
+      <c r="O177" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -10095,8 +9486,8 @@
       <c r="F178" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G178" s="17" t="s">
-        <v>112</v>
+      <c r="G178" s="16" t="s">
+        <v>111</v>
       </c>
       <c r="H178" s="1">
         <v>12</v>
@@ -10104,22 +9495,22 @@
       <c r="I178" s="2">
         <v>0</v>
       </c>
-      <c r="J178" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K178" s="17">
-        <v>0</v>
-      </c>
-      <c r="L178" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M178" s="17">
+      <c r="J178" s="16">
+        <v>-1</v>
+      </c>
+      <c r="K178" s="16">
+        <v>0</v>
+      </c>
+      <c r="L178" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M178" s="16">
         <v>0</v>
       </c>
       <c r="N178">
         <v>100000</v>
       </c>
-      <c r="O178" s="27">
+      <c r="O178" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -10143,8 +9534,8 @@
       <c r="F179" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G179" s="17" t="s">
-        <v>109</v>
+      <c r="G179" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="H179" s="1">
         <v>10</v>
@@ -10152,22 +9543,22 @@
       <c r="I179" s="2">
         <v>0</v>
       </c>
-      <c r="J179" s="17">
+      <c r="J179" s="16">
         <v>-1</v>
       </c>
       <c r="K179" s="1">
         <v>0</v>
       </c>
-      <c r="L179" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M179" s="17">
+      <c r="L179" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M179" s="16">
         <v>0</v>
       </c>
       <c r="N179">
         <v>1000</v>
       </c>
-      <c r="O179" s="27">
+      <c r="O179" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -10191,8 +9582,8 @@
       <c r="F180" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G180" s="17" t="s">
-        <v>111</v>
+      <c r="G180" s="16" t="s">
+        <v>110</v>
       </c>
       <c r="H180" s="1">
         <v>11</v>
@@ -10200,22 +9591,22 @@
       <c r="I180" s="2">
         <v>0</v>
       </c>
-      <c r="J180" s="17">
+      <c r="J180" s="16">
         <v>-1</v>
       </c>
       <c r="K180" s="1">
         <v>0</v>
       </c>
-      <c r="L180" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M180" s="17">
+      <c r="L180" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M180" s="16">
         <v>0</v>
       </c>
       <c r="N180">
         <v>10000</v>
       </c>
-      <c r="O180" s="27">
+      <c r="O180" s="25">
         <v>1980000</v>
       </c>
     </row>
@@ -10239,8 +9630,8 @@
       <c r="F181" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G181" s="17" t="s">
-        <v>112</v>
+      <c r="G181" s="16" t="s">
+        <v>111</v>
       </c>
       <c r="H181" s="1">
         <v>12</v>
@@ -10248,29 +9639,29 @@
       <c r="I181" s="2">
         <v>0</v>
       </c>
-      <c r="J181" s="17">
+      <c r="J181" s="16">
         <v>-1</v>
       </c>
       <c r="K181" s="1">
         <v>0</v>
       </c>
-      <c r="L181" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="M181" s="17">
+      <c r="L181" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M181" s="16">
         <v>0</v>
       </c>
       <c r="N181">
         <v>100000</v>
       </c>
-      <c r="O181" s="27">
+      <c r="O181" s="25">
         <v>1980000</v>
       </c>
     </row>
-    <row r="182" ht="12" customHeight="1"/>
+    <row r="182" spans="1:15" ht="12" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="114">
   <si>
     <t>sid</t>
   </si>
@@ -363,6 +363,12 @@
   </si>
   <si>
     <t>BlessMouse</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>AceDJ</t>
   </si>
   <si>
     <t>虎虎生财</t>
@@ -1659,7 +1665,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S200"/>
+  <dimension ref="A1:S206"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
@@ -4242,10 +4248,11 @@
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="1">
-        <v>1034011</v>
+        <f t="shared" si="0"/>
+        <v>1028001</v>
       </c>
       <c r="B56" s="15">
-        <v>103401</v>
+        <v>102800</v>
       </c>
       <c r="C56" s="15">
         <v>1</v>
@@ -4254,7 +4261,7 @@
         <v>69</v>
       </c>
       <c r="E56" s="16">
-        <v>103400001</v>
+        <v>102800001</v>
       </c>
       <c r="F56" s="16" t="s">
         <v>70</v>
@@ -4289,10 +4296,11 @@
     </row>
     <row r="57" spans="1:15">
       <c r="A57" s="1">
-        <v>1034012</v>
+        <f t="shared" si="0"/>
+        <v>1028002</v>
       </c>
       <c r="B57" s="15">
-        <v>103401</v>
+        <v>102800</v>
       </c>
       <c r="C57" s="15">
         <v>1</v>
@@ -4301,7 +4309,7 @@
         <v>69</v>
       </c>
       <c r="E57" s="16">
-        <v>103400001</v>
+        <v>102800002</v>
       </c>
       <c r="F57" s="16" t="s">
         <v>70</v>
@@ -4336,10 +4344,11 @@
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="1">
-        <v>1034013</v>
+        <f t="shared" si="0"/>
+        <v>1028003</v>
       </c>
       <c r="B58" s="15">
-        <v>103401</v>
+        <v>102800</v>
       </c>
       <c r="C58" s="15">
         <v>1</v>
@@ -4348,7 +4357,7 @@
         <v>69</v>
       </c>
       <c r="E58" s="16">
-        <v>103400001</v>
+        <v>102800003</v>
       </c>
       <c r="F58" s="16" t="s">
         <v>70</v>
@@ -4383,10 +4392,10 @@
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="1">
-        <v>1038001</v>
+        <v>1034011</v>
       </c>
       <c r="B59" s="15">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C59" s="15">
         <v>1</v>
@@ -4395,7 +4404,7 @@
         <v>71</v>
       </c>
       <c r="E59" s="16">
-        <v>103800001</v>
+        <v>103401001</v>
       </c>
       <c r="F59" s="16" t="s">
         <v>72</v>
@@ -4422,7 +4431,7 @@
         <v>34</v>
       </c>
       <c r="N59">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="O59" s="18">
         <v>1990000</v>
@@ -4430,10 +4439,10 @@
     </row>
     <row r="60" spans="1:15">
       <c r="A60" s="1">
-        <v>1038002</v>
+        <v>1034012</v>
       </c>
       <c r="B60" s="15">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C60" s="15">
         <v>1</v>
@@ -4442,7 +4451,7 @@
         <v>71</v>
       </c>
       <c r="E60" s="16">
-        <v>103800001</v>
+        <v>103401001</v>
       </c>
       <c r="F60" s="16" t="s">
         <v>72</v>
@@ -4454,7 +4463,7 @@
         <v>2</v>
       </c>
       <c r="I60" s="3">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="J60" s="20">
         <v>-1</v>
@@ -4469,7 +4478,7 @@
         <v>34</v>
       </c>
       <c r="N60">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="O60" s="18">
         <v>1990000</v>
@@ -4477,10 +4486,10 @@
     </row>
     <row r="61" spans="1:15">
       <c r="A61" s="1">
-        <v>1038003</v>
+        <v>1034013</v>
       </c>
       <c r="B61" s="15">
-        <v>103800</v>
+        <v>103401</v>
       </c>
       <c r="C61" s="15">
         <v>1</v>
@@ -4489,7 +4498,7 @@
         <v>71</v>
       </c>
       <c r="E61" s="16">
-        <v>103800001</v>
+        <v>103401001</v>
       </c>
       <c r="F61" s="16" t="s">
         <v>72</v>
@@ -4501,7 +4510,7 @@
         <v>3</v>
       </c>
       <c r="I61" s="3">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="J61" s="20">
         <v>-1</v>
@@ -4516,7 +4525,7 @@
         <v>34</v>
       </c>
       <c r="N61">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="O61" s="18">
         <v>1990000</v>
@@ -4524,10 +4533,10 @@
     </row>
     <row r="62" spans="1:15">
       <c r="A62" s="1">
-        <v>1040001</v>
+        <v>1038001</v>
       </c>
       <c r="B62" s="15">
-        <v>104000</v>
+        <v>103800</v>
       </c>
       <c r="C62" s="15">
         <v>1</v>
@@ -4536,9 +4545,9 @@
         <v>73</v>
       </c>
       <c r="E62" s="16">
-        <v>104000001</v>
-      </c>
-      <c r="F62" s="2" t="s">
+        <v>103800001</v>
+      </c>
+      <c r="F62" s="16" t="s">
         <v>74</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -4563,7 +4572,7 @@
         <v>34</v>
       </c>
       <c r="N62">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="O62" s="18">
         <v>1990000</v>
@@ -4571,10 +4580,10 @@
     </row>
     <row r="63" spans="1:15">
       <c r="A63" s="1">
-        <v>1040002</v>
+        <v>1038002</v>
       </c>
       <c r="B63" s="15">
-        <v>104000</v>
+        <v>103800</v>
       </c>
       <c r="C63" s="15">
         <v>1</v>
@@ -4583,9 +4592,9 @@
         <v>73</v>
       </c>
       <c r="E63" s="16">
-        <v>104000001</v>
-      </c>
-      <c r="F63" s="2" t="s">
+        <v>103800001</v>
+      </c>
+      <c r="F63" s="16" t="s">
         <v>74</v>
       </c>
       <c r="G63" s="1" t="s">
@@ -4595,7 +4604,7 @@
         <v>2</v>
       </c>
       <c r="I63" s="3">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="J63" s="20">
         <v>-1</v>
@@ -4610,7 +4619,7 @@
         <v>34</v>
       </c>
       <c r="N63">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="O63" s="18">
         <v>1990000</v>
@@ -4618,10 +4627,10 @@
     </row>
     <row r="64" spans="1:15">
       <c r="A64" s="1">
-        <v>1040003</v>
+        <v>1038003</v>
       </c>
       <c r="B64" s="15">
-        <v>104000</v>
+        <v>103800</v>
       </c>
       <c r="C64" s="15">
         <v>1</v>
@@ -4630,9 +4639,9 @@
         <v>73</v>
       </c>
       <c r="E64" s="16">
-        <v>104000001</v>
-      </c>
-      <c r="F64" s="2" t="s">
+        <v>103800001</v>
+      </c>
+      <c r="F64" s="16" t="s">
         <v>74</v>
       </c>
       <c r="G64" s="1" t="s">
@@ -4642,7 +4651,7 @@
         <v>3</v>
       </c>
       <c r="I64" s="3">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="J64" s="20">
         <v>-1</v>
@@ -4657,7 +4666,7 @@
         <v>34</v>
       </c>
       <c r="N64">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="O64" s="18">
         <v>1990000</v>
@@ -4665,21 +4674,21 @@
     </row>
     <row r="65" spans="1:19">
       <c r="A65" s="1">
-        <v>2001001</v>
+        <v>1040001</v>
       </c>
       <c r="B65" s="15">
-        <v>200100</v>
+        <v>104000</v>
       </c>
       <c r="C65" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" s="15" t="s">
         <v>75</v>
       </c>
       <c r="E65" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F65" s="16" t="s">
+        <v>104000001</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G65" s="1" t="s">
@@ -4691,7 +4700,7 @@
       <c r="I65" s="3">
         <v>0</v>
       </c>
-      <c r="J65" s="1">
+      <c r="J65" s="20">
         <v>-1</v>
       </c>
       <c r="K65" s="1">
@@ -4712,21 +4721,21 @@
     </row>
     <row r="66" spans="1:19">
       <c r="A66" s="1">
-        <v>2001002</v>
+        <v>1040002</v>
       </c>
       <c r="B66" s="15">
-        <v>200100</v>
+        <v>104000</v>
       </c>
       <c r="C66" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" s="15" t="s">
         <v>75</v>
       </c>
       <c r="E66" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F66" s="16" t="s">
+        <v>104000001</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -4738,7 +4747,7 @@
       <c r="I66" s="3">
         <v>10000</v>
       </c>
-      <c r="J66" s="1">
+      <c r="J66" s="20">
         <v>-1</v>
       </c>
       <c r="K66" s="1">
@@ -4759,21 +4768,21 @@
     </row>
     <row r="67" spans="1:19">
       <c r="A67" s="1">
-        <v>2001003</v>
+        <v>1040003</v>
       </c>
       <c r="B67" s="15">
-        <v>200100</v>
+        <v>104000</v>
       </c>
       <c r="C67" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" s="15" t="s">
         <v>75</v>
       </c>
       <c r="E67" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F67" s="16" t="s">
+        <v>104000001</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -4785,7 +4794,7 @@
       <c r="I67" s="3">
         <v>100000</v>
       </c>
-      <c r="J67" s="1">
+      <c r="J67" s="20">
         <v>-1</v>
       </c>
       <c r="K67" s="1">
@@ -4803,14 +4812,13 @@
       <c r="O67" s="18">
         <v>1990000</v>
       </c>
-      <c r="Q67"/>
     </row>
     <row r="68" spans="1:19">
       <c r="A68" s="1">
-        <v>2001011</v>
+        <v>2001001</v>
       </c>
       <c r="B68" s="15">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C68" s="15">
         <v>2</v>
@@ -4819,7 +4827,7 @@
         <v>77</v>
       </c>
       <c r="E68" s="16">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F68" s="16" t="s">
         <v>78</v>
@@ -4852,12 +4860,12 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" spans="1:19">
+    <row r="69" spans="1:19">
       <c r="A69" s="1">
-        <v>2001012</v>
+        <v>2001002</v>
       </c>
       <c r="B69" s="15">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C69" s="15">
         <v>2</v>
@@ -4866,7 +4874,7 @@
         <v>77</v>
       </c>
       <c r="E69" s="16">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F69" s="16" t="s">
         <v>78</v>
@@ -4899,12 +4907,12 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" spans="1:19">
+    <row r="70" spans="1:19">
       <c r="A70" s="1">
-        <v>2001013</v>
+        <v>2001003</v>
       </c>
       <c r="B70" s="15">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C70" s="15">
         <v>2</v>
@@ -4913,7 +4921,7 @@
         <v>77</v>
       </c>
       <c r="E70" s="16">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F70" s="16" t="s">
         <v>78</v>
@@ -4945,13 +4953,14 @@
       <c r="O70" s="18">
         <v>1990000</v>
       </c>
+      <c r="Q70"/>
     </row>
     <row r="71" spans="1:19">
       <c r="A71" s="1">
-        <v>2003001</v>
+        <v>2001011</v>
       </c>
       <c r="B71" s="15">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C71" s="15">
         <v>2</v>
@@ -4960,7 +4969,7 @@
         <v>79</v>
       </c>
       <c r="E71" s="16">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F71" s="16" t="s">
         <v>80</v>
@@ -4995,10 +5004,10 @@
     </row>
     <row r="72" s="1" customFormat="1" spans="1:19">
       <c r="A72" s="1">
-        <v>2003002</v>
+        <v>2001012</v>
       </c>
       <c r="B72" s="15">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C72" s="15">
         <v>2</v>
@@ -5007,7 +5016,7 @@
         <v>79</v>
       </c>
       <c r="E72" s="16">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F72" s="16" t="s">
         <v>80</v>
@@ -5039,16 +5048,14 @@
       <c r="O72" s="18">
         <v>1990000</v>
       </c>
-      <c r="Q72" s="3"/>
-      <c r="R72" s="15"/>
       <c r="S72" s="3"/>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:19">
       <c r="A73" s="1">
-        <v>2003003</v>
+        <v>2001013</v>
       </c>
       <c r="B73" s="15">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C73" s="15">
         <v>2</v>
@@ -5057,7 +5064,7 @@
         <v>79</v>
       </c>
       <c r="E73" s="16">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F73" s="16" t="s">
         <v>80</v>
@@ -5089,25 +5096,23 @@
       <c r="O73" s="18">
         <v>1990000</v>
       </c>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="22"/>
-      <c r="S73" s="22"/>
+      <c r="S73" s="3"/>
     </row>
     <row r="74" spans="1:19">
       <c r="A74" s="1">
-        <v>2004001</v>
+        <v>2003001</v>
       </c>
       <c r="B74" s="15">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C74" s="15">
         <v>2</v>
       </c>
-      <c r="D74" s="22" t="s">
+      <c r="D74" s="15" t="s">
         <v>81</v>
       </c>
       <c r="E74" s="16">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F74" s="16" t="s">
         <v>82</v>
@@ -5139,25 +5144,22 @@
       <c r="O74" s="18">
         <v>1990000</v>
       </c>
-      <c r="Q74" s="3"/>
-      <c r="R74" s="22"/>
-      <c r="S74" s="22"/>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:19">
       <c r="A75" s="1">
-        <v>2004002</v>
+        <v>2003002</v>
       </c>
       <c r="B75" s="15">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C75" s="15">
         <v>2</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="D75" s="15" t="s">
         <v>81</v>
       </c>
       <c r="E75" s="16">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F75" s="16" t="s">
         <v>82</v>
@@ -5190,24 +5192,24 @@
         <v>1990000</v>
       </c>
       <c r="Q75" s="3"/>
-      <c r="R75" s="22"/>
-      <c r="S75" s="22"/>
+      <c r="R75" s="15"/>
+      <c r="S75" s="3"/>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:19">
       <c r="A76" s="1">
-        <v>2004003</v>
+        <v>2003003</v>
       </c>
       <c r="B76" s="15">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C76" s="15">
         <v>2</v>
       </c>
-      <c r="D76" s="22" t="s">
+      <c r="D76" s="15" t="s">
         <v>81</v>
       </c>
       <c r="E76" s="16">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F76" s="16" t="s">
         <v>82</v>
@@ -5245,19 +5247,19 @@
     </row>
     <row r="77" spans="1:19">
       <c r="A77" s="1">
-        <v>2005001</v>
+        <v>2004001</v>
       </c>
       <c r="B77" s="15">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C77" s="15">
         <v>2</v>
       </c>
-      <c r="D77" s="15" t="s">
+      <c r="D77" s="22" t="s">
         <v>83</v>
       </c>
       <c r="E77" s="16">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F77" s="16" t="s">
         <v>84</v>
@@ -5281,7 +5283,7 @@
         <v>33</v>
       </c>
       <c r="M77" s="31" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="N77">
         <v>1000</v>
@@ -5293,21 +5295,21 @@
       <c r="R77" s="22"/>
       <c r="S77" s="22"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" s="1" customFormat="1" spans="1:19">
       <c r="A78" s="1">
-        <v>2005002</v>
+        <v>2004002</v>
       </c>
       <c r="B78" s="15">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C78" s="15">
         <v>2</v>
       </c>
-      <c r="D78" s="15" t="s">
+      <c r="D78" s="22" t="s">
         <v>83</v>
       </c>
       <c r="E78" s="16">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F78" s="16" t="s">
         <v>84</v>
@@ -5331,7 +5333,7 @@
         <v>33</v>
       </c>
       <c r="M78" s="31" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="N78">
         <v>10000</v>
@@ -5343,21 +5345,21 @@
       <c r="R78" s="22"/>
       <c r="S78" s="22"/>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" s="1" customFormat="1" spans="1:19">
       <c r="A79" s="1">
-        <v>2005003</v>
+        <v>2004003</v>
       </c>
       <c r="B79" s="15">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C79" s="15">
         <v>2</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D79" s="22" t="s">
         <v>83</v>
       </c>
       <c r="E79" s="16">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F79" s="16" t="s">
         <v>84</v>
@@ -5381,7 +5383,7 @@
         <v>33</v>
       </c>
       <c r="M79" s="31" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="N79">
         <v>100000</v>
@@ -5395,22 +5397,22 @@
     </row>
     <row r="80" spans="1:19">
       <c r="A80" s="1">
-        <v>2006001</v>
+        <v>2005001</v>
       </c>
       <c r="B80" s="15">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C80" s="15">
         <v>2</v>
       </c>
-      <c r="D80" s="16" t="s">
+      <c r="D80" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E80" s="16">
+        <v>200500025</v>
+      </c>
+      <c r="F80" s="16" t="s">
         <v>86</v>
-      </c>
-      <c r="E80" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F80" s="16" t="s">
-        <v>87</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>32</v>
@@ -5431,7 +5433,7 @@
         <v>33</v>
       </c>
       <c r="M80" s="31" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="N80">
         <v>1000</v>
@@ -5443,24 +5445,24 @@
       <c r="R80" s="22"/>
       <c r="S80" s="22"/>
     </row>
-    <row r="81" s="1" customFormat="1" spans="1:19">
+    <row r="81" spans="1:19">
       <c r="A81" s="1">
-        <v>2006002</v>
+        <v>2005002</v>
       </c>
       <c r="B81" s="15">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C81" s="15">
         <v>2</v>
       </c>
-      <c r="D81" s="16" t="s">
+      <c r="D81" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E81" s="16">
+        <v>200500025</v>
+      </c>
+      <c r="F81" s="16" t="s">
         <v>86</v>
-      </c>
-      <c r="E81" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F81" s="16" t="s">
-        <v>87</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>35</v>
@@ -5481,7 +5483,7 @@
         <v>33</v>
       </c>
       <c r="M81" s="31" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="N81">
         <v>10000</v>
@@ -5493,24 +5495,24 @@
       <c r="R81" s="22"/>
       <c r="S81" s="22"/>
     </row>
-    <row r="82" s="1" customFormat="1" spans="1:19">
+    <row r="82" spans="1:19">
       <c r="A82" s="1">
-        <v>2006003</v>
+        <v>2005003</v>
       </c>
       <c r="B82" s="15">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C82" s="15">
         <v>2</v>
       </c>
-      <c r="D82" s="16" t="s">
+      <c r="D82" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E82" s="16">
+        <v>200500025</v>
+      </c>
+      <c r="F82" s="16" t="s">
         <v>86</v>
-      </c>
-      <c r="E82" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F82" s="16" t="s">
-        <v>87</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>36</v>
@@ -5531,7 +5533,7 @@
         <v>33</v>
       </c>
       <c r="M82" s="31" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="N82">
         <v>100000</v>
@@ -5540,24 +5542,24 @@
         <v>1990000</v>
       </c>
       <c r="Q82" s="3"/>
-      <c r="R82"/>
+      <c r="R82" s="22"/>
       <c r="S82" s="22"/>
     </row>
     <row r="83" spans="1:19">
       <c r="A83" s="1">
-        <v>2007001</v>
+        <v>2006001</v>
       </c>
       <c r="B83" s="15">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C83" s="15">
         <v>2</v>
       </c>
-      <c r="D83" s="15" t="s">
+      <c r="D83" s="16" t="s">
         <v>88</v>
       </c>
       <c r="E83" s="16">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F83" s="16" t="s">
         <v>89</v>
@@ -5595,19 +5597,19 @@
     </row>
     <row r="84" s="1" customFormat="1" spans="1:19">
       <c r="A84" s="1">
-        <v>2007002</v>
+        <v>2006002</v>
       </c>
       <c r="B84" s="15">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C84" s="15">
         <v>2</v>
       </c>
-      <c r="D84" s="15" t="s">
+      <c r="D84" s="16" t="s">
         <v>88</v>
       </c>
       <c r="E84" s="16">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F84" s="16" t="s">
         <v>89</v>
@@ -5645,19 +5647,19 @@
     </row>
     <row r="85" s="1" customFormat="1" spans="1:19">
       <c r="A85" s="1">
-        <v>2007003</v>
+        <v>2006003</v>
       </c>
       <c r="B85" s="15">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C85" s="15">
         <v>2</v>
       </c>
-      <c r="D85" s="15" t="s">
+      <c r="D85" s="16" t="s">
         <v>88</v>
       </c>
       <c r="E85" s="16">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F85" s="16" t="s">
         <v>89</v>
@@ -5689,23 +5691,25 @@
       <c r="O85" s="18">
         <v>1990000</v>
       </c>
-      <c r="S85" s="3"/>
-    </row>
-    <row r="86" s="1" customFormat="1" spans="1:19">
+      <c r="Q85" s="3"/>
+      <c r="R85"/>
+      <c r="S85" s="22"/>
+    </row>
+    <row r="86" spans="1:19">
       <c r="A86" s="1">
-        <v>2008001</v>
+        <v>2007001</v>
       </c>
       <c r="B86" s="15">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C86" s="15">
         <v>2</v>
       </c>
-      <c r="D86" s="16" t="s">
+      <c r="D86" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E86" s="16">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F86" s="16" t="s">
         <v>91</v>
@@ -5737,23 +5741,25 @@
       <c r="O86" s="18">
         <v>1990000</v>
       </c>
-      <c r="S86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
     </row>
     <row r="87" s="1" customFormat="1" spans="1:19">
       <c r="A87" s="1">
-        <v>2008002</v>
+        <v>2007002</v>
       </c>
       <c r="B87" s="15">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C87" s="15">
         <v>2</v>
       </c>
-      <c r="D87" s="16" t="s">
+      <c r="D87" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E87" s="16">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F87" s="16" t="s">
         <v>91</v>
@@ -5785,23 +5791,25 @@
       <c r="O87" s="18">
         <v>1990000</v>
       </c>
-      <c r="S87" s="3"/>
+      <c r="Q87" s="3"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
     </row>
     <row r="88" s="1" customFormat="1" spans="1:19">
       <c r="A88" s="1">
-        <v>2008003</v>
+        <v>2007003</v>
       </c>
       <c r="B88" s="15">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C88" s="15">
         <v>2</v>
       </c>
-      <c r="D88" s="16" t="s">
+      <c r="D88" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E88" s="16">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F88" s="16" t="s">
         <v>91</v>
@@ -5835,21 +5843,21 @@
       </c>
       <c r="S88" s="3"/>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" s="1" customFormat="1" spans="1:19">
       <c r="A89" s="1">
-        <v>2009001</v>
-      </c>
-      <c r="B89" s="23">
-        <v>200900</v>
+        <v>2008001</v>
+      </c>
+      <c r="B89" s="15">
+        <v>200800</v>
       </c>
       <c r="C89" s="15">
         <v>2</v>
       </c>
-      <c r="D89" s="23" t="s">
+      <c r="D89" s="16" t="s">
         <v>92</v>
       </c>
       <c r="E89" s="16">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F89" s="16" t="s">
         <v>93</v>
@@ -5881,22 +5889,23 @@
       <c r="O89" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="90" spans="1:19">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" s="1" customFormat="1" spans="1:19">
       <c r="A90" s="1">
-        <v>2009002</v>
+        <v>2008002</v>
       </c>
       <c r="B90" s="15">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C90" s="15">
         <v>2</v>
       </c>
-      <c r="D90" s="15" t="s">
+      <c r="D90" s="16" t="s">
         <v>92</v>
       </c>
       <c r="E90" s="16">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F90" s="16" t="s">
         <v>93</v>
@@ -5928,22 +5937,23 @@
       <c r="O90" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="91" spans="1:19">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" s="1" customFormat="1" spans="1:19">
       <c r="A91" s="1">
-        <v>2009003</v>
+        <v>2008003</v>
       </c>
       <c r="B91" s="15">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C91" s="15">
         <v>2</v>
       </c>
-      <c r="D91" s="15" t="s">
+      <c r="D91" s="16" t="s">
         <v>92</v>
       </c>
       <c r="E91" s="16">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F91" s="16" t="s">
         <v>93</v>
@@ -5975,22 +5985,23 @@
       <c r="O91" s="18">
         <v>1990000</v>
       </c>
+      <c r="S91" s="3"/>
     </row>
     <row r="92" spans="1:19">
       <c r="A92" s="1">
-        <v>3001001</v>
-      </c>
-      <c r="B92" s="15">
-        <v>300100</v>
+        <v>2009001</v>
+      </c>
+      <c r="B92" s="23">
+        <v>200900</v>
       </c>
       <c r="C92" s="15">
-        <v>3</v>
-      </c>
-      <c r="D92" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" s="23" t="s">
         <v>94</v>
       </c>
       <c r="E92" s="16">
-        <v>300100001</v>
+        <v>200900001</v>
       </c>
       <c r="F92" s="16" t="s">
         <v>95</v>
@@ -6011,10 +6022,10 @@
         <v>0</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="M92" s="31" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="N92">
         <v>1000</v>
@@ -6023,21 +6034,21 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="93" s="1" customFormat="1" spans="1:19">
+    <row r="93" spans="1:19">
       <c r="A93" s="1">
-        <v>3001002</v>
+        <v>2009002</v>
       </c>
       <c r="B93" s="15">
-        <v>300100</v>
+        <v>200900</v>
       </c>
       <c r="C93" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D93" s="15" t="s">
         <v>94</v>
       </c>
       <c r="E93" s="16">
-        <v>300100001</v>
+        <v>200900001</v>
       </c>
       <c r="F93" s="16" t="s">
         <v>95</v>
@@ -6058,10 +6069,10 @@
         <v>0</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="M93" s="31" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="N93">
         <v>10000</v>
@@ -6069,23 +6080,22 @@
       <c r="O93" s="18">
         <v>1990000</v>
       </c>
-      <c r="S93" s="3"/>
-    </row>
-    <row r="94" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="94" spans="1:19">
       <c r="A94" s="1">
-        <v>3001003</v>
+        <v>2009003</v>
       </c>
       <c r="B94" s="15">
-        <v>300100</v>
+        <v>200900</v>
       </c>
       <c r="C94" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" s="15" t="s">
         <v>94</v>
       </c>
       <c r="E94" s="16">
-        <v>300100001</v>
+        <v>200900001</v>
       </c>
       <c r="F94" s="16" t="s">
         <v>95</v>
@@ -6106,10 +6116,10 @@
         <v>0</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="M94" s="31" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="N94">
         <v>100000</v>
@@ -6117,26 +6127,25 @@
       <c r="O94" s="18">
         <v>1990000</v>
       </c>
-      <c r="S94" s="3"/>
-    </row>
-    <row r="95" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="95" spans="1:19">
       <c r="A95" s="1">
-        <v>3002001</v>
+        <v>3001001</v>
       </c>
       <c r="B95" s="15">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C95" s="15">
         <v>3</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E95" s="16">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>32</v>
@@ -6145,7 +6154,7 @@
         <v>1</v>
       </c>
       <c r="I95" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J95" s="1">
         <v>-1</v>
@@ -6154,37 +6163,36 @@
         <v>0</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M95" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="N95" s="24">
+        <v>99</v>
+      </c>
+      <c r="N95">
         <v>1000</v>
       </c>
       <c r="O95" s="18">
         <v>1990000</v>
       </c>
-      <c r="S95" s="3"/>
     </row>
     <row r="96" s="1" customFormat="1" spans="1:19">
       <c r="A96" s="1">
-        <v>3002002</v>
+        <v>3001002</v>
       </c>
       <c r="B96" s="15">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C96" s="15">
         <v>3</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E96" s="16">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F96" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>35</v>
@@ -6202,12 +6210,12 @@
         <v>0</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M96" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="N96" s="24">
+        <v>99</v>
+      </c>
+      <c r="N96">
         <v>10000</v>
       </c>
       <c r="O96" s="18">
@@ -6217,22 +6225,22 @@
     </row>
     <row r="97" s="1" customFormat="1" spans="1:19">
       <c r="A97" s="1">
-        <v>3002003</v>
+        <v>3001003</v>
       </c>
       <c r="B97" s="15">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C97" s="15">
         <v>3</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E97" s="16">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F97" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>36</v>
@@ -6250,12 +6258,12 @@
         <v>0</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M97" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="N97" s="24">
+        <v>99</v>
+      </c>
+      <c r="N97">
         <v>100000</v>
       </c>
       <c r="O97" s="18">
@@ -6265,22 +6273,22 @@
     </row>
     <row r="98" s="1" customFormat="1" spans="1:19">
       <c r="A98" s="1">
-        <v>3004001</v>
+        <v>3002001</v>
       </c>
       <c r="B98" s="15">
-        <v>300400</v>
-      </c>
-      <c r="C98" s="1">
+        <v>300200</v>
+      </c>
+      <c r="C98" s="15">
         <v>3</v>
       </c>
       <c r="D98" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E98" s="16">
+        <v>300200006</v>
+      </c>
+      <c r="F98" s="16" t="s">
         <v>101</v>
-      </c>
-      <c r="E98" s="16">
-        <v>300400023</v>
-      </c>
-      <c r="F98" s="25" t="s">
-        <v>102</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>32</v>
@@ -6288,9 +6296,8 @@
       <c r="H98" s="1">
         <v>1</v>
       </c>
-      <c r="I98" s="26">
-        <f>N98*52</f>
-        <v>5200</v>
+      <c r="I98" s="3">
+        <v>1000</v>
       </c>
       <c r="J98" s="1">
         <v>-1</v>
@@ -6299,13 +6306,13 @@
         <v>0</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M98" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="N98" s="26">
-        <v>100</v>
+        <v>99</v>
+      </c>
+      <c r="N98" s="24">
+        <v>1000</v>
       </c>
       <c r="O98" s="18">
         <v>1990000</v>
@@ -6314,22 +6321,22 @@
     </row>
     <row r="99" s="1" customFormat="1" spans="1:19">
       <c r="A99" s="1">
-        <v>3004002</v>
+        <v>3002002</v>
       </c>
       <c r="B99" s="15">
-        <v>300400</v>
+        <v>300200</v>
       </c>
       <c r="C99" s="15">
         <v>3</v>
       </c>
       <c r="D99" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E99" s="16">
+        <v>300200006</v>
+      </c>
+      <c r="F99" s="16" t="s">
         <v>101</v>
-      </c>
-      <c r="E99" s="16">
-        <v>300400023</v>
-      </c>
-      <c r="F99" s="25" t="s">
-        <v>102</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>35</v>
@@ -6337,9 +6344,8 @@
       <c r="H99" s="1">
         <v>2</v>
       </c>
-      <c r="I99" s="26">
-        <f>N99*52</f>
-        <v>52000</v>
+      <c r="I99" s="3">
+        <v>10000</v>
       </c>
       <c r="J99" s="1">
         <v>-1</v>
@@ -6348,13 +6354,13 @@
         <v>0</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M99" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="N99" s="26">
-        <v>1000</v>
+        <v>99</v>
+      </c>
+      <c r="N99" s="24">
+        <v>10000</v>
       </c>
       <c r="O99" s="18">
         <v>1990000</v>
@@ -6363,22 +6369,22 @@
     </row>
     <row r="100" s="1" customFormat="1" spans="1:19">
       <c r="A100" s="1">
-        <v>3004003</v>
+        <v>3002003</v>
       </c>
       <c r="B100" s="15">
-        <v>300400</v>
+        <v>300200</v>
       </c>
       <c r="C100" s="15">
         <v>3</v>
       </c>
       <c r="D100" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E100" s="16">
+        <v>300200006</v>
+      </c>
+      <c r="F100" s="16" t="s">
         <v>101</v>
-      </c>
-      <c r="E100" s="16">
-        <v>300400023</v>
-      </c>
-      <c r="F100" s="25" t="s">
-        <v>102</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>36</v>
@@ -6386,9 +6392,8 @@
       <c r="H100" s="1">
         <v>3</v>
       </c>
-      <c r="I100" s="26">
-        <f>N100*52</f>
-        <v>520000</v>
+      <c r="I100" s="3">
+        <v>100000</v>
       </c>
       <c r="J100" s="1">
         <v>-1</v>
@@ -6397,13 +6402,13 @@
         <v>0</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M100" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="N100" s="26">
-        <v>10000</v>
+        <v>99</v>
+      </c>
+      <c r="N100" s="24">
+        <v>100000</v>
       </c>
       <c r="O100" s="18">
         <v>1990000</v>
@@ -6412,22 +6417,22 @@
     </row>
     <row r="101" s="1" customFormat="1" spans="1:19">
       <c r="A101" s="1">
-        <v>2012001</v>
+        <v>3004001</v>
       </c>
       <c r="B101" s="15">
-        <v>201200</v>
-      </c>
-      <c r="C101" s="15">
-        <v>2</v>
+        <v>300400</v>
+      </c>
+      <c r="C101" s="1">
+        <v>3</v>
       </c>
       <c r="D101" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E101" s="16">
+        <v>300400001</v>
+      </c>
+      <c r="F101" s="25" t="s">
         <v>104</v>
-      </c>
-      <c r="E101" s="16">
-        <v>201200001</v>
-      </c>
-      <c r="F101" s="25" t="s">
-        <v>105</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>32</v>
@@ -6435,8 +6440,9 @@
       <c r="H101" s="1">
         <v>1</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="I101" s="26">
+        <f>N101*52</f>
+        <v>5200</v>
       </c>
       <c r="J101" s="1">
         <v>-1</v>
@@ -6445,13 +6451,13 @@
         <v>0</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="M101" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="N101">
-        <v>1000</v>
+        <v>99</v>
+      </c>
+      <c r="N101" s="26">
+        <v>100</v>
       </c>
       <c r="O101" s="18">
         <v>1990000</v>
@@ -6460,22 +6466,22 @@
     </row>
     <row r="102" s="1" customFormat="1" spans="1:19">
       <c r="A102" s="1">
-        <v>2012002</v>
+        <v>3004002</v>
       </c>
       <c r="B102" s="15">
-        <v>201200</v>
+        <v>300400</v>
       </c>
       <c r="C102" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D102" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E102" s="16">
+        <v>300400001</v>
+      </c>
+      <c r="F102" s="25" t="s">
         <v>104</v>
-      </c>
-      <c r="E102" s="16">
-        <v>201200001</v>
-      </c>
-      <c r="F102" s="25" t="s">
-        <v>105</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>35</v>
@@ -6483,8 +6489,9 @@
       <c r="H102" s="1">
         <v>2</v>
       </c>
-      <c r="I102" s="3">
-        <v>10000</v>
+      <c r="I102" s="26">
+        <f>N102*52</f>
+        <v>52000</v>
       </c>
       <c r="J102" s="1">
         <v>-1</v>
@@ -6493,13 +6500,13 @@
         <v>0</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="M102" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="N102">
-        <v>10000</v>
+        <v>99</v>
+      </c>
+      <c r="N102" s="26">
+        <v>1000</v>
       </c>
       <c r="O102" s="18">
         <v>1990000</v>
@@ -6508,22 +6515,22 @@
     </row>
     <row r="103" s="1" customFormat="1" spans="1:19">
       <c r="A103" s="1">
-        <v>2012003</v>
+        <v>3004003</v>
       </c>
       <c r="B103" s="15">
-        <v>201200</v>
+        <v>300400</v>
       </c>
       <c r="C103" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D103" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E103" s="16">
+        <v>300400001</v>
+      </c>
+      <c r="F103" s="25" t="s">
         <v>104</v>
-      </c>
-      <c r="E103" s="16">
-        <v>201200001</v>
-      </c>
-      <c r="F103" s="25" t="s">
-        <v>105</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>36</v>
@@ -6531,8 +6538,9 @@
       <c r="H103" s="1">
         <v>3</v>
       </c>
-      <c r="I103" s="3">
-        <v>100000</v>
+      <c r="I103" s="26">
+        <f>N103*52</f>
+        <v>520000</v>
       </c>
       <c r="J103" s="1">
         <v>-1</v>
@@ -6541,13 +6549,13 @@
         <v>0</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="M103" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="N103">
-        <v>100000</v>
+        <v>99</v>
+      </c>
+      <c r="N103" s="26">
+        <v>10000</v>
       </c>
       <c r="O103" s="18">
         <v>1990000</v>
@@ -6556,154 +6564,154 @@
     </row>
     <row r="104" s="1" customFormat="1" spans="1:19">
       <c r="A104" s="1">
-        <v>20010010</v>
-      </c>
-      <c r="B104" s="19">
-        <v>200100</v>
-      </c>
-      <c r="C104" s="19">
+        <v>2012001</v>
+      </c>
+      <c r="B104" s="15">
+        <v>201200</v>
+      </c>
+      <c r="C104" s="15">
         <v>2</v>
       </c>
-      <c r="D104" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E104" s="19">
-        <v>200100038</v>
-      </c>
-      <c r="F104" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G104" s="20" t="s">
+      <c r="D104" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="H104" s="20">
-        <v>10</v>
-      </c>
-      <c r="I104" s="27">
-        <v>0</v>
-      </c>
-      <c r="J104" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K104" s="20">
-        <v>0</v>
-      </c>
-      <c r="L104" s="28" t="s">
+      <c r="E104" s="16">
+        <v>201200001</v>
+      </c>
+      <c r="F104" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="M104" s="20">
-        <v>0</v>
+      <c r="G104" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H104" s="1">
+        <v>1</v>
+      </c>
+      <c r="I104" s="3">
+        <v>0</v>
+      </c>
+      <c r="J104" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K104" s="1">
+        <v>0</v>
+      </c>
+      <c r="L104" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M104" s="31" t="s">
+        <v>87</v>
       </c>
       <c r="N104">
         <v>1000</v>
       </c>
-      <c r="O104" s="29">
-        <v>1980000</v>
+      <c r="O104" s="18">
+        <v>1990000</v>
       </c>
       <c r="S104" s="3"/>
     </row>
     <row r="105" s="1" customFormat="1" spans="1:19">
       <c r="A105" s="1">
-        <v>20010011</v>
-      </c>
-      <c r="B105" s="19">
-        <v>200100</v>
-      </c>
-      <c r="C105" s="19">
+        <v>2012002</v>
+      </c>
+      <c r="B105" s="15">
+        <v>201200</v>
+      </c>
+      <c r="C105" s="15">
         <v>2</v>
       </c>
-      <c r="D105" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E105" s="19">
-        <v>200100038</v>
-      </c>
-      <c r="F105" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G105" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="H105" s="20">
-        <v>11</v>
-      </c>
-      <c r="I105" s="27">
-        <v>0</v>
-      </c>
-      <c r="J105" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K105" s="20">
-        <v>0</v>
-      </c>
-      <c r="L105" s="28" t="s">
+      <c r="D105" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E105" s="16">
+        <v>201200001</v>
+      </c>
+      <c r="F105" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="M105" s="20">
-        <v>0</v>
+      <c r="G105" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H105" s="1">
+        <v>2</v>
+      </c>
+      <c r="I105" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J105" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K105" s="1">
+        <v>0</v>
+      </c>
+      <c r="L105" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M105" s="31" t="s">
+        <v>87</v>
       </c>
       <c r="N105">
         <v>10000</v>
       </c>
-      <c r="O105" s="29">
-        <v>1980000</v>
+      <c r="O105" s="18">
+        <v>1990000</v>
       </c>
       <c r="S105" s="3"/>
     </row>
     <row r="106" s="1" customFormat="1" spans="1:19">
       <c r="A106" s="1">
-        <v>20010012</v>
-      </c>
-      <c r="B106" s="19">
-        <v>200100</v>
-      </c>
-      <c r="C106" s="19">
+        <v>2012003</v>
+      </c>
+      <c r="B106" s="15">
+        <v>201200</v>
+      </c>
+      <c r="C106" s="15">
         <v>2</v>
       </c>
-      <c r="D106" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E106" s="19">
-        <v>200100038</v>
-      </c>
-      <c r="F106" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G106" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="H106" s="20">
-        <v>12</v>
-      </c>
-      <c r="I106" s="27">
-        <v>0</v>
-      </c>
-      <c r="J106" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K106" s="20">
-        <v>0</v>
-      </c>
-      <c r="L106" s="28" t="s">
+      <c r="D106" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E106" s="16">
+        <v>201200001</v>
+      </c>
+      <c r="F106" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="M106" s="20">
-        <v>0</v>
+      <c r="G106" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H106" s="1">
+        <v>3</v>
+      </c>
+      <c r="I106" s="3">
+        <v>100000</v>
+      </c>
+      <c r="J106" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K106" s="1">
+        <v>0</v>
+      </c>
+      <c r="L106" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M106" s="31" t="s">
+        <v>87</v>
       </c>
       <c r="N106">
         <v>100000</v>
       </c>
-      <c r="O106" s="29">
-        <v>1980000</v>
+      <c r="O106" s="18">
+        <v>1990000</v>
       </c>
       <c r="S106" s="3"/>
     </row>
     <row r="107" s="1" customFormat="1" spans="1:19">
       <c r="A107" s="1">
-        <v>20010110</v>
+        <v>20010010</v>
       </c>
       <c r="B107" s="19">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C107" s="19">
         <v>2</v>
@@ -6712,13 +6720,13 @@
         <v>77</v>
       </c>
       <c r="E107" s="19">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F107" s="19" t="s">
         <v>78</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H107" s="20">
         <v>10</v>
@@ -6733,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="L107" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M107" s="20">
         <v>0</v>
@@ -6748,10 +6756,10 @@
     </row>
     <row r="108" s="1" customFormat="1" spans="1:19">
       <c r="A108" s="1">
-        <v>20010111</v>
+        <v>20010011</v>
       </c>
       <c r="B108" s="19">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C108" s="19">
         <v>2</v>
@@ -6760,13 +6768,13 @@
         <v>77</v>
       </c>
       <c r="E108" s="19">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F108" s="19" t="s">
         <v>78</v>
       </c>
       <c r="G108" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H108" s="20">
         <v>11</v>
@@ -6781,7 +6789,7 @@
         <v>0</v>
       </c>
       <c r="L108" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M108" s="20">
         <v>0</v>
@@ -6796,10 +6804,10 @@
     </row>
     <row r="109" s="1" customFormat="1" spans="1:19">
       <c r="A109" s="1">
-        <v>20010112</v>
+        <v>20010012</v>
       </c>
       <c r="B109" s="19">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C109" s="19">
         <v>2</v>
@@ -6808,13 +6816,13 @@
         <v>77</v>
       </c>
       <c r="E109" s="19">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F109" s="19" t="s">
         <v>78</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H109" s="20">
         <v>12</v>
@@ -6829,7 +6837,7 @@
         <v>0</v>
       </c>
       <c r="L109" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M109" s="20">
         <v>0</v>
@@ -6844,10 +6852,10 @@
     </row>
     <row r="110" s="1" customFormat="1" spans="1:19">
       <c r="A110" s="1">
-        <v>20030010</v>
+        <v>20010110</v>
       </c>
       <c r="B110" s="19">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C110" s="19">
         <v>2</v>
@@ -6856,13 +6864,13 @@
         <v>79</v>
       </c>
       <c r="E110" s="19">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F110" s="19" t="s">
         <v>80</v>
       </c>
       <c r="G110" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H110" s="20">
         <v>10</v>
@@ -6877,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="L110" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M110" s="20">
         <v>0</v>
@@ -6892,10 +6900,10 @@
     </row>
     <row r="111" s="1" customFormat="1" spans="1:19">
       <c r="A111" s="1">
-        <v>20030011</v>
+        <v>20010111</v>
       </c>
       <c r="B111" s="19">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C111" s="19">
         <v>2</v>
@@ -6904,13 +6912,13 @@
         <v>79</v>
       </c>
       <c r="E111" s="19">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F111" s="19" t="s">
         <v>80</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H111" s="20">
         <v>11</v>
@@ -6925,7 +6933,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M111" s="20">
         <v>0</v>
@@ -6940,10 +6948,10 @@
     </row>
     <row r="112" s="1" customFormat="1" spans="1:19">
       <c r="A112" s="1">
-        <v>20030012</v>
+        <v>20010112</v>
       </c>
       <c r="B112" s="19">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C112" s="19">
         <v>2</v>
@@ -6952,13 +6960,13 @@
         <v>79</v>
       </c>
       <c r="E112" s="19">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F112" s="19" t="s">
         <v>80</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H112" s="20">
         <v>12</v>
@@ -6973,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M112" s="20">
         <v>0</v>
@@ -6988,25 +6996,25 @@
     </row>
     <row r="113" s="1" customFormat="1" spans="1:19">
       <c r="A113" s="1">
-        <v>20040010</v>
+        <v>20030010</v>
       </c>
       <c r="B113" s="19">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C113" s="19">
         <v>2</v>
       </c>
-      <c r="D113" s="30" t="s">
+      <c r="D113" s="19" t="s">
         <v>81</v>
       </c>
       <c r="E113" s="19">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F113" s="19" t="s">
         <v>82</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H113" s="20">
         <v>10</v>
@@ -7021,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="L113" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M113" s="20">
         <v>0</v>
@@ -7036,25 +7044,25 @@
     </row>
     <row r="114" s="1" customFormat="1" spans="1:19">
       <c r="A114" s="1">
-        <v>20040011</v>
+        <v>20030011</v>
       </c>
       <c r="B114" s="19">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C114" s="19">
         <v>2</v>
       </c>
-      <c r="D114" s="30" t="s">
+      <c r="D114" s="19" t="s">
         <v>81</v>
       </c>
       <c r="E114" s="19">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F114" s="19" t="s">
         <v>82</v>
       </c>
       <c r="G114" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H114" s="20">
         <v>11</v>
@@ -7069,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="L114" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M114" s="20">
         <v>0</v>
@@ -7084,25 +7092,25 @@
     </row>
     <row r="115" s="1" customFormat="1" spans="1:19">
       <c r="A115" s="1">
-        <v>20040012</v>
+        <v>20030012</v>
       </c>
       <c r="B115" s="19">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C115" s="19">
         <v>2</v>
       </c>
-      <c r="D115" s="30" t="s">
+      <c r="D115" s="19" t="s">
         <v>81</v>
       </c>
       <c r="E115" s="19">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F115" s="19" t="s">
         <v>82</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H115" s="20">
         <v>12</v>
@@ -7117,7 +7125,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M115" s="20">
         <v>0</v>
@@ -7132,25 +7140,25 @@
     </row>
     <row r="116" s="1" customFormat="1" spans="1:19">
       <c r="A116" s="1">
-        <v>20050010</v>
+        <v>20040010</v>
       </c>
       <c r="B116" s="19">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C116" s="19">
         <v>2</v>
       </c>
-      <c r="D116" s="19" t="s">
+      <c r="D116" s="30" t="s">
         <v>83</v>
       </c>
       <c r="E116" s="19">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F116" s="19" t="s">
         <v>84</v>
       </c>
       <c r="G116" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H116" s="20">
         <v>10</v>
@@ -7165,7 +7173,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M116" s="20">
         <v>0</v>
@@ -7180,25 +7188,25 @@
     </row>
     <row r="117" s="1" customFormat="1" spans="1:19">
       <c r="A117" s="1">
-        <v>20050011</v>
+        <v>20040011</v>
       </c>
       <c r="B117" s="19">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C117" s="19">
         <v>2</v>
       </c>
-      <c r="D117" s="19" t="s">
+      <c r="D117" s="30" t="s">
         <v>83</v>
       </c>
       <c r="E117" s="19">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F117" s="19" t="s">
         <v>84</v>
       </c>
       <c r="G117" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H117" s="20">
         <v>11</v>
@@ -7213,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="L117" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M117" s="20">
         <v>0</v>
@@ -7228,25 +7236,25 @@
     </row>
     <row r="118" s="1" customFormat="1" spans="1:19">
       <c r="A118" s="1">
-        <v>20050012</v>
+        <v>20040012</v>
       </c>
       <c r="B118" s="19">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C118" s="19">
         <v>2</v>
       </c>
-      <c r="D118" s="19" t="s">
+      <c r="D118" s="30" t="s">
         <v>83</v>
       </c>
       <c r="E118" s="19">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F118" s="19" t="s">
         <v>84</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H118" s="20">
         <v>12</v>
@@ -7261,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="L118" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M118" s="20">
         <v>0</v>
@@ -7274,27 +7282,27 @@
       </c>
       <c r="S118" s="3"/>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" s="1" customFormat="1" spans="1:19">
       <c r="A119" s="1">
-        <v>20060010</v>
+        <v>20050010</v>
       </c>
       <c r="B119" s="19">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C119" s="19">
         <v>2</v>
       </c>
       <c r="D119" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E119" s="19">
+        <v>200500025</v>
+      </c>
+      <c r="F119" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="E119" s="19">
-        <v>200600001</v>
-      </c>
-      <c r="F119" s="19" t="s">
-        <v>87</v>
-      </c>
       <c r="G119" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H119" s="20">
         <v>10</v>
@@ -7309,7 +7317,7 @@
         <v>0</v>
       </c>
       <c r="L119" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M119" s="20">
         <v>0</v>
@@ -7320,28 +7328,29 @@
       <c r="O119" s="29">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="120" spans="1:19">
+      <c r="S119" s="3"/>
+    </row>
+    <row r="120" s="1" customFormat="1" spans="1:19">
       <c r="A120" s="1">
-        <v>20060011</v>
+        <v>20050011</v>
       </c>
       <c r="B120" s="19">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C120" s="19">
         <v>2</v>
       </c>
       <c r="D120" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E120" s="19">
+        <v>200500025</v>
+      </c>
+      <c r="F120" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="E120" s="19">
-        <v>200600001</v>
-      </c>
-      <c r="F120" s="19" t="s">
-        <v>87</v>
-      </c>
       <c r="G120" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H120" s="20">
         <v>11</v>
@@ -7356,7 +7365,7 @@
         <v>0</v>
       </c>
       <c r="L120" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M120" s="20">
         <v>0</v>
@@ -7367,28 +7376,29 @@
       <c r="O120" s="29">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="121" spans="1:19">
+      <c r="S120" s="3"/>
+    </row>
+    <row r="121" s="1" customFormat="1" spans="1:19">
       <c r="A121" s="1">
-        <v>20060012</v>
+        <v>20050012</v>
       </c>
       <c r="B121" s="19">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C121" s="19">
         <v>2</v>
       </c>
       <c r="D121" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E121" s="19">
+        <v>200500025</v>
+      </c>
+      <c r="F121" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="E121" s="19">
-        <v>200600001</v>
-      </c>
-      <c r="F121" s="19" t="s">
-        <v>87</v>
-      </c>
       <c r="G121" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H121" s="20">
         <v>12</v>
@@ -7403,7 +7413,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M121" s="20">
         <v>0</v>
@@ -7414,13 +7424,14 @@
       <c r="O121" s="29">
         <v>1980000</v>
       </c>
+      <c r="S121" s="3"/>
     </row>
     <row r="122" spans="1:19">
       <c r="A122" s="1">
-        <v>20070010</v>
+        <v>20060010</v>
       </c>
       <c r="B122" s="19">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C122" s="19">
         <v>2</v>
@@ -7429,13 +7440,13 @@
         <v>88</v>
       </c>
       <c r="E122" s="19">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F122" s="19" t="s">
         <v>89</v>
       </c>
       <c r="G122" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H122" s="20">
         <v>10</v>
@@ -7450,7 +7461,7 @@
         <v>0</v>
       </c>
       <c r="L122" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M122" s="20">
         <v>0</v>
@@ -7464,10 +7475,10 @@
     </row>
     <row r="123" spans="1:19">
       <c r="A123" s="1">
-        <v>20070011</v>
+        <v>20060011</v>
       </c>
       <c r="B123" s="19">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C123" s="19">
         <v>2</v>
@@ -7476,13 +7487,13 @@
         <v>88</v>
       </c>
       <c r="E123" s="19">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F123" s="19" t="s">
         <v>89</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H123" s="20">
         <v>11</v>
@@ -7497,7 +7508,7 @@
         <v>0</v>
       </c>
       <c r="L123" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M123" s="20">
         <v>0</v>
@@ -7511,10 +7522,10 @@
     </row>
     <row r="124" spans="1:19">
       <c r="A124" s="1">
-        <v>20070012</v>
+        <v>20060012</v>
       </c>
       <c r="B124" s="19">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C124" s="19">
         <v>2</v>
@@ -7523,13 +7534,13 @@
         <v>88</v>
       </c>
       <c r="E124" s="19">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F124" s="19" t="s">
         <v>89</v>
       </c>
       <c r="G124" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H124" s="20">
         <v>12</v>
@@ -7544,7 +7555,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M124" s="20">
         <v>0</v>
@@ -7558,10 +7569,10 @@
     </row>
     <row r="125" spans="1:19">
       <c r="A125" s="1">
-        <v>20080010</v>
+        <v>20070010</v>
       </c>
       <c r="B125" s="19">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C125" s="19">
         <v>2</v>
@@ -7570,13 +7581,13 @@
         <v>90</v>
       </c>
       <c r="E125" s="19">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F125" s="19" t="s">
         <v>91</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H125" s="20">
         <v>10</v>
@@ -7591,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M125" s="20">
         <v>0</v>
@@ -7605,10 +7616,10 @@
     </row>
     <row r="126" spans="1:19">
       <c r="A126" s="1">
-        <v>20080011</v>
+        <v>20070011</v>
       </c>
       <c r="B126" s="19">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C126" s="19">
         <v>2</v>
@@ -7617,13 +7628,13 @@
         <v>90</v>
       </c>
       <c r="E126" s="19">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F126" s="19" t="s">
         <v>91</v>
       </c>
       <c r="G126" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H126" s="20">
         <v>11</v>
@@ -7638,7 +7649,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M126" s="20">
         <v>0</v>
@@ -7652,10 +7663,10 @@
     </row>
     <row r="127" spans="1:19">
       <c r="A127" s="1">
-        <v>20080012</v>
+        <v>20070012</v>
       </c>
       <c r="B127" s="19">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C127" s="19">
         <v>2</v>
@@ -7664,13 +7675,13 @@
         <v>90</v>
       </c>
       <c r="E127" s="19">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F127" s="19" t="s">
         <v>91</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H127" s="20">
         <v>12</v>
@@ -7685,7 +7696,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M127" s="20">
         <v>0</v>
@@ -7699,10 +7710,10 @@
     </row>
     <row r="128" spans="1:19">
       <c r="A128" s="1">
-        <v>20090010</v>
+        <v>20080010</v>
       </c>
       <c r="B128" s="19">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C128" s="19">
         <v>2</v>
@@ -7711,13 +7722,13 @@
         <v>92</v>
       </c>
       <c r="E128" s="19">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F128" s="19" t="s">
         <v>93</v>
       </c>
       <c r="G128" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H128" s="20">
         <v>10</v>
@@ -7732,7 +7743,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M128" s="20">
         <v>0</v>
@@ -7746,10 +7757,10 @@
     </row>
     <row r="129" spans="1:19">
       <c r="A129" s="1">
-        <v>20090011</v>
+        <v>20080011</v>
       </c>
       <c r="B129" s="19">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C129" s="19">
         <v>2</v>
@@ -7758,13 +7769,13 @@
         <v>92</v>
       </c>
       <c r="E129" s="19">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F129" s="19" t="s">
         <v>93</v>
       </c>
       <c r="G129" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H129" s="20">
         <v>11</v>
@@ -7779,7 +7790,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M129" s="20">
         <v>0</v>
@@ -7793,10 +7804,10 @@
     </row>
     <row r="130" spans="1:19">
       <c r="A130" s="1">
-        <v>20090012</v>
+        <v>20080012</v>
       </c>
       <c r="B130" s="19">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C130" s="19">
         <v>2</v>
@@ -7805,13 +7816,13 @@
         <v>92</v>
       </c>
       <c r="E130" s="19">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F130" s="19" t="s">
         <v>93</v>
       </c>
       <c r="G130" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H130" s="20">
         <v>12</v>
@@ -7826,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M130" s="20">
         <v>0</v>
@@ -7838,27 +7849,27 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="131" s="1" customFormat="1" spans="1:19">
+    <row r="131" spans="1:19">
       <c r="A131" s="1">
-        <v>30020010</v>
+        <v>20090010</v>
       </c>
       <c r="B131" s="19">
-        <v>300200</v>
+        <v>200900</v>
       </c>
       <c r="C131" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D131" s="19" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E131" s="19">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F131" s="19" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G131" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H131" s="20">
         <v>10</v>
@@ -7872,41 +7883,40 @@
       <c r="K131" s="20">
         <v>0</v>
       </c>
-      <c r="L131" s="4" t="s">
-        <v>110</v>
+      <c r="L131" s="28" t="s">
+        <v>109</v>
       </c>
       <c r="M131" s="20">
         <v>0</v>
       </c>
-      <c r="N131" s="24">
+      <c r="N131">
         <v>1000</v>
       </c>
       <c r="O131" s="29">
         <v>1980000</v>
       </c>
-      <c r="S131" s="3"/>
-    </row>
-    <row r="132" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="132" spans="1:19">
       <c r="A132" s="1">
-        <v>30020011</v>
+        <v>20090011</v>
       </c>
       <c r="B132" s="19">
-        <v>300200</v>
+        <v>200900</v>
       </c>
       <c r="C132" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D132" s="19" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E132" s="19">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F132" s="19" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G132" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H132" s="20">
         <v>11</v>
@@ -7920,41 +7930,40 @@
       <c r="K132" s="20">
         <v>0</v>
       </c>
-      <c r="L132" s="4" t="s">
-        <v>110</v>
+      <c r="L132" s="28" t="s">
+        <v>109</v>
       </c>
       <c r="M132" s="20">
         <v>0</v>
       </c>
-      <c r="N132" s="24">
+      <c r="N132">
         <v>10000</v>
       </c>
       <c r="O132" s="29">
         <v>1980000</v>
       </c>
-      <c r="S132" s="3"/>
-    </row>
-    <row r="133" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="133" spans="1:19">
       <c r="A133" s="1">
-        <v>30020012</v>
+        <v>20090012</v>
       </c>
       <c r="B133" s="19">
-        <v>300200</v>
+        <v>200900</v>
       </c>
       <c r="C133" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E133" s="19">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F133" s="19" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G133" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H133" s="20">
         <v>12</v>
@@ -7968,41 +7977,40 @@
       <c r="K133" s="20">
         <v>0</v>
       </c>
-      <c r="L133" s="4" t="s">
-        <v>110</v>
+      <c r="L133" s="28" t="s">
+        <v>109</v>
       </c>
       <c r="M133" s="20">
         <v>0</v>
       </c>
-      <c r="N133" s="24">
+      <c r="N133">
         <v>100000</v>
       </c>
       <c r="O133" s="29">
         <v>1980000</v>
       </c>
-      <c r="S133" s="3"/>
-    </row>
-    <row r="134" customFormat="1" spans="1:19">
+    </row>
+    <row r="134" s="1" customFormat="1" spans="1:19">
       <c r="A134" s="1">
-        <v>30040010</v>
-      </c>
-      <c r="B134" s="15">
-        <v>300400</v>
+        <v>30020010</v>
+      </c>
+      <c r="B134" s="19">
+        <v>300200</v>
       </c>
       <c r="C134" s="19">
         <v>3</v>
       </c>
-      <c r="D134" s="15" t="s">
+      <c r="D134" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E134" s="19">
+        <v>300200006</v>
+      </c>
+      <c r="F134" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E134" s="16">
-        <v>300400023</v>
-      </c>
-      <c r="F134" s="25" t="s">
-        <v>102</v>
-      </c>
       <c r="G134" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H134" s="20">
         <v>10</v>
@@ -8017,40 +8025,40 @@
         <v>0</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M134" s="20">
         <v>0</v>
       </c>
-      <c r="N134" s="26">
-        <v>100</v>
+      <c r="N134" s="24">
+        <v>1000</v>
       </c>
       <c r="O134" s="29">
         <v>1980000</v>
       </c>
       <c r="S134" s="3"/>
     </row>
-    <row r="135" customFormat="1" spans="1:19">
+    <row r="135" s="1" customFormat="1" spans="1:19">
       <c r="A135" s="1">
-        <v>30040011</v>
-      </c>
-      <c r="B135" s="15">
-        <v>300400</v>
+        <v>30020011</v>
+      </c>
+      <c r="B135" s="19">
+        <v>300200</v>
       </c>
       <c r="C135" s="19">
         <v>3</v>
       </c>
-      <c r="D135" s="15" t="s">
+      <c r="D135" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E135" s="19">
+        <v>300200006</v>
+      </c>
+      <c r="F135" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E135" s="16">
-        <v>300400023</v>
-      </c>
-      <c r="F135" s="25" t="s">
-        <v>102</v>
-      </c>
       <c r="G135" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H135" s="20">
         <v>11</v>
@@ -8065,40 +8073,40 @@
         <v>0</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M135" s="20">
         <v>0</v>
       </c>
-      <c r="N135" s="26">
-        <v>1000</v>
+      <c r="N135" s="24">
+        <v>10000</v>
       </c>
       <c r="O135" s="29">
         <v>1980000</v>
       </c>
       <c r="S135" s="3"/>
     </row>
-    <row r="136" customFormat="1" spans="1:19">
+    <row r="136" s="1" customFormat="1" spans="1:19">
       <c r="A136" s="1">
-        <v>30040012</v>
-      </c>
-      <c r="B136" s="15">
-        <v>300400</v>
+        <v>30020012</v>
+      </c>
+      <c r="B136" s="19">
+        <v>300200</v>
       </c>
       <c r="C136" s="19">
         <v>3</v>
       </c>
-      <c r="D136" s="15" t="s">
+      <c r="D136" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E136" s="19">
+        <v>300200006</v>
+      </c>
+      <c r="F136" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E136" s="16">
-        <v>300400023</v>
-      </c>
-      <c r="F136" s="25" t="s">
-        <v>102</v>
-      </c>
       <c r="G136" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H136" s="20">
         <v>12</v>
@@ -8113,13 +8121,13 @@
         <v>0</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M136" s="20">
         <v>0</v>
       </c>
-      <c r="N136" s="26">
-        <v>10000</v>
+      <c r="N136" s="24">
+        <v>100000</v>
       </c>
       <c r="O136" s="29">
         <v>1980000</v>
@@ -8128,25 +8136,25 @@
     </row>
     <row r="137" customFormat="1" spans="1:19">
       <c r="A137" s="1">
-        <v>20120010</v>
+        <v>30040010</v>
       </c>
       <c r="B137" s="15">
-        <v>201200</v>
+        <v>300400</v>
       </c>
       <c r="C137" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D137" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E137" s="16">
+        <v>300400001</v>
+      </c>
+      <c r="F137" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="E137" s="16">
-        <v>201200001</v>
-      </c>
-      <c r="F137" s="25" t="s">
-        <v>105</v>
-      </c>
       <c r="G137" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H137" s="20">
         <v>10</v>
@@ -8160,14 +8168,14 @@
       <c r="K137" s="20">
         <v>0</v>
       </c>
-      <c r="L137" s="28" t="s">
-        <v>107</v>
+      <c r="L137" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="M137" s="20">
         <v>0</v>
       </c>
-      <c r="N137">
-        <v>1000</v>
+      <c r="N137" s="26">
+        <v>100</v>
       </c>
       <c r="O137" s="29">
         <v>1980000</v>
@@ -8176,25 +8184,25 @@
     </row>
     <row r="138" customFormat="1" spans="1:19">
       <c r="A138" s="1">
-        <v>20120011</v>
+        <v>30040011</v>
       </c>
       <c r="B138" s="15">
-        <v>201200</v>
+        <v>300400</v>
       </c>
       <c r="C138" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D138" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E138" s="16">
+        <v>300400001</v>
+      </c>
+      <c r="F138" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="E138" s="16">
-        <v>201200001</v>
-      </c>
-      <c r="F138" s="25" t="s">
-        <v>105</v>
-      </c>
       <c r="G138" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H138" s="20">
         <v>11</v>
@@ -8208,14 +8216,14 @@
       <c r="K138" s="20">
         <v>0</v>
       </c>
-      <c r="L138" s="28" t="s">
-        <v>107</v>
+      <c r="L138" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="M138" s="20">
         <v>0</v>
       </c>
-      <c r="N138">
-        <v>10000</v>
+      <c r="N138" s="26">
+        <v>1000</v>
       </c>
       <c r="O138" s="29">
         <v>1980000</v>
@@ -8224,25 +8232,25 @@
     </row>
     <row r="139" customFormat="1" spans="1:19">
       <c r="A139" s="1">
-        <v>20120012</v>
+        <v>30040012</v>
       </c>
       <c r="B139" s="15">
-        <v>201200</v>
+        <v>300400</v>
       </c>
       <c r="C139" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D139" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E139" s="16">
+        <v>300400001</v>
+      </c>
+      <c r="F139" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="E139" s="16">
-        <v>201200001</v>
-      </c>
-      <c r="F139" s="25" t="s">
-        <v>105</v>
-      </c>
       <c r="G139" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H139" s="20">
         <v>12</v>
@@ -8256,42 +8264,41 @@
       <c r="K139" s="20">
         <v>0</v>
       </c>
-      <c r="L139" s="28" t="s">
-        <v>107</v>
+      <c r="L139" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="M139" s="20">
         <v>0</v>
       </c>
-      <c r="N139">
-        <v>100000</v>
+      <c r="N139" s="26">
+        <v>10000</v>
       </c>
       <c r="O139" s="29">
         <v>1980000</v>
       </c>
       <c r="S139" s="3"/>
     </row>
-    <row r="140" spans="1:19">
+    <row r="140" customFormat="1" spans="1:19">
       <c r="A140" s="1">
-        <f>B140*100+H140</f>
-        <v>10010010</v>
-      </c>
-      <c r="B140" s="19">
-        <v>100100</v>
+        <v>20120010</v>
+      </c>
+      <c r="B140" s="15">
+        <v>201200</v>
       </c>
       <c r="C140" s="19">
-        <v>1</v>
-      </c>
-      <c r="D140" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E140" s="19">
-        <v>100100026</v>
-      </c>
-      <c r="F140" s="19" t="s">
-        <v>31</v>
+        <v>2</v>
+      </c>
+      <c r="D140" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E140" s="16">
+        <v>201200001</v>
+      </c>
+      <c r="F140" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="G140" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H140" s="20">
         <v>10</v>
@@ -8306,7 +8313,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M140" s="20">
         <v>0</v>
@@ -8317,30 +8324,29 @@
       <c r="O140" s="29">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="141" spans="1:19">
+      <c r="S140" s="3"/>
+    </row>
+    <row r="141" customFormat="1" spans="1:19">
       <c r="A141" s="1">
-        <f>B141*100+H141</f>
-        <v>10010011</v>
-      </c>
-      <c r="B141" s="19">
-        <v>100100</v>
+        <v>20120011</v>
+      </c>
+      <c r="B141" s="15">
+        <v>201200</v>
       </c>
       <c r="C141" s="19">
-        <v>1</v>
-      </c>
-      <c r="D141" s="19" t="str">
-        <f t="shared" ref="D141:D145" si="1">D140</f>
-        <v>金礦大亨</v>
-      </c>
-      <c r="E141" s="19">
-        <v>100100026</v>
-      </c>
-      <c r="F141" s="19" t="s">
-        <v>31</v>
+        <v>2</v>
+      </c>
+      <c r="D141" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E141" s="16">
+        <v>201200001</v>
+      </c>
+      <c r="F141" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="G141" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H141" s="20">
         <v>11</v>
@@ -8355,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M141" s="20">
         <v>0</v>
@@ -8366,178 +8372,176 @@
       <c r="O141" s="29">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="142" spans="1:19">
+      <c r="S141" s="3"/>
+    </row>
+    <row r="142" customFormat="1" spans="1:19">
       <c r="A142" s="1">
-        <f>B142*100+H142</f>
+        <v>20120012</v>
+      </c>
+      <c r="B142" s="15">
+        <v>201200</v>
+      </c>
+      <c r="C142" s="19">
+        <v>2</v>
+      </c>
+      <c r="D142" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E142" s="16">
+        <v>201200001</v>
+      </c>
+      <c r="F142" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="G142" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H142" s="20">
+        <v>12</v>
+      </c>
+      <c r="I142" s="27">
+        <v>0</v>
+      </c>
+      <c r="J142" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K142" s="20">
+        <v>0</v>
+      </c>
+      <c r="L142" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="M142" s="20">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>100000</v>
+      </c>
+      <c r="O142" s="29">
+        <v>1980000</v>
+      </c>
+      <c r="S142" s="3"/>
+    </row>
+    <row r="143" spans="1:19">
+      <c r="A143" s="1">
+        <f>B143*100+H143</f>
+        <v>10010010</v>
+      </c>
+      <c r="B143" s="19">
+        <v>100100</v>
+      </c>
+      <c r="C143" s="19">
+        <v>1</v>
+      </c>
+      <c r="D143" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E143" s="19">
+        <v>100100026</v>
+      </c>
+      <c r="F143" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G143" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H143" s="20">
+        <v>10</v>
+      </c>
+      <c r="I143" s="27">
+        <v>0</v>
+      </c>
+      <c r="J143" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K143" s="20">
+        <v>0</v>
+      </c>
+      <c r="L143" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="M143" s="20">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>1000</v>
+      </c>
+      <c r="O143" s="29">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19">
+      <c r="A144" s="1">
+        <f>B144*100+H144</f>
+        <v>10010011</v>
+      </c>
+      <c r="B144" s="19">
+        <v>100100</v>
+      </c>
+      <c r="C144" s="19">
+        <v>1</v>
+      </c>
+      <c r="D144" s="19" t="str">
+        <f t="shared" ref="D144:D148" si="1">D143</f>
+        <v>金礦大亨</v>
+      </c>
+      <c r="E144" s="19">
+        <v>100100026</v>
+      </c>
+      <c r="F144" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G144" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="H144" s="20">
+        <v>11</v>
+      </c>
+      <c r="I144" s="27">
+        <v>0</v>
+      </c>
+      <c r="J144" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K144" s="20">
+        <v>0</v>
+      </c>
+      <c r="L144" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="M144" s="20">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>10000</v>
+      </c>
+      <c r="O144" s="29">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
+      <c r="A145" s="1">
+        <f>B145*100+H145</f>
         <v>10010012</v>
       </c>
-      <c r="B142" s="19">
+      <c r="B145" s="19">
         <v>100100</v>
       </c>
-      <c r="C142" s="19">
-        <v>1</v>
-      </c>
-      <c r="D142" s="19" t="str">
+      <c r="C145" s="19">
+        <v>1</v>
+      </c>
+      <c r="D145" s="19" t="str">
         <f t="shared" si="1"/>
         <v>金礦大亨</v>
       </c>
-      <c r="E142" s="19">
+      <c r="E145" s="19">
         <v>100100026</v>
       </c>
-      <c r="F142" s="19" t="s">
+      <c r="F145" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="G142" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="H142" s="20">
-        <v>12</v>
-      </c>
-      <c r="I142" s="27">
-        <v>0</v>
-      </c>
-      <c r="J142" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K142" s="20">
-        <v>0</v>
-      </c>
-      <c r="L142" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="M142" s="20">
-        <v>0</v>
-      </c>
-      <c r="N142">
-        <v>100000</v>
-      </c>
-      <c r="O142" s="29">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="143" spans="1:19">
-      <c r="A143" s="1">
-        <f t="shared" ref="A143:A193" si="2">B143*100+H143</f>
-        <v>10030010</v>
-      </c>
-      <c r="B143" s="19">
-        <v>100300</v>
-      </c>
-      <c r="C143" s="19">
-        <v>1</v>
-      </c>
-      <c r="D143" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="E143" s="19">
-        <v>100300001</v>
-      </c>
-      <c r="F143" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G143" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="H143" s="20">
-        <v>10</v>
-      </c>
-      <c r="I143" s="27">
-        <v>0</v>
-      </c>
-      <c r="J143" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K143" s="20">
-        <v>0</v>
-      </c>
-      <c r="L143" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="M143" s="20">
-        <v>0</v>
-      </c>
-      <c r="N143">
-        <v>1000</v>
-      </c>
-      <c r="O143" s="29">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="144" spans="1:19">
-      <c r="A144" s="1">
-        <f t="shared" si="2"/>
-        <v>10030011</v>
-      </c>
-      <c r="B144" s="19">
-        <v>100300</v>
-      </c>
-      <c r="C144" s="19">
-        <v>1</v>
-      </c>
-      <c r="D144" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>超级明星</v>
-      </c>
-      <c r="E144" s="19">
-        <v>100300001</v>
-      </c>
-      <c r="F144" s="19" t="str">
-        <f t="shared" ref="F144:F148" si="3">F143</f>
-        <v>SuperStar</v>
-      </c>
-      <c r="G144" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="H144" s="20">
-        <v>11</v>
-      </c>
-      <c r="I144" s="27">
-        <v>0</v>
-      </c>
-      <c r="J144" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K144" s="20">
-        <v>0</v>
-      </c>
-      <c r="L144" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="M144" s="20">
-        <v>0</v>
-      </c>
-      <c r="N144">
-        <v>10000</v>
-      </c>
-      <c r="O144" s="29">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15">
-      <c r="A145" s="1">
-        <f t="shared" si="2"/>
-        <v>10030012</v>
-      </c>
-      <c r="B145" s="19">
-        <v>100300</v>
-      </c>
-      <c r="C145" s="19">
-        <v>1</v>
-      </c>
-      <c r="D145" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v>超级明星</v>
-      </c>
-      <c r="E145" s="19">
-        <v>100300001</v>
-      </c>
-      <c r="F145" s="19" t="str">
-        <f t="shared" si="3"/>
-        <v>SuperStar</v>
-      </c>
       <c r="G145" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H145" s="20">
         <v>12</v>
@@ -8552,7 +8556,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M145" s="20">
         <v>0</v>
@@ -8566,26 +8570,26 @@
     </row>
     <row r="146" spans="1:15">
       <c r="A146" s="1">
-        <f t="shared" si="2"/>
-        <v>10070010</v>
+        <f t="shared" ref="A146:A196" si="2">B146*100+H146</f>
+        <v>10030010</v>
       </c>
       <c r="B146" s="19">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C146" s="19">
         <v>1</v>
       </c>
       <c r="D146" s="19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E146" s="19">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="F146" s="19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G146" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H146" s="20">
         <v>10</v>
@@ -8600,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M146" s="20">
         <v>0</v>
@@ -8615,27 +8619,27 @@
     <row r="147" spans="1:15">
       <c r="A147" s="1">
         <f t="shared" si="2"/>
-        <v>10070011</v>
+        <v>10030011</v>
       </c>
       <c r="B147" s="19">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C147" s="19">
         <v>1</v>
       </c>
       <c r="D147" s="19" t="str">
-        <f t="shared" ref="D147:D151" si="4">D146</f>
-        <v>麻将胡了</v>
+        <f t="shared" si="1"/>
+        <v>超级明星</v>
       </c>
       <c r="E147" s="19">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="F147" s="19" t="str">
-        <f t="shared" si="3"/>
-        <v>MahjongWays</v>
+        <f t="shared" ref="F147:F151" si="3">F146</f>
+        <v>SuperStar</v>
       </c>
       <c r="G147" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H147" s="20">
         <v>11</v>
@@ -8650,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M147" s="20">
         <v>0</v>
@@ -8665,27 +8669,27 @@
     <row r="148" spans="1:15">
       <c r="A148" s="1">
         <f t="shared" si="2"/>
-        <v>10070012</v>
+        <v>10030012</v>
       </c>
       <c r="B148" s="19">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C148" s="19">
         <v>1</v>
       </c>
       <c r="D148" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v>麻将胡了</v>
+        <f t="shared" si="1"/>
+        <v>超级明星</v>
       </c>
       <c r="E148" s="19">
-        <v>100700001</v>
+        <v>100300001</v>
       </c>
       <c r="F148" s="19" t="str">
         <f t="shared" si="3"/>
-        <v>MahjongWays</v>
+        <v>SuperStar</v>
       </c>
       <c r="G148" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H148" s="20">
         <v>12</v>
@@ -8700,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M148" s="20">
         <v>0</v>
@@ -8715,25 +8719,25 @@
     <row r="149" spans="1:15">
       <c r="A149" s="1">
         <f t="shared" si="2"/>
-        <v>10120010</v>
+        <v>10070010</v>
       </c>
       <c r="B149" s="19">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="C149" s="19">
         <v>1</v>
       </c>
       <c r="D149" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E149" s="19">
-        <v>101200001</v>
+        <v>100700001</v>
       </c>
       <c r="F149" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G149" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H149" s="20">
         <v>10</v>
@@ -8748,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M149" s="20">
         <v>0</v>
@@ -8763,27 +8767,27 @@
     <row r="150" spans="1:15">
       <c r="A150" s="1">
         <f t="shared" si="2"/>
-        <v>10120011</v>
+        <v>10070011</v>
       </c>
       <c r="B150" s="19">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="C150" s="19">
         <v>1</v>
       </c>
       <c r="D150" s="19" t="str">
-        <f t="shared" si="4"/>
-        <v>财神</v>
+        <f t="shared" ref="D150:D154" si="4">D149</f>
+        <v>麻将胡了</v>
       </c>
       <c r="E150" s="19">
-        <v>101200001</v>
+        <v>100700001</v>
       </c>
       <c r="F150" s="19" t="str">
-        <f t="shared" ref="F150:F154" si="5">F149</f>
-        <v>Godofwealth</v>
+        <f t="shared" si="3"/>
+        <v>MahjongWays</v>
       </c>
       <c r="G150" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H150" s="20">
         <v>11</v>
@@ -8798,7 +8802,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M150" s="20">
         <v>0</v>
@@ -8813,27 +8817,27 @@
     <row r="151" spans="1:15">
       <c r="A151" s="1">
         <f t="shared" si="2"/>
-        <v>10120012</v>
+        <v>10070012</v>
       </c>
       <c r="B151" s="19">
-        <v>101200</v>
+        <v>100700</v>
       </c>
       <c r="C151" s="19">
         <v>1</v>
       </c>
       <c r="D151" s="19" t="str">
         <f t="shared" si="4"/>
-        <v>财神</v>
+        <v>麻将胡了</v>
       </c>
       <c r="E151" s="19">
-        <v>101200001</v>
+        <v>100700001</v>
       </c>
       <c r="F151" s="19" t="str">
-        <f t="shared" si="5"/>
-        <v>Godofwealth</v>
+        <f t="shared" si="3"/>
+        <v>MahjongWays</v>
       </c>
       <c r="G151" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H151" s="20">
         <v>12</v>
@@ -8848,7 +8852,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M151" s="20">
         <v>0</v>
@@ -8863,25 +8867,25 @@
     <row r="152" spans="1:15">
       <c r="A152" s="1">
         <f t="shared" si="2"/>
-        <v>10140010</v>
+        <v>10120010</v>
       </c>
       <c r="B152" s="19">
-        <v>101400</v>
+        <v>101200</v>
       </c>
       <c r="C152" s="19">
         <v>1</v>
       </c>
       <c r="D152" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E152" s="19">
-        <v>101400001</v>
+        <v>101200001</v>
       </c>
       <c r="F152" s="19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G152" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H152" s="20">
         <v>10</v>
@@ -8896,7 +8900,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M152" s="20">
         <v>0</v>
@@ -8911,27 +8915,27 @@
     <row r="153" spans="1:15">
       <c r="A153" s="1">
         <f t="shared" si="2"/>
-        <v>10140011</v>
+        <v>10120011</v>
       </c>
       <c r="B153" s="19">
-        <v>101400</v>
+        <v>101200</v>
       </c>
       <c r="C153" s="19">
         <v>1</v>
       </c>
       <c r="D153" s="19" t="str">
-        <f t="shared" ref="D153:D157" si="6">D152</f>
-        <v>埃及艳后</v>
+        <f t="shared" si="4"/>
+        <v>财神</v>
       </c>
       <c r="E153" s="19">
-        <v>101400001</v>
+        <v>101200001</v>
       </c>
       <c r="F153" s="19" t="str">
-        <f t="shared" si="5"/>
-        <v>Cleopatra</v>
+        <f t="shared" ref="F153:F157" si="5">F152</f>
+        <v>Godofwealth</v>
       </c>
       <c r="G153" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H153" s="20">
         <v>11</v>
@@ -8946,7 +8950,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M153" s="20">
         <v>0</v>
@@ -8961,27 +8965,27 @@
     <row r="154" spans="1:15">
       <c r="A154" s="1">
         <f t="shared" si="2"/>
-        <v>10140012</v>
+        <v>10120012</v>
       </c>
       <c r="B154" s="19">
-        <v>101400</v>
+        <v>101200</v>
       </c>
       <c r="C154" s="19">
         <v>1</v>
       </c>
       <c r="D154" s="19" t="str">
-        <f t="shared" si="6"/>
-        <v>埃及艳后</v>
+        <f t="shared" si="4"/>
+        <v>财神</v>
       </c>
       <c r="E154" s="19">
-        <v>101400001</v>
+        <v>101200001</v>
       </c>
       <c r="F154" s="19" t="str">
         <f t="shared" si="5"/>
-        <v>Cleopatra</v>
+        <v>Godofwealth</v>
       </c>
       <c r="G154" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H154" s="20">
         <v>12</v>
@@ -8996,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M154" s="20">
         <v>0</v>
@@ -9011,25 +9015,25 @@
     <row r="155" spans="1:15">
       <c r="A155" s="1">
         <f t="shared" si="2"/>
-        <v>10240010</v>
+        <v>10140010</v>
       </c>
       <c r="B155" s="19">
-        <v>102400</v>
+        <v>101400</v>
       </c>
       <c r="C155" s="19">
         <v>1</v>
       </c>
       <c r="D155" s="19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E155" s="19">
-        <v>102400026</v>
+        <v>101400001</v>
       </c>
       <c r="F155" s="19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G155" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H155" s="20">
         <v>10</v>
@@ -9044,7 +9048,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M155" s="20">
         <v>0</v>
@@ -9059,26 +9063,27 @@
     <row r="156" spans="1:15">
       <c r="A156" s="1">
         <f t="shared" si="2"/>
-        <v>10240011</v>
+        <v>10140011</v>
       </c>
       <c r="B156" s="19">
-        <v>102400</v>
+        <v>101400</v>
       </c>
       <c r="C156" s="19">
         <v>1</v>
       </c>
       <c r="D156" s="19" t="str">
-        <f t="shared" si="6"/>
-        <v>财富银行</v>
+        <f t="shared" ref="D156:D160" si="6">D155</f>
+        <v>埃及艳后</v>
       </c>
       <c r="E156" s="19">
-        <v>102400026</v>
-      </c>
-      <c r="F156" s="19" t="s">
-        <v>46</v>
+        <v>101400001</v>
+      </c>
+      <c r="F156" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>Cleopatra</v>
       </c>
       <c r="G156" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H156" s="20">
         <v>11</v>
@@ -9093,7 +9098,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M156" s="20">
         <v>0</v>
@@ -9108,26 +9113,27 @@
     <row r="157" spans="1:15">
       <c r="A157" s="1">
         <f t="shared" si="2"/>
-        <v>10240012</v>
+        <v>10140012</v>
       </c>
       <c r="B157" s="19">
-        <v>102400</v>
+        <v>101400</v>
       </c>
       <c r="C157" s="19">
         <v>1</v>
       </c>
       <c r="D157" s="19" t="str">
         <f t="shared" si="6"/>
-        <v>财富银行</v>
+        <v>埃及艳后</v>
       </c>
       <c r="E157" s="19">
-        <v>102400026</v>
-      </c>
-      <c r="F157" s="19" t="s">
-        <v>46</v>
+        <v>101400001</v>
+      </c>
+      <c r="F157" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>Cleopatra</v>
       </c>
       <c r="G157" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H157" s="20">
         <v>12</v>
@@ -9142,7 +9148,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M157" s="20">
         <v>0</v>
@@ -9157,25 +9163,25 @@
     <row r="158" spans="1:15">
       <c r="A158" s="1">
         <f t="shared" si="2"/>
-        <v>10220010</v>
+        <v>10240010</v>
       </c>
       <c r="B158" s="19">
-        <v>102200</v>
+        <v>102400</v>
       </c>
       <c r="C158" s="19">
         <v>1</v>
       </c>
       <c r="D158" s="19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E158" s="19">
-        <v>102200001</v>
+        <v>102400026</v>
       </c>
       <c r="F158" s="19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G158" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H158" s="20">
         <v>10</v>
@@ -9190,7 +9196,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M158" s="20">
         <v>0</v>
@@ -9205,25 +9211,26 @@
     <row r="159" spans="1:15">
       <c r="A159" s="1">
         <f t="shared" si="2"/>
-        <v>10220011</v>
+        <v>10240011</v>
       </c>
       <c r="B159" s="19">
-        <v>102200</v>
+        <v>102400</v>
       </c>
       <c r="C159" s="19">
         <v>1</v>
       </c>
-      <c r="D159" s="19" t="s">
-        <v>47</v>
+      <c r="D159" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>财富银行</v>
       </c>
       <c r="E159" s="19">
-        <v>102200001</v>
+        <v>102400026</v>
       </c>
       <c r="F159" s="19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G159" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H159" s="20">
         <v>11</v>
@@ -9238,7 +9245,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M159" s="20">
         <v>0</v>
@@ -9253,25 +9260,26 @@
     <row r="160" spans="1:15">
       <c r="A160" s="1">
         <f t="shared" si="2"/>
-        <v>10220012</v>
+        <v>10240012</v>
       </c>
       <c r="B160" s="19">
-        <v>102200</v>
+        <v>102400</v>
       </c>
       <c r="C160" s="19">
         <v>1</v>
       </c>
-      <c r="D160" s="19" t="s">
-        <v>47</v>
+      <c r="D160" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>财富银行</v>
       </c>
       <c r="E160" s="19">
-        <v>102200001</v>
+        <v>102400026</v>
       </c>
       <c r="F160" s="19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G160" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H160" s="20">
         <v>12</v>
@@ -9286,7 +9294,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M160" s="20">
         <v>0</v>
@@ -9301,25 +9309,25 @@
     <row r="161" spans="1:15">
       <c r="A161" s="1">
         <f t="shared" si="2"/>
-        <v>10170010</v>
+        <v>10220010</v>
       </c>
       <c r="B161" s="19">
-        <v>101700</v>
+        <v>102200</v>
       </c>
       <c r="C161" s="19">
         <v>1</v>
       </c>
       <c r="D161" s="19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E161" s="19">
-        <v>101700001</v>
+        <v>102200001</v>
       </c>
       <c r="F161" s="19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G161" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H161" s="20">
         <v>10</v>
@@ -9334,7 +9342,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M161" s="20">
         <v>0</v>
@@ -9349,25 +9357,25 @@
     <row r="162" spans="1:15">
       <c r="A162" s="1">
         <f t="shared" si="2"/>
-        <v>10170011</v>
+        <v>10220011</v>
       </c>
       <c r="B162" s="19">
-        <v>101700</v>
+        <v>102200</v>
       </c>
       <c r="C162" s="19">
         <v>1</v>
       </c>
       <c r="D162" s="19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E162" s="19">
-        <v>101700001</v>
+        <v>102200001</v>
       </c>
       <c r="F162" s="19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G162" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H162" s="20">
         <v>11</v>
@@ -9382,7 +9390,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M162" s="20">
         <v>0</v>
@@ -9397,25 +9405,25 @@
     <row r="163" spans="1:15">
       <c r="A163" s="1">
         <f t="shared" si="2"/>
-        <v>10170012</v>
+        <v>10220012</v>
       </c>
       <c r="B163" s="19">
-        <v>101700</v>
+        <v>102200</v>
       </c>
       <c r="C163" s="19">
         <v>1</v>
       </c>
       <c r="D163" s="19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E163" s="19">
-        <v>101700001</v>
+        <v>102200001</v>
       </c>
       <c r="F163" s="19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G163" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H163" s="20">
         <v>12</v>
@@ -9430,7 +9438,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M163" s="20">
         <v>0</v>
@@ -9445,25 +9453,25 @@
     <row r="164" spans="1:15">
       <c r="A164" s="1">
         <f t="shared" si="2"/>
-        <v>10210010</v>
+        <v>10170010</v>
       </c>
       <c r="B164" s="19">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C164" s="19">
         <v>1</v>
       </c>
       <c r="D164" s="19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E164" s="19">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="F164" s="19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G164" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H164" s="20">
         <v>10</v>
@@ -9478,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M164" s="20">
         <v>0</v>
@@ -9493,25 +9501,25 @@
     <row r="165" spans="1:15">
       <c r="A165" s="1">
         <f t="shared" si="2"/>
-        <v>10210011</v>
+        <v>10170011</v>
       </c>
       <c r="B165" s="19">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C165" s="19">
         <v>1</v>
       </c>
       <c r="D165" s="19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E165" s="19">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="F165" s="19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G165" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H165" s="20">
         <v>11</v>
@@ -9526,7 +9534,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M165" s="20">
         <v>0</v>
@@ -9541,25 +9549,25 @@
     <row r="166" spans="1:15">
       <c r="A166" s="1">
         <f t="shared" si="2"/>
-        <v>10210012</v>
+        <v>10170012</v>
       </c>
       <c r="B166" s="19">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C166" s="19">
         <v>1</v>
       </c>
       <c r="D166" s="19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E166" s="19">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="F166" s="19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G166" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H166" s="20">
         <v>12</v>
@@ -9574,7 +9582,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M166" s="20">
         <v>0</v>
@@ -9589,25 +9597,25 @@
     <row r="167" spans="1:15">
       <c r="A167" s="1">
         <f t="shared" si="2"/>
-        <v>10180010</v>
+        <v>10210010</v>
       </c>
       <c r="B167" s="19">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C167" s="19">
         <v>1</v>
       </c>
       <c r="D167" s="19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E167" s="19">
-        <v>101800001</v>
+        <v>102100001</v>
       </c>
       <c r="F167" s="19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G167" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H167" s="20">
         <v>10</v>
@@ -9622,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M167" s="20">
         <v>0</v>
@@ -9637,25 +9645,25 @@
     <row r="168" spans="1:15">
       <c r="A168" s="1">
         <f t="shared" si="2"/>
-        <v>10180011</v>
+        <v>10210011</v>
       </c>
       <c r="B168" s="19">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C168" s="19">
         <v>1</v>
       </c>
       <c r="D168" s="19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E168" s="19">
-        <v>101800001</v>
+        <v>102100001</v>
       </c>
       <c r="F168" s="19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G168" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H168" s="20">
         <v>11</v>
@@ -9670,7 +9678,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M168" s="20">
         <v>0</v>
@@ -9685,25 +9693,25 @@
     <row r="169" spans="1:15">
       <c r="A169" s="1">
         <f t="shared" si="2"/>
-        <v>10180012</v>
+        <v>10210012</v>
       </c>
       <c r="B169" s="19">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C169" s="19">
         <v>1</v>
       </c>
       <c r="D169" s="19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E169" s="19">
-        <v>101800001</v>
+        <v>102100001</v>
       </c>
       <c r="F169" s="19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G169" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H169" s="20">
         <v>12</v>
@@ -9718,7 +9726,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M169" s="20">
         <v>0</v>
@@ -9733,25 +9741,25 @@
     <row r="170" spans="1:15">
       <c r="A170" s="1">
         <f t="shared" si="2"/>
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B170" s="19">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C170" s="19">
         <v>1</v>
       </c>
       <c r="D170" s="19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E170" s="19">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="F170" s="19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G170" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H170" s="20">
         <v>10</v>
@@ -9766,7 +9774,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M170" s="20">
         <v>0</v>
@@ -9781,25 +9789,25 @@
     <row r="171" spans="1:15">
       <c r="A171" s="1">
         <f t="shared" si="2"/>
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B171" s="19">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C171" s="19">
         <v>1</v>
       </c>
       <c r="D171" s="19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E171" s="19">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="F171" s="19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G171" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H171" s="20">
         <v>11</v>
@@ -9814,7 +9822,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M171" s="20">
         <v>0</v>
@@ -9829,25 +9837,25 @@
     <row r="172" spans="1:15">
       <c r="A172" s="1">
         <f t="shared" si="2"/>
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B172" s="19">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C172" s="19">
         <v>1</v>
       </c>
       <c r="D172" s="19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E172" s="19">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="F172" s="19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G172" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H172" s="20">
         <v>12</v>
@@ -9862,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M172" s="20">
         <v>0</v>
@@ -9877,25 +9885,25 @@
     <row r="173" spans="1:15">
       <c r="A173" s="1">
         <f t="shared" si="2"/>
-        <v>10230010</v>
+        <v>10250010</v>
       </c>
       <c r="B173" s="19">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C173" s="19">
         <v>1</v>
       </c>
       <c r="D173" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E173" s="19">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="F173" s="19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G173" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H173" s="20">
         <v>10</v>
@@ -9910,7 +9918,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M173" s="20">
         <v>0</v>
@@ -9925,25 +9933,25 @@
     <row r="174" spans="1:15">
       <c r="A174" s="1">
         <f t="shared" si="2"/>
-        <v>10230011</v>
+        <v>10250011</v>
       </c>
       <c r="B174" s="19">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C174" s="19">
         <v>1</v>
       </c>
       <c r="D174" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E174" s="19">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="F174" s="19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G174" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H174" s="20">
         <v>11</v>
@@ -9958,7 +9966,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M174" s="20">
         <v>0</v>
@@ -9973,25 +9981,25 @@
     <row r="175" spans="1:15">
       <c r="A175" s="1">
         <f t="shared" si="2"/>
-        <v>10230012</v>
+        <v>10250012</v>
       </c>
       <c r="B175" s="19">
-        <v>102300</v>
+        <v>102500</v>
       </c>
       <c r="C175" s="19">
         <v>1</v>
       </c>
       <c r="D175" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E175" s="19">
-        <v>102300001</v>
+        <v>102500001</v>
       </c>
       <c r="F175" s="19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G175" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H175" s="20">
         <v>12</v>
@@ -10006,7 +10014,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M175" s="20">
         <v>0</v>
@@ -10021,30 +10029,30 @@
     <row r="176" spans="1:15">
       <c r="A176" s="1">
         <f t="shared" si="2"/>
-        <v>10340010</v>
-      </c>
-      <c r="B176" s="15">
-        <v>103400</v>
-      </c>
-      <c r="C176" s="15">
-        <v>1</v>
-      </c>
-      <c r="D176" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E176" s="16">
-        <v>103000001</v>
-      </c>
-      <c r="F176" s="16" t="s">
-        <v>60</v>
+        <v>10230010</v>
+      </c>
+      <c r="B176" s="19">
+        <v>102300</v>
+      </c>
+      <c r="C176" s="19">
+        <v>1</v>
+      </c>
+      <c r="D176" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E176" s="19">
+        <v>102300001</v>
+      </c>
+      <c r="F176" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="G176" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="H176" s="1">
+        <v>108</v>
+      </c>
+      <c r="H176" s="20">
         <v>10</v>
       </c>
-      <c r="I176" s="3">
+      <c r="I176" s="27">
         <v>0</v>
       </c>
       <c r="J176" s="20">
@@ -10054,7 +10062,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M176" s="20">
         <v>0</v>
@@ -10069,30 +10077,30 @@
     <row r="177" spans="1:15">
       <c r="A177" s="1">
         <f t="shared" si="2"/>
-        <v>10340011</v>
-      </c>
-      <c r="B177" s="15">
-        <v>103400</v>
-      </c>
-      <c r="C177" s="15">
-        <v>1</v>
-      </c>
-      <c r="D177" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E177" s="16">
-        <v>103000001</v>
-      </c>
-      <c r="F177" s="16" t="s">
-        <v>60</v>
+        <v>10230011</v>
+      </c>
+      <c r="B177" s="19">
+        <v>102300</v>
+      </c>
+      <c r="C177" s="19">
+        <v>1</v>
+      </c>
+      <c r="D177" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E177" s="19">
+        <v>102300001</v>
+      </c>
+      <c r="F177" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="G177" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="H177" s="1">
+        <v>110</v>
+      </c>
+      <c r="H177" s="20">
         <v>11</v>
       </c>
-      <c r="I177" s="3">
+      <c r="I177" s="27">
         <v>0</v>
       </c>
       <c r="J177" s="20">
@@ -10102,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M177" s="20">
         <v>0</v>
@@ -10117,40 +10125,40 @@
     <row r="178" spans="1:15">
       <c r="A178" s="1">
         <f t="shared" si="2"/>
-        <v>10340012</v>
-      </c>
-      <c r="B178" s="15">
-        <v>103400</v>
-      </c>
-      <c r="C178" s="15">
-        <v>1</v>
-      </c>
-      <c r="D178" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E178" s="16">
-        <v>103000001</v>
-      </c>
-      <c r="F178" s="16" t="s">
-        <v>60</v>
+        <v>10230012</v>
+      </c>
+      <c r="B178" s="19">
+        <v>102300</v>
+      </c>
+      <c r="C178" s="19">
+        <v>1</v>
+      </c>
+      <c r="D178" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E178" s="19">
+        <v>102300001</v>
+      </c>
+      <c r="F178" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="G178" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H178" s="20">
+        <v>12</v>
+      </c>
+      <c r="I178" s="27">
+        <v>0</v>
+      </c>
+      <c r="J178" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K178" s="20">
+        <v>0</v>
+      </c>
+      <c r="L178" s="28" t="s">
         <v>109</v>
-      </c>
-      <c r="H178" s="1">
-        <v>12</v>
-      </c>
-      <c r="I178" s="3">
-        <v>0</v>
-      </c>
-      <c r="J178" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K178" s="20">
-        <v>0</v>
-      </c>
-      <c r="L178" s="28" t="s">
-        <v>107</v>
       </c>
       <c r="M178" s="20">
         <v>0</v>
@@ -10165,25 +10173,25 @@
     <row r="179" spans="1:15">
       <c r="A179" s="1">
         <f t="shared" si="2"/>
-        <v>10350010</v>
+        <v>10340010</v>
       </c>
       <c r="B179" s="15">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C179" s="15">
         <v>1</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E179" s="16">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="F179" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G179" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H179" s="1">
         <v>10</v>
@@ -10198,7 +10206,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M179" s="20">
         <v>0</v>
@@ -10213,25 +10221,25 @@
     <row r="180" spans="1:15">
       <c r="A180" s="1">
         <f t="shared" si="2"/>
-        <v>10350011</v>
+        <v>10340011</v>
       </c>
       <c r="B180" s="15">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C180" s="15">
         <v>1</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E180" s="16">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="F180" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G180" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H180" s="1">
         <v>11</v>
@@ -10246,7 +10254,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M180" s="20">
         <v>0</v>
@@ -10261,25 +10269,25 @@
     <row r="181" spans="1:15">
       <c r="A181" s="1">
         <f t="shared" si="2"/>
-        <v>10350012</v>
+        <v>10340012</v>
       </c>
       <c r="B181" s="15">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C181" s="15">
         <v>1</v>
       </c>
       <c r="D181" s="15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E181" s="16">
-        <v>102900001</v>
+        <v>103000001</v>
       </c>
       <c r="F181" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G181" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H181" s="1">
         <v>12</v>
@@ -10294,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M181" s="20">
         <v>0</v>
@@ -10309,25 +10317,25 @@
     <row r="182" spans="1:15">
       <c r="A182" s="1">
         <f t="shared" si="2"/>
-        <v>10350110</v>
+        <v>10350010</v>
       </c>
       <c r="B182" s="15">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C182" s="15">
         <v>1</v>
       </c>
       <c r="D182" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E182" s="16">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="F182" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G182" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H182" s="1">
         <v>10</v>
@@ -10338,11 +10346,11 @@
       <c r="J182" s="20">
         <v>-1</v>
       </c>
-      <c r="K182" s="1">
+      <c r="K182" s="20">
         <v>0</v>
       </c>
       <c r="L182" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M182" s="20">
         <v>0</v>
@@ -10357,25 +10365,25 @@
     <row r="183" spans="1:15">
       <c r="A183" s="1">
         <f t="shared" si="2"/>
-        <v>10350111</v>
+        <v>10350011</v>
       </c>
       <c r="B183" s="15">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C183" s="15">
         <v>1</v>
       </c>
       <c r="D183" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E183" s="16">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="F183" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G183" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H183" s="1">
         <v>11</v>
@@ -10386,11 +10394,11 @@
       <c r="J183" s="20">
         <v>-1</v>
       </c>
-      <c r="K183" s="1">
+      <c r="K183" s="20">
         <v>0</v>
       </c>
       <c r="L183" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M183" s="20">
         <v>0</v>
@@ -10405,25 +10413,25 @@
     <row r="184" spans="1:15">
       <c r="A184" s="1">
         <f t="shared" si="2"/>
-        <v>10350112</v>
+        <v>10350012</v>
       </c>
       <c r="B184" s="15">
-        <v>103501</v>
+        <v>103500</v>
       </c>
       <c r="C184" s="15">
         <v>1</v>
       </c>
       <c r="D184" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E184" s="16">
-        <v>103501001</v>
+        <v>102900001</v>
       </c>
       <c r="F184" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G184" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H184" s="1">
         <v>12</v>
@@ -10434,11 +10442,11 @@
       <c r="J184" s="20">
         <v>-1</v>
       </c>
-      <c r="K184" s="1">
+      <c r="K184" s="20">
         <v>0</v>
       </c>
       <c r="L184" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M184" s="20">
         <v>0</v>
@@ -10453,25 +10461,25 @@
     <row r="185" spans="1:15">
       <c r="A185" s="1">
         <f t="shared" si="2"/>
-        <v>10200010</v>
+        <v>10350110</v>
       </c>
       <c r="B185" s="15">
-        <v>102000</v>
+        <v>103501</v>
       </c>
       <c r="C185" s="15">
         <v>1</v>
       </c>
       <c r="D185" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E185" s="16">
-        <v>102000001</v>
+        <v>103501001</v>
       </c>
       <c r="F185" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G185" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H185" s="1">
         <v>10</v>
@@ -10486,13 +10494,13 @@
         <v>0</v>
       </c>
       <c r="L185" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M185" s="20">
         <v>0</v>
       </c>
       <c r="N185">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="O185" s="29">
         <v>1980000</v>
@@ -10501,25 +10509,25 @@
     <row r="186" spans="1:15">
       <c r="A186" s="1">
         <f t="shared" si="2"/>
-        <v>10200011</v>
+        <v>10350111</v>
       </c>
       <c r="B186" s="15">
-        <v>102000</v>
+        <v>103501</v>
       </c>
       <c r="C186" s="15">
         <v>1</v>
       </c>
       <c r="D186" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E186" s="16">
-        <v>102000001</v>
+        <v>103501001</v>
       </c>
       <c r="F186" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G186" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H186" s="1">
         <v>11</v>
@@ -10534,13 +10542,13 @@
         <v>0</v>
       </c>
       <c r="L186" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M186" s="20">
         <v>0</v>
       </c>
       <c r="N186">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="O186" s="29">
         <v>1980000</v>
@@ -10549,25 +10557,25 @@
     <row r="187" spans="1:15">
       <c r="A187" s="1">
         <f t="shared" si="2"/>
-        <v>10200012</v>
+        <v>10350112</v>
       </c>
       <c r="B187" s="15">
-        <v>102000</v>
+        <v>103501</v>
       </c>
       <c r="C187" s="15">
         <v>1</v>
       </c>
       <c r="D187" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E187" s="16">
-        <v>102000001</v>
+        <v>103501001</v>
       </c>
       <c r="F187" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G187" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H187" s="1">
         <v>12</v>
@@ -10582,13 +10590,13 @@
         <v>0</v>
       </c>
       <c r="L187" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M187" s="20">
         <v>0</v>
       </c>
       <c r="N187">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="O187" s="29">
         <v>1980000</v>
@@ -10597,25 +10605,25 @@
     <row r="188" spans="1:15">
       <c r="A188" s="1">
         <f t="shared" si="2"/>
-        <v>10360010</v>
+        <v>10200010</v>
       </c>
       <c r="B188" s="15">
-        <v>103600</v>
+        <v>102000</v>
       </c>
       <c r="C188" s="15">
         <v>1</v>
       </c>
       <c r="D188" s="15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E188" s="16">
-        <v>103600001</v>
+        <v>102000001</v>
       </c>
       <c r="F188" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G188" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H188" s="1">
         <v>10</v>
@@ -10630,13 +10638,13 @@
         <v>0</v>
       </c>
       <c r="L188" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M188" s="20">
         <v>0</v>
       </c>
       <c r="N188">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="O188" s="29">
         <v>1980000</v>
@@ -10645,25 +10653,25 @@
     <row r="189" spans="1:15">
       <c r="A189" s="1">
         <f t="shared" si="2"/>
-        <v>10360011</v>
+        <v>10200011</v>
       </c>
       <c r="B189" s="15">
-        <v>103600</v>
+        <v>102000</v>
       </c>
       <c r="C189" s="15">
         <v>1</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E189" s="16">
-        <v>103600001</v>
+        <v>102000001</v>
       </c>
       <c r="F189" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G189" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H189" s="1">
         <v>11</v>
@@ -10678,13 +10686,13 @@
         <v>0</v>
       </c>
       <c r="L189" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M189" s="20">
         <v>0</v>
       </c>
       <c r="N189">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="O189" s="29">
         <v>1980000</v>
@@ -10693,25 +10701,25 @@
     <row r="190" spans="1:15">
       <c r="A190" s="1">
         <f t="shared" si="2"/>
-        <v>10360012</v>
+        <v>10200012</v>
       </c>
       <c r="B190" s="15">
-        <v>103600</v>
+        <v>102000</v>
       </c>
       <c r="C190" s="15">
         <v>1</v>
       </c>
       <c r="D190" s="15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E190" s="16">
-        <v>103600001</v>
+        <v>102000001</v>
       </c>
       <c r="F190" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G190" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H190" s="1">
         <v>12</v>
@@ -10726,13 +10734,13 @@
         <v>0</v>
       </c>
       <c r="L190" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M190" s="20">
         <v>0</v>
       </c>
       <c r="N190">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="O190" s="29">
         <v>1980000</v>
@@ -10740,25 +10748,26 @@
     </row>
     <row r="191" spans="1:15">
       <c r="A191" s="1">
-        <v>10340110</v>
+        <f t="shared" si="2"/>
+        <v>10360010</v>
       </c>
       <c r="B191" s="15">
-        <v>103401</v>
+        <v>103600</v>
       </c>
       <c r="C191" s="15">
         <v>1</v>
       </c>
       <c r="D191" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E191" s="16">
-        <v>103400001</v>
+        <v>103600001</v>
       </c>
       <c r="F191" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G191" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H191" s="1">
         <v>10</v>
@@ -10773,7 +10782,7 @@
         <v>0</v>
       </c>
       <c r="L191" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M191" s="20">
         <v>0</v>
@@ -10787,25 +10796,26 @@
     </row>
     <row r="192" spans="1:15">
       <c r="A192" s="1">
-        <v>10340111</v>
+        <f t="shared" si="2"/>
+        <v>10360011</v>
       </c>
       <c r="B192" s="15">
-        <v>103401</v>
+        <v>103600</v>
       </c>
       <c r="C192" s="15">
         <v>1</v>
       </c>
       <c r="D192" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E192" s="16">
-        <v>103400001</v>
+        <v>103600001</v>
       </c>
       <c r="F192" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G192" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H192" s="1">
         <v>11</v>
@@ -10820,7 +10830,7 @@
         <v>0</v>
       </c>
       <c r="L192" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M192" s="20">
         <v>0</v>
@@ -10834,25 +10844,26 @@
     </row>
     <row r="193" spans="1:19">
       <c r="A193" s="1">
-        <v>10340112</v>
+        <f t="shared" si="2"/>
+        <v>10360012</v>
       </c>
       <c r="B193" s="15">
-        <v>103401</v>
+        <v>103600</v>
       </c>
       <c r="C193" s="15">
         <v>1</v>
       </c>
       <c r="D193" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E193" s="16">
-        <v>103400001</v>
+        <v>103600001</v>
       </c>
       <c r="F193" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G193" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H193" s="1">
         <v>12</v>
@@ -10867,7 +10878,7 @@
         <v>0</v>
       </c>
       <c r="L193" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M193" s="20">
         <v>0</v>
@@ -10881,25 +10892,26 @@
     </row>
     <row r="194" spans="1:19">
       <c r="A194" s="1">
-        <v>10380010</v>
+        <f t="shared" si="2"/>
+        <v>10280010</v>
       </c>
       <c r="B194" s="15">
-        <v>103800</v>
+        <v>102800</v>
       </c>
       <c r="C194" s="15">
         <v>1</v>
       </c>
       <c r="D194" s="15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E194" s="16">
-        <v>103800001</v>
+        <v>102800001</v>
       </c>
       <c r="F194" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G194" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H194" s="1">
         <v>10</v>
@@ -10914,13 +10926,13 @@
         <v>0</v>
       </c>
       <c r="L194" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M194" s="20">
         <v>0</v>
       </c>
       <c r="N194">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="O194" s="29">
         <v>1980000</v>
@@ -10928,25 +10940,26 @@
     </row>
     <row r="195" spans="1:19">
       <c r="A195" s="1">
-        <v>10380011</v>
+        <f t="shared" si="2"/>
+        <v>10280011</v>
       </c>
       <c r="B195" s="15">
-        <v>103800</v>
+        <v>102800</v>
       </c>
       <c r="C195" s="15">
         <v>1</v>
       </c>
       <c r="D195" s="15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E195" s="16">
-        <v>103800001</v>
+        <v>102800001</v>
       </c>
       <c r="F195" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G195" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H195" s="1">
         <v>11</v>
@@ -10961,13 +10974,13 @@
         <v>0</v>
       </c>
       <c r="L195" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M195" s="20">
         <v>0</v>
       </c>
       <c r="N195">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="O195" s="29">
         <v>1980000</v>
@@ -10975,25 +10988,26 @@
     </row>
     <row r="196" spans="1:19">
       <c r="A196" s="1">
-        <v>10380012</v>
+        <f t="shared" si="2"/>
+        <v>10280012</v>
       </c>
       <c r="B196" s="15">
-        <v>103800</v>
+        <v>102800</v>
       </c>
       <c r="C196" s="15">
         <v>1</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E196" s="16">
-        <v>103800001</v>
+        <v>102800001</v>
       </c>
       <c r="F196" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G196" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H196" s="1">
         <v>12</v>
@@ -11008,39 +11022,39 @@
         <v>0</v>
       </c>
       <c r="L196" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M196" s="20">
         <v>0</v>
       </c>
       <c r="N196">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="O196" s="29">
         <v>1980000</v>
       </c>
     </row>
-    <row r="197" s="2" customFormat="1" spans="1:19">
+    <row r="197" spans="1:19">
       <c r="A197" s="1">
-        <v>10400010</v>
-      </c>
-      <c r="B197" s="2">
-        <v>104000</v>
-      </c>
-      <c r="C197" s="2">
-        <v>1</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E197" s="2">
-        <v>104000001</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>74</v>
+        <v>10340110</v>
+      </c>
+      <c r="B197" s="15">
+        <v>103401</v>
+      </c>
+      <c r="C197" s="15">
+        <v>1</v>
+      </c>
+      <c r="D197" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E197" s="16">
+        <v>103401001</v>
+      </c>
+      <c r="F197" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="G197" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H197" s="1">
         <v>10</v>
@@ -11055,7 +11069,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M197" s="20">
         <v>0</v>
@@ -11066,32 +11080,28 @@
       <c r="O197" s="29">
         <v>1980000</v>
       </c>
-      <c r="P197" s="2"/>
-      <c r="Q197" s="2"/>
-      <c r="R197" s="2"/>
-      <c r="S197" s="26"/>
-    </row>
-    <row r="198" s="2" customFormat="1" spans="1:19">
+    </row>
+    <row r="198" spans="1:19">
       <c r="A198" s="1">
-        <v>10400011</v>
-      </c>
-      <c r="B198" s="2">
-        <v>104000</v>
-      </c>
-      <c r="C198" s="2">
-        <v>1</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E198" s="2">
-        <v>104000001</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>74</v>
+        <v>10340111</v>
+      </c>
+      <c r="B198" s="15">
+        <v>103401</v>
+      </c>
+      <c r="C198" s="15">
+        <v>1</v>
+      </c>
+      <c r="D198" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E198" s="16">
+        <v>103401001</v>
+      </c>
+      <c r="F198" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="G198" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H198" s="1">
         <v>11</v>
@@ -11106,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="L198" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M198" s="20">
         <v>0</v>
@@ -11117,32 +11127,28 @@
       <c r="O198" s="29">
         <v>1980000</v>
       </c>
-      <c r="P198" s="2"/>
-      <c r="Q198" s="2"/>
-      <c r="R198" s="2"/>
-      <c r="S198" s="26"/>
-    </row>
-    <row r="199" s="2" customFormat="1" spans="1:19">
+    </row>
+    <row r="199" spans="1:19">
       <c r="A199" s="1">
-        <v>10400012</v>
-      </c>
-      <c r="B199" s="2">
-        <v>104000</v>
-      </c>
-      <c r="C199" s="2">
-        <v>1</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E199" s="2">
-        <v>104000001</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>74</v>
+        <v>10340112</v>
+      </c>
+      <c r="B199" s="15">
+        <v>103401</v>
+      </c>
+      <c r="C199" s="15">
+        <v>1</v>
+      </c>
+      <c r="D199" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E199" s="16">
+        <v>103401001</v>
+      </c>
+      <c r="F199" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="G199" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H199" s="1">
         <v>12</v>
@@ -11157,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="L199" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M199" s="20">
         <v>0</v>
@@ -11168,12 +11174,302 @@
       <c r="O199" s="29">
         <v>1980000</v>
       </c>
-      <c r="P199" s="2"/>
-      <c r="Q199" s="2"/>
-      <c r="R199" s="2"/>
-      <c r="S199" s="26"/>
-    </row>
-    <row r="200" ht="12" customHeight="1"/>
+    </row>
+    <row r="200" spans="1:19">
+      <c r="A200" s="1">
+        <v>10380010</v>
+      </c>
+      <c r="B200" s="15">
+        <v>103800</v>
+      </c>
+      <c r="C200" s="15">
+        <v>1</v>
+      </c>
+      <c r="D200" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E200" s="16">
+        <v>103800001</v>
+      </c>
+      <c r="F200" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G200" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H200" s="1">
+        <v>10</v>
+      </c>
+      <c r="I200" s="3">
+        <v>0</v>
+      </c>
+      <c r="J200" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K200" s="1">
+        <v>0</v>
+      </c>
+      <c r="L200" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="M200" s="20">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>2000</v>
+      </c>
+      <c r="O200" s="29">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19">
+      <c r="A201" s="1">
+        <v>10380011</v>
+      </c>
+      <c r="B201" s="15">
+        <v>103800</v>
+      </c>
+      <c r="C201" s="15">
+        <v>1</v>
+      </c>
+      <c r="D201" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E201" s="16">
+        <v>103800001</v>
+      </c>
+      <c r="F201" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G201" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="H201" s="1">
+        <v>11</v>
+      </c>
+      <c r="I201" s="3">
+        <v>0</v>
+      </c>
+      <c r="J201" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K201" s="1">
+        <v>0</v>
+      </c>
+      <c r="L201" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="M201" s="20">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>20000</v>
+      </c>
+      <c r="O201" s="29">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19">
+      <c r="A202" s="1">
+        <v>10380012</v>
+      </c>
+      <c r="B202" s="15">
+        <v>103800</v>
+      </c>
+      <c r="C202" s="15">
+        <v>1</v>
+      </c>
+      <c r="D202" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E202" s="16">
+        <v>103800001</v>
+      </c>
+      <c r="F202" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G202" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H202" s="1">
+        <v>12</v>
+      </c>
+      <c r="I202" s="3">
+        <v>0</v>
+      </c>
+      <c r="J202" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K202" s="1">
+        <v>0</v>
+      </c>
+      <c r="L202" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="M202" s="20">
+        <v>0</v>
+      </c>
+      <c r="N202">
+        <v>200000</v>
+      </c>
+      <c r="O202" s="29">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="203" s="2" customFormat="1" spans="1:19">
+      <c r="A203" s="1">
+        <v>10400010</v>
+      </c>
+      <c r="B203" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C203" s="2">
+        <v>1</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E203" s="2">
+        <v>104000001</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G203" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H203" s="1">
+        <v>10</v>
+      </c>
+      <c r="I203" s="3">
+        <v>0</v>
+      </c>
+      <c r="J203" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K203" s="1">
+        <v>0</v>
+      </c>
+      <c r="L203" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="M203" s="20">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>1000</v>
+      </c>
+      <c r="O203" s="29">
+        <v>1980000</v>
+      </c>
+      <c r="P203" s="2"/>
+      <c r="Q203" s="2"/>
+      <c r="R203" s="2"/>
+      <c r="S203" s="26"/>
+    </row>
+    <row r="204" s="2" customFormat="1" spans="1:19">
+      <c r="A204" s="1">
+        <v>10400011</v>
+      </c>
+      <c r="B204" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C204" s="2">
+        <v>1</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E204" s="2">
+        <v>104000001</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G204" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="H204" s="1">
+        <v>11</v>
+      </c>
+      <c r="I204" s="3">
+        <v>0</v>
+      </c>
+      <c r="J204" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K204" s="1">
+        <v>0</v>
+      </c>
+      <c r="L204" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="M204" s="20">
+        <v>0</v>
+      </c>
+      <c r="N204">
+        <v>10000</v>
+      </c>
+      <c r="O204" s="29">
+        <v>1980000</v>
+      </c>
+      <c r="P204" s="2"/>
+      <c r="Q204" s="2"/>
+      <c r="R204" s="2"/>
+      <c r="S204" s="26"/>
+    </row>
+    <row r="205" s="2" customFormat="1" spans="1:19">
+      <c r="A205" s="1">
+        <v>10400012</v>
+      </c>
+      <c r="B205" s="2">
+        <v>104000</v>
+      </c>
+      <c r="C205" s="2">
+        <v>1</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E205" s="2">
+        <v>104000001</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G205" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H205" s="1">
+        <v>12</v>
+      </c>
+      <c r="I205" s="3">
+        <v>0</v>
+      </c>
+      <c r="J205" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K205" s="1">
+        <v>0</v>
+      </c>
+      <c r="L205" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="M205" s="20">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>100000</v>
+      </c>
+      <c r="O205" s="29">
+        <v>1980000</v>
+      </c>
+      <c r="P205" s="2"/>
+      <c r="Q205" s="2"/>
+      <c r="R205" s="2"/>
+      <c r="S205" s="26"/>
+    </row>
+    <row r="206" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -561,7 +561,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -755,13 +755,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
@@ -779,7 +772,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -878,18 +871,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -897,12 +878,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -945,12 +920,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1211,31 +1180,43 @@
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1265,35 +1246,23 @@
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -9529,7 +9498,7 @@
         <v>3</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E167" s="14">
         <v>300401001</v>
@@ -9577,7 +9546,7 @@
         <v>3</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E168" s="14">
         <v>300401001</v>
@@ -9625,7 +9594,7 @@
         <v>3</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E169" s="14">
         <v>300401001</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="112">
   <si>
     <t>sid</t>
   </si>
@@ -468,6 +468,9 @@
   </si>
   <si>
     <t>4:4</t>
+  </si>
+  <si>
+    <t>0:0</t>
   </si>
   <si>
     <t>俄罗斯轮盘</t>
@@ -6299,7 +6302,7 @@
         <v>103</v>
       </c>
       <c r="M98" s="31" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N98" s="26">
         <v>100</v>
@@ -6348,7 +6351,7 @@
         <v>103</v>
       </c>
       <c r="M99" s="31" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N99" s="26">
         <v>1000</v>
@@ -6397,7 +6400,7 @@
         <v>103</v>
       </c>
       <c r="M100" s="31" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N100" s="26">
         <v>10000</v>
@@ -6418,13 +6421,13 @@
         <v>2</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E101" s="15">
         <v>201200001</v>
       </c>
       <c r="F101" s="25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>32</v>
@@ -6466,13 +6469,13 @@
         <v>2</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E102" s="15">
         <v>201200001</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>35</v>
@@ -6514,13 +6517,13 @@
         <v>2</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E103" s="15">
         <v>201200001</v>
       </c>
       <c r="F103" s="25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>36</v>
@@ -6571,7 +6574,7 @@
         <v>76</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H104" s="19">
         <v>10</v>
@@ -6586,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="L104" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M104" s="19">
         <v>0</v>
@@ -6619,7 +6622,7 @@
         <v>76</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H105" s="19">
         <v>11</v>
@@ -6634,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="L105" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M105" s="19">
         <v>0</v>
@@ -6667,7 +6670,7 @@
         <v>76</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H106" s="19">
         <v>12</v>
@@ -6682,7 +6685,7 @@
         <v>0</v>
       </c>
       <c r="L106" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M106" s="19">
         <v>0</v>
@@ -6715,7 +6718,7 @@
         <v>78</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H107" s="19">
         <v>10</v>
@@ -6730,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="L107" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M107" s="19">
         <v>0</v>
@@ -6763,7 +6766,7 @@
         <v>78</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H108" s="19">
         <v>11</v>
@@ -6778,7 +6781,7 @@
         <v>0</v>
       </c>
       <c r="L108" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M108" s="19">
         <v>0</v>
@@ -6811,7 +6814,7 @@
         <v>78</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H109" s="19">
         <v>12</v>
@@ -6826,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="L109" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M109" s="19">
         <v>0</v>
@@ -6859,7 +6862,7 @@
         <v>80</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H110" s="19">
         <v>10</v>
@@ -6874,7 +6877,7 @@
         <v>0</v>
       </c>
       <c r="L110" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M110" s="19">
         <v>0</v>
@@ -6907,7 +6910,7 @@
         <v>80</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H111" s="19">
         <v>11</v>
@@ -6922,7 +6925,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M111" s="19">
         <v>0</v>
@@ -6955,7 +6958,7 @@
         <v>80</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H112" s="19">
         <v>12</v>
@@ -6970,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M112" s="19">
         <v>0</v>
@@ -7003,7 +7006,7 @@
         <v>82</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H113" s="19">
         <v>10</v>
@@ -7018,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="L113" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M113" s="19">
         <v>0</v>
@@ -7051,7 +7054,7 @@
         <v>82</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H114" s="19">
         <v>11</v>
@@ -7066,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="L114" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M114" s="19">
         <v>0</v>
@@ -7099,7 +7102,7 @@
         <v>82</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H115" s="19">
         <v>12</v>
@@ -7114,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M115" s="19">
         <v>0</v>
@@ -7147,7 +7150,7 @@
         <v>84</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H116" s="19">
         <v>10</v>
@@ -7162,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M116" s="19">
         <v>0</v>
@@ -7195,7 +7198,7 @@
         <v>84</v>
       </c>
       <c r="G117" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H117" s="19">
         <v>11</v>
@@ -7210,7 +7213,7 @@
         <v>0</v>
       </c>
       <c r="L117" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M117" s="19">
         <v>0</v>
@@ -7243,7 +7246,7 @@
         <v>84</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H118" s="19">
         <v>12</v>
@@ -7258,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="L118" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M118" s="19">
         <v>0</v>
@@ -7291,7 +7294,7 @@
         <v>87</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H119" s="19">
         <v>10</v>
@@ -7306,7 +7309,7 @@
         <v>0</v>
       </c>
       <c r="L119" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M119" s="19">
         <v>0</v>
@@ -7338,7 +7341,7 @@
         <v>87</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H120" s="19">
         <v>11</v>
@@ -7353,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="L120" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M120" s="19">
         <v>0</v>
@@ -7385,7 +7388,7 @@
         <v>87</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H121" s="19">
         <v>12</v>
@@ -7400,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M121" s="19">
         <v>0</v>
@@ -7432,7 +7435,7 @@
         <v>89</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H122" s="19">
         <v>10</v>
@@ -7447,7 +7450,7 @@
         <v>0</v>
       </c>
       <c r="L122" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M122" s="19">
         <v>0</v>
@@ -7479,7 +7482,7 @@
         <v>89</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H123" s="19">
         <v>11</v>
@@ -7494,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="L123" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M123" s="19">
         <v>0</v>
@@ -7526,7 +7529,7 @@
         <v>89</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H124" s="19">
         <v>12</v>
@@ -7541,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M124" s="19">
         <v>0</v>
@@ -7573,7 +7576,7 @@
         <v>91</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H125" s="19">
         <v>10</v>
@@ -7588,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M125" s="19">
         <v>0</v>
@@ -7620,7 +7623,7 @@
         <v>91</v>
       </c>
       <c r="G126" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H126" s="19">
         <v>11</v>
@@ -7635,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M126" s="19">
         <v>0</v>
@@ -7667,7 +7670,7 @@
         <v>91</v>
       </c>
       <c r="G127" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H127" s="19">
         <v>12</v>
@@ -7682,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M127" s="19">
         <v>0</v>
@@ -7714,7 +7717,7 @@
         <v>93</v>
       </c>
       <c r="G128" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H128" s="19">
         <v>10</v>
@@ -7729,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M128" s="19">
         <v>0</v>
@@ -7761,7 +7764,7 @@
         <v>93</v>
       </c>
       <c r="G129" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H129" s="19">
         <v>11</v>
@@ -7776,7 +7779,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M129" s="19">
         <v>0</v>
@@ -7808,7 +7811,7 @@
         <v>93</v>
       </c>
       <c r="G130" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H130" s="19">
         <v>12</v>
@@ -7823,7 +7826,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M130" s="19">
         <v>0</v>
@@ -7855,7 +7858,7 @@
         <v>99</v>
       </c>
       <c r="G131" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H131" s="19">
         <v>10</v>
@@ -7870,7 +7873,7 @@
         <v>0</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M131" s="19">
         <v>0</v>
@@ -7903,7 +7906,7 @@
         <v>99</v>
       </c>
       <c r="G132" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H132" s="19">
         <v>11</v>
@@ -7918,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M132" s="19">
         <v>0</v>
@@ -7951,7 +7954,7 @@
         <v>99</v>
       </c>
       <c r="G133" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H133" s="19">
         <v>12</v>
@@ -7966,7 +7969,7 @@
         <v>0</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M133" s="19">
         <v>0</v>
@@ -8000,7 +8003,7 @@
         <v>31</v>
       </c>
       <c r="G134" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H134" s="19">
         <v>10</v>
@@ -8015,7 +8018,7 @@
         <v>0</v>
       </c>
       <c r="L134" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M134" s="19">
         <v>0</v>
@@ -8049,7 +8052,7 @@
         <v>31</v>
       </c>
       <c r="G135" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H135" s="19">
         <v>11</v>
@@ -8064,7 +8067,7 @@
         <v>0</v>
       </c>
       <c r="L135" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M135" s="19">
         <v>0</v>
@@ -8098,7 +8101,7 @@
         <v>31</v>
       </c>
       <c r="G136" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H136" s="19">
         <v>12</v>
@@ -8113,7 +8116,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M136" s="19">
         <v>0</v>
@@ -8146,7 +8149,7 @@
         <v>38</v>
       </c>
       <c r="G137" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H137" s="19">
         <v>10</v>
@@ -8161,7 +8164,7 @@
         <v>0</v>
       </c>
       <c r="L137" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M137" s="19">
         <v>0</v>
@@ -8196,7 +8199,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G138" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H138" s="19">
         <v>11</v>
@@ -8211,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M138" s="19">
         <v>0</v>
@@ -8246,7 +8249,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G139" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H139" s="19">
         <v>12</v>
@@ -8261,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="L139" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M139" s="19">
         <v>0</v>
@@ -8294,7 +8297,7 @@
         <v>40</v>
       </c>
       <c r="G140" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H140" s="19">
         <v>10</v>
@@ -8309,7 +8312,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M140" s="19">
         <v>0</v>
@@ -8344,7 +8347,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G141" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H141" s="19">
         <v>11</v>
@@ -8359,7 +8362,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M141" s="19">
         <v>0</v>
@@ -8394,7 +8397,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G142" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H142" s="19">
         <v>12</v>
@@ -8409,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M142" s="19">
         <v>0</v>
@@ -8442,7 +8445,7 @@
         <v>42</v>
       </c>
       <c r="G143" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H143" s="19">
         <v>10</v>
@@ -8457,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M143" s="19">
         <v>0</v>
@@ -8492,7 +8495,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G144" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H144" s="19">
         <v>11</v>
@@ -8507,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M144" s="19">
         <v>0</v>
@@ -8542,7 +8545,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G145" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H145" s="19">
         <v>12</v>
@@ -8557,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M145" s="19">
         <v>0</v>
@@ -8590,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="G146" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H146" s="19">
         <v>10</v>
@@ -8605,7 +8608,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M146" s="19">
         <v>0</v>
@@ -8640,7 +8643,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G147" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H147" s="19">
         <v>11</v>
@@ -8655,7 +8658,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M147" s="19">
         <v>0</v>
@@ -8690,7 +8693,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G148" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H148" s="19">
         <v>12</v>
@@ -8705,7 +8708,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M148" s="19">
         <v>0</v>
@@ -8738,7 +8741,7 @@
         <v>46</v>
       </c>
       <c r="G149" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H149" s="19">
         <v>10</v>
@@ -8753,7 +8756,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M149" s="19">
         <v>0</v>
@@ -8787,7 +8790,7 @@
         <v>46</v>
       </c>
       <c r="G150" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H150" s="19">
         <v>11</v>
@@ -8802,7 +8805,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M150" s="19">
         <v>0</v>
@@ -8836,7 +8839,7 @@
         <v>46</v>
       </c>
       <c r="G151" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H151" s="19">
         <v>12</v>
@@ -8851,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M151" s="19">
         <v>0</v>
@@ -8884,7 +8887,7 @@
         <v>48</v>
       </c>
       <c r="G152" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H152" s="19">
         <v>10</v>
@@ -8899,7 +8902,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M152" s="19">
         <v>0</v>
@@ -8932,7 +8935,7 @@
         <v>48</v>
       </c>
       <c r="G153" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H153" s="19">
         <v>11</v>
@@ -8947,7 +8950,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M153" s="19">
         <v>0</v>
@@ -8980,7 +8983,7 @@
         <v>48</v>
       </c>
       <c r="G154" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H154" s="19">
         <v>12</v>
@@ -8995,7 +8998,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M154" s="19">
         <v>0</v>
@@ -9028,7 +9031,7 @@
         <v>50</v>
       </c>
       <c r="G155" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H155" s="19">
         <v>10</v>
@@ -9043,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M155" s="19">
         <v>0</v>
@@ -9076,7 +9079,7 @@
         <v>50</v>
       </c>
       <c r="G156" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H156" s="19">
         <v>11</v>
@@ -9091,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M156" s="19">
         <v>0</v>
@@ -9124,7 +9127,7 @@
         <v>50</v>
       </c>
       <c r="G157" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H157" s="19">
         <v>12</v>
@@ -9139,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M157" s="19">
         <v>0</v>
@@ -9172,7 +9175,7 @@
         <v>52</v>
       </c>
       <c r="G158" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H158" s="19">
         <v>10</v>
@@ -9187,7 +9190,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M158" s="19">
         <v>0</v>
@@ -9220,7 +9223,7 @@
         <v>52</v>
       </c>
       <c r="G159" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H159" s="19">
         <v>11</v>
@@ -9235,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M159" s="19">
         <v>0</v>
@@ -9268,7 +9271,7 @@
         <v>52</v>
       </c>
       <c r="G160" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H160" s="19">
         <v>12</v>
@@ -9283,7 +9286,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M160" s="19">
         <v>0</v>
@@ -9316,7 +9319,7 @@
         <v>54</v>
       </c>
       <c r="G161" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H161" s="19">
         <v>10</v>
@@ -9331,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M161" s="19">
         <v>0</v>
@@ -9364,7 +9367,7 @@
         <v>54</v>
       </c>
       <c r="G162" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H162" s="19">
         <v>11</v>
@@ -9379,7 +9382,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M162" s="19">
         <v>0</v>
@@ -9412,7 +9415,7 @@
         <v>54</v>
       </c>
       <c r="G163" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H163" s="19">
         <v>12</v>
@@ -9427,7 +9430,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M163" s="19">
         <v>0</v>
@@ -9460,7 +9463,7 @@
         <v>56</v>
       </c>
       <c r="G164" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H164" s="19">
         <v>10</v>
@@ -9475,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M164" s="19">
         <v>0</v>
@@ -9508,7 +9511,7 @@
         <v>56</v>
       </c>
       <c r="G165" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H165" s="19">
         <v>11</v>
@@ -9523,7 +9526,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M165" s="19">
         <v>0</v>
@@ -9556,7 +9559,7 @@
         <v>56</v>
       </c>
       <c r="G166" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H166" s="19">
         <v>12</v>
@@ -9571,7 +9574,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M166" s="19">
         <v>0</v>
@@ -9604,7 +9607,7 @@
         <v>58</v>
       </c>
       <c r="G167" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H167" s="19">
         <v>10</v>
@@ -9619,7 +9622,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M167" s="19">
         <v>0</v>
@@ -9652,7 +9655,7 @@
         <v>58</v>
       </c>
       <c r="G168" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H168" s="19">
         <v>11</v>
@@ -9667,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M168" s="19">
         <v>0</v>
@@ -9700,7 +9703,7 @@
         <v>58</v>
       </c>
       <c r="G169" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H169" s="19">
         <v>12</v>
@@ -9715,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M169" s="19">
         <v>0</v>
@@ -9748,7 +9751,7 @@
         <v>60</v>
       </c>
       <c r="G170" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H170" s="1">
         <v>10</v>
@@ -9763,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M170" s="19">
         <v>0</v>
@@ -9796,7 +9799,7 @@
         <v>60</v>
       </c>
       <c r="G171" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H171" s="1">
         <v>11</v>
@@ -9811,7 +9814,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M171" s="19">
         <v>0</v>
@@ -9844,7 +9847,7 @@
         <v>60</v>
       </c>
       <c r="G172" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H172" s="1">
         <v>12</v>
@@ -9859,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M172" s="19">
         <v>0</v>
@@ -9892,7 +9895,7 @@
         <v>62</v>
       </c>
       <c r="G173" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H173" s="1">
         <v>10</v>
@@ -9907,7 +9910,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M173" s="19">
         <v>0</v>
@@ -9940,7 +9943,7 @@
         <v>62</v>
       </c>
       <c r="G174" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H174" s="1">
         <v>11</v>
@@ -9955,7 +9958,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M174" s="19">
         <v>0</v>
@@ -9988,7 +9991,7 @@
         <v>62</v>
       </c>
       <c r="G175" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H175" s="1">
         <v>12</v>
@@ -10003,7 +10006,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M175" s="19">
         <v>0</v>
@@ -10036,7 +10039,7 @@
         <v>64</v>
       </c>
       <c r="G176" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H176" s="1">
         <v>10</v>
@@ -10051,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M176" s="19">
         <v>0</v>
@@ -10084,7 +10087,7 @@
         <v>64</v>
       </c>
       <c r="G177" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H177" s="1">
         <v>11</v>
@@ -10099,7 +10102,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M177" s="19">
         <v>0</v>
@@ -10132,7 +10135,7 @@
         <v>64</v>
       </c>
       <c r="G178" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H178" s="1">
         <v>12</v>
@@ -10147,7 +10150,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M178" s="19">
         <v>0</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="794"/>
+    <workbookView windowWidth="28770" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="117">
   <si>
     <t>sid</t>
   </si>
@@ -471,6 +471,9 @@
   </si>
   <si>
     <t>南方前进-体验场</t>
+  </si>
+  <si>
+    <t>TienLenMienNamTY</t>
   </si>
   <si>
     <t>俄罗斯轮盘</t>
@@ -6382,7 +6385,9 @@
       <c r="E101" s="13">
         <v>300402001</v>
       </c>
-      <c r="F101" s="22"/>
+      <c r="F101" s="22" t="s">
+        <v>105</v>
+      </c>
       <c r="G101" s="1" t="s">
         <v>32</v>
       </c>
@@ -6428,7 +6433,9 @@
       <c r="E102" s="13">
         <v>300402001</v>
       </c>
-      <c r="F102" s="22"/>
+      <c r="F102" s="22" t="s">
+        <v>105</v>
+      </c>
       <c r="G102" s="1" t="s">
         <v>35</v>
       </c>
@@ -6474,7 +6481,9 @@
       <c r="E103" s="13">
         <v>300402001</v>
       </c>
-      <c r="F103" s="22"/>
+      <c r="F103" s="22" t="s">
+        <v>105</v>
+      </c>
       <c r="G103" s="1" t="s">
         <v>36</v>
       </c>
@@ -6515,13 +6524,13 @@
         <v>2</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E104" s="13">
         <v>201200001</v>
       </c>
       <c r="F104" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>32</v>
@@ -6562,13 +6571,13 @@
         <v>2</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E105" s="13">
         <v>201200001</v>
       </c>
       <c r="F105" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>35</v>
@@ -6609,13 +6618,13 @@
         <v>2</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E106" s="13">
         <v>201200001</v>
       </c>
       <c r="F106" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>36</v>
@@ -6665,7 +6674,7 @@
         <v>76</v>
       </c>
       <c r="G107" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H107" s="17">
         <v>10</v>
@@ -6680,7 +6689,7 @@
         <v>0</v>
       </c>
       <c r="L107" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M107" s="17">
         <v>0</v>
@@ -6712,7 +6721,7 @@
         <v>76</v>
       </c>
       <c r="G108" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H108" s="17">
         <v>11</v>
@@ -6727,7 +6736,7 @@
         <v>0</v>
       </c>
       <c r="L108" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M108" s="17">
         <v>0</v>
@@ -6759,7 +6768,7 @@
         <v>76</v>
       </c>
       <c r="G109" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H109" s="17">
         <v>12</v>
@@ -6774,7 +6783,7 @@
         <v>0</v>
       </c>
       <c r="L109" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M109" s="17">
         <v>0</v>
@@ -6806,7 +6815,7 @@
         <v>78</v>
       </c>
       <c r="G110" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H110" s="17">
         <v>10</v>
@@ -6821,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="L110" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M110" s="17">
         <v>0</v>
@@ -6853,7 +6862,7 @@
         <v>78</v>
       </c>
       <c r="G111" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H111" s="17">
         <v>11</v>
@@ -6868,7 +6877,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M111" s="17">
         <v>0</v>
@@ -6900,7 +6909,7 @@
         <v>78</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H112" s="17">
         <v>12</v>
@@ -6915,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M112" s="17">
         <v>0</v>
@@ -6947,7 +6956,7 @@
         <v>80</v>
       </c>
       <c r="G113" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H113" s="17">
         <v>10</v>
@@ -6962,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="L113" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M113" s="17">
         <v>0</v>
@@ -6994,7 +7003,7 @@
         <v>80</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H114" s="17">
         <v>11</v>
@@ -7009,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="L114" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M114" s="17">
         <v>0</v>
@@ -7041,7 +7050,7 @@
         <v>80</v>
       </c>
       <c r="G115" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H115" s="17">
         <v>12</v>
@@ -7056,7 +7065,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M115" s="17">
         <v>0</v>
@@ -7088,7 +7097,7 @@
         <v>82</v>
       </c>
       <c r="G116" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H116" s="17">
         <v>10</v>
@@ -7103,7 +7112,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M116" s="17">
         <v>0</v>
@@ -7135,7 +7144,7 @@
         <v>82</v>
       </c>
       <c r="G117" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H117" s="17">
         <v>11</v>
@@ -7150,7 +7159,7 @@
         <v>0</v>
       </c>
       <c r="L117" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M117" s="17">
         <v>0</v>
@@ -7182,7 +7191,7 @@
         <v>82</v>
       </c>
       <c r="G118" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H118" s="17">
         <v>12</v>
@@ -7197,7 +7206,7 @@
         <v>0</v>
       </c>
       <c r="L118" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M118" s="17">
         <v>0</v>
@@ -7229,7 +7238,7 @@
         <v>84</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H119" s="17">
         <v>10</v>
@@ -7244,7 +7253,7 @@
         <v>0</v>
       </c>
       <c r="L119" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M119" s="17">
         <v>0</v>
@@ -7276,7 +7285,7 @@
         <v>84</v>
       </c>
       <c r="G120" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H120" s="17">
         <v>11</v>
@@ -7291,7 +7300,7 @@
         <v>0</v>
       </c>
       <c r="L120" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M120" s="17">
         <v>0</v>
@@ -7323,7 +7332,7 @@
         <v>84</v>
       </c>
       <c r="G121" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H121" s="17">
         <v>12</v>
@@ -7338,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M121" s="17">
         <v>0</v>
@@ -7370,7 +7379,7 @@
         <v>87</v>
       </c>
       <c r="G122" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H122" s="17">
         <v>10</v>
@@ -7385,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="L122" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M122" s="17">
         <v>0</v>
@@ -7417,7 +7426,7 @@
         <v>87</v>
       </c>
       <c r="G123" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H123" s="17">
         <v>11</v>
@@ -7432,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="L123" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M123" s="17">
         <v>0</v>
@@ -7464,7 +7473,7 @@
         <v>87</v>
       </c>
       <c r="G124" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H124" s="17">
         <v>12</v>
@@ -7479,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M124" s="17">
         <v>0</v>
@@ -7511,7 +7520,7 @@
         <v>89</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H125" s="17">
         <v>10</v>
@@ -7526,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M125" s="17">
         <v>0</v>
@@ -7558,7 +7567,7 @@
         <v>89</v>
       </c>
       <c r="G126" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H126" s="17">
         <v>11</v>
@@ -7573,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M126" s="17">
         <v>0</v>
@@ -7605,7 +7614,7 @@
         <v>89</v>
       </c>
       <c r="G127" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H127" s="17">
         <v>12</v>
@@ -7620,7 +7629,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M127" s="17">
         <v>0</v>
@@ -7652,7 +7661,7 @@
         <v>91</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H128" s="17">
         <v>10</v>
@@ -7667,7 +7676,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M128" s="17">
         <v>0</v>
@@ -7699,7 +7708,7 @@
         <v>91</v>
       </c>
       <c r="G129" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H129" s="17">
         <v>11</v>
@@ -7714,7 +7723,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M129" s="17">
         <v>0</v>
@@ -7746,7 +7755,7 @@
         <v>91</v>
       </c>
       <c r="G130" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H130" s="17">
         <v>12</v>
@@ -7761,7 +7770,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M130" s="17">
         <v>0</v>
@@ -7793,7 +7802,7 @@
         <v>93</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H131" s="17">
         <v>10</v>
@@ -7808,7 +7817,7 @@
         <v>0</v>
       </c>
       <c r="L131" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M131" s="17">
         <v>0</v>
@@ -7840,7 +7849,7 @@
         <v>93</v>
       </c>
       <c r="G132" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H132" s="17">
         <v>11</v>
@@ -7855,7 +7864,7 @@
         <v>0</v>
       </c>
       <c r="L132" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M132" s="17">
         <v>0</v>
@@ -7887,7 +7896,7 @@
         <v>93</v>
       </c>
       <c r="G133" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H133" s="17">
         <v>12</v>
@@ -7902,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="L133" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M133" s="17">
         <v>0</v>
@@ -7934,7 +7943,7 @@
         <v>99</v>
       </c>
       <c r="G134" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H134" s="17">
         <v>10</v>
@@ -7949,7 +7958,7 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M134" s="17">
         <v>0</v>
@@ -7981,7 +7990,7 @@
         <v>99</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H135" s="17">
         <v>11</v>
@@ -7996,7 +8005,7 @@
         <v>0</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M135" s="17">
         <v>0</v>
@@ -8028,7 +8037,7 @@
         <v>99</v>
       </c>
       <c r="G136" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H136" s="17">
         <v>12</v>
@@ -8043,7 +8052,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M136" s="17">
         <v>0</v>
@@ -8076,7 +8085,7 @@
         <v>31</v>
       </c>
       <c r="G137" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H137" s="17">
         <v>10</v>
@@ -8091,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="L137" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M137" s="17">
         <v>0</v>
@@ -8125,7 +8134,7 @@
         <v>31</v>
       </c>
       <c r="G138" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H138" s="17">
         <v>11</v>
@@ -8140,7 +8149,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M138" s="17">
         <v>0</v>
@@ -8174,7 +8183,7 @@
         <v>31</v>
       </c>
       <c r="G139" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H139" s="17">
         <v>12</v>
@@ -8189,7 +8198,7 @@
         <v>0</v>
       </c>
       <c r="L139" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M139" s="17">
         <v>0</v>
@@ -8222,7 +8231,7 @@
         <v>38</v>
       </c>
       <c r="G140" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H140" s="17">
         <v>10</v>
@@ -8237,7 +8246,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M140" s="17">
         <v>0</v>
@@ -8272,7 +8281,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G141" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H141" s="17">
         <v>11</v>
@@ -8287,7 +8296,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M141" s="17">
         <v>0</v>
@@ -8322,7 +8331,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G142" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H142" s="17">
         <v>12</v>
@@ -8337,7 +8346,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M142" s="17">
         <v>0</v>
@@ -8370,7 +8379,7 @@
         <v>40</v>
       </c>
       <c r="G143" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H143" s="17">
         <v>10</v>
@@ -8385,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M143" s="17">
         <v>0</v>
@@ -8420,7 +8429,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G144" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H144" s="17">
         <v>11</v>
@@ -8435,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M144" s="17">
         <v>0</v>
@@ -8470,7 +8479,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H145" s="17">
         <v>12</v>
@@ -8485,7 +8494,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M145" s="17">
         <v>0</v>
@@ -8518,7 +8527,7 @@
         <v>42</v>
       </c>
       <c r="G146" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H146" s="17">
         <v>10</v>
@@ -8533,7 +8542,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M146" s="17">
         <v>0</v>
@@ -8568,7 +8577,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G147" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H147" s="17">
         <v>11</v>
@@ -8583,7 +8592,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M147" s="17">
         <v>0</v>
@@ -8618,7 +8627,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G148" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H148" s="17">
         <v>12</v>
@@ -8633,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M148" s="17">
         <v>0</v>
@@ -8666,7 +8675,7 @@
         <v>44</v>
       </c>
       <c r="G149" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H149" s="17">
         <v>10</v>
@@ -8681,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M149" s="17">
         <v>0</v>
@@ -8716,7 +8725,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H150" s="17">
         <v>11</v>
@@ -8731,7 +8740,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M150" s="17">
         <v>0</v>
@@ -8766,7 +8775,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G151" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H151" s="17">
         <v>12</v>
@@ -8781,7 +8790,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M151" s="17">
         <v>0</v>
@@ -8814,7 +8823,7 @@
         <v>46</v>
       </c>
       <c r="G152" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H152" s="17">
         <v>10</v>
@@ -8829,7 +8838,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M152" s="17">
         <v>0</v>
@@ -8863,7 +8872,7 @@
         <v>46</v>
       </c>
       <c r="G153" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H153" s="17">
         <v>11</v>
@@ -8878,7 +8887,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M153" s="17">
         <v>0</v>
@@ -8912,7 +8921,7 @@
         <v>46</v>
       </c>
       <c r="G154" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H154" s="17">
         <v>12</v>
@@ -8927,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M154" s="17">
         <v>0</v>
@@ -8960,7 +8969,7 @@
         <v>48</v>
       </c>
       <c r="G155" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H155" s="17">
         <v>10</v>
@@ -8975,7 +8984,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M155" s="17">
         <v>0</v>
@@ -9008,7 +9017,7 @@
         <v>48</v>
       </c>
       <c r="G156" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H156" s="17">
         <v>11</v>
@@ -9023,7 +9032,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M156" s="17">
         <v>0</v>
@@ -9056,7 +9065,7 @@
         <v>48</v>
       </c>
       <c r="G157" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H157" s="17">
         <v>12</v>
@@ -9071,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M157" s="17">
         <v>0</v>
@@ -9104,7 +9113,7 @@
         <v>50</v>
       </c>
       <c r="G158" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H158" s="17">
         <v>10</v>
@@ -9119,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M158" s="17">
         <v>0</v>
@@ -9152,7 +9161,7 @@
         <v>50</v>
       </c>
       <c r="G159" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H159" s="17">
         <v>11</v>
@@ -9167,7 +9176,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M159" s="17">
         <v>0</v>
@@ -9200,7 +9209,7 @@
         <v>50</v>
       </c>
       <c r="G160" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H160" s="17">
         <v>12</v>
@@ -9215,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M160" s="17">
         <v>0</v>
@@ -9248,7 +9257,7 @@
         <v>52</v>
       </c>
       <c r="G161" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H161" s="17">
         <v>10</v>
@@ -9263,7 +9272,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M161" s="17">
         <v>0</v>
@@ -9296,7 +9305,7 @@
         <v>52</v>
       </c>
       <c r="G162" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H162" s="17">
         <v>11</v>
@@ -9311,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M162" s="17">
         <v>0</v>
@@ -9344,7 +9353,7 @@
         <v>52</v>
       </c>
       <c r="G163" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H163" s="17">
         <v>12</v>
@@ -9359,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M163" s="17">
         <v>0</v>
@@ -9392,7 +9401,7 @@
         <v>54</v>
       </c>
       <c r="G164" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H164" s="17">
         <v>10</v>
@@ -9407,7 +9416,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M164" s="17">
         <v>0</v>
@@ -9440,7 +9449,7 @@
         <v>54</v>
       </c>
       <c r="G165" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H165" s="17">
         <v>11</v>
@@ -9455,7 +9464,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M165" s="17">
         <v>0</v>
@@ -9488,7 +9497,7 @@
         <v>54</v>
       </c>
       <c r="G166" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H166" s="17">
         <v>12</v>
@@ -9503,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M166" s="17">
         <v>0</v>
@@ -9536,7 +9545,7 @@
         <v>56</v>
       </c>
       <c r="G167" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H167" s="17">
         <v>10</v>
@@ -9551,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M167" s="17">
         <v>0</v>
@@ -9584,7 +9593,7 @@
         <v>56</v>
       </c>
       <c r="G168" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H168" s="17">
         <v>11</v>
@@ -9599,7 +9608,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M168" s="17">
         <v>0</v>
@@ -9632,7 +9641,7 @@
         <v>56</v>
       </c>
       <c r="G169" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H169" s="17">
         <v>12</v>
@@ -9647,7 +9656,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M169" s="17">
         <v>0</v>
@@ -9680,7 +9689,7 @@
         <v>58</v>
       </c>
       <c r="G170" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H170" s="17">
         <v>10</v>
@@ -9695,7 +9704,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M170" s="17">
         <v>0</v>
@@ -9728,7 +9737,7 @@
         <v>58</v>
       </c>
       <c r="G171" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H171" s="17">
         <v>11</v>
@@ -9743,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M171" s="17">
         <v>0</v>
@@ -9776,7 +9785,7 @@
         <v>58</v>
       </c>
       <c r="G172" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H172" s="17">
         <v>12</v>
@@ -9791,7 +9800,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M172" s="17">
         <v>0</v>
@@ -9824,7 +9833,7 @@
         <v>60</v>
       </c>
       <c r="G173" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H173" s="1">
         <v>10</v>
@@ -9839,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M173" s="17">
         <v>0</v>
@@ -9872,7 +9881,7 @@
         <v>60</v>
       </c>
       <c r="G174" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H174" s="1">
         <v>11</v>
@@ -9887,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M174" s="17">
         <v>0</v>
@@ -9920,7 +9929,7 @@
         <v>60</v>
       </c>
       <c r="G175" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H175" s="1">
         <v>12</v>
@@ -9935,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M175" s="17">
         <v>0</v>
@@ -9968,7 +9977,7 @@
         <v>62</v>
       </c>
       <c r="G176" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H176" s="1">
         <v>10</v>
@@ -9983,7 +9992,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M176" s="17">
         <v>0</v>
@@ -10016,7 +10025,7 @@
         <v>62</v>
       </c>
       <c r="G177" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H177" s="1">
         <v>11</v>
@@ -10031,7 +10040,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M177" s="17">
         <v>0</v>
@@ -10064,7 +10073,7 @@
         <v>62</v>
       </c>
       <c r="G178" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H178" s="1">
         <v>12</v>
@@ -10079,7 +10088,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M178" s="17">
         <v>0</v>
@@ -10112,7 +10121,7 @@
         <v>64</v>
       </c>
       <c r="G179" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H179" s="1">
         <v>10</v>
@@ -10127,7 +10136,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M179" s="17">
         <v>0</v>
@@ -10160,7 +10169,7 @@
         <v>64</v>
       </c>
       <c r="G180" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H180" s="1">
         <v>11</v>
@@ -10175,7 +10184,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M180" s="17">
         <v>0</v>
@@ -10208,7 +10217,7 @@
         <v>64</v>
       </c>
       <c r="G181" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H181" s="1">
         <v>12</v>
@@ -10223,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M181" s="17">
         <v>0</v>
@@ -10255,7 +10264,7 @@
         <v>102</v>
       </c>
       <c r="G182" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H182" s="1">
         <v>10</v>
@@ -10271,7 +10280,7 @@
         <v>0</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M182" s="17">
         <v>0</v>
@@ -10303,7 +10312,7 @@
         <v>102</v>
       </c>
       <c r="G183" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H183" s="1">
         <v>11</v>
@@ -10319,7 +10328,7 @@
         <v>0</v>
       </c>
       <c r="L183" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M183" s="17">
         <v>0</v>
@@ -10351,7 +10360,7 @@
         <v>102</v>
       </c>
       <c r="G184" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H184" s="1">
         <v>12</v>
@@ -10367,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M184" s="17">
         <v>0</v>
@@ -10399,7 +10408,7 @@
         <v>31</v>
       </c>
       <c r="G185" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H185" s="1">
         <v>21</v>
@@ -10446,7 +10455,7 @@
         <v>31</v>
       </c>
       <c r="G186" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H186" s="1">
         <v>22</v>
@@ -10493,7 +10502,7 @@
         <v>31</v>
       </c>
       <c r="G187" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H187" s="1">
         <v>23</v>
@@ -10540,7 +10549,7 @@
         <v>38</v>
       </c>
       <c r="G188" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H188" s="1">
         <v>21</v>
@@ -10587,7 +10596,7 @@
         <v>38</v>
       </c>
       <c r="G189" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H189" s="1">
         <v>22</v>
@@ -10634,7 +10643,7 @@
         <v>38</v>
       </c>
       <c r="G190" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H190" s="1">
         <v>23</v>
@@ -10681,7 +10690,7 @@
         <v>40</v>
       </c>
       <c r="G191" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H191" s="1">
         <v>21</v>
@@ -10728,7 +10737,7 @@
         <v>40</v>
       </c>
       <c r="G192" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H192" s="1">
         <v>22</v>
@@ -10775,7 +10784,7 @@
         <v>40</v>
       </c>
       <c r="G193" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H193" s="1">
         <v>23</v>
@@ -10822,7 +10831,7 @@
         <v>42</v>
       </c>
       <c r="G194" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H194" s="1">
         <v>21</v>
@@ -10869,7 +10878,7 @@
         <v>42</v>
       </c>
       <c r="G195" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H195" s="1">
         <v>22</v>
@@ -10916,7 +10925,7 @@
         <v>42</v>
       </c>
       <c r="G196" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H196" s="1">
         <v>23</v>
@@ -10963,7 +10972,7 @@
         <v>44</v>
       </c>
       <c r="G197" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H197" s="1">
         <v>21</v>
@@ -11010,7 +11019,7 @@
         <v>44</v>
       </c>
       <c r="G198" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H198" s="1">
         <v>22</v>
@@ -11057,7 +11066,7 @@
         <v>44</v>
       </c>
       <c r="G199" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H199" s="1">
         <v>23</v>
@@ -11104,7 +11113,7 @@
         <v>46</v>
       </c>
       <c r="G200" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H200" s="1">
         <v>21</v>
@@ -11151,7 +11160,7 @@
         <v>46</v>
       </c>
       <c r="G201" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H201" s="1">
         <v>22</v>
@@ -11198,7 +11207,7 @@
         <v>46</v>
       </c>
       <c r="G202" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H202" s="1">
         <v>23</v>
@@ -11245,7 +11254,7 @@
         <v>48</v>
       </c>
       <c r="G203" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H203" s="1">
         <v>21</v>
@@ -11292,7 +11301,7 @@
         <v>48</v>
       </c>
       <c r="G204" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H204" s="1">
         <v>22</v>
@@ -11339,7 +11348,7 @@
         <v>48</v>
       </c>
       <c r="G205" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H205" s="1">
         <v>23</v>
@@ -11386,7 +11395,7 @@
         <v>50</v>
       </c>
       <c r="G206" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H206" s="1">
         <v>21</v>
@@ -11433,7 +11442,7 @@
         <v>50</v>
       </c>
       <c r="G207" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H207" s="1">
         <v>22</v>
@@ -11480,7 +11489,7 @@
         <v>50</v>
       </c>
       <c r="G208" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H208" s="1">
         <v>23</v>
@@ -11527,7 +11536,7 @@
         <v>52</v>
       </c>
       <c r="G209" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H209" s="1">
         <v>21</v>
@@ -11574,7 +11583,7 @@
         <v>52</v>
       </c>
       <c r="G210" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H210" s="1">
         <v>22</v>
@@ -11621,7 +11630,7 @@
         <v>52</v>
       </c>
       <c r="G211" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H211" s="1">
         <v>23</v>
@@ -11669,7 +11678,7 @@
         <v>54</v>
       </c>
       <c r="G212" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H212" s="1">
         <v>21</v>
@@ -11717,7 +11726,7 @@
         <v>54</v>
       </c>
       <c r="G213" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H213" s="1">
         <v>22</v>
@@ -11765,7 +11774,7 @@
         <v>54</v>
       </c>
       <c r="G214" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H214" s="1">
         <v>23</v>
@@ -11813,7 +11822,7 @@
         <v>56</v>
       </c>
       <c r="G215" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H215" s="1">
         <v>21</v>
@@ -11861,7 +11870,7 @@
         <v>56</v>
       </c>
       <c r="G216" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H216" s="1">
         <v>22</v>
@@ -11909,7 +11918,7 @@
         <v>56</v>
       </c>
       <c r="G217" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H217" s="1">
         <v>23</v>
@@ -11957,7 +11966,7 @@
         <v>58</v>
       </c>
       <c r="G218" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H218" s="1">
         <v>21</v>
@@ -12005,7 +12014,7 @@
         <v>58</v>
       </c>
       <c r="G219" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H219" s="1">
         <v>22</v>
@@ -12053,7 +12062,7 @@
         <v>58</v>
       </c>
       <c r="G220" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H220" s="1">
         <v>23</v>
@@ -12100,7 +12109,7 @@
         <v>60</v>
       </c>
       <c r="G221" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H221" s="1">
         <v>21</v>
@@ -12147,7 +12156,7 @@
         <v>60</v>
       </c>
       <c r="G222" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H222" s="1">
         <v>22</v>
@@ -12194,7 +12203,7 @@
         <v>60</v>
       </c>
       <c r="G223" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H223" s="1">
         <v>23</v>
@@ -12242,7 +12251,7 @@
         <v>62</v>
       </c>
       <c r="G224" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H224" s="1">
         <v>21</v>
@@ -12290,7 +12299,7 @@
         <v>62</v>
       </c>
       <c r="G225" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H225" s="1">
         <v>22</v>
@@ -12338,7 +12347,7 @@
         <v>62</v>
       </c>
       <c r="G226" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H226" s="1">
         <v>23</v>
@@ -12385,7 +12394,7 @@
         <v>64</v>
       </c>
       <c r="G227" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H227" s="1">
         <v>21</v>
@@ -12432,7 +12441,7 @@
         <v>64</v>
       </c>
       <c r="G228" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H228" s="1">
         <v>22</v>
@@ -12479,7 +12488,7 @@
         <v>64</v>
       </c>
       <c r="G229" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H229" s="1">
         <v>23</v>
@@ -12526,7 +12535,7 @@
         <v>66</v>
       </c>
       <c r="G230" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H230" s="1">
         <v>21</v>
@@ -12573,7 +12582,7 @@
         <v>66</v>
       </c>
       <c r="G231" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H231" s="1">
         <v>22</v>
@@ -12620,7 +12629,7 @@
         <v>66</v>
       </c>
       <c r="G232" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H232" s="1">
         <v>23</v>
@@ -12668,7 +12677,7 @@
         <v>68</v>
       </c>
       <c r="G233" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H233" s="1">
         <v>21</v>
@@ -12716,7 +12725,7 @@
         <v>68</v>
       </c>
       <c r="G234" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H234" s="1">
         <v>22</v>
@@ -12764,7 +12773,7 @@
         <v>68</v>
       </c>
       <c r="G235" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H235" s="1">
         <v>23</v>
@@ -12811,7 +12820,7 @@
         <v>70</v>
       </c>
       <c r="G236" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H236" s="1">
         <v>21</v>
@@ -12858,7 +12867,7 @@
         <v>70</v>
       </c>
       <c r="G237" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H237" s="1">
         <v>22</v>
@@ -12905,7 +12914,7 @@
         <v>70</v>
       </c>
       <c r="G238" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H238" s="1">
         <v>23</v>
@@ -12952,7 +12961,7 @@
         <v>72</v>
       </c>
       <c r="G239" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H239" s="1">
         <v>21</v>
@@ -12999,7 +13008,7 @@
         <v>72</v>
       </c>
       <c r="G240" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H240" s="1">
         <v>22</v>
@@ -13046,7 +13055,7 @@
         <v>72</v>
       </c>
       <c r="G241" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H241" s="1">
         <v>23</v>
@@ -13093,7 +13102,7 @@
         <v>74</v>
       </c>
       <c r="G242" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H242" s="1">
         <v>21</v>
@@ -13140,7 +13149,7 @@
         <v>74</v>
       </c>
       <c r="G243" s="27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H243" s="1">
         <v>22</v>
@@ -13187,7 +13196,7 @@
         <v>74</v>
       </c>
       <c r="G244" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H244" s="1">
         <v>23</v>
@@ -14949,13 +14958,13 @@
         <v>2</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E281" s="13">
         <v>201200001</v>
       </c>
       <c r="F281" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>32</v>
@@ -14996,13 +15005,13 @@
         <v>2</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E282" s="13">
         <v>201200001</v>
       </c>
       <c r="F282" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>35</v>
@@ -15043,13 +15052,13 @@
         <v>2</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E283" s="13">
         <v>201200001</v>
       </c>
       <c r="F283" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>36</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="117">
   <si>
     <t>sid</t>
   </si>
@@ -470,9 +470,6 @@
     <t>4:4</t>
   </si>
   <si>
-    <t>南方前进-体验场</t>
-  </si>
-  <si>
     <t>俄罗斯轮盘</t>
   </si>
   <si>
@@ -504,6 +501,12 @@
   </si>
   <si>
     <t>高级场-特殊</t>
+  </si>
+  <si>
+    <t>南方前进-体验场</t>
+  </si>
+  <si>
+    <t>TienLenMienNamTY</t>
   </si>
 </sst>
 </file>
@@ -716,12 +719,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6248,7 +6251,7 @@
         <v>1</v>
       </c>
       <c r="I98" s="23">
-        <f t="shared" ref="I98:I103" si="1">N98*52</f>
+        <f>N98*52</f>
         <v>5200</v>
       </c>
       <c r="J98" s="1">
@@ -6296,7 +6299,7 @@
         <v>2</v>
       </c>
       <c r="I99" s="23">
-        <f t="shared" si="1"/>
+        <f>N99*52</f>
         <v>52000</v>
       </c>
       <c r="J99" s="1">
@@ -6344,7 +6347,7 @@
         <v>3</v>
       </c>
       <c r="I100" s="23">
-        <f t="shared" si="1"/>
+        <f>N100*52</f>
         <v>520000</v>
       </c>
       <c r="J100" s="1">
@@ -6368,30 +6371,31 @@
     </row>
     <row r="101" spans="1:15">
       <c r="A101" s="1">
-        <v>3004021</v>
+        <v>2012001</v>
       </c>
       <c r="B101" s="4">
-        <v>300402</v>
-      </c>
-      <c r="C101" s="1">
-        <v>3</v>
+        <v>201200</v>
+      </c>
+      <c r="C101" s="4">
+        <v>2</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>104</v>
       </c>
       <c r="E101" s="13">
-        <v>300402001</v>
-      </c>
-      <c r="F101" s="22"/>
+        <v>201200001</v>
+      </c>
+      <c r="F101" s="22" t="s">
+        <v>105</v>
+      </c>
       <c r="G101" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H101" s="1">
         <v>1</v>
       </c>
-      <c r="I101" s="23">
-        <f t="shared" si="1"/>
-        <v>5200</v>
+      <c r="I101" s="2">
+        <v>0</v>
       </c>
       <c r="J101" s="1">
         <v>-1</v>
@@ -6400,44 +6404,45 @@
         <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M101" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N101" s="23">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="N101">
+        <v>1000</v>
       </c>
       <c r="O101" s="15">
-        <v>1970000</v>
+        <v>1990000</v>
       </c>
     </row>
     <row r="102" spans="1:15">
       <c r="A102" s="1">
-        <v>3004022</v>
+        <v>2012002</v>
       </c>
       <c r="B102" s="4">
-        <v>300402</v>
+        <v>201200</v>
       </c>
       <c r="C102" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>104</v>
       </c>
       <c r="E102" s="13">
-        <v>300402001</v>
-      </c>
-      <c r="F102" s="22"/>
+        <v>201200001</v>
+      </c>
+      <c r="F102" s="22" t="s">
+        <v>105</v>
+      </c>
       <c r="G102" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H102" s="1">
         <v>2</v>
       </c>
-      <c r="I102" s="23">
-        <f t="shared" si="1"/>
-        <v>52000</v>
+      <c r="I102" s="2">
+        <v>10000</v>
       </c>
       <c r="J102" s="1">
         <v>-1</v>
@@ -6446,44 +6451,45 @@
         <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M102" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N102" s="23">
-        <v>1000</v>
+        <v>85</v>
+      </c>
+      <c r="N102">
+        <v>10000</v>
       </c>
       <c r="O102" s="15">
-        <v>1970000</v>
+        <v>1990000</v>
       </c>
     </row>
     <row r="103" spans="1:15">
       <c r="A103" s="1">
-        <v>3004023</v>
+        <v>2012003</v>
       </c>
       <c r="B103" s="4">
-        <v>300402</v>
+        <v>201200</v>
       </c>
       <c r="C103" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>104</v>
       </c>
       <c r="E103" s="13">
-        <v>300402001</v>
-      </c>
-      <c r="F103" s="22"/>
+        <v>201200001</v>
+      </c>
+      <c r="F103" s="22" t="s">
+        <v>105</v>
+      </c>
       <c r="G103" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H103" s="1">
         <v>3</v>
       </c>
-      <c r="I103" s="23">
-        <f t="shared" si="1"/>
-        <v>520000</v>
+      <c r="I103" s="2">
+        <v>100000</v>
       </c>
       <c r="J103" s="1">
         <v>-1</v>
@@ -6492,180 +6498,180 @@
         <v>0</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M103" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N103" s="23">
-        <v>10000</v>
+        <v>85</v>
+      </c>
+      <c r="N103">
+        <v>100000</v>
       </c>
       <c r="O103" s="15">
-        <v>1970000</v>
+        <v>1990000</v>
       </c>
     </row>
     <row r="104" spans="1:15">
       <c r="A104" s="1">
-        <v>2012001</v>
-      </c>
-      <c r="B104" s="4">
-        <v>201200</v>
-      </c>
-      <c r="C104" s="4">
+        <v>20010010</v>
+      </c>
+      <c r="B104" s="16">
+        <v>200100</v>
+      </c>
+      <c r="C104" s="16">
         <v>2</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E104" s="13">
-        <v>201200001</v>
-      </c>
-      <c r="F104" s="22" t="s">
+      <c r="D104" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E104" s="16">
+        <v>200100038</v>
+      </c>
+      <c r="F104" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G104" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="G104" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H104" s="1">
-        <v>1</v>
-      </c>
-      <c r="I104" s="2">
-        <v>0</v>
-      </c>
-      <c r="J104" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K104" s="1">
-        <v>0</v>
-      </c>
-      <c r="L104" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M104" s="28" t="s">
-        <v>85</v>
+      <c r="H104" s="17">
+        <v>10</v>
+      </c>
+      <c r="I104" s="24">
+        <v>0</v>
+      </c>
+      <c r="J104" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K104" s="17">
+        <v>0</v>
+      </c>
+      <c r="L104" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="M104" s="17">
+        <v>0</v>
       </c>
       <c r="N104">
         <v>1000</v>
       </c>
-      <c r="O104" s="15">
-        <v>1990000</v>
+      <c r="O104" s="26">
+        <v>1980000</v>
       </c>
     </row>
     <row r="105" spans="1:15">
       <c r="A105" s="1">
-        <v>2012002</v>
-      </c>
-      <c r="B105" s="4">
-        <v>201200</v>
-      </c>
-      <c r="C105" s="4">
+        <v>20010011</v>
+      </c>
+      <c r="B105" s="16">
+        <v>200100</v>
+      </c>
+      <c r="C105" s="16">
         <v>2</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E105" s="13">
-        <v>201200001</v>
-      </c>
-      <c r="F105" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H105" s="1">
-        <v>2</v>
-      </c>
-      <c r="I105" s="2">
-        <v>10000</v>
-      </c>
-      <c r="J105" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K105" s="1">
-        <v>0</v>
-      </c>
-      <c r="L105" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M105" s="28" t="s">
-        <v>85</v>
+      <c r="D105" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E105" s="16">
+        <v>200100038</v>
+      </c>
+      <c r="F105" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G105" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="H105" s="17">
+        <v>11</v>
+      </c>
+      <c r="I105" s="24">
+        <v>0</v>
+      </c>
+      <c r="J105" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K105" s="17">
+        <v>0</v>
+      </c>
+      <c r="L105" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="M105" s="17">
+        <v>0</v>
       </c>
       <c r="N105">
         <v>10000</v>
       </c>
-      <c r="O105" s="15">
-        <v>1990000</v>
+      <c r="O105" s="26">
+        <v>1980000</v>
       </c>
     </row>
     <row r="106" spans="1:15">
       <c r="A106" s="1">
-        <v>2012003</v>
-      </c>
-      <c r="B106" s="4">
-        <v>201200</v>
-      </c>
-      <c r="C106" s="4">
+        <v>20010012</v>
+      </c>
+      <c r="B106" s="16">
+        <v>200100</v>
+      </c>
+      <c r="C106" s="16">
         <v>2</v>
       </c>
-      <c r="D106" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E106" s="13">
-        <v>201200001</v>
-      </c>
-      <c r="F106" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H106" s="1">
-        <v>3</v>
-      </c>
-      <c r="I106" s="2">
-        <v>100000</v>
-      </c>
-      <c r="J106" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K106" s="1">
-        <v>0</v>
-      </c>
-      <c r="L106" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M106" s="28" t="s">
-        <v>85</v>
+      <c r="D106" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E106" s="16">
+        <v>200100038</v>
+      </c>
+      <c r="F106" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G106" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H106" s="17">
+        <v>12</v>
+      </c>
+      <c r="I106" s="24">
+        <v>0</v>
+      </c>
+      <c r="J106" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K106" s="17">
+        <v>0</v>
+      </c>
+      <c r="L106" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="M106" s="17">
+        <v>0</v>
       </c>
       <c r="N106">
         <v>100000</v>
       </c>
-      <c r="O106" s="15">
-        <v>1990000</v>
+      <c r="O106" s="26">
+        <v>1980000</v>
       </c>
     </row>
     <row r="107" spans="1:15">
       <c r="A107" s="1">
-        <v>20010010</v>
+        <v>20010110</v>
       </c>
       <c r="B107" s="16">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C107" s="16">
         <v>2</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E107" s="16">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F107" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G107" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H107" s="17">
         <v>10</v>
@@ -6680,7 +6686,7 @@
         <v>0</v>
       </c>
       <c r="L107" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M107" s="17">
         <v>0</v>
@@ -6694,25 +6700,25 @@
     </row>
     <row r="108" spans="1:15">
       <c r="A108" s="1">
-        <v>20010011</v>
+        <v>20010111</v>
       </c>
       <c r="B108" s="16">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C108" s="16">
         <v>2</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E108" s="16">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F108" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G108" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H108" s="17">
         <v>11</v>
@@ -6727,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="L108" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M108" s="17">
         <v>0</v>
@@ -6741,25 +6747,25 @@
     </row>
     <row r="109" spans="1:15">
       <c r="A109" s="1">
-        <v>20010012</v>
+        <v>20010112</v>
       </c>
       <c r="B109" s="16">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C109" s="16">
         <v>2</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E109" s="16">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F109" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G109" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H109" s="17">
         <v>12</v>
@@ -6774,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="L109" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M109" s="17">
         <v>0</v>
@@ -6788,25 +6794,25 @@
     </row>
     <row r="110" spans="1:15">
       <c r="A110" s="1">
-        <v>20010110</v>
+        <v>20030010</v>
       </c>
       <c r="B110" s="16">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C110" s="16">
         <v>2</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E110" s="16">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F110" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G110" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H110" s="17">
         <v>10</v>
@@ -6821,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="L110" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M110" s="17">
         <v>0</v>
@@ -6835,25 +6841,25 @@
     </row>
     <row r="111" spans="1:15">
       <c r="A111" s="1">
-        <v>20010111</v>
+        <v>20030011</v>
       </c>
       <c r="B111" s="16">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C111" s="16">
         <v>2</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E111" s="16">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F111" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G111" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H111" s="17">
         <v>11</v>
@@ -6868,7 +6874,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M111" s="17">
         <v>0</v>
@@ -6882,25 +6888,25 @@
     </row>
     <row r="112" spans="1:15">
       <c r="A112" s="1">
-        <v>20010112</v>
+        <v>20030012</v>
       </c>
       <c r="B112" s="16">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C112" s="16">
         <v>2</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E112" s="16">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F112" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H112" s="17">
         <v>12</v>
@@ -6915,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M112" s="17">
         <v>0</v>
@@ -6929,25 +6935,25 @@
     </row>
     <row r="113" spans="1:15">
       <c r="A113" s="1">
-        <v>20030010</v>
+        <v>20040010</v>
       </c>
       <c r="B113" s="16">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C113" s="16">
         <v>2</v>
       </c>
-      <c r="D113" s="16" t="s">
-        <v>79</v>
+      <c r="D113" s="24" t="s">
+        <v>81</v>
       </c>
       <c r="E113" s="16">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F113" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G113" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H113" s="17">
         <v>10</v>
@@ -6962,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="L113" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M113" s="17">
         <v>0</v>
@@ -6976,25 +6982,25 @@
     </row>
     <row r="114" spans="1:15">
       <c r="A114" s="1">
-        <v>20030011</v>
+        <v>20040011</v>
       </c>
       <c r="B114" s="16">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C114" s="16">
         <v>2</v>
       </c>
-      <c r="D114" s="16" t="s">
-        <v>79</v>
+      <c r="D114" s="24" t="s">
+        <v>81</v>
       </c>
       <c r="E114" s="16">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H114" s="17">
         <v>11</v>
@@ -7009,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="L114" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M114" s="17">
         <v>0</v>
@@ -7023,25 +7029,25 @@
     </row>
     <row r="115" spans="1:15">
       <c r="A115" s="1">
-        <v>20030012</v>
+        <v>20040012</v>
       </c>
       <c r="B115" s="16">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C115" s="16">
         <v>2</v>
       </c>
-      <c r="D115" s="16" t="s">
-        <v>79</v>
+      <c r="D115" s="24" t="s">
+        <v>81</v>
       </c>
       <c r="E115" s="16">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F115" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G115" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H115" s="17">
         <v>12</v>
@@ -7056,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M115" s="17">
         <v>0</v>
@@ -7070,25 +7076,25 @@
     </row>
     <row r="116" spans="1:15">
       <c r="A116" s="1">
-        <v>20040010</v>
+        <v>20050010</v>
       </c>
       <c r="B116" s="16">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C116" s="16">
         <v>2</v>
       </c>
-      <c r="D116" s="24" t="s">
-        <v>81</v>
+      <c r="D116" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="E116" s="16">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F116" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G116" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H116" s="17">
         <v>10</v>
@@ -7103,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M116" s="17">
         <v>0</v>
@@ -7117,25 +7123,25 @@
     </row>
     <row r="117" spans="1:15">
       <c r="A117" s="1">
-        <v>20040011</v>
+        <v>20050011</v>
       </c>
       <c r="B117" s="16">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C117" s="16">
         <v>2</v>
       </c>
-      <c r="D117" s="24" t="s">
-        <v>81</v>
+      <c r="D117" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="E117" s="16">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F117" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G117" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H117" s="17">
         <v>11</v>
@@ -7150,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="L117" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M117" s="17">
         <v>0</v>
@@ -7164,25 +7170,25 @@
     </row>
     <row r="118" spans="1:15">
       <c r="A118" s="1">
-        <v>20040012</v>
+        <v>20050012</v>
       </c>
       <c r="B118" s="16">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C118" s="16">
         <v>2</v>
       </c>
-      <c r="D118" s="24" t="s">
-        <v>81</v>
+      <c r="D118" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="E118" s="16">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F118" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G118" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H118" s="17">
         <v>12</v>
@@ -7197,7 +7203,7 @@
         <v>0</v>
       </c>
       <c r="L118" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M118" s="17">
         <v>0</v>
@@ -7211,25 +7217,25 @@
     </row>
     <row r="119" spans="1:15">
       <c r="A119" s="1">
-        <v>20050010</v>
+        <v>20060010</v>
       </c>
       <c r="B119" s="16">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C119" s="16">
         <v>2</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E119" s="16">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F119" s="16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H119" s="17">
         <v>10</v>
@@ -7244,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="L119" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M119" s="17">
         <v>0</v>
@@ -7258,25 +7264,25 @@
     </row>
     <row r="120" spans="1:15">
       <c r="A120" s="1">
-        <v>20050011</v>
+        <v>20060011</v>
       </c>
       <c r="B120" s="16">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C120" s="16">
         <v>2</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E120" s="16">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F120" s="16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G120" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H120" s="17">
         <v>11</v>
@@ -7291,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L120" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M120" s="17">
         <v>0</v>
@@ -7305,25 +7311,25 @@
     </row>
     <row r="121" spans="1:15">
       <c r="A121" s="1">
-        <v>20050012</v>
+        <v>20060012</v>
       </c>
       <c r="B121" s="16">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C121" s="16">
         <v>2</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E121" s="16">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F121" s="16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G121" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H121" s="17">
         <v>12</v>
@@ -7338,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M121" s="17">
         <v>0</v>
@@ -7352,25 +7358,25 @@
     </row>
     <row r="122" spans="1:15">
       <c r="A122" s="1">
-        <v>20060010</v>
+        <v>20070010</v>
       </c>
       <c r="B122" s="16">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C122" s="16">
         <v>2</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E122" s="16">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F122" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G122" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H122" s="17">
         <v>10</v>
@@ -7385,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="L122" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M122" s="17">
         <v>0</v>
@@ -7399,25 +7405,25 @@
     </row>
     <row r="123" spans="1:15">
       <c r="A123" s="1">
-        <v>20060011</v>
+        <v>20070011</v>
       </c>
       <c r="B123" s="16">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C123" s="16">
         <v>2</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E123" s="16">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F123" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G123" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H123" s="17">
         <v>11</v>
@@ -7432,7 +7438,7 @@
         <v>0</v>
       </c>
       <c r="L123" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M123" s="17">
         <v>0</v>
@@ -7446,25 +7452,25 @@
     </row>
     <row r="124" spans="1:15">
       <c r="A124" s="1">
-        <v>20060012</v>
+        <v>20070012</v>
       </c>
       <c r="B124" s="16">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C124" s="16">
         <v>2</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E124" s="16">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F124" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G124" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H124" s="17">
         <v>12</v>
@@ -7479,7 +7485,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M124" s="17">
         <v>0</v>
@@ -7493,25 +7499,25 @@
     </row>
     <row r="125" spans="1:15">
       <c r="A125" s="1">
-        <v>20070010</v>
+        <v>20080010</v>
       </c>
       <c r="B125" s="16">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C125" s="16">
         <v>2</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E125" s="16">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F125" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H125" s="17">
         <v>10</v>
@@ -7526,7 +7532,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M125" s="17">
         <v>0</v>
@@ -7540,25 +7546,25 @@
     </row>
     <row r="126" spans="1:15">
       <c r="A126" s="1">
-        <v>20070011</v>
+        <v>20080011</v>
       </c>
       <c r="B126" s="16">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C126" s="16">
         <v>2</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E126" s="16">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F126" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G126" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H126" s="17">
         <v>11</v>
@@ -7573,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M126" s="17">
         <v>0</v>
@@ -7587,25 +7593,25 @@
     </row>
     <row r="127" spans="1:15">
       <c r="A127" s="1">
-        <v>20070012</v>
+        <v>20080012</v>
       </c>
       <c r="B127" s="16">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C127" s="16">
         <v>2</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E127" s="16">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F127" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G127" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H127" s="17">
         <v>12</v>
@@ -7620,7 +7626,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M127" s="17">
         <v>0</v>
@@ -7634,25 +7640,25 @@
     </row>
     <row r="128" spans="1:15">
       <c r="A128" s="1">
-        <v>20080010</v>
+        <v>20090010</v>
       </c>
       <c r="B128" s="16">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C128" s="16">
         <v>2</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E128" s="16">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F128" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H128" s="17">
         <v>10</v>
@@ -7667,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M128" s="17">
         <v>0</v>
@@ -7681,25 +7687,25 @@
     </row>
     <row r="129" spans="1:15">
       <c r="A129" s="1">
-        <v>20080011</v>
+        <v>20090011</v>
       </c>
       <c r="B129" s="16">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C129" s="16">
         <v>2</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E129" s="16">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F129" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G129" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H129" s="17">
         <v>11</v>
@@ -7714,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M129" s="17">
         <v>0</v>
@@ -7728,25 +7734,25 @@
     </row>
     <row r="130" spans="1:15">
       <c r="A130" s="1">
-        <v>20080012</v>
+        <v>20090012</v>
       </c>
       <c r="B130" s="16">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C130" s="16">
         <v>2</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E130" s="16">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F130" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G130" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H130" s="17">
         <v>12</v>
@@ -7761,7 +7767,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M130" s="17">
         <v>0</v>
@@ -7775,25 +7781,25 @@
     </row>
     <row r="131" spans="1:15">
       <c r="A131" s="1">
-        <v>20090010</v>
+        <v>30020010</v>
       </c>
       <c r="B131" s="16">
-        <v>200900</v>
+        <v>300200</v>
       </c>
       <c r="C131" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E131" s="16">
-        <v>200900001</v>
+        <v>300200006</v>
       </c>
       <c r="F131" s="16" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H131" s="17">
         <v>10</v>
@@ -7807,13 +7813,13 @@
       <c r="K131" s="17">
         <v>0</v>
       </c>
-      <c r="L131" s="25" t="s">
-        <v>108</v>
+      <c r="L131" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="M131" s="17">
         <v>0</v>
       </c>
-      <c r="N131">
+      <c r="N131" s="21">
         <v>1000</v>
       </c>
       <c r="O131" s="26">
@@ -7822,25 +7828,25 @@
     </row>
     <row r="132" spans="1:15">
       <c r="A132" s="1">
-        <v>20090011</v>
+        <v>30020011</v>
       </c>
       <c r="B132" s="16">
-        <v>200900</v>
+        <v>300200</v>
       </c>
       <c r="C132" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E132" s="16">
-        <v>200900001</v>
+        <v>300200006</v>
       </c>
       <c r="F132" s="16" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G132" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H132" s="17">
         <v>11</v>
@@ -7854,13 +7860,13 @@
       <c r="K132" s="17">
         <v>0</v>
       </c>
-      <c r="L132" s="25" t="s">
-        <v>108</v>
+      <c r="L132" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="M132" s="17">
         <v>0</v>
       </c>
-      <c r="N132">
+      <c r="N132" s="21">
         <v>10000</v>
       </c>
       <c r="O132" s="26">
@@ -7869,25 +7875,25 @@
     </row>
     <row r="133" spans="1:15">
       <c r="A133" s="1">
-        <v>20090012</v>
+        <v>30020012</v>
       </c>
       <c r="B133" s="16">
-        <v>200900</v>
+        <v>300200</v>
       </c>
       <c r="C133" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E133" s="16">
-        <v>200900001</v>
+        <v>300200006</v>
       </c>
       <c r="F133" s="16" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G133" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H133" s="17">
         <v>12</v>
@@ -7901,13 +7907,13 @@
       <c r="K133" s="17">
         <v>0</v>
       </c>
-      <c r="L133" s="25" t="s">
-        <v>108</v>
+      <c r="L133" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="M133" s="17">
         <v>0</v>
       </c>
-      <c r="N133">
+      <c r="N133" s="21">
         <v>100000</v>
       </c>
       <c r="O133" s="26">
@@ -7916,25 +7922,26 @@
     </row>
     <row r="134" spans="1:15">
       <c r="A134" s="1">
-        <v>30020010</v>
+        <f>B134*100+H134</f>
+        <v>10010010</v>
       </c>
       <c r="B134" s="16">
-        <v>300200</v>
+        <v>100100</v>
       </c>
       <c r="C134" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="E134" s="16">
-        <v>300200006</v>
+        <v>100100026</v>
       </c>
       <c r="F134" s="16" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G134" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H134" s="17">
         <v>10</v>
@@ -7948,13 +7955,13 @@
       <c r="K134" s="17">
         <v>0</v>
       </c>
-      <c r="L134" s="3" t="s">
-        <v>111</v>
+      <c r="L134" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="M134" s="17">
         <v>0</v>
       </c>
-      <c r="N134" s="21">
+      <c r="N134">
         <v>1000</v>
       </c>
       <c r="O134" s="26">
@@ -7963,25 +7970,27 @@
     </row>
     <row r="135" spans="1:15">
       <c r="A135" s="1">
-        <v>30020011</v>
+        <f>B135*100+H135</f>
+        <v>10010011</v>
       </c>
       <c r="B135" s="16">
-        <v>300200</v>
+        <v>100100</v>
       </c>
       <c r="C135" s="16">
-        <v>3</v>
-      </c>
-      <c r="D135" s="16" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="D135" s="16" t="str">
+        <f t="shared" ref="D135:D139" si="1">D134</f>
+        <v>金礦大亨</v>
       </c>
       <c r="E135" s="16">
-        <v>300200006</v>
+        <v>100100026</v>
       </c>
       <c r="F135" s="16" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H135" s="17">
         <v>11</v>
@@ -7995,13 +8004,13 @@
       <c r="K135" s="17">
         <v>0</v>
       </c>
-      <c r="L135" s="3" t="s">
-        <v>111</v>
+      <c r="L135" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="M135" s="17">
         <v>0</v>
       </c>
-      <c r="N135" s="21">
+      <c r="N135">
         <v>10000</v>
       </c>
       <c r="O135" s="26">
@@ -8010,25 +8019,27 @@
     </row>
     <row r="136" spans="1:15">
       <c r="A136" s="1">
-        <v>30020012</v>
+        <f>B136*100+H136</f>
+        <v>10010012</v>
       </c>
       <c r="B136" s="16">
-        <v>300200</v>
+        <v>100100</v>
       </c>
       <c r="C136" s="16">
-        <v>3</v>
-      </c>
-      <c r="D136" s="16" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="D136" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>金礦大亨</v>
       </c>
       <c r="E136" s="16">
-        <v>300200006</v>
+        <v>100100026</v>
       </c>
       <c r="F136" s="16" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G136" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H136" s="17">
         <v>12</v>
@@ -8042,13 +8053,13 @@
       <c r="K136" s="17">
         <v>0</v>
       </c>
-      <c r="L136" s="3" t="s">
-        <v>111</v>
+      <c r="L136" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="M136" s="17">
         <v>0</v>
       </c>
-      <c r="N136" s="21">
+      <c r="N136">
         <v>100000</v>
       </c>
       <c r="O136" s="26">
@@ -8057,26 +8068,26 @@
     </row>
     <row r="137" spans="1:15">
       <c r="A137" s="1">
-        <f>B137*100+H137</f>
-        <v>10010010</v>
+        <f t="shared" ref="A137:A178" si="2">B137*100+H137</f>
+        <v>10030010</v>
       </c>
       <c r="B137" s="16">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C137" s="16">
         <v>1</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E137" s="16">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="F137" s="16" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G137" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H137" s="17">
         <v>10</v>
@@ -8091,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="L137" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M137" s="17">
         <v>0</v>
@@ -8105,27 +8116,28 @@
     </row>
     <row r="138" spans="1:15">
       <c r="A138" s="1">
-        <f>B138*100+H138</f>
-        <v>10010011</v>
+        <f t="shared" si="2"/>
+        <v>10030011</v>
       </c>
       <c r="B138" s="16">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C138" s="16">
         <v>1</v>
       </c>
       <c r="D138" s="16" t="str">
-        <f t="shared" ref="D138:D142" si="2">D137</f>
-        <v>金礦大亨</v>
+        <f t="shared" si="1"/>
+        <v>超级明星</v>
       </c>
       <c r="E138" s="16">
-        <v>100100026</v>
-      </c>
-      <c r="F138" s="16" t="s">
-        <v>31</v>
+        <v>100300001</v>
+      </c>
+      <c r="F138" s="16" t="str">
+        <f t="shared" ref="F138:F142" si="3">F137</f>
+        <v>SuperStar</v>
       </c>
       <c r="G138" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H138" s="17">
         <v>11</v>
@@ -8140,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M138" s="17">
         <v>0</v>
@@ -8154,27 +8166,28 @@
     </row>
     <row r="139" spans="1:15">
       <c r="A139" s="1">
-        <f>B139*100+H139</f>
-        <v>10010012</v>
+        <f t="shared" si="2"/>
+        <v>10030012</v>
       </c>
       <c r="B139" s="16">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C139" s="16">
         <v>1</v>
       </c>
       <c r="D139" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v>金礦大亨</v>
+        <f t="shared" si="1"/>
+        <v>超级明星</v>
       </c>
       <c r="E139" s="16">
-        <v>100100026</v>
-      </c>
-      <c r="F139" s="16" t="s">
-        <v>31</v>
+        <v>100300001</v>
+      </c>
+      <c r="F139" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>SuperStar</v>
       </c>
       <c r="G139" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H139" s="17">
         <v>12</v>
@@ -8189,7 +8202,7 @@
         <v>0</v>
       </c>
       <c r="L139" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M139" s="17">
         <v>0</v>
@@ -8203,26 +8216,26 @@
     </row>
     <row r="140" spans="1:15">
       <c r="A140" s="1">
-        <f t="shared" ref="A140:A181" si="3">B140*100+H140</f>
-        <v>10030010</v>
+        <f t="shared" si="2"/>
+        <v>10070010</v>
       </c>
       <c r="B140" s="16">
-        <v>100300</v>
+        <v>100700</v>
       </c>
       <c r="C140" s="16">
         <v>1</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E140" s="16">
-        <v>100300001</v>
+        <v>100700001</v>
       </c>
       <c r="F140" s="16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G140" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H140" s="17">
         <v>10</v>
@@ -8237,7 +8250,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M140" s="17">
         <v>0</v>
@@ -8251,28 +8264,28 @@
     </row>
     <row r="141" spans="1:15">
       <c r="A141" s="1">
+        <f t="shared" si="2"/>
+        <v>10070011</v>
+      </c>
+      <c r="B141" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C141" s="16">
+        <v>1</v>
+      </c>
+      <c r="D141" s="16" t="str">
+        <f t="shared" ref="D141:D145" si="4">D140</f>
+        <v>麻将胡了</v>
+      </c>
+      <c r="E141" s="16">
+        <v>100700001</v>
+      </c>
+      <c r="F141" s="16" t="str">
         <f t="shared" si="3"/>
-        <v>10030011</v>
-      </c>
-      <c r="B141" s="16">
-        <v>100300</v>
-      </c>
-      <c r="C141" s="16">
-        <v>1</v>
-      </c>
-      <c r="D141" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v>超级明星</v>
-      </c>
-      <c r="E141" s="16">
-        <v>100300001</v>
-      </c>
-      <c r="F141" s="16" t="str">
-        <f t="shared" ref="F141:F145" si="4">F140</f>
-        <v>SuperStar</v>
+        <v>MahjongWays</v>
       </c>
       <c r="G141" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H141" s="17">
         <v>11</v>
@@ -8287,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M141" s="17">
         <v>0</v>
@@ -8301,28 +8314,28 @@
     </row>
     <row r="142" spans="1:15">
       <c r="A142" s="1">
+        <f t="shared" si="2"/>
+        <v>10070012</v>
+      </c>
+      <c r="B142" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C142" s="16">
+        <v>1</v>
+      </c>
+      <c r="D142" s="16" t="str">
+        <f t="shared" si="4"/>
+        <v>麻将胡了</v>
+      </c>
+      <c r="E142" s="16">
+        <v>100700001</v>
+      </c>
+      <c r="F142" s="16" t="str">
         <f t="shared" si="3"/>
-        <v>10030012</v>
-      </c>
-      <c r="B142" s="16">
-        <v>100300</v>
-      </c>
-      <c r="C142" s="16">
-        <v>1</v>
-      </c>
-      <c r="D142" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v>超级明星</v>
-      </c>
-      <c r="E142" s="16">
-        <v>100300001</v>
-      </c>
-      <c r="F142" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>SuperStar</v>
+        <v>MahjongWays</v>
       </c>
       <c r="G142" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H142" s="17">
         <v>12</v>
@@ -8337,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M142" s="17">
         <v>0</v>
@@ -8351,26 +8364,26 @@
     </row>
     <row r="143" spans="1:15">
       <c r="A143" s="1">
-        <f t="shared" si="3"/>
-        <v>10070010</v>
+        <f t="shared" si="2"/>
+        <v>10120010</v>
       </c>
       <c r="B143" s="16">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C143" s="16">
         <v>1</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E143" s="16">
-        <v>100700001</v>
+        <v>101200001</v>
       </c>
       <c r="F143" s="16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G143" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H143" s="17">
         <v>10</v>
@@ -8385,7 +8398,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M143" s="17">
         <v>0</v>
@@ -8399,28 +8412,28 @@
     </row>
     <row r="144" spans="1:15">
       <c r="A144" s="1">
-        <f t="shared" si="3"/>
-        <v>10070011</v>
+        <f t="shared" si="2"/>
+        <v>10120011</v>
       </c>
       <c r="B144" s="16">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C144" s="16">
         <v>1</v>
       </c>
       <c r="D144" s="16" t="str">
-        <f t="shared" ref="D144:D148" si="5">D143</f>
-        <v>麻将胡了</v>
+        <f t="shared" si="4"/>
+        <v>财神</v>
       </c>
       <c r="E144" s="16">
-        <v>100700001</v>
+        <v>101200001</v>
       </c>
       <c r="F144" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>MahjongWays</v>
+        <f t="shared" ref="F144:F148" si="5">F143</f>
+        <v>Godofwealth</v>
       </c>
       <c r="G144" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H144" s="17">
         <v>11</v>
@@ -8435,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M144" s="17">
         <v>0</v>
@@ -8449,28 +8462,28 @@
     </row>
     <row r="145" spans="1:15">
       <c r="A145" s="1">
-        <f t="shared" si="3"/>
-        <v>10070012</v>
+        <f t="shared" si="2"/>
+        <v>10120012</v>
       </c>
       <c r="B145" s="16">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C145" s="16">
         <v>1</v>
       </c>
       <c r="D145" s="16" t="str">
+        <f t="shared" si="4"/>
+        <v>财神</v>
+      </c>
+      <c r="E145" s="16">
+        <v>101200001</v>
+      </c>
+      <c r="F145" s="16" t="str">
         <f t="shared" si="5"/>
-        <v>麻将胡了</v>
-      </c>
-      <c r="E145" s="16">
-        <v>100700001</v>
-      </c>
-      <c r="F145" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>MahjongWays</v>
+        <v>Godofwealth</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H145" s="17">
         <v>12</v>
@@ -8485,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M145" s="17">
         <v>0</v>
@@ -8499,26 +8512,26 @@
     </row>
     <row r="146" spans="1:15">
       <c r="A146" s="1">
-        <f t="shared" si="3"/>
-        <v>10120010</v>
+        <f t="shared" si="2"/>
+        <v>10140010</v>
       </c>
       <c r="B146" s="16">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C146" s="16">
         <v>1</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E146" s="16">
-        <v>101200001</v>
+        <v>101400001</v>
       </c>
       <c r="F146" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G146" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H146" s="17">
         <v>10</v>
@@ -8533,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M146" s="17">
         <v>0</v>
@@ -8547,28 +8560,28 @@
     </row>
     <row r="147" spans="1:15">
       <c r="A147" s="1">
-        <f t="shared" si="3"/>
-        <v>10120011</v>
+        <f t="shared" si="2"/>
+        <v>10140011</v>
       </c>
       <c r="B147" s="16">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C147" s="16">
         <v>1</v>
       </c>
       <c r="D147" s="16" t="str">
+        <f t="shared" ref="D147:D151" si="6">D146</f>
+        <v>埃及艳后</v>
+      </c>
+      <c r="E147" s="16">
+        <v>101400001</v>
+      </c>
+      <c r="F147" s="16" t="str">
         <f t="shared" si="5"/>
-        <v>财神</v>
-      </c>
-      <c r="E147" s="16">
-        <v>101200001</v>
-      </c>
-      <c r="F147" s="16" t="str">
-        <f t="shared" ref="F147:F151" si="6">F146</f>
-        <v>Godofwealth</v>
+        <v>Cleopatra</v>
       </c>
       <c r="G147" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H147" s="17">
         <v>11</v>
@@ -8583,7 +8596,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M147" s="17">
         <v>0</v>
@@ -8597,28 +8610,28 @@
     </row>
     <row r="148" spans="1:15">
       <c r="A148" s="1">
-        <f t="shared" si="3"/>
-        <v>10120012</v>
+        <f t="shared" si="2"/>
+        <v>10140012</v>
       </c>
       <c r="B148" s="16">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C148" s="16">
         <v>1</v>
       </c>
       <c r="D148" s="16" t="str">
+        <f t="shared" si="6"/>
+        <v>埃及艳后</v>
+      </c>
+      <c r="E148" s="16">
+        <v>101400001</v>
+      </c>
+      <c r="F148" s="16" t="str">
         <f t="shared" si="5"/>
-        <v>财神</v>
-      </c>
-      <c r="E148" s="16">
-        <v>101200001</v>
-      </c>
-      <c r="F148" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v>Godofwealth</v>
+        <v>Cleopatra</v>
       </c>
       <c r="G148" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H148" s="17">
         <v>12</v>
@@ -8633,7 +8646,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M148" s="17">
         <v>0</v>
@@ -8647,26 +8660,26 @@
     </row>
     <row r="149" spans="1:15">
       <c r="A149" s="1">
-        <f t="shared" si="3"/>
-        <v>10140010</v>
+        <f t="shared" si="2"/>
+        <v>10240010</v>
       </c>
       <c r="B149" s="16">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C149" s="16">
         <v>1</v>
       </c>
       <c r="D149" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E149" s="16">
-        <v>101400001</v>
+        <v>102400026</v>
       </c>
       <c r="F149" s="16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G149" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H149" s="17">
         <v>10</v>
@@ -8681,7 +8694,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M149" s="17">
         <v>0</v>
@@ -8695,28 +8708,27 @@
     </row>
     <row r="150" spans="1:15">
       <c r="A150" s="1">
-        <f t="shared" si="3"/>
-        <v>10140011</v>
+        <f t="shared" si="2"/>
+        <v>10240011</v>
       </c>
       <c r="B150" s="16">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C150" s="16">
         <v>1</v>
       </c>
       <c r="D150" s="16" t="str">
-        <f t="shared" ref="D150:D154" si="7">D149</f>
-        <v>埃及艳后</v>
+        <f t="shared" si="6"/>
+        <v>财富银行</v>
       </c>
       <c r="E150" s="16">
-        <v>101400001</v>
-      </c>
-      <c r="F150" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v>Cleopatra</v>
+        <v>102400026</v>
+      </c>
+      <c r="F150" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H150" s="17">
         <v>11</v>
@@ -8731,7 +8743,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M150" s="17">
         <v>0</v>
@@ -8745,28 +8757,27 @@
     </row>
     <row r="151" spans="1:15">
       <c r="A151" s="1">
-        <f t="shared" si="3"/>
-        <v>10140012</v>
+        <f t="shared" si="2"/>
+        <v>10240012</v>
       </c>
       <c r="B151" s="16">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C151" s="16">
         <v>1</v>
       </c>
       <c r="D151" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v>埃及艳后</v>
+        <f t="shared" si="6"/>
+        <v>财富银行</v>
       </c>
       <c r="E151" s="16">
-        <v>101400001</v>
-      </c>
-      <c r="F151" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v>Cleopatra</v>
+        <v>102400026</v>
+      </c>
+      <c r="F151" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="G151" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H151" s="17">
         <v>12</v>
@@ -8781,7 +8792,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M151" s="17">
         <v>0</v>
@@ -8795,26 +8806,26 @@
     </row>
     <row r="152" spans="1:15">
       <c r="A152" s="1">
-        <f t="shared" si="3"/>
-        <v>10240010</v>
+        <f t="shared" si="2"/>
+        <v>10220010</v>
       </c>
       <c r="B152" s="16">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C152" s="16">
         <v>1</v>
       </c>
       <c r="D152" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E152" s="16">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F152" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G152" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H152" s="17">
         <v>10</v>
@@ -8829,7 +8840,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M152" s="17">
         <v>0</v>
@@ -8843,27 +8854,26 @@
     </row>
     <row r="153" spans="1:15">
       <c r="A153" s="1">
-        <f t="shared" si="3"/>
-        <v>10240011</v>
+        <f t="shared" si="2"/>
+        <v>10220011</v>
       </c>
       <c r="B153" s="16">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C153" s="16">
         <v>1</v>
       </c>
-      <c r="D153" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v>财富银行</v>
+      <c r="D153" s="16" t="s">
+        <v>47</v>
       </c>
       <c r="E153" s="16">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F153" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G153" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H153" s="17">
         <v>11</v>
@@ -8878,7 +8888,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M153" s="17">
         <v>0</v>
@@ -8892,27 +8902,26 @@
     </row>
     <row r="154" spans="1:15">
       <c r="A154" s="1">
-        <f t="shared" si="3"/>
-        <v>10240012</v>
+        <f t="shared" si="2"/>
+        <v>10220012</v>
       </c>
       <c r="B154" s="16">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C154" s="16">
         <v>1</v>
       </c>
-      <c r="D154" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v>财富银行</v>
+      <c r="D154" s="16" t="s">
+        <v>47</v>
       </c>
       <c r="E154" s="16">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F154" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G154" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H154" s="17">
         <v>12</v>
@@ -8927,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M154" s="17">
         <v>0</v>
@@ -8941,26 +8950,26 @@
     </row>
     <row r="155" spans="1:15">
       <c r="A155" s="1">
-        <f t="shared" si="3"/>
-        <v>10220010</v>
+        <f t="shared" si="2"/>
+        <v>10170010</v>
       </c>
       <c r="B155" s="16">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C155" s="16">
         <v>1</v>
       </c>
       <c r="D155" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E155" s="16">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F155" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G155" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H155" s="17">
         <v>10</v>
@@ -8975,7 +8984,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M155" s="17">
         <v>0</v>
@@ -8989,26 +8998,26 @@
     </row>
     <row r="156" spans="1:15">
       <c r="A156" s="1">
-        <f t="shared" si="3"/>
-        <v>10220011</v>
+        <f t="shared" si="2"/>
+        <v>10170011</v>
       </c>
       <c r="B156" s="16">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C156" s="16">
         <v>1</v>
       </c>
       <c r="D156" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E156" s="16">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F156" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G156" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H156" s="17">
         <v>11</v>
@@ -9023,7 +9032,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M156" s="17">
         <v>0</v>
@@ -9037,26 +9046,26 @@
     </row>
     <row r="157" spans="1:15">
       <c r="A157" s="1">
-        <f t="shared" si="3"/>
-        <v>10220012</v>
+        <f t="shared" si="2"/>
+        <v>10170012</v>
       </c>
       <c r="B157" s="16">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C157" s="16">
         <v>1</v>
       </c>
       <c r="D157" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E157" s="16">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F157" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G157" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H157" s="17">
         <v>12</v>
@@ -9071,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M157" s="17">
         <v>0</v>
@@ -9085,26 +9094,26 @@
     </row>
     <row r="158" spans="1:15">
       <c r="A158" s="1">
-        <f t="shared" si="3"/>
-        <v>10170010</v>
+        <f t="shared" si="2"/>
+        <v>10210010</v>
       </c>
       <c r="B158" s="16">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C158" s="16">
         <v>1</v>
       </c>
       <c r="D158" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E158" s="16">
-        <v>101700001</v>
+        <v>102100001</v>
       </c>
       <c r="F158" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G158" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H158" s="17">
         <v>10</v>
@@ -9119,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M158" s="17">
         <v>0</v>
@@ -9133,26 +9142,26 @@
     </row>
     <row r="159" spans="1:15">
       <c r="A159" s="1">
-        <f t="shared" si="3"/>
-        <v>10170011</v>
+        <f t="shared" si="2"/>
+        <v>10210011</v>
       </c>
       <c r="B159" s="16">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C159" s="16">
         <v>1</v>
       </c>
       <c r="D159" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E159" s="16">
-        <v>101700001</v>
+        <v>102100001</v>
       </c>
       <c r="F159" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G159" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H159" s="17">
         <v>11</v>
@@ -9167,7 +9176,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M159" s="17">
         <v>0</v>
@@ -9181,26 +9190,26 @@
     </row>
     <row r="160" spans="1:15">
       <c r="A160" s="1">
-        <f t="shared" si="3"/>
-        <v>10170012</v>
+        <f t="shared" si="2"/>
+        <v>10210012</v>
       </c>
       <c r="B160" s="16">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C160" s="16">
         <v>1</v>
       </c>
       <c r="D160" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E160" s="16">
-        <v>101700001</v>
+        <v>102100001</v>
       </c>
       <c r="F160" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G160" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H160" s="17">
         <v>12</v>
@@ -9215,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M160" s="17">
         <v>0</v>
@@ -9229,26 +9238,26 @@
     </row>
     <row r="161" spans="1:15">
       <c r="A161" s="1">
-        <f t="shared" si="3"/>
-        <v>10210010</v>
+        <f t="shared" si="2"/>
+        <v>10180010</v>
       </c>
       <c r="B161" s="16">
-        <v>102100</v>
+        <v>101800</v>
       </c>
       <c r="C161" s="16">
         <v>1</v>
       </c>
       <c r="D161" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E161" s="16">
-        <v>102100001</v>
+        <v>101800001</v>
       </c>
       <c r="F161" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G161" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H161" s="17">
         <v>10</v>
@@ -9263,7 +9272,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M161" s="17">
         <v>0</v>
@@ -9277,26 +9286,26 @@
     </row>
     <row r="162" spans="1:15">
       <c r="A162" s="1">
-        <f t="shared" si="3"/>
-        <v>10210011</v>
+        <f t="shared" si="2"/>
+        <v>10180011</v>
       </c>
       <c r="B162" s="16">
-        <v>102100</v>
+        <v>101800</v>
       </c>
       <c r="C162" s="16">
         <v>1</v>
       </c>
       <c r="D162" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E162" s="16">
-        <v>102100001</v>
+        <v>101800001</v>
       </c>
       <c r="F162" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G162" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H162" s="17">
         <v>11</v>
@@ -9311,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M162" s="17">
         <v>0</v>
@@ -9325,26 +9334,26 @@
     </row>
     <row r="163" spans="1:15">
       <c r="A163" s="1">
-        <f t="shared" si="3"/>
-        <v>10210012</v>
+        <f t="shared" si="2"/>
+        <v>10180012</v>
       </c>
       <c r="B163" s="16">
-        <v>102100</v>
+        <v>101800</v>
       </c>
       <c r="C163" s="16">
         <v>1</v>
       </c>
       <c r="D163" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E163" s="16">
-        <v>102100001</v>
+        <v>101800001</v>
       </c>
       <c r="F163" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G163" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H163" s="17">
         <v>12</v>
@@ -9359,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M163" s="17">
         <v>0</v>
@@ -9373,26 +9382,26 @@
     </row>
     <row r="164" spans="1:15">
       <c r="A164" s="1">
-        <f t="shared" si="3"/>
-        <v>10180010</v>
+        <f t="shared" si="2"/>
+        <v>10250010</v>
       </c>
       <c r="B164" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C164" s="16">
         <v>1</v>
       </c>
       <c r="D164" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E164" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F164" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G164" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H164" s="17">
         <v>10</v>
@@ -9407,7 +9416,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M164" s="17">
         <v>0</v>
@@ -9421,26 +9430,26 @@
     </row>
     <row r="165" spans="1:15">
       <c r="A165" s="1">
-        <f t="shared" si="3"/>
-        <v>10180011</v>
+        <f t="shared" si="2"/>
+        <v>10250011</v>
       </c>
       <c r="B165" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C165" s="16">
         <v>1</v>
       </c>
       <c r="D165" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E165" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F165" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G165" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H165" s="17">
         <v>11</v>
@@ -9455,7 +9464,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M165" s="17">
         <v>0</v>
@@ -9469,26 +9478,26 @@
     </row>
     <row r="166" spans="1:15">
       <c r="A166" s="1">
-        <f t="shared" si="3"/>
-        <v>10180012</v>
+        <f t="shared" si="2"/>
+        <v>10250012</v>
       </c>
       <c r="B166" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C166" s="16">
         <v>1</v>
       </c>
       <c r="D166" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E166" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F166" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G166" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H166" s="17">
         <v>12</v>
@@ -9503,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M166" s="17">
         <v>0</v>
@@ -9517,26 +9526,26 @@
     </row>
     <row r="167" spans="1:15">
       <c r="A167" s="1">
-        <f t="shared" si="3"/>
-        <v>10250010</v>
+        <f t="shared" si="2"/>
+        <v>10230010</v>
       </c>
       <c r="B167" s="16">
-        <v>102500</v>
+        <v>102300</v>
       </c>
       <c r="C167" s="16">
         <v>1</v>
       </c>
       <c r="D167" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E167" s="16">
-        <v>102500001</v>
+        <v>102300001</v>
       </c>
       <c r="F167" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G167" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H167" s="17">
         <v>10</v>
@@ -9551,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M167" s="17">
         <v>0</v>
@@ -9565,26 +9574,26 @@
     </row>
     <row r="168" spans="1:15">
       <c r="A168" s="1">
-        <f t="shared" si="3"/>
-        <v>10250011</v>
+        <f t="shared" si="2"/>
+        <v>10230011</v>
       </c>
       <c r="B168" s="16">
-        <v>102500</v>
+        <v>102300</v>
       </c>
       <c r="C168" s="16">
         <v>1</v>
       </c>
       <c r="D168" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E168" s="16">
-        <v>102500001</v>
+        <v>102300001</v>
       </c>
       <c r="F168" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G168" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H168" s="17">
         <v>11</v>
@@ -9599,7 +9608,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M168" s="17">
         <v>0</v>
@@ -9613,26 +9622,26 @@
     </row>
     <row r="169" spans="1:15">
       <c r="A169" s="1">
-        <f t="shared" si="3"/>
-        <v>10250012</v>
+        <f t="shared" si="2"/>
+        <v>10230012</v>
       </c>
       <c r="B169" s="16">
-        <v>102500</v>
+        <v>102300</v>
       </c>
       <c r="C169" s="16">
         <v>1</v>
       </c>
       <c r="D169" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E169" s="16">
-        <v>102500001</v>
+        <v>102300001</v>
       </c>
       <c r="F169" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G169" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H169" s="17">
         <v>12</v>
@@ -9647,7 +9656,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M169" s="17">
         <v>0</v>
@@ -9661,41 +9670,41 @@
     </row>
     <row r="170" spans="1:15">
       <c r="A170" s="1">
-        <f t="shared" si="3"/>
-        <v>10230010</v>
-      </c>
-      <c r="B170" s="16">
-        <v>102300</v>
-      </c>
-      <c r="C170" s="16">
-        <v>1</v>
-      </c>
-      <c r="D170" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E170" s="16">
-        <v>102300001</v>
-      </c>
-      <c r="F170" s="16" t="s">
-        <v>58</v>
+        <f t="shared" si="2"/>
+        <v>10340010</v>
+      </c>
+      <c r="B170" s="4">
+        <v>103400</v>
+      </c>
+      <c r="C170" s="4">
+        <v>1</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E170" s="13">
+        <v>103000001</v>
+      </c>
+      <c r="F170" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="G170" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H170" s="1">
+        <v>10</v>
+      </c>
+      <c r="I170" s="2">
+        <v>0</v>
+      </c>
+      <c r="J170" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K170" s="17">
+        <v>0</v>
+      </c>
+      <c r="L170" s="25" t="s">
         <v>107</v>
-      </c>
-      <c r="H170" s="17">
-        <v>10</v>
-      </c>
-      <c r="I170" s="24">
-        <v>0</v>
-      </c>
-      <c r="J170" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K170" s="17">
-        <v>0</v>
-      </c>
-      <c r="L170" s="25" t="s">
-        <v>108</v>
       </c>
       <c r="M170" s="17">
         <v>0</v>
@@ -9709,31 +9718,31 @@
     </row>
     <row r="171" spans="1:15">
       <c r="A171" s="1">
-        <f t="shared" si="3"/>
-        <v>10230011</v>
-      </c>
-      <c r="B171" s="16">
-        <v>102300</v>
-      </c>
-      <c r="C171" s="16">
-        <v>1</v>
-      </c>
-      <c r="D171" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E171" s="16">
-        <v>102300001</v>
-      </c>
-      <c r="F171" s="16" t="s">
-        <v>58</v>
+        <f t="shared" si="2"/>
+        <v>10340011</v>
+      </c>
+      <c r="B171" s="4">
+        <v>103400</v>
+      </c>
+      <c r="C171" s="4">
+        <v>1</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E171" s="13">
+        <v>103000001</v>
+      </c>
+      <c r="F171" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="G171" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="H171" s="17">
+        <v>108</v>
+      </c>
+      <c r="H171" s="1">
         <v>11</v>
       </c>
-      <c r="I171" s="24">
+      <c r="I171" s="2">
         <v>0</v>
       </c>
       <c r="J171" s="17">
@@ -9743,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M171" s="17">
         <v>0</v>
@@ -9757,31 +9766,31 @@
     </row>
     <row r="172" spans="1:15">
       <c r="A172" s="1">
-        <f t="shared" si="3"/>
-        <v>10230012</v>
-      </c>
-      <c r="B172" s="16">
-        <v>102300</v>
-      </c>
-      <c r="C172" s="16">
-        <v>1</v>
-      </c>
-      <c r="D172" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E172" s="16">
-        <v>102300001</v>
-      </c>
-      <c r="F172" s="16" t="s">
-        <v>58</v>
+        <f t="shared" si="2"/>
+        <v>10340012</v>
+      </c>
+      <c r="B172" s="4">
+        <v>103400</v>
+      </c>
+      <c r="C172" s="4">
+        <v>1</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E172" s="13">
+        <v>103000001</v>
+      </c>
+      <c r="F172" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="G172" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H172" s="17">
+        <v>109</v>
+      </c>
+      <c r="H172" s="1">
         <v>12</v>
       </c>
-      <c r="I172" s="24">
+      <c r="I172" s="2">
         <v>0</v>
       </c>
       <c r="J172" s="17">
@@ -9791,7 +9800,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M172" s="17">
         <v>0</v>
@@ -9805,26 +9814,26 @@
     </row>
     <row r="173" spans="1:15">
       <c r="A173" s="1">
-        <f t="shared" si="3"/>
-        <v>10340010</v>
+        <f t="shared" si="2"/>
+        <v>10350010</v>
       </c>
       <c r="B173" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C173" s="4">
         <v>1</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E173" s="13">
-        <v>103000001</v>
+        <v>102900001</v>
       </c>
       <c r="F173" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G173" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H173" s="1">
         <v>10</v>
@@ -9839,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M173" s="17">
         <v>0</v>
@@ -9853,26 +9862,26 @@
     </row>
     <row r="174" spans="1:15">
       <c r="A174" s="1">
-        <f t="shared" si="3"/>
-        <v>10340011</v>
+        <f t="shared" si="2"/>
+        <v>10350011</v>
       </c>
       <c r="B174" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C174" s="4">
         <v>1</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E174" s="13">
-        <v>103000001</v>
+        <v>102900001</v>
       </c>
       <c r="F174" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G174" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H174" s="1">
         <v>11</v>
@@ -9887,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M174" s="17">
         <v>0</v>
@@ -9901,26 +9910,26 @@
     </row>
     <row r="175" spans="1:15">
       <c r="A175" s="1">
-        <f t="shared" si="3"/>
-        <v>10340012</v>
+        <f t="shared" si="2"/>
+        <v>10350012</v>
       </c>
       <c r="B175" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C175" s="4">
         <v>1</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E175" s="13">
-        <v>103000001</v>
+        <v>102900001</v>
       </c>
       <c r="F175" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G175" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H175" s="1">
         <v>12</v>
@@ -9935,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M175" s="17">
         <v>0</v>
@@ -9949,26 +9958,26 @@
     </row>
     <row r="176" spans="1:15">
       <c r="A176" s="1">
-        <f t="shared" si="3"/>
-        <v>10350010</v>
+        <f t="shared" si="2"/>
+        <v>10350110</v>
       </c>
       <c r="B176" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C176" s="4">
         <v>1</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E176" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F176" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G176" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H176" s="1">
         <v>10</v>
@@ -9979,11 +9988,11 @@
       <c r="J176" s="17">
         <v>-1</v>
       </c>
-      <c r="K176" s="17">
+      <c r="K176" s="1">
         <v>0</v>
       </c>
       <c r="L176" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M176" s="17">
         <v>0</v>
@@ -9997,26 +10006,26 @@
     </row>
     <row r="177" spans="1:15">
       <c r="A177" s="1">
-        <f t="shared" si="3"/>
-        <v>10350011</v>
+        <f t="shared" si="2"/>
+        <v>10350111</v>
       </c>
       <c r="B177" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C177" s="4">
         <v>1</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E177" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F177" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G177" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H177" s="1">
         <v>11</v>
@@ -10027,11 +10036,11 @@
       <c r="J177" s="17">
         <v>-1</v>
       </c>
-      <c r="K177" s="17">
+      <c r="K177" s="1">
         <v>0</v>
       </c>
       <c r="L177" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M177" s="17">
         <v>0</v>
@@ -10045,26 +10054,26 @@
     </row>
     <row r="178" spans="1:15">
       <c r="A178" s="1">
-        <f t="shared" si="3"/>
-        <v>10350012</v>
+        <f t="shared" si="2"/>
+        <v>10350112</v>
       </c>
       <c r="B178" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C178" s="4">
         <v>1</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E178" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F178" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G178" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H178" s="1">
         <v>12</v>
@@ -10075,11 +10084,11 @@
       <c r="J178" s="17">
         <v>-1</v>
       </c>
-      <c r="K178" s="17">
+      <c r="K178" s="1">
         <v>0</v>
       </c>
       <c r="L178" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M178" s="17">
         <v>0</v>
@@ -10093,47 +10102,47 @@
     </row>
     <row r="179" spans="1:15">
       <c r="A179" s="1">
-        <f t="shared" si="3"/>
-        <v>10350110</v>
+        <v>30040010</v>
       </c>
       <c r="B179" s="4">
-        <v>103501</v>
+        <v>300400</v>
       </c>
       <c r="C179" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E179" s="13">
-        <v>103501001</v>
+        <v>300400023</v>
       </c>
       <c r="F179" s="13" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="G179" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H179" s="1">
         <v>10</v>
       </c>
-      <c r="I179" s="2">
-        <v>0</v>
-      </c>
-      <c r="J179" s="17">
+      <c r="I179" s="23">
+        <f t="shared" ref="I179:I181" si="7">N179*52</f>
+        <v>5200</v>
+      </c>
+      <c r="J179" s="1">
         <v>-1</v>
       </c>
       <c r="K179" s="1">
         <v>0</v>
       </c>
-      <c r="L179" s="25" t="s">
-        <v>108</v>
+      <c r="L179" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="M179" s="17">
         <v>0</v>
       </c>
-      <c r="N179">
-        <v>1000</v>
+      <c r="N179" s="23">
+        <v>100</v>
       </c>
       <c r="O179" s="26">
         <v>1980000</v>
@@ -10141,47 +10150,47 @@
     </row>
     <row r="180" spans="1:15">
       <c r="A180" s="1">
-        <f t="shared" si="3"/>
-        <v>10350111</v>
+        <v>30040011</v>
       </c>
       <c r="B180" s="4">
-        <v>103501</v>
+        <v>300400</v>
       </c>
       <c r="C180" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E180" s="13">
-        <v>103501001</v>
+        <v>300400023</v>
       </c>
       <c r="F180" s="13" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="G180" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H180" s="1">
         <v>11</v>
       </c>
-      <c r="I180" s="2">
-        <v>0</v>
-      </c>
-      <c r="J180" s="17">
+      <c r="I180" s="23">
+        <f t="shared" si="7"/>
+        <v>52000</v>
+      </c>
+      <c r="J180" s="1">
         <v>-1</v>
       </c>
       <c r="K180" s="1">
         <v>0</v>
       </c>
-      <c r="L180" s="25" t="s">
-        <v>108</v>
+      <c r="L180" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="M180" s="17">
         <v>0</v>
       </c>
-      <c r="N180">
-        <v>10000</v>
+      <c r="N180" s="23">
+        <v>1000</v>
       </c>
       <c r="O180" s="26">
         <v>1980000</v>
@@ -10189,47 +10198,47 @@
     </row>
     <row r="181" spans="1:15">
       <c r="A181" s="1">
-        <f t="shared" si="3"/>
-        <v>10350112</v>
+        <v>30040012</v>
       </c>
       <c r="B181" s="4">
-        <v>103501</v>
+        <v>300400</v>
       </c>
       <c r="C181" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E181" s="13">
-        <v>103501001</v>
+        <v>300400023</v>
       </c>
       <c r="F181" s="13" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="G181" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H181" s="1">
         <v>12</v>
       </c>
-      <c r="I181" s="2">
-        <v>0</v>
-      </c>
-      <c r="J181" s="17">
+      <c r="I181" s="23">
+        <f t="shared" si="7"/>
+        <v>520000</v>
+      </c>
+      <c r="J181" s="1">
         <v>-1</v>
       </c>
       <c r="K181" s="1">
         <v>0</v>
       </c>
-      <c r="L181" s="25" t="s">
-        <v>108</v>
+      <c r="L181" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="M181" s="17">
         <v>0</v>
       </c>
-      <c r="N181">
-        <v>100000</v>
+      <c r="N181" s="23">
+        <v>10000</v>
       </c>
       <c r="O181" s="26">
         <v>1980000</v>
@@ -10237,32 +10246,31 @@
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="1">
-        <v>30040010</v>
+        <v>10010021</v>
       </c>
       <c r="B182" s="4">
-        <v>300400</v>
+        <v>100100</v>
       </c>
       <c r="C182" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="E182" s="13">
-        <v>300400023</v>
+        <v>100100026</v>
       </c>
       <c r="F182" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="G182" s="17" t="s">
-        <v>107</v>
+        <v>31</v>
+      </c>
+      <c r="G182" s="27" t="s">
+        <v>112</v>
       </c>
       <c r="H182" s="1">
-        <v>10</v>
-      </c>
-      <c r="I182" s="23">
-        <f t="shared" ref="I182:I184" si="8">N182*52</f>
-        <v>5200</v>
+        <v>21</v>
+      </c>
+      <c r="I182" s="2">
+        <v>0</v>
       </c>
       <c r="J182" s="1">
         <v>-1</v>
@@ -10271,46 +10279,45 @@
         <v>0</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="M182" s="17">
-        <v>0</v>
-      </c>
-      <c r="N182" s="23">
-        <v>100</v>
-      </c>
-      <c r="O182" s="26">
-        <v>1980000</v>
+        <v>33</v>
+      </c>
+      <c r="M182" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="N182">
+        <v>1000</v>
+      </c>
+      <c r="O182" s="15">
+        <v>1990000</v>
       </c>
     </row>
     <row r="183" spans="1:15">
       <c r="A183" s="1">
-        <v>30040011</v>
+        <v>10010022</v>
       </c>
       <c r="B183" s="4">
-        <v>300400</v>
+        <v>100100</v>
       </c>
       <c r="C183" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="E183" s="13">
-        <v>300400023</v>
+        <v>100100026</v>
       </c>
       <c r="F183" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="G183" s="17" t="s">
-        <v>109</v>
+        <v>31</v>
+      </c>
+      <c r="G183" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="H183" s="1">
-        <v>11</v>
-      </c>
-      <c r="I183" s="23">
-        <f t="shared" si="8"/>
-        <v>52000</v>
+        <v>22</v>
+      </c>
+      <c r="I183" s="2">
+        <v>10000</v>
       </c>
       <c r="J183" s="1">
         <v>-1</v>
@@ -10319,46 +10326,45 @@
         <v>0</v>
       </c>
       <c r="L183" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="M183" s="17">
-        <v>0</v>
-      </c>
-      <c r="N183" s="23">
-        <v>1000</v>
-      </c>
-      <c r="O183" s="26">
-        <v>1980000</v>
+        <v>33</v>
+      </c>
+      <c r="M183" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="N183">
+        <v>10000</v>
+      </c>
+      <c r="O183" s="15">
+        <v>1990000</v>
       </c>
     </row>
     <row r="184" spans="1:15">
       <c r="A184" s="1">
-        <v>30040012</v>
+        <v>10010023</v>
       </c>
       <c r="B184" s="4">
-        <v>300400</v>
+        <v>100100</v>
       </c>
       <c r="C184" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="E184" s="13">
-        <v>300400023</v>
+        <v>100100026</v>
       </c>
       <c r="F184" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="G184" s="17" t="s">
-        <v>110</v>
+        <v>31</v>
+      </c>
+      <c r="G184" s="27" t="s">
+        <v>114</v>
       </c>
       <c r="H184" s="1">
-        <v>12</v>
-      </c>
-      <c r="I184" s="23">
-        <f t="shared" si="8"/>
-        <v>520000</v>
+        <v>23</v>
+      </c>
+      <c r="I184" s="2">
+        <v>100000</v>
       </c>
       <c r="J184" s="1">
         <v>-1</v>
@@ -10367,39 +10373,39 @@
         <v>0</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="M184" s="17">
-        <v>0</v>
-      </c>
-      <c r="N184" s="23">
-        <v>10000</v>
-      </c>
-      <c r="O184" s="26">
-        <v>1980000</v>
+        <v>33</v>
+      </c>
+      <c r="M184" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="N184">
+        <v>100000</v>
+      </c>
+      <c r="O184" s="15">
+        <v>1990000</v>
       </c>
     </row>
     <row r="185" spans="1:15">
       <c r="A185" s="1">
-        <v>10010021</v>
+        <v>10030021</v>
       </c>
       <c r="B185" s="4">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C185" s="4">
         <v>1</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E185" s="13">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="F185" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G185" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H185" s="1">
         <v>21</v>
@@ -10428,25 +10434,25 @@
     </row>
     <row r="186" spans="1:15">
       <c r="A186" s="1">
-        <v>10010022</v>
+        <v>10030022</v>
       </c>
       <c r="B186" s="4">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C186" s="4">
         <v>1</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E186" s="13">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="F186" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G186" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H186" s="1">
         <v>22</v>
@@ -10475,25 +10481,25 @@
     </row>
     <row r="187" spans="1:15">
       <c r="A187" s="1">
-        <v>10010023</v>
+        <v>10030023</v>
       </c>
       <c r="B187" s="4">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C187" s="4">
         <v>1</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E187" s="13">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="F187" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G187" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H187" s="1">
         <v>23</v>
@@ -10522,25 +10528,25 @@
     </row>
     <row r="188" spans="1:15">
       <c r="A188" s="1">
-        <v>10030021</v>
+        <v>10070021</v>
       </c>
       <c r="B188" s="4">
-        <v>100300</v>
+        <v>100700</v>
       </c>
       <c r="C188" s="4">
         <v>1</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E188" s="13">
-        <v>100300001</v>
+        <v>100700001</v>
       </c>
       <c r="F188" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G188" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H188" s="1">
         <v>21</v>
@@ -10569,25 +10575,25 @@
     </row>
     <row r="189" spans="1:15">
       <c r="A189" s="1">
-        <v>10030022</v>
+        <v>10070022</v>
       </c>
       <c r="B189" s="4">
-        <v>100300</v>
+        <v>100700</v>
       </c>
       <c r="C189" s="4">
         <v>1</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E189" s="13">
-        <v>100300001</v>
+        <v>100700001</v>
       </c>
       <c r="F189" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G189" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H189" s="1">
         <v>22</v>
@@ -10616,25 +10622,25 @@
     </row>
     <row r="190" spans="1:15">
       <c r="A190" s="1">
-        <v>10030023</v>
+        <v>10070023</v>
       </c>
       <c r="B190" s="4">
-        <v>100300</v>
+        <v>100700</v>
       </c>
       <c r="C190" s="4">
         <v>1</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E190" s="13">
-        <v>100300001</v>
+        <v>100700001</v>
       </c>
       <c r="F190" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G190" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H190" s="1">
         <v>23</v>
@@ -10663,25 +10669,25 @@
     </row>
     <row r="191" spans="1:15">
       <c r="A191" s="1">
-        <v>10070021</v>
+        <v>10120021</v>
       </c>
       <c r="B191" s="4">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C191" s="4">
         <v>1</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E191" s="13">
-        <v>100700001</v>
+        <v>101200001</v>
       </c>
       <c r="F191" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G191" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H191" s="1">
         <v>21</v>
@@ -10702,7 +10708,7 @@
         <v>34</v>
       </c>
       <c r="N191">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="O191" s="15">
         <v>1990000</v>
@@ -10710,31 +10716,31 @@
     </row>
     <row r="192" spans="1:15">
       <c r="A192" s="1">
-        <v>10070022</v>
+        <v>10120022</v>
       </c>
       <c r="B192" s="4">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C192" s="4">
         <v>1</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E192" s="13">
-        <v>100700001</v>
+        <v>101200001</v>
       </c>
       <c r="F192" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G192" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H192" s="1">
         <v>22</v>
       </c>
       <c r="I192" s="2">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="J192" s="1">
         <v>-1</v>
@@ -10749,7 +10755,7 @@
         <v>34</v>
       </c>
       <c r="N192">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="O192" s="15">
         <v>1990000</v>
@@ -10757,31 +10763,31 @@
     </row>
     <row r="193" spans="1:15">
       <c r="A193" s="1">
-        <v>10070023</v>
+        <v>10120023</v>
       </c>
       <c r="B193" s="4">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C193" s="4">
         <v>1</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E193" s="13">
-        <v>100700001</v>
+        <v>101200001</v>
       </c>
       <c r="F193" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G193" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H193" s="1">
         <v>23</v>
       </c>
       <c r="I193" s="2">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="J193" s="1">
         <v>-1</v>
@@ -10796,7 +10802,7 @@
         <v>34</v>
       </c>
       <c r="N193">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="O193" s="15">
         <v>1990000</v>
@@ -10804,25 +10810,25 @@
     </row>
     <row r="194" spans="1:15">
       <c r="A194" s="1">
-        <v>10120021</v>
+        <v>10140021</v>
       </c>
       <c r="B194" s="4">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C194" s="4">
         <v>1</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E194" s="13">
-        <v>101200001</v>
+        <v>101400001</v>
       </c>
       <c r="F194" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G194" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H194" s="1">
         <v>21</v>
@@ -10843,7 +10849,7 @@
         <v>34</v>
       </c>
       <c r="N194">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="O194" s="15">
         <v>1990000</v>
@@ -10851,31 +10857,31 @@
     </row>
     <row r="195" spans="1:15">
       <c r="A195" s="1">
-        <v>10120022</v>
+        <v>10140022</v>
       </c>
       <c r="B195" s="4">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C195" s="4">
         <v>1</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E195" s="13">
-        <v>101200001</v>
+        <v>101400001</v>
       </c>
       <c r="F195" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G195" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H195" s="1">
         <v>22</v>
       </c>
       <c r="I195" s="2">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="J195" s="1">
         <v>-1</v>
@@ -10890,7 +10896,7 @@
         <v>34</v>
       </c>
       <c r="N195">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="O195" s="15">
         <v>1990000</v>
@@ -10898,31 +10904,31 @@
     </row>
     <row r="196" spans="1:15">
       <c r="A196" s="1">
-        <v>10120023</v>
+        <v>10140023</v>
       </c>
       <c r="B196" s="4">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C196" s="4">
         <v>1</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E196" s="13">
-        <v>101200001</v>
+        <v>101400001</v>
       </c>
       <c r="F196" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G196" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H196" s="1">
         <v>23</v>
       </c>
       <c r="I196" s="2">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="J196" s="1">
         <v>-1</v>
@@ -10937,7 +10943,7 @@
         <v>34</v>
       </c>
       <c r="N196">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="O196" s="15">
         <v>1990000</v>
@@ -10945,25 +10951,25 @@
     </row>
     <row r="197" spans="1:15">
       <c r="A197" s="1">
-        <v>10140021</v>
+        <v>10240021</v>
       </c>
       <c r="B197" s="4">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C197" s="4">
         <v>1</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E197" s="13">
-        <v>101400001</v>
+        <v>102400026</v>
       </c>
       <c r="F197" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G197" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H197" s="1">
         <v>21</v>
@@ -10984,7 +10990,7 @@
         <v>34</v>
       </c>
       <c r="N197">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O197" s="15">
         <v>1990000</v>
@@ -10992,25 +10998,25 @@
     </row>
     <row r="198" spans="1:15">
       <c r="A198" s="1">
-        <v>10140022</v>
+        <v>10240022</v>
       </c>
       <c r="B198" s="4">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C198" s="4">
         <v>1</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E198" s="13">
-        <v>101400001</v>
+        <v>102400026</v>
       </c>
       <c r="F198" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G198" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H198" s="1">
         <v>22</v>
@@ -11039,25 +11045,25 @@
     </row>
     <row r="199" spans="1:15">
       <c r="A199" s="1">
-        <v>10140023</v>
+        <v>10240023</v>
       </c>
       <c r="B199" s="4">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C199" s="4">
         <v>1</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E199" s="13">
-        <v>101400001</v>
+        <v>102400026</v>
       </c>
       <c r="F199" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G199" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H199" s="1">
         <v>23</v>
@@ -11086,25 +11092,25 @@
     </row>
     <row r="200" spans="1:15">
       <c r="A200" s="1">
-        <v>10240021</v>
+        <v>10220021</v>
       </c>
       <c r="B200" s="4">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C200" s="4">
         <v>1</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E200" s="13">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F200" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G200" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H200" s="1">
         <v>21</v>
@@ -11125,7 +11131,7 @@
         <v>34</v>
       </c>
       <c r="N200">
-        <v>100</v>
+        <v>1250</v>
       </c>
       <c r="O200" s="15">
         <v>1990000</v>
@@ -11133,31 +11139,31 @@
     </row>
     <row r="201" spans="1:15">
       <c r="A201" s="1">
-        <v>10240022</v>
+        <v>10220022</v>
       </c>
       <c r="B201" s="4">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C201" s="4">
         <v>1</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E201" s="13">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F201" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G201" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H201" s="1">
         <v>22</v>
       </c>
       <c r="I201" s="2">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="J201" s="1">
         <v>-1</v>
@@ -11172,7 +11178,7 @@
         <v>34</v>
       </c>
       <c r="N201">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="O201" s="15">
         <v>1990000</v>
@@ -11180,31 +11186,31 @@
     </row>
     <row r="202" spans="1:15">
       <c r="A202" s="1">
-        <v>10240023</v>
+        <v>10220023</v>
       </c>
       <c r="B202" s="4">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C202" s="4">
         <v>1</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E202" s="13">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F202" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G202" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H202" s="1">
         <v>23</v>
       </c>
       <c r="I202" s="2">
-        <v>100000</v>
+        <v>125000</v>
       </c>
       <c r="J202" s="1">
         <v>-1</v>
@@ -11219,7 +11225,7 @@
         <v>34</v>
       </c>
       <c r="N202">
-        <v>100000</v>
+        <v>125000</v>
       </c>
       <c r="O202" s="15">
         <v>1990000</v>
@@ -11227,25 +11233,25 @@
     </row>
     <row r="203" spans="1:15">
       <c r="A203" s="1">
-        <v>10220021</v>
+        <v>10170021</v>
       </c>
       <c r="B203" s="4">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C203" s="4">
         <v>1</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E203" s="13">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F203" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G203" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H203" s="1">
         <v>21</v>
@@ -11266,7 +11272,7 @@
         <v>34</v>
       </c>
       <c r="N203">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="O203" s="15">
         <v>1990000</v>
@@ -11274,31 +11280,31 @@
     </row>
     <row r="204" spans="1:15">
       <c r="A204" s="1">
-        <v>10220022</v>
+        <v>10170022</v>
       </c>
       <c r="B204" s="4">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C204" s="4">
         <v>1</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E204" s="13">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F204" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G204" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H204" s="1">
         <v>22</v>
       </c>
       <c r="I204" s="2">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="J204" s="1">
         <v>-1</v>
@@ -11313,7 +11319,7 @@
         <v>34</v>
       </c>
       <c r="N204">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="O204" s="15">
         <v>1990000</v>
@@ -11321,31 +11327,31 @@
     </row>
     <row r="205" spans="1:15">
       <c r="A205" s="1">
-        <v>10220023</v>
+        <v>10170023</v>
       </c>
       <c r="B205" s="4">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C205" s="4">
         <v>1</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E205" s="13">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F205" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G205" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H205" s="1">
         <v>23</v>
       </c>
       <c r="I205" s="2">
-        <v>125000</v>
+        <v>100000</v>
       </c>
       <c r="J205" s="1">
         <v>-1</v>
@@ -11360,7 +11366,7 @@
         <v>34</v>
       </c>
       <c r="N205">
-        <v>125000</v>
+        <v>100000</v>
       </c>
       <c r="O205" s="15">
         <v>1990000</v>
@@ -11368,25 +11374,25 @@
     </row>
     <row r="206" spans="1:15">
       <c r="A206" s="1">
-        <v>10170021</v>
+        <v>10210021</v>
       </c>
       <c r="B206" s="4">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C206" s="4">
         <v>1</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E206" s="13">
-        <v>101700001</v>
-      </c>
-      <c r="F206" s="13" t="s">
-        <v>50</v>
+        <v>102100001</v>
+      </c>
+      <c r="F206" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="G206" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H206" s="1">
         <v>21</v>
@@ -11415,25 +11421,25 @@
     </row>
     <row r="207" spans="1:15">
       <c r="A207" s="1">
-        <v>10170022</v>
+        <v>10210022</v>
       </c>
       <c r="B207" s="4">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C207" s="4">
         <v>1</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E207" s="13">
-        <v>101700001</v>
-      </c>
-      <c r="F207" s="13" t="s">
-        <v>50</v>
+        <v>102100001</v>
+      </c>
+      <c r="F207" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="G207" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H207" s="1">
         <v>22</v>
@@ -11462,25 +11468,25 @@
     </row>
     <row r="208" spans="1:15">
       <c r="A208" s="1">
-        <v>10170023</v>
+        <v>10210023</v>
       </c>
       <c r="B208" s="4">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C208" s="4">
         <v>1</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E208" s="13">
-        <v>101700001</v>
-      </c>
-      <c r="F208" s="13" t="s">
-        <v>50</v>
+        <v>102100001</v>
+      </c>
+      <c r="F208" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="G208" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H208" s="1">
         <v>23</v>
@@ -11509,25 +11515,26 @@
     </row>
     <row r="209" spans="1:15">
       <c r="A209" s="1">
-        <v>10210021</v>
-      </c>
-      <c r="B209" s="4">
-        <v>102100</v>
-      </c>
-      <c r="C209" s="4">
-        <v>1</v>
-      </c>
-      <c r="D209" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E209" s="13">
-        <v>102100001</v>
+        <f>B209*100+H209</f>
+        <v>10180021</v>
+      </c>
+      <c r="B209" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C209" s="16">
+        <v>1</v>
+      </c>
+      <c r="D209" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E209" s="16">
+        <v>101800001</v>
       </c>
       <c r="F209" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G209" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H209" s="1">
         <v>21</v>
@@ -11535,10 +11542,10 @@
       <c r="I209" s="2">
         <v>0</v>
       </c>
-      <c r="J209" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K209" s="1">
+      <c r="J209" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K209" s="17">
         <v>0</v>
       </c>
       <c r="L209" s="3" t="s">
@@ -11556,25 +11563,26 @@
     </row>
     <row r="210" spans="1:15">
       <c r="A210" s="1">
-        <v>10210022</v>
-      </c>
-      <c r="B210" s="4">
-        <v>102100</v>
-      </c>
-      <c r="C210" s="4">
-        <v>1</v>
-      </c>
-      <c r="D210" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E210" s="13">
-        <v>102100001</v>
+        <f t="shared" ref="A210:A217" si="8">B210*100+H210</f>
+        <v>10180022</v>
+      </c>
+      <c r="B210" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C210" s="16">
+        <v>1</v>
+      </c>
+      <c r="D210" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E210" s="16">
+        <v>101800001</v>
       </c>
       <c r="F210" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G210" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H210" s="1">
         <v>22</v>
@@ -11582,10 +11590,10 @@
       <c r="I210" s="2">
         <v>10000</v>
       </c>
-      <c r="J210" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K210" s="1">
+      <c r="J210" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K210" s="17">
         <v>0</v>
       </c>
       <c r="L210" s="3" t="s">
@@ -11603,25 +11611,26 @@
     </row>
     <row r="211" spans="1:15">
       <c r="A211" s="1">
-        <v>10210023</v>
-      </c>
-      <c r="B211" s="4">
-        <v>102100</v>
-      </c>
-      <c r="C211" s="4">
-        <v>1</v>
-      </c>
-      <c r="D211" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E211" s="13">
-        <v>102100001</v>
+        <f t="shared" si="8"/>
+        <v>10180023</v>
+      </c>
+      <c r="B211" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C211" s="16">
+        <v>1</v>
+      </c>
+      <c r="D211" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E211" s="16">
+        <v>101800001</v>
       </c>
       <c r="F211" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G211" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H211" s="1">
         <v>23</v>
@@ -11629,10 +11638,10 @@
       <c r="I211" s="2">
         <v>100000</v>
       </c>
-      <c r="J211" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K211" s="1">
+      <c r="J211" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K211" s="17">
         <v>0</v>
       </c>
       <c r="L211" s="3" t="s">
@@ -11650,26 +11659,26 @@
     </row>
     <row r="212" spans="1:15">
       <c r="A212" s="1">
-        <f>B212*100+H212</f>
-        <v>10180021</v>
+        <f t="shared" si="8"/>
+        <v>10250021</v>
       </c>
       <c r="B212" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C212" s="16">
         <v>1</v>
       </c>
       <c r="D212" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E212" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F212" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G212" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H212" s="1">
         <v>21</v>
@@ -11698,26 +11707,26 @@
     </row>
     <row r="213" spans="1:15">
       <c r="A213" s="1">
-        <f t="shared" ref="A213:A220" si="9">B213*100+H213</f>
-        <v>10180022</v>
+        <f t="shared" si="8"/>
+        <v>10250022</v>
       </c>
       <c r="B213" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C213" s="16">
         <v>1</v>
       </c>
       <c r="D213" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E213" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F213" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G213" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H213" s="1">
         <v>22</v>
@@ -11746,26 +11755,26 @@
     </row>
     <row r="214" spans="1:15">
       <c r="A214" s="1">
-        <f t="shared" si="9"/>
-        <v>10180023</v>
+        <f t="shared" si="8"/>
+        <v>10250023</v>
       </c>
       <c r="B214" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C214" s="16">
         <v>1</v>
       </c>
       <c r="D214" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E214" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F214" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G214" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H214" s="1">
         <v>23</v>
@@ -11794,26 +11803,26 @@
     </row>
     <row r="215" spans="1:15">
       <c r="A215" s="1">
-        <f t="shared" si="9"/>
-        <v>10250021</v>
-      </c>
-      <c r="B215" s="16">
-        <v>102500</v>
-      </c>
-      <c r="C215" s="16">
-        <v>1</v>
-      </c>
-      <c r="D215" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E215" s="16">
-        <v>102500001</v>
-      </c>
-      <c r="F215" s="16" t="s">
-        <v>56</v>
+        <f t="shared" si="8"/>
+        <v>10230021</v>
+      </c>
+      <c r="B215" s="4">
+        <v>102300</v>
+      </c>
+      <c r="C215" s="4">
+        <v>1</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E215" s="13">
+        <v>102300001</v>
+      </c>
+      <c r="F215" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G215" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H215" s="1">
         <v>21</v>
@@ -11842,26 +11851,26 @@
     </row>
     <row r="216" spans="1:15">
       <c r="A216" s="1">
-        <f t="shared" si="9"/>
-        <v>10250022</v>
-      </c>
-      <c r="B216" s="16">
-        <v>102500</v>
-      </c>
-      <c r="C216" s="16">
-        <v>1</v>
-      </c>
-      <c r="D216" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E216" s="16">
-        <v>102500001</v>
-      </c>
-      <c r="F216" s="16" t="s">
-        <v>56</v>
+        <f t="shared" si="8"/>
+        <v>10230022</v>
+      </c>
+      <c r="B216" s="4">
+        <v>102300</v>
+      </c>
+      <c r="C216" s="4">
+        <v>1</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E216" s="13">
+        <v>102300001</v>
+      </c>
+      <c r="F216" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G216" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H216" s="1">
         <v>22</v>
@@ -11890,26 +11899,26 @@
     </row>
     <row r="217" spans="1:15">
       <c r="A217" s="1">
-        <f t="shared" si="9"/>
-        <v>10250023</v>
-      </c>
-      <c r="B217" s="16">
-        <v>102500</v>
-      </c>
-      <c r="C217" s="16">
-        <v>1</v>
-      </c>
-      <c r="D217" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E217" s="16">
-        <v>102500001</v>
-      </c>
-      <c r="F217" s="16" t="s">
-        <v>56</v>
+        <f t="shared" si="8"/>
+        <v>10230023</v>
+      </c>
+      <c r="B217" s="4">
+        <v>102300</v>
+      </c>
+      <c r="C217" s="4">
+        <v>1</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E217" s="13">
+        <v>102300001</v>
+      </c>
+      <c r="F217" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G217" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H217" s="1">
         <v>23</v>
@@ -11938,26 +11947,25 @@
     </row>
     <row r="218" spans="1:15">
       <c r="A218" s="1">
-        <f t="shared" si="9"/>
-        <v>10230021</v>
+        <v>10340021</v>
       </c>
       <c r="B218" s="4">
-        <v>102300</v>
+        <v>103400</v>
       </c>
       <c r="C218" s="4">
         <v>1</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E218" s="13">
-        <v>102300001</v>
-      </c>
-      <c r="F218" s="13" t="s">
-        <v>58</v>
+        <v>103000001</v>
+      </c>
+      <c r="F218" s="18" t="s">
+        <v>60</v>
       </c>
       <c r="G218" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H218" s="1">
         <v>21</v>
@@ -11978,7 +11986,7 @@
         <v>34</v>
       </c>
       <c r="N218">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O218" s="15">
         <v>1990000</v>
@@ -11986,26 +11994,25 @@
     </row>
     <row r="219" spans="1:15">
       <c r="A219" s="1">
-        <f t="shared" si="9"/>
-        <v>10230022</v>
+        <v>10340022</v>
       </c>
       <c r="B219" s="4">
-        <v>102300</v>
+        <v>103400</v>
       </c>
       <c r="C219" s="4">
         <v>1</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E219" s="13">
-        <v>102300001</v>
-      </c>
-      <c r="F219" s="13" t="s">
-        <v>58</v>
+        <v>103000001</v>
+      </c>
+      <c r="F219" s="18" t="s">
+        <v>60</v>
       </c>
       <c r="G219" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H219" s="1">
         <v>22</v>
@@ -12034,26 +12041,25 @@
     </row>
     <row r="220" spans="1:15">
       <c r="A220" s="1">
-        <f t="shared" si="9"/>
-        <v>10230023</v>
+        <v>10340023</v>
       </c>
       <c r="B220" s="4">
-        <v>102300</v>
+        <v>103400</v>
       </c>
       <c r="C220" s="4">
         <v>1</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E220" s="13">
-        <v>102300001</v>
-      </c>
-      <c r="F220" s="13" t="s">
-        <v>58</v>
+        <v>103000001</v>
+      </c>
+      <c r="F220" s="18" t="s">
+        <v>60</v>
       </c>
       <c r="G220" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H220" s="1">
         <v>23</v>
@@ -12082,25 +12088,26 @@
     </row>
     <row r="221" spans="1:15">
       <c r="A221" s="1">
-        <v>10340021</v>
+        <f>B221*100+H221</f>
+        <v>10350021</v>
       </c>
       <c r="B221" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C221" s="4">
         <v>1</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E221" s="13">
-        <v>103000001</v>
-      </c>
-      <c r="F221" s="18" t="s">
-        <v>60</v>
+        <v>102900001</v>
+      </c>
+      <c r="F221" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="G221" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H221" s="1">
         <v>21</v>
@@ -12121,7 +12128,7 @@
         <v>34</v>
       </c>
       <c r="N221">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="O221" s="15">
         <v>1990000</v>
@@ -12129,25 +12136,26 @@
     </row>
     <row r="222" spans="1:15">
       <c r="A222" s="1">
-        <v>10340022</v>
+        <f t="shared" ref="A222:A223" si="9">B222*100+H222</f>
+        <v>10350022</v>
       </c>
       <c r="B222" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C222" s="4">
         <v>1</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E222" s="13">
-        <v>103000001</v>
-      </c>
-      <c r="F222" s="18" t="s">
-        <v>60</v>
+        <v>102900001</v>
+      </c>
+      <c r="F222" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="G222" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H222" s="1">
         <v>22</v>
@@ -12176,25 +12184,26 @@
     </row>
     <row r="223" spans="1:15">
       <c r="A223" s="1">
-        <v>10340023</v>
+        <f t="shared" si="9"/>
+        <v>10350023</v>
       </c>
       <c r="B223" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C223" s="4">
         <v>1</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E223" s="13">
-        <v>103000001</v>
-      </c>
-      <c r="F223" s="18" t="s">
-        <v>60</v>
+        <v>102900001</v>
+      </c>
+      <c r="F223" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="G223" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H223" s="1">
         <v>23</v>
@@ -12223,26 +12232,25 @@
     </row>
     <row r="224" spans="1:15">
       <c r="A224" s="1">
-        <f>B224*100+H224</f>
-        <v>10350021</v>
+        <v>10350121</v>
       </c>
       <c r="B224" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C224" s="4">
         <v>1</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E224" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F224" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G224" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H224" s="1">
         <v>21</v>
@@ -12253,7 +12261,7 @@
       <c r="J224" s="17">
         <v>-1</v>
       </c>
-      <c r="K224" s="17">
+      <c r="K224" s="1">
         <v>0</v>
       </c>
       <c r="L224" s="3" t="s">
@@ -12271,26 +12279,25 @@
     </row>
     <row r="225" spans="1:15">
       <c r="A225" s="1">
-        <f t="shared" ref="A225:A226" si="10">B225*100+H225</f>
-        <v>10350022</v>
+        <v>10350122</v>
       </c>
       <c r="B225" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C225" s="4">
         <v>1</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E225" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F225" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G225" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H225" s="1">
         <v>22</v>
@@ -12301,7 +12308,7 @@
       <c r="J225" s="17">
         <v>-1</v>
       </c>
-      <c r="K225" s="17">
+      <c r="K225" s="1">
         <v>0</v>
       </c>
       <c r="L225" s="3" t="s">
@@ -12319,26 +12326,25 @@
     </row>
     <row r="226" spans="1:15">
       <c r="A226" s="1">
-        <f t="shared" si="10"/>
-        <v>10350023</v>
+        <v>10350123</v>
       </c>
       <c r="B226" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C226" s="4">
         <v>1</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E226" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F226" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G226" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H226" s="1">
         <v>23</v>
@@ -12349,7 +12355,7 @@
       <c r="J226" s="17">
         <v>-1</v>
       </c>
-      <c r="K226" s="17">
+      <c r="K226" s="1">
         <v>0</v>
       </c>
       <c r="L226" s="3" t="s">
@@ -12367,25 +12373,25 @@
     </row>
     <row r="227" spans="1:15">
       <c r="A227" s="1">
-        <v>10350121</v>
+        <v>10200021</v>
       </c>
       <c r="B227" s="4">
-        <v>103501</v>
+        <v>102000</v>
       </c>
       <c r="C227" s="4">
         <v>1</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E227" s="13">
-        <v>103501001</v>
+        <v>102000001</v>
       </c>
       <c r="F227" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G227" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H227" s="1">
         <v>21</v>
@@ -12406,7 +12412,7 @@
         <v>34</v>
       </c>
       <c r="N227">
-        <v>1000</v>
+        <v>1125</v>
       </c>
       <c r="O227" s="15">
         <v>1990000</v>
@@ -12414,25 +12420,25 @@
     </row>
     <row r="228" spans="1:15">
       <c r="A228" s="1">
-        <v>10350122</v>
+        <v>10200022</v>
       </c>
       <c r="B228" s="4">
-        <v>103501</v>
+        <v>102000</v>
       </c>
       <c r="C228" s="4">
         <v>1</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E228" s="13">
-        <v>103501001</v>
+        <v>102000001</v>
       </c>
       <c r="F228" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G228" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H228" s="1">
         <v>22</v>
@@ -12453,7 +12459,7 @@
         <v>34</v>
       </c>
       <c r="N228">
-        <v>10000</v>
+        <v>11250</v>
       </c>
       <c r="O228" s="15">
         <v>1990000</v>
@@ -12461,25 +12467,25 @@
     </row>
     <row r="229" spans="1:15">
       <c r="A229" s="1">
-        <v>10350123</v>
+        <v>10200023</v>
       </c>
       <c r="B229" s="4">
-        <v>103501</v>
+        <v>102000</v>
       </c>
       <c r="C229" s="4">
         <v>1</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E229" s="13">
-        <v>103501001</v>
+        <v>102000001</v>
       </c>
       <c r="F229" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G229" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H229" s="1">
         <v>23</v>
@@ -12500,7 +12506,7 @@
         <v>34</v>
       </c>
       <c r="N229">
-        <v>100000</v>
+        <v>112500</v>
       </c>
       <c r="O229" s="15">
         <v>1990000</v>
@@ -12508,25 +12514,26 @@
     </row>
     <row r="230" spans="1:15">
       <c r="A230" s="1">
-        <v>10200021</v>
+        <f>B230*100+H230</f>
+        <v>10360021</v>
       </c>
       <c r="B230" s="4">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C230" s="4">
         <v>1</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E230" s="13">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="F230" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G230" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H230" s="1">
         <v>21</v>
@@ -12547,7 +12554,7 @@
         <v>34</v>
       </c>
       <c r="N230">
-        <v>1125</v>
+        <v>1000</v>
       </c>
       <c r="O230" s="15">
         <v>1990000</v>
@@ -12555,25 +12562,26 @@
     </row>
     <row r="231" spans="1:15">
       <c r="A231" s="1">
-        <v>10200022</v>
+        <f t="shared" ref="A231:A232" si="10">B231*100+H231</f>
+        <v>10360022</v>
       </c>
       <c r="B231" s="4">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C231" s="4">
         <v>1</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E231" s="13">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="F231" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G231" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H231" s="1">
         <v>22</v>
@@ -12594,7 +12602,7 @@
         <v>34</v>
       </c>
       <c r="N231">
-        <v>11250</v>
+        <v>10000</v>
       </c>
       <c r="O231" s="15">
         <v>1990000</v>
@@ -12602,25 +12610,26 @@
     </row>
     <row r="232" spans="1:15">
       <c r="A232" s="1">
-        <v>10200023</v>
+        <f t="shared" si="10"/>
+        <v>10360023</v>
       </c>
       <c r="B232" s="4">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C232" s="4">
         <v>1</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E232" s="13">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="F232" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G232" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H232" s="1">
         <v>23</v>
@@ -12641,7 +12650,7 @@
         <v>34</v>
       </c>
       <c r="N232">
-        <v>112500</v>
+        <v>100000</v>
       </c>
       <c r="O232" s="15">
         <v>1990000</v>
@@ -12649,26 +12658,25 @@
     </row>
     <row r="233" spans="1:15">
       <c r="A233" s="1">
-        <f>B233*100+H233</f>
-        <v>10360021</v>
+        <v>10340121</v>
       </c>
       <c r="B233" s="4">
-        <v>103600</v>
+        <v>103401</v>
       </c>
       <c r="C233" s="4">
         <v>1</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E233" s="13">
-        <v>103600001</v>
+        <v>103400001</v>
       </c>
       <c r="F233" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G233" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H233" s="1">
         <v>21</v>
@@ -12697,26 +12705,25 @@
     </row>
     <row r="234" spans="1:15">
       <c r="A234" s="1">
-        <f t="shared" ref="A234:A235" si="11">B234*100+H234</f>
-        <v>10360022</v>
+        <v>10340122</v>
       </c>
       <c r="B234" s="4">
-        <v>103600</v>
+        <v>103401</v>
       </c>
       <c r="C234" s="4">
         <v>1</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E234" s="13">
-        <v>103600001</v>
+        <v>103400001</v>
       </c>
       <c r="F234" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G234" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H234" s="1">
         <v>22</v>
@@ -12745,26 +12752,25 @@
     </row>
     <row r="235" spans="1:15">
       <c r="A235" s="1">
-        <f t="shared" si="11"/>
-        <v>10360023</v>
+        <v>10340123</v>
       </c>
       <c r="B235" s="4">
-        <v>103600</v>
+        <v>103401</v>
       </c>
       <c r="C235" s="4">
         <v>1</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E235" s="13">
-        <v>103600001</v>
+        <v>103400001</v>
       </c>
       <c r="F235" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G235" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H235" s="1">
         <v>23</v>
@@ -12793,25 +12799,25 @@
     </row>
     <row r="236" spans="1:15">
       <c r="A236" s="1">
-        <v>10340121</v>
+        <v>10380021</v>
       </c>
       <c r="B236" s="4">
-        <v>103401</v>
+        <v>103800</v>
       </c>
       <c r="C236" s="4">
         <v>1</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E236" s="13">
-        <v>103400001</v>
+        <v>103800001</v>
       </c>
       <c r="F236" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G236" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H236" s="1">
         <v>21</v>
@@ -12832,7 +12838,7 @@
         <v>34</v>
       </c>
       <c r="N236">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="O236" s="15">
         <v>1990000</v>
@@ -12840,31 +12846,31 @@
     </row>
     <row r="237" spans="1:15">
       <c r="A237" s="1">
-        <v>10340122</v>
+        <v>10380022</v>
       </c>
       <c r="B237" s="4">
-        <v>103401</v>
+        <v>103800</v>
       </c>
       <c r="C237" s="4">
         <v>1</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E237" s="13">
-        <v>103400001</v>
+        <v>103800001</v>
       </c>
       <c r="F237" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G237" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H237" s="1">
         <v>22</v>
       </c>
       <c r="I237" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="J237" s="17">
         <v>-1</v>
@@ -12879,7 +12885,7 @@
         <v>34</v>
       </c>
       <c r="N237">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="O237" s="15">
         <v>1990000</v>
@@ -12887,31 +12893,31 @@
     </row>
     <row r="238" spans="1:15">
       <c r="A238" s="1">
-        <v>10340123</v>
+        <v>10380023</v>
       </c>
       <c r="B238" s="4">
-        <v>103401</v>
+        <v>103800</v>
       </c>
       <c r="C238" s="4">
         <v>1</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E238" s="13">
-        <v>103400001</v>
+        <v>103800001</v>
       </c>
       <c r="F238" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G238" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H238" s="1">
         <v>23</v>
       </c>
       <c r="I238" s="2">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="J238" s="17">
         <v>-1</v>
@@ -12926,7 +12932,7 @@
         <v>34</v>
       </c>
       <c r="N238">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="O238" s="15">
         <v>1990000</v>
@@ -12934,25 +12940,25 @@
     </row>
     <row r="239" spans="1:15">
       <c r="A239" s="1">
-        <v>10380021</v>
+        <v>10400021</v>
       </c>
       <c r="B239" s="4">
-        <v>103800</v>
+        <v>104000</v>
       </c>
       <c r="C239" s="4">
         <v>1</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E239" s="13">
-        <v>103800001</v>
-      </c>
-      <c r="F239" s="13" t="s">
-        <v>72</v>
+        <v>104000001</v>
+      </c>
+      <c r="F239" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="G239" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H239" s="1">
         <v>21</v>
@@ -12973,7 +12979,7 @@
         <v>34</v>
       </c>
       <c r="N239">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="O239" s="15">
         <v>1990000</v>
@@ -12981,31 +12987,31 @@
     </row>
     <row r="240" spans="1:15">
       <c r="A240" s="1">
-        <v>10380022</v>
+        <v>10400022</v>
       </c>
       <c r="B240" s="4">
-        <v>103800</v>
+        <v>104000</v>
       </c>
       <c r="C240" s="4">
         <v>1</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E240" s="13">
-        <v>103800001</v>
-      </c>
-      <c r="F240" s="13" t="s">
-        <v>72</v>
+        <v>104000001</v>
+      </c>
+      <c r="F240" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="G240" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H240" s="1">
         <v>22</v>
       </c>
       <c r="I240" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="J240" s="17">
         <v>-1</v>
@@ -13020,7 +13026,7 @@
         <v>34</v>
       </c>
       <c r="N240">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="O240" s="15">
         <v>1990000</v>
@@ -13028,31 +13034,31 @@
     </row>
     <row r="241" spans="1:19">
       <c r="A241" s="1">
-        <v>10380023</v>
+        <v>10400023</v>
       </c>
       <c r="B241" s="4">
-        <v>103800</v>
+        <v>104000</v>
       </c>
       <c r="C241" s="4">
         <v>1</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E241" s="13">
-        <v>103800001</v>
-      </c>
-      <c r="F241" s="13" t="s">
-        <v>72</v>
+        <v>104000001</v>
+      </c>
+      <c r="F241" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="G241" s="27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H241" s="1">
         <v>23</v>
       </c>
       <c r="I241" s="2">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="J241" s="17">
         <v>-1</v>
@@ -13067,7 +13073,7 @@
         <v>34</v>
       </c>
       <c r="N241">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="O241" s="15">
         <v>1990000</v>
@@ -13075,25 +13081,25 @@
     </row>
     <row r="242" spans="1:19">
       <c r="A242" s="1">
-        <v>10400021</v>
+        <v>20010021</v>
       </c>
       <c r="B242" s="4">
-        <v>104000</v>
+        <v>200100</v>
       </c>
       <c r="C242" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E242" s="13">
-        <v>104000001</v>
-      </c>
-      <c r="F242" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G242" s="27" t="s">
-        <v>113</v>
+        <v>200100038</v>
+      </c>
+      <c r="F242" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H242" s="1">
         <v>21</v>
@@ -13101,7 +13107,7 @@
       <c r="I242" s="2">
         <v>0</v>
       </c>
-      <c r="J242" s="17">
+      <c r="J242" s="1">
         <v>-1</v>
       </c>
       <c r="K242" s="1">
@@ -13122,25 +13128,25 @@
     </row>
     <row r="243" spans="1:19">
       <c r="A243" s="1">
-        <v>10400022</v>
+        <v>20010022</v>
       </c>
       <c r="B243" s="4">
-        <v>104000</v>
+        <v>200100</v>
       </c>
       <c r="C243" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E243" s="13">
-        <v>104000001</v>
-      </c>
-      <c r="F243" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G243" s="27" t="s">
-        <v>114</v>
+        <v>200100038</v>
+      </c>
+      <c r="F243" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="H243" s="1">
         <v>22</v>
@@ -13148,7 +13154,7 @@
       <c r="I243" s="2">
         <v>10000</v>
       </c>
-      <c r="J243" s="17">
+      <c r="J243" s="1">
         <v>-1</v>
       </c>
       <c r="K243" s="1">
@@ -13169,25 +13175,25 @@
     </row>
     <row r="244" spans="1:19">
       <c r="A244" s="1">
-        <v>10400023</v>
+        <v>20010023</v>
       </c>
       <c r="B244" s="4">
-        <v>104000</v>
+        <v>200100</v>
       </c>
       <c r="C244" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E244" s="13">
-        <v>104000001</v>
-      </c>
-      <c r="F244" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G244" s="27" t="s">
-        <v>115</v>
+        <v>200100038</v>
+      </c>
+      <c r="F244" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G244" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="H244" s="1">
         <v>23</v>
@@ -13195,7 +13201,7 @@
       <c r="I244" s="2">
         <v>100000</v>
       </c>
-      <c r="J244" s="17">
+      <c r="J244" s="1">
         <v>-1</v>
       </c>
       <c r="K244" s="1">
@@ -13213,25 +13219,26 @@
       <c r="O244" s="15">
         <v>1990000</v>
       </c>
+      <c r="Q244"/>
     </row>
     <row r="245" spans="1:19">
       <c r="A245" s="1">
-        <v>20010021</v>
+        <v>20010121</v>
       </c>
       <c r="B245" s="4">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C245" s="4">
         <v>2</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E245" s="13">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F245" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G245" s="1" t="s">
         <v>32</v>
@@ -13263,22 +13270,22 @@
     </row>
     <row r="246" spans="1:19">
       <c r="A246" s="1">
-        <v>20010022</v>
+        <v>20010122</v>
       </c>
       <c r="B246" s="4">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C246" s="4">
         <v>2</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E246" s="13">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F246" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G246" s="1" t="s">
         <v>35</v>
@@ -13307,25 +13314,26 @@
       <c r="O246" s="15">
         <v>1990000</v>
       </c>
+      <c r="S246" s="1"/>
     </row>
     <row r="247" spans="1:19">
       <c r="A247" s="1">
-        <v>20010023</v>
+        <v>20010123</v>
       </c>
       <c r="B247" s="4">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C247" s="4">
         <v>2</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E247" s="13">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F247" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>36</v>
@@ -13354,26 +13362,26 @@
       <c r="O247" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q247"/>
+      <c r="S247" s="1"/>
     </row>
     <row r="248" spans="1:19">
       <c r="A248" s="1">
-        <v>20010121</v>
+        <v>20030021</v>
       </c>
       <c r="B248" s="4">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C248" s="4">
         <v>2</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E248" s="13">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F248" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>32</v>
@@ -13405,22 +13413,22 @@
     </row>
     <row r="249" spans="1:19">
       <c r="A249" s="1">
-        <v>20010122</v>
+        <v>20030022</v>
       </c>
       <c r="B249" s="4">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C249" s="4">
         <v>2</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E249" s="13">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F249" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>35</v>
@@ -13449,26 +13457,27 @@
       <c r="O249" s="15">
         <v>1990000</v>
       </c>
-      <c r="S249" s="1"/>
+      <c r="Q249" s="2"/>
+      <c r="R249" s="4"/>
     </row>
     <row r="250" spans="1:19">
       <c r="A250" s="1">
-        <v>20010123</v>
+        <v>20030023</v>
       </c>
       <c r="B250" s="4">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C250" s="4">
         <v>2</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E250" s="13">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F250" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>36</v>
@@ -13497,26 +13506,27 @@
       <c r="O250" s="15">
         <v>1990000</v>
       </c>
-      <c r="S250" s="1"/>
+      <c r="Q250" s="2"/>
+      <c r="R250" s="2"/>
     </row>
     <row r="251" spans="1:19">
       <c r="A251" s="1">
-        <v>20030021</v>
+        <v>20040021</v>
       </c>
       <c r="B251" s="4">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C251" s="4">
         <v>2</v>
       </c>
-      <c r="D251" s="4" t="s">
-        <v>79</v>
+      <c r="D251" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="E251" s="13">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F251" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>32</v>
@@ -13545,25 +13555,27 @@
       <c r="O251" s="15">
         <v>1990000</v>
       </c>
+      <c r="Q251" s="2"/>
+      <c r="R251" s="2"/>
     </row>
     <row r="252" spans="1:19">
       <c r="A252" s="1">
-        <v>20030022</v>
+        <v>20040022</v>
       </c>
       <c r="B252" s="4">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C252" s="4">
         <v>2</v>
       </c>
-      <c r="D252" s="4" t="s">
-        <v>79</v>
+      <c r="D252" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="E252" s="13">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F252" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>35</v>
@@ -13593,26 +13605,26 @@
         <v>1990000</v>
       </c>
       <c r="Q252" s="2"/>
-      <c r="R252" s="4"/>
+      <c r="R252" s="2"/>
     </row>
     <row r="253" spans="1:19">
       <c r="A253" s="1">
-        <v>20030023</v>
+        <v>20040023</v>
       </c>
       <c r="B253" s="4">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C253" s="4">
         <v>2</v>
       </c>
-      <c r="D253" s="4" t="s">
-        <v>79</v>
+      <c r="D253" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="E253" s="13">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F253" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>36</v>
@@ -13646,22 +13658,22 @@
     </row>
     <row r="254" spans="1:19">
       <c r="A254" s="1">
-        <v>20040021</v>
+        <v>20050021</v>
       </c>
       <c r="B254" s="4">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C254" s="4">
         <v>2</v>
       </c>
-      <c r="D254" s="2" t="s">
-        <v>81</v>
+      <c r="D254" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="E254" s="13">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F254" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G254" s="1" t="s">
         <v>32</v>
@@ -13682,7 +13694,7 @@
         <v>33</v>
       </c>
       <c r="M254" s="28" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="N254">
         <v>1000</v>
@@ -13695,22 +13707,22 @@
     </row>
     <row r="255" spans="1:19">
       <c r="A255" s="1">
-        <v>20040022</v>
+        <v>20050022</v>
       </c>
       <c r="B255" s="4">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C255" s="4">
         <v>2</v>
       </c>
-      <c r="D255" s="2" t="s">
-        <v>81</v>
+      <c r="D255" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="E255" s="13">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F255" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>35</v>
@@ -13731,7 +13743,7 @@
         <v>33</v>
       </c>
       <c r="M255" s="28" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="N255">
         <v>10000</v>
@@ -13744,22 +13756,22 @@
     </row>
     <row r="256" spans="1:19">
       <c r="A256" s="1">
-        <v>20040023</v>
+        <v>20050023</v>
       </c>
       <c r="B256" s="4">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C256" s="4">
         <v>2</v>
       </c>
-      <c r="D256" s="2" t="s">
-        <v>81</v>
+      <c r="D256" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="E256" s="13">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F256" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>36</v>
@@ -13780,7 +13792,7 @@
         <v>33</v>
       </c>
       <c r="M256" s="28" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="N256">
         <v>100000</v>
@@ -13793,22 +13805,22 @@
     </row>
     <row r="257" spans="1:18">
       <c r="A257" s="1">
-        <v>20050021</v>
+        <v>20060021</v>
       </c>
       <c r="B257" s="4">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C257" s="4">
         <v>2</v>
       </c>
-      <c r="D257" s="4" t="s">
-        <v>83</v>
+      <c r="D257" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="E257" s="13">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F257" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>32</v>
@@ -13829,7 +13841,7 @@
         <v>33</v>
       </c>
       <c r="M257" s="28" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="N257">
         <v>1000</v>
@@ -13842,22 +13854,22 @@
     </row>
     <row r="258" spans="1:18">
       <c r="A258" s="1">
-        <v>20050022</v>
+        <v>20060022</v>
       </c>
       <c r="B258" s="4">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C258" s="4">
         <v>2</v>
       </c>
-      <c r="D258" s="4" t="s">
-        <v>83</v>
+      <c r="D258" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="E258" s="13">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F258" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>35</v>
@@ -13878,7 +13890,7 @@
         <v>33</v>
       </c>
       <c r="M258" s="28" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="N258">
         <v>10000</v>
@@ -13891,22 +13903,22 @@
     </row>
     <row r="259" spans="1:18">
       <c r="A259" s="1">
-        <v>20050023</v>
+        <v>20060023</v>
       </c>
       <c r="B259" s="4">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C259" s="4">
         <v>2</v>
       </c>
-      <c r="D259" s="4" t="s">
-        <v>83</v>
+      <c r="D259" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="E259" s="13">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F259" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>36</v>
@@ -13927,7 +13939,7 @@
         <v>33</v>
       </c>
       <c r="M259" s="28" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="N259">
         <v>100000</v>
@@ -13936,26 +13948,26 @@
         <v>1990000</v>
       </c>
       <c r="Q259" s="2"/>
-      <c r="R259" s="2"/>
+      <c r="R259"/>
     </row>
     <row r="260" spans="1:18">
       <c r="A260" s="1">
-        <v>20060021</v>
+        <v>20070021</v>
       </c>
       <c r="B260" s="4">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C260" s="4">
         <v>2</v>
       </c>
-      <c r="D260" s="13" t="s">
-        <v>86</v>
+      <c r="D260" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="E260" s="13">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F260" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G260" s="1" t="s">
         <v>32</v>
@@ -13989,22 +14001,22 @@
     </row>
     <row r="261" spans="1:18">
       <c r="A261" s="1">
-        <v>20060022</v>
+        <v>20070022</v>
       </c>
       <c r="B261" s="4">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C261" s="4">
         <v>2</v>
       </c>
-      <c r="D261" s="13" t="s">
-        <v>86</v>
+      <c r="D261" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="E261" s="13">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F261" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>35</v>
@@ -14038,22 +14050,22 @@
     </row>
     <row r="262" spans="1:18">
       <c r="A262" s="1">
-        <v>20060023</v>
+        <v>20070023</v>
       </c>
       <c r="B262" s="4">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C262" s="4">
         <v>2</v>
       </c>
-      <c r="D262" s="13" t="s">
-        <v>86</v>
+      <c r="D262" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="E262" s="13">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F262" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>36</v>
@@ -14082,27 +14094,25 @@
       <c r="O262" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q262" s="2"/>
-      <c r="R262"/>
     </row>
     <row r="263" spans="1:18">
       <c r="A263" s="1">
-        <v>20070021</v>
+        <v>20080021</v>
       </c>
       <c r="B263" s="4">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C263" s="4">
         <v>2</v>
       </c>
-      <c r="D263" s="4" t="s">
-        <v>88</v>
+      <c r="D263" s="13" t="s">
+        <v>90</v>
       </c>
       <c r="E263" s="13">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F263" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>32</v>
@@ -14131,27 +14141,25 @@
       <c r="O263" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q263" s="2"/>
-      <c r="R263" s="2"/>
     </row>
     <row r="264" spans="1:18">
       <c r="A264" s="1">
-        <v>20070022</v>
+        <v>20080022</v>
       </c>
       <c r="B264" s="4">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C264" s="4">
         <v>2</v>
       </c>
-      <c r="D264" s="4" t="s">
-        <v>88</v>
+      <c r="D264" s="13" t="s">
+        <v>90</v>
       </c>
       <c r="E264" s="13">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F264" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>35</v>
@@ -14180,27 +14188,25 @@
       <c r="O264" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q264" s="2"/>
-      <c r="R264" s="2"/>
     </row>
     <row r="265" spans="1:18">
       <c r="A265" s="1">
-        <v>20070023</v>
+        <v>20080023</v>
       </c>
       <c r="B265" s="4">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C265" s="4">
         <v>2</v>
       </c>
-      <c r="D265" s="4" t="s">
-        <v>88</v>
+      <c r="D265" s="13" t="s">
+        <v>90</v>
       </c>
       <c r="E265" s="13">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F265" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>36</v>
@@ -14232,22 +14238,22 @@
     </row>
     <row r="266" spans="1:18">
       <c r="A266" s="1">
-        <v>20080021</v>
-      </c>
-      <c r="B266" s="4">
-        <v>200800</v>
+        <v>20090021</v>
+      </c>
+      <c r="B266" s="20">
+        <v>200900</v>
       </c>
       <c r="C266" s="4">
         <v>2</v>
       </c>
-      <c r="D266" s="13" t="s">
-        <v>90</v>
+      <c r="D266" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="E266" s="13">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F266" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>32</v>
@@ -14279,22 +14285,22 @@
     </row>
     <row r="267" spans="1:18">
       <c r="A267" s="1">
-        <v>20080022</v>
+        <v>20090022</v>
       </c>
       <c r="B267" s="4">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C267" s="4">
         <v>2</v>
       </c>
-      <c r="D267" s="13" t="s">
-        <v>90</v>
+      <c r="D267" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="E267" s="13">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F267" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>35</v>
@@ -14326,22 +14332,22 @@
     </row>
     <row r="268" spans="1:18">
       <c r="A268" s="1">
-        <v>20080023</v>
+        <v>20090023</v>
       </c>
       <c r="B268" s="4">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C268" s="4">
         <v>2</v>
       </c>
-      <c r="D268" s="13" t="s">
-        <v>90</v>
+      <c r="D268" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="E268" s="13">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F268" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>36</v>
@@ -14373,22 +14379,22 @@
     </row>
     <row r="269" spans="1:18">
       <c r="A269" s="1">
-        <v>20090021</v>
-      </c>
-      <c r="B269" s="20">
-        <v>200900</v>
+        <v>30010021</v>
+      </c>
+      <c r="B269" s="4">
+        <v>300100</v>
       </c>
       <c r="C269" s="4">
-        <v>2</v>
-      </c>
-      <c r="D269" s="20" t="s">
-        <v>92</v>
+        <v>3</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="E269" s="13">
-        <v>200900001</v>
+        <v>300100001</v>
       </c>
       <c r="F269" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>32</v>
@@ -14406,10 +14412,10 @@
         <v>0</v>
       </c>
       <c r="L269" s="3" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="M269" s="28" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="N269">
         <v>1000</v>
@@ -14420,22 +14426,22 @@
     </row>
     <row r="270" spans="1:18">
       <c r="A270" s="1">
-        <v>20090022</v>
+        <v>30010022</v>
       </c>
       <c r="B270" s="4">
-        <v>200900</v>
+        <v>300100</v>
       </c>
       <c r="C270" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E270" s="13">
-        <v>200900001</v>
+        <v>300100001</v>
       </c>
       <c r="F270" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>35</v>
@@ -14453,10 +14459,10 @@
         <v>0</v>
       </c>
       <c r="L270" s="3" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="M270" s="28" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="N270">
         <v>10000</v>
@@ -14467,22 +14473,22 @@
     </row>
     <row r="271" spans="1:18">
       <c r="A271" s="1">
-        <v>20090023</v>
+        <v>30010023</v>
       </c>
       <c r="B271" s="4">
-        <v>200900</v>
+        <v>300100</v>
       </c>
       <c r="C271" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E271" s="13">
-        <v>200900001</v>
+        <v>300100001</v>
       </c>
       <c r="F271" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>36</v>
@@ -14500,10 +14506,10 @@
         <v>0</v>
       </c>
       <c r="L271" s="3" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="M271" s="28" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="N271">
         <v>100000</v>
@@ -14514,22 +14520,22 @@
     </row>
     <row r="272" spans="1:18">
       <c r="A272" s="1">
-        <v>30010021</v>
+        <v>30020021</v>
       </c>
       <c r="B272" s="4">
-        <v>300100</v>
+        <v>300200</v>
       </c>
       <c r="C272" s="4">
         <v>3</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E272" s="13">
-        <v>300100001</v>
+        <v>300200006</v>
       </c>
       <c r="F272" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>32</v>
@@ -14538,7 +14544,7 @@
         <v>21</v>
       </c>
       <c r="I272" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J272" s="1">
         <v>-1</v>
@@ -14547,12 +14553,12 @@
         <v>0</v>
       </c>
       <c r="L272" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M272" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N272">
+      <c r="N272" s="21">
         <v>1000</v>
       </c>
       <c r="O272" s="15">
@@ -14561,22 +14567,22 @@
     </row>
     <row r="273" spans="1:15">
       <c r="A273" s="1">
-        <v>30010022</v>
+        <v>30020022</v>
       </c>
       <c r="B273" s="4">
-        <v>300100</v>
+        <v>300200</v>
       </c>
       <c r="C273" s="4">
         <v>3</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E273" s="13">
-        <v>300100001</v>
+        <v>300200006</v>
       </c>
       <c r="F273" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>35</v>
@@ -14594,12 +14600,12 @@
         <v>0</v>
       </c>
       <c r="L273" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M273" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N273">
+      <c r="N273" s="21">
         <v>10000</v>
       </c>
       <c r="O273" s="15">
@@ -14608,22 +14614,22 @@
     </row>
     <row r="274" spans="1:15">
       <c r="A274" s="1">
-        <v>30010023</v>
+        <v>30020023</v>
       </c>
       <c r="B274" s="4">
-        <v>300100</v>
+        <v>300200</v>
       </c>
       <c r="C274" s="4">
         <v>3</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E274" s="13">
-        <v>300100001</v>
+        <v>300200006</v>
       </c>
       <c r="F274" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>36</v>
@@ -14641,12 +14647,12 @@
         <v>0</v>
       </c>
       <c r="L274" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M274" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N274">
+      <c r="N274" s="21">
         <v>100000</v>
       </c>
       <c r="O274" s="15">
@@ -14655,22 +14661,22 @@
     </row>
     <row r="275" spans="1:15">
       <c r="A275" s="1">
-        <v>30020021</v>
+        <v>30040021</v>
       </c>
       <c r="B275" s="4">
-        <v>300200</v>
-      </c>
-      <c r="C275" s="4">
+        <v>300400</v>
+      </c>
+      <c r="C275" s="1">
         <v>3</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E275" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F275" s="13" t="s">
-        <v>99</v>
+        <v>300400023</v>
+      </c>
+      <c r="F275" s="22" t="s">
+        <v>102</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>32</v>
@@ -14678,8 +14684,9 @@
       <c r="H275" s="1">
         <v>21</v>
       </c>
-      <c r="I275" s="2">
-        <v>1000</v>
+      <c r="I275" s="23">
+        <f>N275*52</f>
+        <v>5200</v>
       </c>
       <c r="J275" s="1">
         <v>-1</v>
@@ -14688,13 +14695,13 @@
         <v>0</v>
       </c>
       <c r="L275" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M275" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N275" s="21">
-        <v>1000</v>
+      <c r="N275" s="23">
+        <v>100</v>
       </c>
       <c r="O275" s="15">
         <v>1990000</v>
@@ -14702,22 +14709,22 @@
     </row>
     <row r="276" spans="1:15">
       <c r="A276" s="1">
-        <v>30020022</v>
+        <v>30040022</v>
       </c>
       <c r="B276" s="4">
-        <v>300200</v>
+        <v>300400</v>
       </c>
       <c r="C276" s="4">
         <v>3</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E276" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F276" s="13" t="s">
-        <v>99</v>
+        <v>300400023</v>
+      </c>
+      <c r="F276" s="22" t="s">
+        <v>102</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>35</v>
@@ -14725,8 +14732,9 @@
       <c r="H276" s="1">
         <v>22</v>
       </c>
-      <c r="I276" s="2">
-        <v>10000</v>
+      <c r="I276" s="23">
+        <f t="shared" ref="I276:I283" si="11">N276*52</f>
+        <v>52000</v>
       </c>
       <c r="J276" s="1">
         <v>-1</v>
@@ -14735,13 +14743,13 @@
         <v>0</v>
       </c>
       <c r="L276" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M276" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N276" s="21">
-        <v>10000</v>
+      <c r="N276" s="23">
+        <v>1000</v>
       </c>
       <c r="O276" s="15">
         <v>1990000</v>
@@ -14749,22 +14757,22 @@
     </row>
     <row r="277" spans="1:15">
       <c r="A277" s="1">
-        <v>30020023</v>
+        <v>30040023</v>
       </c>
       <c r="B277" s="4">
-        <v>300200</v>
+        <v>300400</v>
       </c>
       <c r="C277" s="4">
         <v>3</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E277" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F277" s="13" t="s">
-        <v>99</v>
+        <v>300400023</v>
+      </c>
+      <c r="F277" s="22" t="s">
+        <v>102</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>36</v>
@@ -14772,8 +14780,9 @@
       <c r="H277" s="1">
         <v>23</v>
       </c>
-      <c r="I277" s="2">
-        <v>100000</v>
+      <c r="I277" s="23">
+        <f t="shared" si="11"/>
+        <v>520000</v>
       </c>
       <c r="J277" s="1">
         <v>-1</v>
@@ -14782,13 +14791,13 @@
         <v>0</v>
       </c>
       <c r="L277" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M277" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N277" s="21">
-        <v>100000</v>
+      <c r="N277" s="23">
+        <v>10000</v>
       </c>
       <c r="O277" s="15">
         <v>1990000</v>
@@ -14796,22 +14805,22 @@
     </row>
     <row r="278" spans="1:15">
       <c r="A278" s="1">
-        <v>30040021</v>
+        <v>20120021</v>
       </c>
       <c r="B278" s="4">
-        <v>300400</v>
-      </c>
-      <c r="C278" s="1">
-        <v>3</v>
+        <v>201200</v>
+      </c>
+      <c r="C278" s="4">
+        <v>2</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E278" s="13">
-        <v>300400023</v>
+        <v>201200001</v>
       </c>
       <c r="F278" s="22" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>32</v>
@@ -14819,9 +14828,8 @@
       <c r="H278" s="1">
         <v>21</v>
       </c>
-      <c r="I278" s="23">
-        <f>N278*52</f>
-        <v>5200</v>
+      <c r="I278" s="2">
+        <v>0</v>
       </c>
       <c r="J278" s="1">
         <v>-1</v>
@@ -14830,13 +14838,13 @@
         <v>0</v>
       </c>
       <c r="L278" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M278" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N278" s="23">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="N278">
+        <v>1000</v>
       </c>
       <c r="O278" s="15">
         <v>1990000</v>
@@ -14844,22 +14852,22 @@
     </row>
     <row r="279" spans="1:15">
       <c r="A279" s="1">
-        <v>30040022</v>
+        <v>20120022</v>
       </c>
       <c r="B279" s="4">
-        <v>300400</v>
+        <v>201200</v>
       </c>
       <c r="C279" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E279" s="13">
-        <v>300400023</v>
+        <v>201200001</v>
       </c>
       <c r="F279" s="22" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>35</v>
@@ -14867,9 +14875,8 @@
       <c r="H279" s="1">
         <v>22</v>
       </c>
-      <c r="I279" s="23">
-        <f>N279*52</f>
-        <v>52000</v>
+      <c r="I279" s="2">
+        <v>10000</v>
       </c>
       <c r="J279" s="1">
         <v>-1</v>
@@ -14878,13 +14885,13 @@
         <v>0</v>
       </c>
       <c r="L279" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M279" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N279" s="23">
-        <v>1000</v>
+        <v>85</v>
+      </c>
+      <c r="N279">
+        <v>10000</v>
       </c>
       <c r="O279" s="15">
         <v>1990000</v>
@@ -14892,22 +14899,22 @@
     </row>
     <row r="280" spans="1:15">
       <c r="A280" s="1">
-        <v>30040023</v>
+        <v>20120023</v>
       </c>
       <c r="B280" s="4">
-        <v>300400</v>
+        <v>201200</v>
       </c>
       <c r="C280" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E280" s="13">
-        <v>300400023</v>
+        <v>201200001</v>
       </c>
       <c r="F280" s="22" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>36</v>
@@ -14915,9 +14922,8 @@
       <c r="H280" s="1">
         <v>23</v>
       </c>
-      <c r="I280" s="23">
-        <f>N280*52</f>
-        <v>520000</v>
+      <c r="I280" s="2">
+        <v>100000</v>
       </c>
       <c r="J280" s="1">
         <v>-1</v>
@@ -14926,13 +14932,13 @@
         <v>0</v>
       </c>
       <c r="L280" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M280" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N280" s="23">
-        <v>10000</v>
+        <v>85</v>
+      </c>
+      <c r="N280">
+        <v>100000</v>
       </c>
       <c r="O280" s="15">
         <v>1990000</v>
@@ -14940,31 +14946,32 @@
     </row>
     <row r="281" spans="1:15">
       <c r="A281" s="1">
-        <v>20120021</v>
+        <v>30040231</v>
       </c>
       <c r="B281" s="4">
-        <v>201200</v>
-      </c>
-      <c r="C281" s="4">
-        <v>2</v>
+        <v>300402</v>
+      </c>
+      <c r="C281" s="1">
+        <v>3</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E281" s="13">
-        <v>201200001</v>
+        <v>300402001</v>
       </c>
       <c r="F281" s="22" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H281" s="1">
-        <v>21</v>
-      </c>
-      <c r="I281" s="2">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="I281" s="23">
+        <f t="shared" si="11"/>
+        <v>5200</v>
       </c>
       <c r="J281" s="1">
         <v>-1</v>
@@ -14973,45 +14980,46 @@
         <v>0</v>
       </c>
       <c r="L281" s="3" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="M281" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="N281">
-        <v>1000</v>
+        <v>97</v>
+      </c>
+      <c r="N281" s="23">
+        <v>100</v>
       </c>
       <c r="O281" s="15">
-        <v>1990000</v>
+        <v>1970000</v>
       </c>
     </row>
     <row r="282" spans="1:15">
       <c r="A282" s="1">
-        <v>20120022</v>
+        <v>30040232</v>
       </c>
       <c r="B282" s="4">
-        <v>201200</v>
+        <v>300402</v>
       </c>
       <c r="C282" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E282" s="13">
-        <v>201200001</v>
+        <v>300402001</v>
       </c>
       <c r="F282" s="22" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H282" s="1">
-        <v>22</v>
-      </c>
-      <c r="I282" s="2">
-        <v>10000</v>
+        <v>32</v>
+      </c>
+      <c r="I282" s="23">
+        <f t="shared" si="11"/>
+        <v>52000</v>
       </c>
       <c r="J282" s="1">
         <v>-1</v>
@@ -15020,45 +15028,46 @@
         <v>0</v>
       </c>
       <c r="L282" s="3" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="M282" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="N282">
-        <v>10000</v>
+        <v>97</v>
+      </c>
+      <c r="N282" s="23">
+        <v>1000</v>
       </c>
       <c r="O282" s="15">
-        <v>1990000</v>
+        <v>1970000</v>
       </c>
     </row>
     <row r="283" spans="1:15">
       <c r="A283" s="1">
-        <v>20120023</v>
+        <v>30040233</v>
       </c>
       <c r="B283" s="4">
-        <v>201200</v>
+        <v>300402</v>
       </c>
       <c r="C283" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E283" s="13">
-        <v>201200001</v>
+        <v>300402001</v>
       </c>
       <c r="F283" s="22" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H283" s="1">
-        <v>23</v>
-      </c>
-      <c r="I283" s="2">
-        <v>100000</v>
+        <v>33</v>
+      </c>
+      <c r="I283" s="23">
+        <f t="shared" si="11"/>
+        <v>520000</v>
       </c>
       <c r="J283" s="1">
         <v>-1</v>
@@ -15067,16 +15076,16 @@
         <v>0</v>
       </c>
       <c r="L283" s="3" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="M283" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="N283">
-        <v>100000</v>
+        <v>97</v>
+      </c>
+      <c r="N283" s="23">
+        <v>10000</v>
       </c>
       <c r="O283" s="15">
-        <v>1990000</v>
+        <v>1970000</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28770" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -470,12 +470,6 @@
     <t>4:4</t>
   </si>
   <si>
-    <t>南方前进-体验场</t>
-  </si>
-  <si>
-    <t>TienLenMienNamTY</t>
-  </si>
-  <si>
     <t>俄罗斯轮盘</t>
   </si>
   <si>
@@ -507,6 +501,12 @@
   </si>
   <si>
     <t>高级场-特殊</t>
+  </si>
+  <si>
+    <t>南方前进-体验场</t>
+  </si>
+  <si>
+    <t>TienLenMienNamTY</t>
   </si>
 </sst>
 </file>
@@ -719,12 +719,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6251,7 +6251,7 @@
         <v>1</v>
       </c>
       <c r="I98" s="23">
-        <f t="shared" ref="I98:I103" si="1">N98*52</f>
+        <f>N98*52</f>
         <v>5200</v>
       </c>
       <c r="J98" s="1">
@@ -6299,7 +6299,7 @@
         <v>2</v>
       </c>
       <c r="I99" s="23">
-        <f t="shared" si="1"/>
+        <f>N99*52</f>
         <v>52000</v>
       </c>
       <c r="J99" s="1">
@@ -6347,7 +6347,7 @@
         <v>3</v>
       </c>
       <c r="I100" s="23">
-        <f t="shared" si="1"/>
+        <f>N100*52</f>
         <v>520000</v>
       </c>
       <c r="J100" s="1">
@@ -6371,19 +6371,19 @@
     </row>
     <row r="101" spans="1:15">
       <c r="A101" s="1">
-        <v>3004021</v>
+        <v>2012001</v>
       </c>
       <c r="B101" s="4">
-        <v>300402</v>
-      </c>
-      <c r="C101" s="1">
-        <v>3</v>
+        <v>201200</v>
+      </c>
+      <c r="C101" s="4">
+        <v>2</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>104</v>
       </c>
       <c r="E101" s="13">
-        <v>300402001</v>
+        <v>201200001</v>
       </c>
       <c r="F101" s="22" t="s">
         <v>105</v>
@@ -6394,9 +6394,8 @@
       <c r="H101" s="1">
         <v>1</v>
       </c>
-      <c r="I101" s="23">
-        <f t="shared" si="1"/>
-        <v>5200</v>
+      <c r="I101" s="2">
+        <v>0</v>
       </c>
       <c r="J101" s="1">
         <v>-1</v>
@@ -6405,33 +6404,33 @@
         <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M101" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N101" s="23">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="N101">
+        <v>1000</v>
       </c>
       <c r="O101" s="15">
-        <v>1970000</v>
+        <v>1990000</v>
       </c>
     </row>
     <row r="102" spans="1:15">
       <c r="A102" s="1">
-        <v>3004022</v>
+        <v>2012002</v>
       </c>
       <c r="B102" s="4">
-        <v>300402</v>
+        <v>201200</v>
       </c>
       <c r="C102" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>104</v>
       </c>
       <c r="E102" s="13">
-        <v>300402001</v>
+        <v>201200001</v>
       </c>
       <c r="F102" s="22" t="s">
         <v>105</v>
@@ -6442,9 +6441,8 @@
       <c r="H102" s="1">
         <v>2</v>
       </c>
-      <c r="I102" s="23">
-        <f t="shared" si="1"/>
-        <v>52000</v>
+      <c r="I102" s="2">
+        <v>10000</v>
       </c>
       <c r="J102" s="1">
         <v>-1</v>
@@ -6453,33 +6451,33 @@
         <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M102" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N102" s="23">
-        <v>1000</v>
+        <v>85</v>
+      </c>
+      <c r="N102">
+        <v>10000</v>
       </c>
       <c r="O102" s="15">
-        <v>1970000</v>
+        <v>1990000</v>
       </c>
     </row>
     <row r="103" spans="1:15">
       <c r="A103" s="1">
-        <v>3004023</v>
+        <v>2012003</v>
       </c>
       <c r="B103" s="4">
-        <v>300402</v>
+        <v>201200</v>
       </c>
       <c r="C103" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>104</v>
       </c>
       <c r="E103" s="13">
-        <v>300402001</v>
+        <v>201200001</v>
       </c>
       <c r="F103" s="22" t="s">
         <v>105</v>
@@ -6490,9 +6488,8 @@
       <c r="H103" s="1">
         <v>3</v>
       </c>
-      <c r="I103" s="23">
-        <f t="shared" si="1"/>
-        <v>520000</v>
+      <c r="I103" s="2">
+        <v>100000</v>
       </c>
       <c r="J103" s="1">
         <v>-1</v>
@@ -6501,180 +6498,180 @@
         <v>0</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M103" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N103" s="23">
-        <v>10000</v>
+        <v>85</v>
+      </c>
+      <c r="N103">
+        <v>100000</v>
       </c>
       <c r="O103" s="15">
-        <v>1970000</v>
+        <v>1990000</v>
       </c>
     </row>
     <row r="104" spans="1:15">
       <c r="A104" s="1">
-        <v>2012001</v>
-      </c>
-      <c r="B104" s="4">
-        <v>201200</v>
-      </c>
-      <c r="C104" s="4">
+        <v>20010010</v>
+      </c>
+      <c r="B104" s="16">
+        <v>200100</v>
+      </c>
+      <c r="C104" s="16">
         <v>2</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="D104" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E104" s="16">
+        <v>200100038</v>
+      </c>
+      <c r="F104" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G104" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="E104" s="13">
-        <v>201200001</v>
-      </c>
-      <c r="F104" s="22" t="s">
+      <c r="H104" s="17">
+        <v>10</v>
+      </c>
+      <c r="I104" s="24">
+        <v>0</v>
+      </c>
+      <c r="J104" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K104" s="17">
+        <v>0</v>
+      </c>
+      <c r="L104" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="G104" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H104" s="1">
-        <v>1</v>
-      </c>
-      <c r="I104" s="2">
-        <v>0</v>
-      </c>
-      <c r="J104" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K104" s="1">
-        <v>0</v>
-      </c>
-      <c r="L104" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M104" s="28" t="s">
-        <v>85</v>
+      <c r="M104" s="17">
+        <v>0</v>
       </c>
       <c r="N104">
         <v>1000</v>
       </c>
-      <c r="O104" s="15">
-        <v>1990000</v>
+      <c r="O104" s="26">
+        <v>1980000</v>
       </c>
     </row>
     <row r="105" spans="1:15">
       <c r="A105" s="1">
-        <v>2012002</v>
-      </c>
-      <c r="B105" s="4">
-        <v>201200</v>
-      </c>
-      <c r="C105" s="4">
+        <v>20010011</v>
+      </c>
+      <c r="B105" s="16">
+        <v>200100</v>
+      </c>
+      <c r="C105" s="16">
         <v>2</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E105" s="13">
-        <v>201200001</v>
-      </c>
-      <c r="F105" s="22" t="s">
+      <c r="D105" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E105" s="16">
+        <v>200100038</v>
+      </c>
+      <c r="F105" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G105" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="H105" s="17">
+        <v>11</v>
+      </c>
+      <c r="I105" s="24">
+        <v>0</v>
+      </c>
+      <c r="J105" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K105" s="17">
+        <v>0</v>
+      </c>
+      <c r="L105" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="G105" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H105" s="1">
-        <v>2</v>
-      </c>
-      <c r="I105" s="2">
-        <v>10000</v>
-      </c>
-      <c r="J105" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K105" s="1">
-        <v>0</v>
-      </c>
-      <c r="L105" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M105" s="28" t="s">
-        <v>85</v>
+      <c r="M105" s="17">
+        <v>0</v>
       </c>
       <c r="N105">
         <v>10000</v>
       </c>
-      <c r="O105" s="15">
-        <v>1990000</v>
+      <c r="O105" s="26">
+        <v>1980000</v>
       </c>
     </row>
     <row r="106" spans="1:15">
       <c r="A106" s="1">
-        <v>2012003</v>
-      </c>
-      <c r="B106" s="4">
-        <v>201200</v>
-      </c>
-      <c r="C106" s="4">
+        <v>20010012</v>
+      </c>
+      <c r="B106" s="16">
+        <v>200100</v>
+      </c>
+      <c r="C106" s="16">
         <v>2</v>
       </c>
-      <c r="D106" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E106" s="13">
-        <v>201200001</v>
-      </c>
-      <c r="F106" s="22" t="s">
+      <c r="D106" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E106" s="16">
+        <v>200100038</v>
+      </c>
+      <c r="F106" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G106" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H106" s="17">
+        <v>12</v>
+      </c>
+      <c r="I106" s="24">
+        <v>0</v>
+      </c>
+      <c r="J106" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K106" s="17">
+        <v>0</v>
+      </c>
+      <c r="L106" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="G106" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H106" s="1">
-        <v>3</v>
-      </c>
-      <c r="I106" s="2">
-        <v>100000</v>
-      </c>
-      <c r="J106" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K106" s="1">
-        <v>0</v>
-      </c>
-      <c r="L106" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M106" s="28" t="s">
-        <v>85</v>
+      <c r="M106" s="17">
+        <v>0</v>
       </c>
       <c r="N106">
         <v>100000</v>
       </c>
-      <c r="O106" s="15">
-        <v>1990000</v>
+      <c r="O106" s="26">
+        <v>1980000</v>
       </c>
     </row>
     <row r="107" spans="1:15">
       <c r="A107" s="1">
-        <v>20010010</v>
+        <v>20010110</v>
       </c>
       <c r="B107" s="16">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C107" s="16">
         <v>2</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E107" s="16">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F107" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G107" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H107" s="17">
         <v>10</v>
@@ -6689,7 +6686,7 @@
         <v>0</v>
       </c>
       <c r="L107" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M107" s="17">
         <v>0</v>
@@ -6703,25 +6700,25 @@
     </row>
     <row r="108" spans="1:15">
       <c r="A108" s="1">
-        <v>20010011</v>
+        <v>20010111</v>
       </c>
       <c r="B108" s="16">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C108" s="16">
         <v>2</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E108" s="16">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F108" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G108" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H108" s="17">
         <v>11</v>
@@ -6736,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="L108" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M108" s="17">
         <v>0</v>
@@ -6750,25 +6747,25 @@
     </row>
     <row r="109" spans="1:15">
       <c r="A109" s="1">
-        <v>20010012</v>
+        <v>20010112</v>
       </c>
       <c r="B109" s="16">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C109" s="16">
         <v>2</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E109" s="16">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F109" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G109" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H109" s="17">
         <v>12</v>
@@ -6783,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="L109" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M109" s="17">
         <v>0</v>
@@ -6797,25 +6794,25 @@
     </row>
     <row r="110" spans="1:15">
       <c r="A110" s="1">
-        <v>20010110</v>
+        <v>20030010</v>
       </c>
       <c r="B110" s="16">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C110" s="16">
         <v>2</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E110" s="16">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F110" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G110" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H110" s="17">
         <v>10</v>
@@ -6830,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="L110" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M110" s="17">
         <v>0</v>
@@ -6844,25 +6841,25 @@
     </row>
     <row r="111" spans="1:15">
       <c r="A111" s="1">
-        <v>20010111</v>
+        <v>20030011</v>
       </c>
       <c r="B111" s="16">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C111" s="16">
         <v>2</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E111" s="16">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F111" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G111" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H111" s="17">
         <v>11</v>
@@ -6877,7 +6874,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M111" s="17">
         <v>0</v>
@@ -6891,25 +6888,25 @@
     </row>
     <row r="112" spans="1:15">
       <c r="A112" s="1">
-        <v>20010112</v>
+        <v>20030012</v>
       </c>
       <c r="B112" s="16">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C112" s="16">
         <v>2</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E112" s="16">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F112" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H112" s="17">
         <v>12</v>
@@ -6924,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M112" s="17">
         <v>0</v>
@@ -6938,25 +6935,25 @@
     </row>
     <row r="113" spans="1:15">
       <c r="A113" s="1">
-        <v>20030010</v>
+        <v>20040010</v>
       </c>
       <c r="B113" s="16">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C113" s="16">
         <v>2</v>
       </c>
-      <c r="D113" s="16" t="s">
-        <v>79</v>
+      <c r="D113" s="24" t="s">
+        <v>81</v>
       </c>
       <c r="E113" s="16">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F113" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G113" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H113" s="17">
         <v>10</v>
@@ -6971,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="L113" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M113" s="17">
         <v>0</v>
@@ -6985,25 +6982,25 @@
     </row>
     <row r="114" spans="1:15">
       <c r="A114" s="1">
-        <v>20030011</v>
+        <v>20040011</v>
       </c>
       <c r="B114" s="16">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C114" s="16">
         <v>2</v>
       </c>
-      <c r="D114" s="16" t="s">
-        <v>79</v>
+      <c r="D114" s="24" t="s">
+        <v>81</v>
       </c>
       <c r="E114" s="16">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H114" s="17">
         <v>11</v>
@@ -7018,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="L114" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M114" s="17">
         <v>0</v>
@@ -7032,25 +7029,25 @@
     </row>
     <row r="115" spans="1:15">
       <c r="A115" s="1">
-        <v>20030012</v>
+        <v>20040012</v>
       </c>
       <c r="B115" s="16">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C115" s="16">
         <v>2</v>
       </c>
-      <c r="D115" s="16" t="s">
-        <v>79</v>
+      <c r="D115" s="24" t="s">
+        <v>81</v>
       </c>
       <c r="E115" s="16">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F115" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G115" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H115" s="17">
         <v>12</v>
@@ -7065,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M115" s="17">
         <v>0</v>
@@ -7079,25 +7076,25 @@
     </row>
     <row r="116" spans="1:15">
       <c r="A116" s="1">
-        <v>20040010</v>
+        <v>20050010</v>
       </c>
       <c r="B116" s="16">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C116" s="16">
         <v>2</v>
       </c>
-      <c r="D116" s="24" t="s">
-        <v>81</v>
+      <c r="D116" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="E116" s="16">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F116" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G116" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H116" s="17">
         <v>10</v>
@@ -7112,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M116" s="17">
         <v>0</v>
@@ -7126,25 +7123,25 @@
     </row>
     <row r="117" spans="1:15">
       <c r="A117" s="1">
-        <v>20040011</v>
+        <v>20050011</v>
       </c>
       <c r="B117" s="16">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C117" s="16">
         <v>2</v>
       </c>
-      <c r="D117" s="24" t="s">
-        <v>81</v>
+      <c r="D117" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="E117" s="16">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F117" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G117" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H117" s="17">
         <v>11</v>
@@ -7159,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="L117" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M117" s="17">
         <v>0</v>
@@ -7173,25 +7170,25 @@
     </row>
     <row r="118" spans="1:15">
       <c r="A118" s="1">
-        <v>20040012</v>
+        <v>20050012</v>
       </c>
       <c r="B118" s="16">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C118" s="16">
         <v>2</v>
       </c>
-      <c r="D118" s="24" t="s">
-        <v>81</v>
+      <c r="D118" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="E118" s="16">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F118" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G118" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H118" s="17">
         <v>12</v>
@@ -7206,7 +7203,7 @@
         <v>0</v>
       </c>
       <c r="L118" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M118" s="17">
         <v>0</v>
@@ -7220,25 +7217,25 @@
     </row>
     <row r="119" spans="1:15">
       <c r="A119" s="1">
-        <v>20050010</v>
+        <v>20060010</v>
       </c>
       <c r="B119" s="16">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C119" s="16">
         <v>2</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E119" s="16">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F119" s="16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H119" s="17">
         <v>10</v>
@@ -7253,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="L119" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M119" s="17">
         <v>0</v>
@@ -7267,25 +7264,25 @@
     </row>
     <row r="120" spans="1:15">
       <c r="A120" s="1">
-        <v>20050011</v>
+        <v>20060011</v>
       </c>
       <c r="B120" s="16">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C120" s="16">
         <v>2</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E120" s="16">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F120" s="16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G120" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H120" s="17">
         <v>11</v>
@@ -7300,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L120" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M120" s="17">
         <v>0</v>
@@ -7314,25 +7311,25 @@
     </row>
     <row r="121" spans="1:15">
       <c r="A121" s="1">
-        <v>20050012</v>
+        <v>20060012</v>
       </c>
       <c r="B121" s="16">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C121" s="16">
         <v>2</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E121" s="16">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F121" s="16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G121" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H121" s="17">
         <v>12</v>
@@ -7347,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M121" s="17">
         <v>0</v>
@@ -7361,25 +7358,25 @@
     </row>
     <row r="122" spans="1:15">
       <c r="A122" s="1">
-        <v>20060010</v>
+        <v>20070010</v>
       </c>
       <c r="B122" s="16">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C122" s="16">
         <v>2</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E122" s="16">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F122" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G122" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H122" s="17">
         <v>10</v>
@@ -7394,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="L122" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M122" s="17">
         <v>0</v>
@@ -7408,25 +7405,25 @@
     </row>
     <row r="123" spans="1:15">
       <c r="A123" s="1">
-        <v>20060011</v>
+        <v>20070011</v>
       </c>
       <c r="B123" s="16">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C123" s="16">
         <v>2</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E123" s="16">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F123" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G123" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H123" s="17">
         <v>11</v>
@@ -7441,7 +7438,7 @@
         <v>0</v>
       </c>
       <c r="L123" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M123" s="17">
         <v>0</v>
@@ -7455,25 +7452,25 @@
     </row>
     <row r="124" spans="1:15">
       <c r="A124" s="1">
-        <v>20060012</v>
+        <v>20070012</v>
       </c>
       <c r="B124" s="16">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C124" s="16">
         <v>2</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E124" s="16">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F124" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G124" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H124" s="17">
         <v>12</v>
@@ -7488,7 +7485,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M124" s="17">
         <v>0</v>
@@ -7502,25 +7499,25 @@
     </row>
     <row r="125" spans="1:15">
       <c r="A125" s="1">
-        <v>20070010</v>
+        <v>20080010</v>
       </c>
       <c r="B125" s="16">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C125" s="16">
         <v>2</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E125" s="16">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F125" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H125" s="17">
         <v>10</v>
@@ -7535,7 +7532,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M125" s="17">
         <v>0</v>
@@ -7549,25 +7546,25 @@
     </row>
     <row r="126" spans="1:15">
       <c r="A126" s="1">
-        <v>20070011</v>
+        <v>20080011</v>
       </c>
       <c r="B126" s="16">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C126" s="16">
         <v>2</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E126" s="16">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F126" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G126" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H126" s="17">
         <v>11</v>
@@ -7582,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M126" s="17">
         <v>0</v>
@@ -7596,25 +7593,25 @@
     </row>
     <row r="127" spans="1:15">
       <c r="A127" s="1">
-        <v>20070012</v>
+        <v>20080012</v>
       </c>
       <c r="B127" s="16">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C127" s="16">
         <v>2</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E127" s="16">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F127" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G127" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H127" s="17">
         <v>12</v>
@@ -7629,7 +7626,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M127" s="17">
         <v>0</v>
@@ -7643,25 +7640,25 @@
     </row>
     <row r="128" spans="1:15">
       <c r="A128" s="1">
-        <v>20080010</v>
+        <v>20090010</v>
       </c>
       <c r="B128" s="16">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C128" s="16">
         <v>2</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E128" s="16">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F128" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H128" s="17">
         <v>10</v>
@@ -7676,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M128" s="17">
         <v>0</v>
@@ -7690,25 +7687,25 @@
     </row>
     <row r="129" spans="1:15">
       <c r="A129" s="1">
-        <v>20080011</v>
+        <v>20090011</v>
       </c>
       <c r="B129" s="16">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C129" s="16">
         <v>2</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E129" s="16">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F129" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G129" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H129" s="17">
         <v>11</v>
@@ -7723,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M129" s="17">
         <v>0</v>
@@ -7737,25 +7734,25 @@
     </row>
     <row r="130" spans="1:15">
       <c r="A130" s="1">
-        <v>20080012</v>
+        <v>20090012</v>
       </c>
       <c r="B130" s="16">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C130" s="16">
         <v>2</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E130" s="16">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F130" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G130" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H130" s="17">
         <v>12</v>
@@ -7770,7 +7767,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M130" s="17">
         <v>0</v>
@@ -7784,25 +7781,25 @@
     </row>
     <row r="131" spans="1:15">
       <c r="A131" s="1">
-        <v>20090010</v>
+        <v>30020010</v>
       </c>
       <c r="B131" s="16">
-        <v>200900</v>
+        <v>300200</v>
       </c>
       <c r="C131" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E131" s="16">
-        <v>200900001</v>
+        <v>300200006</v>
       </c>
       <c r="F131" s="16" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H131" s="17">
         <v>10</v>
@@ -7816,13 +7813,13 @@
       <c r="K131" s="17">
         <v>0</v>
       </c>
-      <c r="L131" s="25" t="s">
-        <v>109</v>
+      <c r="L131" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="M131" s="17">
         <v>0</v>
       </c>
-      <c r="N131">
+      <c r="N131" s="21">
         <v>1000</v>
       </c>
       <c r="O131" s="26">
@@ -7831,25 +7828,25 @@
     </row>
     <row r="132" spans="1:15">
       <c r="A132" s="1">
-        <v>20090011</v>
+        <v>30020011</v>
       </c>
       <c r="B132" s="16">
-        <v>200900</v>
+        <v>300200</v>
       </c>
       <c r="C132" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E132" s="16">
-        <v>200900001</v>
+        <v>300200006</v>
       </c>
       <c r="F132" s="16" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G132" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H132" s="17">
         <v>11</v>
@@ -7863,13 +7860,13 @@
       <c r="K132" s="17">
         <v>0</v>
       </c>
-      <c r="L132" s="25" t="s">
-        <v>109</v>
+      <c r="L132" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="M132" s="17">
         <v>0</v>
       </c>
-      <c r="N132">
+      <c r="N132" s="21">
         <v>10000</v>
       </c>
       <c r="O132" s="26">
@@ -7878,25 +7875,25 @@
     </row>
     <row r="133" spans="1:15">
       <c r="A133" s="1">
-        <v>20090012</v>
+        <v>30020012</v>
       </c>
       <c r="B133" s="16">
-        <v>200900</v>
+        <v>300200</v>
       </c>
       <c r="C133" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E133" s="16">
-        <v>200900001</v>
+        <v>300200006</v>
       </c>
       <c r="F133" s="16" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G133" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H133" s="17">
         <v>12</v>
@@ -7910,13 +7907,13 @@
       <c r="K133" s="17">
         <v>0</v>
       </c>
-      <c r="L133" s="25" t="s">
-        <v>109</v>
+      <c r="L133" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="M133" s="17">
         <v>0</v>
       </c>
-      <c r="N133">
+      <c r="N133" s="21">
         <v>100000</v>
       </c>
       <c r="O133" s="26">
@@ -7925,25 +7922,26 @@
     </row>
     <row r="134" spans="1:15">
       <c r="A134" s="1">
-        <v>30020010</v>
+        <f>B134*100+H134</f>
+        <v>10010010</v>
       </c>
       <c r="B134" s="16">
-        <v>300200</v>
+        <v>100100</v>
       </c>
       <c r="C134" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="E134" s="16">
-        <v>300200006</v>
+        <v>100100026</v>
       </c>
       <c r="F134" s="16" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G134" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H134" s="17">
         <v>10</v>
@@ -7957,13 +7955,13 @@
       <c r="K134" s="17">
         <v>0</v>
       </c>
-      <c r="L134" s="3" t="s">
-        <v>112</v>
+      <c r="L134" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="M134" s="17">
         <v>0</v>
       </c>
-      <c r="N134" s="21">
+      <c r="N134">
         <v>1000</v>
       </c>
       <c r="O134" s="26">
@@ -7972,25 +7970,27 @@
     </row>
     <row r="135" spans="1:15">
       <c r="A135" s="1">
-        <v>30020011</v>
+        <f>B135*100+H135</f>
+        <v>10010011</v>
       </c>
       <c r="B135" s="16">
-        <v>300200</v>
+        <v>100100</v>
       </c>
       <c r="C135" s="16">
-        <v>3</v>
-      </c>
-      <c r="D135" s="16" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="D135" s="16" t="str">
+        <f t="shared" ref="D135:D139" si="1">D134</f>
+        <v>金礦大亨</v>
       </c>
       <c r="E135" s="16">
-        <v>300200006</v>
+        <v>100100026</v>
       </c>
       <c r="F135" s="16" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H135" s="17">
         <v>11</v>
@@ -8004,13 +8004,13 @@
       <c r="K135" s="17">
         <v>0</v>
       </c>
-      <c r="L135" s="3" t="s">
-        <v>112</v>
+      <c r="L135" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="M135" s="17">
         <v>0</v>
       </c>
-      <c r="N135" s="21">
+      <c r="N135">
         <v>10000</v>
       </c>
       <c r="O135" s="26">
@@ -8019,25 +8019,27 @@
     </row>
     <row r="136" spans="1:15">
       <c r="A136" s="1">
-        <v>30020012</v>
+        <f>B136*100+H136</f>
+        <v>10010012</v>
       </c>
       <c r="B136" s="16">
-        <v>300200</v>
+        <v>100100</v>
       </c>
       <c r="C136" s="16">
-        <v>3</v>
-      </c>
-      <c r="D136" s="16" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="D136" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>金礦大亨</v>
       </c>
       <c r="E136" s="16">
-        <v>300200006</v>
+        <v>100100026</v>
       </c>
       <c r="F136" s="16" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G136" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H136" s="17">
         <v>12</v>
@@ -8051,13 +8053,13 @@
       <c r="K136" s="17">
         <v>0</v>
       </c>
-      <c r="L136" s="3" t="s">
-        <v>112</v>
+      <c r="L136" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="M136" s="17">
         <v>0</v>
       </c>
-      <c r="N136" s="21">
+      <c r="N136">
         <v>100000</v>
       </c>
       <c r="O136" s="26">
@@ -8066,26 +8068,26 @@
     </row>
     <row r="137" spans="1:15">
       <c r="A137" s="1">
-        <f>B137*100+H137</f>
-        <v>10010010</v>
+        <f t="shared" ref="A137:A178" si="2">B137*100+H137</f>
+        <v>10030010</v>
       </c>
       <c r="B137" s="16">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C137" s="16">
         <v>1</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E137" s="16">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="F137" s="16" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G137" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H137" s="17">
         <v>10</v>
@@ -8100,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="L137" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M137" s="17">
         <v>0</v>
@@ -8114,27 +8116,28 @@
     </row>
     <row r="138" spans="1:15">
       <c r="A138" s="1">
-        <f>B138*100+H138</f>
-        <v>10010011</v>
+        <f t="shared" si="2"/>
+        <v>10030011</v>
       </c>
       <c r="B138" s="16">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C138" s="16">
         <v>1</v>
       </c>
       <c r="D138" s="16" t="str">
-        <f t="shared" ref="D138:D142" si="2">D137</f>
-        <v>金礦大亨</v>
+        <f t="shared" si="1"/>
+        <v>超级明星</v>
       </c>
       <c r="E138" s="16">
-        <v>100100026</v>
-      </c>
-      <c r="F138" s="16" t="s">
-        <v>31</v>
+        <v>100300001</v>
+      </c>
+      <c r="F138" s="16" t="str">
+        <f t="shared" ref="F138:F142" si="3">F137</f>
+        <v>SuperStar</v>
       </c>
       <c r="G138" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H138" s="17">
         <v>11</v>
@@ -8149,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M138" s="17">
         <v>0</v>
@@ -8163,27 +8166,28 @@
     </row>
     <row r="139" spans="1:15">
       <c r="A139" s="1">
-        <f>B139*100+H139</f>
-        <v>10010012</v>
+        <f t="shared" si="2"/>
+        <v>10030012</v>
       </c>
       <c r="B139" s="16">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C139" s="16">
         <v>1</v>
       </c>
       <c r="D139" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v>金礦大亨</v>
+        <f t="shared" si="1"/>
+        <v>超级明星</v>
       </c>
       <c r="E139" s="16">
-        <v>100100026</v>
-      </c>
-      <c r="F139" s="16" t="s">
-        <v>31</v>
+        <v>100300001</v>
+      </c>
+      <c r="F139" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>SuperStar</v>
       </c>
       <c r="G139" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H139" s="17">
         <v>12</v>
@@ -8198,7 +8202,7 @@
         <v>0</v>
       </c>
       <c r="L139" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M139" s="17">
         <v>0</v>
@@ -8212,26 +8216,26 @@
     </row>
     <row r="140" spans="1:15">
       <c r="A140" s="1">
-        <f t="shared" ref="A140:A181" si="3">B140*100+H140</f>
-        <v>10030010</v>
+        <f t="shared" si="2"/>
+        <v>10070010</v>
       </c>
       <c r="B140" s="16">
-        <v>100300</v>
+        <v>100700</v>
       </c>
       <c r="C140" s="16">
         <v>1</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E140" s="16">
-        <v>100300001</v>
+        <v>100700001</v>
       </c>
       <c r="F140" s="16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G140" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H140" s="17">
         <v>10</v>
@@ -8246,7 +8250,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M140" s="17">
         <v>0</v>
@@ -8260,28 +8264,28 @@
     </row>
     <row r="141" spans="1:15">
       <c r="A141" s="1">
+        <f t="shared" si="2"/>
+        <v>10070011</v>
+      </c>
+      <c r="B141" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C141" s="16">
+        <v>1</v>
+      </c>
+      <c r="D141" s="16" t="str">
+        <f t="shared" ref="D141:D145" si="4">D140</f>
+        <v>麻将胡了</v>
+      </c>
+      <c r="E141" s="16">
+        <v>100700001</v>
+      </c>
+      <c r="F141" s="16" t="str">
         <f t="shared" si="3"/>
-        <v>10030011</v>
-      </c>
-      <c r="B141" s="16">
-        <v>100300</v>
-      </c>
-      <c r="C141" s="16">
-        <v>1</v>
-      </c>
-      <c r="D141" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v>超级明星</v>
-      </c>
-      <c r="E141" s="16">
-        <v>100300001</v>
-      </c>
-      <c r="F141" s="16" t="str">
-        <f t="shared" ref="F141:F145" si="4">F140</f>
-        <v>SuperStar</v>
+        <v>MahjongWays</v>
       </c>
       <c r="G141" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H141" s="17">
         <v>11</v>
@@ -8296,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M141" s="17">
         <v>0</v>
@@ -8310,28 +8314,28 @@
     </row>
     <row r="142" spans="1:15">
       <c r="A142" s="1">
+        <f t="shared" si="2"/>
+        <v>10070012</v>
+      </c>
+      <c r="B142" s="16">
+        <v>100700</v>
+      </c>
+      <c r="C142" s="16">
+        <v>1</v>
+      </c>
+      <c r="D142" s="16" t="str">
+        <f t="shared" si="4"/>
+        <v>麻将胡了</v>
+      </c>
+      <c r="E142" s="16">
+        <v>100700001</v>
+      </c>
+      <c r="F142" s="16" t="str">
         <f t="shared" si="3"/>
-        <v>10030012</v>
-      </c>
-      <c r="B142" s="16">
-        <v>100300</v>
-      </c>
-      <c r="C142" s="16">
-        <v>1</v>
-      </c>
-      <c r="D142" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v>超级明星</v>
-      </c>
-      <c r="E142" s="16">
-        <v>100300001</v>
-      </c>
-      <c r="F142" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>SuperStar</v>
+        <v>MahjongWays</v>
       </c>
       <c r="G142" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H142" s="17">
         <v>12</v>
@@ -8346,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M142" s="17">
         <v>0</v>
@@ -8360,26 +8364,26 @@
     </row>
     <row r="143" spans="1:15">
       <c r="A143" s="1">
-        <f t="shared" si="3"/>
-        <v>10070010</v>
+        <f t="shared" si="2"/>
+        <v>10120010</v>
       </c>
       <c r="B143" s="16">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C143" s="16">
         <v>1</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E143" s="16">
-        <v>100700001</v>
+        <v>101200001</v>
       </c>
       <c r="F143" s="16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G143" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H143" s="17">
         <v>10</v>
@@ -8394,7 +8398,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M143" s="17">
         <v>0</v>
@@ -8408,28 +8412,28 @@
     </row>
     <row r="144" spans="1:15">
       <c r="A144" s="1">
-        <f t="shared" si="3"/>
-        <v>10070011</v>
+        <f t="shared" si="2"/>
+        <v>10120011</v>
       </c>
       <c r="B144" s="16">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C144" s="16">
         <v>1</v>
       </c>
       <c r="D144" s="16" t="str">
-        <f t="shared" ref="D144:D148" si="5">D143</f>
-        <v>麻将胡了</v>
+        <f t="shared" si="4"/>
+        <v>财神</v>
       </c>
       <c r="E144" s="16">
-        <v>100700001</v>
+        <v>101200001</v>
       </c>
       <c r="F144" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>MahjongWays</v>
+        <f t="shared" ref="F144:F148" si="5">F143</f>
+        <v>Godofwealth</v>
       </c>
       <c r="G144" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H144" s="17">
         <v>11</v>
@@ -8444,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M144" s="17">
         <v>0</v>
@@ -8458,28 +8462,28 @@
     </row>
     <row r="145" spans="1:15">
       <c r="A145" s="1">
-        <f t="shared" si="3"/>
-        <v>10070012</v>
+        <f t="shared" si="2"/>
+        <v>10120012</v>
       </c>
       <c r="B145" s="16">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C145" s="16">
         <v>1</v>
       </c>
       <c r="D145" s="16" t="str">
+        <f t="shared" si="4"/>
+        <v>财神</v>
+      </c>
+      <c r="E145" s="16">
+        <v>101200001</v>
+      </c>
+      <c r="F145" s="16" t="str">
         <f t="shared" si="5"/>
-        <v>麻将胡了</v>
-      </c>
-      <c r="E145" s="16">
-        <v>100700001</v>
-      </c>
-      <c r="F145" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v>MahjongWays</v>
+        <v>Godofwealth</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H145" s="17">
         <v>12</v>
@@ -8494,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M145" s="17">
         <v>0</v>
@@ -8508,26 +8512,26 @@
     </row>
     <row r="146" spans="1:15">
       <c r="A146" s="1">
-        <f t="shared" si="3"/>
-        <v>10120010</v>
+        <f t="shared" si="2"/>
+        <v>10140010</v>
       </c>
       <c r="B146" s="16">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C146" s="16">
         <v>1</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E146" s="16">
-        <v>101200001</v>
+        <v>101400001</v>
       </c>
       <c r="F146" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G146" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H146" s="17">
         <v>10</v>
@@ -8542,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M146" s="17">
         <v>0</v>
@@ -8556,28 +8560,28 @@
     </row>
     <row r="147" spans="1:15">
       <c r="A147" s="1">
-        <f t="shared" si="3"/>
-        <v>10120011</v>
+        <f t="shared" si="2"/>
+        <v>10140011</v>
       </c>
       <c r="B147" s="16">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C147" s="16">
         <v>1</v>
       </c>
       <c r="D147" s="16" t="str">
+        <f t="shared" ref="D147:D151" si="6">D146</f>
+        <v>埃及艳后</v>
+      </c>
+      <c r="E147" s="16">
+        <v>101400001</v>
+      </c>
+      <c r="F147" s="16" t="str">
         <f t="shared" si="5"/>
-        <v>财神</v>
-      </c>
-      <c r="E147" s="16">
-        <v>101200001</v>
-      </c>
-      <c r="F147" s="16" t="str">
-        <f t="shared" ref="F147:F151" si="6">F146</f>
-        <v>Godofwealth</v>
+        <v>Cleopatra</v>
       </c>
       <c r="G147" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H147" s="17">
         <v>11</v>
@@ -8592,7 +8596,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M147" s="17">
         <v>0</v>
@@ -8606,28 +8610,28 @@
     </row>
     <row r="148" spans="1:15">
       <c r="A148" s="1">
-        <f t="shared" si="3"/>
-        <v>10120012</v>
+        <f t="shared" si="2"/>
+        <v>10140012</v>
       </c>
       <c r="B148" s="16">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C148" s="16">
         <v>1</v>
       </c>
       <c r="D148" s="16" t="str">
+        <f t="shared" si="6"/>
+        <v>埃及艳后</v>
+      </c>
+      <c r="E148" s="16">
+        <v>101400001</v>
+      </c>
+      <c r="F148" s="16" t="str">
         <f t="shared" si="5"/>
-        <v>财神</v>
-      </c>
-      <c r="E148" s="16">
-        <v>101200001</v>
-      </c>
-      <c r="F148" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v>Godofwealth</v>
+        <v>Cleopatra</v>
       </c>
       <c r="G148" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H148" s="17">
         <v>12</v>
@@ -8642,7 +8646,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M148" s="17">
         <v>0</v>
@@ -8656,26 +8660,26 @@
     </row>
     <row r="149" spans="1:15">
       <c r="A149" s="1">
-        <f t="shared" si="3"/>
-        <v>10140010</v>
+        <f t="shared" si="2"/>
+        <v>10240010</v>
       </c>
       <c r="B149" s="16">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C149" s="16">
         <v>1</v>
       </c>
       <c r="D149" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E149" s="16">
-        <v>101400001</v>
+        <v>102400026</v>
       </c>
       <c r="F149" s="16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G149" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H149" s="17">
         <v>10</v>
@@ -8690,7 +8694,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M149" s="17">
         <v>0</v>
@@ -8704,28 +8708,27 @@
     </row>
     <row r="150" spans="1:15">
       <c r="A150" s="1">
-        <f t="shared" si="3"/>
-        <v>10140011</v>
+        <f t="shared" si="2"/>
+        <v>10240011</v>
       </c>
       <c r="B150" s="16">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C150" s="16">
         <v>1</v>
       </c>
       <c r="D150" s="16" t="str">
-        <f t="shared" ref="D150:D154" si="7">D149</f>
-        <v>埃及艳后</v>
+        <f t="shared" si="6"/>
+        <v>财富银行</v>
       </c>
       <c r="E150" s="16">
-        <v>101400001</v>
-      </c>
-      <c r="F150" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v>Cleopatra</v>
+        <v>102400026</v>
+      </c>
+      <c r="F150" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H150" s="17">
         <v>11</v>
@@ -8740,7 +8743,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M150" s="17">
         <v>0</v>
@@ -8754,28 +8757,27 @@
     </row>
     <row r="151" spans="1:15">
       <c r="A151" s="1">
-        <f t="shared" si="3"/>
-        <v>10140012</v>
+        <f t="shared" si="2"/>
+        <v>10240012</v>
       </c>
       <c r="B151" s="16">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C151" s="16">
         <v>1</v>
       </c>
       <c r="D151" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v>埃及艳后</v>
+        <f t="shared" si="6"/>
+        <v>财富银行</v>
       </c>
       <c r="E151" s="16">
-        <v>101400001</v>
-      </c>
-      <c r="F151" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v>Cleopatra</v>
+        <v>102400026</v>
+      </c>
+      <c r="F151" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="G151" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H151" s="17">
         <v>12</v>
@@ -8790,7 +8792,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M151" s="17">
         <v>0</v>
@@ -8804,26 +8806,26 @@
     </row>
     <row r="152" spans="1:15">
       <c r="A152" s="1">
-        <f t="shared" si="3"/>
-        <v>10240010</v>
+        <f t="shared" si="2"/>
+        <v>10220010</v>
       </c>
       <c r="B152" s="16">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C152" s="16">
         <v>1</v>
       </c>
       <c r="D152" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E152" s="16">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F152" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G152" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H152" s="17">
         <v>10</v>
@@ -8838,7 +8840,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M152" s="17">
         <v>0</v>
@@ -8852,27 +8854,26 @@
     </row>
     <row r="153" spans="1:15">
       <c r="A153" s="1">
-        <f t="shared" si="3"/>
-        <v>10240011</v>
+        <f t="shared" si="2"/>
+        <v>10220011</v>
       </c>
       <c r="B153" s="16">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C153" s="16">
         <v>1</v>
       </c>
-      <c r="D153" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v>财富银行</v>
+      <c r="D153" s="16" t="s">
+        <v>47</v>
       </c>
       <c r="E153" s="16">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F153" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G153" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H153" s="17">
         <v>11</v>
@@ -8887,7 +8888,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M153" s="17">
         <v>0</v>
@@ -8901,27 +8902,26 @@
     </row>
     <row r="154" spans="1:15">
       <c r="A154" s="1">
-        <f t="shared" si="3"/>
-        <v>10240012</v>
+        <f t="shared" si="2"/>
+        <v>10220012</v>
       </c>
       <c r="B154" s="16">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C154" s="16">
         <v>1</v>
       </c>
-      <c r="D154" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v>财富银行</v>
+      <c r="D154" s="16" t="s">
+        <v>47</v>
       </c>
       <c r="E154" s="16">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F154" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G154" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H154" s="17">
         <v>12</v>
@@ -8936,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M154" s="17">
         <v>0</v>
@@ -8950,26 +8950,26 @@
     </row>
     <row r="155" spans="1:15">
       <c r="A155" s="1">
-        <f t="shared" si="3"/>
-        <v>10220010</v>
+        <f t="shared" si="2"/>
+        <v>10170010</v>
       </c>
       <c r="B155" s="16">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C155" s="16">
         <v>1</v>
       </c>
       <c r="D155" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E155" s="16">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F155" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G155" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H155" s="17">
         <v>10</v>
@@ -8984,7 +8984,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M155" s="17">
         <v>0</v>
@@ -8998,26 +8998,26 @@
     </row>
     <row r="156" spans="1:15">
       <c r="A156" s="1">
-        <f t="shared" si="3"/>
-        <v>10220011</v>
+        <f t="shared" si="2"/>
+        <v>10170011</v>
       </c>
       <c r="B156" s="16">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C156" s="16">
         <v>1</v>
       </c>
       <c r="D156" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E156" s="16">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F156" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G156" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H156" s="17">
         <v>11</v>
@@ -9032,7 +9032,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M156" s="17">
         <v>0</v>
@@ -9046,26 +9046,26 @@
     </row>
     <row r="157" spans="1:15">
       <c r="A157" s="1">
-        <f t="shared" si="3"/>
-        <v>10220012</v>
+        <f t="shared" si="2"/>
+        <v>10170012</v>
       </c>
       <c r="B157" s="16">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C157" s="16">
         <v>1</v>
       </c>
       <c r="D157" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E157" s="16">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F157" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G157" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H157" s="17">
         <v>12</v>
@@ -9080,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M157" s="17">
         <v>0</v>
@@ -9094,26 +9094,26 @@
     </row>
     <row r="158" spans="1:15">
       <c r="A158" s="1">
-        <f t="shared" si="3"/>
-        <v>10170010</v>
+        <f t="shared" si="2"/>
+        <v>10210010</v>
       </c>
       <c r="B158" s="16">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C158" s="16">
         <v>1</v>
       </c>
       <c r="D158" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E158" s="16">
-        <v>101700001</v>
+        <v>102100001</v>
       </c>
       <c r="F158" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G158" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H158" s="17">
         <v>10</v>
@@ -9128,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M158" s="17">
         <v>0</v>
@@ -9142,26 +9142,26 @@
     </row>
     <row r="159" spans="1:15">
       <c r="A159" s="1">
-        <f t="shared" si="3"/>
-        <v>10170011</v>
+        <f t="shared" si="2"/>
+        <v>10210011</v>
       </c>
       <c r="B159" s="16">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C159" s="16">
         <v>1</v>
       </c>
       <c r="D159" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E159" s="16">
-        <v>101700001</v>
+        <v>102100001</v>
       </c>
       <c r="F159" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G159" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H159" s="17">
         <v>11</v>
@@ -9176,7 +9176,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M159" s="17">
         <v>0</v>
@@ -9190,26 +9190,26 @@
     </row>
     <row r="160" spans="1:15">
       <c r="A160" s="1">
-        <f t="shared" si="3"/>
-        <v>10170012</v>
+        <f t="shared" si="2"/>
+        <v>10210012</v>
       </c>
       <c r="B160" s="16">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C160" s="16">
         <v>1</v>
       </c>
       <c r="D160" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E160" s="16">
-        <v>101700001</v>
+        <v>102100001</v>
       </c>
       <c r="F160" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G160" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H160" s="17">
         <v>12</v>
@@ -9224,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M160" s="17">
         <v>0</v>
@@ -9238,26 +9238,26 @@
     </row>
     <row r="161" spans="1:15">
       <c r="A161" s="1">
-        <f t="shared" si="3"/>
-        <v>10210010</v>
+        <f t="shared" si="2"/>
+        <v>10180010</v>
       </c>
       <c r="B161" s="16">
-        <v>102100</v>
+        <v>101800</v>
       </c>
       <c r="C161" s="16">
         <v>1</v>
       </c>
       <c r="D161" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E161" s="16">
-        <v>102100001</v>
+        <v>101800001</v>
       </c>
       <c r="F161" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G161" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H161" s="17">
         <v>10</v>
@@ -9272,7 +9272,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M161" s="17">
         <v>0</v>
@@ -9286,26 +9286,26 @@
     </row>
     <row r="162" spans="1:15">
       <c r="A162" s="1">
-        <f t="shared" si="3"/>
-        <v>10210011</v>
+        <f t="shared" si="2"/>
+        <v>10180011</v>
       </c>
       <c r="B162" s="16">
-        <v>102100</v>
+        <v>101800</v>
       </c>
       <c r="C162" s="16">
         <v>1</v>
       </c>
       <c r="D162" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E162" s="16">
-        <v>102100001</v>
+        <v>101800001</v>
       </c>
       <c r="F162" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G162" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H162" s="17">
         <v>11</v>
@@ -9320,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M162" s="17">
         <v>0</v>
@@ -9334,26 +9334,26 @@
     </row>
     <row r="163" spans="1:15">
       <c r="A163" s="1">
-        <f t="shared" si="3"/>
-        <v>10210012</v>
+        <f t="shared" si="2"/>
+        <v>10180012</v>
       </c>
       <c r="B163" s="16">
-        <v>102100</v>
+        <v>101800</v>
       </c>
       <c r="C163" s="16">
         <v>1</v>
       </c>
       <c r="D163" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E163" s="16">
-        <v>102100001</v>
+        <v>101800001</v>
       </c>
       <c r="F163" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G163" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H163" s="17">
         <v>12</v>
@@ -9368,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M163" s="17">
         <v>0</v>
@@ -9382,26 +9382,26 @@
     </row>
     <row r="164" spans="1:15">
       <c r="A164" s="1">
-        <f t="shared" si="3"/>
-        <v>10180010</v>
+        <f t="shared" si="2"/>
+        <v>10250010</v>
       </c>
       <c r="B164" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C164" s="16">
         <v>1</v>
       </c>
       <c r="D164" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E164" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F164" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G164" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H164" s="17">
         <v>10</v>
@@ -9416,7 +9416,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M164" s="17">
         <v>0</v>
@@ -9430,26 +9430,26 @@
     </row>
     <row r="165" spans="1:15">
       <c r="A165" s="1">
-        <f t="shared" si="3"/>
-        <v>10180011</v>
+        <f t="shared" si="2"/>
+        <v>10250011</v>
       </c>
       <c r="B165" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C165" s="16">
         <v>1</v>
       </c>
       <c r="D165" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E165" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F165" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G165" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H165" s="17">
         <v>11</v>
@@ -9464,7 +9464,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M165" s="17">
         <v>0</v>
@@ -9478,26 +9478,26 @@
     </row>
     <row r="166" spans="1:15">
       <c r="A166" s="1">
-        <f t="shared" si="3"/>
-        <v>10180012</v>
+        <f t="shared" si="2"/>
+        <v>10250012</v>
       </c>
       <c r="B166" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C166" s="16">
         <v>1</v>
       </c>
       <c r="D166" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E166" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F166" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G166" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H166" s="17">
         <v>12</v>
@@ -9512,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M166" s="17">
         <v>0</v>
@@ -9526,26 +9526,26 @@
     </row>
     <row r="167" spans="1:15">
       <c r="A167" s="1">
-        <f t="shared" si="3"/>
-        <v>10250010</v>
+        <f t="shared" si="2"/>
+        <v>10230010</v>
       </c>
       <c r="B167" s="16">
-        <v>102500</v>
+        <v>102300</v>
       </c>
       <c r="C167" s="16">
         <v>1</v>
       </c>
       <c r="D167" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E167" s="16">
-        <v>102500001</v>
+        <v>102300001</v>
       </c>
       <c r="F167" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G167" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H167" s="17">
         <v>10</v>
@@ -9560,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M167" s="17">
         <v>0</v>
@@ -9574,26 +9574,26 @@
     </row>
     <row r="168" spans="1:15">
       <c r="A168" s="1">
-        <f t="shared" si="3"/>
-        <v>10250011</v>
+        <f t="shared" si="2"/>
+        <v>10230011</v>
       </c>
       <c r="B168" s="16">
-        <v>102500</v>
+        <v>102300</v>
       </c>
       <c r="C168" s="16">
         <v>1</v>
       </c>
       <c r="D168" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E168" s="16">
-        <v>102500001</v>
+        <v>102300001</v>
       </c>
       <c r="F168" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G168" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H168" s="17">
         <v>11</v>
@@ -9608,7 +9608,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M168" s="17">
         <v>0</v>
@@ -9622,26 +9622,26 @@
     </row>
     <row r="169" spans="1:15">
       <c r="A169" s="1">
-        <f t="shared" si="3"/>
-        <v>10250012</v>
+        <f t="shared" si="2"/>
+        <v>10230012</v>
       </c>
       <c r="B169" s="16">
-        <v>102500</v>
+        <v>102300</v>
       </c>
       <c r="C169" s="16">
         <v>1</v>
       </c>
       <c r="D169" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E169" s="16">
-        <v>102500001</v>
+        <v>102300001</v>
       </c>
       <c r="F169" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G169" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H169" s="17">
         <v>12</v>
@@ -9656,7 +9656,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M169" s="17">
         <v>0</v>
@@ -9670,31 +9670,31 @@
     </row>
     <row r="170" spans="1:15">
       <c r="A170" s="1">
-        <f t="shared" si="3"/>
-        <v>10230010</v>
-      </c>
-      <c r="B170" s="16">
-        <v>102300</v>
-      </c>
-      <c r="C170" s="16">
-        <v>1</v>
-      </c>
-      <c r="D170" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E170" s="16">
-        <v>102300001</v>
-      </c>
-      <c r="F170" s="16" t="s">
-        <v>58</v>
+        <f t="shared" si="2"/>
+        <v>10340010</v>
+      </c>
+      <c r="B170" s="4">
+        <v>103400</v>
+      </c>
+      <c r="C170" s="4">
+        <v>1</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E170" s="13">
+        <v>103000001</v>
+      </c>
+      <c r="F170" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="G170" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="H170" s="17">
+        <v>106</v>
+      </c>
+      <c r="H170" s="1">
         <v>10</v>
       </c>
-      <c r="I170" s="24">
+      <c r="I170" s="2">
         <v>0</v>
       </c>
       <c r="J170" s="17">
@@ -9704,7 +9704,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M170" s="17">
         <v>0</v>
@@ -9718,31 +9718,31 @@
     </row>
     <row r="171" spans="1:15">
       <c r="A171" s="1">
-        <f t="shared" si="3"/>
-        <v>10230011</v>
-      </c>
-      <c r="B171" s="16">
-        <v>102300</v>
-      </c>
-      <c r="C171" s="16">
-        <v>1</v>
-      </c>
-      <c r="D171" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E171" s="16">
-        <v>102300001</v>
-      </c>
-      <c r="F171" s="16" t="s">
-        <v>58</v>
+        <f t="shared" si="2"/>
+        <v>10340011</v>
+      </c>
+      <c r="B171" s="4">
+        <v>103400</v>
+      </c>
+      <c r="C171" s="4">
+        <v>1</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E171" s="13">
+        <v>103000001</v>
+      </c>
+      <c r="F171" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="G171" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H171" s="17">
+        <v>108</v>
+      </c>
+      <c r="H171" s="1">
         <v>11</v>
       </c>
-      <c r="I171" s="24">
+      <c r="I171" s="2">
         <v>0</v>
       </c>
       <c r="J171" s="17">
@@ -9752,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M171" s="17">
         <v>0</v>
@@ -9766,31 +9766,31 @@
     </row>
     <row r="172" spans="1:15">
       <c r="A172" s="1">
-        <f t="shared" si="3"/>
-        <v>10230012</v>
-      </c>
-      <c r="B172" s="16">
-        <v>102300</v>
-      </c>
-      <c r="C172" s="16">
-        <v>1</v>
-      </c>
-      <c r="D172" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E172" s="16">
-        <v>102300001</v>
-      </c>
-      <c r="F172" s="16" t="s">
-        <v>58</v>
+        <f t="shared" si="2"/>
+        <v>10340012</v>
+      </c>
+      <c r="B172" s="4">
+        <v>103400</v>
+      </c>
+      <c r="C172" s="4">
+        <v>1</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E172" s="13">
+        <v>103000001</v>
+      </c>
+      <c r="F172" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="G172" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H172" s="17">
+        <v>109</v>
+      </c>
+      <c r="H172" s="1">
         <v>12</v>
       </c>
-      <c r="I172" s="24">
+      <c r="I172" s="2">
         <v>0</v>
       </c>
       <c r="J172" s="17">
@@ -9800,7 +9800,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M172" s="17">
         <v>0</v>
@@ -9814,26 +9814,26 @@
     </row>
     <row r="173" spans="1:15">
       <c r="A173" s="1">
-        <f t="shared" si="3"/>
-        <v>10340010</v>
+        <f t="shared" si="2"/>
+        <v>10350010</v>
       </c>
       <c r="B173" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C173" s="4">
         <v>1</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E173" s="13">
-        <v>103000001</v>
+        <v>102900001</v>
       </c>
       <c r="F173" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G173" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H173" s="1">
         <v>10</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M173" s="17">
         <v>0</v>
@@ -9862,26 +9862,26 @@
     </row>
     <row r="174" spans="1:15">
       <c r="A174" s="1">
-        <f t="shared" si="3"/>
-        <v>10340011</v>
+        <f t="shared" si="2"/>
+        <v>10350011</v>
       </c>
       <c r="B174" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C174" s="4">
         <v>1</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E174" s="13">
-        <v>103000001</v>
+        <v>102900001</v>
       </c>
       <c r="F174" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G174" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H174" s="1">
         <v>11</v>
@@ -9896,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M174" s="17">
         <v>0</v>
@@ -9910,26 +9910,26 @@
     </row>
     <row r="175" spans="1:15">
       <c r="A175" s="1">
-        <f t="shared" si="3"/>
-        <v>10340012</v>
+        <f t="shared" si="2"/>
+        <v>10350012</v>
       </c>
       <c r="B175" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C175" s="4">
         <v>1</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E175" s="13">
-        <v>103000001</v>
+        <v>102900001</v>
       </c>
       <c r="F175" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G175" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H175" s="1">
         <v>12</v>
@@ -9944,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M175" s="17">
         <v>0</v>
@@ -9958,26 +9958,26 @@
     </row>
     <row r="176" spans="1:15">
       <c r="A176" s="1">
-        <f t="shared" si="3"/>
-        <v>10350010</v>
+        <f t="shared" si="2"/>
+        <v>10350110</v>
       </c>
       <c r="B176" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C176" s="4">
         <v>1</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E176" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F176" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G176" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H176" s="1">
         <v>10</v>
@@ -9988,11 +9988,11 @@
       <c r="J176" s="17">
         <v>-1</v>
       </c>
-      <c r="K176" s="17">
+      <c r="K176" s="1">
         <v>0</v>
       </c>
       <c r="L176" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M176" s="17">
         <v>0</v>
@@ -10006,26 +10006,26 @@
     </row>
     <row r="177" spans="1:15">
       <c r="A177" s="1">
-        <f t="shared" si="3"/>
-        <v>10350011</v>
+        <f t="shared" si="2"/>
+        <v>10350111</v>
       </c>
       <c r="B177" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C177" s="4">
         <v>1</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E177" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F177" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G177" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H177" s="1">
         <v>11</v>
@@ -10036,11 +10036,11 @@
       <c r="J177" s="17">
         <v>-1</v>
       </c>
-      <c r="K177" s="17">
+      <c r="K177" s="1">
         <v>0</v>
       </c>
       <c r="L177" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M177" s="17">
         <v>0</v>
@@ -10054,26 +10054,26 @@
     </row>
     <row r="178" spans="1:15">
       <c r="A178" s="1">
-        <f t="shared" si="3"/>
-        <v>10350012</v>
+        <f t="shared" si="2"/>
+        <v>10350112</v>
       </c>
       <c r="B178" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C178" s="4">
         <v>1</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E178" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F178" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G178" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H178" s="1">
         <v>12</v>
@@ -10084,11 +10084,11 @@
       <c r="J178" s="17">
         <v>-1</v>
       </c>
-      <c r="K178" s="17">
+      <c r="K178" s="1">
         <v>0</v>
       </c>
       <c r="L178" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M178" s="17">
         <v>0</v>
@@ -10102,47 +10102,47 @@
     </row>
     <row r="179" spans="1:15">
       <c r="A179" s="1">
-        <f t="shared" si="3"/>
-        <v>10350110</v>
+        <v>30040010</v>
       </c>
       <c r="B179" s="4">
-        <v>103501</v>
+        <v>300400</v>
       </c>
       <c r="C179" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E179" s="13">
-        <v>103501001</v>
+        <v>300400023</v>
       </c>
       <c r="F179" s="13" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="G179" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H179" s="1">
         <v>10</v>
       </c>
-      <c r="I179" s="2">
-        <v>0</v>
-      </c>
-      <c r="J179" s="17">
+      <c r="I179" s="23">
+        <f t="shared" ref="I179:I181" si="7">N179*52</f>
+        <v>5200</v>
+      </c>
+      <c r="J179" s="1">
         <v>-1</v>
       </c>
       <c r="K179" s="1">
         <v>0</v>
       </c>
-      <c r="L179" s="25" t="s">
-        <v>109</v>
+      <c r="L179" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="M179" s="17">
         <v>0</v>
       </c>
-      <c r="N179">
-        <v>1000</v>
+      <c r="N179" s="23">
+        <v>100</v>
       </c>
       <c r="O179" s="26">
         <v>1980000</v>
@@ -10150,47 +10150,47 @@
     </row>
     <row r="180" spans="1:15">
       <c r="A180" s="1">
-        <f t="shared" si="3"/>
-        <v>10350111</v>
+        <v>30040011</v>
       </c>
       <c r="B180" s="4">
-        <v>103501</v>
+        <v>300400</v>
       </c>
       <c r="C180" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E180" s="13">
-        <v>103501001</v>
+        <v>300400023</v>
       </c>
       <c r="F180" s="13" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="G180" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H180" s="1">
         <v>11</v>
       </c>
-      <c r="I180" s="2">
-        <v>0</v>
-      </c>
-      <c r="J180" s="17">
+      <c r="I180" s="23">
+        <f t="shared" si="7"/>
+        <v>52000</v>
+      </c>
+      <c r="J180" s="1">
         <v>-1</v>
       </c>
       <c r="K180" s="1">
         <v>0</v>
       </c>
-      <c r="L180" s="25" t="s">
-        <v>109</v>
+      <c r="L180" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="M180" s="17">
         <v>0</v>
       </c>
-      <c r="N180">
-        <v>10000</v>
+      <c r="N180" s="23">
+        <v>1000</v>
       </c>
       <c r="O180" s="26">
         <v>1980000</v>
@@ -10198,47 +10198,47 @@
     </row>
     <row r="181" spans="1:15">
       <c r="A181" s="1">
-        <f t="shared" si="3"/>
-        <v>10350112</v>
+        <v>30040012</v>
       </c>
       <c r="B181" s="4">
-        <v>103501</v>
+        <v>300400</v>
       </c>
       <c r="C181" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E181" s="13">
-        <v>103501001</v>
+        <v>300400023</v>
       </c>
       <c r="F181" s="13" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="G181" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H181" s="1">
         <v>12</v>
       </c>
-      <c r="I181" s="2">
-        <v>0</v>
-      </c>
-      <c r="J181" s="17">
+      <c r="I181" s="23">
+        <f t="shared" si="7"/>
+        <v>520000</v>
+      </c>
+      <c r="J181" s="1">
         <v>-1</v>
       </c>
       <c r="K181" s="1">
         <v>0</v>
       </c>
-      <c r="L181" s="25" t="s">
-        <v>109</v>
+      <c r="L181" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="M181" s="17">
         <v>0</v>
       </c>
-      <c r="N181">
-        <v>100000</v>
+      <c r="N181" s="23">
+        <v>10000</v>
       </c>
       <c r="O181" s="26">
         <v>1980000</v>
@@ -10246,32 +10246,31 @@
     </row>
     <row r="182" spans="1:15">
       <c r="A182" s="1">
-        <v>30040010</v>
+        <v>10010021</v>
       </c>
       <c r="B182" s="4">
-        <v>300400</v>
+        <v>100100</v>
       </c>
       <c r="C182" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="E182" s="13">
-        <v>300400023</v>
+        <v>100100026</v>
       </c>
       <c r="F182" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="G182" s="17" t="s">
-        <v>108</v>
+        <v>31</v>
+      </c>
+      <c r="G182" s="27" t="s">
+        <v>112</v>
       </c>
       <c r="H182" s="1">
-        <v>10</v>
-      </c>
-      <c r="I182" s="23">
-        <f t="shared" ref="I182:I184" si="8">N182*52</f>
-        <v>5200</v>
+        <v>21</v>
+      </c>
+      <c r="I182" s="2">
+        <v>0</v>
       </c>
       <c r="J182" s="1">
         <v>-1</v>
@@ -10280,46 +10279,45 @@
         <v>0</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M182" s="17">
-        <v>0</v>
-      </c>
-      <c r="N182" s="23">
-        <v>100</v>
-      </c>
-      <c r="O182" s="26">
-        <v>1980000</v>
+        <v>33</v>
+      </c>
+      <c r="M182" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="N182">
+        <v>1000</v>
+      </c>
+      <c r="O182" s="15">
+        <v>1990000</v>
       </c>
     </row>
     <row r="183" spans="1:15">
       <c r="A183" s="1">
-        <v>30040011</v>
+        <v>10010022</v>
       </c>
       <c r="B183" s="4">
-        <v>300400</v>
+        <v>100100</v>
       </c>
       <c r="C183" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="E183" s="13">
-        <v>300400023</v>
+        <v>100100026</v>
       </c>
       <c r="F183" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="G183" s="17" t="s">
-        <v>110</v>
+        <v>31</v>
+      </c>
+      <c r="G183" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="H183" s="1">
-        <v>11</v>
-      </c>
-      <c r="I183" s="23">
-        <f t="shared" si="8"/>
-        <v>52000</v>
+        <v>22</v>
+      </c>
+      <c r="I183" s="2">
+        <v>10000</v>
       </c>
       <c r="J183" s="1">
         <v>-1</v>
@@ -10328,46 +10326,45 @@
         <v>0</v>
       </c>
       <c r="L183" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M183" s="17">
-        <v>0</v>
-      </c>
-      <c r="N183" s="23">
-        <v>1000</v>
-      </c>
-      <c r="O183" s="26">
-        <v>1980000</v>
+        <v>33</v>
+      </c>
+      <c r="M183" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="N183">
+        <v>10000</v>
+      </c>
+      <c r="O183" s="15">
+        <v>1990000</v>
       </c>
     </row>
     <row r="184" spans="1:15">
       <c r="A184" s="1">
-        <v>30040012</v>
+        <v>10010023</v>
       </c>
       <c r="B184" s="4">
-        <v>300400</v>
+        <v>100100</v>
       </c>
       <c r="C184" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="E184" s="13">
-        <v>300400023</v>
+        <v>100100026</v>
       </c>
       <c r="F184" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="G184" s="17" t="s">
-        <v>111</v>
+        <v>31</v>
+      </c>
+      <c r="G184" s="27" t="s">
+        <v>114</v>
       </c>
       <c r="H184" s="1">
-        <v>12</v>
-      </c>
-      <c r="I184" s="23">
-        <f t="shared" si="8"/>
-        <v>520000</v>
+        <v>23</v>
+      </c>
+      <c r="I184" s="2">
+        <v>100000</v>
       </c>
       <c r="J184" s="1">
         <v>-1</v>
@@ -10376,39 +10373,39 @@
         <v>0</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M184" s="17">
-        <v>0</v>
-      </c>
-      <c r="N184" s="23">
-        <v>10000</v>
-      </c>
-      <c r="O184" s="26">
-        <v>1980000</v>
+        <v>33</v>
+      </c>
+      <c r="M184" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="N184">
+        <v>100000</v>
+      </c>
+      <c r="O184" s="15">
+        <v>1990000</v>
       </c>
     </row>
     <row r="185" spans="1:15">
       <c r="A185" s="1">
-        <v>10010021</v>
+        <v>10030021</v>
       </c>
       <c r="B185" s="4">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C185" s="4">
         <v>1</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E185" s="13">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="F185" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G185" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H185" s="1">
         <v>21</v>
@@ -10437,25 +10434,25 @@
     </row>
     <row r="186" spans="1:15">
       <c r="A186" s="1">
-        <v>10010022</v>
+        <v>10030022</v>
       </c>
       <c r="B186" s="4">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C186" s="4">
         <v>1</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E186" s="13">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="F186" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G186" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H186" s="1">
         <v>22</v>
@@ -10484,25 +10481,25 @@
     </row>
     <row r="187" spans="1:15">
       <c r="A187" s="1">
-        <v>10010023</v>
+        <v>10030023</v>
       </c>
       <c r="B187" s="4">
-        <v>100100</v>
+        <v>100300</v>
       </c>
       <c r="C187" s="4">
         <v>1</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E187" s="13">
-        <v>100100026</v>
+        <v>100300001</v>
       </c>
       <c r="F187" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G187" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H187" s="1">
         <v>23</v>
@@ -10531,25 +10528,25 @@
     </row>
     <row r="188" spans="1:15">
       <c r="A188" s="1">
-        <v>10030021</v>
+        <v>10070021</v>
       </c>
       <c r="B188" s="4">
-        <v>100300</v>
+        <v>100700</v>
       </c>
       <c r="C188" s="4">
         <v>1</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E188" s="13">
-        <v>100300001</v>
+        <v>100700001</v>
       </c>
       <c r="F188" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G188" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H188" s="1">
         <v>21</v>
@@ -10578,25 +10575,25 @@
     </row>
     <row r="189" spans="1:15">
       <c r="A189" s="1">
-        <v>10030022</v>
+        <v>10070022</v>
       </c>
       <c r="B189" s="4">
-        <v>100300</v>
+        <v>100700</v>
       </c>
       <c r="C189" s="4">
         <v>1</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E189" s="13">
-        <v>100300001</v>
+        <v>100700001</v>
       </c>
       <c r="F189" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G189" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H189" s="1">
         <v>22</v>
@@ -10625,25 +10622,25 @@
     </row>
     <row r="190" spans="1:15">
       <c r="A190" s="1">
-        <v>10030023</v>
+        <v>10070023</v>
       </c>
       <c r="B190" s="4">
-        <v>100300</v>
+        <v>100700</v>
       </c>
       <c r="C190" s="4">
         <v>1</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E190" s="13">
-        <v>100300001</v>
+        <v>100700001</v>
       </c>
       <c r="F190" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G190" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H190" s="1">
         <v>23</v>
@@ -10672,25 +10669,25 @@
     </row>
     <row r="191" spans="1:15">
       <c r="A191" s="1">
-        <v>10070021</v>
+        <v>10120021</v>
       </c>
       <c r="B191" s="4">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C191" s="4">
         <v>1</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E191" s="13">
-        <v>100700001</v>
+        <v>101200001</v>
       </c>
       <c r="F191" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G191" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H191" s="1">
         <v>21</v>
@@ -10711,7 +10708,7 @@
         <v>34</v>
       </c>
       <c r="N191">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="O191" s="15">
         <v>1990000</v>
@@ -10719,31 +10716,31 @@
     </row>
     <row r="192" spans="1:15">
       <c r="A192" s="1">
-        <v>10070022</v>
+        <v>10120022</v>
       </c>
       <c r="B192" s="4">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C192" s="4">
         <v>1</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E192" s="13">
-        <v>100700001</v>
+        <v>101200001</v>
       </c>
       <c r="F192" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G192" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H192" s="1">
         <v>22</v>
       </c>
       <c r="I192" s="2">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="J192" s="1">
         <v>-1</v>
@@ -10758,7 +10755,7 @@
         <v>34</v>
       </c>
       <c r="N192">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="O192" s="15">
         <v>1990000</v>
@@ -10766,31 +10763,31 @@
     </row>
     <row r="193" spans="1:15">
       <c r="A193" s="1">
-        <v>10070023</v>
+        <v>10120023</v>
       </c>
       <c r="B193" s="4">
-        <v>100700</v>
+        <v>101200</v>
       </c>
       <c r="C193" s="4">
         <v>1</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E193" s="13">
-        <v>100700001</v>
+        <v>101200001</v>
       </c>
       <c r="F193" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G193" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H193" s="1">
         <v>23</v>
       </c>
       <c r="I193" s="2">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="J193" s="1">
         <v>-1</v>
@@ -10805,7 +10802,7 @@
         <v>34</v>
       </c>
       <c r="N193">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="O193" s="15">
         <v>1990000</v>
@@ -10813,25 +10810,25 @@
     </row>
     <row r="194" spans="1:15">
       <c r="A194" s="1">
-        <v>10120021</v>
+        <v>10140021</v>
       </c>
       <c r="B194" s="4">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C194" s="4">
         <v>1</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E194" s="13">
-        <v>101200001</v>
+        <v>101400001</v>
       </c>
       <c r="F194" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G194" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H194" s="1">
         <v>21</v>
@@ -10852,7 +10849,7 @@
         <v>34</v>
       </c>
       <c r="N194">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="O194" s="15">
         <v>1990000</v>
@@ -10860,31 +10857,31 @@
     </row>
     <row r="195" spans="1:15">
       <c r="A195" s="1">
-        <v>10120022</v>
+        <v>10140022</v>
       </c>
       <c r="B195" s="4">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C195" s="4">
         <v>1</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E195" s="13">
-        <v>101200001</v>
+        <v>101400001</v>
       </c>
       <c r="F195" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G195" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H195" s="1">
         <v>22</v>
       </c>
       <c r="I195" s="2">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="J195" s="1">
         <v>-1</v>
@@ -10899,7 +10896,7 @@
         <v>34</v>
       </c>
       <c r="N195">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="O195" s="15">
         <v>1990000</v>
@@ -10907,31 +10904,31 @@
     </row>
     <row r="196" spans="1:15">
       <c r="A196" s="1">
-        <v>10120023</v>
+        <v>10140023</v>
       </c>
       <c r="B196" s="4">
-        <v>101200</v>
+        <v>101400</v>
       </c>
       <c r="C196" s="4">
         <v>1</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E196" s="13">
-        <v>101200001</v>
+        <v>101400001</v>
       </c>
       <c r="F196" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G196" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H196" s="1">
         <v>23</v>
       </c>
       <c r="I196" s="2">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="J196" s="1">
         <v>-1</v>
@@ -10946,7 +10943,7 @@
         <v>34</v>
       </c>
       <c r="N196">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="O196" s="15">
         <v>1990000</v>
@@ -10954,25 +10951,25 @@
     </row>
     <row r="197" spans="1:15">
       <c r="A197" s="1">
-        <v>10140021</v>
+        <v>10240021</v>
       </c>
       <c r="B197" s="4">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C197" s="4">
         <v>1</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E197" s="13">
-        <v>101400001</v>
+        <v>102400026</v>
       </c>
       <c r="F197" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G197" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H197" s="1">
         <v>21</v>
@@ -10993,7 +10990,7 @@
         <v>34</v>
       </c>
       <c r="N197">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O197" s="15">
         <v>1990000</v>
@@ -11001,25 +10998,25 @@
     </row>
     <row r="198" spans="1:15">
       <c r="A198" s="1">
-        <v>10140022</v>
+        <v>10240022</v>
       </c>
       <c r="B198" s="4">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C198" s="4">
         <v>1</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E198" s="13">
-        <v>101400001</v>
+        <v>102400026</v>
       </c>
       <c r="F198" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G198" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H198" s="1">
         <v>22</v>
@@ -11048,25 +11045,25 @@
     </row>
     <row r="199" spans="1:15">
       <c r="A199" s="1">
-        <v>10140023</v>
+        <v>10240023</v>
       </c>
       <c r="B199" s="4">
-        <v>101400</v>
+        <v>102400</v>
       </c>
       <c r="C199" s="4">
         <v>1</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E199" s="13">
-        <v>101400001</v>
+        <v>102400026</v>
       </c>
       <c r="F199" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G199" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H199" s="1">
         <v>23</v>
@@ -11095,25 +11092,25 @@
     </row>
     <row r="200" spans="1:15">
       <c r="A200" s="1">
-        <v>10240021</v>
+        <v>10220021</v>
       </c>
       <c r="B200" s="4">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C200" s="4">
         <v>1</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E200" s="13">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F200" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G200" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H200" s="1">
         <v>21</v>
@@ -11134,7 +11131,7 @@
         <v>34</v>
       </c>
       <c r="N200">
-        <v>100</v>
+        <v>1250</v>
       </c>
       <c r="O200" s="15">
         <v>1990000</v>
@@ -11142,31 +11139,31 @@
     </row>
     <row r="201" spans="1:15">
       <c r="A201" s="1">
-        <v>10240022</v>
+        <v>10220022</v>
       </c>
       <c r="B201" s="4">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C201" s="4">
         <v>1</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E201" s="13">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F201" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G201" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H201" s="1">
         <v>22</v>
       </c>
       <c r="I201" s="2">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="J201" s="1">
         <v>-1</v>
@@ -11181,7 +11178,7 @@
         <v>34</v>
       </c>
       <c r="N201">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="O201" s="15">
         <v>1990000</v>
@@ -11189,31 +11186,31 @@
     </row>
     <row r="202" spans="1:15">
       <c r="A202" s="1">
-        <v>10240023</v>
+        <v>10220023</v>
       </c>
       <c r="B202" s="4">
-        <v>102400</v>
+        <v>102200</v>
       </c>
       <c r="C202" s="4">
         <v>1</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E202" s="13">
-        <v>102400026</v>
+        <v>102200001</v>
       </c>
       <c r="F202" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G202" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H202" s="1">
         <v>23</v>
       </c>
       <c r="I202" s="2">
-        <v>100000</v>
+        <v>125000</v>
       </c>
       <c r="J202" s="1">
         <v>-1</v>
@@ -11228,7 +11225,7 @@
         <v>34</v>
       </c>
       <c r="N202">
-        <v>100000</v>
+        <v>125000</v>
       </c>
       <c r="O202" s="15">
         <v>1990000</v>
@@ -11236,25 +11233,25 @@
     </row>
     <row r="203" spans="1:15">
       <c r="A203" s="1">
-        <v>10220021</v>
+        <v>10170021</v>
       </c>
       <c r="B203" s="4">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C203" s="4">
         <v>1</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E203" s="13">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F203" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G203" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H203" s="1">
         <v>21</v>
@@ -11275,7 +11272,7 @@
         <v>34</v>
       </c>
       <c r="N203">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="O203" s="15">
         <v>1990000</v>
@@ -11283,31 +11280,31 @@
     </row>
     <row r="204" spans="1:15">
       <c r="A204" s="1">
-        <v>10220022</v>
+        <v>10170022</v>
       </c>
       <c r="B204" s="4">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C204" s="4">
         <v>1</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E204" s="13">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F204" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G204" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H204" s="1">
         <v>22</v>
       </c>
       <c r="I204" s="2">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="J204" s="1">
         <v>-1</v>
@@ -11322,7 +11319,7 @@
         <v>34</v>
       </c>
       <c r="N204">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="O204" s="15">
         <v>1990000</v>
@@ -11330,31 +11327,31 @@
     </row>
     <row r="205" spans="1:15">
       <c r="A205" s="1">
-        <v>10220023</v>
+        <v>10170023</v>
       </c>
       <c r="B205" s="4">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C205" s="4">
         <v>1</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E205" s="13">
-        <v>102200001</v>
+        <v>101700001</v>
       </c>
       <c r="F205" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G205" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H205" s="1">
         <v>23</v>
       </c>
       <c r="I205" s="2">
-        <v>125000</v>
+        <v>100000</v>
       </c>
       <c r="J205" s="1">
         <v>-1</v>
@@ -11369,7 +11366,7 @@
         <v>34</v>
       </c>
       <c r="N205">
-        <v>125000</v>
+        <v>100000</v>
       </c>
       <c r="O205" s="15">
         <v>1990000</v>
@@ -11377,25 +11374,25 @@
     </row>
     <row r="206" spans="1:15">
       <c r="A206" s="1">
-        <v>10170021</v>
+        <v>10210021</v>
       </c>
       <c r="B206" s="4">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C206" s="4">
         <v>1</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E206" s="13">
-        <v>101700001</v>
-      </c>
-      <c r="F206" s="13" t="s">
-        <v>50</v>
+        <v>102100001</v>
+      </c>
+      <c r="F206" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="G206" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H206" s="1">
         <v>21</v>
@@ -11424,25 +11421,25 @@
     </row>
     <row r="207" spans="1:15">
       <c r="A207" s="1">
-        <v>10170022</v>
+        <v>10210022</v>
       </c>
       <c r="B207" s="4">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C207" s="4">
         <v>1</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E207" s="13">
-        <v>101700001</v>
-      </c>
-      <c r="F207" s="13" t="s">
-        <v>50</v>
+        <v>102100001</v>
+      </c>
+      <c r="F207" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="G207" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H207" s="1">
         <v>22</v>
@@ -11471,25 +11468,25 @@
     </row>
     <row r="208" spans="1:15">
       <c r="A208" s="1">
-        <v>10170023</v>
+        <v>10210023</v>
       </c>
       <c r="B208" s="4">
-        <v>101700</v>
+        <v>102100</v>
       </c>
       <c r="C208" s="4">
         <v>1</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E208" s="13">
-        <v>101700001</v>
-      </c>
-      <c r="F208" s="13" t="s">
-        <v>50</v>
+        <v>102100001</v>
+      </c>
+      <c r="F208" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="G208" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H208" s="1">
         <v>23</v>
@@ -11518,25 +11515,26 @@
     </row>
     <row r="209" spans="1:15">
       <c r="A209" s="1">
-        <v>10210021</v>
-      </c>
-      <c r="B209" s="4">
-        <v>102100</v>
-      </c>
-      <c r="C209" s="4">
-        <v>1</v>
-      </c>
-      <c r="D209" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E209" s="13">
-        <v>102100001</v>
+        <f>B209*100+H209</f>
+        <v>10180021</v>
+      </c>
+      <c r="B209" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C209" s="16">
+        <v>1</v>
+      </c>
+      <c r="D209" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E209" s="16">
+        <v>101800001</v>
       </c>
       <c r="F209" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G209" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H209" s="1">
         <v>21</v>
@@ -11544,10 +11542,10 @@
       <c r="I209" s="2">
         <v>0</v>
       </c>
-      <c r="J209" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K209" s="1">
+      <c r="J209" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K209" s="17">
         <v>0</v>
       </c>
       <c r="L209" s="3" t="s">
@@ -11565,25 +11563,26 @@
     </row>
     <row r="210" spans="1:15">
       <c r="A210" s="1">
-        <v>10210022</v>
-      </c>
-      <c r="B210" s="4">
-        <v>102100</v>
-      </c>
-      <c r="C210" s="4">
-        <v>1</v>
-      </c>
-      <c r="D210" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E210" s="13">
-        <v>102100001</v>
+        <f t="shared" ref="A210:A217" si="8">B210*100+H210</f>
+        <v>10180022</v>
+      </c>
+      <c r="B210" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C210" s="16">
+        <v>1</v>
+      </c>
+      <c r="D210" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E210" s="16">
+        <v>101800001</v>
       </c>
       <c r="F210" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G210" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H210" s="1">
         <v>22</v>
@@ -11591,10 +11590,10 @@
       <c r="I210" s="2">
         <v>10000</v>
       </c>
-      <c r="J210" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K210" s="1">
+      <c r="J210" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K210" s="17">
         <v>0</v>
       </c>
       <c r="L210" s="3" t="s">
@@ -11612,25 +11611,26 @@
     </row>
     <row r="211" spans="1:15">
       <c r="A211" s="1">
-        <v>10210023</v>
-      </c>
-      <c r="B211" s="4">
-        <v>102100</v>
-      </c>
-      <c r="C211" s="4">
-        <v>1</v>
-      </c>
-      <c r="D211" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E211" s="13">
-        <v>102100001</v>
+        <f t="shared" si="8"/>
+        <v>10180023</v>
+      </c>
+      <c r="B211" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C211" s="16">
+        <v>1</v>
+      </c>
+      <c r="D211" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E211" s="16">
+        <v>101800001</v>
       </c>
       <c r="F211" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G211" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H211" s="1">
         <v>23</v>
@@ -11638,10 +11638,10 @@
       <c r="I211" s="2">
         <v>100000</v>
       </c>
-      <c r="J211" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K211" s="1">
+      <c r="J211" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K211" s="17">
         <v>0</v>
       </c>
       <c r="L211" s="3" t="s">
@@ -11659,26 +11659,26 @@
     </row>
     <row r="212" spans="1:15">
       <c r="A212" s="1">
-        <f>B212*100+H212</f>
-        <v>10180021</v>
+        <f t="shared" si="8"/>
+        <v>10250021</v>
       </c>
       <c r="B212" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C212" s="16">
         <v>1</v>
       </c>
       <c r="D212" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E212" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F212" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G212" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H212" s="1">
         <v>21</v>
@@ -11707,26 +11707,26 @@
     </row>
     <row r="213" spans="1:15">
       <c r="A213" s="1">
-        <f t="shared" ref="A213:A220" si="9">B213*100+H213</f>
-        <v>10180022</v>
+        <f t="shared" si="8"/>
+        <v>10250022</v>
       </c>
       <c r="B213" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C213" s="16">
         <v>1</v>
       </c>
       <c r="D213" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E213" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F213" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G213" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H213" s="1">
         <v>22</v>
@@ -11755,26 +11755,26 @@
     </row>
     <row r="214" spans="1:15">
       <c r="A214" s="1">
-        <f t="shared" si="9"/>
-        <v>10180023</v>
+        <f t="shared" si="8"/>
+        <v>10250023</v>
       </c>
       <c r="B214" s="16">
-        <v>101800</v>
+        <v>102500</v>
       </c>
       <c r="C214" s="16">
         <v>1</v>
       </c>
       <c r="D214" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E214" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F214" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G214" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H214" s="1">
         <v>23</v>
@@ -11803,26 +11803,26 @@
     </row>
     <row r="215" spans="1:15">
       <c r="A215" s="1">
-        <f t="shared" si="9"/>
-        <v>10250021</v>
-      </c>
-      <c r="B215" s="16">
-        <v>102500</v>
-      </c>
-      <c r="C215" s="16">
-        <v>1</v>
-      </c>
-      <c r="D215" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E215" s="16">
-        <v>102500001</v>
-      </c>
-      <c r="F215" s="16" t="s">
-        <v>56</v>
+        <f t="shared" si="8"/>
+        <v>10230021</v>
+      </c>
+      <c r="B215" s="4">
+        <v>102300</v>
+      </c>
+      <c r="C215" s="4">
+        <v>1</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E215" s="13">
+        <v>102300001</v>
+      </c>
+      <c r="F215" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G215" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H215" s="1">
         <v>21</v>
@@ -11851,26 +11851,26 @@
     </row>
     <row r="216" spans="1:15">
       <c r="A216" s="1">
-        <f t="shared" si="9"/>
-        <v>10250022</v>
-      </c>
-      <c r="B216" s="16">
-        <v>102500</v>
-      </c>
-      <c r="C216" s="16">
-        <v>1</v>
-      </c>
-      <c r="D216" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E216" s="16">
-        <v>102500001</v>
-      </c>
-      <c r="F216" s="16" t="s">
-        <v>56</v>
+        <f t="shared" si="8"/>
+        <v>10230022</v>
+      </c>
+      <c r="B216" s="4">
+        <v>102300</v>
+      </c>
+      <c r="C216" s="4">
+        <v>1</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E216" s="13">
+        <v>102300001</v>
+      </c>
+      <c r="F216" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G216" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H216" s="1">
         <v>22</v>
@@ -11899,26 +11899,26 @@
     </row>
     <row r="217" spans="1:15">
       <c r="A217" s="1">
-        <f t="shared" si="9"/>
-        <v>10250023</v>
-      </c>
-      <c r="B217" s="16">
-        <v>102500</v>
-      </c>
-      <c r="C217" s="16">
-        <v>1</v>
-      </c>
-      <c r="D217" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E217" s="16">
-        <v>102500001</v>
-      </c>
-      <c r="F217" s="16" t="s">
-        <v>56</v>
+        <f t="shared" si="8"/>
+        <v>10230023</v>
+      </c>
+      <c r="B217" s="4">
+        <v>102300</v>
+      </c>
+      <c r="C217" s="4">
+        <v>1</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E217" s="13">
+        <v>102300001</v>
+      </c>
+      <c r="F217" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="G217" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H217" s="1">
         <v>23</v>
@@ -11947,26 +11947,25 @@
     </row>
     <row r="218" spans="1:15">
       <c r="A218" s="1">
-        <f t="shared" si="9"/>
-        <v>10230021</v>
+        <v>10340021</v>
       </c>
       <c r="B218" s="4">
-        <v>102300</v>
+        <v>103400</v>
       </c>
       <c r="C218" s="4">
         <v>1</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E218" s="13">
-        <v>102300001</v>
-      </c>
-      <c r="F218" s="13" t="s">
-        <v>58</v>
+        <v>103000001</v>
+      </c>
+      <c r="F218" s="18" t="s">
+        <v>60</v>
       </c>
       <c r="G218" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H218" s="1">
         <v>21</v>
@@ -11987,7 +11986,7 @@
         <v>34</v>
       </c>
       <c r="N218">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O218" s="15">
         <v>1990000</v>
@@ -11995,26 +11994,25 @@
     </row>
     <row r="219" spans="1:15">
       <c r="A219" s="1">
-        <f t="shared" si="9"/>
-        <v>10230022</v>
+        <v>10340022</v>
       </c>
       <c r="B219" s="4">
-        <v>102300</v>
+        <v>103400</v>
       </c>
       <c r="C219" s="4">
         <v>1</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E219" s="13">
-        <v>102300001</v>
-      </c>
-      <c r="F219" s="13" t="s">
-        <v>58</v>
+        <v>103000001</v>
+      </c>
+      <c r="F219" s="18" t="s">
+        <v>60</v>
       </c>
       <c r="G219" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H219" s="1">
         <v>22</v>
@@ -12043,26 +12041,25 @@
     </row>
     <row r="220" spans="1:15">
       <c r="A220" s="1">
-        <f t="shared" si="9"/>
-        <v>10230023</v>
+        <v>10340023</v>
       </c>
       <c r="B220" s="4">
-        <v>102300</v>
+        <v>103400</v>
       </c>
       <c r="C220" s="4">
         <v>1</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E220" s="13">
-        <v>102300001</v>
-      </c>
-      <c r="F220" s="13" t="s">
-        <v>58</v>
+        <v>103000001</v>
+      </c>
+      <c r="F220" s="18" t="s">
+        <v>60</v>
       </c>
       <c r="G220" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H220" s="1">
         <v>23</v>
@@ -12091,25 +12088,26 @@
     </row>
     <row r="221" spans="1:15">
       <c r="A221" s="1">
-        <v>10340021</v>
+        <f>B221*100+H221</f>
+        <v>10350021</v>
       </c>
       <c r="B221" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C221" s="4">
         <v>1</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E221" s="13">
-        <v>103000001</v>
-      </c>
-      <c r="F221" s="18" t="s">
-        <v>60</v>
+        <v>102900001</v>
+      </c>
+      <c r="F221" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="G221" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H221" s="1">
         <v>21</v>
@@ -12130,7 +12128,7 @@
         <v>34</v>
       </c>
       <c r="N221">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="O221" s="15">
         <v>1990000</v>
@@ -12138,25 +12136,26 @@
     </row>
     <row r="222" spans="1:15">
       <c r="A222" s="1">
-        <v>10340022</v>
+        <f t="shared" ref="A222:A223" si="9">B222*100+H222</f>
+        <v>10350022</v>
       </c>
       <c r="B222" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C222" s="4">
         <v>1</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E222" s="13">
-        <v>103000001</v>
-      </c>
-      <c r="F222" s="18" t="s">
-        <v>60</v>
+        <v>102900001</v>
+      </c>
+      <c r="F222" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="G222" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H222" s="1">
         <v>22</v>
@@ -12185,25 +12184,26 @@
     </row>
     <row r="223" spans="1:15">
       <c r="A223" s="1">
-        <v>10340023</v>
+        <f t="shared" si="9"/>
+        <v>10350023</v>
       </c>
       <c r="B223" s="4">
-        <v>103400</v>
+        <v>103500</v>
       </c>
       <c r="C223" s="4">
         <v>1</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E223" s="13">
-        <v>103000001</v>
-      </c>
-      <c r="F223" s="18" t="s">
-        <v>60</v>
+        <v>102900001</v>
+      </c>
+      <c r="F223" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="G223" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H223" s="1">
         <v>23</v>
@@ -12232,26 +12232,25 @@
     </row>
     <row r="224" spans="1:15">
       <c r="A224" s="1">
-        <f>B224*100+H224</f>
-        <v>10350021</v>
+        <v>10350121</v>
       </c>
       <c r="B224" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C224" s="4">
         <v>1</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E224" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F224" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G224" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H224" s="1">
         <v>21</v>
@@ -12262,7 +12261,7 @@
       <c r="J224" s="17">
         <v>-1</v>
       </c>
-      <c r="K224" s="17">
+      <c r="K224" s="1">
         <v>0</v>
       </c>
       <c r="L224" s="3" t="s">
@@ -12280,26 +12279,25 @@
     </row>
     <row r="225" spans="1:15">
       <c r="A225" s="1">
-        <f t="shared" ref="A225:A226" si="10">B225*100+H225</f>
-        <v>10350022</v>
+        <v>10350122</v>
       </c>
       <c r="B225" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C225" s="4">
         <v>1</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E225" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F225" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G225" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H225" s="1">
         <v>22</v>
@@ -12310,7 +12308,7 @@
       <c r="J225" s="17">
         <v>-1</v>
       </c>
-      <c r="K225" s="17">
+      <c r="K225" s="1">
         <v>0</v>
       </c>
       <c r="L225" s="3" t="s">
@@ -12328,26 +12326,25 @@
     </row>
     <row r="226" spans="1:15">
       <c r="A226" s="1">
-        <f t="shared" si="10"/>
-        <v>10350023</v>
+        <v>10350123</v>
       </c>
       <c r="B226" s="4">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="C226" s="4">
         <v>1</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E226" s="13">
-        <v>102900001</v>
+        <v>103501001</v>
       </c>
       <c r="F226" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G226" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H226" s="1">
         <v>23</v>
@@ -12358,7 +12355,7 @@
       <c r="J226" s="17">
         <v>-1</v>
       </c>
-      <c r="K226" s="17">
+      <c r="K226" s="1">
         <v>0</v>
       </c>
       <c r="L226" s="3" t="s">
@@ -12376,25 +12373,25 @@
     </row>
     <row r="227" spans="1:15">
       <c r="A227" s="1">
-        <v>10350121</v>
+        <v>10200021</v>
       </c>
       <c r="B227" s="4">
-        <v>103501</v>
+        <v>102000</v>
       </c>
       <c r="C227" s="4">
         <v>1</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E227" s="13">
-        <v>103501001</v>
+        <v>102000001</v>
       </c>
       <c r="F227" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G227" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H227" s="1">
         <v>21</v>
@@ -12415,7 +12412,7 @@
         <v>34</v>
       </c>
       <c r="N227">
-        <v>1000</v>
+        <v>1125</v>
       </c>
       <c r="O227" s="15">
         <v>1990000</v>
@@ -12423,25 +12420,25 @@
     </row>
     <row r="228" spans="1:15">
       <c r="A228" s="1">
-        <v>10350122</v>
+        <v>10200022</v>
       </c>
       <c r="B228" s="4">
-        <v>103501</v>
+        <v>102000</v>
       </c>
       <c r="C228" s="4">
         <v>1</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E228" s="13">
-        <v>103501001</v>
+        <v>102000001</v>
       </c>
       <c r="F228" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G228" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H228" s="1">
         <v>22</v>
@@ -12462,7 +12459,7 @@
         <v>34</v>
       </c>
       <c r="N228">
-        <v>10000</v>
+        <v>11250</v>
       </c>
       <c r="O228" s="15">
         <v>1990000</v>
@@ -12470,25 +12467,25 @@
     </row>
     <row r="229" spans="1:15">
       <c r="A229" s="1">
-        <v>10350123</v>
+        <v>10200023</v>
       </c>
       <c r="B229" s="4">
-        <v>103501</v>
+        <v>102000</v>
       </c>
       <c r="C229" s="4">
         <v>1</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E229" s="13">
-        <v>103501001</v>
+        <v>102000001</v>
       </c>
       <c r="F229" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G229" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H229" s="1">
         <v>23</v>
@@ -12509,7 +12506,7 @@
         <v>34</v>
       </c>
       <c r="N229">
-        <v>100000</v>
+        <v>112500</v>
       </c>
       <c r="O229" s="15">
         <v>1990000</v>
@@ -12517,25 +12514,26 @@
     </row>
     <row r="230" spans="1:15">
       <c r="A230" s="1">
-        <v>10200021</v>
+        <f>B230*100+H230</f>
+        <v>10360021</v>
       </c>
       <c r="B230" s="4">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C230" s="4">
         <v>1</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E230" s="13">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="F230" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G230" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H230" s="1">
         <v>21</v>
@@ -12556,7 +12554,7 @@
         <v>34</v>
       </c>
       <c r="N230">
-        <v>1125</v>
+        <v>1000</v>
       </c>
       <c r="O230" s="15">
         <v>1990000</v>
@@ -12564,25 +12562,26 @@
     </row>
     <row r="231" spans="1:15">
       <c r="A231" s="1">
-        <v>10200022</v>
+        <f t="shared" ref="A231:A232" si="10">B231*100+H231</f>
+        <v>10360022</v>
       </c>
       <c r="B231" s="4">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C231" s="4">
         <v>1</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E231" s="13">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="F231" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G231" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H231" s="1">
         <v>22</v>
@@ -12603,7 +12602,7 @@
         <v>34</v>
       </c>
       <c r="N231">
-        <v>11250</v>
+        <v>10000</v>
       </c>
       <c r="O231" s="15">
         <v>1990000</v>
@@ -12611,25 +12610,26 @@
     </row>
     <row r="232" spans="1:15">
       <c r="A232" s="1">
-        <v>10200023</v>
+        <f t="shared" si="10"/>
+        <v>10360023</v>
       </c>
       <c r="B232" s="4">
-        <v>102000</v>
+        <v>103600</v>
       </c>
       <c r="C232" s="4">
         <v>1</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E232" s="13">
-        <v>102000001</v>
+        <v>103600001</v>
       </c>
       <c r="F232" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G232" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H232" s="1">
         <v>23</v>
@@ -12650,7 +12650,7 @@
         <v>34</v>
       </c>
       <c r="N232">
-        <v>112500</v>
+        <v>100000</v>
       </c>
       <c r="O232" s="15">
         <v>1990000</v>
@@ -12658,26 +12658,25 @@
     </row>
     <row r="233" spans="1:15">
       <c r="A233" s="1">
-        <f>B233*100+H233</f>
-        <v>10360021</v>
+        <v>10340121</v>
       </c>
       <c r="B233" s="4">
-        <v>103600</v>
+        <v>103401</v>
       </c>
       <c r="C233" s="4">
         <v>1</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E233" s="13">
-        <v>103600001</v>
+        <v>103400001</v>
       </c>
       <c r="F233" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G233" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H233" s="1">
         <v>21</v>
@@ -12706,26 +12705,25 @@
     </row>
     <row r="234" spans="1:15">
       <c r="A234" s="1">
-        <f t="shared" ref="A234:A235" si="11">B234*100+H234</f>
-        <v>10360022</v>
+        <v>10340122</v>
       </c>
       <c r="B234" s="4">
-        <v>103600</v>
+        <v>103401</v>
       </c>
       <c r="C234" s="4">
         <v>1</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E234" s="13">
-        <v>103600001</v>
+        <v>103400001</v>
       </c>
       <c r="F234" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G234" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H234" s="1">
         <v>22</v>
@@ -12754,26 +12752,25 @@
     </row>
     <row r="235" spans="1:15">
       <c r="A235" s="1">
-        <f t="shared" si="11"/>
-        <v>10360023</v>
+        <v>10340123</v>
       </c>
       <c r="B235" s="4">
-        <v>103600</v>
+        <v>103401</v>
       </c>
       <c r="C235" s="4">
         <v>1</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E235" s="13">
-        <v>103600001</v>
+        <v>103400001</v>
       </c>
       <c r="F235" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G235" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H235" s="1">
         <v>23</v>
@@ -12802,25 +12799,25 @@
     </row>
     <row r="236" spans="1:15">
       <c r="A236" s="1">
-        <v>10340121</v>
+        <v>10380021</v>
       </c>
       <c r="B236" s="4">
-        <v>103401</v>
+        <v>103800</v>
       </c>
       <c r="C236" s="4">
         <v>1</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E236" s="13">
-        <v>103400001</v>
+        <v>103800001</v>
       </c>
       <c r="F236" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G236" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H236" s="1">
         <v>21</v>
@@ -12841,7 +12838,7 @@
         <v>34</v>
       </c>
       <c r="N236">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="O236" s="15">
         <v>1990000</v>
@@ -12849,31 +12846,31 @@
     </row>
     <row r="237" spans="1:15">
       <c r="A237" s="1">
-        <v>10340122</v>
+        <v>10380022</v>
       </c>
       <c r="B237" s="4">
-        <v>103401</v>
+        <v>103800</v>
       </c>
       <c r="C237" s="4">
         <v>1</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E237" s="13">
-        <v>103400001</v>
+        <v>103800001</v>
       </c>
       <c r="F237" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G237" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H237" s="1">
         <v>22</v>
       </c>
       <c r="I237" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="J237" s="17">
         <v>-1</v>
@@ -12888,7 +12885,7 @@
         <v>34</v>
       </c>
       <c r="N237">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="O237" s="15">
         <v>1990000</v>
@@ -12896,31 +12893,31 @@
     </row>
     <row r="238" spans="1:15">
       <c r="A238" s="1">
-        <v>10340123</v>
+        <v>10380023</v>
       </c>
       <c r="B238" s="4">
-        <v>103401</v>
+        <v>103800</v>
       </c>
       <c r="C238" s="4">
         <v>1</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E238" s="13">
-        <v>103400001</v>
+        <v>103800001</v>
       </c>
       <c r="F238" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G238" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H238" s="1">
         <v>23</v>
       </c>
       <c r="I238" s="2">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="J238" s="17">
         <v>-1</v>
@@ -12935,7 +12932,7 @@
         <v>34</v>
       </c>
       <c r="N238">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="O238" s="15">
         <v>1990000</v>
@@ -12943,25 +12940,25 @@
     </row>
     <row r="239" spans="1:15">
       <c r="A239" s="1">
-        <v>10380021</v>
+        <v>10400021</v>
       </c>
       <c r="B239" s="4">
-        <v>103800</v>
+        <v>104000</v>
       </c>
       <c r="C239" s="4">
         <v>1</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E239" s="13">
-        <v>103800001</v>
-      </c>
-      <c r="F239" s="13" t="s">
-        <v>72</v>
+        <v>104000001</v>
+      </c>
+      <c r="F239" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="G239" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H239" s="1">
         <v>21</v>
@@ -12982,7 +12979,7 @@
         <v>34</v>
       </c>
       <c r="N239">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="O239" s="15">
         <v>1990000</v>
@@ -12990,31 +12987,31 @@
     </row>
     <row r="240" spans="1:15">
       <c r="A240" s="1">
-        <v>10380022</v>
+        <v>10400022</v>
       </c>
       <c r="B240" s="4">
-        <v>103800</v>
+        <v>104000</v>
       </c>
       <c r="C240" s="4">
         <v>1</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E240" s="13">
-        <v>103800001</v>
-      </c>
-      <c r="F240" s="13" t="s">
-        <v>72</v>
+        <v>104000001</v>
+      </c>
+      <c r="F240" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="G240" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H240" s="1">
         <v>22</v>
       </c>
       <c r="I240" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="J240" s="17">
         <v>-1</v>
@@ -13029,7 +13026,7 @@
         <v>34</v>
       </c>
       <c r="N240">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="O240" s="15">
         <v>1990000</v>
@@ -13037,31 +13034,31 @@
     </row>
     <row r="241" spans="1:19">
       <c r="A241" s="1">
-        <v>10380023</v>
+        <v>10400023</v>
       </c>
       <c r="B241" s="4">
-        <v>103800</v>
+        <v>104000</v>
       </c>
       <c r="C241" s="4">
         <v>1</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E241" s="13">
-        <v>103800001</v>
-      </c>
-      <c r="F241" s="13" t="s">
-        <v>72</v>
+        <v>104000001</v>
+      </c>
+      <c r="F241" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="G241" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H241" s="1">
         <v>23</v>
       </c>
       <c r="I241" s="2">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="J241" s="17">
         <v>-1</v>
@@ -13076,7 +13073,7 @@
         <v>34</v>
       </c>
       <c r="N241">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="O241" s="15">
         <v>1990000</v>
@@ -13084,25 +13081,25 @@
     </row>
     <row r="242" spans="1:19">
       <c r="A242" s="1">
-        <v>10400021</v>
+        <v>20010021</v>
       </c>
       <c r="B242" s="4">
-        <v>104000</v>
+        <v>200100</v>
       </c>
       <c r="C242" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E242" s="13">
-        <v>104000001</v>
-      </c>
-      <c r="F242" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G242" s="27" t="s">
-        <v>114</v>
+        <v>200100038</v>
+      </c>
+      <c r="F242" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H242" s="1">
         <v>21</v>
@@ -13110,7 +13107,7 @@
       <c r="I242" s="2">
         <v>0</v>
       </c>
-      <c r="J242" s="17">
+      <c r="J242" s="1">
         <v>-1</v>
       </c>
       <c r="K242" s="1">
@@ -13131,25 +13128,25 @@
     </row>
     <row r="243" spans="1:19">
       <c r="A243" s="1">
-        <v>10400022</v>
+        <v>20010022</v>
       </c>
       <c r="B243" s="4">
-        <v>104000</v>
+        <v>200100</v>
       </c>
       <c r="C243" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E243" s="13">
-        <v>104000001</v>
-      </c>
-      <c r="F243" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G243" s="27" t="s">
-        <v>115</v>
+        <v>200100038</v>
+      </c>
+      <c r="F243" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="H243" s="1">
         <v>22</v>
@@ -13157,7 +13154,7 @@
       <c r="I243" s="2">
         <v>10000</v>
       </c>
-      <c r="J243" s="17">
+      <c r="J243" s="1">
         <v>-1</v>
       </c>
       <c r="K243" s="1">
@@ -13178,25 +13175,25 @@
     </row>
     <row r="244" spans="1:19">
       <c r="A244" s="1">
-        <v>10400023</v>
+        <v>20010023</v>
       </c>
       <c r="B244" s="4">
-        <v>104000</v>
+        <v>200100</v>
       </c>
       <c r="C244" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E244" s="13">
-        <v>104000001</v>
-      </c>
-      <c r="F244" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G244" s="27" t="s">
-        <v>116</v>
+        <v>200100038</v>
+      </c>
+      <c r="F244" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G244" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="H244" s="1">
         <v>23</v>
@@ -13204,7 +13201,7 @@
       <c r="I244" s="2">
         <v>100000</v>
       </c>
-      <c r="J244" s="17">
+      <c r="J244" s="1">
         <v>-1</v>
       </c>
       <c r="K244" s="1">
@@ -13222,25 +13219,26 @@
       <c r="O244" s="15">
         <v>1990000</v>
       </c>
+      <c r="Q244"/>
     </row>
     <row r="245" spans="1:19">
       <c r="A245" s="1">
-        <v>20010021</v>
+        <v>20010121</v>
       </c>
       <c r="B245" s="4">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C245" s="4">
         <v>2</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E245" s="13">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F245" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G245" s="1" t="s">
         <v>32</v>
@@ -13272,22 +13270,22 @@
     </row>
     <row r="246" spans="1:19">
       <c r="A246" s="1">
-        <v>20010022</v>
+        <v>20010122</v>
       </c>
       <c r="B246" s="4">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C246" s="4">
         <v>2</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E246" s="13">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F246" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G246" s="1" t="s">
         <v>35</v>
@@ -13316,25 +13314,26 @@
       <c r="O246" s="15">
         <v>1990000</v>
       </c>
+      <c r="S246" s="1"/>
     </row>
     <row r="247" spans="1:19">
       <c r="A247" s="1">
-        <v>20010023</v>
+        <v>20010123</v>
       </c>
       <c r="B247" s="4">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C247" s="4">
         <v>2</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E247" s="13">
-        <v>200100038</v>
+        <v>200101001</v>
       </c>
       <c r="F247" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>36</v>
@@ -13363,26 +13362,26 @@
       <c r="O247" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q247"/>
+      <c r="S247" s="1"/>
     </row>
     <row r="248" spans="1:19">
       <c r="A248" s="1">
-        <v>20010121</v>
+        <v>20030021</v>
       </c>
       <c r="B248" s="4">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C248" s="4">
         <v>2</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E248" s="13">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F248" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>32</v>
@@ -13414,22 +13413,22 @@
     </row>
     <row r="249" spans="1:19">
       <c r="A249" s="1">
-        <v>20010122</v>
+        <v>20030022</v>
       </c>
       <c r="B249" s="4">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C249" s="4">
         <v>2</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E249" s="13">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F249" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>35</v>
@@ -13458,26 +13457,27 @@
       <c r="O249" s="15">
         <v>1990000</v>
       </c>
-      <c r="S249" s="1"/>
+      <c r="Q249" s="2"/>
+      <c r="R249" s="4"/>
     </row>
     <row r="250" spans="1:19">
       <c r="A250" s="1">
-        <v>20010123</v>
+        <v>20030023</v>
       </c>
       <c r="B250" s="4">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C250" s="4">
         <v>2</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E250" s="13">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="F250" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>36</v>
@@ -13506,26 +13506,27 @@
       <c r="O250" s="15">
         <v>1990000</v>
       </c>
-      <c r="S250" s="1"/>
+      <c r="Q250" s="2"/>
+      <c r="R250" s="2"/>
     </row>
     <row r="251" spans="1:19">
       <c r="A251" s="1">
-        <v>20030021</v>
+        <v>20040021</v>
       </c>
       <c r="B251" s="4">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C251" s="4">
         <v>2</v>
       </c>
-      <c r="D251" s="4" t="s">
-        <v>79</v>
+      <c r="D251" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="E251" s="13">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F251" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>32</v>
@@ -13554,25 +13555,27 @@
       <c r="O251" s="15">
         <v>1990000</v>
       </c>
+      <c r="Q251" s="2"/>
+      <c r="R251" s="2"/>
     </row>
     <row r="252" spans="1:19">
       <c r="A252" s="1">
-        <v>20030022</v>
+        <v>20040022</v>
       </c>
       <c r="B252" s="4">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C252" s="4">
         <v>2</v>
       </c>
-      <c r="D252" s="4" t="s">
-        <v>79</v>
+      <c r="D252" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="E252" s="13">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F252" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>35</v>
@@ -13602,26 +13605,26 @@
         <v>1990000</v>
       </c>
       <c r="Q252" s="2"/>
-      <c r="R252" s="4"/>
+      <c r="R252" s="2"/>
     </row>
     <row r="253" spans="1:19">
       <c r="A253" s="1">
-        <v>20030023</v>
+        <v>20040023</v>
       </c>
       <c r="B253" s="4">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C253" s="4">
         <v>2</v>
       </c>
-      <c r="D253" s="4" t="s">
-        <v>79</v>
+      <c r="D253" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="E253" s="13">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="F253" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>36</v>
@@ -13655,22 +13658,22 @@
     </row>
     <row r="254" spans="1:19">
       <c r="A254" s="1">
-        <v>20040021</v>
+        <v>20050021</v>
       </c>
       <c r="B254" s="4">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C254" s="4">
         <v>2</v>
       </c>
-      <c r="D254" s="2" t="s">
-        <v>81</v>
+      <c r="D254" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="E254" s="13">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F254" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G254" s="1" t="s">
         <v>32</v>
@@ -13691,7 +13694,7 @@
         <v>33</v>
       </c>
       <c r="M254" s="28" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="N254">
         <v>1000</v>
@@ -13704,22 +13707,22 @@
     </row>
     <row r="255" spans="1:19">
       <c r="A255" s="1">
-        <v>20040022</v>
+        <v>20050022</v>
       </c>
       <c r="B255" s="4">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C255" s="4">
         <v>2</v>
       </c>
-      <c r="D255" s="2" t="s">
-        <v>81</v>
+      <c r="D255" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="E255" s="13">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F255" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>35</v>
@@ -13740,7 +13743,7 @@
         <v>33</v>
       </c>
       <c r="M255" s="28" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="N255">
         <v>10000</v>
@@ -13753,22 +13756,22 @@
     </row>
     <row r="256" spans="1:19">
       <c r="A256" s="1">
-        <v>20040023</v>
+        <v>20050023</v>
       </c>
       <c r="B256" s="4">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C256" s="4">
         <v>2</v>
       </c>
-      <c r="D256" s="2" t="s">
-        <v>81</v>
+      <c r="D256" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="E256" s="13">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="F256" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>36</v>
@@ -13789,7 +13792,7 @@
         <v>33</v>
       </c>
       <c r="M256" s="28" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="N256">
         <v>100000</v>
@@ -13802,22 +13805,22 @@
     </row>
     <row r="257" spans="1:18">
       <c r="A257" s="1">
-        <v>20050021</v>
+        <v>20060021</v>
       </c>
       <c r="B257" s="4">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C257" s="4">
         <v>2</v>
       </c>
-      <c r="D257" s="4" t="s">
-        <v>83</v>
+      <c r="D257" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="E257" s="13">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F257" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>32</v>
@@ -13838,7 +13841,7 @@
         <v>33</v>
       </c>
       <c r="M257" s="28" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="N257">
         <v>1000</v>
@@ -13851,22 +13854,22 @@
     </row>
     <row r="258" spans="1:18">
       <c r="A258" s="1">
-        <v>20050022</v>
+        <v>20060022</v>
       </c>
       <c r="B258" s="4">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C258" s="4">
         <v>2</v>
       </c>
-      <c r="D258" s="4" t="s">
-        <v>83</v>
+      <c r="D258" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="E258" s="13">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F258" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>35</v>
@@ -13887,7 +13890,7 @@
         <v>33</v>
       </c>
       <c r="M258" s="28" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="N258">
         <v>10000</v>
@@ -13900,22 +13903,22 @@
     </row>
     <row r="259" spans="1:18">
       <c r="A259" s="1">
-        <v>20050023</v>
+        <v>20060023</v>
       </c>
       <c r="B259" s="4">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C259" s="4">
         <v>2</v>
       </c>
-      <c r="D259" s="4" t="s">
-        <v>83</v>
+      <c r="D259" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="E259" s="13">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="F259" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>36</v>
@@ -13936,7 +13939,7 @@
         <v>33</v>
       </c>
       <c r="M259" s="28" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="N259">
         <v>100000</v>
@@ -13945,26 +13948,26 @@
         <v>1990000</v>
       </c>
       <c r="Q259" s="2"/>
-      <c r="R259" s="2"/>
+      <c r="R259"/>
     </row>
     <row r="260" spans="1:18">
       <c r="A260" s="1">
-        <v>20060021</v>
+        <v>20070021</v>
       </c>
       <c r="B260" s="4">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C260" s="4">
         <v>2</v>
       </c>
-      <c r="D260" s="13" t="s">
-        <v>86</v>
+      <c r="D260" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="E260" s="13">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F260" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G260" s="1" t="s">
         <v>32</v>
@@ -13998,22 +14001,22 @@
     </row>
     <row r="261" spans="1:18">
       <c r="A261" s="1">
-        <v>20060022</v>
+        <v>20070022</v>
       </c>
       <c r="B261" s="4">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C261" s="4">
         <v>2</v>
       </c>
-      <c r="D261" s="13" t="s">
-        <v>86</v>
+      <c r="D261" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="E261" s="13">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F261" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>35</v>
@@ -14047,22 +14050,22 @@
     </row>
     <row r="262" spans="1:18">
       <c r="A262" s="1">
-        <v>20060023</v>
+        <v>20070023</v>
       </c>
       <c r="B262" s="4">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C262" s="4">
         <v>2</v>
       </c>
-      <c r="D262" s="13" t="s">
-        <v>86</v>
+      <c r="D262" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="E262" s="13">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="F262" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>36</v>
@@ -14091,27 +14094,25 @@
       <c r="O262" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q262" s="2"/>
-      <c r="R262"/>
     </row>
     <row r="263" spans="1:18">
       <c r="A263" s="1">
-        <v>20070021</v>
+        <v>20080021</v>
       </c>
       <c r="B263" s="4">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C263" s="4">
         <v>2</v>
       </c>
-      <c r="D263" s="4" t="s">
-        <v>88</v>
+      <c r="D263" s="13" t="s">
+        <v>90</v>
       </c>
       <c r="E263" s="13">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F263" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>32</v>
@@ -14140,27 +14141,25 @@
       <c r="O263" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q263" s="2"/>
-      <c r="R263" s="2"/>
     </row>
     <row r="264" spans="1:18">
       <c r="A264" s="1">
-        <v>20070022</v>
+        <v>20080022</v>
       </c>
       <c r="B264" s="4">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C264" s="4">
         <v>2</v>
       </c>
-      <c r="D264" s="4" t="s">
-        <v>88</v>
+      <c r="D264" s="13" t="s">
+        <v>90</v>
       </c>
       <c r="E264" s="13">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F264" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>35</v>
@@ -14189,27 +14188,25 @@
       <c r="O264" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q264" s="2"/>
-      <c r="R264" s="2"/>
     </row>
     <row r="265" spans="1:18">
       <c r="A265" s="1">
-        <v>20070023</v>
+        <v>20080023</v>
       </c>
       <c r="B265" s="4">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C265" s="4">
         <v>2</v>
       </c>
-      <c r="D265" s="4" t="s">
-        <v>88</v>
+      <c r="D265" s="13" t="s">
+        <v>90</v>
       </c>
       <c r="E265" s="13">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="F265" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>36</v>
@@ -14241,22 +14238,22 @@
     </row>
     <row r="266" spans="1:18">
       <c r="A266" s="1">
-        <v>20080021</v>
-      </c>
-      <c r="B266" s="4">
-        <v>200800</v>
+        <v>20090021</v>
+      </c>
+      <c r="B266" s="20">
+        <v>200900</v>
       </c>
       <c r="C266" s="4">
         <v>2</v>
       </c>
-      <c r="D266" s="13" t="s">
-        <v>90</v>
+      <c r="D266" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="E266" s="13">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F266" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>32</v>
@@ -14288,22 +14285,22 @@
     </row>
     <row r="267" spans="1:18">
       <c r="A267" s="1">
-        <v>20080022</v>
+        <v>20090022</v>
       </c>
       <c r="B267" s="4">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C267" s="4">
         <v>2</v>
       </c>
-      <c r="D267" s="13" t="s">
-        <v>90</v>
+      <c r="D267" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="E267" s="13">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F267" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>35</v>
@@ -14335,22 +14332,22 @@
     </row>
     <row r="268" spans="1:18">
       <c r="A268" s="1">
-        <v>20080023</v>
+        <v>20090023</v>
       </c>
       <c r="B268" s="4">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C268" s="4">
         <v>2</v>
       </c>
-      <c r="D268" s="13" t="s">
-        <v>90</v>
+      <c r="D268" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="E268" s="13">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="F268" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>36</v>
@@ -14382,22 +14379,22 @@
     </row>
     <row r="269" spans="1:18">
       <c r="A269" s="1">
-        <v>20090021</v>
-      </c>
-      <c r="B269" s="20">
-        <v>200900</v>
+        <v>30010021</v>
+      </c>
+      <c r="B269" s="4">
+        <v>300100</v>
       </c>
       <c r="C269" s="4">
-        <v>2</v>
-      </c>
-      <c r="D269" s="20" t="s">
-        <v>92</v>
+        <v>3</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="E269" s="13">
-        <v>200900001</v>
+        <v>300100001</v>
       </c>
       <c r="F269" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>32</v>
@@ -14415,10 +14412,10 @@
         <v>0</v>
       </c>
       <c r="L269" s="3" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="M269" s="28" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="N269">
         <v>1000</v>
@@ -14429,22 +14426,22 @@
     </row>
     <row r="270" spans="1:18">
       <c r="A270" s="1">
-        <v>20090022</v>
+        <v>30010022</v>
       </c>
       <c r="B270" s="4">
-        <v>200900</v>
+        <v>300100</v>
       </c>
       <c r="C270" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E270" s="13">
-        <v>200900001</v>
+        <v>300100001</v>
       </c>
       <c r="F270" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>35</v>
@@ -14462,10 +14459,10 @@
         <v>0</v>
       </c>
       <c r="L270" s="3" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="M270" s="28" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="N270">
         <v>10000</v>
@@ -14476,22 +14473,22 @@
     </row>
     <row r="271" spans="1:18">
       <c r="A271" s="1">
-        <v>20090023</v>
+        <v>30010023</v>
       </c>
       <c r="B271" s="4">
-        <v>200900</v>
+        <v>300100</v>
       </c>
       <c r="C271" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E271" s="13">
-        <v>200900001</v>
+        <v>300100001</v>
       </c>
       <c r="F271" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>36</v>
@@ -14509,10 +14506,10 @@
         <v>0</v>
       </c>
       <c r="L271" s="3" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="M271" s="28" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="N271">
         <v>100000</v>
@@ -14523,22 +14520,22 @@
     </row>
     <row r="272" spans="1:18">
       <c r="A272" s="1">
-        <v>30010021</v>
+        <v>30020021</v>
       </c>
       <c r="B272" s="4">
-        <v>300100</v>
+        <v>300200</v>
       </c>
       <c r="C272" s="4">
         <v>3</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E272" s="13">
-        <v>300100001</v>
+        <v>300200006</v>
       </c>
       <c r="F272" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>32</v>
@@ -14547,7 +14544,7 @@
         <v>21</v>
       </c>
       <c r="I272" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J272" s="1">
         <v>-1</v>
@@ -14556,12 +14553,12 @@
         <v>0</v>
       </c>
       <c r="L272" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M272" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N272">
+      <c r="N272" s="21">
         <v>1000</v>
       </c>
       <c r="O272" s="15">
@@ -14570,22 +14567,22 @@
     </row>
     <row r="273" spans="1:15">
       <c r="A273" s="1">
-        <v>30010022</v>
+        <v>30020022</v>
       </c>
       <c r="B273" s="4">
-        <v>300100</v>
+        <v>300200</v>
       </c>
       <c r="C273" s="4">
         <v>3</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E273" s="13">
-        <v>300100001</v>
+        <v>300200006</v>
       </c>
       <c r="F273" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>35</v>
@@ -14603,12 +14600,12 @@
         <v>0</v>
       </c>
       <c r="L273" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M273" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N273">
+      <c r="N273" s="21">
         <v>10000</v>
       </c>
       <c r="O273" s="15">
@@ -14617,22 +14614,22 @@
     </row>
     <row r="274" spans="1:15">
       <c r="A274" s="1">
-        <v>30010023</v>
+        <v>30020023</v>
       </c>
       <c r="B274" s="4">
-        <v>300100</v>
+        <v>300200</v>
       </c>
       <c r="C274" s="4">
         <v>3</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E274" s="13">
-        <v>300100001</v>
+        <v>300200006</v>
       </c>
       <c r="F274" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>36</v>
@@ -14650,12 +14647,12 @@
         <v>0</v>
       </c>
       <c r="L274" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M274" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N274">
+      <c r="N274" s="21">
         <v>100000</v>
       </c>
       <c r="O274" s="15">
@@ -14664,22 +14661,22 @@
     </row>
     <row r="275" spans="1:15">
       <c r="A275" s="1">
-        <v>30020021</v>
+        <v>30040021</v>
       </c>
       <c r="B275" s="4">
-        <v>300200</v>
-      </c>
-      <c r="C275" s="4">
+        <v>300400</v>
+      </c>
+      <c r="C275" s="1">
         <v>3</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E275" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F275" s="13" t="s">
-        <v>99</v>
+        <v>300400023</v>
+      </c>
+      <c r="F275" s="22" t="s">
+        <v>102</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>32</v>
@@ -14687,8 +14684,9 @@
       <c r="H275" s="1">
         <v>21</v>
       </c>
-      <c r="I275" s="2">
-        <v>1000</v>
+      <c r="I275" s="23">
+        <f>N275*52</f>
+        <v>5200</v>
       </c>
       <c r="J275" s="1">
         <v>-1</v>
@@ -14697,13 +14695,13 @@
         <v>0</v>
       </c>
       <c r="L275" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M275" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N275" s="21">
-        <v>1000</v>
+      <c r="N275" s="23">
+        <v>100</v>
       </c>
       <c r="O275" s="15">
         <v>1990000</v>
@@ -14711,22 +14709,22 @@
     </row>
     <row r="276" spans="1:15">
       <c r="A276" s="1">
-        <v>30020022</v>
+        <v>30040022</v>
       </c>
       <c r="B276" s="4">
-        <v>300200</v>
+        <v>300400</v>
       </c>
       <c r="C276" s="4">
         <v>3</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E276" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F276" s="13" t="s">
-        <v>99</v>
+        <v>300400023</v>
+      </c>
+      <c r="F276" s="22" t="s">
+        <v>102</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>35</v>
@@ -14734,8 +14732,9 @@
       <c r="H276" s="1">
         <v>22</v>
       </c>
-      <c r="I276" s="2">
-        <v>10000</v>
+      <c r="I276" s="23">
+        <f t="shared" ref="I276:I283" si="11">N276*52</f>
+        <v>52000</v>
       </c>
       <c r="J276" s="1">
         <v>-1</v>
@@ -14744,13 +14743,13 @@
         <v>0</v>
       </c>
       <c r="L276" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M276" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N276" s="21">
-        <v>10000</v>
+      <c r="N276" s="23">
+        <v>1000</v>
       </c>
       <c r="O276" s="15">
         <v>1990000</v>
@@ -14758,22 +14757,22 @@
     </row>
     <row r="277" spans="1:15">
       <c r="A277" s="1">
-        <v>30020023</v>
+        <v>30040023</v>
       </c>
       <c r="B277" s="4">
-        <v>300200</v>
+        <v>300400</v>
       </c>
       <c r="C277" s="4">
         <v>3</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E277" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F277" s="13" t="s">
-        <v>99</v>
+        <v>300400023</v>
+      </c>
+      <c r="F277" s="22" t="s">
+        <v>102</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>36</v>
@@ -14781,8 +14780,9 @@
       <c r="H277" s="1">
         <v>23</v>
       </c>
-      <c r="I277" s="2">
-        <v>100000</v>
+      <c r="I277" s="23">
+        <f t="shared" si="11"/>
+        <v>520000</v>
       </c>
       <c r="J277" s="1">
         <v>-1</v>
@@ -14791,13 +14791,13 @@
         <v>0</v>
       </c>
       <c r="L277" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M277" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N277" s="21">
-        <v>100000</v>
+      <c r="N277" s="23">
+        <v>10000</v>
       </c>
       <c r="O277" s="15">
         <v>1990000</v>
@@ -14805,22 +14805,22 @@
     </row>
     <row r="278" spans="1:15">
       <c r="A278" s="1">
-        <v>30040021</v>
+        <v>20120021</v>
       </c>
       <c r="B278" s="4">
-        <v>300400</v>
-      </c>
-      <c r="C278" s="1">
-        <v>3</v>
+        <v>201200</v>
+      </c>
+      <c r="C278" s="4">
+        <v>2</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E278" s="13">
-        <v>300400023</v>
+        <v>201200001</v>
       </c>
       <c r="F278" s="22" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>32</v>
@@ -14828,9 +14828,8 @@
       <c r="H278" s="1">
         <v>21</v>
       </c>
-      <c r="I278" s="23">
-        <f>N278*52</f>
-        <v>5200</v>
+      <c r="I278" s="2">
+        <v>0</v>
       </c>
       <c r="J278" s="1">
         <v>-1</v>
@@ -14839,13 +14838,13 @@
         <v>0</v>
       </c>
       <c r="L278" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M278" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N278" s="23">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="N278">
+        <v>1000</v>
       </c>
       <c r="O278" s="15">
         <v>1990000</v>
@@ -14853,22 +14852,22 @@
     </row>
     <row r="279" spans="1:15">
       <c r="A279" s="1">
-        <v>30040022</v>
+        <v>20120022</v>
       </c>
       <c r="B279" s="4">
-        <v>300400</v>
+        <v>201200</v>
       </c>
       <c r="C279" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E279" s="13">
-        <v>300400023</v>
+        <v>201200001</v>
       </c>
       <c r="F279" s="22" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>35</v>
@@ -14876,9 +14875,8 @@
       <c r="H279" s="1">
         <v>22</v>
       </c>
-      <c r="I279" s="23">
-        <f>N279*52</f>
-        <v>52000</v>
+      <c r="I279" s="2">
+        <v>10000</v>
       </c>
       <c r="J279" s="1">
         <v>-1</v>
@@ -14887,13 +14885,13 @@
         <v>0</v>
       </c>
       <c r="L279" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M279" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N279" s="23">
-        <v>1000</v>
+        <v>85</v>
+      </c>
+      <c r="N279">
+        <v>10000</v>
       </c>
       <c r="O279" s="15">
         <v>1990000</v>
@@ -14901,22 +14899,22 @@
     </row>
     <row r="280" spans="1:15">
       <c r="A280" s="1">
-        <v>30040023</v>
+        <v>20120023</v>
       </c>
       <c r="B280" s="4">
-        <v>300400</v>
+        <v>201200</v>
       </c>
       <c r="C280" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E280" s="13">
-        <v>300400023</v>
+        <v>201200001</v>
       </c>
       <c r="F280" s="22" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>36</v>
@@ -14924,9 +14922,8 @@
       <c r="H280" s="1">
         <v>23</v>
       </c>
-      <c r="I280" s="23">
-        <f>N280*52</f>
-        <v>520000</v>
+      <c r="I280" s="2">
+        <v>100000</v>
       </c>
       <c r="J280" s="1">
         <v>-1</v>
@@ -14935,13 +14932,13 @@
         <v>0</v>
       </c>
       <c r="L280" s="3" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="M280" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N280" s="23">
-        <v>10000</v>
+        <v>85</v>
+      </c>
+      <c r="N280">
+        <v>100000</v>
       </c>
       <c r="O280" s="15">
         <v>1990000</v>
@@ -14949,31 +14946,32 @@
     </row>
     <row r="281" spans="1:15">
       <c r="A281" s="1">
-        <v>20120021</v>
+        <v>30040231</v>
       </c>
       <c r="B281" s="4">
-        <v>201200</v>
-      </c>
-      <c r="C281" s="4">
-        <v>2</v>
+        <v>300402</v>
+      </c>
+      <c r="C281" s="1">
+        <v>3</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E281" s="13">
-        <v>201200001</v>
+        <v>300402001</v>
       </c>
       <c r="F281" s="22" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H281" s="1">
-        <v>21</v>
-      </c>
-      <c r="I281" s="2">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="I281" s="23">
+        <f t="shared" si="11"/>
+        <v>5200</v>
       </c>
       <c r="J281" s="1">
         <v>-1</v>
@@ -14982,45 +14980,46 @@
         <v>0</v>
       </c>
       <c r="L281" s="3" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="M281" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="N281">
-        <v>1000</v>
+        <v>97</v>
+      </c>
+      <c r="N281" s="23">
+        <v>100</v>
       </c>
       <c r="O281" s="15">
-        <v>1990000</v>
+        <v>1970000</v>
       </c>
     </row>
     <row r="282" spans="1:15">
       <c r="A282" s="1">
-        <v>20120022</v>
+        <v>30040232</v>
       </c>
       <c r="B282" s="4">
-        <v>201200</v>
+        <v>300402</v>
       </c>
       <c r="C282" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E282" s="13">
-        <v>201200001</v>
+        <v>300402001</v>
       </c>
       <c r="F282" s="22" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H282" s="1">
-        <v>22</v>
-      </c>
-      <c r="I282" s="2">
-        <v>10000</v>
+        <v>32</v>
+      </c>
+      <c r="I282" s="23">
+        <f t="shared" si="11"/>
+        <v>52000</v>
       </c>
       <c r="J282" s="1">
         <v>-1</v>
@@ -15029,45 +15028,46 @@
         <v>0</v>
       </c>
       <c r="L282" s="3" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="M282" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="N282">
-        <v>10000</v>
+        <v>97</v>
+      </c>
+      <c r="N282" s="23">
+        <v>1000</v>
       </c>
       <c r="O282" s="15">
-        <v>1990000</v>
+        <v>1970000</v>
       </c>
     </row>
     <row r="283" spans="1:15">
       <c r="A283" s="1">
-        <v>20120023</v>
+        <v>30040233</v>
       </c>
       <c r="B283" s="4">
-        <v>201200</v>
+        <v>300402</v>
       </c>
       <c r="C283" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E283" s="13">
-        <v>201200001</v>
+        <v>300402001</v>
       </c>
       <c r="F283" s="22" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H283" s="1">
-        <v>23</v>
-      </c>
-      <c r="I283" s="2">
-        <v>100000</v>
+        <v>33</v>
+      </c>
+      <c r="I283" s="23">
+        <f t="shared" si="11"/>
+        <v>520000</v>
       </c>
       <c r="J283" s="1">
         <v>-1</v>
@@ -15076,16 +15076,16 @@
         <v>0</v>
       </c>
       <c r="L283" s="3" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="M283" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="N283">
-        <v>100000</v>
+        <v>97</v>
+      </c>
+      <c r="N283" s="23">
+        <v>10000</v>
       </c>
       <c r="O283" s="15">
-        <v>1990000</v>
+        <v>1970000</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="117">
   <si>
     <t>sid</t>
   </si>
@@ -719,12 +719,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1641,7 +1641,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S283"/>
+  <dimension ref="A1:S274"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375" style="1"/>
@@ -14379,22 +14379,22 @@
     </row>
     <row r="269" spans="1:18">
       <c r="A269" s="1">
-        <v>30010021</v>
+        <v>20120021</v>
       </c>
       <c r="B269" s="4">
-        <v>300100</v>
+        <v>201200</v>
       </c>
       <c r="C269" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E269" s="13">
-        <v>300100001</v>
-      </c>
-      <c r="F269" s="13" t="s">
-        <v>95</v>
+        <v>201200001</v>
+      </c>
+      <c r="F269" s="22" t="s">
+        <v>105</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>32</v>
@@ -14412,10 +14412,10 @@
         <v>0</v>
       </c>
       <c r="L269" s="3" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="M269" s="28" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="N269">
         <v>1000</v>
@@ -14426,22 +14426,22 @@
     </row>
     <row r="270" spans="1:18">
       <c r="A270" s="1">
-        <v>30010022</v>
+        <v>20120022</v>
       </c>
       <c r="B270" s="4">
-        <v>300100</v>
+        <v>201200</v>
       </c>
       <c r="C270" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E270" s="13">
-        <v>300100001</v>
-      </c>
-      <c r="F270" s="13" t="s">
-        <v>95</v>
+        <v>201200001</v>
+      </c>
+      <c r="F270" s="22" t="s">
+        <v>105</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>35</v>
@@ -14459,10 +14459,10 @@
         <v>0</v>
       </c>
       <c r="L270" s="3" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="M270" s="28" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="N270">
         <v>10000</v>
@@ -14473,22 +14473,22 @@
     </row>
     <row r="271" spans="1:18">
       <c r="A271" s="1">
-        <v>30010023</v>
+        <v>20120023</v>
       </c>
       <c r="B271" s="4">
-        <v>300100</v>
+        <v>201200</v>
       </c>
       <c r="C271" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E271" s="13">
-        <v>300100001</v>
-      </c>
-      <c r="F271" s="13" t="s">
-        <v>95</v>
+        <v>201200001</v>
+      </c>
+      <c r="F271" s="22" t="s">
+        <v>105</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>36</v>
@@ -14506,10 +14506,10 @@
         <v>0</v>
       </c>
       <c r="L271" s="3" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="M271" s="28" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="N271">
         <v>100000</v>
@@ -14520,31 +14520,32 @@
     </row>
     <row r="272" spans="1:18">
       <c r="A272" s="1">
-        <v>30020021</v>
+        <v>30040231</v>
       </c>
       <c r="B272" s="4">
-        <v>300200</v>
-      </c>
-      <c r="C272" s="4">
+        <v>300402</v>
+      </c>
+      <c r="C272" s="1">
         <v>3</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E272" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F272" s="13" t="s">
-        <v>99</v>
+        <v>300402001</v>
+      </c>
+      <c r="F272" s="22" t="s">
+        <v>116</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H272" s="1">
-        <v>21</v>
-      </c>
-      <c r="I272" s="2">
-        <v>1000</v>
+        <v>31</v>
+      </c>
+      <c r="I272" s="23">
+        <f t="shared" ref="I269:I274" si="11">N272*52</f>
+        <v>5200</v>
       </c>
       <c r="J272" s="1">
         <v>-1</v>
@@ -14553,45 +14554,46 @@
         <v>0</v>
       </c>
       <c r="L272" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M272" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N272" s="21">
-        <v>1000</v>
+      <c r="N272" s="23">
+        <v>100</v>
       </c>
       <c r="O272" s="15">
-        <v>1990000</v>
+        <v>1970000</v>
       </c>
     </row>
     <row r="273" spans="1:15">
       <c r="A273" s="1">
-        <v>30020022</v>
+        <v>30040232</v>
       </c>
       <c r="B273" s="4">
-        <v>300200</v>
+        <v>300402</v>
       </c>
       <c r="C273" s="4">
         <v>3</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E273" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F273" s="13" t="s">
-        <v>99</v>
+        <v>300402001</v>
+      </c>
+      <c r="F273" s="22" t="s">
+        <v>116</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H273" s="1">
-        <v>22</v>
-      </c>
-      <c r="I273" s="2">
-        <v>10000</v>
+        <v>32</v>
+      </c>
+      <c r="I273" s="23">
+        <f t="shared" si="11"/>
+        <v>52000</v>
       </c>
       <c r="J273" s="1">
         <v>-1</v>
@@ -14600,45 +14602,46 @@
         <v>0</v>
       </c>
       <c r="L273" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M273" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N273" s="21">
-        <v>10000</v>
+      <c r="N273" s="23">
+        <v>1000</v>
       </c>
       <c r="O273" s="15">
-        <v>1990000</v>
+        <v>1970000</v>
       </c>
     </row>
     <row r="274" spans="1:15">
       <c r="A274" s="1">
-        <v>30020023</v>
+        <v>30040233</v>
       </c>
       <c r="B274" s="4">
-        <v>300200</v>
+        <v>300402</v>
       </c>
       <c r="C274" s="4">
         <v>3</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E274" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F274" s="13" t="s">
-        <v>99</v>
+        <v>300402001</v>
+      </c>
+      <c r="F274" s="22" t="s">
+        <v>116</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>36</v>
       </c>
       <c r="H274" s="1">
-        <v>23</v>
-      </c>
-      <c r="I274" s="2">
-        <v>100000</v>
+        <v>33</v>
+      </c>
+      <c r="I274" s="23">
+        <f t="shared" si="11"/>
+        <v>520000</v>
       </c>
       <c r="J274" s="1">
         <v>-1</v>
@@ -14647,444 +14650,15 @@
         <v>0</v>
       </c>
       <c r="L274" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M274" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="N274" s="21">
-        <v>100000</v>
+      <c r="N274" s="23">
+        <v>10000</v>
       </c>
       <c r="O274" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="275" spans="1:15">
-      <c r="A275" s="1">
-        <v>30040021</v>
-      </c>
-      <c r="B275" s="4">
-        <v>300400</v>
-      </c>
-      <c r="C275" s="1">
-        <v>3</v>
-      </c>
-      <c r="D275" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E275" s="13">
-        <v>300400023</v>
-      </c>
-      <c r="F275" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G275" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H275" s="1">
-        <v>21</v>
-      </c>
-      <c r="I275" s="23">
-        <f>N275*52</f>
-        <v>5200</v>
-      </c>
-      <c r="J275" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K275" s="1">
-        <v>0</v>
-      </c>
-      <c r="L275" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="M275" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N275" s="23">
-        <v>100</v>
-      </c>
-      <c r="O275" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="276" spans="1:15">
-      <c r="A276" s="1">
-        <v>30040022</v>
-      </c>
-      <c r="B276" s="4">
-        <v>300400</v>
-      </c>
-      <c r="C276" s="4">
-        <v>3</v>
-      </c>
-      <c r="D276" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E276" s="13">
-        <v>300400023</v>
-      </c>
-      <c r="F276" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G276" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H276" s="1">
-        <v>22</v>
-      </c>
-      <c r="I276" s="23">
-        <f t="shared" ref="I276:I283" si="11">N276*52</f>
-        <v>52000</v>
-      </c>
-      <c r="J276" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K276" s="1">
-        <v>0</v>
-      </c>
-      <c r="L276" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="M276" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N276" s="23">
-        <v>1000</v>
-      </c>
-      <c r="O276" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="277" spans="1:15">
-      <c r="A277" s="1">
-        <v>30040023</v>
-      </c>
-      <c r="B277" s="4">
-        <v>300400</v>
-      </c>
-      <c r="C277" s="4">
-        <v>3</v>
-      </c>
-      <c r="D277" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E277" s="13">
-        <v>300400023</v>
-      </c>
-      <c r="F277" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G277" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H277" s="1">
-        <v>23</v>
-      </c>
-      <c r="I277" s="23">
-        <f t="shared" si="11"/>
-        <v>520000</v>
-      </c>
-      <c r="J277" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K277" s="1">
-        <v>0</v>
-      </c>
-      <c r="L277" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="M277" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N277" s="23">
-        <v>10000</v>
-      </c>
-      <c r="O277" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="278" spans="1:15">
-      <c r="A278" s="1">
-        <v>20120021</v>
-      </c>
-      <c r="B278" s="4">
-        <v>201200</v>
-      </c>
-      <c r="C278" s="4">
-        <v>2</v>
-      </c>
-      <c r="D278" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E278" s="13">
-        <v>201200001</v>
-      </c>
-      <c r="F278" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="G278" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H278" s="1">
-        <v>21</v>
-      </c>
-      <c r="I278" s="2">
-        <v>0</v>
-      </c>
-      <c r="J278" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K278" s="1">
-        <v>0</v>
-      </c>
-      <c r="L278" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M278" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="N278">
-        <v>1000</v>
-      </c>
-      <c r="O278" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="279" spans="1:15">
-      <c r="A279" s="1">
-        <v>20120022</v>
-      </c>
-      <c r="B279" s="4">
-        <v>201200</v>
-      </c>
-      <c r="C279" s="4">
-        <v>2</v>
-      </c>
-      <c r="D279" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E279" s="13">
-        <v>201200001</v>
-      </c>
-      <c r="F279" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="G279" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H279" s="1">
-        <v>22</v>
-      </c>
-      <c r="I279" s="2">
-        <v>10000</v>
-      </c>
-      <c r="J279" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K279" s="1">
-        <v>0</v>
-      </c>
-      <c r="L279" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M279" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="N279">
-        <v>10000</v>
-      </c>
-      <c r="O279" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="280" spans="1:15">
-      <c r="A280" s="1">
-        <v>20120023</v>
-      </c>
-      <c r="B280" s="4">
-        <v>201200</v>
-      </c>
-      <c r="C280" s="4">
-        <v>2</v>
-      </c>
-      <c r="D280" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E280" s="13">
-        <v>201200001</v>
-      </c>
-      <c r="F280" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="G280" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H280" s="1">
-        <v>23</v>
-      </c>
-      <c r="I280" s="2">
-        <v>100000</v>
-      </c>
-      <c r="J280" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K280" s="1">
-        <v>0</v>
-      </c>
-      <c r="L280" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M280" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="N280">
-        <v>100000</v>
-      </c>
-      <c r="O280" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="281" spans="1:15">
-      <c r="A281" s="1">
-        <v>30040231</v>
-      </c>
-      <c r="B281" s="4">
-        <v>300402</v>
-      </c>
-      <c r="C281" s="1">
-        <v>3</v>
-      </c>
-      <c r="D281" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E281" s="13">
-        <v>300402001</v>
-      </c>
-      <c r="F281" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="G281" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H281" s="1">
-        <v>31</v>
-      </c>
-      <c r="I281" s="23">
-        <f t="shared" si="11"/>
-        <v>5200</v>
-      </c>
-      <c r="J281" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K281" s="1">
-        <v>0</v>
-      </c>
-      <c r="L281" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="M281" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N281" s="23">
-        <v>100</v>
-      </c>
-      <c r="O281" s="15">
-        <v>1970000</v>
-      </c>
-    </row>
-    <row r="282" spans="1:15">
-      <c r="A282" s="1">
-        <v>30040232</v>
-      </c>
-      <c r="B282" s="4">
-        <v>300402</v>
-      </c>
-      <c r="C282" s="4">
-        <v>3</v>
-      </c>
-      <c r="D282" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E282" s="13">
-        <v>300402001</v>
-      </c>
-      <c r="F282" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H282" s="1">
-        <v>32</v>
-      </c>
-      <c r="I282" s="23">
-        <f t="shared" si="11"/>
-        <v>52000</v>
-      </c>
-      <c r="J282" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K282" s="1">
-        <v>0</v>
-      </c>
-      <c r="L282" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="M282" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N282" s="23">
-        <v>1000</v>
-      </c>
-      <c r="O282" s="15">
-        <v>1970000</v>
-      </c>
-    </row>
-    <row r="283" spans="1:15">
-      <c r="A283" s="1">
-        <v>30040233</v>
-      </c>
-      <c r="B283" s="4">
-        <v>300402</v>
-      </c>
-      <c r="C283" s="4">
-        <v>3</v>
-      </c>
-      <c r="D283" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E283" s="13">
-        <v>300402001</v>
-      </c>
-      <c r="F283" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="G283" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H283" s="1">
-        <v>33</v>
-      </c>
-      <c r="I283" s="23">
-        <f t="shared" si="11"/>
-        <v>520000</v>
-      </c>
-      <c r="J283" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K283" s="1">
-        <v>0</v>
-      </c>
-      <c r="L283" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="M283" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N283" s="23">
-        <v>10000</v>
-      </c>
-      <c r="O283" s="15">
         <v>1970000</v>
       </c>
     </row>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="141">
   <si>
     <t>sid</t>
   </si>
@@ -533,7 +533,13 @@
     <t>糖果派对</t>
   </si>
   <si>
+    <t>CandyParty</t>
+  </si>
+  <si>
     <t>伽罗宝石</t>
+  </si>
+  <si>
+    <t>GaloGemstone</t>
   </si>
   <si>
     <t>伽罗宝石1</t>
@@ -7856,7 +7862,9 @@
       <c r="E131" s="5">
         <v>105100001</v>
       </c>
-      <c r="F131" s="5"/>
+      <c r="F131" t="s">
+        <v>125</v>
+      </c>
       <c r="G131" s="1" t="s">
         <v>32</v>
       </c>
@@ -7901,7 +7909,9 @@
       <c r="E132" s="5">
         <v>105100001</v>
       </c>
-      <c r="F132" s="5"/>
+      <c r="F132" t="s">
+        <v>125</v>
+      </c>
       <c r="G132" s="1" t="s">
         <v>35</v>
       </c>
@@ -7946,7 +7956,9 @@
       <c r="E133" s="5">
         <v>105100001</v>
       </c>
-      <c r="F133" s="5"/>
+      <c r="F133" t="s">
+        <v>125</v>
+      </c>
       <c r="G133" s="1" t="s">
         <v>36</v>
       </c>
@@ -7986,12 +7998,14 @@
         <v>1</v>
       </c>
       <c r="D134" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E134" s="24">
         <v>105500001</v>
       </c>
-      <c r="F134" s="24"/>
+      <c r="F134" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G134" s="1" t="s">
         <v>32</v>
       </c>
@@ -8031,12 +8045,14 @@
         <v>1</v>
       </c>
       <c r="D135" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E135" s="24">
         <v>105500001</v>
       </c>
-      <c r="F135" s="24"/>
+      <c r="F135" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G135" s="1" t="s">
         <v>35</v>
       </c>
@@ -8076,12 +8092,14 @@
         <v>1</v>
       </c>
       <c r="D136" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E136" s="24">
         <v>105500001</v>
       </c>
-      <c r="F136" s="24"/>
+      <c r="F136" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G136" s="1" t="s">
         <v>36</v>
       </c>
@@ -8121,7 +8139,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E137" s="24">
         <v>105501001</v>
@@ -8166,7 +8184,7 @@
         <v>1</v>
       </c>
       <c r="D138" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E138" s="24">
         <v>105501001</v>
@@ -8211,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E139" s="24">
         <v>105501001</v>
@@ -8256,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="D140" s="24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E140" s="24">
         <v>105502001</v>
@@ -8301,7 +8319,7 @@
         <v>1</v>
       </c>
       <c r="D141" s="24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E141" s="24">
         <v>105502001</v>
@@ -8346,7 +8364,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E142" s="24">
         <v>105502001</v>
@@ -8400,7 +8418,7 @@
         <v>78</v>
       </c>
       <c r="G143" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H143" s="18">
         <v>10</v>
@@ -8415,7 +8433,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M143" s="18">
         <v>0</v>
@@ -8447,7 +8465,7 @@
         <v>78</v>
       </c>
       <c r="G144" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H144" s="18">
         <v>11</v>
@@ -8462,7 +8480,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M144" s="18">
         <v>0</v>
@@ -8494,7 +8512,7 @@
         <v>78</v>
       </c>
       <c r="G145" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H145" s="18">
         <v>12</v>
@@ -8509,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M145" s="18">
         <v>0</v>
@@ -8541,7 +8559,7 @@
         <v>80</v>
       </c>
       <c r="G146" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H146" s="18">
         <v>10</v>
@@ -8556,7 +8574,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M146" s="18">
         <v>0</v>
@@ -8588,7 +8606,7 @@
         <v>80</v>
       </c>
       <c r="G147" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H147" s="18">
         <v>11</v>
@@ -8603,7 +8621,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M147" s="18">
         <v>0</v>
@@ -8635,7 +8653,7 @@
         <v>80</v>
       </c>
       <c r="G148" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H148" s="18">
         <v>12</v>
@@ -8650,7 +8668,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M148" s="18">
         <v>0</v>
@@ -8682,7 +8700,7 @@
         <v>82</v>
       </c>
       <c r="G149" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H149" s="18">
         <v>10</v>
@@ -8697,7 +8715,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M149" s="18">
         <v>0</v>
@@ -8729,7 +8747,7 @@
         <v>82</v>
       </c>
       <c r="G150" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H150" s="18">
         <v>11</v>
@@ -8744,7 +8762,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M150" s="18">
         <v>0</v>
@@ -8776,7 +8794,7 @@
         <v>82</v>
       </c>
       <c r="G151" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H151" s="18">
         <v>12</v>
@@ -8791,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M151" s="18">
         <v>0</v>
@@ -8823,7 +8841,7 @@
         <v>84</v>
       </c>
       <c r="G152" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H152" s="18">
         <v>10</v>
@@ -8838,7 +8856,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M152" s="18">
         <v>0</v>
@@ -8870,7 +8888,7 @@
         <v>84</v>
       </c>
       <c r="G153" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H153" s="18">
         <v>11</v>
@@ -8885,7 +8903,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M153" s="18">
         <v>0</v>
@@ -8917,7 +8935,7 @@
         <v>84</v>
       </c>
       <c r="G154" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H154" s="18">
         <v>12</v>
@@ -8932,7 +8950,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M154" s="18">
         <v>0</v>
@@ -8964,7 +8982,7 @@
         <v>86</v>
       </c>
       <c r="G155" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H155" s="18">
         <v>10</v>
@@ -8979,7 +8997,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M155" s="18">
         <v>0</v>
@@ -9011,7 +9029,7 @@
         <v>86</v>
       </c>
       <c r="G156" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H156" s="18">
         <v>11</v>
@@ -9026,7 +9044,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M156" s="18">
         <v>0</v>
@@ -9058,7 +9076,7 @@
         <v>86</v>
       </c>
       <c r="G157" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H157" s="18">
         <v>12</v>
@@ -9073,7 +9091,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M157" s="18">
         <v>0</v>
@@ -9105,7 +9123,7 @@
         <v>89</v>
       </c>
       <c r="G158" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H158" s="18">
         <v>10</v>
@@ -9120,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M158" s="18">
         <v>0</v>
@@ -9152,7 +9170,7 @@
         <v>89</v>
       </c>
       <c r="G159" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H159" s="18">
         <v>11</v>
@@ -9167,7 +9185,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M159" s="18">
         <v>0</v>
@@ -9199,7 +9217,7 @@
         <v>89</v>
       </c>
       <c r="G160" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H160" s="18">
         <v>12</v>
@@ -9214,7 +9232,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M160" s="18">
         <v>0</v>
@@ -9246,7 +9264,7 @@
         <v>91</v>
       </c>
       <c r="G161" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H161" s="18">
         <v>10</v>
@@ -9261,7 +9279,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M161" s="18">
         <v>0</v>
@@ -9293,7 +9311,7 @@
         <v>91</v>
       </c>
       <c r="G162" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H162" s="18">
         <v>11</v>
@@ -9308,7 +9326,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M162" s="18">
         <v>0</v>
@@ -9340,7 +9358,7 @@
         <v>91</v>
       </c>
       <c r="G163" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H163" s="18">
         <v>12</v>
@@ -9355,7 +9373,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M163" s="18">
         <v>0</v>
@@ -9387,7 +9405,7 @@
         <v>93</v>
       </c>
       <c r="G164" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H164" s="18">
         <v>10</v>
@@ -9402,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M164" s="18">
         <v>0</v>
@@ -9434,7 +9452,7 @@
         <v>93</v>
       </c>
       <c r="G165" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H165" s="18">
         <v>11</v>
@@ -9449,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M165" s="18">
         <v>0</v>
@@ -9481,7 +9499,7 @@
         <v>93</v>
       </c>
       <c r="G166" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H166" s="18">
         <v>12</v>
@@ -9496,7 +9514,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M166" s="18">
         <v>0</v>
@@ -9528,7 +9546,7 @@
         <v>95</v>
       </c>
       <c r="G167" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H167" s="18">
         <v>10</v>
@@ -9543,7 +9561,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M167" s="18">
         <v>0</v>
@@ -9575,7 +9593,7 @@
         <v>95</v>
       </c>
       <c r="G168" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H168" s="18">
         <v>11</v>
@@ -9590,7 +9608,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M168" s="18">
         <v>0</v>
@@ -9622,7 +9640,7 @@
         <v>95</v>
       </c>
       <c r="G169" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H169" s="18">
         <v>12</v>
@@ -9637,7 +9655,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M169" s="18">
         <v>0</v>
@@ -9669,7 +9687,7 @@
         <v>101</v>
       </c>
       <c r="G170" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H170" s="18">
         <v>10</v>
@@ -9684,7 +9702,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M170" s="18">
         <v>0</v>
@@ -9716,7 +9734,7 @@
         <v>101</v>
       </c>
       <c r="G171" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H171" s="18">
         <v>11</v>
@@ -9731,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M171" s="18">
         <v>0</v>
@@ -9763,7 +9781,7 @@
         <v>101</v>
       </c>
       <c r="G172" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H172" s="18">
         <v>12</v>
@@ -9778,7 +9796,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M172" s="18">
         <v>0</v>
@@ -9810,7 +9828,7 @@
         <v>104</v>
       </c>
       <c r="G173" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H173" s="18">
         <v>10</v>
@@ -9825,7 +9843,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M173" s="18">
         <v>0</v>
@@ -9858,7 +9876,7 @@
         <v>104</v>
       </c>
       <c r="G174" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H174" s="18">
         <v>11</v>
@@ -9873,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M174" s="18">
         <v>0</v>
@@ -9906,7 +9924,7 @@
         <v>104</v>
       </c>
       <c r="G175" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H175" s="18">
         <v>12</v>
@@ -9921,7 +9939,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M175" s="18">
         <v>0</v>
@@ -9954,7 +9972,7 @@
         <v>107</v>
       </c>
       <c r="G176" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H176" s="18">
         <v>10</v>
@@ -9969,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M176" s="18">
         <v>0</v>
@@ -10002,7 +10020,7 @@
         <v>107</v>
       </c>
       <c r="G177" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H177" s="18">
         <v>11</v>
@@ -10017,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M177" s="18">
         <v>0</v>
@@ -10050,7 +10068,7 @@
         <v>107</v>
       </c>
       <c r="G178" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H178" s="18">
         <v>12</v>
@@ -10065,7 +10083,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M178" s="18">
         <v>0</v>
@@ -10098,7 +10116,7 @@
         <v>109</v>
       </c>
       <c r="G179" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H179" s="18">
         <v>10</v>
@@ -10113,7 +10131,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M179" s="18">
         <v>0</v>
@@ -10146,7 +10164,7 @@
         <v>109</v>
       </c>
       <c r="G180" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H180" s="18">
         <v>11</v>
@@ -10161,7 +10179,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M180" s="18">
         <v>0</v>
@@ -10194,7 +10212,7 @@
         <v>109</v>
       </c>
       <c r="G181" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H181" s="18">
         <v>12</v>
@@ -10209,7 +10227,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M181" s="18">
         <v>0</v>
@@ -10243,7 +10261,7 @@
         <v>31</v>
       </c>
       <c r="G182" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H182" s="18">
         <v>10</v>
@@ -10258,7 +10276,7 @@
         <v>0</v>
       </c>
       <c r="L182" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M182" s="18">
         <v>0</v>
@@ -10292,7 +10310,7 @@
         <v>31</v>
       </c>
       <c r="G183" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H183" s="18">
         <v>11</v>
@@ -10307,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="L183" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M183" s="18">
         <v>0</v>
@@ -10341,7 +10359,7 @@
         <v>31</v>
       </c>
       <c r="G184" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H184" s="18">
         <v>12</v>
@@ -10356,7 +10374,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M184" s="18">
         <v>0</v>
@@ -10389,7 +10407,7 @@
         <v>38</v>
       </c>
       <c r="G185" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H185" s="18">
         <v>10</v>
@@ -10404,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="L185" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M185" s="18">
         <v>0</v>
@@ -10439,7 +10457,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G186" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H186" s="18">
         <v>11</v>
@@ -10454,7 +10472,7 @@
         <v>0</v>
       </c>
       <c r="L186" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M186" s="18">
         <v>0</v>
@@ -10489,7 +10507,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G187" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H187" s="18">
         <v>12</v>
@@ -10504,7 +10522,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M187" s="18">
         <v>0</v>
@@ -10537,7 +10555,7 @@
         <v>40</v>
       </c>
       <c r="G188" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H188" s="18">
         <v>10</v>
@@ -10552,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="L188" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M188" s="18">
         <v>0</v>
@@ -10587,7 +10605,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G189" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H189" s="18">
         <v>11</v>
@@ -10602,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="L189" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M189" s="18">
         <v>0</v>
@@ -10637,7 +10655,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G190" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H190" s="18">
         <v>12</v>
@@ -10652,7 +10670,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M190" s="18">
         <v>0</v>
@@ -10685,7 +10703,7 @@
         <v>42</v>
       </c>
       <c r="G191" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H191" s="18">
         <v>10</v>
@@ -10700,7 +10718,7 @@
         <v>0</v>
       </c>
       <c r="L191" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M191" s="18">
         <v>0</v>
@@ -10735,7 +10753,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G192" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H192" s="18">
         <v>11</v>
@@ -10750,7 +10768,7 @@
         <v>0</v>
       </c>
       <c r="L192" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M192" s="18">
         <v>0</v>
@@ -10785,7 +10803,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G193" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H193" s="18">
         <v>12</v>
@@ -10800,7 +10818,7 @@
         <v>0</v>
       </c>
       <c r="L193" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M193" s="18">
         <v>0</v>
@@ -10833,7 +10851,7 @@
         <v>44</v>
       </c>
       <c r="G194" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H194" s="18">
         <v>10</v>
@@ -10848,7 +10866,7 @@
         <v>0</v>
       </c>
       <c r="L194" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M194" s="18">
         <v>0</v>
@@ -10883,7 +10901,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G195" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H195" s="18">
         <v>11</v>
@@ -10898,7 +10916,7 @@
         <v>0</v>
       </c>
       <c r="L195" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M195" s="18">
         <v>0</v>
@@ -10933,7 +10951,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G196" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H196" s="18">
         <v>12</v>
@@ -10948,7 +10966,7 @@
         <v>0</v>
       </c>
       <c r="L196" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M196" s="18">
         <v>0</v>
@@ -10981,7 +10999,7 @@
         <v>46</v>
       </c>
       <c r="G197" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H197" s="18">
         <v>10</v>
@@ -10996,7 +11014,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M197" s="18">
         <v>0</v>
@@ -11030,7 +11048,7 @@
         <v>46</v>
       </c>
       <c r="G198" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H198" s="18">
         <v>11</v>
@@ -11045,7 +11063,7 @@
         <v>0</v>
       </c>
       <c r="L198" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M198" s="18">
         <v>0</v>
@@ -11079,7 +11097,7 @@
         <v>46</v>
       </c>
       <c r="G199" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H199" s="18">
         <v>12</v>
@@ -11094,7 +11112,7 @@
         <v>0</v>
       </c>
       <c r="L199" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M199" s="18">
         <v>0</v>
@@ -11127,7 +11145,7 @@
         <v>48</v>
       </c>
       <c r="G200" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H200" s="18">
         <v>10</v>
@@ -11142,7 +11160,7 @@
         <v>0</v>
       </c>
       <c r="L200" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M200" s="18">
         <v>0</v>
@@ -11175,7 +11193,7 @@
         <v>48</v>
       </c>
       <c r="G201" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H201" s="18">
         <v>11</v>
@@ -11190,7 +11208,7 @@
         <v>0</v>
       </c>
       <c r="L201" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M201" s="18">
         <v>0</v>
@@ -11223,7 +11241,7 @@
         <v>48</v>
       </c>
       <c r="G202" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H202" s="18">
         <v>12</v>
@@ -11238,7 +11256,7 @@
         <v>0</v>
       </c>
       <c r="L202" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M202" s="18">
         <v>0</v>
@@ -11271,7 +11289,7 @@
         <v>50</v>
       </c>
       <c r="G203" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H203" s="18">
         <v>10</v>
@@ -11286,7 +11304,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M203" s="18">
         <v>0</v>
@@ -11319,7 +11337,7 @@
         <v>50</v>
       </c>
       <c r="G204" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H204" s="18">
         <v>11</v>
@@ -11334,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M204" s="18">
         <v>0</v>
@@ -11367,7 +11385,7 @@
         <v>50</v>
       </c>
       <c r="G205" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H205" s="18">
         <v>12</v>
@@ -11382,7 +11400,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M205" s="18">
         <v>0</v>
@@ -11415,7 +11433,7 @@
         <v>52</v>
       </c>
       <c r="G206" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H206" s="18">
         <v>10</v>
@@ -11430,7 +11448,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M206" s="18">
         <v>0</v>
@@ -11463,7 +11481,7 @@
         <v>52</v>
       </c>
       <c r="G207" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H207" s="18">
         <v>11</v>
@@ -11478,7 +11496,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M207" s="18">
         <v>0</v>
@@ -11511,7 +11529,7 @@
         <v>52</v>
       </c>
       <c r="G208" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H208" s="18">
         <v>12</v>
@@ -11526,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="L208" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M208" s="18">
         <v>0</v>
@@ -11559,7 +11577,7 @@
         <v>54</v>
       </c>
       <c r="G209" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H209" s="18">
         <v>10</v>
@@ -11574,7 +11592,7 @@
         <v>0</v>
       </c>
       <c r="L209" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M209" s="18">
         <v>0</v>
@@ -11607,7 +11625,7 @@
         <v>54</v>
       </c>
       <c r="G210" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H210" s="18">
         <v>11</v>
@@ -11622,7 +11640,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M210" s="18">
         <v>0</v>
@@ -11655,7 +11673,7 @@
         <v>54</v>
       </c>
       <c r="G211" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H211" s="18">
         <v>12</v>
@@ -11670,7 +11688,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M211" s="18">
         <v>0</v>
@@ -11703,7 +11721,7 @@
         <v>56</v>
       </c>
       <c r="G212" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H212" s="18">
         <v>10</v>
@@ -11718,7 +11736,7 @@
         <v>0</v>
       </c>
       <c r="L212" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M212" s="18">
         <v>0</v>
@@ -11751,7 +11769,7 @@
         <v>56</v>
       </c>
       <c r="G213" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H213" s="18">
         <v>11</v>
@@ -11766,7 +11784,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M213" s="18">
         <v>0</v>
@@ -11799,7 +11817,7 @@
         <v>56</v>
       </c>
       <c r="G214" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H214" s="18">
         <v>12</v>
@@ -11814,7 +11832,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M214" s="18">
         <v>0</v>
@@ -11847,7 +11865,7 @@
         <v>58</v>
       </c>
       <c r="G215" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H215" s="18">
         <v>10</v>
@@ -11862,7 +11880,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M215" s="18">
         <v>0</v>
@@ -11895,7 +11913,7 @@
         <v>58</v>
       </c>
       <c r="G216" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H216" s="18">
         <v>11</v>
@@ -11910,7 +11928,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M216" s="18">
         <v>0</v>
@@ -11943,7 +11961,7 @@
         <v>58</v>
       </c>
       <c r="G217" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H217" s="18">
         <v>12</v>
@@ -11958,7 +11976,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M217" s="18">
         <v>0</v>
@@ -11991,7 +12009,7 @@
         <v>60</v>
       </c>
       <c r="G218" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H218" s="1">
         <v>10</v>
@@ -12006,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="L218" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M218" s="18">
         <v>0</v>
@@ -12039,7 +12057,7 @@
         <v>60</v>
       </c>
       <c r="G219" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H219" s="1">
         <v>11</v>
@@ -12054,7 +12072,7 @@
         <v>0</v>
       </c>
       <c r="L219" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M219" s="18">
         <v>0</v>
@@ -12087,7 +12105,7 @@
         <v>60</v>
       </c>
       <c r="G220" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H220" s="1">
         <v>12</v>
@@ -12102,7 +12120,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M220" s="18">
         <v>0</v>
@@ -12135,7 +12153,7 @@
         <v>62</v>
       </c>
       <c r="G221" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H221" s="1">
         <v>10</v>
@@ -12150,7 +12168,7 @@
         <v>0</v>
       </c>
       <c r="L221" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M221" s="18">
         <v>0</v>
@@ -12183,7 +12201,7 @@
         <v>62</v>
       </c>
       <c r="G222" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H222" s="1">
         <v>11</v>
@@ -12198,7 +12216,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M222" s="18">
         <v>0</v>
@@ -12231,7 +12249,7 @@
         <v>62</v>
       </c>
       <c r="G223" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H223" s="1">
         <v>12</v>
@@ -12246,7 +12264,7 @@
         <v>0</v>
       </c>
       <c r="L223" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M223" s="18">
         <v>0</v>
@@ -12279,7 +12297,7 @@
         <v>64</v>
       </c>
       <c r="G224" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H224" s="1">
         <v>10</v>
@@ -12294,7 +12312,7 @@
         <v>0</v>
       </c>
       <c r="L224" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M224" s="18">
         <v>0</v>
@@ -12327,7 +12345,7 @@
         <v>64</v>
       </c>
       <c r="G225" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H225" s="1">
         <v>11</v>
@@ -12342,7 +12360,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M225" s="18">
         <v>0</v>
@@ -12375,7 +12393,7 @@
         <v>64</v>
       </c>
       <c r="G226" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H226" s="1">
         <v>12</v>
@@ -12390,7 +12408,7 @@
         <v>0</v>
       </c>
       <c r="L226" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M226" s="18">
         <v>0</v>
@@ -12423,7 +12441,7 @@
         <v>66</v>
       </c>
       <c r="G227" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H227" s="1">
         <v>10</v>
@@ -12438,7 +12456,7 @@
         <v>0</v>
       </c>
       <c r="L227" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M227" s="18">
         <v>0</v>
@@ -12471,7 +12489,7 @@
         <v>66</v>
       </c>
       <c r="G228" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H228" s="1">
         <v>11</v>
@@ -12486,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M228" s="18">
         <v>0</v>
@@ -12519,7 +12537,7 @@
         <v>66</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H229" s="1">
         <v>12</v>
@@ -12534,7 +12552,7 @@
         <v>0</v>
       </c>
       <c r="L229" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M229" s="18">
         <v>0</v>
@@ -12567,7 +12585,7 @@
         <v>68</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H230" s="1">
         <v>10</v>
@@ -12582,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="L230" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M230" s="18">
         <v>0</v>
@@ -12615,7 +12633,7 @@
         <v>68</v>
       </c>
       <c r="G231" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H231" s="1">
         <v>11</v>
@@ -12630,7 +12648,7 @@
         <v>0</v>
       </c>
       <c r="L231" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M231" s="18">
         <v>0</v>
@@ -12663,7 +12681,7 @@
         <v>68</v>
       </c>
       <c r="G232" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H232" s="1">
         <v>12</v>
@@ -12678,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="L232" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M232" s="18">
         <v>0</v>
@@ -12711,7 +12729,7 @@
         <v>70</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H233" s="1">
         <v>10</v>
@@ -12726,7 +12744,7 @@
         <v>0</v>
       </c>
       <c r="L233" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M233" s="18">
         <v>0</v>
@@ -12759,7 +12777,7 @@
         <v>70</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H234" s="1">
         <v>11</v>
@@ -12774,7 +12792,7 @@
         <v>0</v>
       </c>
       <c r="L234" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M234" s="18">
         <v>0</v>
@@ -12807,7 +12825,7 @@
         <v>70</v>
       </c>
       <c r="G235" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H235" s="1">
         <v>12</v>
@@ -12822,7 +12840,7 @@
         <v>0</v>
       </c>
       <c r="L235" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M235" s="18">
         <v>0</v>
@@ -12854,7 +12872,7 @@
         <v>72</v>
       </c>
       <c r="G236" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H236" s="1">
         <v>10</v>
@@ -12869,7 +12887,7 @@
         <v>0</v>
       </c>
       <c r="L236" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M236" s="18">
         <v>0</v>
@@ -12901,7 +12919,7 @@
         <v>72</v>
       </c>
       <c r="G237" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H237" s="1">
         <v>11</v>
@@ -12916,7 +12934,7 @@
         <v>0</v>
       </c>
       <c r="L237" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M237" s="18">
         <v>0</v>
@@ -12948,7 +12966,7 @@
         <v>72</v>
       </c>
       <c r="G238" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H238" s="1">
         <v>12</v>
@@ -12963,7 +12981,7 @@
         <v>0</v>
       </c>
       <c r="L238" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M238" s="18">
         <v>0</v>
@@ -12995,7 +13013,7 @@
         <v>74</v>
       </c>
       <c r="G239" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H239" s="1">
         <v>10</v>
@@ -13010,7 +13028,7 @@
         <v>0</v>
       </c>
       <c r="L239" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M239" s="18">
         <v>0</v>
@@ -13042,7 +13060,7 @@
         <v>74</v>
       </c>
       <c r="G240" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H240" s="1">
         <v>11</v>
@@ -13057,7 +13075,7 @@
         <v>0</v>
       </c>
       <c r="L240" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M240" s="18">
         <v>0</v>
@@ -13089,7 +13107,7 @@
         <v>74</v>
       </c>
       <c r="G241" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H241" s="1">
         <v>12</v>
@@ -13104,7 +13122,7 @@
         <v>0</v>
       </c>
       <c r="L241" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M241" s="18">
         <v>0</v>
@@ -13136,7 +13154,7 @@
         <v>76</v>
       </c>
       <c r="G242" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H242" s="1">
         <v>10</v>
@@ -13151,7 +13169,7 @@
         <v>0</v>
       </c>
       <c r="L242" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M242" s="18">
         <v>0</v>
@@ -13184,7 +13202,7 @@
         <v>76</v>
       </c>
       <c r="G243" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H243" s="1">
         <v>11</v>
@@ -13199,7 +13217,7 @@
         <v>0</v>
       </c>
       <c r="L243" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M243" s="18">
         <v>0</v>
@@ -13232,7 +13250,7 @@
         <v>76</v>
       </c>
       <c r="G244" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H244" s="1">
         <v>12</v>
@@ -13247,7 +13265,7 @@
         <v>0</v>
       </c>
       <c r="L244" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M244" s="18">
         <v>0</v>
@@ -13280,7 +13298,7 @@
         <v>116</v>
       </c>
       <c r="G245" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H245" s="1">
         <v>10</v>
@@ -13295,7 +13313,7 @@
         <v>0</v>
       </c>
       <c r="L245" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M245" s="18">
         <v>0</v>
@@ -13327,7 +13345,7 @@
         <v>116</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H246" s="1">
         <v>11</v>
@@ -13342,7 +13360,7 @@
         <v>0</v>
       </c>
       <c r="L246" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M246" s="18">
         <v>0</v>
@@ -13374,7 +13392,7 @@
         <v>116</v>
       </c>
       <c r="G247" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H247" s="1">
         <v>12</v>
@@ -13389,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="L247" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M247" s="18">
         <v>0</v>
@@ -13421,7 +13439,7 @@
         <v>118</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H248" s="1">
         <v>10</v>
@@ -13436,7 +13454,7 @@
         <v>0</v>
       </c>
       <c r="L248" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M248" s="18">
         <v>0</v>
@@ -13468,7 +13486,7 @@
         <v>118</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H249" s="1">
         <v>11</v>
@@ -13483,7 +13501,7 @@
         <v>0</v>
       </c>
       <c r="L249" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M249" s="18">
         <v>0</v>
@@ -13515,7 +13533,7 @@
         <v>118</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H250" s="1">
         <v>12</v>
@@ -13530,7 +13548,7 @@
         <v>0</v>
       </c>
       <c r="L250" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M250" s="18">
         <v>0</v>
@@ -13562,7 +13580,7 @@
         <v>120</v>
       </c>
       <c r="G251" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H251" s="1">
         <v>10</v>
@@ -13577,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="L251" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M251" s="18">
         <v>0</v>
@@ -13609,7 +13627,7 @@
         <v>120</v>
       </c>
       <c r="G252" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H252" s="1">
         <v>11</v>
@@ -13624,7 +13642,7 @@
         <v>0</v>
       </c>
       <c r="L252" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M252" s="18">
         <v>0</v>
@@ -13656,7 +13674,7 @@
         <v>120</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H253" s="1">
         <v>12</v>
@@ -13671,7 +13689,7 @@
         <v>0</v>
       </c>
       <c r="L253" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M253" s="18">
         <v>0</v>
@@ -13701,7 +13719,7 @@
       </c>
       <c r="F254" s="5"/>
       <c r="G254" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H254" s="1">
         <v>10</v>
@@ -13716,7 +13734,7 @@
         <v>0</v>
       </c>
       <c r="L254" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M254" s="18">
         <v>0</v>
@@ -13746,7 +13764,7 @@
       </c>
       <c r="F255" s="5"/>
       <c r="G255" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H255" s="1">
         <v>11</v>
@@ -13761,7 +13779,7 @@
         <v>0</v>
       </c>
       <c r="L255" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M255" s="18">
         <v>0</v>
@@ -13791,7 +13809,7 @@
       </c>
       <c r="F256" s="5"/>
       <c r="G256" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H256" s="1">
         <v>12</v>
@@ -13806,7 +13824,7 @@
         <v>0</v>
       </c>
       <c r="L256" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M256" s="18">
         <v>0</v>
@@ -13836,7 +13854,7 @@
       </c>
       <c r="F257" s="5"/>
       <c r="G257" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H257" s="1">
         <v>10</v>
@@ -13851,7 +13869,7 @@
         <v>0</v>
       </c>
       <c r="L257" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M257" s="18">
         <v>0</v>
@@ -13881,7 +13899,7 @@
       </c>
       <c r="F258" s="5"/>
       <c r="G258" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H258" s="1">
         <v>11</v>
@@ -13896,7 +13914,7 @@
         <v>0</v>
       </c>
       <c r="L258" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M258" s="18">
         <v>0</v>
@@ -13926,7 +13944,7 @@
       </c>
       <c r="F259" s="5"/>
       <c r="G259" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H259" s="1">
         <v>12</v>
@@ -13941,7 +13959,7 @@
         <v>0</v>
       </c>
       <c r="L259" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M259" s="18">
         <v>0</v>
@@ -13971,7 +13989,7 @@
       </c>
       <c r="F260" s="5"/>
       <c r="G260" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H260" s="1">
         <v>10</v>
@@ -13986,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="L260" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M260" s="18">
         <v>0</v>
@@ -14016,7 +14034,7 @@
       </c>
       <c r="F261" s="5"/>
       <c r="G261" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H261" s="1">
         <v>11</v>
@@ -14031,7 +14049,7 @@
         <v>0</v>
       </c>
       <c r="L261" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M261" s="18">
         <v>0</v>
@@ -14061,7 +14079,7 @@
       </c>
       <c r="F262" s="5"/>
       <c r="G262" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H262" s="1">
         <v>12</v>
@@ -14076,7 +14094,7 @@
         <v>0</v>
       </c>
       <c r="L262" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M262" s="18">
         <v>0</v>
@@ -14104,9 +14122,11 @@
       <c r="E263" s="5">
         <v>105100001</v>
       </c>
-      <c r="F263" s="5"/>
+      <c r="F263" s="22" t="s">
+        <v>125</v>
+      </c>
       <c r="G263" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H263" s="1">
         <v>10</v>
@@ -14121,7 +14141,7 @@
         <v>0</v>
       </c>
       <c r="L263" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M263" s="18">
         <v>0</v>
@@ -14149,9 +14169,11 @@
       <c r="E264" s="5">
         <v>105100001</v>
       </c>
-      <c r="F264" s="5"/>
+      <c r="F264" s="22" t="s">
+        <v>125</v>
+      </c>
       <c r="G264" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H264" s="1">
         <v>11</v>
@@ -14166,7 +14188,7 @@
         <v>0</v>
       </c>
       <c r="L264" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M264" s="18">
         <v>0</v>
@@ -14194,9 +14216,11 @@
       <c r="E265" s="5">
         <v>105100001</v>
       </c>
-      <c r="F265" s="5"/>
+      <c r="F265" s="22" t="s">
+        <v>125</v>
+      </c>
       <c r="G265" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H265" s="1">
         <v>12</v>
@@ -14211,7 +14235,7 @@
         <v>0</v>
       </c>
       <c r="L265" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M265" s="18">
         <v>0</v>
@@ -14234,14 +14258,16 @@
         <v>1</v>
       </c>
       <c r="D266" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E266" s="2">
         <v>105500001</v>
       </c>
-      <c r="F266" s="2"/>
+      <c r="F266" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G266" s="28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H266" s="2">
         <v>10</v>
@@ -14256,7 +14282,7 @@
         <v>0</v>
       </c>
       <c r="L266" s="29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M266" s="28">
         <v>0</v>
@@ -14283,14 +14309,16 @@
         <v>1</v>
       </c>
       <c r="D267" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E267" s="2">
         <v>105500001</v>
       </c>
-      <c r="F267" s="2"/>
+      <c r="F267" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G267" s="28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H267" s="2">
         <v>11</v>
@@ -14305,7 +14333,7 @@
         <v>0</v>
       </c>
       <c r="L267" s="29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M267" s="28">
         <v>0</v>
@@ -14332,14 +14360,16 @@
         <v>1</v>
       </c>
       <c r="D268" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E268" s="2">
         <v>105500001</v>
       </c>
-      <c r="F268" s="2"/>
+      <c r="F268" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G268" s="28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H268" s="2">
         <v>12</v>
@@ -14354,7 +14384,7 @@
         <v>0</v>
       </c>
       <c r="L268" s="29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M268" s="28">
         <v>0</v>
@@ -14381,14 +14411,14 @@
         <v>1</v>
       </c>
       <c r="D269" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E269" s="2">
         <v>105501001</v>
       </c>
       <c r="F269" s="2"/>
       <c r="G269" s="28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H269" s="2">
         <v>10</v>
@@ -14403,7 +14433,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M269" s="28">
         <v>0</v>
@@ -14430,14 +14460,14 @@
         <v>1</v>
       </c>
       <c r="D270" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E270" s="2">
         <v>105501001</v>
       </c>
       <c r="F270" s="2"/>
       <c r="G270" s="28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H270" s="2">
         <v>11</v>
@@ -14452,7 +14482,7 @@
         <v>0</v>
       </c>
       <c r="L270" s="29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M270" s="28">
         <v>0</v>
@@ -14479,14 +14509,14 @@
         <v>1</v>
       </c>
       <c r="D271" s="24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E271" s="2">
         <v>105501001</v>
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H271" s="2">
         <v>12</v>
@@ -14501,7 +14531,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M271" s="28">
         <v>0</v>
@@ -14528,14 +14558,14 @@
         <v>1</v>
       </c>
       <c r="D272" s="24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E272" s="2">
         <v>105502001</v>
       </c>
       <c r="F272" s="2"/>
       <c r="G272" s="28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H272" s="2">
         <v>10</v>
@@ -14550,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M272" s="28">
         <v>0</v>
@@ -14577,14 +14607,14 @@
         <v>1</v>
       </c>
       <c r="D273" s="24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E273" s="2">
         <v>105502001</v>
       </c>
       <c r="F273" s="2"/>
       <c r="G273" s="28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H273" s="2">
         <v>11</v>
@@ -14599,7 +14629,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M273" s="28">
         <v>0</v>
@@ -14626,14 +14656,14 @@
         <v>1</v>
       </c>
       <c r="D274" s="24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E274" s="2">
         <v>105502001</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H274" s="2">
         <v>12</v>
@@ -14648,7 +14678,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="29" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M274" s="28">
         <v>0</v>
@@ -14684,7 +14714,7 @@
         <v>31</v>
       </c>
       <c r="G275" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H275" s="1">
         <v>21</v>
@@ -14732,7 +14762,7 @@
         <v>31</v>
       </c>
       <c r="G276" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H276" s="1">
         <v>22</v>
@@ -14780,7 +14810,7 @@
         <v>31</v>
       </c>
       <c r="G277" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H277" s="1">
         <v>23</v>
@@ -14828,7 +14858,7 @@
         <v>38</v>
       </c>
       <c r="G278" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H278" s="1">
         <v>21</v>
@@ -14876,7 +14906,7 @@
         <v>38</v>
       </c>
       <c r="G279" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H279" s="1">
         <v>22</v>
@@ -14924,7 +14954,7 @@
         <v>38</v>
       </c>
       <c r="G280" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H280" s="1">
         <v>23</v>
@@ -14972,7 +15002,7 @@
         <v>40</v>
       </c>
       <c r="G281" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H281" s="1">
         <v>21</v>
@@ -15020,7 +15050,7 @@
         <v>40</v>
       </c>
       <c r="G282" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H282" s="1">
         <v>22</v>
@@ -15068,7 +15098,7 @@
         <v>40</v>
       </c>
       <c r="G283" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H283" s="1">
         <v>23</v>
@@ -15116,7 +15146,7 @@
         <v>42</v>
       </c>
       <c r="G284" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H284" s="1">
         <v>21</v>
@@ -15164,7 +15194,7 @@
         <v>42</v>
       </c>
       <c r="G285" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H285" s="1">
         <v>22</v>
@@ -15212,7 +15242,7 @@
         <v>42</v>
       </c>
       <c r="G286" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H286" s="1">
         <v>23</v>
@@ -15260,7 +15290,7 @@
         <v>44</v>
       </c>
       <c r="G287" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H287" s="1">
         <v>21</v>
@@ -15308,7 +15338,7 @@
         <v>44</v>
       </c>
       <c r="G288" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H288" s="1">
         <v>22</v>
@@ -15356,7 +15386,7 @@
         <v>44</v>
       </c>
       <c r="G289" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H289" s="1">
         <v>23</v>
@@ -15404,7 +15434,7 @@
         <v>46</v>
       </c>
       <c r="G290" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H290" s="1">
         <v>21</v>
@@ -15452,7 +15482,7 @@
         <v>46</v>
       </c>
       <c r="G291" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H291" s="1">
         <v>22</v>
@@ -15500,7 +15530,7 @@
         <v>46</v>
       </c>
       <c r="G292" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H292" s="1">
         <v>23</v>
@@ -15548,7 +15578,7 @@
         <v>48</v>
       </c>
       <c r="G293" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H293" s="1">
         <v>21</v>
@@ -15596,7 +15626,7 @@
         <v>48</v>
       </c>
       <c r="G294" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H294" s="1">
         <v>22</v>
@@ -15644,7 +15674,7 @@
         <v>48</v>
       </c>
       <c r="G295" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H295" s="1">
         <v>23</v>
@@ -15692,7 +15722,7 @@
         <v>50</v>
       </c>
       <c r="G296" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H296" s="1">
         <v>21</v>
@@ -15740,7 +15770,7 @@
         <v>50</v>
       </c>
       <c r="G297" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H297" s="1">
         <v>22</v>
@@ -15788,7 +15818,7 @@
         <v>50</v>
       </c>
       <c r="G298" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H298" s="1">
         <v>23</v>
@@ -15836,7 +15866,7 @@
         <v>52</v>
       </c>
       <c r="G299" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H299" s="1">
         <v>21</v>
@@ -15884,7 +15914,7 @@
         <v>52</v>
       </c>
       <c r="G300" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H300" s="1">
         <v>22</v>
@@ -15932,7 +15962,7 @@
         <v>52</v>
       </c>
       <c r="G301" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H301" s="1">
         <v>23</v>
@@ -15981,7 +16011,7 @@
         <v>54</v>
       </c>
       <c r="G302" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H302" s="1">
         <v>21</v>
@@ -16030,7 +16060,7 @@
         <v>54</v>
       </c>
       <c r="G303" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H303" s="1">
         <v>22</v>
@@ -16079,7 +16109,7 @@
         <v>54</v>
       </c>
       <c r="G304" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H304" s="1">
         <v>23</v>
@@ -16128,7 +16158,7 @@
         <v>56</v>
       </c>
       <c r="G305" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H305" s="1">
         <v>21</v>
@@ -16177,7 +16207,7 @@
         <v>56</v>
       </c>
       <c r="G306" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H306" s="1">
         <v>22</v>
@@ -16226,7 +16256,7 @@
         <v>56</v>
       </c>
       <c r="G307" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H307" s="1">
         <v>23</v>
@@ -16275,7 +16305,7 @@
         <v>58</v>
       </c>
       <c r="G308" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H308" s="1">
         <v>21</v>
@@ -16324,7 +16354,7 @@
         <v>58</v>
       </c>
       <c r="G309" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H309" s="1">
         <v>22</v>
@@ -16373,7 +16403,7 @@
         <v>58</v>
       </c>
       <c r="G310" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H310" s="1">
         <v>23</v>
@@ -16421,7 +16451,7 @@
         <v>60</v>
       </c>
       <c r="G311" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H311" s="1">
         <v>21</v>
@@ -16469,7 +16499,7 @@
         <v>60</v>
       </c>
       <c r="G312" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H312" s="1">
         <v>22</v>
@@ -16517,7 +16547,7 @@
         <v>60</v>
       </c>
       <c r="G313" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H313" s="1">
         <v>23</v>
@@ -16566,7 +16596,7 @@
         <v>62</v>
       </c>
       <c r="G314" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H314" s="1">
         <v>21</v>
@@ -16615,7 +16645,7 @@
         <v>62</v>
       </c>
       <c r="G315" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H315" s="1">
         <v>22</v>
@@ -16664,7 +16694,7 @@
         <v>62</v>
       </c>
       <c r="G316" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H316" s="1">
         <v>23</v>
@@ -16712,7 +16742,7 @@
         <v>64</v>
       </c>
       <c r="G317" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H317" s="1">
         <v>21</v>
@@ -16760,7 +16790,7 @@
         <v>64</v>
       </c>
       <c r="G318" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H318" s="1">
         <v>22</v>
@@ -16808,7 +16838,7 @@
         <v>64</v>
       </c>
       <c r="G319" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H319" s="1">
         <v>23</v>
@@ -16856,7 +16886,7 @@
         <v>66</v>
       </c>
       <c r="G320" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H320" s="1">
         <v>21</v>
@@ -16904,7 +16934,7 @@
         <v>66</v>
       </c>
       <c r="G321" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H321" s="1">
         <v>22</v>
@@ -16952,7 +16982,7 @@
         <v>66</v>
       </c>
       <c r="G322" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H322" s="1">
         <v>23</v>
@@ -17001,7 +17031,7 @@
         <v>68</v>
       </c>
       <c r="G323" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H323" s="1">
         <v>21</v>
@@ -17050,7 +17080,7 @@
         <v>68</v>
       </c>
       <c r="G324" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H324" s="1">
         <v>22</v>
@@ -17099,7 +17129,7 @@
         <v>68</v>
       </c>
       <c r="G325" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H325" s="1">
         <v>23</v>
@@ -17147,7 +17177,7 @@
         <v>72</v>
       </c>
       <c r="G326" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H326" s="1">
         <v>21</v>
@@ -17195,7 +17225,7 @@
         <v>72</v>
       </c>
       <c r="G327" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H327" s="1">
         <v>22</v>
@@ -17243,7 +17273,7 @@
         <v>72</v>
       </c>
       <c r="G328" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H328" s="1">
         <v>23</v>
@@ -17291,7 +17321,7 @@
         <v>74</v>
       </c>
       <c r="G329" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H329" s="1">
         <v>21</v>
@@ -17339,7 +17369,7 @@
         <v>74</v>
       </c>
       <c r="G330" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H330" s="1">
         <v>22</v>
@@ -17387,7 +17417,7 @@
         <v>74</v>
       </c>
       <c r="G331" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H331" s="1">
         <v>23</v>
@@ -17435,7 +17465,7 @@
         <v>76</v>
       </c>
       <c r="G332" s="30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H332" s="1">
         <v>21</v>
@@ -17483,7 +17513,7 @@
         <v>76</v>
       </c>
       <c r="G333" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H333" s="1">
         <v>22</v>
@@ -17531,7 +17561,7 @@
         <v>76</v>
       </c>
       <c r="G334" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H334" s="1">
         <v>23</v>
@@ -19035,13 +19065,13 @@
         <v>3</v>
       </c>
       <c r="D365" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E365" s="14">
         <v>300402001</v>
       </c>
       <c r="F365" s="22" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>32</v>
@@ -19084,13 +19114,13 @@
         <v>3</v>
       </c>
       <c r="D366" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E366" s="14">
         <v>300402001</v>
       </c>
       <c r="F366" s="22" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>35</v>
@@ -19133,13 +19163,13 @@
         <v>3</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E367" s="14">
         <v>300402001</v>
       </c>
       <c r="F367" s="22" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>36</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="148">
   <si>
     <t>sid</t>
   </si>
@@ -515,7 +515,13 @@
     <t>狼月</t>
   </si>
   <si>
+    <t>Wolfmoon</t>
+  </si>
+  <si>
     <t>麻将胡了2</t>
+  </si>
+  <si>
+    <t>MahjongWays2</t>
   </si>
   <si>
     <t>糖果派对</t>
@@ -7484,7 +7490,9 @@
       <c r="E122" s="5">
         <v>101500001</v>
       </c>
-      <c r="F122" s="5"/>
+      <c r="F122" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G122" s="1" t="s">
         <v>32</v>
       </c>
@@ -7529,7 +7537,9 @@
       <c r="E123" s="5">
         <v>101500001</v>
       </c>
-      <c r="F123" s="5"/>
+      <c r="F123" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G123" s="1" t="s">
         <v>35</v>
       </c>
@@ -7574,7 +7584,9 @@
       <c r="E124" s="5">
         <v>101500001</v>
       </c>
-      <c r="F124" s="5"/>
+      <c r="F124" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G124" s="1" t="s">
         <v>36</v>
       </c>
@@ -7614,12 +7626,14 @@
         <v>1</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E125" s="5">
         <v>105300001</v>
       </c>
-      <c r="F125" s="5"/>
+      <c r="F125" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G125" s="1" t="s">
         <v>32</v>
       </c>
@@ -7659,12 +7673,14 @@
         <v>1</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E126" s="5">
         <v>105300001</v>
       </c>
-      <c r="F126" s="5"/>
+      <c r="F126" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G126" s="1" t="s">
         <v>35</v>
       </c>
@@ -7704,12 +7720,14 @@
         <v>1</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E127" s="5">
         <v>105300001</v>
       </c>
-      <c r="F127" s="5"/>
+      <c r="F127" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G127" s="1" t="s">
         <v>36</v>
       </c>
@@ -7749,13 +7767,13 @@
         <v>1</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E128" s="5">
         <v>105100001</v>
       </c>
       <c r="F128" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>32</v>
@@ -7796,13 +7814,13 @@
         <v>1</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E129" s="5">
         <v>105100001</v>
       </c>
       <c r="F129" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>35</v>
@@ -7843,13 +7861,13 @@
         <v>1</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E130" s="5">
         <v>105100001</v>
       </c>
       <c r="F130" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>36</v>
@@ -7890,13 +7908,13 @@
         <v>1</v>
       </c>
       <c r="D131" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E131" s="24">
         <v>105500001</v>
       </c>
       <c r="F131" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>32</v>
@@ -7937,13 +7955,13 @@
         <v>1</v>
       </c>
       <c r="D132" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E132" s="24">
         <v>105500001</v>
       </c>
       <c r="F132" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>35</v>
@@ -7984,13 +8002,13 @@
         <v>1</v>
       </c>
       <c r="D133" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E133" s="24">
         <v>105500001</v>
       </c>
       <c r="F133" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>36</v>
@@ -8031,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E134" s="24">
         <v>105501001</v>
@@ -8076,7 +8094,7 @@
         <v>1</v>
       </c>
       <c r="D135" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E135" s="24">
         <v>105501001</v>
@@ -8121,7 +8139,7 @@
         <v>1</v>
       </c>
       <c r="D136" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E136" s="24">
         <v>105501001</v>
@@ -8166,7 +8184,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E137" s="24">
         <v>105502001</v>
@@ -8211,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="D138" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E138" s="24">
         <v>105502001</v>
@@ -8256,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E139" s="24">
         <v>105502001</v>
@@ -8301,13 +8319,13 @@
         <v>4</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E140" s="26">
         <v>400400001</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>32</v>
@@ -8325,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M140" s="33" t="s">
         <v>34</v>
@@ -8348,13 +8366,13 @@
         <v>4</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E141" s="26">
         <v>400200001</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>32</v>
@@ -8372,7 +8390,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M141" s="33" t="s">
         <v>34</v>
@@ -8395,13 +8413,13 @@
         <v>4</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E142" s="26">
         <v>400500001</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>32</v>
@@ -8419,7 +8437,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M142" s="33" t="s">
         <v>34</v>
@@ -8442,13 +8460,13 @@
         <v>4</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E143" s="26">
         <v>400700001</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>32</v>
@@ -8466,7 +8484,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M143" s="33" t="s">
         <v>34</v>
@@ -8498,7 +8516,7 @@
         <v>78</v>
       </c>
       <c r="G144" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H144" s="18">
         <v>10</v>
@@ -8513,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M144" s="18">
         <v>0</v>
@@ -8545,7 +8563,7 @@
         <v>78</v>
       </c>
       <c r="G145" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H145" s="18">
         <v>11</v>
@@ -8560,7 +8578,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M145" s="18">
         <v>0</v>
@@ -8592,7 +8610,7 @@
         <v>78</v>
       </c>
       <c r="G146" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H146" s="18">
         <v>12</v>
@@ -8607,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M146" s="18">
         <v>0</v>
@@ -8639,7 +8657,7 @@
         <v>80</v>
       </c>
       <c r="G147" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H147" s="18">
         <v>10</v>
@@ -8654,7 +8672,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M147" s="18">
         <v>0</v>
@@ -8686,7 +8704,7 @@
         <v>80</v>
       </c>
       <c r="G148" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H148" s="18">
         <v>11</v>
@@ -8701,7 +8719,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M148" s="18">
         <v>0</v>
@@ -8733,7 +8751,7 @@
         <v>80</v>
       </c>
       <c r="G149" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H149" s="18">
         <v>12</v>
@@ -8748,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M149" s="18">
         <v>0</v>
@@ -8780,7 +8798,7 @@
         <v>82</v>
       </c>
       <c r="G150" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H150" s="18">
         <v>10</v>
@@ -8795,7 +8813,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M150" s="18">
         <v>0</v>
@@ -8827,7 +8845,7 @@
         <v>82</v>
       </c>
       <c r="G151" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H151" s="18">
         <v>11</v>
@@ -8842,7 +8860,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M151" s="18">
         <v>0</v>
@@ -8874,7 +8892,7 @@
         <v>82</v>
       </c>
       <c r="G152" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H152" s="18">
         <v>12</v>
@@ -8889,7 +8907,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M152" s="18">
         <v>0</v>
@@ -8921,7 +8939,7 @@
         <v>84</v>
       </c>
       <c r="G153" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H153" s="18">
         <v>10</v>
@@ -8936,7 +8954,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M153" s="18">
         <v>0</v>
@@ -8968,7 +8986,7 @@
         <v>84</v>
       </c>
       <c r="G154" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H154" s="18">
         <v>11</v>
@@ -8983,7 +9001,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M154" s="18">
         <v>0</v>
@@ -9015,7 +9033,7 @@
         <v>84</v>
       </c>
       <c r="G155" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H155" s="18">
         <v>12</v>
@@ -9030,7 +9048,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M155" s="18">
         <v>0</v>
@@ -9062,7 +9080,7 @@
         <v>86</v>
       </c>
       <c r="G156" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H156" s="18">
         <v>10</v>
@@ -9077,7 +9095,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M156" s="18">
         <v>0</v>
@@ -9109,7 +9127,7 @@
         <v>86</v>
       </c>
       <c r="G157" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H157" s="18">
         <v>11</v>
@@ -9124,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M157" s="18">
         <v>0</v>
@@ -9156,7 +9174,7 @@
         <v>86</v>
       </c>
       <c r="G158" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H158" s="18">
         <v>12</v>
@@ -9171,7 +9189,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M158" s="18">
         <v>0</v>
@@ -9203,7 +9221,7 @@
         <v>89</v>
       </c>
       <c r="G159" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H159" s="18">
         <v>10</v>
@@ -9218,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M159" s="18">
         <v>0</v>
@@ -9250,7 +9268,7 @@
         <v>89</v>
       </c>
       <c r="G160" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H160" s="18">
         <v>11</v>
@@ -9265,7 +9283,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M160" s="18">
         <v>0</v>
@@ -9297,7 +9315,7 @@
         <v>89</v>
       </c>
       <c r="G161" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H161" s="18">
         <v>12</v>
@@ -9312,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M161" s="18">
         <v>0</v>
@@ -9344,7 +9362,7 @@
         <v>91</v>
       </c>
       <c r="G162" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H162" s="18">
         <v>10</v>
@@ -9359,7 +9377,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M162" s="18">
         <v>0</v>
@@ -9391,7 +9409,7 @@
         <v>91</v>
       </c>
       <c r="G163" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H163" s="18">
         <v>11</v>
@@ -9406,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M163" s="18">
         <v>0</v>
@@ -9438,7 +9456,7 @@
         <v>91</v>
       </c>
       <c r="G164" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H164" s="18">
         <v>12</v>
@@ -9453,7 +9471,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M164" s="18">
         <v>0</v>
@@ -9485,7 +9503,7 @@
         <v>93</v>
       </c>
       <c r="G165" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H165" s="18">
         <v>10</v>
@@ -9500,7 +9518,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M165" s="18">
         <v>0</v>
@@ -9532,7 +9550,7 @@
         <v>93</v>
       </c>
       <c r="G166" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H166" s="18">
         <v>11</v>
@@ -9547,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M166" s="18">
         <v>0</v>
@@ -9579,7 +9597,7 @@
         <v>93</v>
       </c>
       <c r="G167" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H167" s="18">
         <v>12</v>
@@ -9594,7 +9612,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M167" s="18">
         <v>0</v>
@@ -9626,7 +9644,7 @@
         <v>95</v>
       </c>
       <c r="G168" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H168" s="18">
         <v>10</v>
@@ -9641,7 +9659,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M168" s="18">
         <v>0</v>
@@ -9673,7 +9691,7 @@
         <v>95</v>
       </c>
       <c r="G169" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H169" s="18">
         <v>11</v>
@@ -9688,7 +9706,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M169" s="18">
         <v>0</v>
@@ -9720,7 +9738,7 @@
         <v>95</v>
       </c>
       <c r="G170" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H170" s="18">
         <v>12</v>
@@ -9735,7 +9753,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M170" s="18">
         <v>0</v>
@@ -9767,7 +9785,7 @@
         <v>101</v>
       </c>
       <c r="G171" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H171" s="18">
         <v>10</v>
@@ -9782,7 +9800,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M171" s="18">
         <v>0</v>
@@ -9814,7 +9832,7 @@
         <v>101</v>
       </c>
       <c r="G172" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H172" s="18">
         <v>11</v>
@@ -9829,7 +9847,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M172" s="18">
         <v>0</v>
@@ -9861,7 +9879,7 @@
         <v>101</v>
       </c>
       <c r="G173" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H173" s="18">
         <v>12</v>
@@ -9876,7 +9894,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M173" s="18">
         <v>0</v>
@@ -9908,7 +9926,7 @@
         <v>104</v>
       </c>
       <c r="G174" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H174" s="18">
         <v>10</v>
@@ -9923,7 +9941,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M174" s="18">
         <v>0</v>
@@ -9956,7 +9974,7 @@
         <v>104</v>
       </c>
       <c r="G175" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H175" s="18">
         <v>11</v>
@@ -9971,7 +9989,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M175" s="18">
         <v>0</v>
@@ -10004,7 +10022,7 @@
         <v>104</v>
       </c>
       <c r="G176" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H176" s="18">
         <v>12</v>
@@ -10019,7 +10037,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M176" s="18">
         <v>0</v>
@@ -10052,7 +10070,7 @@
         <v>107</v>
       </c>
       <c r="G177" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H177" s="18">
         <v>10</v>
@@ -10067,7 +10085,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M177" s="18">
         <v>0</v>
@@ -10100,7 +10118,7 @@
         <v>107</v>
       </c>
       <c r="G178" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H178" s="18">
         <v>11</v>
@@ -10115,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M178" s="18">
         <v>0</v>
@@ -10148,7 +10166,7 @@
         <v>107</v>
       </c>
       <c r="G179" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H179" s="18">
         <v>12</v>
@@ -10163,7 +10181,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M179" s="18">
         <v>0</v>
@@ -10196,7 +10214,7 @@
         <v>109</v>
       </c>
       <c r="G180" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H180" s="18">
         <v>10</v>
@@ -10211,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M180" s="18">
         <v>0</v>
@@ -10244,7 +10262,7 @@
         <v>109</v>
       </c>
       <c r="G181" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H181" s="18">
         <v>11</v>
@@ -10259,7 +10277,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M181" s="18">
         <v>0</v>
@@ -10292,7 +10310,7 @@
         <v>109</v>
       </c>
       <c r="G182" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H182" s="18">
         <v>12</v>
@@ -10307,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="L182" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M182" s="18">
         <v>0</v>
@@ -10341,7 +10359,7 @@
         <v>31</v>
       </c>
       <c r="G183" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H183" s="18">
         <v>10</v>
@@ -10356,7 +10374,7 @@
         <v>0</v>
       </c>
       <c r="L183" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M183" s="18">
         <v>0</v>
@@ -10390,7 +10408,7 @@
         <v>31</v>
       </c>
       <c r="G184" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H184" s="18">
         <v>11</v>
@@ -10405,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M184" s="18">
         <v>0</v>
@@ -10439,7 +10457,7 @@
         <v>31</v>
       </c>
       <c r="G185" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H185" s="18">
         <v>12</v>
@@ -10454,7 +10472,7 @@
         <v>0</v>
       </c>
       <c r="L185" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M185" s="18">
         <v>0</v>
@@ -10487,7 +10505,7 @@
         <v>38</v>
       </c>
       <c r="G186" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H186" s="18">
         <v>10</v>
@@ -10502,7 +10520,7 @@
         <v>0</v>
       </c>
       <c r="L186" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M186" s="18">
         <v>0</v>
@@ -10537,7 +10555,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G187" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H187" s="18">
         <v>11</v>
@@ -10552,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M187" s="18">
         <v>0</v>
@@ -10587,7 +10605,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G188" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H188" s="18">
         <v>12</v>
@@ -10602,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="L188" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M188" s="18">
         <v>0</v>
@@ -10635,7 +10653,7 @@
         <v>40</v>
       </c>
       <c r="G189" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H189" s="18">
         <v>10</v>
@@ -10650,7 +10668,7 @@
         <v>0</v>
       </c>
       <c r="L189" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M189" s="18">
         <v>0</v>
@@ -10685,7 +10703,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G190" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H190" s="18">
         <v>11</v>
@@ -10700,7 +10718,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M190" s="18">
         <v>0</v>
@@ -10735,7 +10753,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G191" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H191" s="18">
         <v>12</v>
@@ -10750,7 +10768,7 @@
         <v>0</v>
       </c>
       <c r="L191" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M191" s="18">
         <v>0</v>
@@ -10783,7 +10801,7 @@
         <v>42</v>
       </c>
       <c r="G192" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H192" s="18">
         <v>10</v>
@@ -10798,7 +10816,7 @@
         <v>0</v>
       </c>
       <c r="L192" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M192" s="18">
         <v>0</v>
@@ -10833,7 +10851,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G193" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H193" s="18">
         <v>11</v>
@@ -10848,7 +10866,7 @@
         <v>0</v>
       </c>
       <c r="L193" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M193" s="18">
         <v>0</v>
@@ -10883,7 +10901,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G194" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H194" s="18">
         <v>12</v>
@@ -10898,7 +10916,7 @@
         <v>0</v>
       </c>
       <c r="L194" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M194" s="18">
         <v>0</v>
@@ -10931,7 +10949,7 @@
         <v>44</v>
       </c>
       <c r="G195" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H195" s="18">
         <v>10</v>
@@ -10946,7 +10964,7 @@
         <v>0</v>
       </c>
       <c r="L195" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M195" s="18">
         <v>0</v>
@@ -10981,7 +10999,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G196" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H196" s="18">
         <v>11</v>
@@ -10996,7 +11014,7 @@
         <v>0</v>
       </c>
       <c r="L196" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M196" s="18">
         <v>0</v>
@@ -11031,7 +11049,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G197" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H197" s="18">
         <v>12</v>
@@ -11046,7 +11064,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M197" s="18">
         <v>0</v>
@@ -11079,7 +11097,7 @@
         <v>46</v>
       </c>
       <c r="G198" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H198" s="18">
         <v>10</v>
@@ -11094,7 +11112,7 @@
         <v>0</v>
       </c>
       <c r="L198" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M198" s="18">
         <v>0</v>
@@ -11128,7 +11146,7 @@
         <v>46</v>
       </c>
       <c r="G199" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H199" s="18">
         <v>11</v>
@@ -11143,7 +11161,7 @@
         <v>0</v>
       </c>
       <c r="L199" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M199" s="18">
         <v>0</v>
@@ -11177,7 +11195,7 @@
         <v>46</v>
       </c>
       <c r="G200" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H200" s="18">
         <v>12</v>
@@ -11192,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="L200" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M200" s="18">
         <v>0</v>
@@ -11225,7 +11243,7 @@
         <v>48</v>
       </c>
       <c r="G201" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H201" s="18">
         <v>10</v>
@@ -11240,7 +11258,7 @@
         <v>0</v>
       </c>
       <c r="L201" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M201" s="18">
         <v>0</v>
@@ -11273,7 +11291,7 @@
         <v>48</v>
       </c>
       <c r="G202" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H202" s="18">
         <v>11</v>
@@ -11288,7 +11306,7 @@
         <v>0</v>
       </c>
       <c r="L202" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M202" s="18">
         <v>0</v>
@@ -11321,7 +11339,7 @@
         <v>48</v>
       </c>
       <c r="G203" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H203" s="18">
         <v>12</v>
@@ -11336,7 +11354,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M203" s="18">
         <v>0</v>
@@ -11369,7 +11387,7 @@
         <v>50</v>
       </c>
       <c r="G204" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H204" s="18">
         <v>10</v>
@@ -11384,7 +11402,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M204" s="18">
         <v>0</v>
@@ -11417,7 +11435,7 @@
         <v>50</v>
       </c>
       <c r="G205" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H205" s="18">
         <v>11</v>
@@ -11432,7 +11450,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M205" s="18">
         <v>0</v>
@@ -11465,7 +11483,7 @@
         <v>50</v>
       </c>
       <c r="G206" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H206" s="18">
         <v>12</v>
@@ -11480,7 +11498,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M206" s="18">
         <v>0</v>
@@ -11513,7 +11531,7 @@
         <v>52</v>
       </c>
       <c r="G207" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H207" s="18">
         <v>10</v>
@@ -11528,7 +11546,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M207" s="18">
         <v>0</v>
@@ -11561,7 +11579,7 @@
         <v>52</v>
       </c>
       <c r="G208" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H208" s="18">
         <v>11</v>
@@ -11576,7 +11594,7 @@
         <v>0</v>
       </c>
       <c r="L208" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M208" s="18">
         <v>0</v>
@@ -11609,7 +11627,7 @@
         <v>52</v>
       </c>
       <c r="G209" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H209" s="18">
         <v>12</v>
@@ -11624,7 +11642,7 @@
         <v>0</v>
       </c>
       <c r="L209" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M209" s="18">
         <v>0</v>
@@ -11657,7 +11675,7 @@
         <v>54</v>
       </c>
       <c r="G210" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H210" s="18">
         <v>10</v>
@@ -11672,7 +11690,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M210" s="18">
         <v>0</v>
@@ -11705,7 +11723,7 @@
         <v>54</v>
       </c>
       <c r="G211" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H211" s="18">
         <v>11</v>
@@ -11720,7 +11738,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M211" s="18">
         <v>0</v>
@@ -11753,7 +11771,7 @@
         <v>54</v>
       </c>
       <c r="G212" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H212" s="18">
         <v>12</v>
@@ -11768,7 +11786,7 @@
         <v>0</v>
       </c>
       <c r="L212" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M212" s="18">
         <v>0</v>
@@ -11801,7 +11819,7 @@
         <v>56</v>
       </c>
       <c r="G213" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H213" s="18">
         <v>10</v>
@@ -11816,7 +11834,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M213" s="18">
         <v>0</v>
@@ -11849,7 +11867,7 @@
         <v>56</v>
       </c>
       <c r="G214" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H214" s="18">
         <v>11</v>
@@ -11864,7 +11882,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M214" s="18">
         <v>0</v>
@@ -11897,7 +11915,7 @@
         <v>56</v>
       </c>
       <c r="G215" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H215" s="18">
         <v>12</v>
@@ -11912,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M215" s="18">
         <v>0</v>
@@ -11945,7 +11963,7 @@
         <v>58</v>
       </c>
       <c r="G216" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H216" s="18">
         <v>10</v>
@@ -11960,7 +11978,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M216" s="18">
         <v>0</v>
@@ -11993,7 +12011,7 @@
         <v>58</v>
       </c>
       <c r="G217" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H217" s="18">
         <v>11</v>
@@ -12008,7 +12026,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M217" s="18">
         <v>0</v>
@@ -12041,7 +12059,7 @@
         <v>58</v>
       </c>
       <c r="G218" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H218" s="18">
         <v>12</v>
@@ -12056,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="L218" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M218" s="18">
         <v>0</v>
@@ -12089,7 +12107,7 @@
         <v>60</v>
       </c>
       <c r="G219" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H219" s="1">
         <v>10</v>
@@ -12104,7 +12122,7 @@
         <v>0</v>
       </c>
       <c r="L219" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M219" s="18">
         <v>0</v>
@@ -12137,7 +12155,7 @@
         <v>60</v>
       </c>
       <c r="G220" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H220" s="1">
         <v>11</v>
@@ -12152,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M220" s="18">
         <v>0</v>
@@ -12185,7 +12203,7 @@
         <v>60</v>
       </c>
       <c r="G221" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H221" s="1">
         <v>12</v>
@@ -12200,7 +12218,7 @@
         <v>0</v>
       </c>
       <c r="L221" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M221" s="18">
         <v>0</v>
@@ -12233,7 +12251,7 @@
         <v>62</v>
       </c>
       <c r="G222" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H222" s="1">
         <v>10</v>
@@ -12248,7 +12266,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M222" s="18">
         <v>0</v>
@@ -12281,7 +12299,7 @@
         <v>62</v>
       </c>
       <c r="G223" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H223" s="1">
         <v>11</v>
@@ -12296,7 +12314,7 @@
         <v>0</v>
       </c>
       <c r="L223" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M223" s="18">
         <v>0</v>
@@ -12329,7 +12347,7 @@
         <v>62</v>
       </c>
       <c r="G224" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H224" s="1">
         <v>12</v>
@@ -12344,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="L224" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M224" s="18">
         <v>0</v>
@@ -12377,7 +12395,7 @@
         <v>64</v>
       </c>
       <c r="G225" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H225" s="1">
         <v>10</v>
@@ -12392,7 +12410,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M225" s="18">
         <v>0</v>
@@ -12425,7 +12443,7 @@
         <v>64</v>
       </c>
       <c r="G226" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H226" s="1">
         <v>11</v>
@@ -12440,7 +12458,7 @@
         <v>0</v>
       </c>
       <c r="L226" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M226" s="18">
         <v>0</v>
@@ -12473,7 +12491,7 @@
         <v>64</v>
       </c>
       <c r="G227" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H227" s="1">
         <v>12</v>
@@ -12488,7 +12506,7 @@
         <v>0</v>
       </c>
       <c r="L227" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M227" s="18">
         <v>0</v>
@@ -12521,7 +12539,7 @@
         <v>66</v>
       </c>
       <c r="G228" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H228" s="1">
         <v>10</v>
@@ -12536,7 +12554,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M228" s="18">
         <v>0</v>
@@ -12569,7 +12587,7 @@
         <v>66</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H229" s="1">
         <v>11</v>
@@ -12584,7 +12602,7 @@
         <v>0</v>
       </c>
       <c r="L229" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M229" s="18">
         <v>0</v>
@@ -12617,7 +12635,7 @@
         <v>66</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H230" s="1">
         <v>12</v>
@@ -12632,7 +12650,7 @@
         <v>0</v>
       </c>
       <c r="L230" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M230" s="18">
         <v>0</v>
@@ -12665,7 +12683,7 @@
         <v>68</v>
       </c>
       <c r="G231" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H231" s="1">
         <v>10</v>
@@ -12680,7 +12698,7 @@
         <v>0</v>
       </c>
       <c r="L231" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M231" s="18">
         <v>0</v>
@@ -12713,7 +12731,7 @@
         <v>68</v>
       </c>
       <c r="G232" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H232" s="1">
         <v>11</v>
@@ -12728,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="L232" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M232" s="18">
         <v>0</v>
@@ -12761,7 +12779,7 @@
         <v>68</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H233" s="1">
         <v>12</v>
@@ -12776,7 +12794,7 @@
         <v>0</v>
       </c>
       <c r="L233" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M233" s="18">
         <v>0</v>
@@ -12809,7 +12827,7 @@
         <v>70</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H234" s="1">
         <v>10</v>
@@ -12824,7 +12842,7 @@
         <v>0</v>
       </c>
       <c r="L234" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M234" s="18">
         <v>0</v>
@@ -12857,7 +12875,7 @@
         <v>70</v>
       </c>
       <c r="G235" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H235" s="1">
         <v>11</v>
@@ -12872,7 +12890,7 @@
         <v>0</v>
       </c>
       <c r="L235" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M235" s="18">
         <v>0</v>
@@ -12905,7 +12923,7 @@
         <v>70</v>
       </c>
       <c r="G236" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H236" s="1">
         <v>12</v>
@@ -12920,7 +12938,7 @@
         <v>0</v>
       </c>
       <c r="L236" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M236" s="18">
         <v>0</v>
@@ -12952,7 +12970,7 @@
         <v>72</v>
       </c>
       <c r="G237" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H237" s="1">
         <v>10</v>
@@ -12967,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="L237" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M237" s="18">
         <v>0</v>
@@ -12999,7 +13017,7 @@
         <v>72</v>
       </c>
       <c r="G238" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H238" s="1">
         <v>11</v>
@@ -13014,7 +13032,7 @@
         <v>0</v>
       </c>
       <c r="L238" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M238" s="18">
         <v>0</v>
@@ -13046,7 +13064,7 @@
         <v>72</v>
       </c>
       <c r="G239" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H239" s="1">
         <v>12</v>
@@ -13061,7 +13079,7 @@
         <v>0</v>
       </c>
       <c r="L239" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M239" s="18">
         <v>0</v>
@@ -13093,7 +13111,7 @@
         <v>74</v>
       </c>
       <c r="G240" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H240" s="1">
         <v>10</v>
@@ -13108,7 +13126,7 @@
         <v>0</v>
       </c>
       <c r="L240" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M240" s="18">
         <v>0</v>
@@ -13140,7 +13158,7 @@
         <v>74</v>
       </c>
       <c r="G241" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H241" s="1">
         <v>11</v>
@@ -13155,7 +13173,7 @@
         <v>0</v>
       </c>
       <c r="L241" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M241" s="18">
         <v>0</v>
@@ -13187,7 +13205,7 @@
         <v>74</v>
       </c>
       <c r="G242" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H242" s="1">
         <v>12</v>
@@ -13202,7 +13220,7 @@
         <v>0</v>
       </c>
       <c r="L242" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M242" s="18">
         <v>0</v>
@@ -13234,7 +13252,7 @@
         <v>76</v>
       </c>
       <c r="G243" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H243" s="1">
         <v>10</v>
@@ -13249,7 +13267,7 @@
         <v>0</v>
       </c>
       <c r="L243" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M243" s="18">
         <v>0</v>
@@ -13282,7 +13300,7 @@
         <v>76</v>
       </c>
       <c r="G244" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H244" s="1">
         <v>11</v>
@@ -13297,7 +13315,7 @@
         <v>0</v>
       </c>
       <c r="L244" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M244" s="18">
         <v>0</v>
@@ -13330,7 +13348,7 @@
         <v>76</v>
       </c>
       <c r="G245" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H245" s="1">
         <v>12</v>
@@ -13345,7 +13363,7 @@
         <v>0</v>
       </c>
       <c r="L245" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M245" s="18">
         <v>0</v>
@@ -13378,7 +13396,7 @@
         <v>111</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H246" s="1">
         <v>10</v>
@@ -13393,7 +13411,7 @@
         <v>0</v>
       </c>
       <c r="L246" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M246" s="18">
         <v>0</v>
@@ -13425,7 +13443,7 @@
         <v>111</v>
       </c>
       <c r="G247" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H247" s="1">
         <v>11</v>
@@ -13440,7 +13458,7 @@
         <v>0</v>
       </c>
       <c r="L247" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M247" s="18">
         <v>0</v>
@@ -13472,7 +13490,7 @@
         <v>111</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H248" s="1">
         <v>12</v>
@@ -13487,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="L248" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M248" s="18">
         <v>0</v>
@@ -13519,7 +13537,7 @@
         <v>113</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H249" s="1">
         <v>10</v>
@@ -13534,7 +13552,7 @@
         <v>0</v>
       </c>
       <c r="L249" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M249" s="18">
         <v>0</v>
@@ -13566,7 +13584,7 @@
         <v>113</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H250" s="1">
         <v>11</v>
@@ -13581,7 +13599,7 @@
         <v>0</v>
       </c>
       <c r="L250" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M250" s="18">
         <v>0</v>
@@ -13613,7 +13631,7 @@
         <v>113</v>
       </c>
       <c r="G251" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H251" s="1">
         <v>12</v>
@@ -13628,7 +13646,7 @@
         <v>0</v>
       </c>
       <c r="L251" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M251" s="18">
         <v>0</v>
@@ -13660,7 +13678,7 @@
         <v>115</v>
       </c>
       <c r="G252" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H252" s="1">
         <v>10</v>
@@ -13675,7 +13693,7 @@
         <v>0</v>
       </c>
       <c r="L252" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M252" s="18">
         <v>0</v>
@@ -13707,7 +13725,7 @@
         <v>115</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H253" s="1">
         <v>11</v>
@@ -13722,7 +13740,7 @@
         <v>0</v>
       </c>
       <c r="L253" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M253" s="18">
         <v>0</v>
@@ -13754,7 +13772,7 @@
         <v>115</v>
       </c>
       <c r="G254" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H254" s="1">
         <v>12</v>
@@ -13769,7 +13787,7 @@
         <v>0</v>
       </c>
       <c r="L254" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M254" s="18">
         <v>0</v>
@@ -13797,9 +13815,11 @@
       <c r="E255" s="5">
         <v>103900001</v>
       </c>
-      <c r="F255" s="5"/>
+      <c r="F255" s="5" t="s">
+        <v>117</v>
+      </c>
       <c r="G255" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H255" s="1">
         <v>10</v>
@@ -13814,7 +13834,7 @@
         <v>0</v>
       </c>
       <c r="L255" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M255" s="18">
         <v>0</v>
@@ -13842,9 +13862,11 @@
       <c r="E256" s="5">
         <v>103900001</v>
       </c>
-      <c r="F256" s="5"/>
+      <c r="F256" s="5" t="s">
+        <v>117</v>
+      </c>
       <c r="G256" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H256" s="1">
         <v>11</v>
@@ -13859,7 +13881,7 @@
         <v>0</v>
       </c>
       <c r="L256" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M256" s="18">
         <v>0</v>
@@ -13887,9 +13909,11 @@
       <c r="E257" s="5">
         <v>103900001</v>
       </c>
-      <c r="F257" s="5"/>
+      <c r="F257" s="5" t="s">
+        <v>117</v>
+      </c>
       <c r="G257" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H257" s="1">
         <v>12</v>
@@ -13904,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="L257" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M257" s="18">
         <v>0</v>
@@ -13932,9 +13956,11 @@
       <c r="E258" s="5">
         <v>101500001</v>
       </c>
-      <c r="F258" s="5"/>
+      <c r="F258" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G258" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H258" s="1">
         <v>10</v>
@@ -13949,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L258" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M258" s="18">
         <v>0</v>
@@ -13977,9 +14003,11 @@
       <c r="E259" s="5">
         <v>101500001</v>
       </c>
-      <c r="F259" s="5"/>
+      <c r="F259" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G259" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H259" s="1">
         <v>11</v>
@@ -13994,7 +14022,7 @@
         <v>0</v>
       </c>
       <c r="L259" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M259" s="18">
         <v>0</v>
@@ -14022,9 +14050,11 @@
       <c r="E260" s="5">
         <v>101500001</v>
       </c>
-      <c r="F260" s="5"/>
+      <c r="F260" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="G260" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H260" s="1">
         <v>12</v>
@@ -14039,7 +14069,7 @@
         <v>0</v>
       </c>
       <c r="L260" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M260" s="18">
         <v>0</v>
@@ -14062,14 +14092,16 @@
         <v>1</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E261" s="5">
         <v>105300001</v>
       </c>
-      <c r="F261" s="5"/>
+      <c r="F261" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G261" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H261" s="1">
         <v>10</v>
@@ -14084,7 +14116,7 @@
         <v>0</v>
       </c>
       <c r="L261" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M261" s="18">
         <v>0</v>
@@ -14107,14 +14139,16 @@
         <v>1</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E262" s="5">
         <v>105300001</v>
       </c>
-      <c r="F262" s="5"/>
+      <c r="F262" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G262" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H262" s="1">
         <v>11</v>
@@ -14129,7 +14163,7 @@
         <v>0</v>
       </c>
       <c r="L262" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M262" s="18">
         <v>0</v>
@@ -14152,14 +14186,16 @@
         <v>1</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E263" s="5">
         <v>105300001</v>
       </c>
-      <c r="F263" s="5"/>
+      <c r="F263" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="G263" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H263" s="1">
         <v>12</v>
@@ -14174,7 +14210,7 @@
         <v>0</v>
       </c>
       <c r="L263" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M263" s="18">
         <v>0</v>
@@ -14197,16 +14233,16 @@
         <v>1</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E264" s="5">
         <v>105100001</v>
       </c>
       <c r="F264" s="22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G264" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H264" s="1">
         <v>10</v>
@@ -14221,7 +14257,7 @@
         <v>0</v>
       </c>
       <c r="L264" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M264" s="18">
         <v>0</v>
@@ -14244,16 +14280,16 @@
         <v>1</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E265" s="5">
         <v>105100001</v>
       </c>
       <c r="F265" s="22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G265" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H265" s="1">
         <v>11</v>
@@ -14268,7 +14304,7 @@
         <v>0</v>
       </c>
       <c r="L265" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M265" s="18">
         <v>0</v>
@@ -14291,16 +14327,16 @@
         <v>1</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E266" s="5">
         <v>105100001</v>
       </c>
       <c r="F266" s="22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G266" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H266" s="1">
         <v>12</v>
@@ -14315,7 +14351,7 @@
         <v>0</v>
       </c>
       <c r="L266" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M266" s="18">
         <v>0</v>
@@ -14338,16 +14374,16 @@
         <v>1</v>
       </c>
       <c r="D267" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E267" s="2">
         <v>105500001</v>
       </c>
       <c r="F267" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G267" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H267" s="2">
         <v>10</v>
@@ -14362,7 +14398,7 @@
         <v>0</v>
       </c>
       <c r="L267" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M267" s="30">
         <v>0</v>
@@ -14389,16 +14425,16 @@
         <v>1</v>
       </c>
       <c r="D268" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E268" s="2">
         <v>105500001</v>
       </c>
       <c r="F268" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G268" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H268" s="2">
         <v>11</v>
@@ -14413,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="L268" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M268" s="30">
         <v>0</v>
@@ -14440,16 +14476,16 @@
         <v>1</v>
       </c>
       <c r="D269" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E269" s="2">
         <v>105500001</v>
       </c>
       <c r="F269" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G269" s="30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H269" s="2">
         <v>12</v>
@@ -14464,7 +14500,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M269" s="30">
         <v>0</v>
@@ -14491,14 +14527,14 @@
         <v>1</v>
       </c>
       <c r="D270" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E270" s="2">
         <v>105501001</v>
       </c>
       <c r="F270" s="2"/>
       <c r="G270" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H270" s="2">
         <v>10</v>
@@ -14513,7 +14549,7 @@
         <v>0</v>
       </c>
       <c r="L270" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M270" s="30">
         <v>0</v>
@@ -14540,14 +14576,14 @@
         <v>1</v>
       </c>
       <c r="D271" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E271" s="2">
         <v>105501001</v>
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H271" s="2">
         <v>11</v>
@@ -14562,7 +14598,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M271" s="30">
         <v>0</v>
@@ -14589,14 +14625,14 @@
         <v>1</v>
       </c>
       <c r="D272" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E272" s="2">
         <v>105501001</v>
       </c>
       <c r="F272" s="2"/>
       <c r="G272" s="30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H272" s="2">
         <v>12</v>
@@ -14611,7 +14647,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M272" s="30">
         <v>0</v>
@@ -14638,14 +14674,14 @@
         <v>1</v>
       </c>
       <c r="D273" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E273" s="2">
         <v>105502001</v>
       </c>
       <c r="F273" s="2"/>
       <c r="G273" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H273" s="2">
         <v>10</v>
@@ -14660,7 +14696,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M273" s="30">
         <v>0</v>
@@ -14687,14 +14723,14 @@
         <v>1</v>
       </c>
       <c r="D274" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E274" s="2">
         <v>105502001</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H274" s="2">
         <v>11</v>
@@ -14709,7 +14745,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M274" s="30">
         <v>0</v>
@@ -14736,14 +14772,14 @@
         <v>1</v>
       </c>
       <c r="D275" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E275" s="2">
         <v>105502001</v>
       </c>
       <c r="F275" s="2"/>
       <c r="G275" s="30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H275" s="2">
         <v>12</v>
@@ -14758,7 +14794,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M275" s="30">
         <v>0</v>
@@ -14794,7 +14830,7 @@
         <v>31</v>
       </c>
       <c r="G276" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H276" s="1">
         <v>21</v>
@@ -14842,7 +14878,7 @@
         <v>31</v>
       </c>
       <c r="G277" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H277" s="1">
         <v>22</v>
@@ -14890,7 +14926,7 @@
         <v>31</v>
       </c>
       <c r="G278" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H278" s="1">
         <v>23</v>
@@ -14938,7 +14974,7 @@
         <v>38</v>
       </c>
       <c r="G279" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H279" s="1">
         <v>21</v>
@@ -14986,7 +15022,7 @@
         <v>38</v>
       </c>
       <c r="G280" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H280" s="1">
         <v>22</v>
@@ -15034,7 +15070,7 @@
         <v>38</v>
       </c>
       <c r="G281" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H281" s="1">
         <v>23</v>
@@ -15082,7 +15118,7 @@
         <v>40</v>
       </c>
       <c r="G282" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H282" s="1">
         <v>21</v>
@@ -15130,7 +15166,7 @@
         <v>40</v>
       </c>
       <c r="G283" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H283" s="1">
         <v>22</v>
@@ -15178,7 +15214,7 @@
         <v>40</v>
       </c>
       <c r="G284" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H284" s="1">
         <v>23</v>
@@ -15226,7 +15262,7 @@
         <v>42</v>
       </c>
       <c r="G285" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H285" s="1">
         <v>21</v>
@@ -15274,7 +15310,7 @@
         <v>42</v>
       </c>
       <c r="G286" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H286" s="1">
         <v>22</v>
@@ -15322,7 +15358,7 @@
         <v>42</v>
       </c>
       <c r="G287" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H287" s="1">
         <v>23</v>
@@ -15370,7 +15406,7 @@
         <v>44</v>
       </c>
       <c r="G288" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H288" s="1">
         <v>21</v>
@@ -15418,7 +15454,7 @@
         <v>44</v>
       </c>
       <c r="G289" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H289" s="1">
         <v>22</v>
@@ -15466,7 +15502,7 @@
         <v>44</v>
       </c>
       <c r="G290" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H290" s="1">
         <v>23</v>
@@ -15514,7 +15550,7 @@
         <v>46</v>
       </c>
       <c r="G291" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H291" s="1">
         <v>21</v>
@@ -15562,7 +15598,7 @@
         <v>46</v>
       </c>
       <c r="G292" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H292" s="1">
         <v>22</v>
@@ -15610,7 +15646,7 @@
         <v>46</v>
       </c>
       <c r="G293" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H293" s="1">
         <v>23</v>
@@ -15658,7 +15694,7 @@
         <v>48</v>
       </c>
       <c r="G294" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H294" s="1">
         <v>21</v>
@@ -15706,7 +15742,7 @@
         <v>48</v>
       </c>
       <c r="G295" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H295" s="1">
         <v>22</v>
@@ -15754,7 +15790,7 @@
         <v>48</v>
       </c>
       <c r="G296" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H296" s="1">
         <v>23</v>
@@ -15802,7 +15838,7 @@
         <v>50</v>
       </c>
       <c r="G297" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H297" s="1">
         <v>21</v>
@@ -15850,7 +15886,7 @@
         <v>50</v>
       </c>
       <c r="G298" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H298" s="1">
         <v>22</v>
@@ -15898,7 +15934,7 @@
         <v>50</v>
       </c>
       <c r="G299" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H299" s="1">
         <v>23</v>
@@ -15946,7 +15982,7 @@
         <v>52</v>
       </c>
       <c r="G300" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H300" s="1">
         <v>21</v>
@@ -15994,7 +16030,7 @@
         <v>52</v>
       </c>
       <c r="G301" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H301" s="1">
         <v>22</v>
@@ -16042,7 +16078,7 @@
         <v>52</v>
       </c>
       <c r="G302" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H302" s="1">
         <v>23</v>
@@ -16091,7 +16127,7 @@
         <v>54</v>
       </c>
       <c r="G303" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H303" s="1">
         <v>21</v>
@@ -16140,7 +16176,7 @@
         <v>54</v>
       </c>
       <c r="G304" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H304" s="1">
         <v>22</v>
@@ -16189,7 +16225,7 @@
         <v>54</v>
       </c>
       <c r="G305" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H305" s="1">
         <v>23</v>
@@ -16238,7 +16274,7 @@
         <v>56</v>
       </c>
       <c r="G306" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H306" s="1">
         <v>21</v>
@@ -16287,7 +16323,7 @@
         <v>56</v>
       </c>
       <c r="G307" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H307" s="1">
         <v>22</v>
@@ -16336,7 +16372,7 @@
         <v>56</v>
       </c>
       <c r="G308" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H308" s="1">
         <v>23</v>
@@ -16385,7 +16421,7 @@
         <v>58</v>
       </c>
       <c r="G309" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H309" s="1">
         <v>21</v>
@@ -16434,7 +16470,7 @@
         <v>58</v>
       </c>
       <c r="G310" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H310" s="1">
         <v>22</v>
@@ -16483,7 +16519,7 @@
         <v>58</v>
       </c>
       <c r="G311" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H311" s="1">
         <v>23</v>
@@ -16531,7 +16567,7 @@
         <v>60</v>
       </c>
       <c r="G312" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H312" s="1">
         <v>21</v>
@@ -16579,7 +16615,7 @@
         <v>60</v>
       </c>
       <c r="G313" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H313" s="1">
         <v>22</v>
@@ -16627,7 +16663,7 @@
         <v>60</v>
       </c>
       <c r="G314" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H314" s="1">
         <v>23</v>
@@ -16676,7 +16712,7 @@
         <v>62</v>
       </c>
       <c r="G315" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H315" s="1">
         <v>21</v>
@@ -16725,7 +16761,7 @@
         <v>62</v>
       </c>
       <c r="G316" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H316" s="1">
         <v>22</v>
@@ -16774,7 +16810,7 @@
         <v>62</v>
       </c>
       <c r="G317" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H317" s="1">
         <v>23</v>
@@ -16822,7 +16858,7 @@
         <v>64</v>
       </c>
       <c r="G318" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H318" s="1">
         <v>21</v>
@@ -16870,7 +16906,7 @@
         <v>64</v>
       </c>
       <c r="G319" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H319" s="1">
         <v>22</v>
@@ -16918,7 +16954,7 @@
         <v>64</v>
       </c>
       <c r="G320" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H320" s="1">
         <v>23</v>
@@ -16966,7 +17002,7 @@
         <v>66</v>
       </c>
       <c r="G321" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H321" s="1">
         <v>21</v>
@@ -17014,7 +17050,7 @@
         <v>66</v>
       </c>
       <c r="G322" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H322" s="1">
         <v>22</v>
@@ -17062,7 +17098,7 @@
         <v>66</v>
       </c>
       <c r="G323" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H323" s="1">
         <v>23</v>
@@ -17111,7 +17147,7 @@
         <v>68</v>
       </c>
       <c r="G324" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H324" s="1">
         <v>21</v>
@@ -17160,7 +17196,7 @@
         <v>68</v>
       </c>
       <c r="G325" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H325" s="1">
         <v>22</v>
@@ -17209,7 +17245,7 @@
         <v>68</v>
       </c>
       <c r="G326" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H326" s="1">
         <v>23</v>
@@ -17257,7 +17293,7 @@
         <v>72</v>
       </c>
       <c r="G327" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H327" s="1">
         <v>21</v>
@@ -17305,7 +17341,7 @@
         <v>72</v>
       </c>
       <c r="G328" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H328" s="1">
         <v>22</v>
@@ -17353,7 +17389,7 @@
         <v>72</v>
       </c>
       <c r="G329" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H329" s="1">
         <v>23</v>
@@ -17401,7 +17437,7 @@
         <v>74</v>
       </c>
       <c r="G330" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H330" s="1">
         <v>21</v>
@@ -17449,7 +17485,7 @@
         <v>74</v>
       </c>
       <c r="G331" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H331" s="1">
         <v>22</v>
@@ -17497,7 +17533,7 @@
         <v>74</v>
       </c>
       <c r="G332" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H332" s="1">
         <v>23</v>
@@ -17545,7 +17581,7 @@
         <v>76</v>
       </c>
       <c r="G333" s="32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H333" s="1">
         <v>21</v>
@@ -17593,7 +17629,7 @@
         <v>76</v>
       </c>
       <c r="G334" s="32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H334" s="1">
         <v>22</v>
@@ -17641,7 +17677,7 @@
         <v>76</v>
       </c>
       <c r="G335" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H335" s="1">
         <v>23</v>
@@ -19145,13 +19181,13 @@
         <v>3</v>
       </c>
       <c r="D366" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E366" s="14">
         <v>300402001</v>
       </c>
       <c r="F366" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>32</v>
@@ -19194,13 +19230,13 @@
         <v>3</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E367" s="14">
         <v>300402001</v>
       </c>
       <c r="F367" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>35</v>
@@ -19243,13 +19279,13 @@
         <v>3</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E368" s="14">
         <v>300402001</v>
       </c>
       <c r="F368" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>36</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -8310,7 +8310,7 @@
     </row>
     <row r="140" spans="1:15">
       <c r="A140" s="25">
-        <v>4004001</v>
+        <v>4004004</v>
       </c>
       <c r="B140" s="25">
         <v>400400</v>
@@ -8357,7 +8357,7 @@
     </row>
     <row r="141" spans="1:15">
       <c r="A141" s="2">
-        <v>4002001</v>
+        <v>4002004</v>
       </c>
       <c r="B141" s="2">
         <v>400200</v>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="142" spans="1:15">
       <c r="A142" s="2">
-        <v>4005001</v>
+        <v>4005004</v>
       </c>
       <c r="B142" s="2">
         <v>400500</v>
@@ -8451,7 +8451,7 @@
     </row>
     <row r="143" spans="1:15">
       <c r="A143" s="2">
-        <v>4007001</v>
+        <v>4007004</v>
       </c>
       <c r="B143" s="2">
         <v>400700</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="150">
   <si>
     <t>sid</t>
   </si>
@@ -539,7 +539,13 @@
     <t>伽罗宝石1</t>
   </si>
   <si>
+    <t>GaloGemstone2</t>
+  </si>
+  <si>
     <t>伽罗宝石2</t>
+  </si>
+  <si>
+    <t>GaloGemstone3</t>
   </si>
   <si>
     <t>空袭</t>
@@ -8054,7 +8060,9 @@
       <c r="E134" s="24">
         <v>105501001</v>
       </c>
-      <c r="F134" s="24"/>
+      <c r="F134" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G134" s="1" t="s">
         <v>32</v>
       </c>
@@ -8099,7 +8107,9 @@
       <c r="E135" s="24">
         <v>105501001</v>
       </c>
-      <c r="F135" s="24"/>
+      <c r="F135" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G135" s="1" t="s">
         <v>35</v>
       </c>
@@ -8144,7 +8154,9 @@
       <c r="E136" s="24">
         <v>105501001</v>
       </c>
-      <c r="F136" s="24"/>
+      <c r="F136" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G136" s="1" t="s">
         <v>36</v>
       </c>
@@ -8184,12 +8196,14 @@
         <v>1</v>
       </c>
       <c r="D137" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E137" s="24">
         <v>105502001</v>
       </c>
-      <c r="F137" s="24"/>
+      <c r="F137" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G137" s="1" t="s">
         <v>32</v>
       </c>
@@ -8229,12 +8243,14 @@
         <v>1</v>
       </c>
       <c r="D138" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E138" s="24">
         <v>105502001</v>
       </c>
-      <c r="F138" s="24"/>
+      <c r="F138" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G138" s="1" t="s">
         <v>35</v>
       </c>
@@ -8274,12 +8290,14 @@
         <v>1</v>
       </c>
       <c r="D139" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E139" s="24">
         <v>105502001</v>
       </c>
-      <c r="F139" s="24"/>
+      <c r="F139" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G139" s="1" t="s">
         <v>36</v>
       </c>
@@ -8319,13 +8337,13 @@
         <v>4</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E140" s="26">
         <v>400400001</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>32</v>
@@ -8343,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M140" s="33" t="s">
         <v>34</v>
@@ -8366,13 +8384,13 @@
         <v>4</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E141" s="26">
         <v>400200001</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>32</v>
@@ -8390,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M141" s="33" t="s">
         <v>34</v>
@@ -8413,13 +8431,13 @@
         <v>4</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E142" s="26">
         <v>400500001</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>32</v>
@@ -8437,7 +8455,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M142" s="33" t="s">
         <v>34</v>
@@ -8460,13 +8478,13 @@
         <v>4</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E143" s="26">
         <v>400700001</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>32</v>
@@ -8484,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M143" s="33" t="s">
         <v>34</v>
@@ -8516,7 +8534,7 @@
         <v>78</v>
       </c>
       <c r="G144" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H144" s="18">
         <v>10</v>
@@ -8531,7 +8549,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M144" s="18">
         <v>0</v>
@@ -8563,7 +8581,7 @@
         <v>78</v>
       </c>
       <c r="G145" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H145" s="18">
         <v>11</v>
@@ -8578,7 +8596,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M145" s="18">
         <v>0</v>
@@ -8610,7 +8628,7 @@
         <v>78</v>
       </c>
       <c r="G146" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H146" s="18">
         <v>12</v>
@@ -8625,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M146" s="18">
         <v>0</v>
@@ -8657,7 +8675,7 @@
         <v>80</v>
       </c>
       <c r="G147" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H147" s="18">
         <v>10</v>
@@ -8672,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M147" s="18">
         <v>0</v>
@@ -8704,7 +8722,7 @@
         <v>80</v>
       </c>
       <c r="G148" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H148" s="18">
         <v>11</v>
@@ -8719,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M148" s="18">
         <v>0</v>
@@ -8751,7 +8769,7 @@
         <v>80</v>
       </c>
       <c r="G149" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H149" s="18">
         <v>12</v>
@@ -8766,7 +8784,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M149" s="18">
         <v>0</v>
@@ -8798,7 +8816,7 @@
         <v>82</v>
       </c>
       <c r="G150" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H150" s="18">
         <v>10</v>
@@ -8813,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M150" s="18">
         <v>0</v>
@@ -8845,7 +8863,7 @@
         <v>82</v>
       </c>
       <c r="G151" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H151" s="18">
         <v>11</v>
@@ -8860,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M151" s="18">
         <v>0</v>
@@ -8892,7 +8910,7 @@
         <v>82</v>
       </c>
       <c r="G152" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H152" s="18">
         <v>12</v>
@@ -8907,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M152" s="18">
         <v>0</v>
@@ -8939,7 +8957,7 @@
         <v>84</v>
       </c>
       <c r="G153" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H153" s="18">
         <v>10</v>
@@ -8954,7 +8972,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M153" s="18">
         <v>0</v>
@@ -8986,7 +9004,7 @@
         <v>84</v>
       </c>
       <c r="G154" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H154" s="18">
         <v>11</v>
@@ -9001,7 +9019,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M154" s="18">
         <v>0</v>
@@ -9033,7 +9051,7 @@
         <v>84</v>
       </c>
       <c r="G155" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H155" s="18">
         <v>12</v>
@@ -9048,7 +9066,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M155" s="18">
         <v>0</v>
@@ -9080,7 +9098,7 @@
         <v>86</v>
       </c>
       <c r="G156" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H156" s="18">
         <v>10</v>
@@ -9095,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M156" s="18">
         <v>0</v>
@@ -9127,7 +9145,7 @@
         <v>86</v>
       </c>
       <c r="G157" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H157" s="18">
         <v>11</v>
@@ -9142,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M157" s="18">
         <v>0</v>
@@ -9174,7 +9192,7 @@
         <v>86</v>
       </c>
       <c r="G158" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H158" s="18">
         <v>12</v>
@@ -9189,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M158" s="18">
         <v>0</v>
@@ -9221,7 +9239,7 @@
         <v>89</v>
       </c>
       <c r="G159" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H159" s="18">
         <v>10</v>
@@ -9236,7 +9254,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M159" s="18">
         <v>0</v>
@@ -9268,7 +9286,7 @@
         <v>89</v>
       </c>
       <c r="G160" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H160" s="18">
         <v>11</v>
@@ -9283,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M160" s="18">
         <v>0</v>
@@ -9315,7 +9333,7 @@
         <v>89</v>
       </c>
       <c r="G161" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H161" s="18">
         <v>12</v>
@@ -9330,7 +9348,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M161" s="18">
         <v>0</v>
@@ -9362,7 +9380,7 @@
         <v>91</v>
       </c>
       <c r="G162" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H162" s="18">
         <v>10</v>
@@ -9377,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M162" s="18">
         <v>0</v>
@@ -9409,7 +9427,7 @@
         <v>91</v>
       </c>
       <c r="G163" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H163" s="18">
         <v>11</v>
@@ -9424,7 +9442,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M163" s="18">
         <v>0</v>
@@ -9456,7 +9474,7 @@
         <v>91</v>
       </c>
       <c r="G164" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H164" s="18">
         <v>12</v>
@@ -9471,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M164" s="18">
         <v>0</v>
@@ -9503,7 +9521,7 @@
         <v>93</v>
       </c>
       <c r="G165" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H165" s="18">
         <v>10</v>
@@ -9518,7 +9536,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M165" s="18">
         <v>0</v>
@@ -9550,7 +9568,7 @@
         <v>93</v>
       </c>
       <c r="G166" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H166" s="18">
         <v>11</v>
@@ -9565,7 +9583,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M166" s="18">
         <v>0</v>
@@ -9597,7 +9615,7 @@
         <v>93</v>
       </c>
       <c r="G167" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H167" s="18">
         <v>12</v>
@@ -9612,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M167" s="18">
         <v>0</v>
@@ -9644,7 +9662,7 @@
         <v>95</v>
       </c>
       <c r="G168" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H168" s="18">
         <v>10</v>
@@ -9659,7 +9677,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M168" s="18">
         <v>0</v>
@@ -9691,7 +9709,7 @@
         <v>95</v>
       </c>
       <c r="G169" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H169" s="18">
         <v>11</v>
@@ -9706,7 +9724,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M169" s="18">
         <v>0</v>
@@ -9738,7 +9756,7 @@
         <v>95</v>
       </c>
       <c r="G170" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H170" s="18">
         <v>12</v>
@@ -9753,7 +9771,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M170" s="18">
         <v>0</v>
@@ -9785,7 +9803,7 @@
         <v>101</v>
       </c>
       <c r="G171" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H171" s="18">
         <v>10</v>
@@ -9800,7 +9818,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M171" s="18">
         <v>0</v>
@@ -9832,7 +9850,7 @@
         <v>101</v>
       </c>
       <c r="G172" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H172" s="18">
         <v>11</v>
@@ -9847,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M172" s="18">
         <v>0</v>
@@ -9879,7 +9897,7 @@
         <v>101</v>
       </c>
       <c r="G173" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H173" s="18">
         <v>12</v>
@@ -9894,7 +9912,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M173" s="18">
         <v>0</v>
@@ -9926,7 +9944,7 @@
         <v>104</v>
       </c>
       <c r="G174" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H174" s="18">
         <v>10</v>
@@ -9941,7 +9959,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M174" s="18">
         <v>0</v>
@@ -9974,7 +9992,7 @@
         <v>104</v>
       </c>
       <c r="G175" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H175" s="18">
         <v>11</v>
@@ -9989,7 +10007,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M175" s="18">
         <v>0</v>
@@ -10022,7 +10040,7 @@
         <v>104</v>
       </c>
       <c r="G176" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H176" s="18">
         <v>12</v>
@@ -10037,7 +10055,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M176" s="18">
         <v>0</v>
@@ -10070,7 +10088,7 @@
         <v>107</v>
       </c>
       <c r="G177" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H177" s="18">
         <v>10</v>
@@ -10085,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M177" s="18">
         <v>0</v>
@@ -10118,7 +10136,7 @@
         <v>107</v>
       </c>
       <c r="G178" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H178" s="18">
         <v>11</v>
@@ -10133,7 +10151,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M178" s="18">
         <v>0</v>
@@ -10166,7 +10184,7 @@
         <v>107</v>
       </c>
       <c r="G179" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H179" s="18">
         <v>12</v>
@@ -10181,7 +10199,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M179" s="18">
         <v>0</v>
@@ -10214,7 +10232,7 @@
         <v>109</v>
       </c>
       <c r="G180" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H180" s="18">
         <v>10</v>
@@ -10229,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M180" s="18">
         <v>0</v>
@@ -10262,7 +10280,7 @@
         <v>109</v>
       </c>
       <c r="G181" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H181" s="18">
         <v>11</v>
@@ -10277,7 +10295,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M181" s="18">
         <v>0</v>
@@ -10310,7 +10328,7 @@
         <v>109</v>
       </c>
       <c r="G182" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H182" s="18">
         <v>12</v>
@@ -10325,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="L182" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M182" s="18">
         <v>0</v>
@@ -10359,7 +10377,7 @@
         <v>31</v>
       </c>
       <c r="G183" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H183" s="18">
         <v>10</v>
@@ -10374,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="L183" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M183" s="18">
         <v>0</v>
@@ -10408,7 +10426,7 @@
         <v>31</v>
       </c>
       <c r="G184" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H184" s="18">
         <v>11</v>
@@ -10423,7 +10441,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M184" s="18">
         <v>0</v>
@@ -10457,7 +10475,7 @@
         <v>31</v>
       </c>
       <c r="G185" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H185" s="18">
         <v>12</v>
@@ -10472,7 +10490,7 @@
         <v>0</v>
       </c>
       <c r="L185" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M185" s="18">
         <v>0</v>
@@ -10505,7 +10523,7 @@
         <v>38</v>
       </c>
       <c r="G186" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H186" s="18">
         <v>10</v>
@@ -10520,7 +10538,7 @@
         <v>0</v>
       </c>
       <c r="L186" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M186" s="18">
         <v>0</v>
@@ -10555,7 +10573,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G187" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H187" s="18">
         <v>11</v>
@@ -10570,7 +10588,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M187" s="18">
         <v>0</v>
@@ -10605,7 +10623,7 @@
         <v>SuperStar</v>
       </c>
       <c r="G188" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H188" s="18">
         <v>12</v>
@@ -10620,7 +10638,7 @@
         <v>0</v>
       </c>
       <c r="L188" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M188" s="18">
         <v>0</v>
@@ -10653,7 +10671,7 @@
         <v>40</v>
       </c>
       <c r="G189" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H189" s="18">
         <v>10</v>
@@ -10668,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="L189" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M189" s="18">
         <v>0</v>
@@ -10703,7 +10721,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G190" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H190" s="18">
         <v>11</v>
@@ -10718,7 +10736,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M190" s="18">
         <v>0</v>
@@ -10753,7 +10771,7 @@
         <v>MahjongWays</v>
       </c>
       <c r="G191" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H191" s="18">
         <v>12</v>
@@ -10768,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="L191" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M191" s="18">
         <v>0</v>
@@ -10801,7 +10819,7 @@
         <v>42</v>
       </c>
       <c r="G192" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H192" s="18">
         <v>10</v>
@@ -10816,7 +10834,7 @@
         <v>0</v>
       </c>
       <c r="L192" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M192" s="18">
         <v>0</v>
@@ -10851,7 +10869,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G193" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H193" s="18">
         <v>11</v>
@@ -10866,7 +10884,7 @@
         <v>0</v>
       </c>
       <c r="L193" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M193" s="18">
         <v>0</v>
@@ -10901,7 +10919,7 @@
         <v>Godofwealth</v>
       </c>
       <c r="G194" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H194" s="18">
         <v>12</v>
@@ -10916,7 +10934,7 @@
         <v>0</v>
       </c>
       <c r="L194" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M194" s="18">
         <v>0</v>
@@ -10949,7 +10967,7 @@
         <v>44</v>
       </c>
       <c r="G195" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H195" s="18">
         <v>10</v>
@@ -10964,7 +10982,7 @@
         <v>0</v>
       </c>
       <c r="L195" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M195" s="18">
         <v>0</v>
@@ -10999,7 +11017,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G196" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H196" s="18">
         <v>11</v>
@@ -11014,7 +11032,7 @@
         <v>0</v>
       </c>
       <c r="L196" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M196" s="18">
         <v>0</v>
@@ -11049,7 +11067,7 @@
         <v>Cleopatra</v>
       </c>
       <c r="G197" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H197" s="18">
         <v>12</v>
@@ -11064,7 +11082,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M197" s="18">
         <v>0</v>
@@ -11097,7 +11115,7 @@
         <v>46</v>
       </c>
       <c r="G198" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H198" s="18">
         <v>10</v>
@@ -11112,7 +11130,7 @@
         <v>0</v>
       </c>
       <c r="L198" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M198" s="18">
         <v>0</v>
@@ -11146,7 +11164,7 @@
         <v>46</v>
       </c>
       <c r="G199" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H199" s="18">
         <v>11</v>
@@ -11161,7 +11179,7 @@
         <v>0</v>
       </c>
       <c r="L199" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M199" s="18">
         <v>0</v>
@@ -11195,7 +11213,7 @@
         <v>46</v>
       </c>
       <c r="G200" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H200" s="18">
         <v>12</v>
@@ -11210,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="L200" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M200" s="18">
         <v>0</v>
@@ -11243,7 +11261,7 @@
         <v>48</v>
       </c>
       <c r="G201" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H201" s="18">
         <v>10</v>
@@ -11258,7 +11276,7 @@
         <v>0</v>
       </c>
       <c r="L201" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M201" s="18">
         <v>0</v>
@@ -11291,7 +11309,7 @@
         <v>48</v>
       </c>
       <c r="G202" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H202" s="18">
         <v>11</v>
@@ -11306,7 +11324,7 @@
         <v>0</v>
       </c>
       <c r="L202" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M202" s="18">
         <v>0</v>
@@ -11339,7 +11357,7 @@
         <v>48</v>
       </c>
       <c r="G203" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H203" s="18">
         <v>12</v>
@@ -11354,7 +11372,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M203" s="18">
         <v>0</v>
@@ -11387,7 +11405,7 @@
         <v>50</v>
       </c>
       <c r="G204" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H204" s="18">
         <v>10</v>
@@ -11402,7 +11420,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M204" s="18">
         <v>0</v>
@@ -11435,7 +11453,7 @@
         <v>50</v>
       </c>
       <c r="G205" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H205" s="18">
         <v>11</v>
@@ -11450,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M205" s="18">
         <v>0</v>
@@ -11483,7 +11501,7 @@
         <v>50</v>
       </c>
       <c r="G206" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H206" s="18">
         <v>12</v>
@@ -11498,7 +11516,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M206" s="18">
         <v>0</v>
@@ -11531,7 +11549,7 @@
         <v>52</v>
       </c>
       <c r="G207" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H207" s="18">
         <v>10</v>
@@ -11546,7 +11564,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M207" s="18">
         <v>0</v>
@@ -11579,7 +11597,7 @@
         <v>52</v>
       </c>
       <c r="G208" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H208" s="18">
         <v>11</v>
@@ -11594,7 +11612,7 @@
         <v>0</v>
       </c>
       <c r="L208" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M208" s="18">
         <v>0</v>
@@ -11627,7 +11645,7 @@
         <v>52</v>
       </c>
       <c r="G209" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H209" s="18">
         <v>12</v>
@@ -11642,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="L209" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M209" s="18">
         <v>0</v>
@@ -11675,7 +11693,7 @@
         <v>54</v>
       </c>
       <c r="G210" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H210" s="18">
         <v>10</v>
@@ -11690,7 +11708,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M210" s="18">
         <v>0</v>
@@ -11723,7 +11741,7 @@
         <v>54</v>
       </c>
       <c r="G211" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H211" s="18">
         <v>11</v>
@@ -11738,7 +11756,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M211" s="18">
         <v>0</v>
@@ -11771,7 +11789,7 @@
         <v>54</v>
       </c>
       <c r="G212" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H212" s="18">
         <v>12</v>
@@ -11786,7 +11804,7 @@
         <v>0</v>
       </c>
       <c r="L212" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M212" s="18">
         <v>0</v>
@@ -11819,7 +11837,7 @@
         <v>56</v>
       </c>
       <c r="G213" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H213" s="18">
         <v>10</v>
@@ -11834,7 +11852,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M213" s="18">
         <v>0</v>
@@ -11867,7 +11885,7 @@
         <v>56</v>
       </c>
       <c r="G214" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H214" s="18">
         <v>11</v>
@@ -11882,7 +11900,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M214" s="18">
         <v>0</v>
@@ -11915,7 +11933,7 @@
         <v>56</v>
       </c>
       <c r="G215" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H215" s="18">
         <v>12</v>
@@ -11930,7 +11948,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M215" s="18">
         <v>0</v>
@@ -11963,7 +11981,7 @@
         <v>58</v>
       </c>
       <c r="G216" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H216" s="18">
         <v>10</v>
@@ -11978,7 +11996,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M216" s="18">
         <v>0</v>
@@ -12011,7 +12029,7 @@
         <v>58</v>
       </c>
       <c r="G217" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H217" s="18">
         <v>11</v>
@@ -12026,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M217" s="18">
         <v>0</v>
@@ -12059,7 +12077,7 @@
         <v>58</v>
       </c>
       <c r="G218" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H218" s="18">
         <v>12</v>
@@ -12074,7 +12092,7 @@
         <v>0</v>
       </c>
       <c r="L218" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M218" s="18">
         <v>0</v>
@@ -12107,7 +12125,7 @@
         <v>60</v>
       </c>
       <c r="G219" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H219" s="1">
         <v>10</v>
@@ -12122,7 +12140,7 @@
         <v>0</v>
       </c>
       <c r="L219" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M219" s="18">
         <v>0</v>
@@ -12155,7 +12173,7 @@
         <v>60</v>
       </c>
       <c r="G220" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H220" s="1">
         <v>11</v>
@@ -12170,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M220" s="18">
         <v>0</v>
@@ -12203,7 +12221,7 @@
         <v>60</v>
       </c>
       <c r="G221" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H221" s="1">
         <v>12</v>
@@ -12218,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="L221" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M221" s="18">
         <v>0</v>
@@ -12251,7 +12269,7 @@
         <v>62</v>
       </c>
       <c r="G222" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H222" s="1">
         <v>10</v>
@@ -12266,7 +12284,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M222" s="18">
         <v>0</v>
@@ -12299,7 +12317,7 @@
         <v>62</v>
       </c>
       <c r="G223" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H223" s="1">
         <v>11</v>
@@ -12314,7 +12332,7 @@
         <v>0</v>
       </c>
       <c r="L223" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M223" s="18">
         <v>0</v>
@@ -12347,7 +12365,7 @@
         <v>62</v>
       </c>
       <c r="G224" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H224" s="1">
         <v>12</v>
@@ -12362,7 +12380,7 @@
         <v>0</v>
       </c>
       <c r="L224" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M224" s="18">
         <v>0</v>
@@ -12395,7 +12413,7 @@
         <v>64</v>
       </c>
       <c r="G225" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H225" s="1">
         <v>10</v>
@@ -12410,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M225" s="18">
         <v>0</v>
@@ -12443,7 +12461,7 @@
         <v>64</v>
       </c>
       <c r="G226" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H226" s="1">
         <v>11</v>
@@ -12458,7 +12476,7 @@
         <v>0</v>
       </c>
       <c r="L226" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M226" s="18">
         <v>0</v>
@@ -12491,7 +12509,7 @@
         <v>64</v>
       </c>
       <c r="G227" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H227" s="1">
         <v>12</v>
@@ -12506,7 +12524,7 @@
         <v>0</v>
       </c>
       <c r="L227" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M227" s="18">
         <v>0</v>
@@ -12539,7 +12557,7 @@
         <v>66</v>
       </c>
       <c r="G228" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H228" s="1">
         <v>10</v>
@@ -12554,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M228" s="18">
         <v>0</v>
@@ -12587,7 +12605,7 @@
         <v>66</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H229" s="1">
         <v>11</v>
@@ -12602,7 +12620,7 @@
         <v>0</v>
       </c>
       <c r="L229" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M229" s="18">
         <v>0</v>
@@ -12635,7 +12653,7 @@
         <v>66</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H230" s="1">
         <v>12</v>
@@ -12650,7 +12668,7 @@
         <v>0</v>
       </c>
       <c r="L230" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M230" s="18">
         <v>0</v>
@@ -12683,7 +12701,7 @@
         <v>68</v>
       </c>
       <c r="G231" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H231" s="1">
         <v>10</v>
@@ -12698,7 +12716,7 @@
         <v>0</v>
       </c>
       <c r="L231" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M231" s="18">
         <v>0</v>
@@ -12731,7 +12749,7 @@
         <v>68</v>
       </c>
       <c r="G232" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H232" s="1">
         <v>11</v>
@@ -12746,7 +12764,7 @@
         <v>0</v>
       </c>
       <c r="L232" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M232" s="18">
         <v>0</v>
@@ -12779,7 +12797,7 @@
         <v>68</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H233" s="1">
         <v>12</v>
@@ -12794,7 +12812,7 @@
         <v>0</v>
       </c>
       <c r="L233" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M233" s="18">
         <v>0</v>
@@ -12827,7 +12845,7 @@
         <v>70</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H234" s="1">
         <v>10</v>
@@ -12842,7 +12860,7 @@
         <v>0</v>
       </c>
       <c r="L234" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M234" s="18">
         <v>0</v>
@@ -12875,7 +12893,7 @@
         <v>70</v>
       </c>
       <c r="G235" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H235" s="1">
         <v>11</v>
@@ -12890,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="L235" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M235" s="18">
         <v>0</v>
@@ -12923,7 +12941,7 @@
         <v>70</v>
       </c>
       <c r="G236" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H236" s="1">
         <v>12</v>
@@ -12938,7 +12956,7 @@
         <v>0</v>
       </c>
       <c r="L236" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M236" s="18">
         <v>0</v>
@@ -12970,7 +12988,7 @@
         <v>72</v>
       </c>
       <c r="G237" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H237" s="1">
         <v>10</v>
@@ -12985,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="L237" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M237" s="18">
         <v>0</v>
@@ -13017,7 +13035,7 @@
         <v>72</v>
       </c>
       <c r="G238" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H238" s="1">
         <v>11</v>
@@ -13032,7 +13050,7 @@
         <v>0</v>
       </c>
       <c r="L238" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M238" s="18">
         <v>0</v>
@@ -13064,7 +13082,7 @@
         <v>72</v>
       </c>
       <c r="G239" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H239" s="1">
         <v>12</v>
@@ -13079,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="L239" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M239" s="18">
         <v>0</v>
@@ -13111,7 +13129,7 @@
         <v>74</v>
       </c>
       <c r="G240" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H240" s="1">
         <v>10</v>
@@ -13126,7 +13144,7 @@
         <v>0</v>
       </c>
       <c r="L240" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M240" s="18">
         <v>0</v>
@@ -13158,7 +13176,7 @@
         <v>74</v>
       </c>
       <c r="G241" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H241" s="1">
         <v>11</v>
@@ -13173,7 +13191,7 @@
         <v>0</v>
       </c>
       <c r="L241" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M241" s="18">
         <v>0</v>
@@ -13205,7 +13223,7 @@
         <v>74</v>
       </c>
       <c r="G242" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H242" s="1">
         <v>12</v>
@@ -13220,7 +13238,7 @@
         <v>0</v>
       </c>
       <c r="L242" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M242" s="18">
         <v>0</v>
@@ -13252,7 +13270,7 @@
         <v>76</v>
       </c>
       <c r="G243" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H243" s="1">
         <v>10</v>
@@ -13267,7 +13285,7 @@
         <v>0</v>
       </c>
       <c r="L243" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M243" s="18">
         <v>0</v>
@@ -13300,7 +13318,7 @@
         <v>76</v>
       </c>
       <c r="G244" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H244" s="1">
         <v>11</v>
@@ -13315,7 +13333,7 @@
         <v>0</v>
       </c>
       <c r="L244" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M244" s="18">
         <v>0</v>
@@ -13348,7 +13366,7 @@
         <v>76</v>
       </c>
       <c r="G245" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H245" s="1">
         <v>12</v>
@@ -13363,7 +13381,7 @@
         <v>0</v>
       </c>
       <c r="L245" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M245" s="18">
         <v>0</v>
@@ -13396,7 +13414,7 @@
         <v>111</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H246" s="1">
         <v>10</v>
@@ -13411,7 +13429,7 @@
         <v>0</v>
       </c>
       <c r="L246" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M246" s="18">
         <v>0</v>
@@ -13443,7 +13461,7 @@
         <v>111</v>
       </c>
       <c r="G247" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H247" s="1">
         <v>11</v>
@@ -13458,7 +13476,7 @@
         <v>0</v>
       </c>
       <c r="L247" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M247" s="18">
         <v>0</v>
@@ -13490,7 +13508,7 @@
         <v>111</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H248" s="1">
         <v>12</v>
@@ -13505,7 +13523,7 @@
         <v>0</v>
       </c>
       <c r="L248" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M248" s="18">
         <v>0</v>
@@ -13537,7 +13555,7 @@
         <v>113</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H249" s="1">
         <v>10</v>
@@ -13552,7 +13570,7 @@
         <v>0</v>
       </c>
       <c r="L249" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M249" s="18">
         <v>0</v>
@@ -13584,7 +13602,7 @@
         <v>113</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H250" s="1">
         <v>11</v>
@@ -13599,7 +13617,7 @@
         <v>0</v>
       </c>
       <c r="L250" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M250" s="18">
         <v>0</v>
@@ -13631,7 +13649,7 @@
         <v>113</v>
       </c>
       <c r="G251" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H251" s="1">
         <v>12</v>
@@ -13646,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="L251" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M251" s="18">
         <v>0</v>
@@ -13678,7 +13696,7 @@
         <v>115</v>
       </c>
       <c r="G252" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H252" s="1">
         <v>10</v>
@@ -13693,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="L252" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M252" s="18">
         <v>0</v>
@@ -13725,7 +13743,7 @@
         <v>115</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H253" s="1">
         <v>11</v>
@@ -13740,7 +13758,7 @@
         <v>0</v>
       </c>
       <c r="L253" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M253" s="18">
         <v>0</v>
@@ -13772,7 +13790,7 @@
         <v>115</v>
       </c>
       <c r="G254" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H254" s="1">
         <v>12</v>
@@ -13787,7 +13805,7 @@
         <v>0</v>
       </c>
       <c r="L254" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M254" s="18">
         <v>0</v>
@@ -13819,7 +13837,7 @@
         <v>117</v>
       </c>
       <c r="G255" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H255" s="1">
         <v>10</v>
@@ -13834,7 +13852,7 @@
         <v>0</v>
       </c>
       <c r="L255" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M255" s="18">
         <v>0</v>
@@ -13866,7 +13884,7 @@
         <v>117</v>
       </c>
       <c r="G256" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H256" s="1">
         <v>11</v>
@@ -13881,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L256" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M256" s="18">
         <v>0</v>
@@ -13913,7 +13931,7 @@
         <v>117</v>
       </c>
       <c r="G257" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H257" s="1">
         <v>12</v>
@@ -13928,7 +13946,7 @@
         <v>0</v>
       </c>
       <c r="L257" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M257" s="18">
         <v>0</v>
@@ -13960,7 +13978,7 @@
         <v>119</v>
       </c>
       <c r="G258" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H258" s="1">
         <v>10</v>
@@ -13975,7 +13993,7 @@
         <v>0</v>
       </c>
       <c r="L258" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M258" s="18">
         <v>0</v>
@@ -14007,7 +14025,7 @@
         <v>119</v>
       </c>
       <c r="G259" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H259" s="1">
         <v>11</v>
@@ -14022,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="L259" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M259" s="18">
         <v>0</v>
@@ -14054,7 +14072,7 @@
         <v>119</v>
       </c>
       <c r="G260" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H260" s="1">
         <v>12</v>
@@ -14069,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="L260" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M260" s="18">
         <v>0</v>
@@ -14101,7 +14119,7 @@
         <v>121</v>
       </c>
       <c r="G261" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H261" s="1">
         <v>10</v>
@@ -14116,7 +14134,7 @@
         <v>0</v>
       </c>
       <c r="L261" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M261" s="18">
         <v>0</v>
@@ -14148,7 +14166,7 @@
         <v>121</v>
       </c>
       <c r="G262" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H262" s="1">
         <v>11</v>
@@ -14163,7 +14181,7 @@
         <v>0</v>
       </c>
       <c r="L262" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M262" s="18">
         <v>0</v>
@@ -14195,7 +14213,7 @@
         <v>121</v>
       </c>
       <c r="G263" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H263" s="1">
         <v>12</v>
@@ -14210,7 +14228,7 @@
         <v>0</v>
       </c>
       <c r="L263" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M263" s="18">
         <v>0</v>
@@ -14242,7 +14260,7 @@
         <v>123</v>
       </c>
       <c r="G264" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H264" s="1">
         <v>10</v>
@@ -14257,7 +14275,7 @@
         <v>0</v>
       </c>
       <c r="L264" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M264" s="18">
         <v>0</v>
@@ -14289,7 +14307,7 @@
         <v>123</v>
       </c>
       <c r="G265" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H265" s="1">
         <v>11</v>
@@ -14304,7 +14322,7 @@
         <v>0</v>
       </c>
       <c r="L265" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M265" s="18">
         <v>0</v>
@@ -14336,7 +14354,7 @@
         <v>123</v>
       </c>
       <c r="G266" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H266" s="1">
         <v>12</v>
@@ -14351,7 +14369,7 @@
         <v>0</v>
       </c>
       <c r="L266" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M266" s="18">
         <v>0</v>
@@ -14383,7 +14401,7 @@
         <v>125</v>
       </c>
       <c r="G267" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H267" s="2">
         <v>10</v>
@@ -14398,7 +14416,7 @@
         <v>0</v>
       </c>
       <c r="L267" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M267" s="30">
         <v>0</v>
@@ -14434,7 +14452,7 @@
         <v>125</v>
       </c>
       <c r="G268" s="30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H268" s="2">
         <v>11</v>
@@ -14449,7 +14467,7 @@
         <v>0</v>
       </c>
       <c r="L268" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M268" s="30">
         <v>0</v>
@@ -14485,7 +14503,7 @@
         <v>125</v>
       </c>
       <c r="G269" s="30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H269" s="2">
         <v>12</v>
@@ -14500,7 +14518,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M269" s="30">
         <v>0</v>
@@ -14532,9 +14550,11 @@
       <c r="E270" s="2">
         <v>105501001</v>
       </c>
-      <c r="F270" s="2"/>
+      <c r="F270" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G270" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H270" s="2">
         <v>10</v>
@@ -14549,7 +14569,7 @@
         <v>0</v>
       </c>
       <c r="L270" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M270" s="30">
         <v>0</v>
@@ -14581,9 +14601,11 @@
       <c r="E271" s="2">
         <v>105501001</v>
       </c>
-      <c r="F271" s="2"/>
+      <c r="F271" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G271" s="30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H271" s="2">
         <v>11</v>
@@ -14598,7 +14620,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M271" s="30">
         <v>0</v>
@@ -14630,9 +14652,11 @@
       <c r="E272" s="2">
         <v>105501001</v>
       </c>
-      <c r="F272" s="2"/>
+      <c r="F272" s="22" t="s">
+        <v>127</v>
+      </c>
       <c r="G272" s="30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H272" s="2">
         <v>12</v>
@@ -14647,7 +14671,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M272" s="30">
         <v>0</v>
@@ -14674,14 +14698,16 @@
         <v>1</v>
       </c>
       <c r="D273" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E273" s="2">
         <v>105502001</v>
       </c>
-      <c r="F273" s="2"/>
+      <c r="F273" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G273" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H273" s="2">
         <v>10</v>
@@ -14696,7 +14722,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M273" s="30">
         <v>0</v>
@@ -14723,14 +14749,16 @@
         <v>1</v>
       </c>
       <c r="D274" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E274" s="2">
         <v>105502001</v>
       </c>
-      <c r="F274" s="2"/>
+      <c r="F274" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G274" s="30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H274" s="2">
         <v>11</v>
@@ -14745,7 +14773,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M274" s="30">
         <v>0</v>
@@ -14772,14 +14800,16 @@
         <v>1</v>
       </c>
       <c r="D275" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E275" s="2">
         <v>105502001</v>
       </c>
-      <c r="F275" s="2"/>
+      <c r="F275" s="22" t="s">
+        <v>129</v>
+      </c>
       <c r="G275" s="30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H275" s="2">
         <v>12</v>
@@ -14794,7 +14824,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M275" s="30">
         <v>0</v>
@@ -14830,7 +14860,7 @@
         <v>31</v>
       </c>
       <c r="G276" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H276" s="1">
         <v>21</v>
@@ -14878,7 +14908,7 @@
         <v>31</v>
       </c>
       <c r="G277" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H277" s="1">
         <v>22</v>
@@ -14926,7 +14956,7 @@
         <v>31</v>
       </c>
       <c r="G278" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H278" s="1">
         <v>23</v>
@@ -14974,7 +15004,7 @@
         <v>38</v>
       </c>
       <c r="G279" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H279" s="1">
         <v>21</v>
@@ -15022,7 +15052,7 @@
         <v>38</v>
       </c>
       <c r="G280" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H280" s="1">
         <v>22</v>
@@ -15070,7 +15100,7 @@
         <v>38</v>
       </c>
       <c r="G281" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H281" s="1">
         <v>23</v>
@@ -15118,7 +15148,7 @@
         <v>40</v>
       </c>
       <c r="G282" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H282" s="1">
         <v>21</v>
@@ -15166,7 +15196,7 @@
         <v>40</v>
       </c>
       <c r="G283" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H283" s="1">
         <v>22</v>
@@ -15214,7 +15244,7 @@
         <v>40</v>
       </c>
       <c r="G284" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H284" s="1">
         <v>23</v>
@@ -15262,7 +15292,7 @@
         <v>42</v>
       </c>
       <c r="G285" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H285" s="1">
         <v>21</v>
@@ -15310,7 +15340,7 @@
         <v>42</v>
       </c>
       <c r="G286" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H286" s="1">
         <v>22</v>
@@ -15358,7 +15388,7 @@
         <v>42</v>
       </c>
       <c r="G287" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H287" s="1">
         <v>23</v>
@@ -15406,7 +15436,7 @@
         <v>44</v>
       </c>
       <c r="G288" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H288" s="1">
         <v>21</v>
@@ -15454,7 +15484,7 @@
         <v>44</v>
       </c>
       <c r="G289" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H289" s="1">
         <v>22</v>
@@ -15502,7 +15532,7 @@
         <v>44</v>
       </c>
       <c r="G290" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H290" s="1">
         <v>23</v>
@@ -15550,7 +15580,7 @@
         <v>46</v>
       </c>
       <c r="G291" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H291" s="1">
         <v>21</v>
@@ -15598,7 +15628,7 @@
         <v>46</v>
       </c>
       <c r="G292" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H292" s="1">
         <v>22</v>
@@ -15646,7 +15676,7 @@
         <v>46</v>
       </c>
       <c r="G293" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H293" s="1">
         <v>23</v>
@@ -15694,7 +15724,7 @@
         <v>48</v>
       </c>
       <c r="G294" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H294" s="1">
         <v>21</v>
@@ -15742,7 +15772,7 @@
         <v>48</v>
       </c>
       <c r="G295" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H295" s="1">
         <v>22</v>
@@ -15790,7 +15820,7 @@
         <v>48</v>
       </c>
       <c r="G296" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H296" s="1">
         <v>23</v>
@@ -15838,7 +15868,7 @@
         <v>50</v>
       </c>
       <c r="G297" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H297" s="1">
         <v>21</v>
@@ -15886,7 +15916,7 @@
         <v>50</v>
       </c>
       <c r="G298" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H298" s="1">
         <v>22</v>
@@ -15934,7 +15964,7 @@
         <v>50</v>
       </c>
       <c r="G299" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H299" s="1">
         <v>23</v>
@@ -15982,7 +16012,7 @@
         <v>52</v>
       </c>
       <c r="G300" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H300" s="1">
         <v>21</v>
@@ -16030,7 +16060,7 @@
         <v>52</v>
       </c>
       <c r="G301" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H301" s="1">
         <v>22</v>
@@ -16078,7 +16108,7 @@
         <v>52</v>
       </c>
       <c r="G302" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H302" s="1">
         <v>23</v>
@@ -16127,7 +16157,7 @@
         <v>54</v>
       </c>
       <c r="G303" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H303" s="1">
         <v>21</v>
@@ -16176,7 +16206,7 @@
         <v>54</v>
       </c>
       <c r="G304" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H304" s="1">
         <v>22</v>
@@ -16225,7 +16255,7 @@
         <v>54</v>
       </c>
       <c r="G305" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H305" s="1">
         <v>23</v>
@@ -16274,7 +16304,7 @@
         <v>56</v>
       </c>
       <c r="G306" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H306" s="1">
         <v>21</v>
@@ -16323,7 +16353,7 @@
         <v>56</v>
       </c>
       <c r="G307" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H307" s="1">
         <v>22</v>
@@ -16372,7 +16402,7 @@
         <v>56</v>
       </c>
       <c r="G308" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H308" s="1">
         <v>23</v>
@@ -16421,7 +16451,7 @@
         <v>58</v>
       </c>
       <c r="G309" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H309" s="1">
         <v>21</v>
@@ -16470,7 +16500,7 @@
         <v>58</v>
       </c>
       <c r="G310" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H310" s="1">
         <v>22</v>
@@ -16519,7 +16549,7 @@
         <v>58</v>
       </c>
       <c r="G311" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H311" s="1">
         <v>23</v>
@@ -16567,7 +16597,7 @@
         <v>60</v>
       </c>
       <c r="G312" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H312" s="1">
         <v>21</v>
@@ -16615,7 +16645,7 @@
         <v>60</v>
       </c>
       <c r="G313" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H313" s="1">
         <v>22</v>
@@ -16663,7 +16693,7 @@
         <v>60</v>
       </c>
       <c r="G314" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H314" s="1">
         <v>23</v>
@@ -16712,7 +16742,7 @@
         <v>62</v>
       </c>
       <c r="G315" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H315" s="1">
         <v>21</v>
@@ -16761,7 +16791,7 @@
         <v>62</v>
       </c>
       <c r="G316" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H316" s="1">
         <v>22</v>
@@ -16810,7 +16840,7 @@
         <v>62</v>
       </c>
       <c r="G317" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H317" s="1">
         <v>23</v>
@@ -16858,7 +16888,7 @@
         <v>64</v>
       </c>
       <c r="G318" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H318" s="1">
         <v>21</v>
@@ -16906,7 +16936,7 @@
         <v>64</v>
       </c>
       <c r="G319" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H319" s="1">
         <v>22</v>
@@ -16954,7 +16984,7 @@
         <v>64</v>
       </c>
       <c r="G320" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H320" s="1">
         <v>23</v>
@@ -17002,7 +17032,7 @@
         <v>66</v>
       </c>
       <c r="G321" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H321" s="1">
         <v>21</v>
@@ -17050,7 +17080,7 @@
         <v>66</v>
       </c>
       <c r="G322" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H322" s="1">
         <v>22</v>
@@ -17098,7 +17128,7 @@
         <v>66</v>
       </c>
       <c r="G323" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H323" s="1">
         <v>23</v>
@@ -17147,7 +17177,7 @@
         <v>68</v>
       </c>
       <c r="G324" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H324" s="1">
         <v>21</v>
@@ -17196,7 +17226,7 @@
         <v>68</v>
       </c>
       <c r="G325" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H325" s="1">
         <v>22</v>
@@ -17245,7 +17275,7 @@
         <v>68</v>
       </c>
       <c r="G326" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H326" s="1">
         <v>23</v>
@@ -17293,7 +17323,7 @@
         <v>72</v>
       </c>
       <c r="G327" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H327" s="1">
         <v>21</v>
@@ -17341,7 +17371,7 @@
         <v>72</v>
       </c>
       <c r="G328" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H328" s="1">
         <v>22</v>
@@ -17389,7 +17419,7 @@
         <v>72</v>
       </c>
       <c r="G329" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H329" s="1">
         <v>23</v>
@@ -17437,7 +17467,7 @@
         <v>74</v>
       </c>
       <c r="G330" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H330" s="1">
         <v>21</v>
@@ -17485,7 +17515,7 @@
         <v>74</v>
       </c>
       <c r="G331" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H331" s="1">
         <v>22</v>
@@ -17533,7 +17563,7 @@
         <v>74</v>
       </c>
       <c r="G332" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H332" s="1">
         <v>23</v>
@@ -17581,7 +17611,7 @@
         <v>76</v>
       </c>
       <c r="G333" s="32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H333" s="1">
         <v>21</v>
@@ -17629,7 +17659,7 @@
         <v>76</v>
       </c>
       <c r="G334" s="32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H334" s="1">
         <v>22</v>
@@ -17677,7 +17707,7 @@
         <v>76</v>
       </c>
       <c r="G335" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H335" s="1">
         <v>23</v>
@@ -19181,13 +19211,13 @@
         <v>3</v>
       </c>
       <c r="D366" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E366" s="14">
         <v>300402001</v>
       </c>
       <c r="F366" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>32</v>
@@ -19230,13 +19260,13 @@
         <v>3</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E367" s="14">
         <v>300402001</v>
       </c>
       <c r="F367" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>35</v>
@@ -19279,13 +19309,13 @@
         <v>3</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E368" s="14">
         <v>300402001</v>
       </c>
       <c r="F368" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>36</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -13129,7 +13129,7 @@
         <v>71</v>
       </c>
       <c r="E240" s="14">
-        <v>103401001</v>
+        <v>103400001</v>
       </c>
       <c r="F240" s="14" t="s">
         <v>72</v>
@@ -13176,7 +13176,7 @@
         <v>71</v>
       </c>
       <c r="E241" s="14">
-        <v>103401001</v>
+        <v>103400001</v>
       </c>
       <c r="F241" s="14" t="s">
         <v>72</v>
@@ -13223,7 +13223,7 @@
         <v>71</v>
       </c>
       <c r="E242" s="14">
-        <v>103401001</v>
+        <v>103400001</v>
       </c>
       <c r="F242" s="14" t="s">
         <v>72</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -833,12 +833,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -8714,7 +8714,7 @@
         <v>100</v>
       </c>
       <c r="O147" s="16">
-        <v>1960000</v>
+        <v>1990000</v>
       </c>
       <c r="S147" s="3"/>
     </row>
@@ -8762,7 +8762,7 @@
         <v>1000</v>
       </c>
       <c r="O148" s="16">
-        <v>1960000</v>
+        <v>1990000</v>
       </c>
       <c r="S148" s="3"/>
     </row>
@@ -8810,7 +8810,7 @@
         <v>10000</v>
       </c>
       <c r="O149" s="16">
-        <v>1960000</v>
+        <v>1990000</v>
       </c>
       <c r="S149" s="3"/>
     </row>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -833,12 +833,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -8696,10 +8696,10 @@
         <v>1</v>
       </c>
       <c r="I147" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J147" s="1">
-        <v>200000</v>
+        <v>-1</v>
       </c>
       <c r="K147" s="1">
         <v>0</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -8696,7 +8701,7 @@
         <v>1</v>
       </c>
       <c r="I147" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J147" s="1">
         <v>-1</v>
@@ -8714,7 +8719,7 @@
         <v>100</v>
       </c>
       <c r="O147" s="16">
-        <v>1990000</v>
+        <v>1960000</v>
       </c>
       <c r="S147" s="3"/>
     </row>
@@ -8762,7 +8767,7 @@
         <v>1000</v>
       </c>
       <c r="O148" s="16">
-        <v>1990000</v>
+        <v>1960000</v>
       </c>
       <c r="S148" s="3"/>
     </row>
@@ -8810,7 +8815,7 @@
         <v>10000</v>
       </c>
       <c r="O149" s="16">
-        <v>1990000</v>
+        <v>1960000</v>
       </c>
       <c r="S149" s="3"/>
     </row>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -520,7 +520,7 @@
     <t>狼月</t>
   </si>
   <si>
-    <t>Wolfmoon</t>
+    <t>WolfMoon</t>
   </si>
   <si>
     <t>麻将胡了2</t>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -8683,7 +8683,7 @@
     </row>
     <row r="147" s="1" customFormat="1" spans="1:19">
       <c r="A147" s="2">
-        <v>4008004</v>
+        <v>4008001</v>
       </c>
       <c r="B147" s="2">
         <v>400800</v>
